--- a/CIFAR_Global.xlsx
+++ b/CIFAR_Global.xlsx
@@ -1,41 +1,81 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashleyau/Documents/PhD/Practical_Experiment/Finalised/Finalised_Algorithm_ResNet/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{491F8CC9-D909-134A-9168-6C8CFA6AF6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="34560" windowHeight="19980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-41520" yWindow="-1660" windowWidth="34560" windowHeight="19980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="181029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+  <si>
+    <t>100 Rounds</t>
+  </si>
+  <si>
+    <t>IID</t>
+  </si>
+  <si>
+    <t>Global Accuracy</t>
+  </si>
+  <si>
+    <t>Round</t>
+  </si>
+  <si>
+    <t>Clustering Accuracy</t>
+  </si>
+  <si>
+    <t>Round number</t>
+  </si>
+  <si>
+    <t>Poisoning Accuracy</t>
+  </si>
+  <si>
+    <t>Global Poisoning Accuracy</t>
+  </si>
+  <si>
+    <t>5 rounds</t>
+  </si>
+  <si>
+    <t>Actual</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -54,87 +94,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -454,2144 +435,2126 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B415"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C415"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="15.1640625" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>100 Rounds</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>IID</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Global Accuracy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Round</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" t="n">
-        <v>0.1078</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B6" t="n">
-        <v>0.4665</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B7" t="n">
-        <v>0.644</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>0.10780000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>0.46650000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>0.64400000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" t="n">
-        <v>0.6624</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="B8">
+        <v>0.66239999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
         <v>5</v>
       </c>
-      <c r="B9" t="n">
-        <v>0.7010999999999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="B9">
+        <v>0.70109999999999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
         <v>36</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
         <v>37</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
         <v>39</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
         <v>43</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
         <v>44</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
         <v>45</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
         <v>46</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
         <v>47</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
         <v>48</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
         <v>49</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
         <v>51</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
         <v>52</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="1" t="n">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
         <v>53</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="1" t="n">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
         <v>54</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
         <v>56</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
         <v>57</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="1" t="n">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
         <v>58</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="1" t="n">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
         <v>59</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="1" t="n">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="1" t="n">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
         <v>61</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="1" t="n">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
         <v>62</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="1" t="n">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
         <v>63</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="1" t="n">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
         <v>64</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="1" t="n">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
         <v>65</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="1" t="n">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
         <v>66</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="1" t="n">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
         <v>67</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="1" t="n">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
         <v>68</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="1" t="n">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
         <v>69</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="1" t="n">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
         <v>70</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="1" t="n">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
         <v>71</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="1" t="n">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
         <v>72</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="1" t="n">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
         <v>73</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="1" t="n">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
         <v>74</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="1" t="n">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="1" t="n">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
         <v>76</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="1" t="n">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
         <v>77</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="1" t="n">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
         <v>78</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="1" t="n">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
         <v>79</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="1" t="n">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="1" t="n">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
         <v>81</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="1" t="n">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
         <v>82</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="1" t="n">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A87" s="1">
         <v>83</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="1" t="n">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A88" s="1">
         <v>84</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="1" t="n">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A89" s="1">
         <v>85</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="1" t="n">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A90" s="1">
         <v>86</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="1" t="n">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A91" s="1">
         <v>87</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="1" t="n">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A92" s="1">
         <v>88</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="1" t="n">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A93" s="1">
         <v>89</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="1" t="n">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A94" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="1" t="n">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A95" s="1">
         <v>91</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="1" t="n">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A96" s="1">
         <v>92</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="1" t="n">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" s="1">
         <v>93</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="1" t="n">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" s="1">
         <v>94</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="1" t="n">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" s="1">
         <v>95</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="1" t="n">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" s="1">
         <v>96</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="1" t="n">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" s="1">
         <v>97</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="1" t="n">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" s="1">
         <v>98</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="1" t="n">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" s="1">
         <v>99</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="1" t="n">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="1" t="inlineStr">
-        <is>
-          <t>Clustering Accuracy</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>Round number</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="1" t="n">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108" s="1">
         <v>1</v>
       </c>
-      <c r="B108" t="n">
+      <c r="B108">
         <v>1</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="1" t="n">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" s="1">
         <v>2</v>
       </c>
-      <c r="B109" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="B109">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110" s="1">
         <v>3</v>
       </c>
-      <c r="B110" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="B110">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111" s="1">
         <v>4</v>
       </c>
-      <c r="B111" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="B111">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112" s="1">
         <v>5</v>
       </c>
-      <c r="B112" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="B112">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A113" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="1" t="n">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A114" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="1" t="n">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A115" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="1" t="n">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A116" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="1" t="n">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A117" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="1" t="n">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A118" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="1" t="n">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A119" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="1" t="n">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A120" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="1" t="n">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A121" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="1" t="n">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A122" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="1" t="n">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A123" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="1" t="n">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A124" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="1" t="n">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A125" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="1" t="n">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A126" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="1" t="n">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A127" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="1" t="n">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A128" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="1" t="n">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A129" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="1" t="n">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A130" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="1" t="n">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A131" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="1" t="n">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A132" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="1" t="n">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A133" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="1" t="n">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A134" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="1" t="n">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A135" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="1" t="n">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A136" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="1" t="n">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A137" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="1" t="n">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A138" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="1" t="n">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A139" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="1" t="n">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A140" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="1" t="n">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A141" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="1" t="n">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A142" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="1" t="n">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
         <v>36</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="1" t="n">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
         <v>37</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="1" t="n">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="1" t="n">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
         <v>39</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="1" t="n">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="1" t="n">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A148" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="1" t="n">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A149" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="1" t="n">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A150" s="1">
         <v>43</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="1" t="n">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A151" s="1">
         <v>44</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="1" t="n">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A152" s="1">
         <v>45</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="1" t="n">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A153" s="1">
         <v>46</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="1" t="n">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A154" s="1">
         <v>47</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="1" t="n">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A155" s="1">
         <v>48</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="1" t="n">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A156" s="1">
         <v>49</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="1" t="n">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A157" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="1" t="n">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A158" s="1">
         <v>51</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="1" t="n">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A159" s="1">
         <v>52</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="1" t="n">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A160" s="1">
         <v>53</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="1" t="n">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A161" s="1">
         <v>54</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="1" t="n">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A162" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="1" t="n">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A163" s="1">
         <v>56</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="1" t="n">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A164" s="1">
         <v>57</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="1" t="n">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A165" s="1">
         <v>58</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="1" t="n">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A166" s="1">
         <v>59</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="1" t="n">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A167" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="1" t="n">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A168" s="1">
         <v>61</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="1" t="n">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A169" s="1">
         <v>62</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="1" t="n">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A170" s="1">
         <v>63</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="1" t="n">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A171" s="1">
         <v>64</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="1" t="n">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A172" s="1">
         <v>65</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="1" t="n">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A173" s="1">
         <v>66</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="1" t="n">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A174" s="1">
         <v>67</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="1" t="n">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A175" s="1">
         <v>68</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="1" t="n">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A176" s="1">
         <v>69</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="1" t="n">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A177" s="1">
         <v>70</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="1" t="n">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A178" s="1">
         <v>71</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="1" t="n">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A179" s="1">
         <v>72</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="1" t="n">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A180" s="1">
         <v>73</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="1" t="n">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A181" s="1">
         <v>74</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="1" t="n">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A182" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="1" t="n">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A183" s="1">
         <v>76</v>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="1" t="n">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A184" s="1">
         <v>77</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="1" t="n">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A185" s="1">
         <v>78</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="1" t="n">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A186" s="1">
         <v>79</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="1" t="n">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A187" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="1" t="n">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A188" s="1">
         <v>81</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="1" t="n">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A189" s="1">
         <v>82</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="1" t="n">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A190" s="1">
         <v>83</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="1" t="n">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A191" s="1">
         <v>84</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="1" t="n">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A192" s="1">
         <v>85</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="1" t="n">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A193" s="1">
         <v>86</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="1" t="n">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A194" s="1">
         <v>87</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="1" t="n">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A195" s="1">
         <v>88</v>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="1" t="n">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A196" s="1">
         <v>89</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="1" t="n">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A197" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="1" t="n">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A198" s="1">
         <v>91</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="1" t="n">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A199" s="1">
         <v>92</v>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="1" t="n">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A200" s="1">
         <v>93</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="1" t="n">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A201" s="1">
         <v>94</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="1" t="n">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A202" s="1">
         <v>95</v>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="1" t="n">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A203" s="1">
         <v>96</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="1" t="n">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A204" s="1">
         <v>97</v>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="1" t="n">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A205" s="1">
         <v>98</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="1" t="n">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A206" s="1">
         <v>99</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="1" t="n">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A207" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="1" t="inlineStr">
-        <is>
-          <t>Poisoning Accuracy</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="3" t="inlineStr">
-        <is>
-          <t>Round number</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="1" t="n">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A210" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A211" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A212" s="1">
         <v>1</v>
       </c>
-      <c r="B212" t="n">
-        <v>0.99725</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="B212">
+        <v>0.99724999999999997</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A213" s="1">
         <v>2</v>
       </c>
-      <c r="B213" t="n">
-        <v>0.99065</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="B213">
+        <v>0.99065000000000003</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A214" s="1">
         <v>3</v>
       </c>
-      <c r="B214" t="n">
+      <c r="B214">
         <v>0.9869</v>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="1" t="n">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A215" s="1">
         <v>4</v>
       </c>
-      <c r="B215" t="n">
-        <v>0.97765</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="B215">
+        <v>0.97765000000000002</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A216" s="1">
         <v>5</v>
       </c>
-      <c r="B216" t="n">
-        <v>0.9846</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="B216">
+        <v>0.98460000000000003</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A217" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="1" t="n">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A218" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="1" t="n">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A219" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="1" t="n">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A220" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="1" t="n">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A221" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="1" t="n">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A222" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="1" t="n">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A223" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="1" t="n">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A224" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="1" t="n">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A225" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="1" t="n">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A226" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="1" t="n">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A227" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="1" t="n">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A228" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="1" t="n">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A229" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="1" t="n">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A230" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="1" t="n">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A231" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="1" t="n">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A232" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="1" t="n">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A233" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="1" t="n">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A234" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="1" t="n">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A235" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="1" t="n">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A236" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="1" t="n">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A237" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="1" t="n">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A238" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="1" t="n">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A239" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="1" t="n">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A240" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="1" t="n">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A241" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="1" t="n">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A242" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="1" t="n">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A243" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="1" t="n">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A244" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="1" t="n">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A245" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="1" t="n">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A246" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="1" t="n">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A247" s="1">
         <v>36</v>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="1" t="n">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A248" s="1">
         <v>37</v>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="1" t="n">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A249" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="1" t="n">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A250" s="1">
         <v>39</v>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="1" t="n">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A251" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="1" t="n">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A252" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A253" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="1" t="n">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A254" s="1">
         <v>43</v>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="1" t="n">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A255" s="1">
         <v>44</v>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="1" t="n">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A256" s="1">
         <v>45</v>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="1" t="n">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A257" s="1">
         <v>46</v>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="1" t="n">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A258" s="1">
         <v>47</v>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="1" t="n">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A259" s="1">
         <v>48</v>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="1" t="n">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A260" s="1">
         <v>49</v>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" s="1" t="n">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A261" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="1" t="n">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A262" s="1">
         <v>51</v>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" s="1" t="n">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A263" s="1">
         <v>52</v>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" s="1" t="n">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A264" s="1">
         <v>53</v>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" s="1" t="n">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A265" s="1">
         <v>54</v>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" s="1" t="n">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A266" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" s="1" t="n">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A267" s="1">
         <v>56</v>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" s="1" t="n">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A268" s="1">
         <v>57</v>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" s="1" t="n">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A269" s="1">
         <v>58</v>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" s="1" t="n">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A270" s="1">
         <v>59</v>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" s="1" t="n">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A271" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" s="1" t="n">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A272" s="1">
         <v>61</v>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="1" t="n">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A273" s="1">
         <v>62</v>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="1" t="n">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A274" s="1">
         <v>63</v>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" s="1" t="n">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A275" s="1">
         <v>64</v>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" s="1" t="n">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A276" s="1">
         <v>65</v>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" s="1" t="n">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A277" s="1">
         <v>66</v>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" s="1" t="n">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A278" s="1">
         <v>67</v>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" s="1" t="n">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A279" s="1">
         <v>68</v>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" s="1" t="n">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A280" s="1">
         <v>69</v>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" s="1" t="n">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A281" s="1">
         <v>70</v>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" s="1" t="n">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A282" s="1">
         <v>71</v>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" s="1" t="n">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A283" s="1">
         <v>72</v>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" s="1" t="n">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A284" s="1">
         <v>73</v>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" s="1" t="n">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A285" s="1">
         <v>74</v>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" s="1" t="n">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A286" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" s="1" t="n">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A287" s="1">
         <v>76</v>
       </c>
     </row>
-    <row r="288">
-      <c r="A288" s="1" t="n">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A288" s="1">
         <v>77</v>
       </c>
     </row>
-    <row r="289">
-      <c r="A289" s="1" t="n">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A289" s="1">
         <v>78</v>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" s="1" t="n">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A290" s="1">
         <v>79</v>
       </c>
     </row>
-    <row r="291">
-      <c r="A291" s="1" t="n">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A291" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="292">
-      <c r="A292" s="1" t="n">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A292" s="1">
         <v>81</v>
       </c>
     </row>
-    <row r="293">
-      <c r="A293" s="1" t="n">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A293" s="1">
         <v>82</v>
       </c>
     </row>
-    <row r="294">
-      <c r="A294" s="1" t="n">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A294" s="1">
         <v>83</v>
       </c>
     </row>
-    <row r="295">
-      <c r="A295" s="1" t="n">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A295" s="1">
         <v>84</v>
       </c>
     </row>
-    <row r="296">
-      <c r="A296" s="1" t="n">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A296" s="1">
         <v>85</v>
       </c>
     </row>
-    <row r="297">
-      <c r="A297" s="1" t="n">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A297" s="1">
         <v>86</v>
       </c>
     </row>
-    <row r="298">
-      <c r="A298" s="1" t="n">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A298" s="1">
         <v>87</v>
       </c>
     </row>
-    <row r="299">
-      <c r="A299" s="1" t="n">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A299" s="1">
         <v>88</v>
       </c>
     </row>
-    <row r="300">
-      <c r="A300" s="1" t="n">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A300" s="1">
         <v>89</v>
       </c>
     </row>
-    <row r="301">
-      <c r="A301" s="1" t="n">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A301" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" s="1" t="n">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A302" s="1">
         <v>91</v>
       </c>
     </row>
-    <row r="303">
-      <c r="A303" s="1" t="n">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A303" s="1">
         <v>92</v>
       </c>
     </row>
-    <row r="304">
-      <c r="A304" s="1" t="n">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A304" s="1">
         <v>93</v>
       </c>
     </row>
-    <row r="305">
-      <c r="A305" s="1" t="n">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A305" s="1">
         <v>94</v>
       </c>
     </row>
-    <row r="306">
-      <c r="A306" s="1" t="n">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A306" s="1">
         <v>95</v>
       </c>
     </row>
-    <row r="307">
-      <c r="A307" s="1" t="n">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A307" s="1">
         <v>96</v>
       </c>
     </row>
-    <row r="308">
-      <c r="A308" s="1" t="n">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A308" s="1">
         <v>97</v>
       </c>
     </row>
-    <row r="309">
-      <c r="A309" s="1" t="n">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A309" s="1">
         <v>98</v>
       </c>
     </row>
-    <row r="310">
-      <c r="A310" s="1" t="n">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A310" s="1">
         <v>99</v>
       </c>
     </row>
-    <row r="311">
-      <c r="A311" s="1" t="n">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A311" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="314">
-      <c r="A314" s="1" t="inlineStr">
-        <is>
-          <t>Global Poisoning Accuracy</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="3" t="inlineStr">
-        <is>
-          <t>Round number</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="1" t="n">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A314" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A315" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A316" s="1">
         <v>1</v>
       </c>
-      <c r="B316" t="n">
+      <c r="B316">
         <v>0</v>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" s="1" t="n">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A317" s="1">
         <v>2</v>
       </c>
-      <c r="B317" t="n">
-        <v>0.0939</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="B317">
+        <v>9.3899999999999997E-2</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A318" s="1">
         <v>3</v>
       </c>
-      <c r="B318" t="n">
+      <c r="B318">
         <v>0.1361</v>
       </c>
     </row>
-    <row r="319">
-      <c r="A319" s="1" t="n">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A319" s="1">
         <v>4</v>
       </c>
-      <c r="B319" t="n">
-        <v>0.0891</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="B319">
+        <v>8.9099999999999999E-2</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A320" s="1">
         <v>5</v>
       </c>
-      <c r="B320" t="n">
+      <c r="B320">
         <v>0.1075</v>
       </c>
     </row>
-    <row r="321">
-      <c r="A321" s="1" t="n">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A321" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="322">
-      <c r="A322" s="1" t="n">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A322" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="323">
-      <c r="A323" s="1" t="n">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A323" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="324">
-      <c r="A324" s="1" t="n">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A324" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="325">
-      <c r="A325" s="1" t="n">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A325" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="326">
-      <c r="A326" s="1" t="n">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A326" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="327">
-      <c r="A327" s="1" t="n">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A327" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="328">
-      <c r="A328" s="1" t="n">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A328" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="329">
-      <c r="A329" s="1" t="n">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A329" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="330">
-      <c r="A330" s="1" t="n">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A330" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="331">
-      <c r="A331" s="1" t="n">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A331" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="332">
-      <c r="A332" s="1" t="n">
+    <row r="332" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A332" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="333">
-      <c r="A333" s="1" t="n">
+    <row r="333" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A333" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="334">
-      <c r="A334" s="1" t="n">
+    <row r="334" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A334" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="335">
-      <c r="A335" s="1" t="n">
+    <row r="335" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A335" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="336">
-      <c r="A336" s="1" t="n">
+    <row r="336" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A336" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="337">
-      <c r="A337" s="1" t="n">
+    <row r="337" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A337" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="338">
-      <c r="A338" s="1" t="n">
+    <row r="338" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A338" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="339">
-      <c r="A339" s="1" t="n">
+    <row r="339" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A339" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="340">
-      <c r="A340" s="1" t="n">
+    <row r="340" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A340" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="341">
-      <c r="A341" s="1" t="n">
+    <row r="341" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A341" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="342">
-      <c r="A342" s="1" t="n">
+    <row r="342" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A342" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="343">
-      <c r="A343" s="1" t="n">
+    <row r="343" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A343" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="344">
-      <c r="A344" s="1" t="n">
+    <row r="344" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A344" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="345">
-      <c r="A345" s="1" t="n">
+    <row r="345" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A345" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="346">
-      <c r="A346" s="1" t="n">
+    <row r="346" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A346" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="347">
-      <c r="A347" s="1" t="n">
+    <row r="347" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A347" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="348">
-      <c r="A348" s="1" t="n">
+    <row r="348" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A348" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="349">
-      <c r="A349" s="1" t="n">
+    <row r="349" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A349" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="350">
-      <c r="A350" s="1" t="n">
+    <row r="350" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A350" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="351">
-      <c r="A351" s="1" t="n">
+    <row r="351" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A351" s="1">
         <v>36</v>
       </c>
     </row>
-    <row r="352">
-      <c r="A352" s="1" t="n">
+    <row r="352" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A352" s="1">
         <v>37</v>
       </c>
     </row>
-    <row r="353">
-      <c r="A353" s="1" t="n">
+    <row r="353" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A353" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="354">
-      <c r="A354" s="1" t="n">
+    <row r="354" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A354" s="1">
         <v>39</v>
       </c>
     </row>
-    <row r="355">
-      <c r="A355" s="1" t="n">
+    <row r="355" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A355" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="356">
-      <c r="A356" s="1" t="n">
+    <row r="356" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A356" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="357">
-      <c r="A357" s="1" t="n">
+    <row r="357" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A357" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="358">
-      <c r="A358" s="1" t="n">
+    <row r="358" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A358" s="1">
         <v>43</v>
       </c>
     </row>
-    <row r="359">
-      <c r="A359" s="1" t="n">
+    <row r="359" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A359" s="1">
         <v>44</v>
       </c>
     </row>
-    <row r="360">
-      <c r="A360" s="1" t="n">
+    <row r="360" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A360" s="1">
         <v>45</v>
       </c>
     </row>
-    <row r="361">
-      <c r="A361" s="1" t="n">
+    <row r="361" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A361" s="1">
         <v>46</v>
       </c>
     </row>
-    <row r="362">
-      <c r="A362" s="1" t="n">
+    <row r="362" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A362" s="1">
         <v>47</v>
       </c>
     </row>
-    <row r="363">
-      <c r="A363" s="1" t="n">
+    <row r="363" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A363" s="1">
         <v>48</v>
       </c>
     </row>
-    <row r="364">
-      <c r="A364" s="1" t="n">
+    <row r="364" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A364" s="1">
         <v>49</v>
       </c>
     </row>
-    <row r="365">
-      <c r="A365" s="1" t="n">
+    <row r="365" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A365" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="366">
-      <c r="A366" s="1" t="n">
+    <row r="366" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A366" s="1">
         <v>51</v>
       </c>
     </row>
-    <row r="367">
-      <c r="A367" s="1" t="n">
+    <row r="367" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A367" s="1">
         <v>52</v>
       </c>
     </row>
-    <row r="368">
-      <c r="A368" s="1" t="n">
+    <row r="368" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A368" s="1">
         <v>53</v>
       </c>
     </row>
-    <row r="369">
-      <c r="A369" s="1" t="n">
+    <row r="369" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A369" s="1">
         <v>54</v>
       </c>
     </row>
-    <row r="370">
-      <c r="A370" s="1" t="n">
+    <row r="370" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A370" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="371">
-      <c r="A371" s="1" t="n">
+    <row r="371" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A371" s="1">
         <v>56</v>
       </c>
     </row>
-    <row r="372">
-      <c r="A372" s="1" t="n">
+    <row r="372" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A372" s="1">
         <v>57</v>
       </c>
     </row>
-    <row r="373">
-      <c r="A373" s="1" t="n">
+    <row r="373" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A373" s="1">
         <v>58</v>
       </c>
     </row>
-    <row r="374">
-      <c r="A374" s="1" t="n">
+    <row r="374" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A374" s="1">
         <v>59</v>
       </c>
     </row>
-    <row r="375">
-      <c r="A375" s="1" t="n">
+    <row r="375" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A375" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="376">
-      <c r="A376" s="1" t="n">
+    <row r="376" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A376" s="1">
         <v>61</v>
       </c>
     </row>
-    <row r="377">
-      <c r="A377" s="1" t="n">
+    <row r="377" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A377" s="1">
         <v>62</v>
       </c>
     </row>
-    <row r="378">
-      <c r="A378" s="1" t="n">
+    <row r="378" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A378" s="1">
         <v>63</v>
       </c>
     </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
+    <row r="379" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A379" s="1">
         <v>64</v>
       </c>
     </row>
-    <row r="380">
-      <c r="A380" s="1" t="n">
+    <row r="380" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A380" s="1">
         <v>65</v>
       </c>
     </row>
-    <row r="381">
-      <c r="A381" s="1" t="n">
+    <row r="381" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A381" s="1">
         <v>66</v>
       </c>
     </row>
-    <row r="382">
-      <c r="A382" s="1" t="n">
+    <row r="382" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A382" s="1">
         <v>67</v>
       </c>
     </row>
-    <row r="383">
-      <c r="A383" s="1" t="n">
+    <row r="383" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A383" s="1">
         <v>68</v>
       </c>
     </row>
-    <row r="384">
-      <c r="A384" s="1" t="n">
+    <row r="384" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A384" s="1">
         <v>69</v>
       </c>
     </row>
-    <row r="385">
-      <c r="A385" s="1" t="n">
+    <row r="385" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A385" s="1">
         <v>70</v>
       </c>
     </row>
-    <row r="386">
-      <c r="A386" s="1" t="n">
+    <row r="386" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A386" s="1">
         <v>71</v>
       </c>
     </row>
-    <row r="387">
-      <c r="A387" s="1" t="n">
+    <row r="387" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A387" s="1">
         <v>72</v>
       </c>
     </row>
-    <row r="388">
-      <c r="A388" s="1" t="n">
+    <row r="388" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A388" s="1">
         <v>73</v>
       </c>
     </row>
-    <row r="389">
-      <c r="A389" s="1" t="n">
+    <row r="389" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A389" s="1">
         <v>74</v>
       </c>
     </row>
-    <row r="390">
-      <c r="A390" s="1" t="n">
+    <row r="390" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A390" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="391">
-      <c r="A391" s="1" t="n">
+    <row r="391" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A391" s="1">
         <v>76</v>
       </c>
     </row>
-    <row r="392">
-      <c r="A392" s="1" t="n">
+    <row r="392" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A392" s="1">
         <v>77</v>
       </c>
     </row>
-    <row r="393">
-      <c r="A393" s="1" t="n">
+    <row r="393" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A393" s="1">
         <v>78</v>
       </c>
     </row>
-    <row r="394">
-      <c r="A394" s="1" t="n">
+    <row r="394" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A394" s="1">
         <v>79</v>
       </c>
     </row>
-    <row r="395">
-      <c r="A395" s="1" t="n">
+    <row r="395" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A395" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="396">
-      <c r="A396" s="1" t="n">
+    <row r="396" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A396" s="1">
         <v>81</v>
       </c>
     </row>
-    <row r="397">
-      <c r="A397" s="1" t="n">
+    <row r="397" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A397" s="1">
         <v>82</v>
       </c>
     </row>
-    <row r="398">
-      <c r="A398" s="1" t="n">
+    <row r="398" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A398" s="1">
         <v>83</v>
       </c>
     </row>
-    <row r="399">
-      <c r="A399" s="1" t="n">
+    <row r="399" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A399" s="1">
         <v>84</v>
       </c>
     </row>
-    <row r="400">
-      <c r="A400" s="1" t="n">
+    <row r="400" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A400" s="1">
         <v>85</v>
       </c>
     </row>
-    <row r="401">
-      <c r="A401" s="1" t="n">
+    <row r="401" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A401" s="1">
         <v>86</v>
       </c>
     </row>
-    <row r="402">
-      <c r="A402" s="1" t="n">
+    <row r="402" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A402" s="1">
         <v>87</v>
       </c>
     </row>
-    <row r="403">
-      <c r="A403" s="1" t="n">
+    <row r="403" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A403" s="1">
         <v>88</v>
       </c>
     </row>
-    <row r="404">
-      <c r="A404" s="1" t="n">
+    <row r="404" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A404" s="1">
         <v>89</v>
       </c>
     </row>
-    <row r="405">
-      <c r="A405" s="1" t="n">
+    <row r="405" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A405" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="406">
-      <c r="A406" s="1" t="n">
+    <row r="406" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A406" s="1">
         <v>91</v>
       </c>
     </row>
-    <row r="407">
-      <c r="A407" s="1" t="n">
+    <row r="407" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A407" s="1">
         <v>92</v>
       </c>
     </row>
-    <row r="408">
-      <c r="A408" s="1" t="n">
+    <row r="408" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A408" s="1">
         <v>93</v>
       </c>
     </row>
-    <row r="409">
-      <c r="A409" s="1" t="n">
+    <row r="409" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A409" s="1">
         <v>94</v>
       </c>
     </row>
-    <row r="410">
-      <c r="A410" s="1" t="n">
+    <row r="410" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A410" s="1">
         <v>95</v>
       </c>
     </row>
-    <row r="411">
-      <c r="A411" s="1" t="n">
+    <row r="411" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A411" s="1">
         <v>96</v>
       </c>
     </row>
-    <row r="412">
-      <c r="A412" s="1" t="n">
+    <row r="412" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A412" s="1">
         <v>97</v>
       </c>
     </row>
-    <row r="413">
-      <c r="A413" s="1" t="n">
+    <row r="413" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A413" s="1">
         <v>98</v>
       </c>
     </row>
-    <row r="414">
-      <c r="A414" s="1" t="n">
+    <row r="414" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A414" s="1">
         <v>99</v>
       </c>
     </row>
-    <row r="415">
-      <c r="A415" s="1" t="n">
+    <row r="415" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A415" s="1">
         <v>100</v>
       </c>
     </row>

--- a/CIFAR_Global.xlsx
+++ b/CIFAR_Global.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashleyau/Documents/PhD/Practical_Experiment/Finalised/Finalised_Algorithm_ResNet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{491F8CC9-D909-134A-9168-6C8CFA6AF6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A7B48B-8B69-5C49-8B3D-1B82FC317897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-41520" yWindow="-1660" windowWidth="34560" windowHeight="19980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
     <t>5 rounds</t>
   </si>
   <si>
-    <t>Actual</t>
+    <t>10 rounds</t>
   </si>
 </sst>
 </file>

--- a/CIFAR_Global.xlsx
+++ b/CIFAR_Global.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashleyau/Documents/PhD/Practical_Experiment/Finalised/Finalised_Algorithm_ResNet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A7B48B-8B69-5C49-8B3D-1B82FC317897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45C89EA6-6D06-0144-B0B7-5C3EEA17180A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -117,6 +117,894 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Global Accuracy</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$5:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.10780000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.46650000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.64400000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.66239999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.70109999999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3D86-B14F-BDF7-7FE8A0DDD8FC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="145715327"/>
+        <c:axId val="330977599"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="145715327"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="330977599"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="330977599"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="145715327"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>704850</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBEB8CD0-C7E6-C074-756D-EC6D84062752}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2560,5 +3448,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/CIFAR_Global.xlsx
+++ b/CIFAR_Global.xlsx
@@ -1,41 +1,87 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashleyau/Documents/PhD/Practical_Experiment/Finalised/Finalised_Algorithm_ResNet/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63CC908-95C5-F645-9686-DD8705B9DB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20060" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-39520" yWindow="-2320" windowWidth="34560" windowHeight="20060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+  <si>
+    <t>100 Rounds</t>
+  </si>
+  <si>
+    <t>IID</t>
+  </si>
+  <si>
+    <t>Global Accuracy</t>
+  </si>
+  <si>
+    <t>5 rounds</t>
+  </si>
+  <si>
+    <t>10 rounds</t>
+  </si>
+  <si>
+    <t>Round</t>
+  </si>
+  <si>
+    <t>Clustering Accuracy</t>
+  </si>
+  <si>
+    <t>Round number</t>
+  </si>
+  <si>
+    <t>Poisoning Accuracy</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Global Poisoning Accuracy</t>
+  </si>
+  <si>
+    <t>All Benign</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -54,96 +100,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
           <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
@@ -165,49 +163,30 @@
               <a:t>Global Accuracy</a:t>
             </a:r>
           </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t>None</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </txPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <lineChart>
-        <grouping val="standard"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Without Including Evil</c:v>
+          </c:tx>
+          <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
@@ -215,64 +194,119 @@
               <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <val>
-            <numRef>
-              <f>Sheet1!$B$5:$B$9</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="5"/>
-                <pt idx="0">
-                  <v>0.1078</v>
-                </pt>
-                <pt idx="1">
-                  <v>0.4665</v>
-                </pt>
-                <pt idx="2">
-                  <v>0.644</v>
-                </pt>
-                <pt idx="3">
-                  <v>0.6624</v>
-                </pt>
-                <pt idx="4">
-                  <v>0.7010999999999999</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <smooth val="0"/>
-        <axId val="145715327"/>
-        <axId val="330977599"/>
-      </lineChart>
-      <catAx>
-        <axId val="145715327"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$5:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.10780000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.46650000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.64400000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.66239999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.70109999999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-524D-B94E-A87F-34E43790AFE1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>All Cases Included</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$5:$C$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.30859999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.4859</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.49209999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.50380000000000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.51800000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.53549999999999998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.51219999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.61650000000000005</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.54310000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-524D-B94E-A87F-34E43790AFE1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="145715327"/>
+        <c:axId val="330977599"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="145715327"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
@@ -284,8 +318,8 @@
             <a:prstDash val="solid"/>
             <a:round/>
           </a:ln>
-        </spPr>
-        <txPr>
+        </c:spPr>
+        <c:txPr>
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
@@ -302,28 +336,25 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
-        </txPr>
-        <crossAx val="330977599"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="330977599"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
+        </c:txPr>
+        <c:crossAx val="330977599"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="330977599"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
@@ -334,20 +365,20 @@
               <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="General" sourceLinked="1"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
           <a:noFill/>
           <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
-        </spPr>
-        <txPr>
+        </c:spPr>
+        <c:txPr>
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
@@ -364,21 +395,23 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
-        </txPr>
-        <crossAx val="145715327"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
+        </c:txPr>
+        <c:crossAx val="145715327"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
     <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
@@ -392,40 +425,54 @@
       <a:prstDash val="solid"/>
       <a:round/>
     </a:ln>
-  </spPr>
-</chartSpace>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>704850</colOff>
-      <row>5</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <to>
-      <col>8</col>
-      <colOff>323850</colOff>
-      <row>19</row>
-      <rowOff>88900</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>69850</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -744,2276 +791,2249 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C415"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D415"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="15.1640625" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>100 Rounds</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>IID</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Global Accuracy</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>5 rounds</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>10 rounds</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Round</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" t="n">
-        <v>0.1078</v>
-      </c>
-      <c r="C5" t="n">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>0.10780000000000001</v>
+      </c>
+      <c r="C5">
         <v>0.1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" t="n">
-        <v>0.4665</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.3086</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="B6">
+        <v>0.46650000000000003</v>
+      </c>
+      <c r="C6">
+        <v>0.30859999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" t="n">
-        <v>0.644</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7">
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="C7">
         <v>0.4859</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" t="n">
-        <v>0.6624</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.4921</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="B8">
+        <v>0.66239999999999999</v>
+      </c>
+      <c r="C8">
+        <v>0.49209999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
         <v>5</v>
       </c>
-      <c r="B9" t="n">
-        <v>0.7010999999999999</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.5038</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="B9">
+        <v>0.70109999999999995</v>
+      </c>
+      <c r="C9">
+        <v>0.50380000000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
         <v>6</v>
       </c>
-      <c r="C10" t="n">
-        <v>0.518</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="C10">
+        <v>0.51800000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
         <v>7</v>
       </c>
-      <c r="C11" t="n">
-        <v>0.5355</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="C11">
+        <v>0.53549999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
         <v>8</v>
       </c>
-      <c r="C12" t="n">
-        <v>0.5122</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="C12">
+        <v>0.51219999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
         <v>9</v>
       </c>
-      <c r="C13" t="n">
-        <v>0.6165</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="C13">
+        <v>0.61650000000000005</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
         <v>10</v>
       </c>
-      <c r="C14" t="n">
-        <v>0.5431</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="C14">
+        <v>0.54310000000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
         <v>36</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
         <v>37</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
         <v>39</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
         <v>43</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
         <v>44</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
         <v>45</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
         <v>46</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
         <v>47</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
         <v>48</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
         <v>49</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
         <v>51</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
         <v>52</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="1" t="n">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
         <v>53</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="1" t="n">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
         <v>54</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
         <v>56</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
         <v>57</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="1" t="n">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
         <v>58</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="1" t="n">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
         <v>59</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="1" t="n">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="1" t="n">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
         <v>61</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="1" t="n">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
         <v>62</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="1" t="n">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
         <v>63</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="1" t="n">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
         <v>64</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="1" t="n">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
         <v>65</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="1" t="n">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
         <v>66</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="1" t="n">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
         <v>67</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="1" t="n">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
         <v>68</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="1" t="n">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
         <v>69</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="1" t="n">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
         <v>70</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="1" t="n">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
         <v>71</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="1" t="n">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
         <v>72</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="1" t="n">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
         <v>73</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="1" t="n">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
         <v>74</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="1" t="n">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="1" t="n">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
         <v>76</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="1" t="n">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
         <v>77</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="1" t="n">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
         <v>78</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="1" t="n">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
         <v>79</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="1" t="n">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="1" t="n">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
         <v>81</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="1" t="n">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
         <v>82</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="1" t="n">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A87" s="1">
         <v>83</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="1" t="n">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A88" s="1">
         <v>84</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="1" t="n">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A89" s="1">
         <v>85</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="1" t="n">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A90" s="1">
         <v>86</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="1" t="n">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A91" s="1">
         <v>87</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="1" t="n">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A92" s="1">
         <v>88</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="1" t="n">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A93" s="1">
         <v>89</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="1" t="n">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A94" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="1" t="n">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A95" s="1">
         <v>91</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="1" t="n">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A96" s="1">
         <v>92</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="1" t="n">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A97" s="1">
         <v>93</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="1" t="n">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A98" s="1">
         <v>94</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="1" t="n">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A99" s="1">
         <v>95</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="1" t="n">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A100" s="1">
         <v>96</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="1" t="n">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A101" s="1">
         <v>97</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="1" t="n">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A102" s="1">
         <v>98</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="1" t="n">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A103" s="1">
         <v>99</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="1" t="n">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A104" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="1" t="inlineStr">
-        <is>
-          <t>Clustering Accuracy</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>Round number</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="1" t="n">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A107" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A108" s="1">
         <v>1</v>
       </c>
-      <c r="B108" t="n">
+      <c r="B108">
         <v>1</v>
       </c>
-      <c r="C108" t="n">
+      <c r="C108">
         <v>1</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="1" t="n">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A109" s="1">
         <v>2</v>
       </c>
-      <c r="B109" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="C109" t="n">
+      <c r="B109">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C109">
         <v>0.75</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="1" t="n">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A110" s="1">
         <v>3</v>
       </c>
-      <c r="B110" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="C110" t="n">
+      <c r="B110">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C110">
         <v>1</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="1" t="n">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A111" s="1">
         <v>4</v>
       </c>
-      <c r="B111" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="C111" t="n">
+      <c r="B111">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C111">
         <v>1</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="1" t="n">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A112" s="1">
         <v>5</v>
       </c>
-      <c r="B112" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="C112" t="n">
+      <c r="B112">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C112">
         <v>1</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="1" t="n">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A113" s="1">
         <v>6</v>
       </c>
-      <c r="C113" t="n">
+      <c r="C113">
         <v>1</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="1" t="n">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A114" s="1">
         <v>7</v>
       </c>
-      <c r="C114" t="n">
+      <c r="C114">
         <v>1</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="1" t="n">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A115" s="1">
         <v>8</v>
       </c>
-      <c r="C115" t="n">
+      <c r="C115">
         <v>1</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="1" t="n">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A116" s="1">
         <v>9</v>
       </c>
-      <c r="C116" t="n">
+      <c r="C116">
         <v>1</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="1" t="n">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A117" s="1">
         <v>10</v>
       </c>
-      <c r="C117" t="n">
+      <c r="C117">
         <v>1</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="1" t="n">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A118" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="1" t="n">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A119" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="1" t="n">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A120" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="1" t="n">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A121" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="1" t="n">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A122" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="1" t="n">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A123" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="1" t="n">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A124" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="1" t="n">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A125" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="1" t="n">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A126" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="1" t="n">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A127" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="1" t="n">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A128" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="1" t="n">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A129" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="1" t="n">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A130" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="1" t="n">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A131" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="1" t="n">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A132" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="1" t="n">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A133" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="1" t="n">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A134" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="1" t="n">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A135" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="1" t="n">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A136" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="1" t="n">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A137" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="1" t="n">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A138" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="1" t="n">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A139" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="1" t="n">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A140" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="1" t="n">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A141" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="1" t="n">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A142" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="1" t="n">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
         <v>36</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="1" t="n">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
         <v>37</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="1" t="n">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="1" t="n">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
         <v>39</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="1" t="n">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="1" t="n">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A148" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="1" t="n">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A149" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="1" t="n">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A150" s="1">
         <v>43</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="1" t="n">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A151" s="1">
         <v>44</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="1" t="n">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A152" s="1">
         <v>45</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="1" t="n">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A153" s="1">
         <v>46</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="1" t="n">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A154" s="1">
         <v>47</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="1" t="n">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A155" s="1">
         <v>48</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="1" t="n">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A156" s="1">
         <v>49</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="1" t="n">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A157" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="1" t="n">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A158" s="1">
         <v>51</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="1" t="n">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A159" s="1">
         <v>52</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="1" t="n">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A160" s="1">
         <v>53</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="1" t="n">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A161" s="1">
         <v>54</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="1" t="n">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A162" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="1" t="n">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A163" s="1">
         <v>56</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="1" t="n">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A164" s="1">
         <v>57</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="1" t="n">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A165" s="1">
         <v>58</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="1" t="n">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A166" s="1">
         <v>59</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="1" t="n">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A167" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="1" t="n">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A168" s="1">
         <v>61</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="1" t="n">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A169" s="1">
         <v>62</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="1" t="n">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A170" s="1">
         <v>63</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="1" t="n">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A171" s="1">
         <v>64</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="1" t="n">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A172" s="1">
         <v>65</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="1" t="n">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A173" s="1">
         <v>66</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="1" t="n">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A174" s="1">
         <v>67</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="1" t="n">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A175" s="1">
         <v>68</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="1" t="n">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A176" s="1">
         <v>69</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="1" t="n">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A177" s="1">
         <v>70</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="1" t="n">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A178" s="1">
         <v>71</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="1" t="n">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A179" s="1">
         <v>72</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="1" t="n">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A180" s="1">
         <v>73</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="1" t="n">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A181" s="1">
         <v>74</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="1" t="n">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A182" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="1" t="n">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A183" s="1">
         <v>76</v>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="1" t="n">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A184" s="1">
         <v>77</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="1" t="n">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A185" s="1">
         <v>78</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="1" t="n">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A186" s="1">
         <v>79</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="1" t="n">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A187" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="1" t="n">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A188" s="1">
         <v>81</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="1" t="n">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A189" s="1">
         <v>82</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="1" t="n">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A190" s="1">
         <v>83</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="1" t="n">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A191" s="1">
         <v>84</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="1" t="n">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A192" s="1">
         <v>85</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="1" t="n">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A193" s="1">
         <v>86</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="1" t="n">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A194" s="1">
         <v>87</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="1" t="n">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A195" s="1">
         <v>88</v>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="1" t="n">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A196" s="1">
         <v>89</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="1" t="n">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A197" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="1" t="n">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A198" s="1">
         <v>91</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="1" t="n">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A199" s="1">
         <v>92</v>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="1" t="n">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A200" s="1">
         <v>93</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="1" t="n">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A201" s="1">
         <v>94</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="1" t="n">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A202" s="1">
         <v>95</v>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="1" t="n">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A203" s="1">
         <v>96</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="1" t="n">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A204" s="1">
         <v>97</v>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="1" t="n">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A205" s="1">
         <v>98</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="1" t="n">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A206" s="1">
         <v>99</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="1" t="n">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A207" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="1" t="inlineStr">
-        <is>
-          <t>Poisoning Accuracy</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="3" t="inlineStr">
-        <is>
-          <t>Round number</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="1" t="n">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A210" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A211" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A212" s="1">
         <v>1</v>
       </c>
-      <c r="B212" t="n">
-        <v>0.99725</v>
-      </c>
-      <c r="C212" t="n">
-        <v>0.9959666666666666</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="B212">
+        <v>0.99724999999999997</v>
+      </c>
+      <c r="C212">
+        <v>0.99596666666666656</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A213" s="1">
         <v>2</v>
       </c>
-      <c r="B213" t="n">
-        <v>0.99065</v>
-      </c>
-      <c r="C213" t="n">
-        <v>0.9851</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="B213">
+        <v>0.99065000000000003</v>
+      </c>
+      <c r="C213">
+        <v>0.98509999999999998</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A214" s="1">
         <v>3</v>
       </c>
-      <c r="B214" t="n">
+      <c r="B214">
         <v>0.9869</v>
       </c>
-      <c r="C214" t="n">
-        <v>0.9937333333333335</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="C214">
+        <v>0.99373333333333347</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A215" s="1">
         <v>4</v>
       </c>
-      <c r="B215" t="n">
-        <v>0.97765</v>
-      </c>
-      <c r="C215" t="n">
-        <v>0.909</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="B215">
+        <v>0.97765000000000002</v>
+      </c>
+      <c r="C215">
+        <v>0.90900000000000003</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A216" s="1">
         <v>5</v>
       </c>
-      <c r="B216" t="n">
-        <v>0.9846</v>
-      </c>
-      <c r="C216" t="n">
-        <v>0.9800500000000001</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="B216">
+        <v>0.98460000000000003</v>
+      </c>
+      <c r="C216">
+        <v>0.98005000000000009</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A217" s="1">
         <v>6</v>
       </c>
-      <c r="C217" t="n">
-        <v>0.9918</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="C217">
+        <v>0.99180000000000001</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A218" s="1">
         <v>7</v>
       </c>
-      <c r="C218" t="n">
-        <v>0.9643</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="C218">
+        <v>0.96430000000000005</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A219" s="1">
         <v>8</v>
       </c>
-      <c r="C219" t="n">
-        <v>0.9815</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="C219">
+        <v>0.98150000000000004</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A220" s="1">
         <v>9</v>
       </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="C220" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A221" s="1">
         <v>10</v>
       </c>
-      <c r="C221" t="n">
+      <c r="C221">
         <v>0.9819500000000001</v>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="1" t="n">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A222" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="1" t="n">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A223" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="1" t="n">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A224" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="1" t="n">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A225" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="1" t="n">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A226" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="1" t="n">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A227" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="1" t="n">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A228" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="1" t="n">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A229" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="1" t="n">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A230" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="1" t="n">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A231" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="1" t="n">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A232" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="1" t="n">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A233" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="1" t="n">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A234" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="1" t="n">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A235" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="1" t="n">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A236" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="1" t="n">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A237" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="1" t="n">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A238" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="1" t="n">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A239" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="1" t="n">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A240" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="1" t="n">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A241" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="1" t="n">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A242" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="1" t="n">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A243" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="1" t="n">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A244" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="1" t="n">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A245" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="1" t="n">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A246" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="1" t="n">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A247" s="1">
         <v>36</v>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="1" t="n">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A248" s="1">
         <v>37</v>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="1" t="n">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A249" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="1" t="n">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A250" s="1">
         <v>39</v>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="1" t="n">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A251" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="1" t="n">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A252" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A253" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="1" t="n">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A254" s="1">
         <v>43</v>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="1" t="n">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A255" s="1">
         <v>44</v>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="1" t="n">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A256" s="1">
         <v>45</v>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="1" t="n">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A257" s="1">
         <v>46</v>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="1" t="n">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A258" s="1">
         <v>47</v>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="1" t="n">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A259" s="1">
         <v>48</v>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="1" t="n">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A260" s="1">
         <v>49</v>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" s="1" t="n">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A261" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="1" t="n">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A262" s="1">
         <v>51</v>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" s="1" t="n">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A263" s="1">
         <v>52</v>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" s="1" t="n">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A264" s="1">
         <v>53</v>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" s="1" t="n">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A265" s="1">
         <v>54</v>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" s="1" t="n">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A266" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" s="1" t="n">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A267" s="1">
         <v>56</v>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" s="1" t="n">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A268" s="1">
         <v>57</v>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" s="1" t="n">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A269" s="1">
         <v>58</v>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" s="1" t="n">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A270" s="1">
         <v>59</v>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" s="1" t="n">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A271" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" s="1" t="n">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A272" s="1">
         <v>61</v>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="1" t="n">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A273" s="1">
         <v>62</v>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="1" t="n">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A274" s="1">
         <v>63</v>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" s="1" t="n">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A275" s="1">
         <v>64</v>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" s="1" t="n">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A276" s="1">
         <v>65</v>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" s="1" t="n">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A277" s="1">
         <v>66</v>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" s="1" t="n">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A278" s="1">
         <v>67</v>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" s="1" t="n">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A279" s="1">
         <v>68</v>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" s="1" t="n">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A280" s="1">
         <v>69</v>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" s="1" t="n">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A281" s="1">
         <v>70</v>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" s="1" t="n">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A282" s="1">
         <v>71</v>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" s="1" t="n">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A283" s="1">
         <v>72</v>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" s="1" t="n">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A284" s="1">
         <v>73</v>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" s="1" t="n">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A285" s="1">
         <v>74</v>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" s="1" t="n">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A286" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" s="1" t="n">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A287" s="1">
         <v>76</v>
       </c>
     </row>
-    <row r="288">
-      <c r="A288" s="1" t="n">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A288" s="1">
         <v>77</v>
       </c>
     </row>
-    <row r="289">
-      <c r="A289" s="1" t="n">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A289" s="1">
         <v>78</v>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" s="1" t="n">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A290" s="1">
         <v>79</v>
       </c>
     </row>
-    <row r="291">
-      <c r="A291" s="1" t="n">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A291" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="292">
-      <c r="A292" s="1" t="n">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A292" s="1">
         <v>81</v>
       </c>
     </row>
-    <row r="293">
-      <c r="A293" s="1" t="n">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A293" s="1">
         <v>82</v>
       </c>
     </row>
-    <row r="294">
-      <c r="A294" s="1" t="n">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A294" s="1">
         <v>83</v>
       </c>
     </row>
-    <row r="295">
-      <c r="A295" s="1" t="n">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A295" s="1">
         <v>84</v>
       </c>
     </row>
-    <row r="296">
-      <c r="A296" s="1" t="n">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A296" s="1">
         <v>85</v>
       </c>
     </row>
-    <row r="297">
-      <c r="A297" s="1" t="n">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A297" s="1">
         <v>86</v>
       </c>
     </row>
-    <row r="298">
-      <c r="A298" s="1" t="n">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A298" s="1">
         <v>87</v>
       </c>
     </row>
-    <row r="299">
-      <c r="A299" s="1" t="n">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A299" s="1">
         <v>88</v>
       </c>
     </row>
-    <row r="300">
-      <c r="A300" s="1" t="n">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A300" s="1">
         <v>89</v>
       </c>
     </row>
-    <row r="301">
-      <c r="A301" s="1" t="n">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A301" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" s="1" t="n">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A302" s="1">
         <v>91</v>
       </c>
     </row>
-    <row r="303">
-      <c r="A303" s="1" t="n">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A303" s="1">
         <v>92</v>
       </c>
     </row>
-    <row r="304">
-      <c r="A304" s="1" t="n">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A304" s="1">
         <v>93</v>
       </c>
     </row>
-    <row r="305">
-      <c r="A305" s="1" t="n">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A305" s="1">
         <v>94</v>
       </c>
     </row>
-    <row r="306">
-      <c r="A306" s="1" t="n">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A306" s="1">
         <v>95</v>
       </c>
     </row>
-    <row r="307">
-      <c r="A307" s="1" t="n">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A307" s="1">
         <v>96</v>
       </c>
     </row>
-    <row r="308">
-      <c r="A308" s="1" t="n">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A308" s="1">
         <v>97</v>
       </c>
     </row>
-    <row r="309">
-      <c r="A309" s="1" t="n">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A309" s="1">
         <v>98</v>
       </c>
     </row>
-    <row r="310">
-      <c r="A310" s="1" t="n">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A310" s="1">
         <v>99</v>
       </c>
     </row>
-    <row r="311">
-      <c r="A311" s="1" t="n">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A311" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="314">
-      <c r="A314" s="1" t="inlineStr">
-        <is>
-          <t>Global Poisoning Accuracy</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="3" t="inlineStr">
-        <is>
-          <t>Round number</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="1" t="n">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A314" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A315" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A316" s="1">
         <v>1</v>
       </c>
-      <c r="B316" t="n">
+      <c r="B316">
         <v>0</v>
       </c>
-      <c r="C316" t="n">
+      <c r="C316">
         <v>0</v>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" s="1" t="n">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A317" s="1">
         <v>2</v>
       </c>
-      <c r="B317" t="n">
-        <v>0.0939</v>
-      </c>
-      <c r="C317" t="n">
+      <c r="B317">
+        <v>9.3899999999999997E-2</v>
+      </c>
+      <c r="C317">
         <v>0.1144</v>
       </c>
     </row>
-    <row r="318">
-      <c r="A318" s="1" t="n">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A318" s="1">
         <v>3</v>
       </c>
-      <c r="B318" t="n">
+      <c r="B318">
         <v>0.1361</v>
       </c>
-      <c r="C318" t="n">
-        <v>0.1861</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="C318">
+        <v>0.18609999999999999</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A319" s="1">
         <v>4</v>
       </c>
-      <c r="B319" t="n">
-        <v>0.0891</v>
-      </c>
-      <c r="C319" t="n">
-        <v>0.306</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="B319">
+        <v>8.9099999999999999E-2</v>
+      </c>
+      <c r="C319">
+        <v>0.30599999999999999</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A320" s="1">
         <v>5</v>
       </c>
-      <c r="B320" t="n">
+      <c r="B320">
         <v>0.1075</v>
       </c>
-      <c r="C320" t="n">
-        <v>0.3782</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="1" t="n">
+      <c r="C320">
+        <v>0.37819999999999998</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A321" s="1">
         <v>6</v>
       </c>
-      <c r="C321" t="n">
-        <v>0.3822</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="1" t="n">
+      <c r="C321">
+        <v>0.38219999999999998</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A322" s="1">
         <v>7</v>
       </c>
-      <c r="C322" t="n">
+      <c r="C322">
         <v>0.3821</v>
       </c>
     </row>
-    <row r="323">
-      <c r="A323" s="1" t="n">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A323" s="1">
         <v>8</v>
       </c>
-      <c r="C323" t="n">
+      <c r="C323">
         <v>0.4965</v>
       </c>
     </row>
-    <row r="324">
-      <c r="A324" s="1" t="n">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A324" s="1">
         <v>9</v>
       </c>
-      <c r="C324" t="n">
-        <v>0.1801</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="1" t="n">
+      <c r="C324">
+        <v>0.18010000000000001</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A325" s="1">
         <v>10</v>
       </c>
-      <c r="C325" t="n">
-        <v>0.4515</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="1" t="n">
+      <c r="C325">
+        <v>0.45150000000000001</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A326" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="327">
-      <c r="A327" s="1" t="n">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A327" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="328">
-      <c r="A328" s="1" t="n">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A328" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="329">
-      <c r="A329" s="1" t="n">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A329" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="330">
-      <c r="A330" s="1" t="n">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A330" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="331">
-      <c r="A331" s="1" t="n">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A331" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="332">
-      <c r="A332" s="1" t="n">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A332" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="333">
-      <c r="A333" s="1" t="n">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A333" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="334">
-      <c r="A334" s="1" t="n">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A334" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="335">
-      <c r="A335" s="1" t="n">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A335" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="336">
-      <c r="A336" s="1" t="n">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A336" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="337">
-      <c r="A337" s="1" t="n">
+    <row r="337" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A337" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="338">
-      <c r="A338" s="1" t="n">
+    <row r="338" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A338" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="339">
-      <c r="A339" s="1" t="n">
+    <row r="339" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A339" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="340">
-      <c r="A340" s="1" t="n">
+    <row r="340" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A340" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="341">
-      <c r="A341" s="1" t="n">
+    <row r="341" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A341" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="342">
-      <c r="A342" s="1" t="n">
+    <row r="342" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A342" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="343">
-      <c r="A343" s="1" t="n">
+    <row r="343" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A343" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="344">
-      <c r="A344" s="1" t="n">
+    <row r="344" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A344" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="345">
-      <c r="A345" s="1" t="n">
+    <row r="345" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A345" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="346">
-      <c r="A346" s="1" t="n">
+    <row r="346" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A346" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="347">
-      <c r="A347" s="1" t="n">
+    <row r="347" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A347" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="348">
-      <c r="A348" s="1" t="n">
+    <row r="348" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A348" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="349">
-      <c r="A349" s="1" t="n">
+    <row r="349" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A349" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="350">
-      <c r="A350" s="1" t="n">
+    <row r="350" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A350" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="351">
-      <c r="A351" s="1" t="n">
+    <row r="351" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A351" s="1">
         <v>36</v>
       </c>
     </row>
-    <row r="352">
-      <c r="A352" s="1" t="n">
+    <row r="352" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A352" s="1">
         <v>37</v>
       </c>
     </row>
-    <row r="353">
-      <c r="A353" s="1" t="n">
+    <row r="353" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A353" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="354">
-      <c r="A354" s="1" t="n">
+    <row r="354" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A354" s="1">
         <v>39</v>
       </c>
     </row>
-    <row r="355">
-      <c r="A355" s="1" t="n">
+    <row r="355" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A355" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="356">
-      <c r="A356" s="1" t="n">
+    <row r="356" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A356" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="357">
-      <c r="A357" s="1" t="n">
+    <row r="357" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A357" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="358">
-      <c r="A358" s="1" t="n">
+    <row r="358" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A358" s="1">
         <v>43</v>
       </c>
     </row>
-    <row r="359">
-      <c r="A359" s="1" t="n">
+    <row r="359" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A359" s="1">
         <v>44</v>
       </c>
     </row>
-    <row r="360">
-      <c r="A360" s="1" t="n">
+    <row r="360" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A360" s="1">
         <v>45</v>
       </c>
     </row>
-    <row r="361">
-      <c r="A361" s="1" t="n">
+    <row r="361" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A361" s="1">
         <v>46</v>
       </c>
     </row>
-    <row r="362">
-      <c r="A362" s="1" t="n">
+    <row r="362" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A362" s="1">
         <v>47</v>
       </c>
     </row>
-    <row r="363">
-      <c r="A363" s="1" t="n">
+    <row r="363" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A363" s="1">
         <v>48</v>
       </c>
     </row>
-    <row r="364">
-      <c r="A364" s="1" t="n">
+    <row r="364" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A364" s="1">
         <v>49</v>
       </c>
     </row>
-    <row r="365">
-      <c r="A365" s="1" t="n">
+    <row r="365" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A365" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="366">
-      <c r="A366" s="1" t="n">
+    <row r="366" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A366" s="1">
         <v>51</v>
       </c>
     </row>
-    <row r="367">
-      <c r="A367" s="1" t="n">
+    <row r="367" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A367" s="1">
         <v>52</v>
       </c>
     </row>
-    <row r="368">
-      <c r="A368" s="1" t="n">
+    <row r="368" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A368" s="1">
         <v>53</v>
       </c>
     </row>
-    <row r="369">
-      <c r="A369" s="1" t="n">
+    <row r="369" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A369" s="1">
         <v>54</v>
       </c>
     </row>
-    <row r="370">
-      <c r="A370" s="1" t="n">
+    <row r="370" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A370" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="371">
-      <c r="A371" s="1" t="n">
+    <row r="371" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A371" s="1">
         <v>56</v>
       </c>
     </row>
-    <row r="372">
-      <c r="A372" s="1" t="n">
+    <row r="372" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A372" s="1">
         <v>57</v>
       </c>
     </row>
-    <row r="373">
-      <c r="A373" s="1" t="n">
+    <row r="373" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A373" s="1">
         <v>58</v>
       </c>
     </row>
-    <row r="374">
-      <c r="A374" s="1" t="n">
+    <row r="374" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A374" s="1">
         <v>59</v>
       </c>
     </row>
-    <row r="375">
-      <c r="A375" s="1" t="n">
+    <row r="375" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A375" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="376">
-      <c r="A376" s="1" t="n">
+    <row r="376" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A376" s="1">
         <v>61</v>
       </c>
     </row>
-    <row r="377">
-      <c r="A377" s="1" t="n">
+    <row r="377" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A377" s="1">
         <v>62</v>
       </c>
     </row>
-    <row r="378">
-      <c r="A378" s="1" t="n">
+    <row r="378" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A378" s="1">
         <v>63</v>
       </c>
     </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
+    <row r="379" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A379" s="1">
         <v>64</v>
       </c>
     </row>
-    <row r="380">
-      <c r="A380" s="1" t="n">
+    <row r="380" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A380" s="1">
         <v>65</v>
       </c>
     </row>
-    <row r="381">
-      <c r="A381" s="1" t="n">
+    <row r="381" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A381" s="1">
         <v>66</v>
       </c>
     </row>
-    <row r="382">
-      <c r="A382" s="1" t="n">
+    <row r="382" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A382" s="1">
         <v>67</v>
       </c>
     </row>
-    <row r="383">
-      <c r="A383" s="1" t="n">
+    <row r="383" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A383" s="1">
         <v>68</v>
       </c>
     </row>
-    <row r="384">
-      <c r="A384" s="1" t="n">
+    <row r="384" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A384" s="1">
         <v>69</v>
       </c>
     </row>
-    <row r="385">
-      <c r="A385" s="1" t="n">
+    <row r="385" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A385" s="1">
         <v>70</v>
       </c>
     </row>
-    <row r="386">
-      <c r="A386" s="1" t="n">
+    <row r="386" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A386" s="1">
         <v>71</v>
       </c>
     </row>
-    <row r="387">
-      <c r="A387" s="1" t="n">
+    <row r="387" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A387" s="1">
         <v>72</v>
       </c>
     </row>
-    <row r="388">
-      <c r="A388" s="1" t="n">
+    <row r="388" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A388" s="1">
         <v>73</v>
       </c>
     </row>
-    <row r="389">
-      <c r="A389" s="1" t="n">
+    <row r="389" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A389" s="1">
         <v>74</v>
       </c>
     </row>
-    <row r="390">
-      <c r="A390" s="1" t="n">
+    <row r="390" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A390" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="391">
-      <c r="A391" s="1" t="n">
+    <row r="391" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A391" s="1">
         <v>76</v>
       </c>
     </row>
-    <row r="392">
-      <c r="A392" s="1" t="n">
+    <row r="392" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A392" s="1">
         <v>77</v>
       </c>
     </row>
-    <row r="393">
-      <c r="A393" s="1" t="n">
+    <row r="393" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A393" s="1">
         <v>78</v>
       </c>
     </row>
-    <row r="394">
-      <c r="A394" s="1" t="n">
+    <row r="394" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A394" s="1">
         <v>79</v>
       </c>
     </row>
-    <row r="395">
-      <c r="A395" s="1" t="n">
+    <row r="395" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A395" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="396">
-      <c r="A396" s="1" t="n">
+    <row r="396" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A396" s="1">
         <v>81</v>
       </c>
     </row>
-    <row r="397">
-      <c r="A397" s="1" t="n">
+    <row r="397" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A397" s="1">
         <v>82</v>
       </c>
     </row>
-    <row r="398">
-      <c r="A398" s="1" t="n">
+    <row r="398" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A398" s="1">
         <v>83</v>
       </c>
     </row>
-    <row r="399">
-      <c r="A399" s="1" t="n">
+    <row r="399" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A399" s="1">
         <v>84</v>
       </c>
     </row>
-    <row r="400">
-      <c r="A400" s="1" t="n">
+    <row r="400" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A400" s="1">
         <v>85</v>
       </c>
     </row>
-    <row r="401">
-      <c r="A401" s="1" t="n">
+    <row r="401" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A401" s="1">
         <v>86</v>
       </c>
     </row>
-    <row r="402">
-      <c r="A402" s="1" t="n">
+    <row r="402" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A402" s="1">
         <v>87</v>
       </c>
     </row>
-    <row r="403">
-      <c r="A403" s="1" t="n">
+    <row r="403" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A403" s="1">
         <v>88</v>
       </c>
     </row>
-    <row r="404">
-      <c r="A404" s="1" t="n">
+    <row r="404" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A404" s="1">
         <v>89</v>
       </c>
     </row>
-    <row r="405">
-      <c r="A405" s="1" t="n">
+    <row r="405" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A405" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="406">
-      <c r="A406" s="1" t="n">
+    <row r="406" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A406" s="1">
         <v>91</v>
       </c>
     </row>
-    <row r="407">
-      <c r="A407" s="1" t="n">
+    <row r="407" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A407" s="1">
         <v>92</v>
       </c>
     </row>
-    <row r="408">
-      <c r="A408" s="1" t="n">
+    <row r="408" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A408" s="1">
         <v>93</v>
       </c>
     </row>
-    <row r="409">
-      <c r="A409" s="1" t="n">
+    <row r="409" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A409" s="1">
         <v>94</v>
       </c>
     </row>
-    <row r="410">
-      <c r="A410" s="1" t="n">
+    <row r="410" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A410" s="1">
         <v>95</v>
       </c>
     </row>
-    <row r="411">
-      <c r="A411" s="1" t="n">
+    <row r="411" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A411" s="1">
         <v>96</v>
       </c>
     </row>
-    <row r="412">
-      <c r="A412" s="1" t="n">
+    <row r="412" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A412" s="1">
         <v>97</v>
       </c>
     </row>
-    <row r="413">
-      <c r="A413" s="1" t="n">
+    <row r="413" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A413" s="1">
         <v>98</v>
       </c>
     </row>
-    <row r="414">
-      <c r="A414" s="1" t="n">
+    <row r="414" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A414" s="1">
         <v>99</v>
       </c>
     </row>
-    <row r="415">
-      <c r="A415" s="1" t="n">
+    <row r="415" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A415" s="1">
         <v>100</v>
       </c>
     </row>

--- a/CIFAR_Global.xlsx
+++ b/CIFAR_Global.xlsx
@@ -793,8 +793,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D415"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
+  <dimension ref="A1:E415"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="15.1640625" customWidth="1" min="1" max="1"/>
   </cols>
@@ -855,6 +855,9 @@
       <c r="D5" t="n">
         <v>0.1047</v>
       </c>
+      <c r="E5" t="n">
+        <v>0.0978</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -869,6 +872,9 @@
       <c r="D6" t="n">
         <v>0.4368</v>
       </c>
+      <c r="E6" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -883,6 +889,9 @@
       <c r="D7" t="n">
         <v>0.5074</v>
       </c>
+      <c r="E7" t="n">
+        <v>0.1436</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -897,6 +906,9 @@
       <c r="D8" t="n">
         <v>0.5438</v>
       </c>
+      <c r="E8" t="n">
+        <v>0.2324</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -911,6 +923,9 @@
       <c r="D9" t="n">
         <v>0.5579</v>
       </c>
+      <c r="E9" t="n">
+        <v>0.2914</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -922,6 +937,9 @@
       <c r="D10" t="n">
         <v>0.5887</v>
       </c>
+      <c r="E10" t="n">
+        <v>0.2805</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -933,6 +951,9 @@
       <c r="D11" t="n">
         <v>0.5992</v>
       </c>
+      <c r="E11" t="n">
+        <v>0.2537</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -944,6 +965,9 @@
       <c r="D12" t="n">
         <v>0.638</v>
       </c>
+      <c r="E12" t="n">
+        <v>0.2859</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -955,6 +979,9 @@
       <c r="D13" t="n">
         <v>0.623</v>
       </c>
+      <c r="E13" t="n">
+        <v>0.2921</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -966,455 +993,728 @@
       <c r="D14" t="n">
         <v>0.6455</v>
       </c>
+      <c r="E14" t="n">
+        <v>0.3605</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
         <v>11</v>
       </c>
+      <c r="E15" t="n">
+        <v>0.2782</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="E16" t="n">
+        <v>0.3548</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
         <v>13</v>
       </c>
+      <c r="E17" t="n">
+        <v>0.3451</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
         <v>14</v>
       </c>
+      <c r="E18" t="n">
+        <v>0.3366</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
         <v>15</v>
       </c>
+      <c r="E19" t="n">
+        <v>0.3236</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
         <v>16</v>
       </c>
+      <c r="E20" t="n">
+        <v>0.3423</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
         <v>17</v>
       </c>
+      <c r="E21" t="n">
+        <v>0.392</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
         <v>18</v>
       </c>
+      <c r="E22" t="n">
+        <v>0.3851</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
         <v>19</v>
       </c>
+      <c r="E23" t="n">
+        <v>0.3529</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
         <v>20</v>
       </c>
+      <c r="E24" t="n">
+        <v>0.3535</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
         <v>21</v>
       </c>
+      <c r="E25" t="n">
+        <v>0.3781</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
         <v>22</v>
       </c>
+      <c r="E26" t="n">
+        <v>0.3692</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
         <v>23</v>
       </c>
+      <c r="E27" t="n">
+        <v>0.3728</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
         <v>24</v>
       </c>
+      <c r="E28" t="n">
+        <v>0.3407</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
         <v>25</v>
       </c>
+      <c r="E29" t="n">
+        <v>0.4085</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
         <v>26</v>
       </c>
+      <c r="E30" t="n">
+        <v>0.3367</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
         <v>27</v>
       </c>
+      <c r="E31" t="n">
+        <v>0.4233</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
         <v>28</v>
       </c>
+      <c r="E32" t="n">
+        <v>0.3718</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
         <v>29</v>
       </c>
+      <c r="E33" t="n">
+        <v>0.3846</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
         <v>30</v>
       </c>
+      <c r="E34" t="n">
+        <v>0.4016</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
         <v>31</v>
       </c>
+      <c r="E35" t="n">
+        <v>0.3877</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
         <v>32</v>
       </c>
+      <c r="E36" t="n">
+        <v>0.3932</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
         <v>33</v>
       </c>
+      <c r="E37" t="n">
+        <v>0.4221</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
         <v>34</v>
       </c>
+      <c r="E38" t="n">
+        <v>0.3976</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
         <v>35</v>
       </c>
+      <c r="E39" t="n">
+        <v>0.4136</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
         <v>36</v>
       </c>
+      <c r="E40" t="n">
+        <v>0.4358</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
         <v>37</v>
       </c>
+      <c r="E41" t="n">
+        <v>0.4188</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
         <v>38</v>
       </c>
+      <c r="E42" t="n">
+        <v>0.4136</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
         <v>39</v>
       </c>
+      <c r="E43" t="n">
+        <v>0.4323</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
         <v>40</v>
       </c>
+      <c r="E44" t="n">
+        <v>0.4034</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
         <v>41</v>
       </c>
+      <c r="E45" t="n">
+        <v>0.4305</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
         <v>42</v>
       </c>
+      <c r="E46" t="n">
+        <v>0.4129</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
         <v>43</v>
       </c>
+      <c r="E47" t="n">
+        <v>0.4355</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
         <v>44</v>
       </c>
+      <c r="E48" t="n">
+        <v>0.4359</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
         <v>45</v>
       </c>
+      <c r="E49" t="n">
+        <v>0.4309</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
         <v>46</v>
       </c>
+      <c r="E50" t="n">
+        <v>0.4133</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
         <v>47</v>
       </c>
+      <c r="E51" t="n">
+        <v>0.4394</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
         <v>48</v>
       </c>
+      <c r="E52" t="n">
+        <v>0.4537</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
         <v>49</v>
       </c>
+      <c r="E53" t="n">
+        <v>0.4597</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
         <v>50</v>
       </c>
+      <c r="E54" t="n">
+        <v>0.4371</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
         <v>51</v>
       </c>
+      <c r="E55" t="n">
+        <v>0.4568</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
         <v>52</v>
       </c>
+      <c r="E56" t="n">
+        <v>0.4646</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
         <v>53</v>
       </c>
+      <c r="E57" t="n">
+        <v>0.4916</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
         <v>54</v>
       </c>
+      <c r="E58" t="n">
+        <v>0.4603</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="E59" t="n">
+        <v>0.4577</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
         <v>56</v>
       </c>
+      <c r="E60" t="n">
+        <v>0.4607</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
         <v>57</v>
       </c>
+      <c r="E61" t="n">
+        <v>0.4317</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
         <v>58</v>
       </c>
+      <c r="E62" t="n">
+        <v>0.4537</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
         <v>59</v>
       </c>
+      <c r="E63" t="n">
+        <v>0.4912</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
         <v>60</v>
       </c>
+      <c r="E64" t="n">
+        <v>0.442</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
         <v>61</v>
       </c>
+      <c r="E65" t="n">
+        <v>0.4461</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
         <v>62</v>
       </c>
+      <c r="E66" t="n">
+        <v>0.4288</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
         <v>63</v>
       </c>
+      <c r="E67" t="n">
+        <v>0.4688</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
         <v>64</v>
       </c>
+      <c r="E68" t="n">
+        <v>0.4542</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
         <v>65</v>
       </c>
+      <c r="E69" t="n">
+        <v>0.4656</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
         <v>66</v>
       </c>
+      <c r="E70" t="n">
+        <v>0.4638</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
         <v>67</v>
       </c>
+      <c r="E71" t="n">
+        <v>0.4436</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
         <v>68</v>
       </c>
+      <c r="E72" t="n">
+        <v>0.4336</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
         <v>69</v>
       </c>
+      <c r="E73" t="n">
+        <v>0.444</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
         <v>70</v>
       </c>
+      <c r="E74" t="n">
+        <v>0.4741</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
         <v>71</v>
       </c>
+      <c r="E75" t="n">
+        <v>0.4924</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
         <v>72</v>
       </c>
+      <c r="E76" t="n">
+        <v>0.4861</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
         <v>73</v>
       </c>
+      <c r="E77" t="n">
+        <v>0.4725</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
         <v>74</v>
       </c>
+      <c r="E78" t="n">
+        <v>0.4742</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
         <v>75</v>
       </c>
+      <c r="E79" t="n">
+        <v>0.4487</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
         <v>76</v>
       </c>
+      <c r="E80" t="n">
+        <v>0.4292</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
         <v>77</v>
       </c>
+      <c r="E81" t="n">
+        <v>0.455</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
         <v>78</v>
       </c>
+      <c r="E82" t="n">
+        <v>0.4811</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
         <v>79</v>
       </c>
+      <c r="E83" t="n">
+        <v>0.4628</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
         <v>80</v>
       </c>
+      <c r="E84" t="n">
+        <v>0.4716</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
         <v>81</v>
       </c>
+      <c r="E85" t="n">
+        <v>0.4518</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
         <v>82</v>
       </c>
+      <c r="E86" t="n">
+        <v>0.4601</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
         <v>83</v>
       </c>
+      <c r="E87" t="n">
+        <v>0.4671</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
         <v>84</v>
       </c>
+      <c r="E88" t="n">
+        <v>0.4626</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
         <v>85</v>
       </c>
+      <c r="E89" t="n">
+        <v>0.4746</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
         <v>86</v>
       </c>
+      <c r="E90" t="n">
+        <v>0.464</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
         <v>87</v>
       </c>
+      <c r="E91" t="n">
+        <v>0.4874</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
         <v>88</v>
       </c>
+      <c r="E92" t="n">
+        <v>0.4823</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
         <v>89</v>
       </c>
+      <c r="E93" t="n">
+        <v>0.4797</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
         <v>90</v>
       </c>
+      <c r="E94" t="n">
+        <v>0.4738</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
         <v>91</v>
       </c>
+      <c r="E95" t="n">
+        <v>0.4793</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
         <v>92</v>
       </c>
+      <c r="E96" t="n">
+        <v>0.4656</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="E97" t="n">
+        <v>0.4827</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
         <v>94</v>
       </c>
+      <c r="E98" t="n">
+        <v>0.4565</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
         <v>95</v>
       </c>
+      <c r="E99" t="n">
+        <v>0.4743</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
         <v>96</v>
       </c>
+      <c r="E100" t="n">
+        <v>0.4465</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
         <v>97</v>
       </c>
+      <c r="E101" t="n">
+        <v>0.446</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
         <v>98</v>
       </c>
+      <c r="E102" t="n">
+        <v>0.4789</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
         <v>99</v>
       </c>
+      <c r="E103" t="n">
+        <v>0.457</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.4655</v>
       </c>
     </row>
     <row r="106">
@@ -1444,6 +1744,9 @@
       <c r="D108" t="n">
         <v>1</v>
       </c>
+      <c r="E108" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -1458,6 +1761,9 @@
       <c r="D109" t="n">
         <v>1</v>
       </c>
+      <c r="E109" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -1472,6 +1778,9 @@
       <c r="D110" t="n">
         <v>1</v>
       </c>
+      <c r="E110" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -1486,6 +1795,9 @@
       <c r="D111" t="n">
         <v>1</v>
       </c>
+      <c r="E111" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -1500,6 +1812,9 @@
       <c r="D112" t="n">
         <v>0.5</v>
       </c>
+      <c r="E112" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -1511,6 +1826,9 @@
       <c r="D113" t="n">
         <v>1</v>
       </c>
+      <c r="E113" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -1522,6 +1840,9 @@
       <c r="D114" t="n">
         <v>1</v>
       </c>
+      <c r="E114" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -1533,6 +1854,9 @@
       <c r="D115" t="n">
         <v>1</v>
       </c>
+      <c r="E115" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -1544,6 +1868,9 @@
       <c r="D116" t="n">
         <v>0.6666666666666666</v>
       </c>
+      <c r="E116" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -1555,455 +1882,728 @@
       <c r="D117" t="n">
         <v>1</v>
       </c>
+      <c r="E117" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
         <v>11</v>
       </c>
+      <c r="E118" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="E119" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
         <v>13</v>
       </c>
+      <c r="E120" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
         <v>14</v>
       </c>
+      <c r="E121" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
         <v>15</v>
       </c>
+      <c r="E122" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
         <v>16</v>
       </c>
+      <c r="E123" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
         <v>17</v>
       </c>
+      <c r="E124" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
         <v>18</v>
       </c>
+      <c r="E125" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
         <v>19</v>
       </c>
+      <c r="E126" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
         <v>20</v>
       </c>
+      <c r="E127" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
         <v>21</v>
       </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
         <v>22</v>
       </c>
+      <c r="E129" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
         <v>23</v>
       </c>
+      <c r="E130" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
         <v>24</v>
       </c>
+      <c r="E131" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
         <v>25</v>
       </c>
+      <c r="E132" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
         <v>26</v>
       </c>
+      <c r="E133" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
         <v>27</v>
       </c>
+      <c r="E134" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
         <v>28</v>
       </c>
+      <c r="E135" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
         <v>29</v>
       </c>
+      <c r="E136" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
         <v>30</v>
       </c>
+      <c r="E137" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
         <v>31</v>
       </c>
+      <c r="E138" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
         <v>32</v>
       </c>
+      <c r="E139" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
         <v>33</v>
       </c>
+      <c r="E140" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
         <v>34</v>
       </c>
+      <c r="E141" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
         <v>35</v>
       </c>
+      <c r="E142" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
         <v>36</v>
       </c>
+      <c r="E143" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
         <v>37</v>
       </c>
+      <c r="E144" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
         <v>38</v>
       </c>
+      <c r="E145" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
         <v>39</v>
       </c>
+      <c r="E146" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
         <v>40</v>
       </c>
+      <c r="E147" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
         <v>41</v>
       </c>
+      <c r="E148" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
         <v>42</v>
       </c>
+      <c r="E149" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
         <v>43</v>
       </c>
+      <c r="E150" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
         <v>44</v>
       </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
         <v>45</v>
       </c>
+      <c r="E152" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
         <v>46</v>
       </c>
+      <c r="E153" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
         <v>47</v>
       </c>
+      <c r="E154" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
         <v>48</v>
       </c>
+      <c r="E155" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
         <v>49</v>
       </c>
+      <c r="E156" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
         <v>50</v>
       </c>
+      <c r="E157" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
         <v>51</v>
       </c>
+      <c r="E158" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
         <v>52</v>
       </c>
+      <c r="E159" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
         <v>53</v>
       </c>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
         <v>54</v>
       </c>
+      <c r="E161" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="E162" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
         <v>56</v>
       </c>
+      <c r="E163" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
         <v>57</v>
       </c>
+      <c r="E164" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
         <v>58</v>
       </c>
+      <c r="E165" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
         <v>59</v>
       </c>
+      <c r="E166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
         <v>60</v>
       </c>
+      <c r="E167" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
         <v>61</v>
       </c>
+      <c r="E168" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
         <v>62</v>
       </c>
+      <c r="E169" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
         <v>63</v>
       </c>
+      <c r="E170" t="n">
+        <v>0.9333333333333333</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
         <v>64</v>
       </c>
+      <c r="E171" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
         <v>65</v>
       </c>
+      <c r="E172" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
         <v>66</v>
       </c>
+      <c r="E173" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
         <v>67</v>
       </c>
+      <c r="E174" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
         <v>68</v>
       </c>
+      <c r="E175" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
         <v>69</v>
       </c>
+      <c r="E176" t="n">
+        <v>0.9444444444444444</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
         <v>70</v>
       </c>
+      <c r="E177" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
         <v>71</v>
       </c>
+      <c r="E178" t="n">
+        <v>0.9230769230769231</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
         <v>72</v>
       </c>
+      <c r="E179" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
         <v>73</v>
       </c>
+      <c r="E180" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
         <v>74</v>
       </c>
+      <c r="E181" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
         <v>75</v>
       </c>
+      <c r="E182" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
         <v>76</v>
       </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
         <v>77</v>
       </c>
+      <c r="E184" t="n">
+        <v>0.9444444444444444</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
         <v>78</v>
       </c>
+      <c r="E185" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
         <v>79</v>
       </c>
+      <c r="E186" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
         <v>80</v>
       </c>
+      <c r="E187" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
         <v>81</v>
       </c>
+      <c r="E188" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
         <v>82</v>
       </c>
+      <c r="E189" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
         <v>83</v>
       </c>
+      <c r="E190" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
         <v>84</v>
       </c>
+      <c r="E191" t="n">
+        <v>0.05555555555555555</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
         <v>85</v>
       </c>
+      <c r="E192" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
         <v>86</v>
       </c>
+      <c r="E193" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
         <v>87</v>
       </c>
+      <c r="E194" t="n">
+        <v>0.9411764705882353</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
         <v>88</v>
       </c>
+      <c r="E195" t="n">
+        <v>0.8235294117647058</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
         <v>89</v>
       </c>
+      <c r="E196" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
         <v>90</v>
       </c>
+      <c r="E197" t="n">
+        <v>0.0625</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
         <v>91</v>
       </c>
+      <c r="E198" t="n">
+        <v>0.8947368421052632</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
         <v>92</v>
       </c>
+      <c r="E199" t="n">
+        <v>0.9523809523809523</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="E200" t="n">
+        <v>0.9333333333333333</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
         <v>94</v>
       </c>
+      <c r="E201" t="n">
+        <v>0.05263157894736842</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
         <v>95</v>
       </c>
+      <c r="E202" t="n">
+        <v>0.8666666666666667</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
         <v>96</v>
       </c>
+      <c r="E203" t="n">
+        <v>0.05882352941176471</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
         <v>97</v>
       </c>
+      <c r="E204" t="n">
+        <v>0.9444444444444444</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
         <v>98</v>
       </c>
+      <c r="E205" t="n">
+        <v>0.8636363636363636</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
         <v>99</v>
       </c>
+      <c r="E206" t="n">
+        <v>0.7647058823529411</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="E207" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="210">
@@ -2033,6 +2633,9 @@
       <c r="D212" t="n">
         <v>0.9785</v>
       </c>
+      <c r="E212" t="n">
+        <v>0.9709923076923077</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -2047,6 +2650,9 @@
       <c r="D213" t="n">
         <v>0.9876333333333333</v>
       </c>
+      <c r="E213" t="n">
+        <v>0.9801818181818184</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
@@ -2061,6 +2667,9 @@
       <c r="D214" t="n">
         <v>0.9711333333333334</v>
       </c>
+      <c r="E214" t="n">
+        <v>0.9762090909090908</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
@@ -2075,6 +2684,9 @@
       <c r="D215" t="n">
         <v>0.9834000000000001</v>
       </c>
+      <c r="E215" t="n">
+        <v>0.97499</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
@@ -2089,6 +2701,9 @@
       <c r="D216" t="n">
         <v>0.9816666666666668</v>
       </c>
+      <c r="E216" t="n">
+        <v>0.9700941176470588</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
@@ -2100,6 +2715,9 @@
       <c r="D217" t="n">
         <v>0.97925</v>
       </c>
+      <c r="E217" t="n">
+        <v>0.9712916666666666</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
@@ -2110,6 +2728,9 @@
       </c>
       <c r="D218" t="n">
         <v>0.9803333333333333</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0.9814846153846155</v>
       </c>
     </row>
     <row r="219">
@@ -2124,6 +2745,9 @@
           <t>N/A</t>
         </is>
       </c>
+      <c r="E219" t="n">
+        <v>0.9802</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
@@ -2137,6 +2761,9 @@
       <c r="D220" t="n">
         <v>0.9706666666666667</v>
       </c>
+      <c r="E220" t="n">
+        <v>0.9824615384615385</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -2148,455 +2775,728 @@
       <c r="D221" t="n">
         <v>0.9721</v>
       </c>
+      <c r="E221" t="n">
+        <v>0.9902500000000001</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
         <v>11</v>
       </c>
+      <c r="E222" t="n">
+        <v>0.9826875000000002</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="E223" t="n">
+        <v>0.980375</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
         <v>13</v>
       </c>
+      <c r="E224" t="n">
+        <v>0.9835357142857143</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
         <v>14</v>
       </c>
+      <c r="E225" t="n">
+        <v>0.9790777777777778</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
         <v>15</v>
       </c>
+      <c r="E226" t="n">
+        <v>0.9892200000000001</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
         <v>16</v>
       </c>
+      <c r="E227" t="n">
+        <v>0.97965</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
         <v>17</v>
       </c>
+      <c r="E228" t="n">
+        <v>0.9833428571428572</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
         <v>18</v>
       </c>
+      <c r="E229" t="n">
+        <v>0.9876499999999999</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
         <v>19</v>
       </c>
+      <c r="E230" t="n">
+        <v>0.9819428571428572</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
         <v>20</v>
       </c>
+      <c r="E231" t="n">
+        <v>0.9856</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
         <v>21</v>
       </c>
+      <c r="E232" t="n">
+        <v>0.9883857142857143</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
         <v>22</v>
       </c>
+      <c r="E233" t="n">
+        <v>0.9915222222222222</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
         <v>23</v>
       </c>
+      <c r="E234" t="n">
+        <v>0.9821090909090909</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
         <v>24</v>
       </c>
+      <c r="E235" t="n">
+        <v>0.988892857142857</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
         <v>25</v>
       </c>
+      <c r="E236" t="n">
+        <v>0.9878416666666667</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
         <v>26</v>
       </c>
+      <c r="E237" t="n">
+        <v>0.9878833333333333</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
         <v>27</v>
       </c>
+      <c r="E238" t="n">
+        <v>0.9911888888888889</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
         <v>28</v>
       </c>
+      <c r="E239" t="n">
+        <v>0.9864846153846153</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
         <v>29</v>
       </c>
+      <c r="E240" t="n">
+        <v>0.9853687499999999</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
         <v>30</v>
       </c>
+      <c r="E241" t="n">
+        <v>0.9859083333333333</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
         <v>31</v>
       </c>
+      <c r="E242" t="n">
+        <v>0.9875583333333333</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
         <v>32</v>
       </c>
+      <c r="E243" t="n">
+        <v>0.9885428571428572</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
         <v>33</v>
       </c>
+      <c r="E244" t="n">
+        <v>0.9870272727272728</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
         <v>34</v>
       </c>
+      <c r="E245" t="n">
+        <v>0.9875000000000002</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
         <v>35</v>
       </c>
+      <c r="E246" t="n">
+        <v>0.988288888888889</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
         <v>36</v>
       </c>
+      <c r="E247" t="n">
+        <v>0.9876083333333333</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
         <v>37</v>
       </c>
+      <c r="E248" t="n">
+        <v>0.9829363636363637</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
         <v>38</v>
       </c>
+      <c r="E249" t="n">
+        <v>0.9854454545454545</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
         <v>39</v>
       </c>
+      <c r="E250" t="n">
+        <v>0.9870266666666667</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
         <v>40</v>
       </c>
+      <c r="E251" t="n">
+        <v>0.9902571428571428</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
         <v>41</v>
       </c>
+      <c r="E252" t="n">
+        <v>0.98739375</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
         <v>42</v>
       </c>
+      <c r="E253" t="n">
+        <v>0.9869454545454545</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
         <v>43</v>
       </c>
+      <c r="E254" t="n">
+        <v>0.9892727272727274</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
         <v>44</v>
       </c>
+      <c r="E255" t="n">
+        <v>0.9848555555555557</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
         <v>45</v>
       </c>
+      <c r="E256" t="n">
+        <v>0.9867076923076923</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
         <v>46</v>
       </c>
+      <c r="E257" t="n">
+        <v>0.9894666666666667</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
         <v>47</v>
       </c>
+      <c r="E258" t="n">
+        <v>0.98924</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
         <v>48</v>
       </c>
+      <c r="E259" t="n">
+        <v>0.9895615384615386</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
         <v>49</v>
       </c>
+      <c r="E260" t="n">
+        <v>0.9855749999999999</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
         <v>50</v>
       </c>
+      <c r="E261" t="n">
+        <v>0.9872181818181819</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
         <v>51</v>
       </c>
+      <c r="E262" t="n">
+        <v>0.98842</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
         <v>52</v>
       </c>
+      <c r="E263" t="n">
+        <v>0.98715</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
         <v>53</v>
       </c>
+      <c r="E264" t="n">
+        <v>0.9866714285714284</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
         <v>54</v>
       </c>
+      <c r="E265" t="n">
+        <v>0.9876500000000002</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="E266" t="n">
+        <v>0.9872777777777778</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
         <v>56</v>
       </c>
+      <c r="E267" t="n">
+        <v>0.9873142857142857</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
         <v>57</v>
       </c>
+      <c r="E268" t="n">
+        <v>0.9854111111111111</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
         <v>58</v>
       </c>
+      <c r="E269" t="n">
+        <v>0.9871545454545455</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
         <v>59</v>
       </c>
+      <c r="E270" t="n">
+        <v>0.9863818181818181</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
         <v>60</v>
       </c>
+      <c r="E271" t="n">
+        <v>0.9846199999999999</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
         <v>61</v>
       </c>
+      <c r="E272" t="n">
+        <v>0.988</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
         <v>62</v>
       </c>
+      <c r="E273" t="n">
+        <v>0.9863800000000001</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
         <v>63</v>
       </c>
+      <c r="E274" t="n">
+        <v>0.9846</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
         <v>64</v>
       </c>
+      <c r="E275" t="n">
+        <v>0.9869416666666666</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
         <v>65</v>
       </c>
+      <c r="E276" t="n">
+        <v>0.9880272727272726</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
         <v>66</v>
       </c>
+      <c r="E277" t="n">
+        <v>0.9878</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
         <v>67</v>
       </c>
+      <c r="E278" t="n">
+        <v>0.988375</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
         <v>68</v>
       </c>
+      <c r="E279" t="n">
+        <v>0.98689</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
         <v>69</v>
       </c>
+      <c r="E280" t="n">
+        <v>0.9867416666666666</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
         <v>70</v>
       </c>
+      <c r="E281" t="n">
+        <v>0.9859166666666668</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
         <v>71</v>
       </c>
+      <c r="E282" t="n">
+        <v>0.9857823529411763</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
         <v>72</v>
       </c>
+      <c r="E283" t="n">
+        <v>0.9892846153846153</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
         <v>73</v>
       </c>
+      <c r="E284" t="n">
+        <v>0.9876833333333334</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
         <v>74</v>
       </c>
+      <c r="E285" t="n">
+        <v>0.9848499999999999</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
         <v>75</v>
       </c>
+      <c r="E286" t="n">
+        <v>0.9863214285714286</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
         <v>76</v>
       </c>
+      <c r="E287" t="n">
+        <v>0.9866923076923076</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
         <v>77</v>
       </c>
+      <c r="E288" t="n">
+        <v>0.98325</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
         <v>78</v>
       </c>
+      <c r="E289" t="n">
+        <v>0.9890777777777777</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
         <v>79</v>
       </c>
+      <c r="E290" t="n">
+        <v>0.988425</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
         <v>80</v>
       </c>
+      <c r="E291" t="n">
+        <v>0.9874599999999999</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
         <v>81</v>
       </c>
+      <c r="E292" t="n">
+        <v>0.9872583333333335</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
         <v>82</v>
       </c>
+      <c r="E293" t="n">
+        <v>0.9836499999999999</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
         <v>83</v>
       </c>
+      <c r="E294" t="n">
+        <v>0.9884692307692309</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
         <v>84</v>
       </c>
+      <c r="E295" t="n">
+        <v>0.9862833333333333</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
         <v>85</v>
       </c>
+      <c r="E296" t="n">
+        <v>0.9873454545454545</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
         <v>86</v>
       </c>
+      <c r="E297" t="n">
+        <v>0.9859266666666666</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
         <v>87</v>
       </c>
+      <c r="E298" t="n">
+        <v>0.9866230769230769</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
         <v>88</v>
       </c>
+      <c r="E299" t="n">
+        <v>0.9836076923076923</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
         <v>89</v>
       </c>
+      <c r="E300" t="n">
+        <v>0.9845533333333332</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
         <v>90</v>
       </c>
+      <c r="E301" t="n">
+        <v>0.9839714285714286</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
         <v>91</v>
       </c>
+      <c r="E302" t="n">
+        <v>0.9833545454545457</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
         <v>92</v>
       </c>
+      <c r="E303" t="n">
+        <v>0.9866</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="E304" t="n">
+        <v>0.9858333333333335</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
         <v>94</v>
       </c>
+      <c r="E305" t="n">
+        <v>0.9889545454545455</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
         <v>95</v>
       </c>
+      <c r="E306" t="n">
+        <v>0.9872533333333332</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
         <v>96</v>
       </c>
+      <c r="E307" t="n">
+        <v>0.9855692307692308</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
         <v>97</v>
       </c>
+      <c r="E308" t="n">
+        <v>0.9867166666666666</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
         <v>98</v>
       </c>
+      <c r="E309" t="n">
+        <v>0.9853375</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
         <v>99</v>
       </c>
+      <c r="E310" t="n">
+        <v>0.9862230769230768</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="E311" t="n">
+        <v>0.9857799999999999</v>
       </c>
     </row>
     <row r="314">
@@ -2626,6 +3526,9 @@
       <c r="D316" t="n">
         <v>0.0136</v>
       </c>
+      <c r="E316" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
@@ -2640,6 +3543,9 @@
       <c r="D317" t="n">
         <v>0.145</v>
       </c>
+      <c r="E317" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
@@ -2654,6 +3560,9 @@
       <c r="D318" t="n">
         <v>0.1174</v>
       </c>
+      <c r="E318" t="n">
+        <v>0.0001</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
@@ -2668,6 +3577,9 @@
       <c r="D319" t="n">
         <v>0.146</v>
       </c>
+      <c r="E319" t="n">
+        <v>0.1163</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
@@ -2682,6 +3594,9 @@
       <c r="D320" t="n">
         <v>0.1194</v>
       </c>
+      <c r="E320" t="n">
+        <v>0.2358</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
@@ -2693,6 +3608,9 @@
       <c r="D321" t="n">
         <v>0.0993</v>
       </c>
+      <c r="E321" t="n">
+        <v>0.6919999999999999</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
@@ -2704,6 +3622,9 @@
       <c r="D322" t="n">
         <v>0.1138</v>
       </c>
+      <c r="E322" t="n">
+        <v>0.9532</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
@@ -2715,6 +3636,9 @@
       <c r="D323" t="n">
         <v>0.0989</v>
       </c>
+      <c r="E323" t="n">
+        <v>0.7634</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
@@ -2726,6 +3650,9 @@
       <c r="D324" t="n">
         <v>0.0815</v>
       </c>
+      <c r="E324" t="n">
+        <v>0.7855</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
@@ -2737,455 +3664,728 @@
       <c r="D325" t="n">
         <v>0.09619999999999999</v>
       </c>
+      <c r="E325" t="n">
+        <v>0.4849</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
         <v>11</v>
       </c>
+      <c r="E326" t="n">
+        <v>0.9316</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="E327" t="n">
+        <v>0.0592</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
         <v>13</v>
       </c>
+      <c r="E328" t="n">
+        <v>0.7209</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
         <v>14</v>
       </c>
+      <c r="E329" t="n">
+        <v>0.6419</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
         <v>15</v>
       </c>
+      <c r="E330" t="n">
+        <v>0.8536</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
         <v>16</v>
       </c>
+      <c r="E331" t="n">
+        <v>0.7335</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
         <v>17</v>
       </c>
+      <c r="E332" t="n">
+        <v>0.4055</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
         <v>18</v>
       </c>
+      <c r="E333" t="n">
+        <v>0.5384</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
         <v>19</v>
       </c>
+      <c r="E334" t="n">
+        <v>0.7105</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
         <v>20</v>
       </c>
+      <c r="E335" t="n">
+        <v>0.7187</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
         <v>21</v>
       </c>
+      <c r="E336" t="n">
+        <v>0.373</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
         <v>22</v>
       </c>
+      <c r="E337" t="n">
+        <v>0.7562</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
         <v>23</v>
       </c>
+      <c r="E338" t="n">
+        <v>0.6973</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
         <v>24</v>
       </c>
+      <c r="E339" t="n">
+        <v>0.8647</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
         <v>25</v>
       </c>
+      <c r="E340" t="n">
+        <v>0.5508</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
         <v>26</v>
       </c>
+      <c r="E341" t="n">
+        <v>0.8935999999999999</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
         <v>27</v>
       </c>
+      <c r="E342" t="n">
+        <v>0.3989</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
         <v>28</v>
       </c>
+      <c r="E343" t="n">
+        <v>0.7151</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
         <v>29</v>
       </c>
+      <c r="E344" t="n">
+        <v>0.5578</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
         <v>30</v>
       </c>
+      <c r="E345" t="n">
+        <v>0.4045</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
         <v>31</v>
       </c>
+      <c r="E346" t="n">
+        <v>0.5693</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
         <v>32</v>
       </c>
+      <c r="E347" t="n">
+        <v>0.5807</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
         <v>33</v>
       </c>
+      <c r="E348" t="n">
+        <v>0.5694</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
         <v>34</v>
       </c>
+      <c r="E349" t="n">
+        <v>0.5735</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
         <v>35</v>
       </c>
+      <c r="E350" t="n">
+        <v>0.5207000000000001</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
         <v>36</v>
       </c>
+      <c r="E351" t="n">
+        <v>0.2961</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
         <v>37</v>
       </c>
+      <c r="E352" t="n">
+        <v>0.2811</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
         <v>38</v>
       </c>
+      <c r="E353" t="n">
+        <v>0.4909</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
         <v>39</v>
       </c>
+      <c r="E354" t="n">
+        <v>0.3285</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
         <v>40</v>
       </c>
+      <c r="E355" t="n">
+        <v>0.5582</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
         <v>41</v>
       </c>
+      <c r="E356" t="n">
+        <v>0.2716</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
         <v>42</v>
       </c>
+      <c r="E357" t="n">
+        <v>0.3391</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
         <v>43</v>
       </c>
+      <c r="E358" t="n">
+        <v>0.2845</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
         <v>44</v>
       </c>
+      <c r="E359" t="n">
+        <v>0.222</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
         <v>45</v>
       </c>
+      <c r="E360" t="n">
+        <v>0.2468</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
         <v>46</v>
       </c>
+      <c r="E361" t="n">
+        <v>0.3934</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
         <v>47</v>
       </c>
+      <c r="E362" t="n">
+        <v>0.2665</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
         <v>48</v>
       </c>
+      <c r="E363" t="n">
+        <v>0.3036</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
         <v>49</v>
       </c>
+      <c r="E364" t="n">
+        <v>0.4545</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
         <v>50</v>
       </c>
+      <c r="E365" t="n">
+        <v>0.2605</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
         <v>51</v>
       </c>
+      <c r="E366" t="n">
+        <v>0.2831</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
         <v>52</v>
       </c>
+      <c r="E367" t="n">
+        <v>0.2075</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
         <v>53</v>
       </c>
+      <c r="E368" t="n">
+        <v>0.2072</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
         <v>54</v>
       </c>
+      <c r="E369" t="n">
+        <v>0.2641</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="E370" t="n">
+        <v>0.3773</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
         <v>56</v>
       </c>
+      <c r="E371" t="n">
+        <v>0.1953</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
         <v>57</v>
       </c>
+      <c r="E372" t="n">
+        <v>0.2344</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
         <v>58</v>
       </c>
+      <c r="E373" t="n">
+        <v>0.212</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
         <v>59</v>
       </c>
+      <c r="E374" t="n">
+        <v>0.106</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
         <v>60</v>
       </c>
+      <c r="E375" t="n">
+        <v>0.2001</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
         <v>61</v>
       </c>
+      <c r="E376" t="n">
+        <v>0.1647</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
         <v>62</v>
       </c>
+      <c r="E377" t="n">
+        <v>0.2335</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
         <v>63</v>
       </c>
+      <c r="E378" t="n">
+        <v>0.1531</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
         <v>64</v>
       </c>
+      <c r="E379" t="n">
+        <v>0.2344</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
         <v>65</v>
       </c>
+      <c r="E380" t="n">
+        <v>0.1842</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
         <v>66</v>
       </c>
+      <c r="E381" t="n">
+        <v>0.1686</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
         <v>67</v>
       </c>
+      <c r="E382" t="n">
+        <v>0.2066</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
         <v>68</v>
       </c>
+      <c r="E383" t="n">
+        <v>0.2286</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
         <v>69</v>
       </c>
+      <c r="E384" t="n">
+        <v>0.1397</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
         <v>70</v>
       </c>
+      <c r="E385" t="n">
+        <v>0.1318</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
         <v>71</v>
       </c>
+      <c r="E386" t="n">
+        <v>0.1606</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
         <v>72</v>
       </c>
+      <c r="E387" t="n">
+        <v>0.0901</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
         <v>73</v>
       </c>
+      <c r="E388" t="n">
+        <v>0.1774</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
         <v>74</v>
       </c>
+      <c r="E389" t="n">
+        <v>0.0789</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
         <v>75</v>
       </c>
+      <c r="E390" t="n">
+        <v>0.1373</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
         <v>76</v>
       </c>
+      <c r="E391" t="n">
+        <v>0.1282</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
         <v>77</v>
       </c>
+      <c r="E392" t="n">
+        <v>0.065</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
         <v>78</v>
       </c>
+      <c r="E393" t="n">
+        <v>0.1142</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
         <v>79</v>
       </c>
+      <c r="E394" t="n">
+        <v>0.1135</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
         <v>80</v>
       </c>
+      <c r="E395" t="n">
+        <v>0.0545</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
         <v>81</v>
       </c>
+      <c r="E396" t="n">
+        <v>0.0699</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
         <v>82</v>
       </c>
+      <c r="E397" t="n">
+        <v>0.07439999999999999</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
         <v>83</v>
       </c>
+      <c r="E398" t="n">
+        <v>0.0415</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
         <v>84</v>
       </c>
+      <c r="E399" t="n">
+        <v>0.0692</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
         <v>85</v>
       </c>
+      <c r="E400" t="n">
+        <v>0.0552</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
         <v>86</v>
       </c>
+      <c r="E401" t="n">
+        <v>0.046</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="n">
         <v>87</v>
       </c>
+      <c r="E402" t="n">
+        <v>0.0772</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
         <v>88</v>
       </c>
+      <c r="E403" t="n">
+        <v>0.0731</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
         <v>89</v>
       </c>
+      <c r="E404" t="n">
+        <v>0.0839</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
         <v>90</v>
       </c>
+      <c r="E405" t="n">
+        <v>0.0833</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
         <v>91</v>
       </c>
+      <c r="E406" t="n">
+        <v>0.0827</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="1" t="n">
         <v>92</v>
       </c>
+      <c r="E407" t="n">
+        <v>0.1303</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
         <v>93</v>
       </c>
+      <c r="E408" t="n">
+        <v>0.0513</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
         <v>94</v>
       </c>
+      <c r="E409" t="n">
+        <v>0.0463</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
         <v>95</v>
       </c>
+      <c r="E410" t="n">
+        <v>0.0631</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="n">
         <v>96</v>
       </c>
+      <c r="E411" t="n">
+        <v>0.0579</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
         <v>97</v>
       </c>
+      <c r="E412" t="n">
+        <v>0.0644</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
         <v>98</v>
       </c>
+      <c r="E413" t="n">
+        <v>0.0458</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="n">
         <v>99</v>
       </c>
+      <c r="E414" t="n">
+        <v>0.0687</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="E415" t="n">
+        <v>0.08550000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/CIFAR_Global.xlsx
+++ b/CIFAR_Global.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashleyau/Documents/PhD/Practical_Experiment/Finalised/Finalised_Algorithm_ResNet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E30B1412-69DE-4744-9E6A-84CBBE4EC5BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6B3852-47CC-874E-8D1E-0A211ADEADE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,10 +82,10 @@
     <t>Global Poisoning Accuracy</t>
   </si>
   <si>
-    <t>20 choose 10</t>
+    <t>From now on, I will use my algorithm's clustering and exclude conv</t>
   </si>
   <si>
-    <t>From now on, I will use my algorithm's clustering and exclude conv</t>
+    <t>20 choose 20</t>
   </si>
 </sst>
 </file>
@@ -192,10 +192,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4385,10 +4385,10 @@
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
-      <c r="Q2" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="R2" s="12"/>
+      <c r="Q2" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" s="11"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -4421,14 +4421,14 @@
       <c r="J3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
+      <c r="K3" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
       <c r="Q3" s="4" t="s">
         <v>10</v>
       </c>

--- a/CIFAR_Global.xlsx
+++ b/CIFAR_Global.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashleyau/Documents/PhD/Practical_Experiment/Finalised/Finalised_Algorithm_ResNet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64F67FF-8A7B-A943-8667-BEC2F630F8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB9022B-F738-FB43-B1E4-3DC42D06DE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
   <si>
     <t>100 Rounds</t>
   </si>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t>Global Poisoning Accuracy</t>
+  </si>
+  <si>
+    <t>Non-IID</t>
   </si>
 </sst>
 </file>
@@ -182,6 +185,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -195,14 +199,18 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFE78AA1"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1327,7 +1335,7 @@
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
-            <c:v>Exclude Conv</c:v>
+            <c:v>50C15 Exclude Conv</c:v>
           </c:tx>
           <c:spPr>
             <a:ln>
@@ -1862,8 +1870,341 @@
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>All Benign</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="E78AA1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$J$108:$J$207</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.14285714285714279</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.8571428571428571</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.8571428571428571</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.7142857142857143</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.88888888888888884</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.88888888888888884</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.88888888888888884</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.7142857142857143</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.8571428571428571</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.83333333333333337</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6E24-D84A-9277-8F71AAE8B43D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="0"/>
-          <c:order val="0"/>
+          <c:order val="1"/>
           <c:tx>
             <c:v>My Alg</c:v>
           </c:tx>
@@ -2174,336 +2515,6 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-6E24-D84A-9277-8F71AAE8B43D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>All Benign</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$J$108:$J$207</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="100"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.14285714285714279</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.875</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0.8571428571428571</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0.8571428571428571</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>0.7142857142857143</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>0.875</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>0.88888888888888884</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>0.88888888888888884</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>0.875</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>0.88888888888888884</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>0.7142857142857143</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>0.8571428571428571</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>0.83333333333333337</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>0.875</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>0.875</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>0.75</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-6E24-D84A-9277-8F71AAE8B43D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2740,8 +2751,341 @@
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>All Benign</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="E78AA1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$J$5:$J$104</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1351</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.31209999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.4748</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.51939999999999997</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.52939999999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.55589999999999995</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.56910000000000005</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.58940000000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.58860000000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.60450000000000004</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.59699999999999998</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.61839999999999995</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.61860000000000004</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.51749999999999996</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.61150000000000004</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.63329999999999997</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.6421</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.64290000000000003</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.64370000000000005</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.64690000000000003</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.65239999999999998</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.65939999999999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.65490000000000004</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.65990000000000004</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.65369999999999995</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.65749999999999997</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.66310000000000002</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.66500000000000004</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.65749999999999997</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.66139999999999999</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.67330000000000001</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.67200000000000004</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.67479999999999996</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.65869999999999995</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.66559999999999997</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.66949999999999998</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.67479999999999996</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.67279999999999995</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.67400000000000004</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.67259999999999998</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.67620000000000002</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.6774</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.67490000000000006</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.6754</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.67469999999999997</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.60019999999999996</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.66520000000000001</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.67689999999999995</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.67879999999999996</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.68159999999999998</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.67879999999999996</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.68079999999999996</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.67689999999999995</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.67430000000000001</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.68540000000000001</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.68220000000000003</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.68169999999999997</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.68159999999999998</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.68220000000000003</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.67920000000000003</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.68689999999999996</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.68369999999999997</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.68400000000000005</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.68340000000000001</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.6774</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.68610000000000004</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.67949999999999999</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.68159999999999998</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.68469999999999998</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.67989999999999995</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.68020000000000003</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.68110000000000004</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.68020000000000003</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.67490000000000006</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.68069999999999997</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.67889999999999995</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.68200000000000005</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.68130000000000002</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.68530000000000002</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.68420000000000003</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.68459999999999999</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.68379999999999996</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.68200000000000005</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.68579999999999997</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.68899999999999995</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.68679999999999997</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.68210000000000004</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.68440000000000001</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.68200000000000005</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.68259999999999998</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.68130000000000002</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.67889999999999995</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.67920000000000003</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.67779999999999996</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.6784</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.67659999999999998</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.66969999999999996</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.65920000000000001</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.67149999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-91CF-B644-853C-44CDAECB5D07}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="0"/>
-          <c:order val="0"/>
+          <c:order val="1"/>
           <c:tx>
             <c:v>My Alg</c:v>
           </c:tx>
@@ -3052,336 +3396,6 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-91CF-B644-853C-44CDAECB5D07}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>All Benign</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$J$5:$J$104</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="100"/>
-                <c:pt idx="0">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.1351</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.31209999999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.4748</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.51939999999999997</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.52939999999999998</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.55589999999999995</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.56910000000000005</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.58940000000000003</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.58860000000000001</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.60450000000000004</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.59699999999999998</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.61839999999999995</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.61860000000000004</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.51749999999999996</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.61150000000000004</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.63329999999999997</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.6421</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.64290000000000003</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.64370000000000005</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.64690000000000003</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.65239999999999998</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.65939999999999999</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.65490000000000004</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.65990000000000004</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.65369999999999995</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.65749999999999997</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.66310000000000002</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.66500000000000004</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.65749999999999997</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.66139999999999999</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.67330000000000001</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.67200000000000004</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.67479999999999996</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.65869999999999995</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.66559999999999997</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.66949999999999998</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.67479999999999996</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.67279999999999995</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.67400000000000004</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.67259999999999998</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.67620000000000002</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.6774</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.67490000000000006</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.6754</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0.67469999999999997</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.60019999999999996</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.66520000000000001</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.67689999999999995</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.67879999999999996</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.68159999999999998</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.67879999999999996</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.68079999999999996</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.67689999999999995</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.67430000000000001</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.68540000000000001</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.68220000000000003</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.68169999999999997</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.68159999999999998</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.68220000000000003</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.67920000000000003</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.68689999999999996</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.68369999999999997</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0.68400000000000005</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0.68340000000000001</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0.6774</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0.68610000000000004</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>0.67949999999999999</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>0.68159999999999998</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0.68469999999999998</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0.67989999999999995</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>0.68020000000000003</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>0.68110000000000004</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>0.68020000000000003</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>0.67490000000000006</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>0.68069999999999997</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>0.67889999999999995</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>0.68200000000000005</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>0.68130000000000002</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>0.68530000000000002</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>0.68420000000000003</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>0.68459999999999999</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>0.68379999999999996</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>0.68200000000000005</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>0.68579999999999997</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>0.68899999999999995</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>0.68679999999999997</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>0.68210000000000004</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>0.68440000000000001</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>0.68200000000000005</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>0.68259999999999998</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>0.68130000000000002</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>0.67889999999999995</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>0.67920000000000003</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>0.67779999999999996</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>0.6784</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>0.67659999999999998</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>0.66969999999999996</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>0.65920000000000001</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>0.67149999999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-91CF-B644-853C-44CDAECB5D07}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3602,16 +3616,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>72813</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>85513</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>100753</xdr:rowOff>
+      <xdr:rowOff>88053</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>749300</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>838200</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3638,16 +3652,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>148721</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>101641</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>59821</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>139741</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>769698</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>115455</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>756998</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>153555</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3674,16 +3688,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>75045</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>116609</xdr:rowOff>
+      <xdr:rowOff>40409</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>774829</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>851029</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>115582</xdr:rowOff>
+      <xdr:rowOff>39382</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4028,7 +4042,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R415"/>
+  <dimension ref="A1:U415"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -4036,41 +4050,54 @@
     <col min="6" max="6" width="11.83203125" customWidth="1"/>
     <col min="7" max="7" width="18.5" customWidth="1"/>
     <col min="9" max="9" width="17.83203125" customWidth="1"/>
+    <col min="11" max="11" width="11.83203125" customWidth="1"/>
     <col min="17" max="17" width="11.83203125" customWidth="1"/>
+    <col min="19" max="19" width="15.1640625" customWidth="1"/>
+    <col min="20" max="20" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="8"/>
+      <c r="D2" s="9"/>
       <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="Q2" s="12" t="s">
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="R2" s="13"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q2" s="13"/>
+      <c r="S2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="T2" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="U2" s="12"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -4101,33 +4128,42 @@
       <c r="J3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="L3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="4" t="s">
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="T3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="R3" s="4"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="U3" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="8"/>
-      <c r="I4" s="7" t="s">
+      <c r="H4" s="9"/>
+      <c r="I4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="8"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="J4" s="9"/>
+      <c r="S4" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -4158,11 +4194,14 @@
       <c r="J5">
         <v>0.1</v>
       </c>
-      <c r="Q5">
+      <c r="K5">
         <v>9.4E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -4193,11 +4232,14 @@
       <c r="J6">
         <v>0.1351</v>
       </c>
-      <c r="Q6">
+      <c r="K6">
         <v>0.16880000000000001</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -4228,11 +4270,14 @@
       <c r="J7">
         <v>0.31209999999999999</v>
       </c>
-      <c r="Q7">
+      <c r="K7">
         <v>0.432</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -4263,11 +4308,14 @@
       <c r="J8">
         <v>0.4748</v>
       </c>
-      <c r="Q8">
+      <c r="K8">
         <v>0.5504</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -4298,11 +4346,14 @@
       <c r="J9">
         <v>0.51939999999999997</v>
       </c>
-      <c r="Q9">
+      <c r="K9">
         <v>0.60099999999999998</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -4330,11 +4381,14 @@
       <c r="J10">
         <v>0.52939999999999998</v>
       </c>
-      <c r="Q10">
+      <c r="K10">
         <v>0.62350000000000005</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -4362,11 +4416,14 @@
       <c r="J11">
         <v>0.55589999999999995</v>
       </c>
-      <c r="Q11">
+      <c r="K11">
         <v>0.64570000000000005</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -4394,11 +4451,14 @@
       <c r="J12">
         <v>0.56910000000000005</v>
       </c>
-      <c r="Q12">
+      <c r="K12">
         <v>0.65449999999999997</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -4426,11 +4486,14 @@
       <c r="J13">
         <v>0.58940000000000003</v>
       </c>
-      <c r="Q13">
+      <c r="K13">
         <v>0.66279999999999994</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -4458,11 +4521,14 @@
       <c r="J14">
         <v>0.58860000000000001</v>
       </c>
-      <c r="Q14">
+      <c r="K14">
         <v>0.66659999999999997</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -4484,11 +4550,14 @@
       <c r="J15">
         <v>0.60450000000000004</v>
       </c>
-      <c r="Q15">
+      <c r="K15">
         <v>0.67190000000000005</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -4510,11 +4579,14 @@
       <c r="J16">
         <v>0.59699999999999998</v>
       </c>
-      <c r="Q16">
+      <c r="K16">
         <v>0.67949999999999999</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S16" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -4536,11 +4608,14 @@
       <c r="J17">
         <v>0.61839999999999995</v>
       </c>
-      <c r="Q17">
+      <c r="K17">
         <v>0.68049999999999999</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S17" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -4562,11 +4637,14 @@
       <c r="J18">
         <v>0.61860000000000004</v>
       </c>
-      <c r="Q18">
+      <c r="K18">
         <v>0.68740000000000001</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S18" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -4588,11 +4666,14 @@
       <c r="J19">
         <v>0.51749999999999996</v>
       </c>
-      <c r="Q19">
+      <c r="K19">
         <v>0.68730000000000002</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S19" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -4614,11 +4695,14 @@
       <c r="J20">
         <v>0.61150000000000004</v>
       </c>
-      <c r="Q20">
+      <c r="K20">
         <v>0.68910000000000005</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S20" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -4640,11 +4724,14 @@
       <c r="J21">
         <v>0.63329999999999997</v>
       </c>
-      <c r="Q21">
+      <c r="K21">
         <v>0.69369999999999998</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S21" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -4666,11 +4753,14 @@
       <c r="J22">
         <v>0.6421</v>
       </c>
-      <c r="Q22">
+      <c r="K22">
         <v>0.6915</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S22" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -4692,11 +4782,14 @@
       <c r="J23">
         <v>0.64290000000000003</v>
       </c>
-      <c r="Q23">
+      <c r="K23">
         <v>0.69140000000000001</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S23" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -4718,11 +4811,14 @@
       <c r="J24">
         <v>0.64370000000000005</v>
       </c>
-      <c r="Q24">
+      <c r="K24">
         <v>0.69259999999999999</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S24" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -4744,11 +4840,14 @@
       <c r="J25">
         <v>0.64690000000000003</v>
       </c>
-      <c r="Q25">
+      <c r="K25">
         <v>0.69430000000000003</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S25" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -4770,11 +4869,14 @@
       <c r="J26">
         <v>0.65239999999999998</v>
       </c>
-      <c r="Q26">
+      <c r="K26">
         <v>0.68889999999999996</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S26" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -4796,11 +4898,14 @@
       <c r="J27">
         <v>0.65939999999999999</v>
       </c>
-      <c r="Q27">
+      <c r="K27">
         <v>0.69569999999999999</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S27" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -4822,11 +4927,14 @@
       <c r="J28">
         <v>0.65490000000000004</v>
       </c>
-      <c r="Q28">
+      <c r="K28">
         <v>0.69510000000000005</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S28" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -4848,11 +4956,14 @@
       <c r="J29">
         <v>0.65990000000000004</v>
       </c>
-      <c r="Q29">
+      <c r="K29">
         <v>0.69510000000000005</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S29" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -4874,11 +4985,14 @@
       <c r="J30">
         <v>0.65369999999999995</v>
       </c>
-      <c r="Q30">
+      <c r="K30">
         <v>0.69269999999999998</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S30" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -4900,11 +5014,14 @@
       <c r="J31">
         <v>0.65749999999999997</v>
       </c>
-      <c r="Q31">
+      <c r="K31">
         <v>0.69369999999999998</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S31" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -4926,11 +5043,14 @@
       <c r="J32">
         <v>0.66310000000000002</v>
       </c>
-      <c r="Q32">
+      <c r="K32">
         <v>0.69189999999999996</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S32" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -4952,11 +5072,14 @@
       <c r="J33">
         <v>0.66500000000000004</v>
       </c>
-      <c r="Q33">
+      <c r="K33">
         <v>0.69450000000000001</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S33" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -4978,11 +5101,14 @@
       <c r="J34">
         <v>0.65749999999999997</v>
       </c>
-      <c r="Q34">
+      <c r="K34">
         <v>0.69650000000000001</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S34" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -5004,11 +5130,14 @@
       <c r="J35">
         <v>0.66139999999999999</v>
       </c>
-      <c r="Q35">
+      <c r="K35">
         <v>0.69410000000000005</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S35" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -5030,11 +5159,14 @@
       <c r="J36">
         <v>0.67330000000000001</v>
       </c>
-      <c r="Q36">
+      <c r="K36">
         <v>0.68869999999999998</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S36" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -5056,11 +5188,14 @@
       <c r="J37">
         <v>0.67200000000000004</v>
       </c>
-      <c r="Q37">
+      <c r="K37">
         <v>0.68879999999999997</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S37" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>34</v>
       </c>
@@ -5082,11 +5217,14 @@
       <c r="J38">
         <v>0.67479999999999996</v>
       </c>
-      <c r="Q38">
+      <c r="K38">
         <v>0.68959999999999999</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S38" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>35</v>
       </c>
@@ -5108,11 +5246,14 @@
       <c r="J39">
         <v>0.65869999999999995</v>
       </c>
-      <c r="Q39">
+      <c r="K39">
         <v>0.68889999999999996</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S39" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>36</v>
       </c>
@@ -5134,11 +5275,14 @@
       <c r="J40">
         <v>0.66559999999999997</v>
       </c>
-      <c r="Q40">
+      <c r="K40">
         <v>0.69220000000000004</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S40" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>37</v>
       </c>
@@ -5160,11 +5304,14 @@
       <c r="J41">
         <v>0.66949999999999998</v>
       </c>
-      <c r="Q41">
+      <c r="K41">
         <v>0.69159999999999999</v>
       </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S41" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>38</v>
       </c>
@@ -5186,11 +5333,14 @@
       <c r="J42">
         <v>0.67479999999999996</v>
       </c>
-      <c r="Q42">
+      <c r="K42">
         <v>0.69199999999999995</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S42" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -5212,11 +5362,14 @@
       <c r="J43">
         <v>0.67279999999999995</v>
       </c>
-      <c r="Q43">
+      <c r="K43">
         <v>0.69410000000000005</v>
       </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S43" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>40</v>
       </c>
@@ -5238,11 +5391,14 @@
       <c r="J44">
         <v>0.67400000000000004</v>
       </c>
-      <c r="Q44">
+      <c r="K44">
         <v>0.69120000000000004</v>
       </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S44" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>41</v>
       </c>
@@ -5264,11 +5420,14 @@
       <c r="J45">
         <v>0.67259999999999998</v>
       </c>
-      <c r="Q45">
+      <c r="K45">
         <v>0.69259999999999999</v>
       </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S45" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>42</v>
       </c>
@@ -5290,11 +5449,14 @@
       <c r="J46">
         <v>0.67620000000000002</v>
       </c>
-      <c r="Q46">
+      <c r="K46">
         <v>0.69340000000000002</v>
       </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S46" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>43</v>
       </c>
@@ -5316,11 +5478,14 @@
       <c r="J47">
         <v>0.6774</v>
       </c>
-      <c r="Q47">
+      <c r="K47">
         <v>0.69120000000000004</v>
       </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S47" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>44</v>
       </c>
@@ -5342,11 +5507,14 @@
       <c r="J48">
         <v>0.67490000000000006</v>
       </c>
-      <c r="Q48">
+      <c r="K48">
         <v>0.69079999999999997</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S48" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>45</v>
       </c>
@@ -5368,11 +5536,14 @@
       <c r="J49">
         <v>0.6754</v>
       </c>
-      <c r="Q49">
+      <c r="K49">
         <v>0.6875</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S49" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -5394,11 +5565,14 @@
       <c r="J50">
         <v>0.67469999999999997</v>
       </c>
-      <c r="Q50">
+      <c r="K50">
         <v>0.68759999999999999</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S50" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>47</v>
       </c>
@@ -5420,11 +5594,14 @@
       <c r="J51">
         <v>0.60019999999999996</v>
       </c>
-      <c r="Q51">
+      <c r="K51">
         <v>0.68859999999999999</v>
       </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S51" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>48</v>
       </c>
@@ -5446,11 +5623,14 @@
       <c r="J52">
         <v>0.66520000000000001</v>
       </c>
-      <c r="Q52">
+      <c r="K52">
         <v>0.6885</v>
       </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S52" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>49</v>
       </c>
@@ -5472,11 +5652,14 @@
       <c r="J53">
         <v>0.67689999999999995</v>
       </c>
-      <c r="Q53">
+      <c r="K53">
         <v>0.68810000000000004</v>
       </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S53" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>50</v>
       </c>
@@ -5498,11 +5681,14 @@
       <c r="J54">
         <v>0.67879999999999996</v>
       </c>
-      <c r="Q54">
+      <c r="K54">
         <v>0.68440000000000001</v>
       </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S54" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>51</v>
       </c>
@@ -5524,11 +5710,14 @@
       <c r="J55">
         <v>0.68159999999999998</v>
       </c>
-      <c r="Q55">
+      <c r="K55">
         <v>0.68740000000000001</v>
       </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S55" s="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>52</v>
       </c>
@@ -5550,11 +5739,14 @@
       <c r="J56">
         <v>0.67879999999999996</v>
       </c>
-      <c r="Q56">
+      <c r="K56">
         <v>0.68979999999999997</v>
       </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S56" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>53</v>
       </c>
@@ -5576,11 +5768,14 @@
       <c r="J57">
         <v>0.68079999999999996</v>
       </c>
-      <c r="Q57">
+      <c r="K57">
         <v>0.68910000000000005</v>
       </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S57" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>54</v>
       </c>
@@ -5602,11 +5797,14 @@
       <c r="J58">
         <v>0.67689999999999995</v>
       </c>
-      <c r="Q58">
+      <c r="K58">
         <v>0.69140000000000001</v>
       </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S58" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>55</v>
       </c>
@@ -5628,11 +5826,14 @@
       <c r="J59">
         <v>0.67430000000000001</v>
       </c>
-      <c r="Q59">
+      <c r="K59">
         <v>0.68820000000000003</v>
       </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S59" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>56</v>
       </c>
@@ -5654,11 +5855,14 @@
       <c r="J60">
         <v>0.68540000000000001</v>
       </c>
-      <c r="Q60">
+      <c r="K60">
         <v>0.69010000000000005</v>
       </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S60" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>57</v>
       </c>
@@ -5680,11 +5884,14 @@
       <c r="J61">
         <v>0.68220000000000003</v>
       </c>
-      <c r="Q61">
+      <c r="K61">
         <v>0.68969999999999998</v>
       </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S61" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>58</v>
       </c>
@@ -5706,11 +5913,14 @@
       <c r="J62">
         <v>0.68169999999999997</v>
       </c>
-      <c r="Q62">
+      <c r="K62">
         <v>0.68910000000000005</v>
       </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S62" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>59</v>
       </c>
@@ -5732,11 +5942,14 @@
       <c r="J63">
         <v>0.68159999999999998</v>
       </c>
-      <c r="Q63">
+      <c r="K63">
         <v>0.68910000000000005</v>
       </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S63" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>60</v>
       </c>
@@ -5758,11 +5971,14 @@
       <c r="J64">
         <v>0.68220000000000003</v>
       </c>
-      <c r="Q64">
+      <c r="K64">
         <v>0.68789999999999996</v>
       </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S64" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>61</v>
       </c>
@@ -5784,11 +6000,14 @@
       <c r="J65">
         <v>0.67920000000000003</v>
       </c>
-      <c r="Q65">
+      <c r="K65">
         <v>0.68830000000000002</v>
       </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S65" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>62</v>
       </c>
@@ -5810,11 +6029,14 @@
       <c r="J66">
         <v>0.68689999999999996</v>
       </c>
-      <c r="Q66">
+      <c r="K66">
         <v>0.68820000000000003</v>
       </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S66" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>63</v>
       </c>
@@ -5836,11 +6058,14 @@
       <c r="J67">
         <v>0.68369999999999997</v>
       </c>
-      <c r="Q67">
+      <c r="K67">
         <v>0.68910000000000005</v>
       </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S67" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>64</v>
       </c>
@@ -5862,11 +6087,14 @@
       <c r="J68">
         <v>0.68400000000000005</v>
       </c>
-      <c r="Q68">
+      <c r="K68">
         <v>0.68740000000000001</v>
       </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S68" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>65</v>
       </c>
@@ -5888,11 +6116,14 @@
       <c r="J69">
         <v>0.68340000000000001</v>
       </c>
-      <c r="Q69">
+      <c r="K69">
         <v>0.68759999999999999</v>
       </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S69" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>66</v>
       </c>
@@ -5914,11 +6145,14 @@
       <c r="J70">
         <v>0.6774</v>
       </c>
-      <c r="Q70">
+      <c r="K70">
         <v>0.68669999999999998</v>
       </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S70" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>67</v>
       </c>
@@ -5940,11 +6174,14 @@
       <c r="J71">
         <v>0.68610000000000004</v>
       </c>
-      <c r="Q71">
+      <c r="K71">
         <v>0.68630000000000002</v>
       </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S71" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>68</v>
       </c>
@@ -5966,11 +6203,14 @@
       <c r="J72">
         <v>0.67949999999999999</v>
       </c>
-      <c r="Q72">
+      <c r="K72">
         <v>0.68710000000000004</v>
       </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S72" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>69</v>
       </c>
@@ -5992,11 +6232,14 @@
       <c r="J73">
         <v>0.68159999999999998</v>
       </c>
-      <c r="Q73">
+      <c r="K73">
         <v>0.6865</v>
       </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S73" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>70</v>
       </c>
@@ -6018,11 +6261,14 @@
       <c r="J74">
         <v>0.68469999999999998</v>
       </c>
-      <c r="Q74">
+      <c r="K74">
         <v>0.68569999999999998</v>
       </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S74" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>71</v>
       </c>
@@ -6044,11 +6290,14 @@
       <c r="J75">
         <v>0.67989999999999995</v>
       </c>
-      <c r="Q75">
+      <c r="K75">
         <v>0.68799999999999994</v>
       </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S75" s="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>72</v>
       </c>
@@ -6070,11 +6319,14 @@
       <c r="J76">
         <v>0.68020000000000003</v>
       </c>
-      <c r="Q76">
+      <c r="K76">
         <v>0.68630000000000002</v>
       </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S76" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>73</v>
       </c>
@@ -6096,11 +6348,14 @@
       <c r="J77">
         <v>0.68110000000000004</v>
       </c>
-      <c r="Q77">
+      <c r="K77">
         <v>0.68689999999999996</v>
       </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S77" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>74</v>
       </c>
@@ -6122,11 +6377,14 @@
       <c r="J78">
         <v>0.68020000000000003</v>
       </c>
-      <c r="Q78">
+      <c r="K78">
         <v>0.68640000000000001</v>
       </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S78" s="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>75</v>
       </c>
@@ -6148,11 +6406,14 @@
       <c r="J79">
         <v>0.67490000000000006</v>
       </c>
-      <c r="Q79">
+      <c r="K79">
         <v>0.68730000000000002</v>
       </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S79" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>76</v>
       </c>
@@ -6174,11 +6435,14 @@
       <c r="J80">
         <v>0.68069999999999997</v>
       </c>
-      <c r="Q80">
+      <c r="K80">
         <v>0.68659999999999999</v>
       </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S80" s="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>77</v>
       </c>
@@ -6200,11 +6464,14 @@
       <c r="J81">
         <v>0.67889999999999995</v>
       </c>
-      <c r="Q81">
+      <c r="K81">
         <v>0.68620000000000003</v>
       </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S81" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>78</v>
       </c>
@@ -6226,11 +6493,14 @@
       <c r="J82">
         <v>0.68200000000000005</v>
       </c>
-      <c r="Q82">
+      <c r="K82">
         <v>0.68659999999999999</v>
       </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S82" s="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>79</v>
       </c>
@@ -6252,11 +6522,14 @@
       <c r="J83">
         <v>0.68130000000000002</v>
       </c>
-      <c r="Q83">
+      <c r="K83">
         <v>0.68630000000000002</v>
       </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S83" s="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>80</v>
       </c>
@@ -6278,11 +6551,14 @@
       <c r="J84">
         <v>0.68530000000000002</v>
       </c>
-      <c r="Q84">
+      <c r="K84">
         <v>0.68479999999999996</v>
       </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S84" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>81</v>
       </c>
@@ -6304,11 +6580,14 @@
       <c r="J85">
         <v>0.68420000000000003</v>
       </c>
-      <c r="Q85">
+      <c r="K85">
         <v>0.68610000000000004</v>
       </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S85" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>82</v>
       </c>
@@ -6330,11 +6609,14 @@
       <c r="J86">
         <v>0.68459999999999999</v>
       </c>
-      <c r="Q86">
+      <c r="K86">
         <v>0.6855</v>
       </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S86" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>83</v>
       </c>
@@ -6356,11 +6638,14 @@
       <c r="J87">
         <v>0.68379999999999996</v>
       </c>
-      <c r="Q87">
+      <c r="K87">
         <v>0.68310000000000004</v>
       </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S87" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>84</v>
       </c>
@@ -6382,11 +6667,14 @@
       <c r="J88">
         <v>0.68200000000000005</v>
       </c>
-      <c r="Q88">
+      <c r="K88">
         <v>0.68020000000000003</v>
       </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S88" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>85</v>
       </c>
@@ -6408,11 +6696,14 @@
       <c r="J89">
         <v>0.68579999999999997</v>
       </c>
-      <c r="Q89">
+      <c r="K89">
         <v>0.67779999999999996</v>
       </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S89" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>86</v>
       </c>
@@ -6434,11 +6725,14 @@
       <c r="J90">
         <v>0.68899999999999995</v>
       </c>
-      <c r="Q90">
+      <c r="K90">
         <v>0.67620000000000002</v>
       </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S90" s="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>87</v>
       </c>
@@ -6460,11 +6754,14 @@
       <c r="J91">
         <v>0.68679999999999997</v>
       </c>
-      <c r="Q91">
+      <c r="K91">
         <v>0.67669999999999997</v>
       </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S91" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>88</v>
       </c>
@@ -6486,11 +6783,14 @@
       <c r="J92">
         <v>0.68210000000000004</v>
       </c>
-      <c r="Q92">
+      <c r="K92">
         <v>0.67400000000000004</v>
       </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S92" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>89</v>
       </c>
@@ -6512,11 +6812,14 @@
       <c r="J93">
         <v>0.68440000000000001</v>
       </c>
-      <c r="Q93">
+      <c r="K93">
         <v>0.67610000000000003</v>
       </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S93" s="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>90</v>
       </c>
@@ -6538,11 +6841,14 @@
       <c r="J94">
         <v>0.68200000000000005</v>
       </c>
-      <c r="Q94">
+      <c r="K94">
         <v>0.67649999999999999</v>
       </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S94" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>91</v>
       </c>
@@ -6564,11 +6870,14 @@
       <c r="J95">
         <v>0.68259999999999998</v>
       </c>
-      <c r="Q95">
+      <c r="K95">
         <v>0.67789999999999995</v>
       </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S95" s="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>92</v>
       </c>
@@ -6590,11 +6899,14 @@
       <c r="J96">
         <v>0.68130000000000002</v>
       </c>
-      <c r="Q96">
+      <c r="K96">
         <v>0.67610000000000003</v>
       </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S96" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>93</v>
       </c>
@@ -6616,11 +6928,14 @@
       <c r="J97">
         <v>0.67889999999999995</v>
       </c>
-      <c r="Q97">
+      <c r="K97">
         <v>0.67649999999999999</v>
       </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S97" s="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>94</v>
       </c>
@@ -6642,11 +6957,14 @@
       <c r="J98">
         <v>0.67920000000000003</v>
       </c>
-      <c r="Q98">
+      <c r="K98">
         <v>0.67479999999999996</v>
       </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S98" s="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>95</v>
       </c>
@@ -6665,11 +6983,14 @@
       <c r="J99">
         <v>0.67779999999999996</v>
       </c>
-      <c r="Q99">
+      <c r="K99">
         <v>0.67910000000000004</v>
       </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S99" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>96</v>
       </c>
@@ -6688,11 +7009,14 @@
       <c r="J100">
         <v>0.6784</v>
       </c>
-      <c r="Q100">
+      <c r="K100">
         <v>0.67500000000000004</v>
       </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S100" s="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>97</v>
       </c>
@@ -6711,11 +7035,14 @@
       <c r="J101">
         <v>0.67659999999999998</v>
       </c>
-      <c r="Q101">
+      <c r="K101">
         <v>0.67349999999999999</v>
       </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S101" s="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>98</v>
       </c>
@@ -6734,11 +7061,14 @@
       <c r="J102">
         <v>0.66969999999999996</v>
       </c>
-      <c r="Q102">
+      <c r="K102">
         <v>0.67510000000000003</v>
       </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S102" s="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>99</v>
       </c>
@@ -6757,11 +7087,14 @@
       <c r="J103">
         <v>0.65920000000000001</v>
       </c>
-      <c r="Q103">
+      <c r="K103">
         <v>0.67490000000000006</v>
       </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S103" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>100</v>
       </c>
@@ -6780,21 +7113,30 @@
       <c r="J104">
         <v>0.67149999999999999</v>
       </c>
-      <c r="Q104">
+      <c r="K104">
         <v>0.67669999999999997</v>
       </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S104" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S106" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S107" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>1</v>
       </c>
@@ -6825,11 +7167,14 @@
       <c r="J108">
         <v>1</v>
       </c>
-      <c r="Q108">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K108">
+        <v>1</v>
+      </c>
+      <c r="S108" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>2</v>
       </c>
@@ -6860,11 +7205,14 @@
       <c r="J109">
         <v>1</v>
       </c>
-      <c r="Q109">
+      <c r="K109">
         <v>0.58333333333333337</v>
       </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S109" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>3</v>
       </c>
@@ -6895,11 +7243,14 @@
       <c r="J110">
         <v>1</v>
       </c>
-      <c r="Q110">
+      <c r="K110">
         <v>0.58333333333333337</v>
       </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S110" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>4</v>
       </c>
@@ -6930,11 +7281,14 @@
       <c r="J111">
         <v>1</v>
       </c>
-      <c r="Q111">
+      <c r="K111">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S111" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>5</v>
       </c>
@@ -6965,11 +7319,14 @@
       <c r="J112">
         <v>1</v>
       </c>
-      <c r="Q112">
+      <c r="K112">
         <v>0.91666666666666663</v>
       </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S112" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>6</v>
       </c>
@@ -6997,11 +7354,14 @@
       <c r="J113">
         <v>1</v>
       </c>
-      <c r="Q113">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K113">
+        <v>1</v>
+      </c>
+      <c r="S113" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>7</v>
       </c>
@@ -7029,11 +7389,14 @@
       <c r="J114">
         <v>1</v>
       </c>
-      <c r="Q114">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K114">
+        <v>1</v>
+      </c>
+      <c r="S114" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>8</v>
       </c>
@@ -7061,11 +7424,14 @@
       <c r="J115">
         <v>1</v>
       </c>
-      <c r="Q115">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K115">
+        <v>1</v>
+      </c>
+      <c r="S115" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>9</v>
       </c>
@@ -7093,11 +7459,14 @@
       <c r="J116">
         <v>1</v>
       </c>
-      <c r="Q116">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K116">
+        <v>1</v>
+      </c>
+      <c r="S116" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>10</v>
       </c>
@@ -7125,11 +7494,14 @@
       <c r="J117">
         <v>1</v>
       </c>
-      <c r="Q117">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K117">
+        <v>1</v>
+      </c>
+      <c r="S117" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>11</v>
       </c>
@@ -7151,11 +7523,14 @@
       <c r="J118">
         <v>1</v>
       </c>
-      <c r="Q118">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K118">
+        <v>1</v>
+      </c>
+      <c r="S118" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>12</v>
       </c>
@@ -7177,11 +7552,14 @@
       <c r="J119">
         <v>1</v>
       </c>
-      <c r="Q119">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K119">
+        <v>1</v>
+      </c>
+      <c r="S119" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>13</v>
       </c>
@@ -7203,11 +7581,14 @@
       <c r="J120">
         <v>1</v>
       </c>
-      <c r="Q120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K120">
+        <v>1</v>
+      </c>
+      <c r="S120" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>14</v>
       </c>
@@ -7229,11 +7610,14 @@
       <c r="J121">
         <v>1</v>
       </c>
-      <c r="Q121">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K121">
+        <v>1</v>
+      </c>
+      <c r="S121" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>15</v>
       </c>
@@ -7255,11 +7639,14 @@
       <c r="J122">
         <v>0.14285714285714279</v>
       </c>
-      <c r="Q122">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K122">
+        <v>1</v>
+      </c>
+      <c r="S122" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>16</v>
       </c>
@@ -7281,11 +7668,14 @@
       <c r="J123">
         <v>1</v>
       </c>
-      <c r="Q123">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K123">
+        <v>1</v>
+      </c>
+      <c r="S123" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>17</v>
       </c>
@@ -7307,11 +7697,14 @@
       <c r="J124">
         <v>1</v>
       </c>
-      <c r="Q124">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K124">
+        <v>1</v>
+      </c>
+      <c r="S124" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>18</v>
       </c>
@@ -7333,11 +7726,14 @@
       <c r="J125">
         <v>1</v>
       </c>
-      <c r="Q125">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K125">
+        <v>1</v>
+      </c>
+      <c r="S125" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>19</v>
       </c>
@@ -7359,11 +7755,14 @@
       <c r="J126">
         <v>1</v>
       </c>
-      <c r="Q126">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K126">
+        <v>1</v>
+      </c>
+      <c r="S126" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>20</v>
       </c>
@@ -7385,11 +7784,14 @@
       <c r="J127">
         <v>0.875</v>
       </c>
-      <c r="Q127">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K127">
+        <v>1</v>
+      </c>
+      <c r="S127" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>21</v>
       </c>
@@ -7411,11 +7813,14 @@
       <c r="J128">
         <v>1</v>
       </c>
-      <c r="Q128">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K128">
+        <v>1</v>
+      </c>
+      <c r="S128" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>22</v>
       </c>
@@ -7437,11 +7842,14 @@
       <c r="J129">
         <v>1</v>
       </c>
-      <c r="Q129">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K129">
+        <v>1</v>
+      </c>
+      <c r="S129" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>23</v>
       </c>
@@ -7463,11 +7871,14 @@
       <c r="J130">
         <v>1</v>
       </c>
-      <c r="Q130">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K130">
+        <v>1</v>
+      </c>
+      <c r="S130" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>24</v>
       </c>
@@ -7489,11 +7900,14 @@
       <c r="J131">
         <v>1</v>
       </c>
-      <c r="Q131">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K131">
+        <v>1</v>
+      </c>
+      <c r="S131" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>25</v>
       </c>
@@ -7515,11 +7929,14 @@
       <c r="J132">
         <v>1</v>
       </c>
-      <c r="Q132">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K132">
+        <v>1</v>
+      </c>
+      <c r="S132" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>26</v>
       </c>
@@ -7541,11 +7958,14 @@
       <c r="J133">
         <v>1</v>
       </c>
-      <c r="Q133">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K133">
+        <v>1</v>
+      </c>
+      <c r="S133" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>27</v>
       </c>
@@ -7567,11 +7987,14 @@
       <c r="J134">
         <v>1</v>
       </c>
-      <c r="Q134">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K134">
+        <v>1</v>
+      </c>
+      <c r="S134" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>28</v>
       </c>
@@ -7593,11 +8016,14 @@
       <c r="J135">
         <v>1</v>
       </c>
-      <c r="Q135">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K135">
+        <v>1</v>
+      </c>
+      <c r="S135" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>29</v>
       </c>
@@ -7619,11 +8045,14 @@
       <c r="J136">
         <v>1</v>
       </c>
-      <c r="Q136">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K136">
+        <v>1</v>
+      </c>
+      <c r="S136" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>30</v>
       </c>
@@ -7645,11 +8074,14 @@
       <c r="J137">
         <v>1</v>
       </c>
-      <c r="Q137">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K137">
+        <v>1</v>
+      </c>
+      <c r="S137" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>31</v>
       </c>
@@ -7671,11 +8103,14 @@
       <c r="J138">
         <v>1</v>
       </c>
-      <c r="Q138">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K138">
+        <v>1</v>
+      </c>
+      <c r="S138" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>32</v>
       </c>
@@ -7697,11 +8132,14 @@
       <c r="J139">
         <v>1</v>
       </c>
-      <c r="Q139">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K139">
+        <v>1</v>
+      </c>
+      <c r="S139" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>33</v>
       </c>
@@ -7723,11 +8161,14 @@
       <c r="J140">
         <v>1</v>
       </c>
-      <c r="Q140">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K140">
+        <v>1</v>
+      </c>
+      <c r="S140" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="141" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>34</v>
       </c>
@@ -7749,11 +8190,14 @@
       <c r="J141">
         <v>1</v>
       </c>
-      <c r="Q141">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K141">
+        <v>1</v>
+      </c>
+      <c r="S141" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="142" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>35</v>
       </c>
@@ -7775,11 +8219,14 @@
       <c r="J142">
         <v>1</v>
       </c>
-      <c r="Q142">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K142">
+        <v>1</v>
+      </c>
+      <c r="S142" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>36</v>
       </c>
@@ -7801,11 +8248,14 @@
       <c r="J143">
         <v>1</v>
       </c>
-      <c r="Q143">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K143">
+        <v>1</v>
+      </c>
+      <c r="S143" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="144" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>37</v>
       </c>
@@ -7827,11 +8277,14 @@
       <c r="J144">
         <v>1</v>
       </c>
-      <c r="Q144">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K144">
+        <v>1</v>
+      </c>
+      <c r="S144" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="145" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>38</v>
       </c>
@@ -7853,11 +8306,14 @@
       <c r="J145">
         <v>1</v>
       </c>
-      <c r="Q145">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K145">
+        <v>1</v>
+      </c>
+      <c r="S145" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="146" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>39</v>
       </c>
@@ -7879,11 +8335,14 @@
       <c r="J146">
         <v>1</v>
       </c>
-      <c r="Q146">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K146">
+        <v>1</v>
+      </c>
+      <c r="S146" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="147" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>40</v>
       </c>
@@ -7905,11 +8364,14 @@
       <c r="J147">
         <v>1</v>
       </c>
-      <c r="Q147">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K147">
+        <v>1</v>
+      </c>
+      <c r="S147" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="148" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>41</v>
       </c>
@@ -7931,11 +8393,14 @@
       <c r="J148">
         <v>1</v>
       </c>
-      <c r="Q148">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K148">
+        <v>1</v>
+      </c>
+      <c r="S148" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="149" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>42</v>
       </c>
@@ -7957,11 +8422,14 @@
       <c r="J149">
         <v>1</v>
       </c>
-      <c r="Q149">
+      <c r="K149">
         <v>0.91666666666666663</v>
       </c>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S149" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="150" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>43</v>
       </c>
@@ -7983,11 +8451,14 @@
       <c r="J150">
         <v>1</v>
       </c>
-      <c r="Q150">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K150">
+        <v>1</v>
+      </c>
+      <c r="S150" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="151" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>44</v>
       </c>
@@ -8009,11 +8480,14 @@
       <c r="J151">
         <v>1</v>
       </c>
-      <c r="Q151">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K151">
+        <v>1</v>
+      </c>
+      <c r="S151" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="152" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>45</v>
       </c>
@@ -8035,11 +8509,14 @@
       <c r="J152">
         <v>1</v>
       </c>
-      <c r="Q152">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K152">
+        <v>1</v>
+      </c>
+      <c r="S152" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="153" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>46</v>
       </c>
@@ -8061,11 +8538,14 @@
       <c r="J153">
         <v>1</v>
       </c>
-      <c r="Q153">
+      <c r="K153">
         <v>0.90909090909090906</v>
       </c>
-    </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S153" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="154" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>47</v>
       </c>
@@ -8087,11 +8567,14 @@
       <c r="J154">
         <v>0.1</v>
       </c>
-      <c r="Q154">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K154">
+        <v>1</v>
+      </c>
+      <c r="S154" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="155" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>48</v>
       </c>
@@ -8113,11 +8596,14 @@
       <c r="J155">
         <v>1</v>
       </c>
-      <c r="Q155">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K155">
+        <v>1</v>
+      </c>
+      <c r="S155" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="156" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>49</v>
       </c>
@@ -8139,11 +8625,14 @@
       <c r="J156">
         <v>1</v>
       </c>
-      <c r="Q156">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K156">
+        <v>1</v>
+      </c>
+      <c r="S156" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="157" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>50</v>
       </c>
@@ -8165,11 +8654,14 @@
       <c r="J157">
         <v>1</v>
       </c>
-      <c r="Q157">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K157">
+        <v>1</v>
+      </c>
+      <c r="S157" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>51</v>
       </c>
@@ -8191,11 +8683,14 @@
       <c r="J158">
         <v>1</v>
       </c>
-      <c r="Q158">
+      <c r="K158">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S158" s="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="159" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>52</v>
       </c>
@@ -8217,11 +8712,14 @@
       <c r="J159">
         <v>1</v>
       </c>
-      <c r="Q159">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K159">
+        <v>1</v>
+      </c>
+      <c r="S159" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="160" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>53</v>
       </c>
@@ -8243,11 +8741,14 @@
       <c r="J160">
         <v>1</v>
       </c>
-      <c r="Q160">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K160">
+        <v>1</v>
+      </c>
+      <c r="S160" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>54</v>
       </c>
@@ -8269,11 +8770,14 @@
       <c r="J161">
         <v>1</v>
       </c>
-      <c r="Q161">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K161">
+        <v>1</v>
+      </c>
+      <c r="S161" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="162" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>55</v>
       </c>
@@ -8295,11 +8799,14 @@
       <c r="J162">
         <v>1</v>
       </c>
-      <c r="Q162">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K162">
+        <v>1</v>
+      </c>
+      <c r="S162" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="163" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>56</v>
       </c>
@@ -8321,11 +8828,14 @@
       <c r="J163">
         <v>1</v>
       </c>
-      <c r="Q163">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K163">
+        <v>1</v>
+      </c>
+      <c r="S163" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="164" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>57</v>
       </c>
@@ -8347,11 +8857,14 @@
       <c r="J164">
         <v>1</v>
       </c>
-      <c r="Q164">
+      <c r="K164">
         <v>0.88888888888888884</v>
       </c>
-    </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S164" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="165" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>58</v>
       </c>
@@ -8373,11 +8886,14 @@
       <c r="J165">
         <v>1</v>
       </c>
-      <c r="Q165">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K165">
+        <v>1</v>
+      </c>
+      <c r="S165" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="166" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>59</v>
       </c>
@@ -8399,11 +8915,14 @@
       <c r="J166">
         <v>1</v>
       </c>
-      <c r="Q166">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K166">
+        <v>1</v>
+      </c>
+      <c r="S166" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="167" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>60</v>
       </c>
@@ -8425,11 +8944,14 @@
       <c r="J167">
         <v>1</v>
       </c>
-      <c r="Q167">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K167">
+        <v>1</v>
+      </c>
+      <c r="S167" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="168" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>61</v>
       </c>
@@ -8451,11 +8973,14 @@
       <c r="J168">
         <v>1</v>
       </c>
-      <c r="Q168">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K168">
+        <v>1</v>
+      </c>
+      <c r="S168" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="169" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>62</v>
       </c>
@@ -8477,11 +9002,14 @@
       <c r="J169">
         <v>1</v>
       </c>
-      <c r="Q169">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K169">
+        <v>1</v>
+      </c>
+      <c r="S169" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="170" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>63</v>
       </c>
@@ -8503,11 +9031,14 @@
       <c r="J170">
         <v>1</v>
       </c>
-      <c r="Q170">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K170">
+        <v>1</v>
+      </c>
+      <c r="S170" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="171" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>64</v>
       </c>
@@ -8529,11 +9060,14 @@
       <c r="J171">
         <v>1</v>
       </c>
-      <c r="Q171">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K171">
+        <v>1</v>
+      </c>
+      <c r="S171" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="172" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>65</v>
       </c>
@@ -8555,11 +9089,14 @@
       <c r="J172">
         <v>1</v>
       </c>
-      <c r="Q172">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K172">
+        <v>1</v>
+      </c>
+      <c r="S172" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="173" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>66</v>
       </c>
@@ -8581,11 +9118,14 @@
       <c r="J173">
         <v>0.8571428571428571</v>
       </c>
-      <c r="Q173">
+      <c r="K173">
         <v>0.875</v>
       </c>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S173" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="174" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>67</v>
       </c>
@@ -8607,11 +9147,14 @@
       <c r="J174">
         <v>1</v>
       </c>
-      <c r="Q174">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K174">
+        <v>1</v>
+      </c>
+      <c r="S174" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="175" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>68</v>
       </c>
@@ -8633,11 +9176,14 @@
       <c r="J175">
         <v>1</v>
       </c>
-      <c r="Q175">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K175">
+        <v>1</v>
+      </c>
+      <c r="S175" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="176" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>69</v>
       </c>
@@ -8659,11 +9205,14 @@
       <c r="J176">
         <v>1</v>
       </c>
-      <c r="Q176">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K176">
+        <v>1</v>
+      </c>
+      <c r="S176" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="177" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>70</v>
       </c>
@@ -8685,11 +9234,14 @@
       <c r="J177">
         <v>1</v>
       </c>
-      <c r="Q177">
+      <c r="K177">
         <v>0.8571428571428571</v>
       </c>
-    </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S177" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="178" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>71</v>
       </c>
@@ -8711,11 +9263,14 @@
       <c r="J178">
         <v>0.8571428571428571</v>
       </c>
-      <c r="Q178">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K178">
+        <v>1</v>
+      </c>
+      <c r="S178" s="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="179" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>72</v>
       </c>
@@ -8737,11 +9292,14 @@
       <c r="J179">
         <v>1</v>
       </c>
-      <c r="Q179">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K179">
+        <v>1</v>
+      </c>
+      <c r="S179" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="180" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>73</v>
       </c>
@@ -8763,11 +9321,14 @@
       <c r="J180">
         <v>1</v>
       </c>
-      <c r="Q180">
+      <c r="K180">
         <v>0.83333333333333337</v>
       </c>
-    </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S180" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="181" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>74</v>
       </c>
@@ -8789,11 +9350,14 @@
       <c r="J181">
         <v>0.9</v>
       </c>
-      <c r="Q181">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K181">
+        <v>1</v>
+      </c>
+      <c r="S181" s="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="182" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>75</v>
       </c>
@@ -8815,11 +9379,14 @@
       <c r="J182">
         <v>0.7142857142857143</v>
       </c>
-      <c r="Q182">
+      <c r="K182">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S182" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="183" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>76</v>
       </c>
@@ -8841,11 +9408,14 @@
       <c r="J183">
         <v>0.875</v>
       </c>
-      <c r="Q183">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K183">
+        <v>1</v>
+      </c>
+      <c r="S183" s="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="184" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>77</v>
       </c>
@@ -8867,11 +9437,14 @@
       <c r="J184">
         <v>0.88888888888888884</v>
       </c>
-      <c r="Q184">
+      <c r="K184">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S184" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="185" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>78</v>
       </c>
@@ -8893,11 +9466,14 @@
       <c r="J185">
         <v>1</v>
       </c>
-      <c r="Q185">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K185">
+        <v>1</v>
+      </c>
+      <c r="S185" s="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="186" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>79</v>
       </c>
@@ -8919,11 +9495,14 @@
       <c r="J186">
         <v>1</v>
       </c>
-      <c r="Q186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K186">
+        <v>1</v>
+      </c>
+      <c r="S186" s="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="187" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>80</v>
       </c>
@@ -8945,11 +9524,14 @@
       <c r="J187">
         <v>0.88888888888888884</v>
       </c>
-      <c r="Q187">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K187">
+        <v>1</v>
+      </c>
+      <c r="S187" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="188" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>81</v>
       </c>
@@ -8971,11 +9553,14 @@
       <c r="J188">
         <v>1</v>
       </c>
-      <c r="Q188">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K188">
+        <v>1</v>
+      </c>
+      <c r="S188" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="189" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>82</v>
       </c>
@@ -8997,11 +9582,14 @@
       <c r="J189">
         <v>1</v>
       </c>
-      <c r="Q189">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K189">
+        <v>1</v>
+      </c>
+      <c r="S189" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="190" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>83</v>
       </c>
@@ -9023,11 +9611,14 @@
       <c r="J190">
         <v>1</v>
       </c>
-      <c r="Q190">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K190">
+        <v>1</v>
+      </c>
+      <c r="S190" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="191" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>84</v>
       </c>
@@ -9049,11 +9640,14 @@
       <c r="J191">
         <v>1</v>
       </c>
-      <c r="Q191">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K191">
+        <v>1</v>
+      </c>
+      <c r="S191" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="192" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>85</v>
       </c>
@@ -9075,11 +9669,14 @@
       <c r="J192">
         <v>1</v>
       </c>
-      <c r="Q192">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K192">
+        <v>1</v>
+      </c>
+      <c r="S192" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="193" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>86</v>
       </c>
@@ -9101,11 +9698,14 @@
       <c r="J193">
         <v>0.875</v>
       </c>
-      <c r="Q193">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K193">
+        <v>1</v>
+      </c>
+      <c r="S193" s="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="194" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>87</v>
       </c>
@@ -9127,11 +9727,14 @@
       <c r="J194">
         <v>0.88888888888888884</v>
       </c>
-      <c r="Q194">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K194">
+        <v>1</v>
+      </c>
+      <c r="S194" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="195" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>88</v>
       </c>
@@ -9153,11 +9756,14 @@
       <c r="J195">
         <v>0.7142857142857143</v>
       </c>
-      <c r="Q195">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K195">
+        <v>1</v>
+      </c>
+      <c r="S195" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="196" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>89</v>
       </c>
@@ -9179,11 +9785,14 @@
       <c r="J196">
         <v>1</v>
       </c>
-      <c r="Q196">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K196">
+        <v>1</v>
+      </c>
+      <c r="S196" s="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="197" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>90</v>
       </c>
@@ -9205,11 +9814,14 @@
       <c r="J197">
         <v>0.8571428571428571</v>
       </c>
-      <c r="Q197">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K197">
+        <v>1</v>
+      </c>
+      <c r="S197" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="198" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>91</v>
       </c>
@@ -9231,11 +9843,14 @@
       <c r="J198">
         <v>1</v>
       </c>
-      <c r="Q198">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K198">
+        <v>1</v>
+      </c>
+      <c r="S198" s="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="199" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>92</v>
       </c>
@@ -9257,11 +9872,14 @@
       <c r="J199">
         <v>1</v>
       </c>
-      <c r="Q199">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K199">
+        <v>1</v>
+      </c>
+      <c r="S199" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="200" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>93</v>
       </c>
@@ -9283,11 +9901,14 @@
       <c r="J200">
         <v>0.83333333333333337</v>
       </c>
-      <c r="Q200">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K200">
+        <v>1</v>
+      </c>
+      <c r="S200" s="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="201" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>94</v>
       </c>
@@ -9309,11 +9930,14 @@
       <c r="J201">
         <v>0.875</v>
       </c>
-      <c r="Q201">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K201">
+        <v>1</v>
+      </c>
+      <c r="S201" s="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="202" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>95</v>
       </c>
@@ -9332,11 +9956,14 @@
       <c r="J202">
         <v>0.875</v>
       </c>
-      <c r="Q202">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K202">
+        <v>1</v>
+      </c>
+      <c r="S202" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="203" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>96</v>
       </c>
@@ -9355,11 +9982,14 @@
       <c r="J203">
         <v>1</v>
       </c>
-      <c r="Q203">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K203">
+        <v>1</v>
+      </c>
+      <c r="S203" s="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="204" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>97</v>
       </c>
@@ -9378,11 +10008,14 @@
       <c r="J204">
         <v>1</v>
       </c>
-      <c r="Q204">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K204">
+        <v>1</v>
+      </c>
+      <c r="S204" s="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="205" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>98</v>
       </c>
@@ -9401,11 +10034,14 @@
       <c r="J205">
         <v>1</v>
       </c>
-      <c r="Q205">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K205">
+        <v>1</v>
+      </c>
+      <c r="S205" s="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="206" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>99</v>
       </c>
@@ -9424,11 +10060,14 @@
       <c r="J206">
         <v>1</v>
       </c>
-      <c r="Q206">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K206">
+        <v>1</v>
+      </c>
+      <c r="S206" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="207" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>100</v>
       </c>
@@ -9447,21 +10086,30 @@
       <c r="J207">
         <v>0.75</v>
       </c>
-      <c r="Q207">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K207">
+        <v>1</v>
+      </c>
+      <c r="S207" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="210" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S210" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="211" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S211" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="212" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>1</v>
       </c>
@@ -9492,11 +10140,14 @@
       <c r="J212">
         <v>0.97970000000000002</v>
       </c>
-      <c r="Q212">
+      <c r="K212">
         <v>0.98693750000000002</v>
       </c>
-    </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S212" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>2</v>
       </c>
@@ -9527,11 +10178,14 @@
       <c r="J213">
         <v>0.97943999999999998</v>
       </c>
-      <c r="Q213">
+      <c r="K213">
         <v>0.98435000000000006</v>
       </c>
-    </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S213" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>3</v>
       </c>
@@ -9562,11 +10216,14 @@
       <c r="J214">
         <v>0.97349999999999992</v>
       </c>
-      <c r="Q214">
+      <c r="K214">
         <v>0.98704999999999998</v>
       </c>
-    </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S214" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="215" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>4</v>
       </c>
@@ -9597,11 +10254,14 @@
       <c r="J215">
         <v>0.97373333333333323</v>
       </c>
-      <c r="Q215">
+      <c r="K215">
         <v>0.97666249999999999</v>
       </c>
-    </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S215" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>5</v>
       </c>
@@ -9632,11 +10292,14 @@
       <c r="J216">
         <v>0.95366666666666655</v>
       </c>
-      <c r="Q216">
+      <c r="K216">
         <v>0.97836249999999991</v>
       </c>
-    </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S216" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>6</v>
       </c>
@@ -9664,11 +10327,14 @@
       <c r="J217">
         <v>0.95196000000000003</v>
       </c>
-      <c r="Q217">
+      <c r="K217">
         <v>0.97642499999999999</v>
       </c>
-    </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S217" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="218" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>7</v>
       </c>
@@ -9696,11 +10362,14 @@
       <c r="J218">
         <v>0.971225</v>
       </c>
-      <c r="Q218">
+      <c r="K218">
         <v>0.98567499999999997</v>
       </c>
-    </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S218" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="219" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>8</v>
       </c>
@@ -9728,11 +10397,14 @@
       <c r="J219">
         <v>0.97144444444444444</v>
       </c>
-      <c r="Q219">
+      <c r="K219">
         <v>0.97106249999999994</v>
       </c>
-    </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S219" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="220" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>9</v>
       </c>
@@ -9760,11 +10432,14 @@
       <c r="J220">
         <v>0.97467142857142852</v>
       </c>
-      <c r="Q220">
+      <c r="K220">
         <v>0.97282499999999994</v>
       </c>
-    </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S220" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="221" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>10</v>
       </c>
@@ -9792,11 +10467,14 @@
       <c r="J221">
         <v>0.96319999999999995</v>
       </c>
-      <c r="Q221">
+      <c r="K221">
         <v>0.98088750000000002</v>
       </c>
-    </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S221" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="222" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>11</v>
       </c>
@@ -9818,11 +10496,14 @@
       <c r="J222">
         <v>0.98293333333333344</v>
       </c>
-      <c r="Q222">
+      <c r="K222">
         <v>0.98151250000000001</v>
       </c>
-    </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S222" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="223" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>12</v>
       </c>
@@ -9844,11 +10525,14 @@
       <c r="J223">
         <v>0.97118571428571432</v>
       </c>
-      <c r="Q223">
+      <c r="K223">
         <v>0.9807125000000001</v>
       </c>
-    </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S223" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="224" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>13</v>
       </c>
@@ -9870,11 +10554,14 @@
       <c r="J224">
         <v>0.97124999999999995</v>
       </c>
-      <c r="Q224">
+      <c r="K224">
         <v>0.9760875</v>
       </c>
-    </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S224" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="225" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>14</v>
       </c>
@@ -9896,11 +10583,14 @@
       <c r="J225">
         <v>0.97566666666666668</v>
       </c>
-      <c r="Q225">
+      <c r="K225">
         <v>0.98082499999999995</v>
       </c>
-    </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S225" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="226" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>15</v>
       </c>
@@ -9922,11 +10612,14 @@
       <c r="J226">
         <v>0.98197500000000004</v>
       </c>
-      <c r="Q226">
+      <c r="K226">
         <v>0.97872500000000007</v>
       </c>
-    </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S226" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="227" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>16</v>
       </c>
@@ -9948,11 +10641,14 @@
       <c r="J227">
         <v>0.96831999999999996</v>
       </c>
-      <c r="Q227">
+      <c r="K227">
         <v>0.97936250000000014</v>
       </c>
-    </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S227" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="228" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>17</v>
       </c>
@@ -9974,11 +10670,14 @@
       <c r="J228">
         <v>0.97763999999999984</v>
       </c>
-      <c r="Q228">
+      <c r="K228">
         <v>0.97966249999999999</v>
       </c>
-    </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S228" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="229" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>18</v>
       </c>
@@ -10000,11 +10699,14 @@
       <c r="J229">
         <v>0.98183333333333334</v>
       </c>
-      <c r="Q229">
+      <c r="K229">
         <v>0.97897500000000004</v>
       </c>
-    </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S229" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="230" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>19</v>
       </c>
@@ -10026,11 +10728,14 @@
       <c r="J230">
         <v>0.97803333333333331</v>
       </c>
-      <c r="Q230">
+      <c r="K230">
         <v>0.98377499999999996</v>
       </c>
-    </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S230" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="231" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>20</v>
       </c>
@@ -10052,11 +10757,14 @@
       <c r="J231">
         <v>0.9743571428571427</v>
       </c>
-      <c r="Q231">
+      <c r="K231">
         <v>0.97541250000000002</v>
       </c>
-    </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S231" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="232" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>21</v>
       </c>
@@ -10078,11 +10786,14 @@
       <c r="J232">
         <v>0.97684285714285723</v>
       </c>
-      <c r="Q232">
+      <c r="K232">
         <v>0.97896250000000007</v>
       </c>
-    </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S232" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="233" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>22</v>
       </c>
@@ -10104,11 +10815,14 @@
       <c r="J233">
         <v>0.98381666666666645</v>
       </c>
-      <c r="Q233">
+      <c r="K233">
         <v>0.98047499999999999</v>
       </c>
-    </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S233" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="234" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>23</v>
       </c>
@@ -10130,11 +10844,14 @@
       <c r="J234">
         <v>0.97453999999999996</v>
       </c>
-      <c r="Q234">
+      <c r="K234">
         <v>0.9764250000000001</v>
       </c>
-    </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S234" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="235" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>24</v>
       </c>
@@ -10156,11 +10873,14 @@
       <c r="J235">
         <v>0.97433333333333338</v>
       </c>
-      <c r="Q235">
+      <c r="K235">
         <v>0.98250000000000004</v>
       </c>
-    </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S235" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="236" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>25</v>
       </c>
@@ -10182,11 +10902,14 @@
       <c r="J236">
         <v>0.98126000000000002</v>
       </c>
-      <c r="Q236">
+      <c r="K236">
         <v>0.98208750000000011</v>
       </c>
-    </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S236" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="237" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <v>26</v>
       </c>
@@ -10208,11 +10931,14 @@
       <c r="J237">
         <v>0.96943749999999995</v>
       </c>
-      <c r="Q237">
+      <c r="K237">
         <v>0.9754624999999999</v>
       </c>
-    </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S237" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="238" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <v>27</v>
       </c>
@@ -10234,11 +10960,14 @@
       <c r="J238">
         <v>0.9731599999999998</v>
       </c>
-      <c r="Q238">
+      <c r="K238">
         <v>0.98350000000000004</v>
       </c>
-    </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S238" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="239" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <v>28</v>
       </c>
@@ -10260,11 +10989,14 @@
       <c r="J239">
         <v>0.9728</v>
       </c>
-      <c r="Q239">
+      <c r="K239">
         <v>0.97853750000000006</v>
       </c>
-    </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S239" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="240" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <v>29</v>
       </c>
@@ -10286,11 +11018,14 @@
       <c r="J240">
         <v>0.97033999999999998</v>
       </c>
-      <c r="Q240">
+      <c r="K240">
         <v>0.97983750000000014</v>
       </c>
-    </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S240" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="241" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <v>30</v>
       </c>
@@ -10312,11 +11047,14 @@
       <c r="J241">
         <v>0.97602857142857136</v>
       </c>
-      <c r="Q241">
+      <c r="K241">
         <v>0.98202500000000004</v>
       </c>
-    </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S241" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="242" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>31</v>
       </c>
@@ -10338,11 +11076,14 @@
       <c r="J242">
         <v>0.97409999999999997</v>
       </c>
-      <c r="Q242">
+      <c r="K242">
         <v>0.97918749999999988</v>
       </c>
-    </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S242" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="243" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <v>32</v>
       </c>
@@ -10364,11 +11105,14 @@
       <c r="J243">
         <v>0.96785999999999994</v>
       </c>
-      <c r="Q243">
+      <c r="K243">
         <v>0.9765625</v>
       </c>
-    </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S243" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="244" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>33</v>
       </c>
@@ -10390,11 +11134,14 @@
       <c r="J244">
         <v>0.97739999999999994</v>
       </c>
-      <c r="Q244">
+      <c r="K244">
         <v>0.981325</v>
       </c>
-    </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S244" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="245" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>34</v>
       </c>
@@ -10416,11 +11163,14 @@
       <c r="J245">
         <v>0.97585999999999995</v>
       </c>
-      <c r="Q245">
+      <c r="K245">
         <v>0.98352499999999998</v>
       </c>
-    </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S245" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="246" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>35</v>
       </c>
@@ -10442,11 +11192,14 @@
       <c r="J246">
         <v>0.97463333333333324</v>
       </c>
-      <c r="Q246">
+      <c r="K246">
         <v>0.97599999999999998</v>
       </c>
-    </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S246" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="247" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <v>36</v>
       </c>
@@ -10468,11 +11221,14 @@
       <c r="J247">
         <v>0.97368571428571438</v>
       </c>
-      <c r="Q247">
+      <c r="K247">
         <v>0.98186249999999997</v>
       </c>
-    </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S247" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="248" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>37</v>
       </c>
@@ -10494,11 +11250,14 @@
       <c r="J248">
         <v>0.97250000000000003</v>
       </c>
-      <c r="Q248">
+      <c r="K248">
         <v>0.98206250000000006</v>
       </c>
-    </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S248" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="249" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>38</v>
       </c>
@@ -10520,11 +11279,14 @@
       <c r="J249">
         <v>0.98175999999999986</v>
       </c>
-      <c r="Q249">
+      <c r="K249">
         <v>0.9805625</v>
       </c>
-    </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S249" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="250" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>39</v>
       </c>
@@ -10546,11 +11308,14 @@
       <c r="J250">
         <v>0.96805000000000008</v>
       </c>
-      <c r="Q250">
+      <c r="K250">
         <v>0.98076249999999998</v>
       </c>
-    </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S250" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="251" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>40</v>
       </c>
@@ -10572,11 +11337,14 @@
       <c r="J251">
         <v>0.97534999999999983</v>
       </c>
-      <c r="Q251">
+      <c r="K251">
         <v>0.97984999999999989</v>
       </c>
-    </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S251" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="252" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>41</v>
       </c>
@@ -10598,11 +11366,14 @@
       <c r="J252">
         <v>0.97548749999999995</v>
       </c>
-      <c r="Q252">
+      <c r="K252">
         <v>0.98190000000000011</v>
       </c>
-    </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S252" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="253" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>42</v>
       </c>
@@ -10624,11 +11395,14 @@
       <c r="J253">
         <v>0.97524999999999995</v>
       </c>
-      <c r="Q253">
+      <c r="K253">
         <v>0.97888750000000002</v>
       </c>
-    </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S253" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="254" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>43</v>
       </c>
@@ -10650,11 +11424,14 @@
       <c r="J254">
         <v>0.97273999999999994</v>
       </c>
-      <c r="Q254">
+      <c r="K254">
         <v>0.88317777777777773</v>
       </c>
-    </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S254" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="255" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>44</v>
       </c>
@@ -10676,11 +11453,14 @@
       <c r="J255">
         <v>0.97871999999999981</v>
       </c>
-      <c r="Q255">
+      <c r="K255">
         <v>0.8807222222222223</v>
       </c>
-    </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S255" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="256" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <v>45</v>
       </c>
@@ -10702,11 +11482,14 @@
       <c r="J256">
         <v>0.97180000000000011</v>
       </c>
-      <c r="Q256">
+      <c r="K256">
         <v>0.88358888888888887</v>
       </c>
-    </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S256" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="257" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>46</v>
       </c>
@@ -10728,11 +11511,14 @@
       <c r="J257">
         <v>0.97057142857142864</v>
       </c>
-      <c r="Q257">
+      <c r="K257">
         <v>0.88413333333333333</v>
       </c>
-    </row>
-    <row r="258" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S257" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="258" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <v>47</v>
       </c>
@@ -10754,11 +11540,14 @@
       <c r="J258">
         <v>0.9657</v>
       </c>
-      <c r="Q258">
+      <c r="K258">
         <v>0.80829000000000006</v>
       </c>
-    </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S258" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="259" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>48</v>
       </c>
@@ -10780,11 +11569,14 @@
       <c r="J259">
         <v>0.97477499999999995</v>
       </c>
-      <c r="Q259">
+      <c r="K259">
         <v>0.80259000000000003</v>
       </c>
-    </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S259" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="260" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>49</v>
       </c>
@@ -10806,11 +11598,14 @@
       <c r="J260">
         <v>0.96693999999999991</v>
       </c>
-      <c r="Q260">
+      <c r="K260">
         <v>0.80153999999999992</v>
       </c>
-    </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S260" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="261" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>50</v>
       </c>
@@ -10832,11 +11627,14 @@
       <c r="J261">
         <v>0.97770000000000012</v>
       </c>
-      <c r="Q261">
+      <c r="K261">
         <v>0.81021999999999994</v>
       </c>
-    </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S261" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="262" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>51</v>
       </c>
@@ -10858,11 +11656,14 @@
       <c r="J262">
         <v>0.98339999999999994</v>
       </c>
-      <c r="Q262">
+      <c r="K262">
         <v>0.79897000000000007</v>
       </c>
-    </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S262" s="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="263" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>52</v>
       </c>
@@ -10884,11 +11685,14 @@
       <c r="J263">
         <v>0.98091666666666655</v>
       </c>
-      <c r="Q263">
+      <c r="K263">
         <v>0.74464545454545439</v>
       </c>
-    </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S263" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="264" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>53</v>
       </c>
@@ -10910,11 +11714,14 @@
       <c r="J264">
         <v>0.97477999999999998</v>
       </c>
-      <c r="Q264">
+      <c r="K264">
         <v>0.74029999999999996</v>
       </c>
-    </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S264" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="265" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>54</v>
       </c>
@@ -10936,11 +11743,14 @@
       <c r="J265">
         <v>0.97060000000000002</v>
       </c>
-      <c r="Q265">
+      <c r="K265">
         <v>0.74370909090909099</v>
       </c>
-    </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S265" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="266" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>55</v>
       </c>
@@ -10962,11 +11772,14 @@
       <c r="J266">
         <v>0.97516249999999993</v>
       </c>
-      <c r="Q266">
+      <c r="K266">
         <v>0.73859999999999992</v>
       </c>
-    </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S266" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="267" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>56</v>
       </c>
@@ -10988,11 +11801,14 @@
       <c r="J267">
         <v>0.97058</v>
       </c>
-      <c r="Q267">
+      <c r="K267">
         <v>0.74379090909090906</v>
       </c>
-    </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S267" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="268" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>57</v>
       </c>
@@ -11014,11 +11830,14 @@
       <c r="J268">
         <v>0.97916666666666663</v>
       </c>
-      <c r="Q268">
+      <c r="K268">
         <v>0.74036363636363622</v>
       </c>
-    </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S268" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="269" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>58</v>
       </c>
@@ -11040,11 +11859,14 @@
       <c r="J269">
         <v>0.97889999999999999</v>
       </c>
-      <c r="Q269">
+      <c r="K269">
         <v>0.68714166666666665</v>
       </c>
-    </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S269" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="270" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>59</v>
       </c>
@@ -11066,11 +11888,14 @@
       <c r="J270">
         <v>0.97664285714285715</v>
       </c>
-      <c r="Q270">
+      <c r="K270">
         <v>0.68956666666666655</v>
       </c>
-    </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S270" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="271" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>60</v>
       </c>
@@ -11092,11 +11917,14 @@
       <c r="J271">
         <v>0.96952499999999997</v>
       </c>
-      <c r="Q271">
+      <c r="K271">
         <v>0.68432499999999996</v>
       </c>
-    </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S271" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="272" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>61</v>
       </c>
@@ -11118,11 +11946,14 @@
       <c r="J272">
         <v>0.97160000000000002</v>
       </c>
-      <c r="Q272">
+      <c r="K272">
         <v>0.68239166666666662</v>
       </c>
-    </row>
-    <row r="273" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S272" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="273" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>62</v>
       </c>
@@ -11144,11 +11975,14 @@
       <c r="J273">
         <v>0.97338000000000002</v>
       </c>
-      <c r="Q273">
+      <c r="K273">
         <v>0.68491666666666662</v>
       </c>
-    </row>
-    <row r="274" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S273" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="274" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>63</v>
       </c>
@@ -11170,11 +12004,14 @@
       <c r="J274">
         <v>0.97720000000000007</v>
       </c>
-      <c r="Q274">
+      <c r="K274">
         <v>0.69059999999999999</v>
       </c>
-    </row>
-    <row r="275" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S274" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="275" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>64</v>
       </c>
@@ -11196,11 +12033,14 @@
       <c r="J275">
         <v>0.98195999999999994</v>
       </c>
-      <c r="Q275">
+      <c r="K275">
         <v>0.69778333333333331</v>
       </c>
-    </row>
-    <row r="276" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S275" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="276" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <v>65</v>
       </c>
@@ -11222,11 +12062,14 @@
       <c r="J276">
         <v>0.97433333333333338</v>
       </c>
-      <c r="Q276">
+      <c r="K276">
         <v>0.68842499999999995</v>
       </c>
-    </row>
-    <row r="277" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S276" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="277" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <v>66</v>
       </c>
@@ -11248,11 +12091,14 @@
       <c r="J277">
         <v>0.97625000000000006</v>
       </c>
-      <c r="Q277">
+      <c r="K277">
         <v>0.69053333333333333</v>
       </c>
-    </row>
-    <row r="278" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S277" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="278" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>67</v>
       </c>
@@ -11274,11 +12120,14 @@
       <c r="J278">
         <v>0.98260000000000003</v>
       </c>
-      <c r="Q278">
+      <c r="K278">
         <v>0.64610769230769249</v>
       </c>
-    </row>
-    <row r="279" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S278" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="279" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>68</v>
       </c>
@@ -11300,11 +12149,14 @@
       <c r="J279">
         <v>0.97378750000000003</v>
       </c>
-      <c r="Q279">
+      <c r="K279">
         <v>0.64163076923076923</v>
       </c>
-    </row>
-    <row r="280" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S279" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="280" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>69</v>
       </c>
@@ -11326,11 +12178,14 @@
       <c r="J280">
         <v>0.97740000000000005</v>
       </c>
-      <c r="Q280">
+      <c r="K280">
         <v>0.645323076923077</v>
       </c>
-    </row>
-    <row r="281" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S280" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="281" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>70</v>
       </c>
@@ -11352,11 +12207,14 @@
       <c r="J281">
         <v>0.97663333333333335</v>
       </c>
-      <c r="Q281">
+      <c r="K281">
         <v>0.64583846153846147</v>
       </c>
-    </row>
-    <row r="282" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S281" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="282" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>71</v>
       </c>
@@ -11378,11 +12236,14 @@
       <c r="J282">
         <v>0.96336250000000001</v>
       </c>
-      <c r="Q282">
+      <c r="K282">
         <v>0.60136428571428568</v>
       </c>
-    </row>
-    <row r="283" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S282" s="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="283" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>72</v>
       </c>
@@ -11404,11 +12265,14 @@
       <c r="J283">
         <v>0.97528750000000008</v>
       </c>
-      <c r="Q283">
+      <c r="K283">
         <v>0.60235000000000016</v>
       </c>
-    </row>
-    <row r="284" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S283" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="284" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>73</v>
       </c>
@@ -11430,11 +12294,14 @@
       <c r="J284">
         <v>0.9754799999999999</v>
       </c>
-      <c r="Q284">
+      <c r="K284">
         <v>0.60471428571428576</v>
       </c>
-    </row>
-    <row r="285" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S284" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="285" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>74</v>
       </c>
@@ -11456,11 +12323,14 @@
       <c r="J285">
         <v>0.97542000000000006</v>
       </c>
-      <c r="Q285">
+      <c r="K285">
         <v>0.57020000000000004</v>
       </c>
-    </row>
-    <row r="286" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S285" s="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="286" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>75</v>
       </c>
@@ -11482,11 +12352,14 @@
       <c r="J286">
         <v>0.75514999999999999</v>
       </c>
-      <c r="Q286">
+      <c r="K286">
         <v>0.57103999999999999</v>
       </c>
-    </row>
-    <row r="287" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S286" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="287" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>76</v>
       </c>
@@ -11508,11 +12381,14 @@
       <c r="J287">
         <v>0.85325714285714283</v>
       </c>
-      <c r="Q287">
+      <c r="K287">
         <v>0.54065625000000006</v>
       </c>
-    </row>
-    <row r="288" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S287" s="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="288" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>77</v>
       </c>
@@ -11534,11 +12410,14 @@
       <c r="J288">
         <v>0.69355</v>
       </c>
-      <c r="Q288">
+      <c r="K288">
         <v>0.539825</v>
       </c>
-    </row>
-    <row r="289" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S288" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="289" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>78</v>
       </c>
@@ -11560,11 +12439,14 @@
       <c r="J289">
         <v>0.68238333333333345</v>
       </c>
-      <c r="Q289">
+      <c r="K289">
         <v>0.51399411764705882</v>
       </c>
-    </row>
-    <row r="290" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S289" s="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="290" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>79</v>
       </c>
@@ -11586,11 +12468,14 @@
       <c r="J290">
         <v>0.85240000000000005</v>
       </c>
-      <c r="Q290">
+      <c r="K290">
         <v>0.51433529411764711</v>
       </c>
-    </row>
-    <row r="291" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S290" s="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="291" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>80</v>
       </c>
@@ -11612,11 +12497,14 @@
       <c r="J291">
         <v>0.97631666666666661</v>
       </c>
-      <c r="Q291">
+      <c r="K291">
         <v>0.51543529411764699</v>
       </c>
-    </row>
-    <row r="292" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S291" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="292" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>81</v>
       </c>
@@ -11638,11 +12526,14 @@
       <c r="J292">
         <v>0.65776250000000003</v>
       </c>
-      <c r="Q292">
+      <c r="K292">
         <v>0.51409411764705892</v>
       </c>
-    </row>
-    <row r="293" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S292" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="293" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>82</v>
       </c>
@@ -11664,11 +12555,14 @@
       <c r="J293">
         <v>0.97682857142857138</v>
       </c>
-      <c r="Q293">
+      <c r="K293">
         <v>0.51354705882352936</v>
       </c>
-    </row>
-    <row r="294" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S293" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="294" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>83</v>
       </c>
@@ -11690,11 +12584,14 @@
       <c r="J294">
         <v>0.85202857142857147</v>
       </c>
-      <c r="Q294">
+      <c r="K294">
         <v>0.51684705882352944</v>
       </c>
-    </row>
-    <row r="295" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S294" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="295" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>84</v>
       </c>
@@ -11716,11 +12613,14 @@
       <c r="J295">
         <v>0.85185714285714287</v>
       </c>
-      <c r="Q295">
+      <c r="K295">
         <v>0.51502352941176466</v>
       </c>
-    </row>
-    <row r="296" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S295" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="296" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>85</v>
       </c>
@@ -11742,11 +12642,14 @@
       <c r="J296">
         <v>0.97160000000000002</v>
       </c>
-      <c r="Q296">
+      <c r="K296">
         <v>0.5149588235294118</v>
       </c>
-    </row>
-    <row r="297" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S296" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="297" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>86</v>
       </c>
@@ -11768,11 +12671,14 @@
       <c r="J297">
         <v>0.84199999999999986</v>
       </c>
-      <c r="Q297">
+      <c r="K297">
         <v>0.50755294117647065</v>
       </c>
-    </row>
-    <row r="298" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S297" s="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="298" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>87</v>
       </c>
@@ -11794,11 +12700,14 @@
       <c r="J298">
         <v>0.68338333333333334</v>
       </c>
-      <c r="Q298">
+      <c r="K298">
         <v>0.5132000000000001</v>
       </c>
-    </row>
-    <row r="299" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S298" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="299" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>88</v>
       </c>
@@ -11820,11 +12729,14 @@
       <c r="J299">
         <v>0.76566250000000002</v>
       </c>
-      <c r="Q299">
+      <c r="K299">
         <v>0.51038823529411759</v>
       </c>
-    </row>
-    <row r="300" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S299" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="300" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>89</v>
       </c>
@@ -11846,11 +12758,14 @@
       <c r="J300">
         <v>0.79380000000000006</v>
       </c>
-      <c r="Q300">
+      <c r="K300">
         <v>0.51598823529411775</v>
       </c>
-    </row>
-    <row r="301" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S300" s="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="301" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>90</v>
       </c>
@@ -11872,11 +12787,14 @@
       <c r="J301">
         <v>0.75133749999999999</v>
       </c>
-      <c r="Q301">
+      <c r="K301">
         <v>0.51523529411764712</v>
       </c>
-    </row>
-    <row r="302" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S301" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="302" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>91</v>
       </c>
@@ -11898,11 +12816,14 @@
       <c r="J302">
         <v>0.59385714285714286</v>
       </c>
-      <c r="Q302">
+      <c r="K302">
         <v>0.51751764705882353</v>
       </c>
-    </row>
-    <row r="303" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S302" s="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="303" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
         <v>92</v>
       </c>
@@ -11924,11 +12845,14 @@
       <c r="J303">
         <v>0.79848999999999992</v>
       </c>
-      <c r="Q303">
+      <c r="K303">
         <v>0.51643529411764699</v>
       </c>
-    </row>
-    <row r="304" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S303" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="304" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
         <v>93</v>
       </c>
@@ -11950,11 +12874,14 @@
       <c r="J304">
         <v>0.6880666666666666</v>
       </c>
-      <c r="Q304">
+      <c r="K304">
         <v>0.51661764705882351</v>
       </c>
-    </row>
-    <row r="305" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S304" s="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="305" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
         <v>94</v>
       </c>
@@ -11976,11 +12903,14 @@
       <c r="J305">
         <v>0.47578571428571431</v>
       </c>
-      <c r="Q305">
+      <c r="K305">
         <v>0.51122941176470571</v>
       </c>
-    </row>
-    <row r="306" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S305" s="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="306" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
         <v>95</v>
       </c>
@@ -11999,11 +12929,14 @@
       <c r="J306">
         <v>0.85844285714285706</v>
       </c>
-      <c r="Q306">
+      <c r="K306">
         <v>0.51626470588235296</v>
       </c>
-    </row>
-    <row r="307" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S306" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="307" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
         <v>96</v>
       </c>
@@ -12022,11 +12955,14 @@
       <c r="J307">
         <v>0.53275833333333333</v>
       </c>
-      <c r="Q307">
+      <c r="K307">
         <v>0.51674705882352934</v>
       </c>
-    </row>
-    <row r="308" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S307" s="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="308" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A308" s="1">
         <v>97</v>
       </c>
@@ -12045,11 +12981,14 @@
       <c r="J308">
         <v>0.80098999999999998</v>
       </c>
-      <c r="Q308">
+      <c r="K308">
         <v>0.5147176470588235</v>
       </c>
-    </row>
-    <row r="309" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S308" s="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="309" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A309" s="1">
         <v>98</v>
       </c>
@@ -12068,11 +13007,14 @@
       <c r="J309">
         <v>0.53750833333333325</v>
       </c>
-      <c r="Q309">
+      <c r="K309">
         <v>0.51680000000000004</v>
       </c>
-    </row>
-    <row r="310" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S309" s="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="310" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A310" s="1">
         <v>99</v>
       </c>
@@ -12091,11 +13033,14 @@
       <c r="J310">
         <v>0.57557272727272724</v>
       </c>
-      <c r="Q310">
+      <c r="K310">
         <v>0.51939411764705878</v>
       </c>
-    </row>
-    <row r="311" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S310" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="311" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A311" s="1">
         <v>100</v>
       </c>
@@ -12114,21 +13059,30 @@
       <c r="J311">
         <v>0.72270000000000001</v>
       </c>
-      <c r="Q311">
+      <c r="K311">
         <v>0.51005882352941168</v>
       </c>
-    </row>
-    <row r="314" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S311" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="314" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="315" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S314" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="315" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A315" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="316" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S315" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="316" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A316" s="1">
         <v>1</v>
       </c>
@@ -12159,11 +13113,14 @@
       <c r="J316">
         <v>0</v>
       </c>
-      <c r="Q316">
+      <c r="K316">
         <v>0</v>
       </c>
-    </row>
-    <row r="317" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S316" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A317" s="1">
         <v>2</v>
       </c>
@@ -12194,11 +13151,14 @@
       <c r="J317">
         <v>0</v>
       </c>
-      <c r="Q317">
+      <c r="K317">
         <v>2.5000000000000001E-3</v>
       </c>
-    </row>
-    <row r="318" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S317" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="318" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A318" s="1">
         <v>3</v>
       </c>
@@ -12229,11 +13189,14 @@
       <c r="J318">
         <v>8.2699999999999996E-2</v>
       </c>
-      <c r="Q318">
+      <c r="K318">
         <v>0.153</v>
       </c>
-    </row>
-    <row r="319" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S318" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="319" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A319" s="1">
         <v>4</v>
       </c>
@@ -12264,11 +13227,14 @@
       <c r="J319">
         <v>0.1065</v>
       </c>
-      <c r="Q319">
+      <c r="K319">
         <v>0.1108</v>
       </c>
-    </row>
-    <row r="320" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S319" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="320" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A320" s="1">
         <v>5</v>
       </c>
@@ -12299,11 +13265,14 @@
       <c r="J320">
         <v>0.1019</v>
       </c>
-      <c r="Q320">
+      <c r="K320">
         <v>0.1124</v>
       </c>
-    </row>
-    <row r="321" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S320" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="321" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A321" s="1">
         <v>6</v>
       </c>
@@ -12331,11 +13300,14 @@
       <c r="J321">
         <v>0.1222</v>
       </c>
-      <c r="Q321">
+      <c r="K321">
         <v>0.1032</v>
       </c>
-    </row>
-    <row r="322" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S321" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="322" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A322" s="1">
         <v>7</v>
       </c>
@@ -12363,11 +13335,14 @@
       <c r="J322">
         <v>0.11269999999999999</v>
       </c>
-      <c r="Q322">
+      <c r="K322">
         <v>0.1024</v>
       </c>
-    </row>
-    <row r="323" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S322" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="323" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A323" s="1">
         <v>8</v>
       </c>
@@ -12395,11 +13370,14 @@
       <c r="J323">
         <v>0.10100000000000001</v>
       </c>
-      <c r="Q323">
+      <c r="K323">
         <v>0.11550000000000001</v>
       </c>
-    </row>
-    <row r="324" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S323" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="324" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
         <v>9</v>
       </c>
@@ -12427,11 +13405,14 @@
       <c r="J324">
         <v>0.10100000000000001</v>
       </c>
-      <c r="Q324">
+      <c r="K324">
         <v>0.109</v>
       </c>
-    </row>
-    <row r="325" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S324" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="325" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
         <v>10</v>
       </c>
@@ -12459,11 +13440,14 @@
       <c r="J325">
         <v>8.4900000000000003E-2</v>
       </c>
-      <c r="Q325">
+      <c r="K325">
         <v>9.9500000000000005E-2</v>
       </c>
-    </row>
-    <row r="326" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S325" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="326" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A326" s="1">
         <v>11</v>
       </c>
@@ -12485,11 +13469,14 @@
       <c r="J326">
         <v>9.0700000000000003E-2</v>
       </c>
-      <c r="Q326">
+      <c r="K326">
         <v>0.1019</v>
       </c>
-    </row>
-    <row r="327" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S326" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="327" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A327" s="1">
         <v>12</v>
       </c>
@@ -12511,11 +13498,14 @@
       <c r="J327">
         <v>7.9200000000000007E-2</v>
       </c>
-      <c r="Q327">
+      <c r="K327">
         <v>0.1023</v>
       </c>
-    </row>
-    <row r="328" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S327" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="328" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
         <v>13</v>
       </c>
@@ -12537,11 +13527,14 @@
       <c r="J328">
         <v>9.4100000000000003E-2</v>
       </c>
-      <c r="Q328">
+      <c r="K328">
         <v>0.10199999999999999</v>
       </c>
-    </row>
-    <row r="329" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S328" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="329" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A329" s="1">
         <v>14</v>
       </c>
@@ -12563,11 +13556,14 @@
       <c r="J329">
         <v>9.4100000000000003E-2</v>
       </c>
-      <c r="Q329">
+      <c r="K329">
         <v>0.10299999999999999</v>
       </c>
-    </row>
-    <row r="330" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S329" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="330" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A330" s="1">
         <v>15</v>
       </c>
@@ -12589,11 +13585,14 @@
       <c r="J330">
         <v>9.8199999999999996E-2</v>
       </c>
-      <c r="Q330">
+      <c r="K330">
         <v>9.7600000000000006E-2</v>
       </c>
-    </row>
-    <row r="331" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S330" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="331" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A331" s="1">
         <v>16</v>
       </c>
@@ -12615,11 +13614,14 @@
       <c r="J331">
         <v>9.4899999999999998E-2</v>
       </c>
-      <c r="Q331">
+      <c r="K331">
         <v>9.9699999999999997E-2</v>
       </c>
-    </row>
-    <row r="332" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S331" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="332" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A332" s="1">
         <v>17</v>
       </c>
@@ -12641,11 +13643,14 @@
       <c r="J332">
         <v>9.5200000000000007E-2</v>
       </c>
-      <c r="Q332">
+      <c r="K332">
         <v>0.1007</v>
       </c>
-    </row>
-    <row r="333" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S332" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="333" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A333" s="1">
         <v>18</v>
       </c>
@@ -12667,11 +13672,14 @@
       <c r="J333">
         <v>9.98E-2</v>
       </c>
-      <c r="Q333">
+      <c r="K333">
         <v>9.9699999999999997E-2</v>
       </c>
-    </row>
-    <row r="334" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S333" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="334" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A334" s="1">
         <v>19</v>
       </c>
@@ -12693,11 +13701,14 @@
       <c r="J334">
         <v>9.4100000000000003E-2</v>
       </c>
-      <c r="Q334">
+      <c r="K334">
         <v>9.69E-2</v>
       </c>
-    </row>
-    <row r="335" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S334" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="335" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A335" s="1">
         <v>20</v>
       </c>
@@ -12719,11 +13730,14 @@
       <c r="J335">
         <v>0.1017</v>
       </c>
-      <c r="Q335">
+      <c r="K335">
         <v>9.11E-2</v>
       </c>
-    </row>
-    <row r="336" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S335" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="336" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A336" s="1">
         <v>21</v>
       </c>
@@ -12745,11 +13759,14 @@
       <c r="J336">
         <v>8.5500000000000007E-2</v>
       </c>
-      <c r="Q336">
+      <c r="K336">
         <v>0.1026</v>
       </c>
-    </row>
-    <row r="337" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S336" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="337" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A337" s="1">
         <v>22</v>
       </c>
@@ -12771,11 +13788,14 @@
       <c r="J337">
         <v>9.4700000000000006E-2</v>
       </c>
-      <c r="Q337">
+      <c r="K337">
         <v>9.1899999999999996E-2</v>
       </c>
-    </row>
-    <row r="338" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S337" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="338" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A338" s="1">
         <v>23</v>
       </c>
@@ -12797,11 +13817,14 @@
       <c r="J338">
         <v>8.6099999999999996E-2</v>
       </c>
-      <c r="Q338">
+      <c r="K338">
         <v>9.5799999999999996E-2</v>
       </c>
-    </row>
-    <row r="339" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S338" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="339" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A339" s="1">
         <v>24</v>
       </c>
@@ -12823,11 +13846,14 @@
       <c r="J339">
         <v>9.11E-2</v>
       </c>
-      <c r="Q339">
+      <c r="K339">
         <v>9.6600000000000005E-2</v>
       </c>
-    </row>
-    <row r="340" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S339" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="340" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A340" s="1">
         <v>25</v>
       </c>
@@ -12849,11 +13875,14 @@
       <c r="J340">
         <v>8.4199999999999997E-2</v>
       </c>
-      <c r="Q340">
+      <c r="K340">
         <v>9.7500000000000003E-2</v>
       </c>
-    </row>
-    <row r="341" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S340" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="341" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A341" s="1">
         <v>26</v>
       </c>
@@ -12875,11 +13904,14 @@
       <c r="J341">
         <v>9.3899999999999997E-2</v>
       </c>
-      <c r="Q341">
+      <c r="K341">
         <v>9.5500000000000002E-2</v>
       </c>
-    </row>
-    <row r="342" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S341" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="342" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A342" s="1">
         <v>27</v>
       </c>
@@ -12901,11 +13933,14 @@
       <c r="J342">
         <v>8.43E-2</v>
       </c>
-      <c r="Q342">
+      <c r="K342">
         <v>9.6500000000000002E-2</v>
       </c>
-    </row>
-    <row r="343" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S342" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="343" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A343" s="1">
         <v>28</v>
       </c>
@@ -12927,11 +13962,14 @@
       <c r="J343">
         <v>8.9700000000000002E-2</v>
       </c>
-      <c r="Q343">
+      <c r="K343">
         <v>9.8299999999999998E-2</v>
       </c>
-    </row>
-    <row r="344" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S343" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="344" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A344" s="1">
         <v>29</v>
       </c>
@@ -12953,11 +13991,14 @@
       <c r="J344">
         <v>9.6500000000000002E-2</v>
       </c>
-      <c r="Q344">
+      <c r="K344">
         <v>9.4700000000000006E-2</v>
       </c>
-    </row>
-    <row r="345" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S344" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="345" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A345" s="1">
         <v>30</v>
       </c>
@@ -12979,11 +14020,14 @@
       <c r="J345">
         <v>0.10199999999999999</v>
       </c>
-      <c r="Q345">
+      <c r="K345">
         <v>9.8799999999999999E-2</v>
       </c>
-    </row>
-    <row r="346" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S345" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="346" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A346" s="1">
         <v>31</v>
       </c>
@@ -13005,11 +14049,14 @@
       <c r="J346">
         <v>9.3399999999999997E-2</v>
       </c>
-      <c r="Q346">
+      <c r="K346">
         <v>9.7199999999999995E-2</v>
       </c>
-    </row>
-    <row r="347" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S346" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="347" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A347" s="1">
         <v>32</v>
       </c>
@@ -13031,11 +14078,14 @@
       <c r="J347">
         <v>9.0200000000000002E-2</v>
       </c>
-      <c r="Q347">
+      <c r="K347">
         <v>9.4899999999999998E-2</v>
       </c>
-    </row>
-    <row r="348" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S347" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="348" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A348" s="1">
         <v>33</v>
       </c>
@@ -13057,11 +14107,14 @@
       <c r="J348">
         <v>9.2799999999999994E-2</v>
       </c>
-      <c r="Q348">
+      <c r="K348">
         <v>9.3899999999999997E-2</v>
       </c>
-    </row>
-    <row r="349" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S348" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="349" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A349" s="1">
         <v>34</v>
       </c>
@@ -13083,11 +14136,14 @@
       <c r="J349">
         <v>9.35E-2</v>
       </c>
-      <c r="Q349">
+      <c r="K349">
         <v>9.3399999999999997E-2</v>
       </c>
-    </row>
-    <row r="350" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S349" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="350" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A350" s="1">
         <v>35</v>
       </c>
@@ -13109,11 +14165,14 @@
       <c r="J350">
         <v>9.8599999999999993E-2</v>
       </c>
-      <c r="Q350">
+      <c r="K350">
         <v>9.7699999999999995E-2</v>
       </c>
-    </row>
-    <row r="351" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S350" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="351" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A351" s="1">
         <v>36</v>
       </c>
@@ -13135,11 +14194,14 @@
       <c r="J351">
         <v>9.4700000000000006E-2</v>
       </c>
-      <c r="Q351">
+      <c r="K351">
         <v>9.5299999999999996E-2</v>
       </c>
-    </row>
-    <row r="352" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S351" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="352" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A352" s="1">
         <v>37</v>
       </c>
@@ -13161,11 +14223,14 @@
       <c r="J352">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="Q352">
+      <c r="K352">
         <v>9.5600000000000004E-2</v>
       </c>
-    </row>
-    <row r="353" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S352" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="353" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A353" s="1">
         <v>38</v>
       </c>
@@ -13187,11 +14252,14 @@
       <c r="J353">
         <v>9.1899999999999996E-2</v>
       </c>
-      <c r="Q353">
+      <c r="K353">
         <v>9.5799999999999996E-2</v>
       </c>
-    </row>
-    <row r="354" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S353" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="354" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A354" s="1">
         <v>39</v>
       </c>
@@ -13213,11 +14281,14 @@
       <c r="J354">
         <v>9.3399999999999997E-2</v>
       </c>
-      <c r="Q354">
+      <c r="K354">
         <v>9.3200000000000005E-2</v>
       </c>
-    </row>
-    <row r="355" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S354" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="355" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A355" s="1">
         <v>40</v>
       </c>
@@ -13239,11 +14310,14 @@
       <c r="J355">
         <v>8.7499999999999994E-2</v>
       </c>
-      <c r="Q355">
+      <c r="K355">
         <v>9.7299999999999998E-2</v>
       </c>
-    </row>
-    <row r="356" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S355" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="356" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A356" s="1">
         <v>41</v>
       </c>
@@ -13265,11 +14339,14 @@
       <c r="J356">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="Q356">
+      <c r="K356">
         <v>9.5000000000000001E-2</v>
       </c>
-    </row>
-    <row r="357" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S356" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="357" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A357" s="1">
         <v>42</v>
       </c>
@@ -13291,11 +14368,14 @@
       <c r="J357">
         <v>8.8900000000000007E-2</v>
       </c>
-      <c r="Q357">
+      <c r="K357">
         <v>9.9599999999999994E-2</v>
       </c>
-    </row>
-    <row r="358" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S357" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="358" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A358" s="1">
         <v>43</v>
       </c>
@@ -13317,11 +14397,14 @@
       <c r="J358">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="Q358">
+      <c r="K358">
         <v>9.9900000000000003E-2</v>
       </c>
-    </row>
-    <row r="359" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S358" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="359" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A359" s="1">
         <v>44</v>
       </c>
@@ -13343,11 +14426,14 @@
       <c r="J359">
         <v>8.8700000000000001E-2</v>
       </c>
-      <c r="Q359">
+      <c r="K359">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="360" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S359" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="360" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A360" s="1">
         <v>45</v>
       </c>
@@ -13369,11 +14455,14 @@
       <c r="J360">
         <v>9.5200000000000007E-2</v>
       </c>
-      <c r="Q360">
+      <c r="K360">
         <v>0.1017</v>
       </c>
-    </row>
-    <row r="361" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S360" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="361" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A361" s="1">
         <v>46</v>
       </c>
@@ -13395,11 +14484,14 @@
       <c r="J361">
         <v>9.1600000000000001E-2</v>
       </c>
-      <c r="Q361">
+      <c r="K361">
         <v>9.8900000000000002E-2</v>
       </c>
-    </row>
-    <row r="362" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S361" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="362" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A362" s="1">
         <v>47</v>
       </c>
@@ -13421,11 +14513,14 @@
       <c r="J362">
         <v>9.64E-2</v>
       </c>
-      <c r="Q362">
+      <c r="K362">
         <v>9.8000000000000004E-2</v>
       </c>
-    </row>
-    <row r="363" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S362" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="363" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A363" s="1">
         <v>48</v>
       </c>
@@ -13447,11 +14542,14 @@
       <c r="J363">
         <v>9.1700000000000004E-2</v>
       </c>
-      <c r="Q363">
+      <c r="K363">
         <v>9.9000000000000005E-2</v>
       </c>
-    </row>
-    <row r="364" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S363" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="364" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A364" s="1">
         <v>49</v>
       </c>
@@ -13473,11 +14571,14 @@
       <c r="J364">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="Q364">
+      <c r="K364">
         <v>9.5799999999999996E-2</v>
       </c>
-    </row>
-    <row r="365" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S364" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="365" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A365" s="1">
         <v>50</v>
       </c>
@@ -13499,11 +14600,14 @@
       <c r="J365">
         <v>9.4100000000000003E-2</v>
       </c>
-      <c r="Q365">
+      <c r="K365">
         <v>9.8100000000000007E-2</v>
       </c>
-    </row>
-    <row r="366" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S365" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="366" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A366" s="1">
         <v>51</v>
       </c>
@@ -13525,11 +14629,14 @@
       <c r="J366">
         <v>9.4200000000000006E-2</v>
       </c>
-      <c r="Q366">
+      <c r="K366">
         <v>9.6100000000000005E-2</v>
       </c>
-    </row>
-    <row r="367" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S366" s="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="367" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A367" s="1">
         <v>52</v>
       </c>
@@ -13551,11 +14658,14 @@
       <c r="J367">
         <v>9.5699999999999993E-2</v>
       </c>
-      <c r="Q367">
+      <c r="K367">
         <v>9.8799999999999999E-2</v>
       </c>
-    </row>
-    <row r="368" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S367" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="368" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A368" s="1">
         <v>53</v>
       </c>
@@ -13577,11 +14687,14 @@
       <c r="J368">
         <v>9.1399999999999995E-2</v>
       </c>
-      <c r="Q368">
+      <c r="K368">
         <v>0.1009</v>
       </c>
-    </row>
-    <row r="369" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S368" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="369" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A369" s="1">
         <v>54</v>
       </c>
@@ -13603,11 +14716,14 @@
       <c r="J369">
         <v>8.8599999999999998E-2</v>
       </c>
-      <c r="Q369">
+      <c r="K369">
         <v>9.9699999999999997E-2</v>
       </c>
-    </row>
-    <row r="370" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S369" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="370" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A370" s="1">
         <v>55</v>
       </c>
@@ -13629,11 +14745,14 @@
       <c r="J370">
         <v>9.0300000000000005E-2</v>
       </c>
-      <c r="Q370">
+      <c r="K370">
         <v>0.1027</v>
       </c>
-    </row>
-    <row r="371" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S370" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="371" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A371" s="1">
         <v>56</v>
       </c>
@@ -13655,11 +14774,14 @@
       <c r="J371">
         <v>9.1600000000000001E-2</v>
       </c>
-      <c r="Q371">
+      <c r="K371">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="372" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S371" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="372" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A372" s="1">
         <v>57</v>
       </c>
@@ -13681,11 +14803,14 @@
       <c r="J372">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="Q372">
+      <c r="K372">
         <v>9.9500000000000005E-2</v>
       </c>
-    </row>
-    <row r="373" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S372" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="373" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A373" s="1">
         <v>58</v>
       </c>
@@ -13707,11 +14832,14 @@
       <c r="J373">
         <v>8.7400000000000005E-2</v>
       </c>
-      <c r="Q373">
+      <c r="K373">
         <v>9.8799999999999999E-2</v>
       </c>
-    </row>
-    <row r="374" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S373" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="374" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A374" s="1">
         <v>59</v>
       </c>
@@ -13733,11 +14861,14 @@
       <c r="J374">
         <v>9.3899999999999997E-2</v>
       </c>
-      <c r="Q374">
+      <c r="K374">
         <v>0.1024</v>
       </c>
-    </row>
-    <row r="375" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S374" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="375" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A375" s="1">
         <v>60</v>
       </c>
@@ -13759,11 +14890,14 @@
       <c r="J375">
         <v>9.2899999999999996E-2</v>
       </c>
-      <c r="Q375">
+      <c r="K375">
         <v>0.1038</v>
       </c>
-    </row>
-    <row r="376" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S375" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="376" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A376" s="1">
         <v>61</v>
       </c>
@@ -13785,11 +14919,14 @@
       <c r="J376">
         <v>9.1600000000000001E-2</v>
       </c>
-      <c r="Q376">
+      <c r="K376">
         <v>0.10050000000000001</v>
       </c>
-    </row>
-    <row r="377" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S376" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="377" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A377" s="1">
         <v>62</v>
       </c>
@@ -13811,11 +14948,14 @@
       <c r="J377">
         <v>8.5699999999999998E-2</v>
       </c>
-      <c r="Q377">
+      <c r="K377">
         <v>0.1008</v>
       </c>
-    </row>
-    <row r="378" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S377" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="378" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A378" s="1">
         <v>63</v>
       </c>
@@ -13837,11 +14977,14 @@
       <c r="J378">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="Q378">
+      <c r="K378">
         <v>9.9900000000000003E-2</v>
       </c>
-    </row>
-    <row r="379" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S378" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="379" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A379" s="1">
         <v>64</v>
       </c>
@@ -13863,11 +15006,14 @@
       <c r="J379">
         <v>8.2500000000000004E-2</v>
       </c>
-      <c r="Q379">
+      <c r="K379">
         <v>9.5699999999999993E-2</v>
       </c>
-    </row>
-    <row r="380" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S379" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="380" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A380" s="1">
         <v>65</v>
       </c>
@@ -13889,11 +15035,14 @@
       <c r="J380">
         <v>8.5800000000000001E-2</v>
       </c>
-      <c r="Q380">
+      <c r="K380">
         <v>9.8299999999999998E-2</v>
       </c>
-    </row>
-    <row r="381" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S380" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="381" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A381" s="1">
         <v>66</v>
       </c>
@@ -13915,11 +15064,14 @@
       <c r="J381">
         <v>8.2199999999999995E-2</v>
       </c>
-      <c r="Q381">
+      <c r="K381">
         <v>9.9099999999999994E-2</v>
       </c>
-    </row>
-    <row r="382" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S381" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="382" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A382" s="1">
         <v>67</v>
       </c>
@@ -13941,11 +15093,14 @@
       <c r="J382">
         <v>8.6599999999999996E-2</v>
       </c>
-      <c r="Q382">
+      <c r="K382">
         <v>0.1003</v>
       </c>
-    </row>
-    <row r="383" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S382" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="383" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A383" s="1">
         <v>68</v>
       </c>
@@ -13967,11 +15122,14 @@
       <c r="J383">
         <v>9.1200000000000003E-2</v>
       </c>
-      <c r="Q383">
+      <c r="K383">
         <v>9.8299999999999998E-2</v>
       </c>
-    </row>
-    <row r="384" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S383" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="384" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A384" s="1">
         <v>69</v>
       </c>
@@ -13993,11 +15151,14 @@
       <c r="J384">
         <v>9.2200000000000004E-2</v>
       </c>
-      <c r="Q384">
+      <c r="K384">
         <v>0.1007</v>
       </c>
-    </row>
-    <row r="385" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S384" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="385" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A385" s="1">
         <v>70</v>
       </c>
@@ -14019,11 +15180,14 @@
       <c r="J385">
         <v>9.3700000000000006E-2</v>
       </c>
-      <c r="Q385">
+      <c r="K385">
         <v>0.1026</v>
       </c>
-    </row>
-    <row r="386" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S385" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="386" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A386" s="1">
         <v>71</v>
       </c>
@@ -14045,11 +15209,14 @@
       <c r="J386">
         <v>9.0499999999999997E-2</v>
       </c>
-      <c r="Q386">
+      <c r="K386">
         <v>0.1021</v>
       </c>
-    </row>
-    <row r="387" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S386" s="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="387" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A387" s="1">
         <v>72</v>
       </c>
@@ -14071,11 +15238,14 @@
       <c r="J387">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="Q387">
+      <c r="K387">
         <v>0.10150000000000001</v>
       </c>
-    </row>
-    <row r="388" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S387" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="388" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A388" s="1">
         <v>73</v>
       </c>
@@ -14097,11 +15267,14 @@
       <c r="J388">
         <v>8.6599999999999996E-2</v>
       </c>
-      <c r="Q388">
+      <c r="K388">
         <v>0.1052</v>
       </c>
-    </row>
-    <row r="389" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S388" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="389" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A389" s="1">
         <v>74</v>
       </c>
@@ -14123,11 +15296,14 @@
       <c r="J389">
         <v>8.5400000000000004E-2</v>
       </c>
-      <c r="Q389">
+      <c r="K389">
         <v>0.1042</v>
       </c>
-    </row>
-    <row r="390" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S389" s="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="390" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A390" s="1">
         <v>75</v>
       </c>
@@ -14149,11 +15325,14 @@
       <c r="J390">
         <v>8.8800000000000004E-2</v>
       </c>
-      <c r="Q390">
+      <c r="K390">
         <v>9.9299999999999999E-2</v>
       </c>
-    </row>
-    <row r="391" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S390" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="391" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A391" s="1">
         <v>76</v>
       </c>
@@ -14175,11 +15354,14 @@
       <c r="J391">
         <v>9.6100000000000005E-2</v>
       </c>
-      <c r="Q391">
+      <c r="K391">
         <v>0.1032</v>
       </c>
-    </row>
-    <row r="392" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S391" s="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="392" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A392" s="1">
         <v>77</v>
       </c>
@@ -14201,11 +15383,14 @@
       <c r="J392">
         <v>9.2299999999999993E-2</v>
       </c>
-      <c r="Q392">
+      <c r="K392">
         <v>0.1014</v>
       </c>
-    </row>
-    <row r="393" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S392" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="393" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A393" s="1">
         <v>78</v>
       </c>
@@ -14227,11 +15412,14 @@
       <c r="J393">
         <v>9.35E-2</v>
       </c>
-      <c r="Q393">
+      <c r="K393">
         <v>9.7600000000000006E-2</v>
       </c>
-    </row>
-    <row r="394" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S393" s="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="394" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A394" s="1">
         <v>79</v>
       </c>
@@ -14253,11 +15441,14 @@
       <c r="J394">
         <v>9.2100000000000001E-2</v>
       </c>
-      <c r="Q394">
+      <c r="K394">
         <v>0.10100000000000001</v>
       </c>
-    </row>
-    <row r="395" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S394" s="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="395" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A395" s="1">
         <v>80</v>
       </c>
@@ -14279,11 +15470,14 @@
       <c r="J395">
         <v>9.5600000000000004E-2</v>
       </c>
-      <c r="Q395">
+      <c r="K395">
         <v>0.1013</v>
       </c>
-    </row>
-    <row r="396" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S395" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="396" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A396" s="1">
         <v>81</v>
       </c>
@@ -14305,11 +15499,14 @@
       <c r="J396">
         <v>8.9399999999999993E-2</v>
       </c>
-      <c r="Q396">
+      <c r="K396">
         <v>0.10150000000000001</v>
       </c>
-    </row>
-    <row r="397" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S396" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="397" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A397" s="1">
         <v>82</v>
       </c>
@@ -14331,11 +15528,14 @@
       <c r="J397">
         <v>8.9700000000000002E-2</v>
       </c>
-      <c r="Q397">
+      <c r="K397">
         <v>9.7100000000000006E-2</v>
       </c>
-    </row>
-    <row r="398" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S397" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="398" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A398" s="1">
         <v>83</v>
       </c>
@@ -14357,11 +15557,14 @@
       <c r="J398">
         <v>8.7900000000000006E-2</v>
       </c>
-      <c r="Q398">
+      <c r="K398">
         <v>0.1003</v>
       </c>
-    </row>
-    <row r="399" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S398" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="399" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A399" s="1">
         <v>84</v>
       </c>
@@ -14383,11 +15586,14 @@
       <c r="J399">
         <v>8.6699999999999999E-2</v>
       </c>
-      <c r="Q399">
+      <c r="K399">
         <v>9.7600000000000006E-2</v>
       </c>
-    </row>
-    <row r="400" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S399" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="400" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A400" s="1">
         <v>85</v>
       </c>
@@ -14409,11 +15615,14 @@
       <c r="J400">
         <v>8.8099999999999998E-2</v>
       </c>
-      <c r="Q400">
+      <c r="K400">
         <v>9.9000000000000005E-2</v>
       </c>
-    </row>
-    <row r="401" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S400" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="401" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A401" s="1">
         <v>86</v>
       </c>
@@ -14435,11 +15644,14 @@
       <c r="J401">
         <v>8.9499999999999996E-2</v>
       </c>
-      <c r="Q401">
+      <c r="K401">
         <v>0.1026</v>
       </c>
-    </row>
-    <row r="402" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S401" s="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="402" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A402" s="1">
         <v>87</v>
       </c>
@@ -14461,11 +15673,14 @@
       <c r="J402">
         <v>9.11E-2</v>
       </c>
-      <c r="Q402">
+      <c r="K402">
         <v>0.1036</v>
       </c>
-    </row>
-    <row r="403" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S402" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="403" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A403" s="1">
         <v>88</v>
       </c>
@@ -14487,11 +15702,14 @@
       <c r="J403">
         <v>9.64E-2</v>
       </c>
-      <c r="Q403">
+      <c r="K403">
         <v>9.2299999999999993E-2</v>
       </c>
-    </row>
-    <row r="404" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S403" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="404" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A404" s="1">
         <v>89</v>
       </c>
@@ -14513,11 +15731,14 @@
       <c r="J404">
         <v>9.0899999999999995E-2</v>
       </c>
-      <c r="Q404">
+      <c r="K404">
         <v>9.3100000000000002E-2</v>
       </c>
-    </row>
-    <row r="405" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S404" s="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="405" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A405" s="1">
         <v>90</v>
       </c>
@@ -14539,11 +15760,14 @@
       <c r="J405">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="Q405">
+      <c r="K405">
         <v>0.1019</v>
       </c>
-    </row>
-    <row r="406" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S405" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="406" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A406" s="1">
         <v>91</v>
       </c>
@@ -14565,11 +15789,14 @@
       <c r="J406">
         <v>9.06E-2</v>
       </c>
-      <c r="Q406">
+      <c r="K406">
         <v>9.7199999999999995E-2</v>
       </c>
-    </row>
-    <row r="407" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S406" s="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="407" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A407" s="1">
         <v>92</v>
       </c>
@@ -14591,11 +15818,14 @@
       <c r="J407">
         <v>9.0200000000000002E-2</v>
       </c>
-      <c r="Q407">
+      <c r="K407">
         <v>9.7600000000000006E-2</v>
       </c>
-    </row>
-    <row r="408" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S407" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="408" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A408" s="1">
         <v>93</v>
       </c>
@@ -14617,11 +15847,14 @@
       <c r="J408">
         <v>8.9399999999999993E-2</v>
       </c>
-      <c r="Q408">
+      <c r="K408">
         <v>9.6299999999999997E-2</v>
       </c>
-    </row>
-    <row r="409" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S408" s="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="409" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A409" s="1">
         <v>94</v>
       </c>
@@ -14643,11 +15876,14 @@
       <c r="J409">
         <v>9.0200000000000002E-2</v>
       </c>
-      <c r="Q409">
+      <c r="K409">
         <v>9.5200000000000007E-2</v>
       </c>
-    </row>
-    <row r="410" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S409" s="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="410" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A410" s="1">
         <v>95</v>
       </c>
@@ -14666,11 +15902,14 @@
       <c r="J410">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="Q410">
+      <c r="K410">
         <v>9.8599999999999993E-2</v>
       </c>
-    </row>
-    <row r="411" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S410" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="411" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A411" s="1">
         <v>96</v>
       </c>
@@ -14689,11 +15928,14 @@
       <c r="J411">
         <v>9.01E-2</v>
       </c>
-      <c r="Q411">
+      <c r="K411">
         <v>9.9099999999999994E-2</v>
       </c>
-    </row>
-    <row r="412" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S411" s="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="412" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A412" s="1">
         <v>97</v>
       </c>
@@ -14712,11 +15954,14 @@
       <c r="J412">
         <v>9.0700000000000003E-2</v>
       </c>
-      <c r="Q412">
+      <c r="K412">
         <v>0.1043</v>
       </c>
-    </row>
-    <row r="413" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S412" s="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="413" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A413" s="1">
         <v>98</v>
       </c>
@@ -14735,11 +15980,14 @@
       <c r="J413">
         <v>9.5899999999999999E-2</v>
       </c>
-      <c r="Q413">
+      <c r="K413">
         <v>0.1023</v>
       </c>
-    </row>
-    <row r="414" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S413" s="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="414" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A414" s="1">
         <v>99</v>
       </c>
@@ -14758,11 +16006,14 @@
       <c r="J414">
         <v>7.5200000000000003E-2</v>
       </c>
-      <c r="Q414">
+      <c r="K414">
         <v>9.5600000000000004E-2</v>
       </c>
-    </row>
-    <row r="415" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S414" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="415" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A415" s="1">
         <v>100</v>
       </c>
@@ -14781,16 +16032,20 @@
       <c r="J415">
         <v>9.4600000000000004E-2</v>
       </c>
-      <c r="Q415">
+      <c r="K415">
         <v>9.2799999999999994E-2</v>
       </c>
+      <c r="S415" s="1">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="L3:Q3"/>
+    <mergeCell ref="T2:U2"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="C2:D2"/>
-    <mergeCell ref="K3:P3"/>
     <mergeCell ref="F2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/CIFAR_Global.xlsx
+++ b/CIFAR_Global.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashleyau/Documents/PhD/Practical_Experiment/Finalised/Finalised_Algorithm_ResNet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07DC9284-FF97-5446-B1C6-C2497DB9B1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24E2666-CA2D-D247-BC8B-C16C3158DF52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="19980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="27">
   <si>
     <t>100 Rounds</t>
   </si>
@@ -99,12 +99,15 @@
   <si>
     <t>Updated Cluster</t>
   </si>
+  <si>
+    <t>FL-Defender</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -126,6 +129,19 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -184,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -205,14 +221,21 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3645,15 +3668,682 @@
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>All Benign</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$U$5:$U$104</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>0.1134</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.15129999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1401</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.15040000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.15229999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.17299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.1865</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.1799</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.1951</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.189</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.2011</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.20599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.20749999999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.1981</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.1741</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.17810000000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.2092</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.21529999999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.19950000000000001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.21690000000000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.2218</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.20899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.21490000000000001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.21829999999999999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.22090000000000001</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.22670000000000001</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.22589999999999999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.23430000000000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.23219999999999999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.2155</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.2382</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.2266</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.21940000000000001</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.22059999999999999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.24129999999999999</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.2432</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.2424</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.24099999999999999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.23630000000000001</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.23960000000000001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.24060000000000001</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.24740000000000001</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.24079999999999999</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.23980000000000001</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.24010000000000001</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.24410000000000001</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.24149999999999999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.246</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.24360000000000001</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.24579999999999999</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.2374</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.245</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.2477</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.2477</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.248</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.24379999999999999</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.24879999999999999</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.25069999999999998</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.24479999999999999</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.24310000000000001</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.23830000000000001</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.24160000000000001</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.25130000000000002</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.2445</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.24429999999999999</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.2467</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.2389</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.2482</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.25190000000000001</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.24970000000000001</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.25059999999999999</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.24840000000000001</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.2442</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.2457</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.25019999999999998</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.25019999999999998</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.25019999999999998</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.25159999999999999</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.24410000000000001</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.2399</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.25269999999999998</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.25569999999999998</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.25340000000000001</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.24540000000000001</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.25269999999999998</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.2477</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.24970000000000001</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.25119999999999998</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.2404</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.24840000000000001</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.25069999999999998</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.2515</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.24199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.25309999999999999</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.246</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.24410000000000001</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.24410000000000001</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.24629999999999999</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.248</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-F5F0-0441-97D0-DF748EB9399D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>FL-Defender</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AE$5:$AE$104</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.1172</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.1144</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.15079999999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.1069</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.15140000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.11840000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.12509999999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.10050000000000001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.15690000000000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.1419</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.10730000000000001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>9.2399999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.152</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>9.5100000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.16259999999999999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.1014</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.16009999999999999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.1091</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.1338</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.1023</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.18079999999999999</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.2407</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.1207</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.1356</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.10249999999999999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.1812</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.13969999999999999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.12479999999999999</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.2036</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.12959999999999999</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.21099999999999999</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>9.7299999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.1552</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.19120000000000001</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.19589999999999999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.20349999999999999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.20100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.24440000000000001</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.18260000000000001</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.1298</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.1812</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.13969999999999999</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.12479999999999999</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.1057</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.13639999999999999</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.1203</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.1797</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.16739999999999999</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.1424</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.16850000000000001</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.15429999999999999</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.16650000000000001</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.1137</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.22739999999999999</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.20899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.26329999999999998</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.20749999999999999</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.21010000000000001</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.1305</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.15629999999999999</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.17630000000000001</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.1094</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.1966</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.15110000000000001</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.15809999999999999</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.2205</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.28560000000000002</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.2031</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.20530000000000001</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.12239999999999999</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.14000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.1981</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.19</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.2021</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.29859999999999998</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.29189999999999999</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.20599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.28810000000000002</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.21</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.3518</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.2094</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.2097</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.21049999999999999</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.35680000000000001</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.19239999999999999</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.14530000000000001</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.16569999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4447-BF44-B98A-4BC225D62C50}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="0"/>
-          <c:order val="0"/>
+          <c:order val="2"/>
           <c:tx>
             <c:v>My Alg</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:prstDash val="solid"/>
               <a:round/>
@@ -3975,340 +4665,6 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-F5F0-0441-97D0-DF748EB9399D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>All Benign</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="E78BA0"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$U$5:$U$104</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="100"/>
-                <c:pt idx="0">
-                  <c:v>0.1134</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.15129999999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.1401</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.15040000000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.15229999999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.17299999999999999</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.1865</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.1799</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.1951</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.189</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.2011</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.20599999999999999</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.20749999999999999</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.1981</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.1741</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.17810000000000001</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.2092</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.21529999999999999</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.19950000000000001</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.21690000000000001</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.2218</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.20899999999999999</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.21490000000000001</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.21829999999999999</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.22090000000000001</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.22670000000000001</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.22589999999999999</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.23430000000000001</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.23219999999999999</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.2155</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.2382</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.2266</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.21940000000000001</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.22059999999999999</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.24129999999999999</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.2432</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.2424</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.24099999999999999</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.23630000000000001</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.23960000000000001</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.24060000000000001</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.24740000000000001</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.24079999999999999</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.23980000000000001</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.24010000000000001</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0.24410000000000001</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.24149999999999999</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.246</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.24360000000000001</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.24579999999999999</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.2374</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.245</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.2477</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.2477</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.248</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.24379999999999999</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.24879999999999999</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.25069999999999998</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.24479999999999999</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.24310000000000001</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.23830000000000001</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.24160000000000001</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.25130000000000002</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0.2445</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0.24429999999999999</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0.2467</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0.2389</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>0.2482</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>0.25190000000000001</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0.24970000000000001</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0.25059999999999999</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>0.24840000000000001</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>0.2442</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>0.2457</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>0.25019999999999998</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>0.25019999999999998</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>0.25019999999999998</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>0.25159999999999999</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>0.24410000000000001</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>0.2399</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>0.25</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>0.25269999999999998</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>0.25569999999999998</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>0.25340000000000001</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>0.24540000000000001</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>0.25269999999999998</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>0.2477</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>0.24970000000000001</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>0.25119999999999998</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>0.2404</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>0.24840000000000001</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>0.25069999999999998</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>0.2515</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>0.24199999999999999</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>0.25309999999999999</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>0.246</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>0.24410000000000001</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>0.24410000000000001</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>0.24629999999999999</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>0.248</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-F5F0-0441-97D0-DF748EB9399D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4558,7 +4914,10 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:prstDash val="solid"/>
               <a:round/>
@@ -4890,9 +5249,11 @@
             <c:v>All Benign</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="E78BA0"/>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:prstDash val="solid"/>
               <a:round/>
@@ -5470,15 +5831,691 @@
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>All Benign</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$W$5:$W$104</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>0.124</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.15890000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.15629999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.16350000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.2044</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.21340000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.18579999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.19869999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.20019999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.217</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.2223</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.22850000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.19500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.20680000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.20910000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.22459999999999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.21360000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.223</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.2316</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.22670000000000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.22020000000000001</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.21079999999999999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.23400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.17319999999999999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.20619999999999999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.18659999999999999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.22459999999999999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.182</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.17460000000000001</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.17510000000000001</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.19769999999999999</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.22109999999999999</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.23269999999999999</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.22720000000000001</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.22359999999999999</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.22770000000000001</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.21709999999999999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.21779999999999999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.20610000000000001</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.2064</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.19539999999999999</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.20449999999999999</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.2165</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.222</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.2276</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.215</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.18659999999999999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.2092</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.21440000000000001</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.19889999999999999</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.1585</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.19670000000000001</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.22140000000000001</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.21560000000000001</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.2165</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.20519999999999999</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.21609999999999999</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.2049</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.21390000000000001</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.18729999999999999</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.21149999999999999</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.21460000000000001</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.22620000000000001</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.2155</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.2268</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.224</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.22670000000000001</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.2172</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.19470000000000001</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.19769999999999999</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.2036</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.2122</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.2276</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.2059</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.20810000000000001</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.2102</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.2147</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.1915</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.14699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.1002</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.123</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.1628</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.15890000000000001</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.1055</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.1656</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.1789</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.18140000000000001</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.14680000000000001</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.18640000000000001</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.20610000000000001</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.1961</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.18690000000000001</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.14130000000000001</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.16600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.1646</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.1951</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.18859999999999999</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.186</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.15590000000000001</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.17030000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-EFF3-F846-99E0-D9441215123F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>FL-Defender</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AE$5:$AE$104</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.1172</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.1144</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.15079999999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.1069</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.15140000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.11840000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.12509999999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.10050000000000001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.15690000000000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.1419</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.10730000000000001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>9.2399999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.152</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>9.5100000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.16259999999999999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.1014</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.16009999999999999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.1091</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.1338</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.1023</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.18079999999999999</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.2407</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.1207</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.1356</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.10249999999999999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.1812</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.13969999999999999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.12479999999999999</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.2036</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.12959999999999999</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.21099999999999999</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>9.7299999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.1552</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.19120000000000001</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.19589999999999999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.20349999999999999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.20100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.24440000000000001</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.18260000000000001</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.1298</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.1812</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.13969999999999999</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.12479999999999999</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.1057</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.13639999999999999</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>9.0899999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.1203</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.1797</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.16739999999999999</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.1424</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.16850000000000001</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.15429999999999999</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.16650000000000001</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.1137</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.22739999999999999</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.20899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.26329999999999998</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.20749999999999999</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.21010000000000001</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.1305</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.15629999999999999</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.17630000000000001</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.1094</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.1966</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.15110000000000001</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.15809999999999999</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.2205</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.28560000000000002</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.2031</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.20530000000000001</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.12239999999999999</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.14000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.1981</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.19</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.2021</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.29859999999999998</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.29189999999999999</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.20599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.28810000000000002</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.21</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.3518</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.2094</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.2097</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.21049999999999999</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.35680000000000001</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.19239999999999999</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.14530000000000001</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.16569999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-509C-7C44-A2FC-2FC66763B1B0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="0"/>
-          <c:order val="0"/>
+          <c:order val="2"/>
           <c:tx>
             <c:v>My Alg</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -5800,340 +6837,6 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-EFF3-F846-99E0-D9441215123F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>All Benign</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$W$5:$W$104</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="100"/>
-                <c:pt idx="0">
-                  <c:v>0.124</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.15890000000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.15629999999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.16350000000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.2044</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.21340000000000001</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.18579999999999999</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.19869999999999999</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.20019999999999999</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.217</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.2223</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.22850000000000001</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.19500000000000001</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.20680000000000001</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.20910000000000001</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.22459999999999999</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.21360000000000001</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.223</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.2316</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.22670000000000001</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.22020000000000001</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.21079999999999999</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.23400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.17319999999999999</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.20619999999999999</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.18659999999999999</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.22459999999999999</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.182</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.17460000000000001</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.17510000000000001</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.19769999999999999</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.22109999999999999</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.23269999999999999</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.22720000000000001</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.22359999999999999</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.22770000000000001</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.21709999999999999</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.21779999999999999</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.20610000000000001</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.2064</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.19539999999999999</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.20449999999999999</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.2165</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.222</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.2276</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0.215</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.18659999999999999</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.2092</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.21440000000000001</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.19889999999999999</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.1585</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.19670000000000001</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.22140000000000001</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.21560000000000001</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.2165</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.20519999999999999</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.21609999999999999</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.2049</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.21390000000000001</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.18729999999999999</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.21149999999999999</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.21460000000000001</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.22620000000000001</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0.2155</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0.2268</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0.224</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0.22670000000000001</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>0.2172</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>0.19470000000000001</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0.19769999999999999</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0.2036</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>0.2122</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>0.2276</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>0.2059</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>0.20810000000000001</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>0.2102</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>0.2147</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>0.1915</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>0.14699999999999999</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>0.1002</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>0.123</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>0.1628</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>0.15890000000000001</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>0.1055</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>0.1656</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>0.1789</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>0.18140000000000001</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>0.14680000000000001</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>0.18640000000000001</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>0.20610000000000001</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>0.1961</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>0.18690000000000001</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>0.14130000000000001</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>0.16600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>0.1646</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>0.1951</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>0.18859999999999999</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>0.186</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>0.15590000000000001</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>0.17030000000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-EFF3-F846-99E0-D9441215123F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6414,15 +7117,355 @@
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>All Benign</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$W$108:$W$207</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.91666666666666663</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.63636363636363635</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.90909090909090906</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.81818181818181823</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.91666666666666663</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.81818181818181823</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.7142857142857143</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.76923076923076927</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.77777777777777779</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.88888888888888884</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.83333333333333337</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.77777777777777779</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.83333333333333337</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.77777777777777779</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.81818181818181823</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.8571428571428571</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.90909090909090906</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.81818181818181823</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.77777777777777779</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.63636363636363635</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.66666666666666663</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.83333333333333337</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.83333333333333337</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.77777777777777779</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.81818181818181823</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.8571428571428571</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.88888888888888884</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.88888888888888884</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.77777777777777779</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.7142857142857143</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.7142857142857143</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.83333333333333337</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.8571428571428571</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.8571428571428571</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.8571428571428571</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.7142857142857143</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.83333333333333337</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.66666666666666663</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-25DD-2E47-911D-2E537F7B2013}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="0"/>
-          <c:order val="0"/>
+          <c:order val="1"/>
           <c:tx>
             <c:v>My Alg</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -6744,340 +7787,6 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-25DD-2E47-911D-2E537F7B2013}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>All Benign</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$W$108:$W$207</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="100"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.91666666666666663</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.63636363636363635</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.90909090909090906</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.81818181818181823</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.875</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.8</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.7</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.91666666666666663</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.81818181818181823</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.7142857142857143</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.76923076923076927</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.77777777777777779</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.88888888888888884</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.875</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.83333333333333337</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.7</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.875</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.77777777777777779</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.875</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.8</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.83333333333333337</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.77777777777777779</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.81818181818181823</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.8571428571428571</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.90909090909090906</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.81818181818181823</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.77777777777777779</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.63636363636363635</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.66666666666666663</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.83333333333333337</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.875</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.875</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.83333333333333337</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.77777777777777779</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.81818181818181823</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.8571428571428571</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.88888888888888884</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.88888888888888884</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.8</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0.77777777777777779</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0.7142857142857143</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0.7142857142857143</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0.875</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>0.83333333333333337</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>0.8571428571428571</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>0.8571428571428571</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>0.8571428571428571</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>0.875</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>0.7142857142857143</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>0.83333333333333337</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>0.66666666666666663</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>0.8</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>0.8</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-25DD-2E47-911D-2E537F7B2013}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8543,13 +9252,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>31750</xdr:colOff>
+      <xdr:colOff>91281</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
+      <xdr:colOff>719931</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
@@ -8579,13 +9288,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
+      <xdr:colOff>104775</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>673100</xdr:colOff>
+      <xdr:colOff>752475</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
@@ -9004,7 +9713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z415"/>
+  <dimension ref="A1:AG504"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -9018,7 +9727,7 @@
     <col min="20" max="20" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9026,27 +9735,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="11"/>
+      <c r="D2" s="15"/>
       <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
       <c r="K2" s="7" t="s">
         <v>6</v>
       </c>
@@ -9054,14 +9763,20 @@
       <c r="S2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="13" t="s">
+      <c r="T2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="U2" s="13"/>
-      <c r="V2" s="13"/>
-      <c r="W2" s="13"/>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+      <c r="AD2" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE2" s="12"/>
+      <c r="AF2" s="8"/>
+      <c r="AG2" s="8"/>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -9092,14 +9807,14 @@
       <c r="J3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="14" t="s">
+      <c r="L3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
       <c r="R3" s="4"/>
       <c r="S3" s="1" t="s">
         <v>8</v>
@@ -9119,32 +9834,42 @@
       <c r="Z3" s="9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AD3" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE3" s="14"/>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="10" t="s">
+      <c r="H4" s="15"/>
+      <c r="I4" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="11"/>
+      <c r="J4" s="15"/>
       <c r="S4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="10" t="s">
+      <c r="T4" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="U4" s="10"/>
-      <c r="V4" s="10" t="s">
+      <c r="U4" s="13"/>
+      <c r="V4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="W4" s="10"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="W4" s="13"/>
+      <c r="AD4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -9193,8 +9918,14 @@
       <c r="W5">
         <v>0.124</v>
       </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AD5" s="10">
+        <v>9.2499999999999999E-2</v>
+      </c>
+      <c r="AE5" s="10">
+        <v>9.0899999999999995E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -9243,8 +9974,14 @@
       <c r="W6">
         <v>0.15890000000000001</v>
       </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AD6" s="10">
+        <v>0.1792</v>
+      </c>
+      <c r="AE6" s="10">
+        <v>9.0899999999999995E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -9293,8 +10030,14 @@
       <c r="W7">
         <v>0.15629999999999999</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AD7" s="10">
+        <v>0.36649999999999999</v>
+      </c>
+      <c r="AE7" s="10">
+        <v>9.0899999999999995E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -9343,8 +10086,14 @@
       <c r="W8">
         <v>0.16350000000000001</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AD8" s="10">
+        <v>0.49740000000000001</v>
+      </c>
+      <c r="AE8" s="10">
+        <v>9.0899999999999995E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -9393,8 +10142,14 @@
       <c r="W9">
         <v>0.2044</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AD9" s="10">
+        <v>0.49930000000000002</v>
+      </c>
+      <c r="AE9" s="10">
+        <v>9.0899999999999995E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -9440,8 +10195,14 @@
       <c r="W10">
         <v>0.21340000000000001</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AD10" s="10">
+        <v>0.52329999999999999</v>
+      </c>
+      <c r="AE10" s="10">
+        <v>9.0899999999999995E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -9487,8 +10248,14 @@
       <c r="W11">
         <v>0.18579999999999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AD11" s="10">
+        <v>0.5353</v>
+      </c>
+      <c r="AE11" s="10">
+        <v>9.0899999999999995E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -9534,8 +10301,14 @@
       <c r="W12">
         <v>0.19869999999999999</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AD12" s="10">
+        <v>0.54849999999999999</v>
+      </c>
+      <c r="AE12" s="10">
+        <v>9.0899999999999995E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -9581,8 +10354,14 @@
       <c r="W13">
         <v>0.20019999999999999</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AD13" s="10">
+        <v>0.55320000000000003</v>
+      </c>
+      <c r="AE13" s="10">
+        <v>9.0899999999999995E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -9628,8 +10407,14 @@
       <c r="W14">
         <v>0.217</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AD14" s="10">
+        <v>0.56340000000000001</v>
+      </c>
+      <c r="AE14" s="10">
+        <v>0.1172</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -9669,8 +10454,14 @@
       <c r="W15">
         <v>0.2223</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AD15" s="10">
+        <v>0.58189999999999997</v>
+      </c>
+      <c r="AE15" s="10">
+        <v>9.0899999999999995E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -9710,8 +10501,14 @@
       <c r="W16">
         <v>0.22850000000000001</v>
       </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD16" s="10">
+        <v>0.57550000000000001</v>
+      </c>
+      <c r="AE16" s="10">
+        <v>0.1144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -9751,8 +10548,14 @@
       <c r="W17">
         <v>0.19500000000000001</v>
       </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD17" s="10">
+        <v>0.57909999999999995</v>
+      </c>
+      <c r="AE17" s="10">
+        <v>0.15079999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -9792,8 +10595,14 @@
       <c r="W18">
         <v>0.20680000000000001</v>
       </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD18" s="10">
+        <v>0.59009999999999996</v>
+      </c>
+      <c r="AE18" s="10">
+        <v>0.1069</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -9833,8 +10642,14 @@
       <c r="W19">
         <v>0.20910000000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD19" s="10">
+        <v>0.59279999999999999</v>
+      </c>
+      <c r="AE19" s="10">
+        <v>0.15140000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -9874,8 +10689,14 @@
       <c r="W20">
         <v>0.22459999999999999</v>
       </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD20" s="10">
+        <v>0.59350000000000003</v>
+      </c>
+      <c r="AE20" s="10">
+        <v>9.0899999999999995E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -9915,8 +10736,14 @@
       <c r="W21">
         <v>0.21360000000000001</v>
       </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD21" s="10">
+        <v>0.59830000000000005</v>
+      </c>
+      <c r="AE21" s="10">
+        <v>0.11840000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -9956,8 +10783,14 @@
       <c r="W22">
         <v>0.223</v>
       </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD22" s="10">
+        <v>0.61029999999999995</v>
+      </c>
+      <c r="AE22" s="10">
+        <v>0.12509999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -9997,8 +10830,14 @@
       <c r="W23">
         <v>0.2316</v>
       </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD23" s="10">
+        <v>0.61319999999999997</v>
+      </c>
+      <c r="AE23" s="10">
+        <v>0.10050000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -10038,8 +10877,14 @@
       <c r="W24">
         <v>0.22670000000000001</v>
       </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD24" s="10">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="AE24" s="10">
+        <v>0.15690000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -10079,8 +10924,14 @@
       <c r="W25">
         <v>0.22020000000000001</v>
       </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD25" s="10">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="AE25" s="10">
+        <v>0.1419</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -10120,8 +10971,14 @@
       <c r="W26">
         <v>0.21079999999999999</v>
       </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD26" s="10">
+        <v>0.61780000000000002</v>
+      </c>
+      <c r="AE26" s="10">
+        <v>0.10730000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -10161,8 +11018,14 @@
       <c r="W27">
         <v>0.23400000000000001</v>
       </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD27" s="10">
+        <v>0.61950000000000005</v>
+      </c>
+      <c r="AE27" s="10">
+        <v>9.2399999999999996E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -10202,8 +11065,14 @@
       <c r="W28">
         <v>0.17319999999999999</v>
       </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD28" s="10">
+        <v>0.62749999999999995</v>
+      </c>
+      <c r="AE28" s="10">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -10243,8 +11112,14 @@
       <c r="W29">
         <v>0.20619999999999999</v>
       </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD29" s="10">
+        <v>0.62329999999999997</v>
+      </c>
+      <c r="AE29" s="10">
+        <v>9.5100000000000004E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -10284,8 +11159,14 @@
       <c r="W30">
         <v>0.18659999999999999</v>
       </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD30" s="10">
+        <v>0.623</v>
+      </c>
+      <c r="AE30" s="10">
+        <v>0.16259999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -10325,8 +11206,14 @@
       <c r="W31">
         <v>0.22459999999999999</v>
       </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD31" s="10">
+        <v>0.63249999999999995</v>
+      </c>
+      <c r="AE31" s="10">
+        <v>0.1014</v>
+      </c>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -10366,8 +11253,14 @@
       <c r="W32">
         <v>0.182</v>
       </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD32" s="10">
+        <v>0.63129999999999997</v>
+      </c>
+      <c r="AE32" s="10">
+        <v>0.16009999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -10407,8 +11300,14 @@
       <c r="W33">
         <v>0.17460000000000001</v>
       </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD33" s="10">
+        <v>0.63649999999999995</v>
+      </c>
+      <c r="AE33" s="10">
+        <v>9.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -10448,8 +11347,14 @@
       <c r="W34">
         <v>0.17510000000000001</v>
       </c>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD34" s="10">
+        <v>0.63870000000000005</v>
+      </c>
+      <c r="AE34" s="10">
+        <v>0.1091</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -10489,8 +11394,14 @@
       <c r="W35">
         <v>0.19769999999999999</v>
       </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD35" s="10">
+        <v>0.63319999999999999</v>
+      </c>
+      <c r="AE35" s="10">
+        <v>0.1338</v>
+      </c>
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -10530,8 +11441,14 @@
       <c r="W36">
         <v>0.22109999999999999</v>
       </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD36" s="10">
+        <v>0.64170000000000005</v>
+      </c>
+      <c r="AE36" s="10">
+        <v>0.1023</v>
+      </c>
+    </row>
+    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -10571,8 +11488,14 @@
       <c r="W37">
         <v>0.23269999999999999</v>
       </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD37" s="10">
+        <v>0.63339999999999996</v>
+      </c>
+      <c r="AE37" s="10">
+        <v>0.18079999999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>34</v>
       </c>
@@ -10612,8 +11535,14 @@
       <c r="W38">
         <v>0.22720000000000001</v>
       </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD38" s="10">
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="AE38" s="10">
+        <v>0.2407</v>
+      </c>
+    </row>
+    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>35</v>
       </c>
@@ -10653,8 +11582,14 @@
       <c r="W39">
         <v>0.22359999999999999</v>
       </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD39" s="10">
+        <v>0.64200000000000002</v>
+      </c>
+      <c r="AE39" s="10">
+        <v>0.1207</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>36</v>
       </c>
@@ -10694,8 +11629,14 @@
       <c r="W40">
         <v>0.22770000000000001</v>
       </c>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD40" s="10">
+        <v>0.64770000000000005</v>
+      </c>
+      <c r="AE40" s="10">
+        <v>0.1356</v>
+      </c>
+    </row>
+    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>37</v>
       </c>
@@ -10735,8 +11676,14 @@
       <c r="W41">
         <v>0.21709999999999999</v>
       </c>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD41" s="10">
+        <v>0.65239999999999998</v>
+      </c>
+      <c r="AE41" s="10">
+        <v>0.10249999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>38</v>
       </c>
@@ -10776,8 +11723,14 @@
       <c r="W42">
         <v>0.21779999999999999</v>
       </c>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD42" s="10">
+        <v>0.65749999999999997</v>
+      </c>
+      <c r="AE42" s="10">
+        <v>0.1812</v>
+      </c>
+    </row>
+    <row r="43" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -10817,8 +11770,14 @@
       <c r="W43">
         <v>0.20610000000000001</v>
       </c>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD43" s="10">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="AE43" s="10">
+        <v>0.13969999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>40</v>
       </c>
@@ -10858,8 +11817,14 @@
       <c r="W44">
         <v>0.2064</v>
       </c>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD44" s="10">
+        <v>0.65629999999999999</v>
+      </c>
+      <c r="AE44" s="10">
+        <v>0.12479999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>41</v>
       </c>
@@ -10899,8 +11864,14 @@
       <c r="W45">
         <v>0.19539999999999999</v>
       </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD45" s="10">
+        <v>0.66169999999999995</v>
+      </c>
+      <c r="AE45" s="10">
+        <v>0.2036</v>
+      </c>
+    </row>
+    <row r="46" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>42</v>
       </c>
@@ -10940,8 +11911,14 @@
       <c r="W46">
         <v>0.20449999999999999</v>
       </c>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD46" s="10">
+        <v>0.66310000000000002</v>
+      </c>
+      <c r="AE46" s="10">
+        <v>0.12959999999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>43</v>
       </c>
@@ -10981,8 +11958,14 @@
       <c r="W47">
         <v>0.2165</v>
       </c>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD47" s="10">
+        <v>0.65429999999999999</v>
+      </c>
+      <c r="AE47" s="10">
+        <v>0.21099999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>44</v>
       </c>
@@ -11022,8 +12005,14 @@
       <c r="W48">
         <v>0.222</v>
       </c>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD48" s="10">
+        <v>0.6623</v>
+      </c>
+      <c r="AE48" s="10">
+        <v>9.7299999999999998E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>45</v>
       </c>
@@ -11063,8 +12052,14 @@
       <c r="W49">
         <v>0.2276</v>
       </c>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD49" s="10">
+        <v>0.66969999999999996</v>
+      </c>
+      <c r="AE49" s="10">
+        <v>0.1552</v>
+      </c>
+    </row>
+    <row r="50" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -11104,8 +12099,14 @@
       <c r="W50">
         <v>0.215</v>
       </c>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD50" s="10">
+        <v>0.66369999999999996</v>
+      </c>
+      <c r="AE50" s="10">
+        <v>0.19120000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>47</v>
       </c>
@@ -11145,8 +12146,14 @@
       <c r="W51">
         <v>0.18659999999999999</v>
       </c>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD51" s="10">
+        <v>0.66649999999999998</v>
+      </c>
+      <c r="AE51" s="10">
+        <v>0.19589999999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>48</v>
       </c>
@@ -11186,8 +12193,14 @@
       <c r="W52">
         <v>0.2092</v>
       </c>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD52" s="10">
+        <v>0.66500000000000004</v>
+      </c>
+      <c r="AE52" s="10">
+        <v>0.20349999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>49</v>
       </c>
@@ -11227,8 +12240,14 @@
       <c r="W53">
         <v>0.21440000000000001</v>
       </c>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD53" s="10">
+        <v>0.67249999999999999</v>
+      </c>
+      <c r="AE53" s="10">
+        <v>0.20100000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>50</v>
       </c>
@@ -11268,8 +12287,14 @@
       <c r="W54">
         <v>0.19889999999999999</v>
       </c>
-    </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD54" s="10">
+        <v>0.67949999999999999</v>
+      </c>
+      <c r="AE54" s="10">
+        <v>0.24440000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>51</v>
       </c>
@@ -11309,8 +12334,14 @@
       <c r="W55">
         <v>0.1585</v>
       </c>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD55" s="10">
+        <v>0.66979999999999995</v>
+      </c>
+      <c r="AE55" s="10">
+        <v>0.18260000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>52</v>
       </c>
@@ -11350,8 +12381,14 @@
       <c r="W56">
         <v>0.19670000000000001</v>
       </c>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD56" s="10">
+        <v>0.67179999999999995</v>
+      </c>
+      <c r="AE56" s="10">
+        <v>0.1298</v>
+      </c>
+    </row>
+    <row r="57" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>53</v>
       </c>
@@ -11391,8 +12428,14 @@
       <c r="W57">
         <v>0.22140000000000001</v>
       </c>
-    </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD57" s="10">
+        <v>0.67110000000000003</v>
+      </c>
+      <c r="AE57" s="10">
+        <v>0.1812</v>
+      </c>
+    </row>
+    <row r="58" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>54</v>
       </c>
@@ -11432,8 +12475,14 @@
       <c r="W58">
         <v>0.21560000000000001</v>
       </c>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD58" s="10">
+        <v>0.66979999999999995</v>
+      </c>
+      <c r="AE58" s="10">
+        <v>0.13969999999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>55</v>
       </c>
@@ -11473,8 +12522,14 @@
       <c r="W59">
         <v>0.2165</v>
       </c>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD59" s="10">
+        <v>0.67120000000000002</v>
+      </c>
+      <c r="AE59" s="10">
+        <v>0.12479999999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>56</v>
       </c>
@@ -11514,8 +12569,14 @@
       <c r="W60">
         <v>0.20519999999999999</v>
       </c>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD60" s="10">
+        <v>0.67190000000000005</v>
+      </c>
+      <c r="AE60" s="10">
+        <v>0.1057</v>
+      </c>
+    </row>
+    <row r="61" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>57</v>
       </c>
@@ -11555,8 +12616,14 @@
       <c r="W61">
         <v>0.21609999999999999</v>
       </c>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD61" s="10">
+        <v>0.6764</v>
+      </c>
+      <c r="AE61" s="10">
+        <v>0.13639999999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>58</v>
       </c>
@@ -11596,8 +12663,14 @@
       <c r="W62">
         <v>0.2049</v>
       </c>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD62" s="10">
+        <v>0.66930000000000001</v>
+      </c>
+      <c r="AE62" s="10">
+        <v>9.0899999999999995E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>59</v>
       </c>
@@ -11637,8 +12710,14 @@
       <c r="W63">
         <v>0.21390000000000001</v>
       </c>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD63" s="10">
+        <v>0.67400000000000004</v>
+      </c>
+      <c r="AE63" s="10">
+        <v>0.1203</v>
+      </c>
+    </row>
+    <row r="64" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>60</v>
       </c>
@@ -11678,8 +12757,14 @@
       <c r="W64">
         <v>0.18729999999999999</v>
       </c>
-    </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD64" s="10">
+        <v>0.67120000000000002</v>
+      </c>
+      <c r="AE64" s="10">
+        <v>0.1797</v>
+      </c>
+    </row>
+    <row r="65" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>61</v>
       </c>
@@ -11719,8 +12804,14 @@
       <c r="W65">
         <v>0.21149999999999999</v>
       </c>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD65" s="10">
+        <v>0.67330000000000001</v>
+      </c>
+      <c r="AE65" s="10">
+        <v>0.16739999999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>62</v>
       </c>
@@ -11760,8 +12851,14 @@
       <c r="W66">
         <v>0.21460000000000001</v>
       </c>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD66" s="10">
+        <v>0.67649999999999999</v>
+      </c>
+      <c r="AE66" s="10">
+        <v>0.1424</v>
+      </c>
+    </row>
+    <row r="67" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>63</v>
       </c>
@@ -11801,8 +12898,14 @@
       <c r="W67">
         <v>0.22620000000000001</v>
       </c>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD67" s="10">
+        <v>0.67359999999999998</v>
+      </c>
+      <c r="AE67" s="10">
+        <v>0.16850000000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>64</v>
       </c>
@@ -11842,8 +12945,14 @@
       <c r="W68">
         <v>0.2155</v>
       </c>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD68" s="10">
+        <v>0.6764</v>
+      </c>
+      <c r="AE68" s="10">
+        <v>0.15429999999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>65</v>
       </c>
@@ -11883,8 +12992,14 @@
       <c r="W69">
         <v>0.2268</v>
       </c>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD69" s="10">
+        <v>0.6724</v>
+      </c>
+      <c r="AE69" s="10">
+        <v>0.16650000000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>66</v>
       </c>
@@ -11924,8 +13039,14 @@
       <c r="W70">
         <v>0.224</v>
       </c>
-    </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD70" s="10">
+        <v>0.67649999999999999</v>
+      </c>
+      <c r="AE70" s="10">
+        <v>0.1137</v>
+      </c>
+    </row>
+    <row r="71" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>67</v>
       </c>
@@ -11965,8 +13086,14 @@
       <c r="W71">
         <v>0.22670000000000001</v>
       </c>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD71" s="10">
+        <v>0.67879999999999996</v>
+      </c>
+      <c r="AE71" s="10">
+        <v>0.22739999999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>68</v>
       </c>
@@ -12006,8 +13133,14 @@
       <c r="W72">
         <v>0.2172</v>
       </c>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD72" s="10">
+        <v>0.67620000000000002</v>
+      </c>
+      <c r="AE72" s="10">
+        <v>0.20899999999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>69</v>
       </c>
@@ -12047,8 +13180,14 @@
       <c r="W73">
         <v>0.19470000000000001</v>
       </c>
-    </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD73" s="10">
+        <v>0.66520000000000001</v>
+      </c>
+      <c r="AE73" s="10">
+        <v>0.26329999999999998</v>
+      </c>
+    </row>
+    <row r="74" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>70</v>
       </c>
@@ -12088,8 +13227,14 @@
       <c r="W74">
         <v>0.19769999999999999</v>
       </c>
-    </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD74" s="10">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="AE74" s="10">
+        <v>0.20749999999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>71</v>
       </c>
@@ -12129,8 +13274,14 @@
       <c r="W75">
         <v>0.2036</v>
       </c>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD75" s="10">
+        <v>0.68100000000000005</v>
+      </c>
+      <c r="AE75" s="10">
+        <v>0.21010000000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>72</v>
       </c>
@@ -12170,8 +13321,14 @@
       <c r="W76">
         <v>0.2122</v>
       </c>
-    </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD76" s="10">
+        <v>0.67330000000000001</v>
+      </c>
+      <c r="AE76" s="10">
+        <v>0.1305</v>
+      </c>
+    </row>
+    <row r="77" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>73</v>
       </c>
@@ -12211,8 +13368,14 @@
       <c r="W77">
         <v>0.2276</v>
       </c>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD77" s="10">
+        <v>0.67849999999999999</v>
+      </c>
+      <c r="AE77" s="10">
+        <v>0.15629999999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>74</v>
       </c>
@@ -12252,8 +13415,14 @@
       <c r="W78">
         <v>0.2059</v>
       </c>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD78" s="10">
+        <v>0.67520000000000002</v>
+      </c>
+      <c r="AE78" s="10">
+        <v>0.17630000000000001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>75</v>
       </c>
@@ -12293,8 +13462,14 @@
       <c r="W79">
         <v>0.20810000000000001</v>
       </c>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD79" s="10">
+        <v>0.66849999999999998</v>
+      </c>
+      <c r="AE79" s="10">
+        <v>0.1094</v>
+      </c>
+    </row>
+    <row r="80" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>76</v>
       </c>
@@ -12334,8 +13509,14 @@
       <c r="W80">
         <v>0.2102</v>
       </c>
-    </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD80" s="10">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="AE80" s="10">
+        <v>0.1966</v>
+      </c>
+    </row>
+    <row r="81" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>77</v>
       </c>
@@ -12375,8 +13556,14 @@
       <c r="W81">
         <v>0.2147</v>
       </c>
-    </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD81" s="10">
+        <v>0.67810000000000004</v>
+      </c>
+      <c r="AE81" s="10">
+        <v>0.15110000000000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>78</v>
       </c>
@@ -12416,8 +13603,14 @@
       <c r="W82">
         <v>0.1915</v>
       </c>
-    </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD82" s="10">
+        <v>0.67630000000000001</v>
+      </c>
+      <c r="AE82" s="10">
+        <v>0.15809999999999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>79</v>
       </c>
@@ -12457,8 +13650,14 @@
       <c r="W83">
         <v>0.14699999999999999</v>
       </c>
-    </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD83" s="10">
+        <v>0.67420000000000002</v>
+      </c>
+      <c r="AE83" s="10">
+        <v>0.2205</v>
+      </c>
+    </row>
+    <row r="84" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>80</v>
       </c>
@@ -12498,8 +13697,14 @@
       <c r="W84">
         <v>0.1002</v>
       </c>
-    </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD84" s="10">
+        <v>0.67390000000000005</v>
+      </c>
+      <c r="AE84" s="10">
+        <v>0.28560000000000002</v>
+      </c>
+    </row>
+    <row r="85" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>81</v>
       </c>
@@ -12539,8 +13744,14 @@
       <c r="W85">
         <v>0.123</v>
       </c>
-    </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD85" s="10">
+        <v>0.67810000000000004</v>
+      </c>
+      <c r="AE85" s="10">
+        <v>0.2031</v>
+      </c>
+    </row>
+    <row r="86" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>82</v>
       </c>
@@ -12580,8 +13791,14 @@
       <c r="W86">
         <v>0.1628</v>
       </c>
-    </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD86" s="10">
+        <v>0.67549999999999999</v>
+      </c>
+      <c r="AE86" s="10">
+        <v>0.20530000000000001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>83</v>
       </c>
@@ -12621,8 +13838,14 @@
       <c r="W87">
         <v>0.15890000000000001</v>
       </c>
-    </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD87" s="10">
+        <v>0.67330000000000001</v>
+      </c>
+      <c r="AE87" s="10">
+        <v>0.12239999999999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>84</v>
       </c>
@@ -12662,8 +13885,14 @@
       <c r="W88">
         <v>0.1055</v>
       </c>
-    </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD88" s="10">
+        <v>0.67789999999999995</v>
+      </c>
+      <c r="AE88" s="10">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="89" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>85</v>
       </c>
@@ -12703,8 +13932,14 @@
       <c r="W89">
         <v>0.1656</v>
       </c>
-    </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD89" s="10">
+        <v>0.67849999999999999</v>
+      </c>
+      <c r="AE89" s="10">
+        <v>0.1981</v>
+      </c>
+    </row>
+    <row r="90" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>86</v>
       </c>
@@ -12744,8 +13979,14 @@
       <c r="W90">
         <v>0.1789</v>
       </c>
-    </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD90" s="10">
+        <v>0.67720000000000002</v>
+      </c>
+      <c r="AE90" s="10">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="91" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>87</v>
       </c>
@@ -12785,8 +14026,14 @@
       <c r="W91">
         <v>0.18140000000000001</v>
       </c>
-    </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD91" s="10">
+        <v>0.68120000000000003</v>
+      </c>
+      <c r="AE91" s="10">
+        <v>0.2021</v>
+      </c>
+    </row>
+    <row r="92" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>88</v>
       </c>
@@ -12826,8 +14073,14 @@
       <c r="W92">
         <v>0.14680000000000001</v>
       </c>
-    </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD92" s="10">
+        <v>0.67059999999999997</v>
+      </c>
+      <c r="AE92" s="10">
+        <v>0.29859999999999998</v>
+      </c>
+    </row>
+    <row r="93" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>89</v>
       </c>
@@ -12867,8 +14120,14 @@
       <c r="W93">
         <v>0.18640000000000001</v>
       </c>
-    </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD93" s="10">
+        <v>0.67920000000000003</v>
+      </c>
+      <c r="AE93" s="10">
+        <v>0.29189999999999999</v>
+      </c>
+    </row>
+    <row r="94" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>90</v>
       </c>
@@ -12908,8 +14167,14 @@
       <c r="W94">
         <v>0.20610000000000001</v>
       </c>
-    </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD94" s="10">
+        <v>0.68389999999999995</v>
+      </c>
+      <c r="AE94" s="10">
+        <v>0.20599999999999999</v>
+      </c>
+    </row>
+    <row r="95" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>91</v>
       </c>
@@ -12949,8 +14214,14 @@
       <c r="W95">
         <v>0.1961</v>
       </c>
-    </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD95" s="10">
+        <v>0.67669999999999997</v>
+      </c>
+      <c r="AE95" s="10">
+        <v>0.28810000000000002</v>
+      </c>
+    </row>
+    <row r="96" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>92</v>
       </c>
@@ -12990,8 +14261,14 @@
       <c r="W96">
         <v>0.18690000000000001</v>
       </c>
-    </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD96" s="10">
+        <v>0.68320000000000003</v>
+      </c>
+      <c r="AE96" s="10">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="97" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>93</v>
       </c>
@@ -13031,8 +14308,14 @@
       <c r="W97">
         <v>0.14130000000000001</v>
       </c>
-    </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD97" s="10">
+        <v>0.68269999999999997</v>
+      </c>
+      <c r="AE97" s="10">
+        <v>0.3518</v>
+      </c>
+    </row>
+    <row r="98" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>94</v>
       </c>
@@ -13072,8 +14355,14 @@
       <c r="W98">
         <v>0.16600000000000001</v>
       </c>
-    </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD98" s="10">
+        <v>0.68410000000000004</v>
+      </c>
+      <c r="AE98" s="10">
+        <v>0.2094</v>
+      </c>
+    </row>
+    <row r="99" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>95</v>
       </c>
@@ -13110,8 +14399,14 @@
       <c r="W99">
         <v>0.1646</v>
       </c>
-    </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD99" s="10">
+        <v>0.67979999999999996</v>
+      </c>
+      <c r="AE99" s="10">
+        <v>0.2097</v>
+      </c>
+    </row>
+    <row r="100" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>96</v>
       </c>
@@ -13148,8 +14443,14 @@
       <c r="W100">
         <v>0.1951</v>
       </c>
-    </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD100" s="10">
+        <v>0.68389999999999995</v>
+      </c>
+      <c r="AE100" s="10">
+        <v>0.21049999999999999</v>
+      </c>
+    </row>
+    <row r="101" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>97</v>
       </c>
@@ -13186,8 +14487,14 @@
       <c r="W101">
         <v>0.18859999999999999</v>
       </c>
-    </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD101" s="10">
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="AE101" s="10">
+        <v>0.35680000000000001</v>
+      </c>
+    </row>
+    <row r="102" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>98</v>
       </c>
@@ -13224,8 +14531,14 @@
       <c r="W102">
         <v>0.186</v>
       </c>
-    </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD102" s="10">
+        <v>0.68320000000000003</v>
+      </c>
+      <c r="AE102" s="10">
+        <v>0.19239999999999999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>99</v>
       </c>
@@ -13262,8 +14575,14 @@
       <c r="W103">
         <v>0.15590000000000001</v>
       </c>
-    </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD103" s="10">
+        <v>0.68369999999999997</v>
+      </c>
+      <c r="AE103" s="10">
+        <v>0.14530000000000001</v>
+      </c>
+    </row>
+    <row r="104" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>100</v>
       </c>
@@ -13300,24 +14619,38 @@
       <c r="W104">
         <v>0.17030000000000001</v>
       </c>
-    </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD104" s="10">
+        <v>0.68530000000000002</v>
+      </c>
+      <c r="AE104" s="10">
+        <v>0.16569999999999999</v>
+      </c>
+    </row>
+    <row r="105" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AD105" s="10"/>
+      <c r="AE105" s="10"/>
+    </row>
+    <row r="106" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>19</v>
       </c>
       <c r="S106" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD106" s="10"/>
+      <c r="AE106" s="10"/>
+    </row>
+    <row r="107" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S107" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD107" s="10"/>
+      <c r="AE107" s="10"/>
+    </row>
+    <row r="108" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>1</v>
       </c>
@@ -13366,8 +14699,10 @@
       <c r="W108">
         <v>1</v>
       </c>
-    </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD108" s="10"/>
+      <c r="AE108" s="10"/>
+    </row>
+    <row r="109" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>2</v>
       </c>
@@ -13416,8 +14751,10 @@
       <c r="W109">
         <v>0.91666666666666663</v>
       </c>
-    </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD109" s="10"/>
+      <c r="AE109" s="10"/>
+    </row>
+    <row r="110" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>3</v>
       </c>
@@ -13466,8 +14803,10 @@
       <c r="W110">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD110" s="10"/>
+      <c r="AE110" s="10"/>
+    </row>
+    <row r="111" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>4</v>
       </c>
@@ -13516,8 +14855,10 @@
       <c r="W111">
         <v>0.63636363636363635</v>
       </c>
-    </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD111" s="10"/>
+      <c r="AE111" s="10"/>
+    </row>
+    <row r="112" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>5</v>
       </c>
@@ -13566,8 +14907,10 @@
       <c r="W112">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD112" s="10"/>
+      <c r="AE112" s="10"/>
+    </row>
+    <row r="113" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>6</v>
       </c>
@@ -13613,8 +14956,10 @@
       <c r="W113">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD113" s="10"/>
+      <c r="AE113" s="10"/>
+    </row>
+    <row r="114" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>7</v>
       </c>
@@ -13660,8 +15005,10 @@
       <c r="W114">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD114" s="10"/>
+      <c r="AE114" s="10"/>
+    </row>
+    <row r="115" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>8</v>
       </c>
@@ -13707,8 +15054,10 @@
       <c r="W115">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD115" s="10"/>
+      <c r="AE115" s="10"/>
+    </row>
+    <row r="116" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>9</v>
       </c>
@@ -13754,8 +15103,10 @@
       <c r="W116">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD116" s="10"/>
+      <c r="AE116" s="10"/>
+    </row>
+    <row r="117" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>10</v>
       </c>
@@ -13801,8 +15152,10 @@
       <c r="W117">
         <v>0.90909090909090906</v>
       </c>
-    </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD117" s="10"/>
+      <c r="AE117" s="10"/>
+    </row>
+    <row r="118" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>11</v>
       </c>
@@ -13842,8 +15195,10 @@
       <c r="W118">
         <v>0.81818181818181823</v>
       </c>
-    </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD118" s="10"/>
+      <c r="AE118" s="10"/>
+    </row>
+    <row r="119" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>12</v>
       </c>
@@ -13883,8 +15238,10 @@
       <c r="W119">
         <v>0.875</v>
       </c>
-    </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD119" s="10"/>
+      <c r="AE119" s="10"/>
+    </row>
+    <row r="120" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>13</v>
       </c>
@@ -13924,8 +15281,10 @@
       <c r="W120">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD120" s="10"/>
+      <c r="AE120" s="10"/>
+    </row>
+    <row r="121" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>14</v>
       </c>
@@ -13965,8 +15324,10 @@
       <c r="W121">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD121" s="10"/>
+      <c r="AE121" s="10"/>
+    </row>
+    <row r="122" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>15</v>
       </c>
@@ -14006,8 +15367,10 @@
       <c r="W122">
         <v>0.91666666666666663</v>
       </c>
-    </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD122" s="10"/>
+      <c r="AE122" s="10"/>
+    </row>
+    <row r="123" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>16</v>
       </c>
@@ -14047,8 +15410,10 @@
       <c r="W123">
         <v>0.81818181818181823</v>
       </c>
-    </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD123" s="10"/>
+      <c r="AE123" s="10"/>
+    </row>
+    <row r="124" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>17</v>
       </c>
@@ -14088,8 +15453,10 @@
       <c r="W124">
         <v>0.7142857142857143</v>
       </c>
-    </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD124" s="10"/>
+      <c r="AE124" s="10"/>
+    </row>
+    <row r="125" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>18</v>
       </c>
@@ -14129,8 +15496,10 @@
       <c r="W125">
         <v>0.76923076923076927</v>
       </c>
-    </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD125" s="10"/>
+      <c r="AE125" s="10"/>
+    </row>
+    <row r="126" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>19</v>
       </c>
@@ -14170,8 +15539,10 @@
       <c r="W126">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD126" s="10"/>
+      <c r="AE126" s="10"/>
+    </row>
+    <row r="127" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>20</v>
       </c>
@@ -14211,8 +15582,10 @@
       <c r="W127">
         <v>0.77777777777777779</v>
       </c>
-    </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD127" s="10"/>
+      <c r="AE127" s="10"/>
+    </row>
+    <row r="128" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>21</v>
       </c>
@@ -14252,8 +15625,10 @@
       <c r="W128">
         <v>0.88888888888888884</v>
       </c>
-    </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD128" s="10"/>
+      <c r="AE128" s="10"/>
+    </row>
+    <row r="129" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>22</v>
       </c>
@@ -14293,8 +15668,10 @@
       <c r="W129">
         <v>0.875</v>
       </c>
-    </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD129" s="10"/>
+      <c r="AE129" s="10"/>
+    </row>
+    <row r="130" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>23</v>
       </c>
@@ -14334,8 +15711,10 @@
       <c r="W130">
         <v>0.83333333333333337</v>
       </c>
-    </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD130" s="10"/>
+      <c r="AE130" s="10"/>
+    </row>
+    <row r="131" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>24</v>
       </c>
@@ -14375,8 +15754,10 @@
       <c r="W131">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD131" s="10"/>
+      <c r="AE131" s="10"/>
+    </row>
+    <row r="132" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>25</v>
       </c>
@@ -14416,8 +15797,10 @@
       <c r="W132">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD132" s="10"/>
+      <c r="AE132" s="10"/>
+    </row>
+    <row r="133" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>26</v>
       </c>
@@ -14457,8 +15840,10 @@
       <c r="W133">
         <v>0.875</v>
       </c>
-    </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD133" s="10"/>
+      <c r="AE133" s="10"/>
+    </row>
+    <row r="134" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>27</v>
       </c>
@@ -14498,8 +15883,10 @@
       <c r="W134">
         <v>0.77777777777777779</v>
       </c>
-    </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD134" s="10"/>
+      <c r="AE134" s="10"/>
+    </row>
+    <row r="135" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>28</v>
       </c>
@@ -14539,8 +15926,10 @@
       <c r="W135">
         <v>1</v>
       </c>
-    </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD135" s="10"/>
+      <c r="AE135" s="10"/>
+    </row>
+    <row r="136" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>29</v>
       </c>
@@ -14580,8 +15969,10 @@
       <c r="W136">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD136" s="10"/>
+      <c r="AE136" s="10"/>
+    </row>
+    <row r="137" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>30</v>
       </c>
@@ -14621,8 +16012,10 @@
       <c r="W137">
         <v>0.875</v>
       </c>
-    </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD137" s="10"/>
+      <c r="AE137" s="10"/>
+    </row>
+    <row r="138" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>31</v>
       </c>
@@ -14662,8 +16055,10 @@
       <c r="W138">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD138" s="10"/>
+      <c r="AE138" s="10"/>
+    </row>
+    <row r="139" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>32</v>
       </c>
@@ -14703,8 +16098,10 @@
       <c r="W139">
         <v>0.83333333333333337</v>
       </c>
-    </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD139" s="10"/>
+      <c r="AE139" s="10"/>
+    </row>
+    <row r="140" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>33</v>
       </c>
@@ -14744,8 +16141,10 @@
       <c r="W140">
         <v>0.77777777777777779</v>
       </c>
-    </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD140" s="10"/>
+      <c r="AE140" s="10"/>
+    </row>
+    <row r="141" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>34</v>
       </c>
@@ -14785,8 +16184,10 @@
       <c r="W141">
         <v>0.81818181818181823</v>
       </c>
-    </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD141" s="10"/>
+      <c r="AE141" s="10"/>
+    </row>
+    <row r="142" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>35</v>
       </c>
@@ -14826,8 +16227,10 @@
       <c r="W142">
         <v>0.8571428571428571</v>
       </c>
-    </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD142" s="10"/>
+      <c r="AE142" s="10"/>
+    </row>
+    <row r="143" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>36</v>
       </c>
@@ -14867,8 +16270,10 @@
       <c r="W143">
         <v>0.90909090909090906</v>
       </c>
-    </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD143" s="10"/>
+      <c r="AE143" s="10"/>
+    </row>
+    <row r="144" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>37</v>
       </c>
@@ -14908,8 +16313,10 @@
       <c r="W144">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD144" s="10"/>
+      <c r="AE144" s="10"/>
+    </row>
+    <row r="145" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>38</v>
       </c>
@@ -14949,8 +16356,10 @@
       <c r="W145">
         <v>0.81818181818181823</v>
       </c>
-    </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD145" s="10"/>
+      <c r="AE145" s="10"/>
+    </row>
+    <row r="146" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>39</v>
       </c>
@@ -14990,8 +16399,10 @@
       <c r="W146">
         <v>0.77777777777777779</v>
       </c>
-    </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD146" s="10"/>
+      <c r="AE146" s="10"/>
+    </row>
+    <row r="147" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>40</v>
       </c>
@@ -15031,8 +16442,10 @@
       <c r="W147">
         <v>0.63636363636363635</v>
       </c>
-    </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD147" s="10"/>
+      <c r="AE147" s="10"/>
+    </row>
+    <row r="148" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>41</v>
       </c>
@@ -15072,8 +16485,10 @@
       <c r="W148">
         <v>1</v>
       </c>
-    </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD148" s="10"/>
+      <c r="AE148" s="10"/>
+    </row>
+    <row r="149" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>42</v>
       </c>
@@ -15113,8 +16528,10 @@
       <c r="W149">
         <v>0.66666666666666663</v>
       </c>
-    </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD149" s="10"/>
+      <c r="AE149" s="10"/>
+    </row>
+    <row r="150" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>43</v>
       </c>
@@ -15154,8 +16571,10 @@
       <c r="W150">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD150" s="10"/>
+      <c r="AE150" s="10"/>
+    </row>
+    <row r="151" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>44</v>
       </c>
@@ -15195,8 +16614,10 @@
       <c r="W151">
         <v>0.83333333333333337</v>
       </c>
-    </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD151" s="10"/>
+      <c r="AE151" s="10"/>
+    </row>
+    <row r="152" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>45</v>
       </c>
@@ -15236,8 +16657,10 @@
       <c r="W152">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD152" s="10"/>
+      <c r="AE152" s="10"/>
+    </row>
+    <row r="153" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>46</v>
       </c>
@@ -15277,8 +16700,10 @@
       <c r="W153">
         <v>1</v>
       </c>
-    </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD153" s="10"/>
+      <c r="AE153" s="10"/>
+    </row>
+    <row r="154" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>47</v>
       </c>
@@ -15318,8 +16743,10 @@
       <c r="W154">
         <v>1</v>
       </c>
-    </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD154" s="10"/>
+      <c r="AE154" s="10"/>
+    </row>
+    <row r="155" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>48</v>
       </c>
@@ -15359,8 +16786,10 @@
       <c r="W155">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD155" s="10"/>
+      <c r="AE155" s="10"/>
+    </row>
+    <row r="156" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>49</v>
       </c>
@@ -15400,8 +16829,10 @@
       <c r="W156">
         <v>0.875</v>
       </c>
-    </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD156" s="10"/>
+      <c r="AE156" s="10"/>
+    </row>
+    <row r="157" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>50</v>
       </c>
@@ -15441,8 +16872,10 @@
       <c r="W157">
         <v>0.875</v>
       </c>
-    </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD157" s="10"/>
+      <c r="AE157" s="10"/>
+    </row>
+    <row r="158" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>51</v>
       </c>
@@ -15482,8 +16915,10 @@
       <c r="W158">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD158" s="10"/>
+      <c r="AE158" s="10"/>
+    </row>
+    <row r="159" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>52</v>
       </c>
@@ -15523,8 +16958,10 @@
       <c r="W159">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD159" s="10"/>
+      <c r="AE159" s="10"/>
+    </row>
+    <row r="160" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>53</v>
       </c>
@@ -15564,8 +17001,10 @@
       <c r="W160">
         <v>0.83333333333333337</v>
       </c>
-    </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD160" s="10"/>
+      <c r="AE160" s="10"/>
+    </row>
+    <row r="161" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>54</v>
       </c>
@@ -15605,8 +17044,10 @@
       <c r="W161">
         <v>0.77777777777777779</v>
       </c>
-    </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD161" s="10"/>
+      <c r="AE161" s="10"/>
+    </row>
+    <row r="162" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>55</v>
       </c>
@@ -15646,8 +17087,10 @@
       <c r="W162">
         <v>0.81818181818181823</v>
       </c>
-    </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD162" s="10"/>
+      <c r="AE162" s="10"/>
+    </row>
+    <row r="163" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>56</v>
       </c>
@@ -15687,8 +17130,10 @@
       <c r="W163">
         <v>0.8571428571428571</v>
       </c>
-    </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD163" s="10"/>
+      <c r="AE163" s="10"/>
+    </row>
+    <row r="164" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>57</v>
       </c>
@@ -15728,8 +17173,10 @@
       <c r="W164">
         <v>0.88888888888888884</v>
       </c>
-    </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD164" s="10"/>
+      <c r="AE164" s="10"/>
+    </row>
+    <row r="165" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>58</v>
       </c>
@@ -15769,8 +17216,10 @@
       <c r="W165">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD165" s="10"/>
+      <c r="AE165" s="10"/>
+    </row>
+    <row r="166" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>59</v>
       </c>
@@ -15810,8 +17259,10 @@
       <c r="W166">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD166" s="10"/>
+      <c r="AE166" s="10"/>
+    </row>
+    <row r="167" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>60</v>
       </c>
@@ -15851,8 +17302,10 @@
       <c r="W167">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD167" s="10"/>
+      <c r="AE167" s="10"/>
+    </row>
+    <row r="168" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>61</v>
       </c>
@@ -15892,8 +17345,10 @@
       <c r="W168">
         <v>0.88888888888888884</v>
       </c>
-    </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD168" s="10"/>
+      <c r="AE168" s="10"/>
+    </row>
+    <row r="169" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>62</v>
       </c>
@@ -15933,8 +17388,10 @@
       <c r="W169">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD169" s="10"/>
+      <c r="AE169" s="10"/>
+    </row>
+    <row r="170" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>63</v>
       </c>
@@ -15974,8 +17431,10 @@
       <c r="W170">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD170" s="10"/>
+      <c r="AE170" s="10"/>
+    </row>
+    <row r="171" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>64</v>
       </c>
@@ -16015,8 +17474,10 @@
       <c r="W171">
         <v>1</v>
       </c>
-    </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD171" s="10"/>
+      <c r="AE171" s="10"/>
+    </row>
+    <row r="172" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>65</v>
       </c>
@@ -16056,8 +17517,10 @@
       <c r="W172">
         <v>0.77777777777777779</v>
       </c>
-    </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD172" s="10"/>
+      <c r="AE172" s="10"/>
+    </row>
+    <row r="173" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>66</v>
       </c>
@@ -16097,8 +17560,10 @@
       <c r="W173">
         <v>0.7142857142857143</v>
       </c>
-    </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD173" s="10"/>
+      <c r="AE173" s="10"/>
+    </row>
+    <row r="174" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>67</v>
       </c>
@@ -16138,8 +17603,10 @@
       <c r="W174">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD174" s="10"/>
+      <c r="AE174" s="10"/>
+    </row>
+    <row r="175" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>68</v>
       </c>
@@ -16179,8 +17646,10 @@
       <c r="W175">
         <v>1</v>
       </c>
-    </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD175" s="10"/>
+      <c r="AE175" s="10"/>
+    </row>
+    <row r="176" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>69</v>
       </c>
@@ -16220,8 +17689,10 @@
       <c r="W176">
         <v>1</v>
       </c>
-    </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD176" s="10"/>
+      <c r="AE176" s="10"/>
+    </row>
+    <row r="177" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>70</v>
       </c>
@@ -16261,8 +17732,10 @@
       <c r="W177">
         <v>0.7142857142857143</v>
       </c>
-    </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD177" s="10"/>
+      <c r="AE177" s="10"/>
+    </row>
+    <row r="178" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>71</v>
       </c>
@@ -16302,8 +17775,10 @@
       <c r="W178">
         <v>0.875</v>
       </c>
-    </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD178" s="10"/>
+      <c r="AE178" s="10"/>
+    </row>
+    <row r="179" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>72</v>
       </c>
@@ -16343,8 +17818,10 @@
       <c r="W179">
         <v>0.83333333333333337</v>
       </c>
-    </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD179" s="10"/>
+      <c r="AE179" s="10"/>
+    </row>
+    <row r="180" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>73</v>
       </c>
@@ -16384,8 +17861,10 @@
       <c r="W180">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD180" s="10"/>
+      <c r="AE180" s="10"/>
+    </row>
+    <row r="181" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>74</v>
       </c>
@@ -16425,8 +17904,10 @@
       <c r="W181">
         <v>0.8571428571428571</v>
       </c>
-    </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD181" s="10"/>
+      <c r="AE181" s="10"/>
+    </row>
+    <row r="182" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>75</v>
       </c>
@@ -16466,8 +17947,10 @@
       <c r="W182">
         <v>0.8571428571428571</v>
       </c>
-    </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD182" s="10"/>
+      <c r="AE182" s="10"/>
+    </row>
+    <row r="183" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>76</v>
       </c>
@@ -16507,8 +17990,10 @@
       <c r="W183">
         <v>0.8571428571428571</v>
       </c>
-    </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD183" s="10"/>
+      <c r="AE183" s="10"/>
+    </row>
+    <row r="184" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>77</v>
       </c>
@@ -16548,8 +18033,10 @@
       <c r="W184">
         <v>0.875</v>
       </c>
-    </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD184" s="10"/>
+      <c r="AE184" s="10"/>
+    </row>
+    <row r="185" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>78</v>
       </c>
@@ -16589,8 +18076,10 @@
       <c r="W185">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD185" s="10"/>
+      <c r="AE185" s="10"/>
+    </row>
+    <row r="186" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>79</v>
       </c>
@@ -16630,8 +18119,10 @@
       <c r="W186">
         <v>0.7142857142857143</v>
       </c>
-    </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD186" s="10"/>
+      <c r="AE186" s="10"/>
+    </row>
+    <row r="187" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>80</v>
       </c>
@@ -16671,8 +18162,10 @@
       <c r="W187">
         <v>1</v>
       </c>
-    </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD187" s="10"/>
+      <c r="AE187" s="10"/>
+    </row>
+    <row r="188" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>81</v>
       </c>
@@ -16712,8 +18205,10 @@
       <c r="W188">
         <v>1</v>
       </c>
-    </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD188" s="10"/>
+      <c r="AE188" s="10"/>
+    </row>
+    <row r="189" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>82</v>
       </c>
@@ -16753,8 +18248,10 @@
       <c r="W189">
         <v>1</v>
       </c>
-    </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD189" s="10"/>
+      <c r="AE189" s="10"/>
+    </row>
+    <row r="190" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>83</v>
       </c>
@@ -16794,8 +18291,10 @@
       <c r="W190">
         <v>1</v>
       </c>
-    </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD190" s="10"/>
+      <c r="AE190" s="10"/>
+    </row>
+    <row r="191" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>84</v>
       </c>
@@ -16835,8 +18334,10 @@
       <c r="W191">
         <v>1</v>
       </c>
-    </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD191" s="10"/>
+      <c r="AE191" s="10"/>
+    </row>
+    <row r="192" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>85</v>
       </c>
@@ -16876,8 +18377,10 @@
       <c r="W192">
         <v>0.83333333333333337</v>
       </c>
-    </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD192" s="10"/>
+      <c r="AE192" s="10"/>
+    </row>
+    <row r="193" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>86</v>
       </c>
@@ -16917,8 +18420,10 @@
       <c r="W193">
         <v>1</v>
       </c>
-    </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD193" s="10"/>
+      <c r="AE193" s="10"/>
+    </row>
+    <row r="194" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>87</v>
       </c>
@@ -16958,8 +18463,10 @@
       <c r="W194">
         <v>1</v>
       </c>
-    </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD194" s="10"/>
+      <c r="AE194" s="10"/>
+    </row>
+    <row r="195" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>88</v>
       </c>
@@ -16999,8 +18506,10 @@
       <c r="W195">
         <v>1</v>
       </c>
-    </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD195" s="10"/>
+      <c r="AE195" s="10"/>
+    </row>
+    <row r="196" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>89</v>
       </c>
@@ -17040,8 +18549,10 @@
       <c r="W196">
         <v>1</v>
       </c>
-    </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD196" s="10"/>
+      <c r="AE196" s="10"/>
+    </row>
+    <row r="197" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>90</v>
       </c>
@@ -17081,8 +18592,10 @@
       <c r="W197">
         <v>0.66666666666666663</v>
       </c>
-    </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD197" s="10"/>
+      <c r="AE197" s="10"/>
+    </row>
+    <row r="198" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>91</v>
       </c>
@@ -17122,8 +18635,10 @@
       <c r="W198">
         <v>1</v>
       </c>
-    </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD198" s="10"/>
+      <c r="AE198" s="10"/>
+    </row>
+    <row r="199" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>92</v>
       </c>
@@ -17163,8 +18678,10 @@
       <c r="W199">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="200" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD199" s="10"/>
+      <c r="AE199" s="10"/>
+    </row>
+    <row r="200" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>93</v>
       </c>
@@ -17204,8 +18721,10 @@
       <c r="W200">
         <v>1</v>
       </c>
-    </row>
-    <row r="201" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD200" s="10"/>
+      <c r="AE200" s="10"/>
+    </row>
+    <row r="201" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>94</v>
       </c>
@@ -17245,8 +18764,10 @@
       <c r="W201">
         <v>1</v>
       </c>
-    </row>
-    <row r="202" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD201" s="10"/>
+      <c r="AE201" s="10"/>
+    </row>
+    <row r="202" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>95</v>
       </c>
@@ -17283,8 +18804,10 @@
       <c r="W202">
         <v>1</v>
       </c>
-    </row>
-    <row r="203" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD202" s="10"/>
+      <c r="AE202" s="10"/>
+    </row>
+    <row r="203" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>96</v>
       </c>
@@ -17321,8 +18844,10 @@
       <c r="W203">
         <v>1</v>
       </c>
-    </row>
-    <row r="204" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD203" s="10"/>
+      <c r="AE203" s="10"/>
+    </row>
+    <row r="204" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>97</v>
       </c>
@@ -17359,8 +18884,10 @@
       <c r="W204">
         <v>1</v>
       </c>
-    </row>
-    <row r="205" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD204" s="10"/>
+      <c r="AE204" s="10"/>
+    </row>
+    <row r="205" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>98</v>
       </c>
@@ -17397,8 +18924,10 @@
       <c r="W205">
         <v>1</v>
       </c>
-    </row>
-    <row r="206" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD205" s="10"/>
+      <c r="AE205" s="10"/>
+    </row>
+    <row r="206" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>99</v>
       </c>
@@ -17435,8 +18964,10 @@
       <c r="W206">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="207" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD206" s="10"/>
+      <c r="AE206" s="10"/>
+    </row>
+    <row r="207" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>100</v>
       </c>
@@ -17473,24 +19004,38 @@
       <c r="W207">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="210" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD207" s="10"/>
+      <c r="AE207" s="10"/>
+    </row>
+    <row r="208" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AD208" s="10"/>
+      <c r="AE208" s="10"/>
+    </row>
+    <row r="209" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AD209" s="10"/>
+      <c r="AE209" s="10"/>
+    </row>
+    <row r="210" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
         <v>21</v>
       </c>
       <c r="S210" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="211" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD210" s="10"/>
+      <c r="AE210" s="10"/>
+    </row>
+    <row r="211" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S211" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="212" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD211" s="10"/>
+      <c r="AE211" s="10"/>
+    </row>
+    <row r="212" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>1</v>
       </c>
@@ -17539,8 +19084,10 @@
       <c r="W212">
         <v>0.97721666666666662</v>
       </c>
-    </row>
-    <row r="213" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD212" s="10"/>
+      <c r="AE212" s="10"/>
+    </row>
+    <row r="213" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>2</v>
       </c>
@@ -17589,8 +19136,10 @@
       <c r="W213">
         <v>0.9632571428571427</v>
       </c>
-    </row>
-    <row r="214" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD213" s="10"/>
+      <c r="AE213" s="10"/>
+    </row>
+    <row r="214" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>3</v>
       </c>
@@ -17639,8 +19188,10 @@
       <c r="W214">
         <v>0.85415555555555545</v>
       </c>
-    </row>
-    <row r="215" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD214" s="10"/>
+      <c r="AE214" s="10"/>
+    </row>
+    <row r="215" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>4</v>
       </c>
@@ -17689,8 +19240,10 @@
       <c r="W215">
         <v>0.97684999999999989</v>
       </c>
-    </row>
-    <row r="216" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD215" s="10"/>
+      <c r="AE215" s="10"/>
+    </row>
+    <row r="216" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>5</v>
       </c>
@@ -17739,8 +19292,10 @@
       <c r="W216">
         <v>0.98968333333333325</v>
       </c>
-    </row>
-    <row r="217" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD216" s="10"/>
+      <c r="AE216" s="10"/>
+    </row>
+    <row r="217" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>6</v>
       </c>
@@ -17786,8 +19341,10 @@
       <c r="W217">
         <v>0.97553999999999996</v>
       </c>
-    </row>
-    <row r="218" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD217" s="10"/>
+      <c r="AE217" s="10"/>
+    </row>
+    <row r="218" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>7</v>
       </c>
@@ -17833,8 +19390,10 @@
       <c r="W218">
         <v>0.78948333333333343</v>
       </c>
-    </row>
-    <row r="219" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD218" s="10"/>
+      <c r="AE218" s="10"/>
+    </row>
+    <row r="219" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>8</v>
       </c>
@@ -17880,8 +19439,10 @@
       <c r="W219">
         <v>0.9572666666666666</v>
       </c>
-    </row>
-    <row r="220" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD219" s="10"/>
+      <c r="AE219" s="10"/>
+    </row>
+    <row r="220" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>9</v>
       </c>
@@ -17927,8 +19488,10 @@
       <c r="W220">
         <v>0.82136666666666658</v>
       </c>
-    </row>
-    <row r="221" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD220" s="10"/>
+      <c r="AE220" s="10"/>
+    </row>
+    <row r="221" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>10</v>
       </c>
@@ -17974,8 +19537,10 @@
       <c r="W221">
         <v>0.79379999999999995</v>
       </c>
-    </row>
-    <row r="222" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD221" s="10"/>
+      <c r="AE221" s="10"/>
+    </row>
+    <row r="222" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>11</v>
       </c>
@@ -18015,8 +19580,10 @@
       <c r="W222">
         <v>0.7997833333333334</v>
       </c>
-    </row>
-    <row r="223" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD222" s="10"/>
+      <c r="AE222" s="10"/>
+    </row>
+    <row r="223" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>12</v>
       </c>
@@ -18056,8 +19623,10 @@
       <c r="W223">
         <v>0.8596625</v>
       </c>
-    </row>
-    <row r="224" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD223" s="10"/>
+      <c r="AE223" s="10"/>
+    </row>
+    <row r="224" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>13</v>
       </c>
@@ -18097,8 +19666,10 @@
       <c r="W224">
         <v>0.97779999999999989</v>
       </c>
-    </row>
-    <row r="225" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD224" s="10"/>
+      <c r="AE224" s="10"/>
+    </row>
+    <row r="225" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>14</v>
       </c>
@@ -18138,8 +19709,10 @@
       <c r="W225">
         <v>0.98628750000000009</v>
       </c>
-    </row>
-    <row r="226" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD225" s="10"/>
+      <c r="AE225" s="10"/>
+    </row>
+    <row r="226" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>15</v>
       </c>
@@ -18179,8 +19752,10 @@
       <c r="W226">
         <v>0.97297499999999992</v>
       </c>
-    </row>
-    <row r="227" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD226" s="10"/>
+      <c r="AE226" s="10"/>
+    </row>
+    <row r="227" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>16</v>
       </c>
@@ -18220,8 +19795,10 @@
       <c r="W227">
         <v>0.98293333333333344</v>
       </c>
-    </row>
-    <row r="228" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD227" s="10"/>
+      <c r="AE227" s="10"/>
+    </row>
+    <row r="228" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>17</v>
       </c>
@@ -18261,8 +19838,10 @@
       <c r="W228">
         <v>0.88788</v>
       </c>
-    </row>
-    <row r="229" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD228" s="10"/>
+      <c r="AE228" s="10"/>
+    </row>
+    <row r="229" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>18</v>
       </c>
@@ -18302,8 +19881,10 @@
       <c r="W229">
         <v>0.98428000000000004</v>
       </c>
-    </row>
-    <row r="230" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD229" s="10"/>
+      <c r="AE229" s="10"/>
+    </row>
+    <row r="230" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>19</v>
       </c>
@@ -18343,8 +19924,10 @@
       <c r="W230">
         <v>0.98478333333333323</v>
       </c>
-    </row>
-    <row r="231" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD230" s="10"/>
+      <c r="AE230" s="10"/>
+    </row>
+    <row r="231" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>20</v>
       </c>
@@ -18384,8 +19967,10 @@
       <c r="W231">
         <v>0.97931250000000003</v>
       </c>
-    </row>
-    <row r="232" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD231" s="10"/>
+      <c r="AE231" s="10"/>
+    </row>
+    <row r="232" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>21</v>
       </c>
@@ -18425,8 +20010,10 @@
       <c r="W232">
         <v>0.84510000000000007</v>
       </c>
-    </row>
-    <row r="233" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD232" s="10"/>
+      <c r="AE232" s="10"/>
+    </row>
+    <row r="233" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>22</v>
       </c>
@@ -18466,8 +20053,10 @@
       <c r="W233">
         <v>0.97244999999999993</v>
       </c>
-    </row>
-    <row r="234" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD233" s="10"/>
+      <c r="AE233" s="10"/>
+    </row>
+    <row r="234" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>23</v>
       </c>
@@ -18507,8 +20096,10 @@
       <c r="W234">
         <v>0.98330000000000006</v>
       </c>
-    </row>
-    <row r="235" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD234" s="10"/>
+      <c r="AE234" s="10"/>
+    </row>
+    <row r="235" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>24</v>
       </c>
@@ -18548,8 +20139,10 @@
       <c r="W235">
         <v>0.83290000000000008</v>
       </c>
-    </row>
-    <row r="236" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD235" s="10"/>
+      <c r="AE235" s="10"/>
+    </row>
+    <row r="236" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>25</v>
       </c>
@@ -18589,8 +20182,10 @@
       <c r="W236">
         <v>0.73602499999999993</v>
       </c>
-    </row>
-    <row r="237" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD236" s="10"/>
+      <c r="AE236" s="10"/>
+    </row>
+    <row r="237" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <v>26</v>
       </c>
@@ -18630,8 +20225,10 @@
       <c r="W237">
         <v>0.86617499999999992</v>
       </c>
-    </row>
-    <row r="238" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD237" s="10"/>
+      <c r="AE237" s="10"/>
+    </row>
+    <row r="238" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <v>27</v>
       </c>
@@ -18671,8 +20268,10 @@
       <c r="W238">
         <v>0.74853749999999997</v>
       </c>
-    </row>
-    <row r="239" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD238" s="10"/>
+      <c r="AE238" s="10"/>
+    </row>
+    <row r="239" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <v>28</v>
       </c>
@@ -18712,8 +20311,10 @@
       <c r="W239">
         <v>0.79603333333333337</v>
       </c>
-    </row>
-    <row r="240" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD239" s="10"/>
+      <c r="AE239" s="10"/>
+    </row>
+    <row r="240" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <v>29</v>
       </c>
@@ -18753,8 +20354,10 @@
       <c r="W240">
         <v>0.98022222222222211</v>
       </c>
-    </row>
-    <row r="241" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD240" s="10"/>
+      <c r="AE240" s="10"/>
+    </row>
+    <row r="241" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <v>30</v>
       </c>
@@ -18794,8 +20397,10 @@
       <c r="W241">
         <v>0.6171875</v>
       </c>
-    </row>
-    <row r="242" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD241" s="10"/>
+      <c r="AE241" s="10"/>
+    </row>
+    <row r="242" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>31</v>
       </c>
@@ -18835,8 +20440,10 @@
       <c r="W242">
         <v>0.71375714285714298</v>
       </c>
-    </row>
-    <row r="243" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD242" s="10"/>
+      <c r="AE242" s="10"/>
+    </row>
+    <row r="243" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <v>32</v>
       </c>
@@ -18876,8 +20483,10 @@
       <c r="W243">
         <v>0.79234000000000004</v>
       </c>
-    </row>
-    <row r="244" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD243" s="10"/>
+      <c r="AE243" s="10"/>
+    </row>
+    <row r="244" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>33</v>
       </c>
@@ -18917,8 +20526,10 @@
       <c r="W244">
         <v>0.75946249999999993</v>
       </c>
-    </row>
-    <row r="245" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD244" s="10"/>
+      <c r="AE244" s="10"/>
+    </row>
+    <row r="245" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>34</v>
       </c>
@@ -18958,8 +20569,10 @@
       <c r="W245">
         <v>0.83020000000000005</v>
       </c>
-    </row>
-    <row r="246" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD245" s="10"/>
+      <c r="AE245" s="10"/>
+    </row>
+    <row r="246" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>35</v>
       </c>
@@ -18999,8 +20612,10 @@
       <c r="W246">
         <v>0.76771111111111112</v>
       </c>
-    </row>
-    <row r="247" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD246" s="10"/>
+      <c r="AE246" s="10"/>
+    </row>
+    <row r="247" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <v>36</v>
       </c>
@@ -19040,8 +20655,10 @@
       <c r="W247">
         <v>0.65244000000000013</v>
       </c>
-    </row>
-    <row r="248" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD247" s="10"/>
+      <c r="AE247" s="10"/>
+    </row>
+    <row r="248" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>37</v>
       </c>
@@ -19081,8 +20698,10 @@
       <c r="W248">
         <v>0.76685555555555551</v>
       </c>
-    </row>
-    <row r="249" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD248" s="10"/>
+      <c r="AE248" s="10"/>
+    </row>
+    <row r="249" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>38</v>
       </c>
@@ -19122,8 +20741,10 @@
       <c r="W249">
         <v>0.98936666666666662</v>
       </c>
-    </row>
-    <row r="250" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD249" s="10"/>
+      <c r="AE249" s="10"/>
+    </row>
+    <row r="250" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>39</v>
       </c>
@@ -19163,8 +20784,10 @@
       <c r="W250">
         <v>0.88141250000000015</v>
       </c>
-    </row>
-    <row r="251" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD250" s="10"/>
+      <c r="AE250" s="10"/>
+    </row>
+    <row r="251" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>40</v>
       </c>
@@ -19204,8 +20827,10 @@
       <c r="W251">
         <v>0.79987999999999992</v>
       </c>
-    </row>
-    <row r="252" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD251" s="10"/>
+      <c r="AE251" s="10"/>
+    </row>
+    <row r="252" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>41</v>
       </c>
@@ -19245,8 +20870,10 @@
       <c r="W252">
         <v>0.5904666666666667</v>
       </c>
-    </row>
-    <row r="253" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD252" s="10"/>
+      <c r="AE252" s="10"/>
+    </row>
+    <row r="253" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>42</v>
       </c>
@@ -19286,8 +20913,10 @@
       <c r="W253">
         <v>0.82028181818181811</v>
       </c>
-    </row>
-    <row r="254" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD253" s="10"/>
+      <c r="AE253" s="10"/>
+    </row>
+    <row r="254" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>43</v>
       </c>
@@ -19327,8 +20956,10 @@
       <c r="W254">
         <v>0.64123750000000002</v>
       </c>
-    </row>
-    <row r="255" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD254" s="10"/>
+      <c r="AE254" s="10"/>
+    </row>
+    <row r="255" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>44</v>
       </c>
@@ -19368,8 +20999,10 @@
       <c r="W255">
         <v>0.78409999999999991</v>
       </c>
-    </row>
-    <row r="256" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD255" s="10"/>
+      <c r="AE255" s="10"/>
+    </row>
+    <row r="256" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <v>45</v>
       </c>
@@ -19409,8 +21042,10 @@
       <c r="W256">
         <v>0.66931111111111108</v>
       </c>
-    </row>
-    <row r="257" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD256" s="10"/>
+      <c r="AE256" s="10"/>
+    </row>
+    <row r="257" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>46</v>
       </c>
@@ -19450,8 +21085,10 @@
       <c r="W257">
         <v>0.62033749999999999</v>
       </c>
-    </row>
-    <row r="258" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD257" s="10"/>
+      <c r="AE257" s="10"/>
+    </row>
+    <row r="258" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <v>47</v>
       </c>
@@ -19491,8 +21128,10 @@
       <c r="W258">
         <v>0.75590000000000002</v>
       </c>
-    </row>
-    <row r="259" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD258" s="10"/>
+      <c r="AE258" s="10"/>
+    </row>
+    <row r="259" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>48</v>
       </c>
@@ -19532,8 +21171,10 @@
       <c r="W259">
         <v>0.46441111111111122</v>
       </c>
-    </row>
-    <row r="260" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD259" s="10"/>
+      <c r="AE259" s="10"/>
+    </row>
+    <row r="260" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>49</v>
       </c>
@@ -19573,8 +21214,10 @@
       <c r="W260">
         <v>0.8606125</v>
       </c>
-    </row>
-    <row r="261" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD260" s="10"/>
+      <c r="AE260" s="10"/>
+    </row>
+    <row r="261" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>50</v>
       </c>
@@ -19614,8 +21257,10 @@
       <c r="W261">
         <v>0.86603750000000002</v>
       </c>
-    </row>
-    <row r="262" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD261" s="10"/>
+      <c r="AE261" s="10"/>
+    </row>
+    <row r="262" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>51</v>
       </c>
@@ -19655,8 +21300,10 @@
       <c r="W262">
         <v>0.71680999999999995</v>
       </c>
-    </row>
-    <row r="263" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD262" s="10"/>
+      <c r="AE262" s="10"/>
+    </row>
+    <row r="263" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>52</v>
       </c>
@@ -19696,8 +21343,10 @@
       <c r="W263">
         <v>0.654588888888889</v>
       </c>
-    </row>
-    <row r="264" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD263" s="10"/>
+      <c r="AE263" s="10"/>
+    </row>
+    <row r="264" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>53</v>
       </c>
@@ -19737,8 +21386,10 @@
       <c r="W264">
         <v>0.70977000000000001</v>
       </c>
-    </row>
-    <row r="265" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD264" s="10"/>
+      <c r="AE264" s="10"/>
+    </row>
+    <row r="265" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>54</v>
       </c>
@@ -19778,8 +21429,10 @@
       <c r="W265">
         <v>0.63495000000000001</v>
       </c>
-    </row>
-    <row r="266" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD265" s="10"/>
+      <c r="AE265" s="10"/>
+    </row>
+    <row r="266" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>55</v>
       </c>
@@ -19819,8 +21472,10 @@
       <c r="W266">
         <v>0.97338333333333338</v>
       </c>
-    </row>
-    <row r="267" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD266" s="10"/>
+      <c r="AE266" s="10"/>
+    </row>
+    <row r="267" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>56</v>
       </c>
@@ -19860,8 +21515,10 @@
       <c r="W267">
         <v>0.88502222222222215</v>
       </c>
-    </row>
-    <row r="268" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD267" s="10"/>
+      <c r="AE267" s="10"/>
+    </row>
+    <row r="268" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>57</v>
       </c>
@@ -19901,8 +21558,10 @@
       <c r="W268">
         <v>0.8693142857142856</v>
       </c>
-    </row>
-    <row r="269" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD268" s="10"/>
+      <c r="AE268" s="10"/>
+    </row>
+    <row r="269" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>58</v>
       </c>
@@ -19942,8 +21601,10 @@
       <c r="W269">
         <v>0.56033333333333335</v>
       </c>
-    </row>
-    <row r="270" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD269" s="10"/>
+      <c r="AE269" s="10"/>
+    </row>
+    <row r="270" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>59</v>
       </c>
@@ -19983,8 +21644,10 @@
       <c r="W270">
         <v>0.86207499999999992</v>
       </c>
-    </row>
-    <row r="271" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD270" s="10"/>
+      <c r="AE270" s="10"/>
+    </row>
+    <row r="271" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>60</v>
       </c>
@@ -20024,8 +21687,10 @@
       <c r="W271">
         <v>0.96810000000000007</v>
       </c>
-    </row>
-    <row r="272" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD271" s="10"/>
+      <c r="AE271" s="10"/>
+    </row>
+    <row r="272" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>61</v>
       </c>
@@ -20065,8 +21730,10 @@
       <c r="W272">
         <v>0.55665714285714274</v>
       </c>
-    </row>
-    <row r="273" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD272" s="10"/>
+      <c r="AE272" s="10"/>
+    </row>
+    <row r="273" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>62</v>
       </c>
@@ -20106,8 +21773,10 @@
       <c r="W273">
         <v>0.58240909090909099</v>
       </c>
-    </row>
-    <row r="274" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD273" s="10"/>
+      <c r="AE273" s="10"/>
+    </row>
+    <row r="274" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>63</v>
       </c>
@@ -20147,8 +21816,10 @@
       <c r="W274">
         <v>0.76897777777777776</v>
       </c>
-    </row>
-    <row r="275" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD274" s="10"/>
+      <c r="AE274" s="10"/>
+    </row>
+    <row r="275" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>64</v>
       </c>
@@ -20188,8 +21859,10 @@
       <c r="W275">
         <v>0.86087142857142862</v>
       </c>
-    </row>
-    <row r="276" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD275" s="10"/>
+      <c r="AE275" s="10"/>
+    </row>
+    <row r="276" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <v>65</v>
       </c>
@@ -20229,8 +21902,10 @@
       <c r="W276">
         <v>0.73391250000000008</v>
       </c>
-    </row>
-    <row r="277" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD276" s="10"/>
+      <c r="AE276" s="10"/>
+    </row>
+    <row r="277" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <v>66</v>
       </c>
@@ -20270,8 +21945,10 @@
       <c r="W277">
         <v>0.69578000000000007</v>
       </c>
-    </row>
-    <row r="278" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD277" s="10"/>
+      <c r="AE277" s="10"/>
+    </row>
+    <row r="278" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>67</v>
       </c>
@@ -20311,8 +21988,10 @@
       <c r="W278">
         <v>0.77191111111111121</v>
       </c>
-    </row>
-    <row r="279" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD278" s="10"/>
+      <c r="AE278" s="10"/>
+    </row>
+    <row r="279" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>68</v>
       </c>
@@ -20352,8 +22031,10 @@
       <c r="W279">
         <v>0.77392222222222218</v>
       </c>
-    </row>
-    <row r="280" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD279" s="10"/>
+      <c r="AE279" s="10"/>
+    </row>
+    <row r="280" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>69</v>
       </c>
@@ -20393,8 +22074,10 @@
       <c r="W280">
         <v>0.86148749999999985</v>
       </c>
-    </row>
-    <row r="281" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD280" s="10"/>
+      <c r="AE280" s="10"/>
+    </row>
+    <row r="281" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>70</v>
       </c>
@@ -20434,8 +22117,10 @@
       <c r="W281">
         <v>0.72258</v>
       </c>
-    </row>
-    <row r="282" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD281" s="10"/>
+      <c r="AE281" s="10"/>
+    </row>
+    <row r="282" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>71</v>
       </c>
@@ -20475,8 +22160,10 @@
       <c r="W282">
         <v>0.9699875</v>
       </c>
-    </row>
-    <row r="283" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD282" s="10"/>
+      <c r="AE282" s="10"/>
+    </row>
+    <row r="283" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>72</v>
       </c>
@@ -20516,8 +22203,10 @@
       <c r="W283">
         <v>0.70218999999999987</v>
       </c>
-    </row>
-    <row r="284" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD283" s="10"/>
+      <c r="AE283" s="10"/>
+    </row>
+    <row r="284" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>73</v>
       </c>
@@ -20557,8 +22246,10 @@
       <c r="W284">
         <v>0.66871666666666663</v>
       </c>
-    </row>
-    <row r="285" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD284" s="10"/>
+      <c r="AE284" s="10"/>
+    </row>
+    <row r="285" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>74</v>
       </c>
@@ -20598,8 +22289,10 @@
       <c r="W285">
         <v>0.62717777777777783</v>
       </c>
-    </row>
-    <row r="286" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD285" s="10"/>
+      <c r="AE285" s="10"/>
+    </row>
+    <row r="286" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>75</v>
       </c>
@@ -20639,8 +22332,10 @@
       <c r="W286">
         <v>0.87706666666666655</v>
       </c>
-    </row>
-    <row r="287" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD286" s="10"/>
+      <c r="AE286" s="10"/>
+    </row>
+    <row r="287" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>76</v>
       </c>
@@ -20680,8 +22375,10 @@
       <c r="W287">
         <v>0.87386666666666668</v>
       </c>
-    </row>
-    <row r="288" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD287" s="10"/>
+      <c r="AE287" s="10"/>
+    </row>
+    <row r="288" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>77</v>
       </c>
@@ -20721,8 +22418,10 @@
       <c r="W288">
         <v>0.63101249999999998</v>
       </c>
-    </row>
-    <row r="289" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD288" s="10"/>
+      <c r="AE288" s="10"/>
+    </row>
+    <row r="289" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>78</v>
       </c>
@@ -20762,8 +22461,10 @@
       <c r="W289">
         <v>0.59407142857142858</v>
       </c>
-    </row>
-    <row r="290" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD289" s="10"/>
+      <c r="AE289" s="10"/>
+    </row>
+    <row r="290" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>79</v>
       </c>
@@ -20803,8 +22504,10 @@
       <c r="W290">
         <v>0.59402222222222223</v>
       </c>
-    </row>
-    <row r="291" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD290" s="10"/>
+      <c r="AE290" s="10"/>
+    </row>
+    <row r="291" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>80</v>
       </c>
@@ -20844,8 +22547,10 @@
       <c r="W291">
         <v>0.70433571428571418</v>
       </c>
-    </row>
-    <row r="292" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD291" s="10"/>
+      <c r="AE291" s="10"/>
+    </row>
+    <row r="292" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>81</v>
       </c>
@@ -20885,8 +22590,10 @@
       <c r="W292">
         <v>0.45763333333333328</v>
       </c>
-    </row>
-    <row r="293" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD292" s="10"/>
+      <c r="AE292" s="10"/>
+    </row>
+    <row r="293" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>82</v>
       </c>
@@ -20926,8 +22633,10 @@
       <c r="W293">
         <v>0.58567777777777774</v>
       </c>
-    </row>
-    <row r="294" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD293" s="10"/>
+      <c r="AE293" s="10"/>
+    </row>
+    <row r="294" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>83</v>
       </c>
@@ -20967,8 +22676,10 @@
       <c r="W294">
         <v>0.71356363636363629</v>
       </c>
-    </row>
-    <row r="295" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD294" s="10"/>
+      <c r="AE294" s="10"/>
+    </row>
+    <row r="295" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>84</v>
       </c>
@@ -21008,8 +22719,10 @@
       <c r="W295">
         <v>0.65580833333333333</v>
       </c>
-    </row>
-    <row r="296" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD295" s="10"/>
+      <c r="AE295" s="10"/>
+    </row>
+    <row r="296" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>85</v>
       </c>
@@ -21049,8 +22762,10 @@
       <c r="W296">
         <v>0.41167999999999988</v>
       </c>
-    </row>
-    <row r="297" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD296" s="10"/>
+      <c r="AE296" s="10"/>
+    </row>
+    <row r="297" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>86</v>
       </c>
@@ -21090,8 +22805,10 @@
       <c r="W297">
         <v>0.62680909090909087</v>
       </c>
-    </row>
-    <row r="298" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD297" s="10"/>
+      <c r="AE297" s="10"/>
+    </row>
+    <row r="298" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>87</v>
       </c>
@@ -21131,8 +22848,10 @@
       <c r="W298">
         <v>0.41285000000000011</v>
       </c>
-    </row>
-    <row r="299" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD298" s="10"/>
+      <c r="AE298" s="10"/>
+    </row>
+    <row r="299" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>88</v>
       </c>
@@ -21172,8 +22891,10 @@
       <c r="W299">
         <v>0.39288000000000012</v>
       </c>
-    </row>
-    <row r="300" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD299" s="10"/>
+      <c r="AE299" s="10"/>
+    </row>
+    <row r="300" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>89</v>
       </c>
@@ -21213,8 +22934,10 @@
       <c r="W300">
         <v>0.53818888888888894</v>
       </c>
-    </row>
-    <row r="301" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD300" s="10"/>
+      <c r="AE300" s="10"/>
+    </row>
+    <row r="301" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>90</v>
       </c>
@@ -21254,8 +22977,10 @@
       <c r="W301">
         <v>0.53363076923076924</v>
       </c>
-    </row>
-    <row r="302" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD301" s="10"/>
+      <c r="AE301" s="10"/>
+    </row>
+    <row r="302" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>91</v>
       </c>
@@ -21295,8 +23020,10 @@
       <c r="W302">
         <v>0.49234</v>
       </c>
-    </row>
-    <row r="303" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD302" s="10"/>
+      <c r="AE302" s="10"/>
+    </row>
+    <row r="303" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
         <v>92</v>
       </c>
@@ -21336,8 +23063,10 @@
       <c r="W303">
         <v>0.7704214285714287</v>
       </c>
-    </row>
-    <row r="304" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD303" s="10"/>
+      <c r="AE303" s="10"/>
+    </row>
+    <row r="304" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
         <v>93</v>
       </c>
@@ -21377,8 +23106,10 @@
       <c r="W304">
         <v>0.65303636363636364</v>
       </c>
-    </row>
-    <row r="305" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD304" s="10"/>
+      <c r="AE304" s="10"/>
+    </row>
+    <row r="305" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
         <v>94</v>
       </c>
@@ -21418,8 +23149,10 @@
       <c r="W305">
         <v>0.36426666666666668</v>
       </c>
-    </row>
-    <row r="306" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD305" s="10"/>
+      <c r="AE305" s="10"/>
+    </row>
+    <row r="306" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
         <v>95</v>
       </c>
@@ -21456,8 +23189,10 @@
       <c r="W306">
         <v>0.53970909090909092</v>
       </c>
-    </row>
-    <row r="307" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD306" s="10"/>
+      <c r="AE306" s="10"/>
+    </row>
+    <row r="307" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
         <v>96</v>
       </c>
@@ -21494,8 +23229,10 @@
       <c r="W307">
         <v>0.5343230769230769</v>
       </c>
-    </row>
-    <row r="308" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD307" s="10"/>
+      <c r="AE307" s="10"/>
+    </row>
+    <row r="308" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A308" s="1">
         <v>97</v>
       </c>
@@ -21532,8 +23269,10 @@
       <c r="W308">
         <v>0.53437272727272733</v>
       </c>
-    </row>
-    <row r="309" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD308" s="10"/>
+      <c r="AE308" s="10"/>
+    </row>
+    <row r="309" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A309" s="1">
         <v>98</v>
       </c>
@@ -21570,8 +23309,10 @@
       <c r="W309">
         <v>0.44891818181818183</v>
       </c>
-    </row>
-    <row r="310" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD309" s="10"/>
+      <c r="AE309" s="10"/>
+    </row>
+    <row r="310" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A310" s="1">
         <v>99</v>
       </c>
@@ -21608,8 +23349,10 @@
       <c r="W310">
         <v>0.71606363636363635</v>
       </c>
-    </row>
-    <row r="311" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD310" s="10"/>
+      <c r="AE310" s="10"/>
+    </row>
+    <row r="311" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A311" s="1">
         <v>100</v>
       </c>
@@ -21646,24 +23389,40 @@
       <c r="W311">
         <v>0.71026363636363632</v>
       </c>
-    </row>
-    <row r="314" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD311" s="10">
+        <v>0.84699999999999998</v>
+      </c>
+      <c r="AE311" s="10"/>
+    </row>
+    <row r="312" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AD312" s="10"/>
+      <c r="AE312" s="10"/>
+    </row>
+    <row r="313" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AD313" s="10"/>
+      <c r="AE313" s="10"/>
+    </row>
+    <row r="314" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
         <v>23</v>
       </c>
       <c r="S314" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="315" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD314" s="10"/>
+      <c r="AE314" s="10"/>
+    </row>
+    <row r="315" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A315" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S315" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="316" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD315" s="10"/>
+      <c r="AE315" s="10"/>
+    </row>
+    <row r="316" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A316" s="1">
         <v>1</v>
       </c>
@@ -21712,8 +23471,10 @@
       <c r="W316">
         <v>6.9800000000000001E-2</v>
       </c>
-    </row>
-    <row r="317" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD316" s="10"/>
+      <c r="AE316" s="10"/>
+    </row>
+    <row r="317" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A317" s="1">
         <v>2</v>
       </c>
@@ -21762,8 +23523,10 @@
       <c r="W317">
         <v>3.1899999999999998E-2</v>
       </c>
-    </row>
-    <row r="318" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD317" s="10"/>
+      <c r="AE317" s="10"/>
+    </row>
+    <row r="318" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A318" s="1">
         <v>3</v>
       </c>
@@ -21812,8 +23575,10 @@
       <c r="W318">
         <v>1.66E-2</v>
       </c>
-    </row>
-    <row r="319" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD318" s="10"/>
+      <c r="AE318" s="10"/>
+    </row>
+    <row r="319" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A319" s="1">
         <v>4</v>
       </c>
@@ -21862,8 +23627,10 @@
       <c r="W319">
         <v>0.46360000000000001</v>
       </c>
-    </row>
-    <row r="320" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD319" s="10"/>
+      <c r="AE319" s="10"/>
+    </row>
+    <row r="320" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A320" s="1">
         <v>5</v>
       </c>
@@ -21912,8 +23679,10 @@
       <c r="W320">
         <v>0.33260000000000001</v>
       </c>
-    </row>
-    <row r="321" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD320" s="10"/>
+      <c r="AE320" s="10"/>
+    </row>
+    <row r="321" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A321" s="1">
         <v>6</v>
       </c>
@@ -21959,8 +23728,10 @@
       <c r="W321">
         <v>0.1235</v>
       </c>
-    </row>
-    <row r="322" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD321" s="10"/>
+      <c r="AE321" s="10"/>
+    </row>
+    <row r="322" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A322" s="1">
         <v>7</v>
       </c>
@@ -22006,8 +23777,10 @@
       <c r="W322">
         <v>0.104</v>
       </c>
-    </row>
-    <row r="323" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD322" s="10"/>
+      <c r="AE322" s="10"/>
+    </row>
+    <row r="323" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A323" s="1">
         <v>8</v>
       </c>
@@ -22053,8 +23826,10 @@
       <c r="W323">
         <v>0.4073</v>
       </c>
-    </row>
-    <row r="324" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD323" s="10"/>
+      <c r="AE323" s="10"/>
+    </row>
+    <row r="324" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
         <v>9</v>
       </c>
@@ -22100,8 +23875,10 @@
       <c r="W324">
         <v>9.35E-2</v>
       </c>
-    </row>
-    <row r="325" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD324" s="10"/>
+      <c r="AE324" s="10"/>
+    </row>
+    <row r="325" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
         <v>10</v>
       </c>
@@ -22147,8 +23924,10 @@
       <c r="W325">
         <v>0.51939999999999997</v>
       </c>
-    </row>
-    <row r="326" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD325" s="10"/>
+      <c r="AE325" s="10"/>
+    </row>
+    <row r="326" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A326" s="1">
         <v>11</v>
       </c>
@@ -22188,8 +23967,10 @@
       <c r="W326">
         <v>0.74129999999999996</v>
       </c>
-    </row>
-    <row r="327" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD326" s="10"/>
+      <c r="AE326" s="10"/>
+    </row>
+    <row r="327" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A327" s="1">
         <v>12</v>
       </c>
@@ -22229,8 +24010,10 @@
       <c r="W327">
         <v>0.58169999999999999</v>
       </c>
-    </row>
-    <row r="328" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD327" s="10"/>
+      <c r="AE327" s="10"/>
+    </row>
+    <row r="328" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
         <v>13</v>
       </c>
@@ -22270,8 +24053,10 @@
       <c r="W328">
         <v>0.86040000000000005</v>
       </c>
-    </row>
-    <row r="329" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD328" s="10"/>
+      <c r="AE328" s="10"/>
+    </row>
+    <row r="329" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A329" s="1">
         <v>14</v>
       </c>
@@ -22311,8 +24096,10 @@
       <c r="W329">
         <v>0.8962</v>
       </c>
-    </row>
-    <row r="330" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD329" s="10"/>
+      <c r="AE329" s="10"/>
+    </row>
+    <row r="330" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A330" s="1">
         <v>15</v>
       </c>
@@ -22352,8 +24139,10 @@
       <c r="W330">
         <v>0.90749999999999997</v>
       </c>
-    </row>
-    <row r="331" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD330" s="10"/>
+      <c r="AE330" s="10"/>
+    </row>
+    <row r="331" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A331" s="1">
         <v>16</v>
       </c>
@@ -22393,8 +24182,10 @@
       <c r="W331">
         <v>0.92230000000000001</v>
       </c>
-    </row>
-    <row r="332" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD331" s="10"/>
+      <c r="AE331" s="10"/>
+    </row>
+    <row r="332" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A332" s="1">
         <v>17</v>
       </c>
@@ -22434,8 +24225,10 @@
       <c r="W332">
         <v>0.94610000000000005</v>
       </c>
-    </row>
-    <row r="333" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD332" s="10"/>
+      <c r="AE332" s="10"/>
+    </row>
+    <row r="333" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A333" s="1">
         <v>18</v>
       </c>
@@ -22475,8 +24268,10 @@
       <c r="W333">
         <v>0.93869999999999998</v>
       </c>
-    </row>
-    <row r="334" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD333" s="10"/>
+      <c r="AE333" s="10"/>
+    </row>
+    <row r="334" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A334" s="1">
         <v>19</v>
       </c>
@@ -22516,8 +24311,10 @@
       <c r="W334">
         <v>0.91359999999999997</v>
       </c>
-    </row>
-    <row r="335" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD334" s="10"/>
+      <c r="AE334" s="10"/>
+    </row>
+    <row r="335" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A335" s="1">
         <v>20</v>
       </c>
@@ -22557,8 +24354,10 @@
       <c r="W335">
         <v>0.92490000000000006</v>
       </c>
-    </row>
-    <row r="336" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD335" s="10"/>
+      <c r="AE335" s="10"/>
+    </row>
+    <row r="336" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A336" s="1">
         <v>21</v>
       </c>
@@ -22598,8 +24397,10 @@
       <c r="W336">
         <v>0.89559999999999995</v>
       </c>
-    </row>
-    <row r="337" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD336" s="10"/>
+      <c r="AE336" s="10"/>
+    </row>
+    <row r="337" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A337" s="1">
         <v>22</v>
       </c>
@@ -22639,8 +24440,10 @@
       <c r="W337">
         <v>0.90029999999999999</v>
       </c>
-    </row>
-    <row r="338" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD337" s="10"/>
+      <c r="AE337" s="10"/>
+    </row>
+    <row r="338" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A338" s="1">
         <v>23</v>
       </c>
@@ -22680,8 +24483,10 @@
       <c r="W338">
         <v>0.87719999999999998</v>
       </c>
-    </row>
-    <row r="339" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD338" s="10"/>
+      <c r="AE338" s="10"/>
+    </row>
+    <row r="339" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A339" s="1">
         <v>24</v>
       </c>
@@ -22721,8 +24526,10 @@
       <c r="W339">
         <v>0.88770000000000004</v>
       </c>
-    </row>
-    <row r="340" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD339" s="10"/>
+      <c r="AE339" s="10"/>
+    </row>
+    <row r="340" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A340" s="1">
         <v>25</v>
       </c>
@@ -22762,8 +24569,10 @@
       <c r="W340">
         <v>0.96130000000000004</v>
       </c>
-    </row>
-    <row r="341" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD340" s="10"/>
+      <c r="AE340" s="10"/>
+    </row>
+    <row r="341" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A341" s="1">
         <v>26</v>
       </c>
@@ -22803,8 +24612,10 @@
       <c r="W341">
         <v>0.91279999999999994</v>
       </c>
-    </row>
-    <row r="342" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD341" s="10"/>
+      <c r="AE341" s="10"/>
+    </row>
+    <row r="342" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A342" s="1">
         <v>27</v>
       </c>
@@ -22844,8 +24655,10 @@
       <c r="W342">
         <v>0.94079999999999997</v>
       </c>
-    </row>
-    <row r="343" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD342" s="10"/>
+      <c r="AE342" s="10"/>
+    </row>
+    <row r="343" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A343" s="1">
         <v>28</v>
       </c>
@@ -22885,8 +24698,10 @@
       <c r="W343">
         <v>0.90910000000000002</v>
       </c>
-    </row>
-    <row r="344" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD343" s="10"/>
+      <c r="AE343" s="10"/>
+    </row>
+    <row r="344" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A344" s="1">
         <v>29</v>
       </c>
@@ -22926,8 +24741,10 @@
       <c r="W344">
         <v>0.86409999999999998</v>
       </c>
-    </row>
-    <row r="345" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD344" s="10"/>
+      <c r="AE344" s="10"/>
+    </row>
+    <row r="345" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A345" s="1">
         <v>30</v>
       </c>
@@ -22967,8 +24784,10 @@
       <c r="W345">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="346" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD345" s="10"/>
+      <c r="AE345" s="10"/>
+    </row>
+    <row r="346" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A346" s="1">
         <v>31</v>
       </c>
@@ -23008,8 +24827,10 @@
       <c r="W346">
         <v>0.88219999999999998</v>
       </c>
-    </row>
-    <row r="347" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD346" s="10"/>
+      <c r="AE346" s="10"/>
+    </row>
+    <row r="347" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A347" s="1">
         <v>32</v>
       </c>
@@ -23049,8 +24870,10 @@
       <c r="W347">
         <v>0.94110000000000005</v>
       </c>
-    </row>
-    <row r="348" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD347" s="10"/>
+      <c r="AE347" s="10"/>
+    </row>
+    <row r="348" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A348" s="1">
         <v>33</v>
       </c>
@@ -23090,8 +24913,10 @@
       <c r="W348">
         <v>0.96</v>
       </c>
-    </row>
-    <row r="349" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD348" s="10"/>
+      <c r="AE348" s="10"/>
+    </row>
+    <row r="349" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A349" s="1">
         <v>34</v>
       </c>
@@ -23131,8 +24956,10 @@
       <c r="W349">
         <v>0.92779999999999996</v>
       </c>
-    </row>
-    <row r="350" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD349" s="10"/>
+      <c r="AE349" s="10"/>
+    </row>
+    <row r="350" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A350" s="1">
         <v>35</v>
       </c>
@@ -23172,8 +24999,10 @@
       <c r="W350">
         <v>0.97440000000000004</v>
       </c>
-    </row>
-    <row r="351" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD350" s="10"/>
+      <c r="AE350" s="10"/>
+    </row>
+    <row r="351" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A351" s="1">
         <v>36</v>
       </c>
@@ -23213,8 +25042,10 @@
       <c r="W351">
         <v>0.91679999999999995</v>
       </c>
-    </row>
-    <row r="352" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD351" s="10"/>
+      <c r="AE351" s="10"/>
+    </row>
+    <row r="352" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A352" s="1">
         <v>37</v>
       </c>
@@ -23254,8 +25085,10 @@
       <c r="W352">
         <v>0.97760000000000002</v>
       </c>
-    </row>
-    <row r="353" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD352" s="10"/>
+      <c r="AE352" s="10"/>
+    </row>
+    <row r="353" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A353" s="1">
         <v>38</v>
       </c>
@@ -23295,8 +25128,10 @@
       <c r="W353">
         <v>0.97050000000000003</v>
       </c>
-    </row>
-    <row r="354" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD353" s="10"/>
+      <c r="AE353" s="10"/>
+    </row>
+    <row r="354" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A354" s="1">
         <v>39</v>
       </c>
@@ -23336,8 +25171,10 @@
       <c r="W354">
         <v>0.97219999999999995</v>
       </c>
-    </row>
-    <row r="355" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD354" s="10"/>
+      <c r="AE354" s="10"/>
+    </row>
+    <row r="355" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A355" s="1">
         <v>40</v>
       </c>
@@ -23377,8 +25214,10 @@
       <c r="W355">
         <v>0.95840000000000003</v>
       </c>
-    </row>
-    <row r="356" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD355" s="10"/>
+      <c r="AE355" s="10"/>
+    </row>
+    <row r="356" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A356" s="1">
         <v>41</v>
       </c>
@@ -23418,8 +25257,10 @@
       <c r="W356">
         <v>0.93820000000000003</v>
       </c>
-    </row>
-    <row r="357" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD356" s="10"/>
+      <c r="AE356" s="10"/>
+    </row>
+    <row r="357" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A357" s="1">
         <v>42</v>
       </c>
@@ -23459,8 +25300,10 @@
       <c r="W357">
         <v>0.93479999999999996</v>
       </c>
-    </row>
-    <row r="358" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD357" s="10"/>
+      <c r="AE357" s="10"/>
+    </row>
+    <row r="358" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A358" s="1">
         <v>43</v>
       </c>
@@ -23500,8 +25343,10 @@
       <c r="W358">
         <v>0.92479999999999996</v>
       </c>
-    </row>
-    <row r="359" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD358" s="10"/>
+      <c r="AE358" s="10"/>
+    </row>
+    <row r="359" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A359" s="1">
         <v>44</v>
       </c>
@@ -23541,8 +25386,10 @@
       <c r="W359">
         <v>0.84960000000000002</v>
       </c>
-    </row>
-    <row r="360" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD359" s="10"/>
+      <c r="AE359" s="10"/>
+    </row>
+    <row r="360" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A360" s="1">
         <v>45</v>
       </c>
@@ -23582,8 +25429,10 @@
       <c r="W360">
         <v>0.90290000000000004</v>
       </c>
-    </row>
-    <row r="361" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD360" s="10"/>
+      <c r="AE360" s="10"/>
+    </row>
+    <row r="361" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A361" s="1">
         <v>46</v>
       </c>
@@ -23623,8 +25472,10 @@
       <c r="W361">
         <v>0.93479999999999996</v>
       </c>
-    </row>
-    <row r="362" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD361" s="10"/>
+      <c r="AE361" s="10"/>
+    </row>
+    <row r="362" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A362" s="1">
         <v>47</v>
       </c>
@@ -23664,8 +25515,10 @@
       <c r="W362">
         <v>0.95420000000000005</v>
       </c>
-    </row>
-    <row r="363" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD362" s="10"/>
+      <c r="AE362" s="10"/>
+    </row>
+    <row r="363" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A363" s="1">
         <v>48</v>
       </c>
@@ -23705,8 +25558,10 @@
       <c r="W363">
         <v>0.96479999999999999</v>
       </c>
-    </row>
-    <row r="364" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD363" s="10"/>
+      <c r="AE363" s="10"/>
+    </row>
+    <row r="364" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A364" s="1">
         <v>49</v>
       </c>
@@ -23746,8 +25601,10 @@
       <c r="W364">
         <v>0.96830000000000005</v>
       </c>
-    </row>
-    <row r="365" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD364" s="10"/>
+      <c r="AE364" s="10"/>
+    </row>
+    <row r="365" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A365" s="1">
         <v>50</v>
       </c>
@@ -23787,8 +25644,10 @@
       <c r="W365">
         <v>0.84099999999999997</v>
       </c>
-    </row>
-    <row r="366" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD365" s="10"/>
+      <c r="AE365" s="10"/>
+    </row>
+    <row r="366" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A366" s="1">
         <v>51</v>
       </c>
@@ -23828,8 +25687,10 @@
       <c r="W366">
         <v>0.24079999999999999</v>
       </c>
-    </row>
-    <row r="367" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD366" s="10"/>
+      <c r="AE366" s="10"/>
+    </row>
+    <row r="367" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A367" s="1">
         <v>52</v>
       </c>
@@ -23869,8 +25730,10 @@
       <c r="W367">
         <v>0.91379999999999995</v>
       </c>
-    </row>
-    <row r="368" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD367" s="10"/>
+      <c r="AE367" s="10"/>
+    </row>
+    <row r="368" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A368" s="1">
         <v>53</v>
       </c>
@@ -23910,8 +25773,10 @@
       <c r="W368">
         <v>0.90210000000000001</v>
       </c>
-    </row>
-    <row r="369" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD368" s="10"/>
+      <c r="AE368" s="10"/>
+    </row>
+    <row r="369" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A369" s="1">
         <v>54</v>
       </c>
@@ -23951,8 +25816,10 @@
       <c r="W369">
         <v>0.97640000000000005</v>
       </c>
-    </row>
-    <row r="370" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD369" s="10"/>
+      <c r="AE369" s="10"/>
+    </row>
+    <row r="370" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A370" s="1">
         <v>55</v>
       </c>
@@ -23992,8 +25859,10 @@
       <c r="W370">
         <v>0.98380000000000001</v>
       </c>
-    </row>
-    <row r="371" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD370" s="10"/>
+      <c r="AE370" s="10"/>
+    </row>
+    <row r="371" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A371" s="1">
         <v>56</v>
       </c>
@@ -24033,8 +25902,10 @@
       <c r="W371">
         <v>0.89600000000000002</v>
       </c>
-    </row>
-    <row r="372" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD371" s="10"/>
+      <c r="AE371" s="10"/>
+    </row>
+    <row r="372" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A372" s="1">
         <v>57</v>
       </c>
@@ -24074,8 +25945,10 @@
       <c r="W372">
         <v>0.92269999999999996</v>
       </c>
-    </row>
-    <row r="373" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD372" s="10"/>
+      <c r="AE372" s="10"/>
+    </row>
+    <row r="373" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A373" s="1">
         <v>58</v>
       </c>
@@ -24115,8 +25988,10 @@
       <c r="W373">
         <v>0.77580000000000005</v>
       </c>
-    </row>
-    <row r="374" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD373" s="10"/>
+      <c r="AE373" s="10"/>
+    </row>
+    <row r="374" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A374" s="1">
         <v>59</v>
       </c>
@@ -24156,8 +26031,10 @@
       <c r="W374">
         <v>0.96250000000000002</v>
       </c>
-    </row>
-    <row r="375" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD374" s="10"/>
+      <c r="AE374" s="10"/>
+    </row>
+    <row r="375" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A375" s="1">
         <v>60</v>
       </c>
@@ -24197,8 +26074,10 @@
       <c r="W375">
         <v>0.85729999999999995</v>
       </c>
-    </row>
-    <row r="376" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD375" s="10"/>
+      <c r="AE375" s="10"/>
+    </row>
+    <row r="376" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A376" s="1">
         <v>61</v>
       </c>
@@ -24238,8 +26117,10 @@
       <c r="W376">
         <v>0.95550000000000002</v>
       </c>
-    </row>
-    <row r="377" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD376" s="10"/>
+      <c r="AE376" s="10"/>
+    </row>
+    <row r="377" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A377" s="1">
         <v>62</v>
       </c>
@@ -24279,8 +26160,10 @@
       <c r="W377">
         <v>0.91820000000000002</v>
       </c>
-    </row>
-    <row r="378" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD377" s="10"/>
+      <c r="AE377" s="10"/>
+    </row>
+    <row r="378" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A378" s="1">
         <v>63</v>
       </c>
@@ -24320,8 +26203,10 @@
       <c r="W378">
         <v>0.96519999999999995</v>
       </c>
-    </row>
-    <row r="379" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD378" s="10"/>
+      <c r="AE378" s="10"/>
+    </row>
+    <row r="379" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A379" s="1">
         <v>64</v>
       </c>
@@ -24361,8 +26246,10 @@
       <c r="W379">
         <v>0.66979999999999995</v>
       </c>
-    </row>
-    <row r="380" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD379" s="10"/>
+      <c r="AE379" s="10"/>
+    </row>
+    <row r="380" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A380" s="1">
         <v>65</v>
       </c>
@@ -24402,8 +26289,10 @@
       <c r="W380">
         <v>0.95899999999999996</v>
       </c>
-    </row>
-    <row r="381" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD380" s="10"/>
+      <c r="AE380" s="10"/>
+    </row>
+    <row r="381" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A381" s="1">
         <v>66</v>
       </c>
@@ -24443,8 +26332,10 @@
       <c r="W381">
         <v>0.93889999999999996</v>
       </c>
-    </row>
-    <row r="382" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD381" s="10"/>
+      <c r="AE381" s="10"/>
+    </row>
+    <row r="382" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A382" s="1">
         <v>67</v>
       </c>
@@ -24484,8 +26375,10 @@
       <c r="W382">
         <v>0.94420000000000004</v>
       </c>
-    </row>
-    <row r="383" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD382" s="10"/>
+      <c r="AE382" s="10"/>
+    </row>
+    <row r="383" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A383" s="1">
         <v>68</v>
       </c>
@@ -24525,8 +26418,10 @@
       <c r="W383">
         <v>0.73309999999999997</v>
       </c>
-    </row>
-    <row r="384" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD383" s="10"/>
+      <c r="AE383" s="10"/>
+    </row>
+    <row r="384" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A384" s="1">
         <v>69</v>
       </c>
@@ -24566,8 +26461,10 @@
       <c r="W384">
         <v>0.93899999999999995</v>
       </c>
-    </row>
-    <row r="385" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD384" s="10"/>
+      <c r="AE384" s="10"/>
+    </row>
+    <row r="385" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A385" s="1">
         <v>70</v>
       </c>
@@ -24607,8 +26504,10 @@
       <c r="W385">
         <v>0.99429999999999996</v>
       </c>
-    </row>
-    <row r="386" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD385" s="10"/>
+      <c r="AE385" s="10"/>
+    </row>
+    <row r="386" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A386" s="1">
         <v>71</v>
       </c>
@@ -24648,8 +26547,10 @@
       <c r="W386">
         <v>0.97550000000000003</v>
       </c>
-    </row>
-    <row r="387" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD386" s="10"/>
+      <c r="AE386" s="10"/>
+    </row>
+    <row r="387" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A387" s="1">
         <v>72</v>
       </c>
@@ -24689,8 +26590,10 @@
       <c r="W387">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="388" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD387" s="10"/>
+      <c r="AE387" s="10"/>
+    </row>
+    <row r="388" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A388" s="1">
         <v>73</v>
       </c>
@@ -24730,8 +26633,10 @@
       <c r="W388">
         <v>0.9556</v>
       </c>
-    </row>
-    <row r="389" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD388" s="10"/>
+      <c r="AE388" s="10"/>
+    </row>
+    <row r="389" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A389" s="1">
         <v>74</v>
       </c>
@@ -24771,8 +26676,10 @@
       <c r="W389">
         <v>0.96919999999999995</v>
       </c>
-    </row>
-    <row r="390" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD389" s="10"/>
+      <c r="AE389" s="10"/>
+    </row>
+    <row r="390" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A390" s="1">
         <v>75</v>
       </c>
@@ -24812,8 +26719,10 @@
       <c r="W390">
         <v>0.96479999999999999</v>
       </c>
-    </row>
-    <row r="391" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD390" s="10"/>
+      <c r="AE390" s="10"/>
+    </row>
+    <row r="391" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A391" s="1">
         <v>76</v>
       </c>
@@ -24853,8 +26762,10 @@
       <c r="W391">
         <v>0.92730000000000001</v>
       </c>
-    </row>
-    <row r="392" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD391" s="10"/>
+      <c r="AE391" s="10"/>
+    </row>
+    <row r="392" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A392" s="1">
         <v>77</v>
       </c>
@@ -24894,8 +26805,10 @@
       <c r="W392">
         <v>0.95279999999999998</v>
       </c>
-    </row>
-    <row r="393" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD392" s="10"/>
+      <c r="AE392" s="10"/>
+    </row>
+    <row r="393" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A393" s="1">
         <v>78</v>
       </c>
@@ -24935,8 +26848,10 @@
       <c r="W393">
         <v>0.91790000000000005</v>
       </c>
-    </row>
-    <row r="394" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD393" s="10"/>
+      <c r="AE393" s="10"/>
+    </row>
+    <row r="394" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A394" s="1">
         <v>79</v>
       </c>
@@ -24976,8 +26891,10 @@
       <c r="W394">
         <v>0.92020000000000002</v>
       </c>
-    </row>
-    <row r="395" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD394" s="10"/>
+      <c r="AE394" s="10"/>
+    </row>
+    <row r="395" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A395" s="1">
         <v>80</v>
       </c>
@@ -25017,8 +26934,10 @@
       <c r="W395">
         <v>1</v>
       </c>
-    </row>
-    <row r="396" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD395" s="10"/>
+      <c r="AE395" s="10"/>
+    </row>
+    <row r="396" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A396" s="1">
         <v>81</v>
       </c>
@@ -25058,8 +26977,10 @@
       <c r="W396">
         <v>0.99439999999999995</v>
       </c>
-    </row>
-    <row r="397" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD396" s="10"/>
+      <c r="AE396" s="10"/>
+    </row>
+    <row r="397" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A397" s="1">
         <v>82</v>
       </c>
@@ -25099,8 +27020,10 @@
       <c r="W397">
         <v>0.85270000000000001</v>
       </c>
-    </row>
-    <row r="398" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD397" s="10"/>
+      <c r="AE397" s="10"/>
+    </row>
+    <row r="398" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A398" s="1">
         <v>83</v>
       </c>
@@ -25140,8 +27063,10 @@
       <c r="W398">
         <v>0.88260000000000005</v>
       </c>
-    </row>
-    <row r="399" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD398" s="10"/>
+      <c r="AE398" s="10"/>
+    </row>
+    <row r="399" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A399" s="1">
         <v>84</v>
       </c>
@@ -25181,8 +27106,10 @@
       <c r="W399">
         <v>0.99950000000000006</v>
       </c>
-    </row>
-    <row r="400" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD399" s="10"/>
+      <c r="AE399" s="10"/>
+    </row>
+    <row r="400" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A400" s="1">
         <v>85</v>
       </c>
@@ -25222,8 +27149,10 @@
       <c r="W400">
         <v>0.97640000000000005</v>
       </c>
-    </row>
-    <row r="401" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD400" s="10"/>
+      <c r="AE400" s="10"/>
+    </row>
+    <row r="401" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A401" s="1">
         <v>86</v>
       </c>
@@ -25263,8 +27192,10 @@
       <c r="W401">
         <v>0.95669999999999999</v>
       </c>
-    </row>
-    <row r="402" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD401" s="10"/>
+      <c r="AE401" s="10"/>
+    </row>
+    <row r="402" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A402" s="1">
         <v>87</v>
       </c>
@@ -25304,8 +27235,10 @@
       <c r="W402">
         <v>0.24779999999999999</v>
       </c>
-    </row>
-    <row r="403" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD402" s="10"/>
+      <c r="AE402" s="10"/>
+    </row>
+    <row r="403" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A403" s="1">
         <v>88</v>
       </c>
@@ -25345,8 +27278,10 @@
       <c r="W403">
         <v>0.97550000000000003</v>
       </c>
-    </row>
-    <row r="404" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD403" s="10"/>
+      <c r="AE403" s="10"/>
+    </row>
+    <row r="404" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A404" s="1">
         <v>89</v>
       </c>
@@ -25386,8 +27321,10 @@
       <c r="W404">
         <v>0.90359999999999996</v>
       </c>
-    </row>
-    <row r="405" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD404" s="10"/>
+      <c r="AE404" s="10"/>
+    </row>
+    <row r="405" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A405" s="1">
         <v>90</v>
       </c>
@@ -25427,8 +27364,10 @@
       <c r="W405">
         <v>0.89370000000000005</v>
       </c>
-    </row>
-    <row r="406" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD405" s="10"/>
+      <c r="AE405" s="10"/>
+    </row>
+    <row r="406" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A406" s="1">
         <v>91</v>
       </c>
@@ -25468,8 +27407,10 @@
       <c r="W406">
         <v>0.41949999999999998</v>
       </c>
-    </row>
-    <row r="407" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD406" s="10"/>
+      <c r="AE406" s="10"/>
+    </row>
+    <row r="407" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A407" s="1">
         <v>92</v>
       </c>
@@ -25509,8 +27450,10 @@
       <c r="W407">
         <v>0.83309999999999995</v>
       </c>
-    </row>
-    <row r="408" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD407" s="10"/>
+      <c r="AE407" s="10"/>
+    </row>
+    <row r="408" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A408" s="1">
         <v>93</v>
       </c>
@@ -25550,8 +27493,10 @@
       <c r="W408">
         <v>0.99150000000000005</v>
       </c>
-    </row>
-    <row r="409" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD408" s="10"/>
+      <c r="AE408" s="10"/>
+    </row>
+    <row r="409" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A409" s="1">
         <v>94</v>
       </c>
@@ -25591,8 +27536,10 @@
       <c r="W409">
         <v>0.96120000000000005</v>
       </c>
-    </row>
-    <row r="410" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD409" s="10"/>
+      <c r="AE409" s="10"/>
+    </row>
+    <row r="410" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A410" s="1">
         <v>95</v>
       </c>
@@ -25629,8 +27576,10 @@
       <c r="W410">
         <v>0.93610000000000004</v>
       </c>
-    </row>
-    <row r="411" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD410" s="10"/>
+      <c r="AE410" s="10"/>
+    </row>
+    <row r="411" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A411" s="1">
         <v>96</v>
       </c>
@@ -25667,8 +27616,10 @@
       <c r="W411">
         <v>0.3538</v>
       </c>
-    </row>
-    <row r="412" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD411" s="10"/>
+      <c r="AE411" s="10"/>
+    </row>
+    <row r="412" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A412" s="1">
         <v>97</v>
       </c>
@@ -25705,8 +27656,10 @@
       <c r="W412">
         <v>0.87370000000000003</v>
       </c>
-    </row>
-    <row r="413" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD412" s="10"/>
+      <c r="AE412" s="10"/>
+    </row>
+    <row r="413" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A413" s="1">
         <v>98</v>
       </c>
@@ -25743,8 +27696,10 @@
       <c r="W413">
         <v>0.1381</v>
       </c>
-    </row>
-    <row r="414" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD413" s="10"/>
+      <c r="AE413" s="10"/>
+    </row>
+    <row r="414" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A414" s="1">
         <v>99</v>
       </c>
@@ -25781,8 +27736,10 @@
       <c r="W414">
         <v>0.21329999999999999</v>
       </c>
-    </row>
-    <row r="415" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AD414" s="10"/>
+      <c r="AE414" s="10"/>
+    </row>
+    <row r="415" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A415" s="1">
         <v>100</v>
       </c>
@@ -25819,9 +27776,367 @@
       <c r="W415">
         <v>0.91869999999999996</v>
       </c>
+      <c r="AD415" s="10"/>
+      <c r="AE415" s="10"/>
+    </row>
+    <row r="416" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AD416" s="10"/>
+      <c r="AE416" s="10"/>
+    </row>
+    <row r="417" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD417" s="10"/>
+      <c r="AE417" s="10"/>
+    </row>
+    <row r="418" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD418" s="10"/>
+      <c r="AE418" s="10"/>
+    </row>
+    <row r="419" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD419" s="10"/>
+      <c r="AE419" s="10"/>
+    </row>
+    <row r="420" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD420" s="10"/>
+      <c r="AE420" s="10"/>
+    </row>
+    <row r="421" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD421" s="10"/>
+      <c r="AE421" s="10"/>
+    </row>
+    <row r="422" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD422" s="10"/>
+      <c r="AE422" s="10"/>
+    </row>
+    <row r="423" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD423" s="10"/>
+      <c r="AE423" s="10"/>
+    </row>
+    <row r="424" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD424" s="10"/>
+      <c r="AE424" s="10"/>
+    </row>
+    <row r="425" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD425" s="10"/>
+      <c r="AE425" s="10"/>
+    </row>
+    <row r="426" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD426" s="10"/>
+      <c r="AE426" s="10"/>
+    </row>
+    <row r="427" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD427" s="10"/>
+      <c r="AE427" s="10"/>
+    </row>
+    <row r="428" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD428" s="10"/>
+      <c r="AE428" s="10"/>
+    </row>
+    <row r="429" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD429" s="10"/>
+      <c r="AE429" s="10"/>
+    </row>
+    <row r="430" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD430" s="10"/>
+      <c r="AE430" s="10"/>
+    </row>
+    <row r="431" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD431" s="10"/>
+      <c r="AE431" s="10"/>
+    </row>
+    <row r="432" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD432" s="10"/>
+      <c r="AE432" s="10"/>
+    </row>
+    <row r="433" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD433" s="10"/>
+      <c r="AE433" s="10"/>
+    </row>
+    <row r="434" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD434" s="10"/>
+      <c r="AE434" s="10"/>
+    </row>
+    <row r="435" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD435" s="10"/>
+      <c r="AE435" s="10"/>
+    </row>
+    <row r="436" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD436" s="10"/>
+      <c r="AE436" s="10"/>
+    </row>
+    <row r="437" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD437" s="10"/>
+      <c r="AE437" s="10"/>
+    </row>
+    <row r="438" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD438" s="10"/>
+      <c r="AE438" s="10"/>
+    </row>
+    <row r="439" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD439" s="10"/>
+      <c r="AE439" s="10"/>
+    </row>
+    <row r="440" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD440" s="10"/>
+      <c r="AE440" s="10"/>
+    </row>
+    <row r="441" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD441" s="10"/>
+      <c r="AE441" s="10"/>
+    </row>
+    <row r="442" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD442" s="10"/>
+      <c r="AE442" s="10"/>
+    </row>
+    <row r="443" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD443" s="10"/>
+      <c r="AE443" s="10"/>
+    </row>
+    <row r="444" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD444" s="10"/>
+      <c r="AE444" s="10"/>
+    </row>
+    <row r="445" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD445" s="10"/>
+      <c r="AE445" s="10"/>
+    </row>
+    <row r="446" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD446" s="10"/>
+      <c r="AE446" s="10"/>
+    </row>
+    <row r="447" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD447" s="10"/>
+      <c r="AE447" s="10"/>
+    </row>
+    <row r="448" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD448" s="10"/>
+      <c r="AE448" s="10"/>
+    </row>
+    <row r="449" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD449" s="10"/>
+      <c r="AE449" s="10"/>
+    </row>
+    <row r="450" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD450" s="10"/>
+      <c r="AE450" s="10"/>
+    </row>
+    <row r="451" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD451" s="10"/>
+      <c r="AE451" s="10"/>
+    </row>
+    <row r="452" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD452" s="10"/>
+      <c r="AE452" s="10"/>
+    </row>
+    <row r="453" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD453" s="10"/>
+      <c r="AE453" s="10"/>
+    </row>
+    <row r="454" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD454" s="10"/>
+      <c r="AE454" s="10"/>
+    </row>
+    <row r="455" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD455" s="10"/>
+      <c r="AE455" s="10"/>
+    </row>
+    <row r="456" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD456" s="10"/>
+      <c r="AE456" s="10"/>
+    </row>
+    <row r="457" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD457" s="10"/>
+      <c r="AE457" s="10"/>
+    </row>
+    <row r="458" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD458" s="10"/>
+      <c r="AE458" s="10"/>
+    </row>
+    <row r="459" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD459" s="10"/>
+      <c r="AE459" s="10"/>
+    </row>
+    <row r="460" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD460" s="10"/>
+      <c r="AE460" s="10"/>
+    </row>
+    <row r="461" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD461" s="10"/>
+      <c r="AE461" s="10"/>
+    </row>
+    <row r="462" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD462" s="10"/>
+      <c r="AE462" s="10"/>
+    </row>
+    <row r="463" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD463" s="10"/>
+      <c r="AE463" s="10"/>
+    </row>
+    <row r="464" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD464" s="10"/>
+      <c r="AE464" s="10"/>
+    </row>
+    <row r="465" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD465" s="10"/>
+      <c r="AE465" s="10"/>
+    </row>
+    <row r="466" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD466" s="10"/>
+      <c r="AE466" s="10"/>
+    </row>
+    <row r="467" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD467" s="10"/>
+      <c r="AE467" s="10"/>
+    </row>
+    <row r="468" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD468" s="10"/>
+      <c r="AE468" s="10"/>
+    </row>
+    <row r="469" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD469" s="10"/>
+      <c r="AE469" s="10"/>
+    </row>
+    <row r="470" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD470" s="10"/>
+      <c r="AE470" s="10"/>
+    </row>
+    <row r="471" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD471" s="10"/>
+      <c r="AE471" s="10"/>
+    </row>
+    <row r="472" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD472" s="10"/>
+      <c r="AE472" s="10"/>
+    </row>
+    <row r="473" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD473" s="10"/>
+      <c r="AE473" s="10"/>
+    </row>
+    <row r="474" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD474" s="10"/>
+      <c r="AE474" s="10"/>
+    </row>
+    <row r="475" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD475" s="10"/>
+      <c r="AE475" s="10"/>
+    </row>
+    <row r="476" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD476" s="10"/>
+      <c r="AE476" s="10"/>
+    </row>
+    <row r="477" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD477" s="10"/>
+      <c r="AE477" s="10"/>
+    </row>
+    <row r="478" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD478" s="10"/>
+      <c r="AE478" s="10"/>
+    </row>
+    <row r="479" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD479" s="10"/>
+      <c r="AE479" s="10"/>
+    </row>
+    <row r="480" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD480" s="10"/>
+      <c r="AE480" s="10"/>
+    </row>
+    <row r="481" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD481" s="10"/>
+      <c r="AE481" s="10"/>
+    </row>
+    <row r="482" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD482" s="10"/>
+      <c r="AE482" s="10"/>
+    </row>
+    <row r="483" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD483" s="10"/>
+      <c r="AE483" s="10"/>
+    </row>
+    <row r="484" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD484" s="10"/>
+      <c r="AE484" s="10"/>
+    </row>
+    <row r="485" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD485" s="10"/>
+      <c r="AE485" s="10"/>
+    </row>
+    <row r="486" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD486" s="10"/>
+      <c r="AE486" s="10"/>
+    </row>
+    <row r="487" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD487" s="10"/>
+      <c r="AE487" s="10"/>
+    </row>
+    <row r="488" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD488" s="10"/>
+      <c r="AE488" s="10"/>
+    </row>
+    <row r="489" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD489" s="10"/>
+      <c r="AE489" s="10"/>
+    </row>
+    <row r="490" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD490" s="10"/>
+      <c r="AE490" s="10"/>
+    </row>
+    <row r="491" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD491" s="10"/>
+      <c r="AE491" s="10"/>
+    </row>
+    <row r="492" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD492" s="10"/>
+      <c r="AE492" s="10"/>
+    </row>
+    <row r="493" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD493" s="10"/>
+      <c r="AE493" s="10"/>
+    </row>
+    <row r="494" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD494" s="10"/>
+      <c r="AE494" s="10"/>
+    </row>
+    <row r="495" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD495" s="10"/>
+      <c r="AE495" s="10"/>
+    </row>
+    <row r="496" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD496" s="10"/>
+      <c r="AE496" s="10"/>
+    </row>
+    <row r="497" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD497" s="10"/>
+      <c r="AE497" s="10"/>
+    </row>
+    <row r="498" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD498" s="10"/>
+      <c r="AE498" s="10"/>
+    </row>
+    <row r="499" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD499" s="10"/>
+      <c r="AE499" s="10"/>
+    </row>
+    <row r="500" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD500" s="10"/>
+      <c r="AE500" s="10"/>
+    </row>
+    <row r="501" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD501" s="10"/>
+      <c r="AE501" s="10"/>
+    </row>
+    <row r="502" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD502" s="10"/>
+      <c r="AE502" s="10"/>
+    </row>
+    <row r="503" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD503" s="10"/>
+      <c r="AE503" s="10"/>
+    </row>
+    <row r="504" spans="30:31" x14ac:dyDescent="0.2">
+      <c r="AD504" s="10"/>
+      <c r="AE504" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="C2:D2"/>
@@ -25830,6 +28145,8 @@
     <mergeCell ref="T2:W2"/>
     <mergeCell ref="T4:U4"/>
     <mergeCell ref="V4:W4"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AD2:AE2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/CIFAR_Global.xlsx
+++ b/CIFAR_Global.xlsx
@@ -8628,6 +8628,9 @@
       <c r="K5" t="n">
         <v>0.094</v>
       </c>
+      <c r="R5" t="n">
+        <v>0.1001</v>
+      </c>
       <c r="S5" s="1" t="n">
         <v>1</v>
       </c>
@@ -8648,6 +8651,9 @@
       </c>
       <c r="AE5" s="10" t="n">
         <v>0.09089999999999999</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.1023</v>
       </c>
       <c r="AG5" t="n">
         <v>0.1394</v>
@@ -8687,6 +8693,9 @@
       <c r="K6" t="n">
         <v>0.1688</v>
       </c>
+      <c r="R6" t="n">
+        <v>0.1727</v>
+      </c>
       <c r="S6" s="1" t="n">
         <v>2</v>
       </c>
@@ -8707,6 +8716,9 @@
       </c>
       <c r="AE6" s="10" t="n">
         <v>0.09089999999999999</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.213</v>
       </c>
       <c r="AG6" t="n">
         <v>0.1707</v>
@@ -8746,6 +8758,9 @@
       <c r="K7" t="n">
         <v>0.432</v>
       </c>
+      <c r="R7" t="n">
+        <v>0.1943</v>
+      </c>
       <c r="S7" s="1" t="n">
         <v>3</v>
       </c>
@@ -8766,6 +8781,9 @@
       </c>
       <c r="AE7" s="10" t="n">
         <v>0.09089999999999999</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.3268</v>
       </c>
       <c r="AG7" t="n">
         <v>0.1938</v>
@@ -8805,6 +8823,9 @@
       <c r="K8" t="n">
         <v>0.5504</v>
       </c>
+      <c r="R8" t="n">
+        <v>0.1761</v>
+      </c>
       <c r="S8" s="1" t="n">
         <v>4</v>
       </c>
@@ -8825,6 +8846,9 @@
       </c>
       <c r="AE8" s="10" t="n">
         <v>0.09089999999999999</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.3877</v>
       </c>
       <c r="AG8" t="n">
         <v>0.2288</v>
@@ -8864,6 +8888,9 @@
       <c r="K9" t="n">
         <v>0.601</v>
       </c>
+      <c r="R9" t="n">
+        <v>0.2647</v>
+      </c>
       <c r="S9" s="1" t="n">
         <v>5</v>
       </c>
@@ -8884,6 +8911,9 @@
       </c>
       <c r="AE9" s="10" t="n">
         <v>0.09089999999999999</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.4428</v>
       </c>
     </row>
     <row r="10">
@@ -8917,6 +8947,9 @@
       <c r="K10" t="n">
         <v>0.6235000000000001</v>
       </c>
+      <c r="R10" t="n">
+        <v>0.2774</v>
+      </c>
       <c r="S10" s="1" t="n">
         <v>6</v>
       </c>
@@ -8937,6 +8970,9 @@
       </c>
       <c r="AE10" s="10" t="n">
         <v>0.09089999999999999</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.4663</v>
       </c>
     </row>
     <row r="11">
@@ -8970,6 +9006,9 @@
       <c r="K11" t="n">
         <v>0.6457000000000001</v>
       </c>
+      <c r="R11" t="n">
+        <v>0.2132</v>
+      </c>
       <c r="S11" s="1" t="n">
         <v>7</v>
       </c>
@@ -8990,6 +9029,9 @@
       </c>
       <c r="AE11" s="10" t="n">
         <v>0.09089999999999999</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.4921</v>
       </c>
     </row>
     <row r="12">
@@ -9023,6 +9065,9 @@
       <c r="K12" t="n">
         <v>0.6545</v>
       </c>
+      <c r="R12" t="n">
+        <v>0.2452</v>
+      </c>
       <c r="S12" s="1" t="n">
         <v>8</v>
       </c>
@@ -9043,6 +9088,9 @@
       </c>
       <c r="AE12" s="10" t="n">
         <v>0.09089999999999999</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.4943</v>
       </c>
     </row>
     <row r="13">
@@ -9076,6 +9124,9 @@
       <c r="K13" t="n">
         <v>0.6627999999999999</v>
       </c>
+      <c r="R13" t="n">
+        <v>0.2296</v>
+      </c>
       <c r="S13" s="1" t="n">
         <v>9</v>
       </c>
@@ -9096,6 +9147,9 @@
       </c>
       <c r="AE13" s="10" t="n">
         <v>0.09089999999999999</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.5113</v>
       </c>
     </row>
     <row r="14">
@@ -9129,6 +9183,9 @@
       <c r="K14" t="n">
         <v>0.6666</v>
       </c>
+      <c r="R14" t="n">
+        <v>0.2179</v>
+      </c>
       <c r="S14" s="1" t="n">
         <v>10</v>
       </c>
@@ -9149,6 +9206,9 @@
       </c>
       <c r="AE14" s="10" t="n">
         <v>0.1172</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.5191</v>
       </c>
     </row>
     <row r="15">
@@ -9176,6 +9236,9 @@
       <c r="K15" t="n">
         <v>0.6719000000000001</v>
       </c>
+      <c r="R15" t="n">
+        <v>0.2566</v>
+      </c>
       <c r="S15" s="1" t="n">
         <v>11</v>
       </c>
@@ -9196,6 +9259,9 @@
       </c>
       <c r="AE15" s="10" t="n">
         <v>0.09089999999999999</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.529</v>
       </c>
     </row>
     <row r="16">
@@ -9223,6 +9289,9 @@
       <c r="K16" t="n">
         <v>0.6795</v>
       </c>
+      <c r="R16" t="n">
+        <v>0.2587</v>
+      </c>
       <c r="S16" s="1" t="n">
         <v>12</v>
       </c>
@@ -9243,6 +9312,9 @@
       </c>
       <c r="AE16" s="10" t="n">
         <v>0.1144</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.5315</v>
       </c>
     </row>
     <row r="17">
@@ -9270,6 +9342,9 @@
       <c r="K17" t="n">
         <v>0.6805</v>
       </c>
+      <c r="R17" t="n">
+        <v>0.2723</v>
+      </c>
       <c r="S17" s="1" t="n">
         <v>13</v>
       </c>
@@ -9290,6 +9365,9 @@
       </c>
       <c r="AE17" s="10" t="n">
         <v>0.1508</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.5433</v>
       </c>
     </row>
     <row r="18">
@@ -9317,6 +9395,9 @@
       <c r="K18" t="n">
         <v>0.6874</v>
       </c>
+      <c r="R18" t="n">
+        <v>0.2391</v>
+      </c>
       <c r="S18" s="1" t="n">
         <v>14</v>
       </c>
@@ -9337,6 +9418,9 @@
       </c>
       <c r="AE18" s="10" t="n">
         <v>0.1069</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.5454</v>
       </c>
     </row>
     <row r="19">
@@ -9364,6 +9448,9 @@
       <c r="K19" t="n">
         <v>0.6873</v>
       </c>
+      <c r="R19" t="n">
+        <v>0.2751</v>
+      </c>
       <c r="S19" s="1" t="n">
         <v>15</v>
       </c>
@@ -9384,6 +9471,9 @@
       </c>
       <c r="AE19" s="10" t="n">
         <v>0.1514</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.5534</v>
       </c>
     </row>
     <row r="20">
@@ -9411,6 +9501,9 @@
       <c r="K20" t="n">
         <v>0.6891</v>
       </c>
+      <c r="R20" t="n">
+        <v>0.2973</v>
+      </c>
       <c r="S20" s="1" t="n">
         <v>16</v>
       </c>
@@ -9431,6 +9524,9 @@
       </c>
       <c r="AE20" s="10" t="n">
         <v>0.09089999999999999</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.5506</v>
       </c>
     </row>
     <row r="21">
@@ -9458,6 +9554,9 @@
       <c r="K21" t="n">
         <v>0.6937</v>
       </c>
+      <c r="R21" t="n">
+        <v>0.2607</v>
+      </c>
       <c r="S21" s="1" t="n">
         <v>17</v>
       </c>
@@ -9478,6 +9577,9 @@
       </c>
       <c r="AE21" s="10" t="n">
         <v>0.1184</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.4998</v>
       </c>
     </row>
     <row r="22">
@@ -9505,6 +9607,9 @@
       <c r="K22" t="n">
         <v>0.6915</v>
       </c>
+      <c r="R22" t="n">
+        <v>0.2761</v>
+      </c>
       <c r="S22" s="1" t="n">
         <v>18</v>
       </c>
@@ -9525,6 +9630,9 @@
       </c>
       <c r="AE22" s="10" t="n">
         <v>0.1251</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.545</v>
       </c>
     </row>
     <row r="23">
@@ -9552,6 +9660,9 @@
       <c r="K23" t="n">
         <v>0.6914</v>
       </c>
+      <c r="R23" t="n">
+        <v>0.2625</v>
+      </c>
       <c r="S23" s="1" t="n">
         <v>19</v>
       </c>
@@ -9572,6 +9683,9 @@
       </c>
       <c r="AE23" s="10" t="n">
         <v>0.1005</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.5599</v>
       </c>
     </row>
     <row r="24">
@@ -9599,6 +9713,9 @@
       <c r="K24" t="n">
         <v>0.6926</v>
       </c>
+      <c r="R24" t="n">
+        <v>0.286</v>
+      </c>
       <c r="S24" s="1" t="n">
         <v>20</v>
       </c>
@@ -9619,6 +9736,9 @@
       </c>
       <c r="AE24" s="10" t="n">
         <v>0.1569</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.5652</v>
       </c>
     </row>
     <row r="25">
@@ -9646,6 +9766,9 @@
       <c r="K25" t="n">
         <v>0.6943</v>
       </c>
+      <c r="R25" t="n">
+        <v>0.295</v>
+      </c>
       <c r="S25" s="1" t="n">
         <v>21</v>
       </c>
@@ -9666,6 +9789,9 @@
       </c>
       <c r="AE25" s="10" t="n">
         <v>0.1419</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.5721000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -9693,6 +9819,9 @@
       <c r="K26" t="n">
         <v>0.6889</v>
       </c>
+      <c r="R26" t="n">
+        <v>0.2797</v>
+      </c>
       <c r="S26" s="1" t="n">
         <v>22</v>
       </c>
@@ -9713,6 +9842,9 @@
       </c>
       <c r="AE26" s="10" t="n">
         <v>0.1073</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.5728</v>
       </c>
     </row>
     <row r="27">
@@ -9740,6 +9872,9 @@
       <c r="K27" t="n">
         <v>0.6957</v>
       </c>
+      <c r="R27" t="n">
+        <v>0.2526</v>
+      </c>
       <c r="S27" s="1" t="n">
         <v>23</v>
       </c>
@@ -9760,6 +9895,9 @@
       </c>
       <c r="AE27" s="10" t="n">
         <v>0.0924</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.5707</v>
       </c>
     </row>
     <row r="28">
@@ -9787,6 +9925,9 @@
       <c r="K28" t="n">
         <v>0.6951000000000001</v>
       </c>
+      <c r="R28" t="n">
+        <v>0.2759</v>
+      </c>
       <c r="S28" s="1" t="n">
         <v>24</v>
       </c>
@@ -9807,6 +9948,9 @@
       </c>
       <c r="AE28" s="10" t="n">
         <v>0.152</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.575</v>
       </c>
     </row>
     <row r="29">
@@ -9834,6 +9978,9 @@
       <c r="K29" t="n">
         <v>0.6951000000000001</v>
       </c>
+      <c r="R29" t="n">
+        <v>0.2789</v>
+      </c>
       <c r="S29" s="1" t="n">
         <v>25</v>
       </c>
@@ -9854,6 +10001,9 @@
       </c>
       <c r="AE29" s="10" t="n">
         <v>0.0951</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.5803</v>
       </c>
     </row>
     <row r="30">
@@ -9881,6 +10031,9 @@
       <c r="K30" t="n">
         <v>0.6927</v>
       </c>
+      <c r="R30" t="n">
+        <v>0.2538</v>
+      </c>
       <c r="S30" s="1" t="n">
         <v>26</v>
       </c>
@@ -9901,6 +10054,9 @@
       </c>
       <c r="AE30" s="10" t="n">
         <v>0.1626</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.579</v>
       </c>
     </row>
     <row r="31">
@@ -9928,6 +10084,9 @@
       <c r="K31" t="n">
         <v>0.6937</v>
       </c>
+      <c r="R31" t="n">
+        <v>0.2355</v>
+      </c>
       <c r="S31" s="1" t="n">
         <v>27</v>
       </c>
@@ -9948,6 +10107,9 @@
       </c>
       <c r="AE31" s="10" t="n">
         <v>0.1014</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.5832000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -9975,6 +10137,9 @@
       <c r="K32" t="n">
         <v>0.6919</v>
       </c>
+      <c r="R32" t="n">
+        <v>0.2747</v>
+      </c>
       <c r="S32" s="1" t="n">
         <v>28</v>
       </c>
@@ -9995,6 +10160,9 @@
       </c>
       <c r="AE32" s="10" t="n">
         <v>0.1601</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.5775</v>
       </c>
     </row>
     <row r="33">
@@ -10022,6 +10190,9 @@
       <c r="K33" t="n">
         <v>0.6945</v>
       </c>
+      <c r="R33" t="n">
+        <v>0.2565</v>
+      </c>
       <c r="S33" s="1" t="n">
         <v>29</v>
       </c>
@@ -10042,6 +10213,9 @@
       </c>
       <c r="AE33" s="10" t="n">
         <v>0.092</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.5831</v>
       </c>
     </row>
     <row r="34">
@@ -10069,6 +10243,9 @@
       <c r="K34" t="n">
         <v>0.6965</v>
       </c>
+      <c r="R34" t="n">
+        <v>0.2632</v>
+      </c>
       <c r="S34" s="1" t="n">
         <v>30</v>
       </c>
@@ -10089,6 +10266,9 @@
       </c>
       <c r="AE34" s="10" t="n">
         <v>0.1091</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.585</v>
       </c>
     </row>
     <row r="35">
@@ -10116,6 +10296,9 @@
       <c r="K35" t="n">
         <v>0.6941000000000001</v>
       </c>
+      <c r="R35" t="n">
+        <v>0.2663</v>
+      </c>
       <c r="S35" s="1" t="n">
         <v>31</v>
       </c>
@@ -10136,6 +10319,9 @@
       </c>
       <c r="AE35" s="10" t="n">
         <v>0.1338</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.594</v>
       </c>
     </row>
     <row r="36">
@@ -10163,6 +10349,9 @@
       <c r="K36" t="n">
         <v>0.6887</v>
       </c>
+      <c r="R36" t="n">
+        <v>0.2694</v>
+      </c>
       <c r="S36" s="1" t="n">
         <v>32</v>
       </c>
@@ -10183,6 +10372,9 @@
       </c>
       <c r="AE36" s="10" t="n">
         <v>0.1023</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.5963000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -10210,6 +10402,9 @@
       <c r="K37" t="n">
         <v>0.6888</v>
       </c>
+      <c r="R37" t="n">
+        <v>0.2458</v>
+      </c>
       <c r="S37" s="1" t="n">
         <v>33</v>
       </c>
@@ -10230,6 +10425,9 @@
       </c>
       <c r="AE37" s="10" t="n">
         <v>0.1808</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.5869</v>
       </c>
     </row>
     <row r="38">
@@ -10257,6 +10455,9 @@
       <c r="K38" t="n">
         <v>0.6896</v>
       </c>
+      <c r="R38" t="n">
+        <v>0.2697</v>
+      </c>
       <c r="S38" s="1" t="n">
         <v>34</v>
       </c>
@@ -10277,6 +10478,9 @@
       </c>
       <c r="AE38" s="10" t="n">
         <v>0.2407</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.5866</v>
       </c>
     </row>
     <row r="39">
@@ -10304,6 +10508,9 @@
       <c r="K39" t="n">
         <v>0.6889</v>
       </c>
+      <c r="R39" t="n">
+        <v>0.2578</v>
+      </c>
       <c r="S39" s="1" t="n">
         <v>35</v>
       </c>
@@ -10324,6 +10531,9 @@
       </c>
       <c r="AE39" s="10" t="n">
         <v>0.1207</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.555</v>
       </c>
     </row>
     <row r="40">
@@ -10351,6 +10561,9 @@
       <c r="K40" t="n">
         <v>0.6922</v>
       </c>
+      <c r="R40" t="n">
+        <v>0.2501</v>
+      </c>
       <c r="S40" s="1" t="n">
         <v>36</v>
       </c>
@@ -10371,6 +10584,9 @@
       </c>
       <c r="AE40" s="10" t="n">
         <v>0.1356</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0.5855</v>
       </c>
     </row>
     <row r="41">
@@ -10398,6 +10614,9 @@
       <c r="K41" t="n">
         <v>0.6916</v>
       </c>
+      <c r="R41" t="n">
+        <v>0.2544</v>
+      </c>
       <c r="S41" s="1" t="n">
         <v>37</v>
       </c>
@@ -10418,6 +10637,9 @@
       </c>
       <c r="AE41" s="10" t="n">
         <v>0.1025</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0.5727</v>
       </c>
     </row>
     <row r="42">
@@ -10445,6 +10667,9 @@
       <c r="K42" t="n">
         <v>0.6919999999999999</v>
       </c>
+      <c r="R42" t="n">
+        <v>0.2571</v>
+      </c>
       <c r="S42" s="1" t="n">
         <v>38</v>
       </c>
@@ -10465,6 +10690,9 @@
       </c>
       <c r="AE42" s="10" t="n">
         <v>0.1812</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0.5913</v>
       </c>
     </row>
     <row r="43">
@@ -10492,6 +10720,9 @@
       <c r="K43" t="n">
         <v>0.6941000000000001</v>
       </c>
+      <c r="R43" t="n">
+        <v>0.2555</v>
+      </c>
       <c r="S43" s="1" t="n">
         <v>39</v>
       </c>
@@ -10512,6 +10743,9 @@
       </c>
       <c r="AE43" s="10" t="n">
         <v>0.1397</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0.6002</v>
       </c>
     </row>
     <row r="44">
@@ -10539,6 +10773,9 @@
       <c r="K44" t="n">
         <v>0.6912</v>
       </c>
+      <c r="R44" t="n">
+        <v>0.2409</v>
+      </c>
       <c r="S44" s="1" t="n">
         <v>40</v>
       </c>
@@ -10559,6 +10796,9 @@
       </c>
       <c r="AE44" s="10" t="n">
         <v>0.1248</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0.596</v>
       </c>
     </row>
     <row r="45">
@@ -10586,6 +10826,9 @@
       <c r="K45" t="n">
         <v>0.6926</v>
       </c>
+      <c r="R45" t="n">
+        <v>0.2701</v>
+      </c>
       <c r="S45" s="1" t="n">
         <v>41</v>
       </c>
@@ -10606,6 +10849,9 @@
       </c>
       <c r="AE45" s="10" t="n">
         <v>0.2036</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0.5994</v>
       </c>
     </row>
     <row r="46">
@@ -10633,6 +10879,9 @@
       <c r="K46" t="n">
         <v>0.6934</v>
       </c>
+      <c r="R46" t="n">
+        <v>0.2713</v>
+      </c>
       <c r="S46" s="1" t="n">
         <v>42</v>
       </c>
@@ -10653,6 +10902,9 @@
       </c>
       <c r="AE46" s="10" t="n">
         <v>0.1296</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0.6015</v>
       </c>
     </row>
     <row r="47">
@@ -10680,6 +10932,9 @@
       <c r="K47" t="n">
         <v>0.6912</v>
       </c>
+      <c r="R47" t="n">
+        <v>0.2498</v>
+      </c>
       <c r="S47" s="1" t="n">
         <v>43</v>
       </c>
@@ -10700,6 +10955,9 @@
       </c>
       <c r="AE47" s="10" t="n">
         <v>0.211</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0.6054</v>
       </c>
     </row>
     <row r="48">
@@ -10727,6 +10985,9 @@
       <c r="K48" t="n">
         <v>0.6908</v>
       </c>
+      <c r="R48" t="n">
+        <v>0.264</v>
+      </c>
       <c r="S48" s="1" t="n">
         <v>44</v>
       </c>
@@ -10747,6 +11008,9 @@
       </c>
       <c r="AE48" s="10" t="n">
         <v>0.0973</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0.6119</v>
       </c>
     </row>
     <row r="49">
@@ -10774,6 +11038,9 @@
       <c r="K49" t="n">
         <v>0.6875</v>
       </c>
+      <c r="R49" t="n">
+        <v>0.2728</v>
+      </c>
       <c r="S49" s="1" t="n">
         <v>45</v>
       </c>
@@ -10794,6 +11061,9 @@
       </c>
       <c r="AE49" s="10" t="n">
         <v>0.1552</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0.5997</v>
       </c>
     </row>
     <row r="50">
@@ -10821,6 +11091,9 @@
       <c r="K50" t="n">
         <v>0.6876</v>
       </c>
+      <c r="R50" t="n">
+        <v>0.2679</v>
+      </c>
       <c r="S50" s="1" t="n">
         <v>46</v>
       </c>
@@ -10841,6 +11114,9 @@
       </c>
       <c r="AE50" s="10" t="n">
         <v>0.1912</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0.6078</v>
       </c>
     </row>
     <row r="51">
@@ -10868,6 +11144,9 @@
       <c r="K51" t="n">
         <v>0.6886</v>
       </c>
+      <c r="R51" t="n">
+        <v>0.2442</v>
+      </c>
       <c r="S51" s="1" t="n">
         <v>47</v>
       </c>
@@ -10888,6 +11167,9 @@
       </c>
       <c r="AE51" s="10" t="n">
         <v>0.1959</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0.6089</v>
       </c>
     </row>
     <row r="52">
@@ -10915,6 +11197,9 @@
       <c r="K52" t="n">
         <v>0.6885</v>
       </c>
+      <c r="R52" t="n">
+        <v>0.2305</v>
+      </c>
       <c r="S52" s="1" t="n">
         <v>48</v>
       </c>
@@ -10935,6 +11220,9 @@
       </c>
       <c r="AE52" s="10" t="n">
         <v>0.2035</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0.5989</v>
       </c>
     </row>
     <row r="53">
@@ -10962,6 +11250,9 @@
       <c r="K53" t="n">
         <v>0.6881</v>
       </c>
+      <c r="R53" t="n">
+        <v>0.2635</v>
+      </c>
       <c r="S53" s="1" t="n">
         <v>49</v>
       </c>
@@ -10982,6 +11273,9 @@
       </c>
       <c r="AE53" s="10" t="n">
         <v>0.201</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0.6074000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -11009,6 +11303,9 @@
       <c r="K54" t="n">
         <v>0.6844</v>
       </c>
+      <c r="R54" t="n">
+        <v>0.2647</v>
+      </c>
       <c r="S54" s="1" t="n">
         <v>50</v>
       </c>
@@ -11029,6 +11326,9 @@
       </c>
       <c r="AE54" s="10" t="n">
         <v>0.2444</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0.6108</v>
       </c>
     </row>
     <row r="55">
@@ -11056,6 +11356,9 @@
       <c r="K55" t="n">
         <v>0.6874</v>
       </c>
+      <c r="R55" t="n">
+        <v>0.2748</v>
+      </c>
       <c r="S55" s="1" t="n">
         <v>51</v>
       </c>
@@ -11076,6 +11379,9 @@
       </c>
       <c r="AE55" s="10" t="n">
         <v>0.1826</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0.6139</v>
       </c>
     </row>
     <row r="56">
@@ -11103,6 +11409,9 @@
       <c r="K56" t="n">
         <v>0.6898</v>
       </c>
+      <c r="R56" t="n">
+        <v>0.243</v>
+      </c>
       <c r="S56" s="1" t="n">
         <v>52</v>
       </c>
@@ -11123,6 +11432,9 @@
       </c>
       <c r="AE56" s="10" t="n">
         <v>0.1298</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0.6116</v>
       </c>
     </row>
     <row r="57">
@@ -11150,6 +11462,9 @@
       <c r="K57" t="n">
         <v>0.6891</v>
       </c>
+      <c r="R57" t="n">
+        <v>0.2481</v>
+      </c>
       <c r="S57" s="1" t="n">
         <v>53</v>
       </c>
@@ -11170,6 +11485,9 @@
       </c>
       <c r="AE57" s="10" t="n">
         <v>0.1812</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0.6022</v>
       </c>
     </row>
     <row r="58">
@@ -11197,6 +11515,9 @@
       <c r="K58" t="n">
         <v>0.6914</v>
       </c>
+      <c r="R58" t="n">
+        <v>0.2502</v>
+      </c>
       <c r="S58" s="1" t="n">
         <v>54</v>
       </c>
@@ -11217,6 +11538,9 @@
       </c>
       <c r="AE58" s="10" t="n">
         <v>0.1397</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0.6011</v>
       </c>
     </row>
     <row r="59">
@@ -11244,6 +11568,9 @@
       <c r="K59" t="n">
         <v>0.6882</v>
       </c>
+      <c r="R59" t="n">
+        <v>0.2132</v>
+      </c>
       <c r="S59" s="1" t="n">
         <v>55</v>
       </c>
@@ -11264,6 +11591,9 @@
       </c>
       <c r="AE59" s="10" t="n">
         <v>0.1248</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0.6026</v>
       </c>
     </row>
     <row r="60">
@@ -11291,6 +11621,9 @@
       <c r="K60" t="n">
         <v>0.6901</v>
       </c>
+      <c r="R60" t="n">
+        <v>0.22</v>
+      </c>
       <c r="S60" s="1" t="n">
         <v>56</v>
       </c>
@@ -11311,6 +11644,9 @@
       </c>
       <c r="AE60" s="10" t="n">
         <v>0.1057</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>0.6157</v>
       </c>
     </row>
     <row r="61">
@@ -11338,6 +11674,9 @@
       <c r="K61" t="n">
         <v>0.6897</v>
       </c>
+      <c r="R61" t="n">
+        <v>0.2395</v>
+      </c>
       <c r="S61" s="1" t="n">
         <v>57</v>
       </c>
@@ -11358,6 +11697,9 @@
       </c>
       <c r="AE61" s="10" t="n">
         <v>0.1364</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0.6158</v>
       </c>
     </row>
     <row r="62">
@@ -11385,6 +11727,9 @@
       <c r="K62" t="n">
         <v>0.6891</v>
       </c>
+      <c r="R62" t="n">
+        <v>0.2503</v>
+      </c>
       <c r="S62" s="1" t="n">
         <v>58</v>
       </c>
@@ -11405,6 +11750,9 @@
       </c>
       <c r="AE62" s="10" t="n">
         <v>0.09089999999999999</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>0.6207</v>
       </c>
     </row>
     <row r="63">
@@ -11432,6 +11780,9 @@
       <c r="K63" t="n">
         <v>0.6891</v>
       </c>
+      <c r="R63" t="n">
+        <v>0.2661</v>
+      </c>
       <c r="S63" s="1" t="n">
         <v>59</v>
       </c>
@@ -11452,6 +11803,9 @@
       </c>
       <c r="AE63" s="10" t="n">
         <v>0.1203</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>0.6163999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -11479,6 +11833,9 @@
       <c r="K64" t="n">
         <v>0.6879</v>
       </c>
+      <c r="R64" t="n">
+        <v>0.2653</v>
+      </c>
       <c r="S64" s="1" t="n">
         <v>60</v>
       </c>
@@ -11499,6 +11856,9 @@
       </c>
       <c r="AE64" s="10" t="n">
         <v>0.1797</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0.6199</v>
       </c>
     </row>
     <row r="65">
@@ -11526,6 +11886,9 @@
       <c r="K65" t="n">
         <v>0.6883</v>
       </c>
+      <c r="R65" t="n">
+        <v>0.2695</v>
+      </c>
       <c r="S65" s="1" t="n">
         <v>61</v>
       </c>
@@ -11546,6 +11909,9 @@
       </c>
       <c r="AE65" s="10" t="n">
         <v>0.1674</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>0.617</v>
       </c>
     </row>
     <row r="66">
@@ -11573,6 +11939,9 @@
       <c r="K66" t="n">
         <v>0.6882</v>
       </c>
+      <c r="R66" t="n">
+        <v>0.2541</v>
+      </c>
       <c r="S66" s="1" t="n">
         <v>62</v>
       </c>
@@ -11593,6 +11962,9 @@
       </c>
       <c r="AE66" s="10" t="n">
         <v>0.1424</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0.6274</v>
       </c>
     </row>
     <row r="67">
@@ -11620,6 +11992,9 @@
       <c r="K67" t="n">
         <v>0.6891</v>
       </c>
+      <c r="R67" t="n">
+        <v>0.2559</v>
+      </c>
       <c r="S67" s="1" t="n">
         <v>63</v>
       </c>
@@ -11640,6 +12015,9 @@
       </c>
       <c r="AE67" s="10" t="n">
         <v>0.1685</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0.6188</v>
       </c>
     </row>
     <row r="68">
@@ -11667,6 +12045,9 @@
       <c r="K68" t="n">
         <v>0.6874</v>
       </c>
+      <c r="R68" t="n">
+        <v>0.266</v>
+      </c>
       <c r="S68" s="1" t="n">
         <v>64</v>
       </c>
@@ -11687,6 +12068,9 @@
       </c>
       <c r="AE68" s="10" t="n">
         <v>0.1543</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>0.6215000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -11714,6 +12098,9 @@
       <c r="K69" t="n">
         <v>0.6876</v>
       </c>
+      <c r="R69" t="n">
+        <v>0.2584</v>
+      </c>
       <c r="S69" s="1" t="n">
         <v>65</v>
       </c>
@@ -11734,6 +12121,9 @@
       </c>
       <c r="AE69" s="10" t="n">
         <v>0.1665</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0.6187</v>
       </c>
     </row>
     <row r="70">
@@ -11761,6 +12151,9 @@
       <c r="K70" t="n">
         <v>0.6867</v>
       </c>
+      <c r="R70" t="n">
+        <v>0.2684</v>
+      </c>
       <c r="S70" s="1" t="n">
         <v>66</v>
       </c>
@@ -11781,6 +12174,9 @@
       </c>
       <c r="AE70" s="10" t="n">
         <v>0.1137</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0.6216</v>
       </c>
     </row>
     <row r="71">
@@ -11808,6 +12204,9 @@
       <c r="K71" t="n">
         <v>0.6863</v>
       </c>
+      <c r="R71" t="n">
+        <v>0.2385</v>
+      </c>
       <c r="S71" s="1" t="n">
         <v>67</v>
       </c>
@@ -11828,6 +12227,9 @@
       </c>
       <c r="AE71" s="10" t="n">
         <v>0.2274</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>0.6223</v>
       </c>
     </row>
     <row r="72">
@@ -11855,6 +12257,9 @@
       <c r="K72" t="n">
         <v>0.6871</v>
       </c>
+      <c r="R72" t="n">
+        <v>0.2297</v>
+      </c>
       <c r="S72" s="1" t="n">
         <v>68</v>
       </c>
@@ -11875,6 +12280,9 @@
       </c>
       <c r="AE72" s="10" t="n">
         <v>0.209</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>0.6237</v>
       </c>
     </row>
     <row r="73">
@@ -11902,6 +12310,9 @@
       <c r="K73" t="n">
         <v>0.6865</v>
       </c>
+      <c r="R73" t="n">
+        <v>0.249</v>
+      </c>
       <c r="S73" s="1" t="n">
         <v>69</v>
       </c>
@@ -11922,6 +12333,9 @@
       </c>
       <c r="AE73" s="10" t="n">
         <v>0.2633</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>0.6213</v>
       </c>
     </row>
     <row r="74">
@@ -11949,6 +12363,9 @@
       <c r="K74" t="n">
         <v>0.6857</v>
       </c>
+      <c r="R74" t="n">
+        <v>0.2332</v>
+      </c>
       <c r="S74" s="1" t="n">
         <v>70</v>
       </c>
@@ -11969,6 +12386,9 @@
       </c>
       <c r="AE74" s="10" t="n">
         <v>0.2075</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>0.622</v>
       </c>
     </row>
     <row r="75">
@@ -11996,6 +12416,9 @@
       <c r="K75" t="n">
         <v>0.6879999999999999</v>
       </c>
+      <c r="R75" t="n">
+        <v>0.2105</v>
+      </c>
       <c r="S75" s="1" t="n">
         <v>71</v>
       </c>
@@ -12016,6 +12439,9 @@
       </c>
       <c r="AE75" s="10" t="n">
         <v>0.2101</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0.621</v>
       </c>
     </row>
     <row r="76">
@@ -12043,6 +12469,9 @@
       <c r="K76" t="n">
         <v>0.6863</v>
       </c>
+      <c r="R76" t="n">
+        <v>0.2596</v>
+      </c>
       <c r="S76" s="1" t="n">
         <v>72</v>
       </c>
@@ -12063,6 +12492,9 @@
       </c>
       <c r="AE76" s="10" t="n">
         <v>0.1305</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>0.6233</v>
       </c>
     </row>
     <row r="77">
@@ -12090,6 +12522,9 @@
       <c r="K77" t="n">
         <v>0.6869</v>
       </c>
+      <c r="R77" t="n">
+        <v>0.2663</v>
+      </c>
       <c r="S77" s="1" t="n">
         <v>73</v>
       </c>
@@ -12110,6 +12545,9 @@
       </c>
       <c r="AE77" s="10" t="n">
         <v>0.1563</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>0.6254999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -12137,6 +12575,9 @@
       <c r="K78" t="n">
         <v>0.6864</v>
       </c>
+      <c r="R78" t="n">
+        <v>0.2387</v>
+      </c>
       <c r="S78" s="1" t="n">
         <v>74</v>
       </c>
@@ -12157,6 +12598,9 @@
       </c>
       <c r="AE78" s="10" t="n">
         <v>0.1763</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>0.6232</v>
       </c>
     </row>
     <row r="79">
@@ -12184,6 +12628,9 @@
       <c r="K79" t="n">
         <v>0.6873</v>
       </c>
+      <c r="R79" t="n">
+        <v>0.2521</v>
+      </c>
       <c r="S79" s="1" t="n">
         <v>75</v>
       </c>
@@ -12204,6 +12651,9 @@
       </c>
       <c r="AE79" s="10" t="n">
         <v>0.1094</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>0.6225000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -12231,6 +12681,9 @@
       <c r="K80" t="n">
         <v>0.6866</v>
       </c>
+      <c r="R80" t="n">
+        <v>0.2374</v>
+      </c>
       <c r="S80" s="1" t="n">
         <v>76</v>
       </c>
@@ -12251,6 +12704,9 @@
       </c>
       <c r="AE80" s="10" t="n">
         <v>0.1966</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>0.6279</v>
       </c>
     </row>
     <row r="81">
@@ -12278,6 +12734,9 @@
       <c r="K81" t="n">
         <v>0.6862</v>
       </c>
+      <c r="R81" t="n">
+        <v>0.2313</v>
+      </c>
       <c r="S81" s="1" t="n">
         <v>77</v>
       </c>
@@ -12298,6 +12757,9 @@
       </c>
       <c r="AE81" s="10" t="n">
         <v>0.1511</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>0.63</v>
       </c>
     </row>
     <row r="82">
@@ -12325,6 +12787,9 @@
       <c r="K82" t="n">
         <v>0.6866</v>
       </c>
+      <c r="R82" t="n">
+        <v>0.2262</v>
+      </c>
       <c r="S82" s="1" t="n">
         <v>78</v>
       </c>
@@ -12345,6 +12810,9 @@
       </c>
       <c r="AE82" s="10" t="n">
         <v>0.1581</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>0.6276</v>
       </c>
     </row>
     <row r="83">
@@ -12372,6 +12840,9 @@
       <c r="K83" t="n">
         <v>0.6863</v>
       </c>
+      <c r="R83" t="n">
+        <v>0.2565</v>
+      </c>
       <c r="S83" s="1" t="n">
         <v>79</v>
       </c>
@@ -12392,6 +12863,9 @@
       </c>
       <c r="AE83" s="10" t="n">
         <v>0.2205</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>0.6253</v>
       </c>
     </row>
     <row r="84">
@@ -12419,6 +12893,9 @@
       <c r="K84" t="n">
         <v>0.6848</v>
       </c>
+      <c r="R84" t="n">
+        <v>0.2211</v>
+      </c>
       <c r="S84" s="1" t="n">
         <v>80</v>
       </c>
@@ -12439,6 +12916,9 @@
       </c>
       <c r="AE84" s="10" t="n">
         <v>0.2856</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>0.6251</v>
       </c>
     </row>
     <row r="85">
@@ -12466,6 +12946,9 @@
       <c r="K85" t="n">
         <v>0.6861</v>
       </c>
+      <c r="R85" t="n">
+        <v>0.2497</v>
+      </c>
       <c r="S85" s="1" t="n">
         <v>81</v>
       </c>
@@ -12486,6 +12969,9 @@
       </c>
       <c r="AE85" s="10" t="n">
         <v>0.2031</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>0.627</v>
       </c>
     </row>
     <row r="86">
@@ -12513,6 +12999,9 @@
       <c r="K86" t="n">
         <v>0.6855</v>
       </c>
+      <c r="R86" t="n">
+        <v>0.2471</v>
+      </c>
       <c r="S86" s="1" t="n">
         <v>82</v>
       </c>
@@ -12533,6 +13022,9 @@
       </c>
       <c r="AE86" s="10" t="n">
         <v>0.2053</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>0.6249</v>
       </c>
     </row>
     <row r="87">
@@ -12560,6 +13052,9 @@
       <c r="K87" t="n">
         <v>0.6831</v>
       </c>
+      <c r="R87" t="n">
+        <v>0.2303</v>
+      </c>
       <c r="S87" s="1" t="n">
         <v>83</v>
       </c>
@@ -12580,6 +13075,9 @@
       </c>
       <c r="AE87" s="10" t="n">
         <v>0.1224</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>0.6228</v>
       </c>
     </row>
     <row r="88">
@@ -12607,6 +13105,9 @@
       <c r="K88" t="n">
         <v>0.6802</v>
       </c>
+      <c r="R88" t="n">
+        <v>0.2475</v>
+      </c>
       <c r="S88" s="1" t="n">
         <v>84</v>
       </c>
@@ -12627,6 +13128,9 @@
       </c>
       <c r="AE88" s="10" t="n">
         <v>0.14</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>0.6279</v>
       </c>
     </row>
     <row r="89">
@@ -12654,6 +13158,9 @@
       <c r="K89" t="n">
         <v>0.6778</v>
       </c>
+      <c r="R89" t="n">
+        <v>0.2541</v>
+      </c>
       <c r="S89" s="1" t="n">
         <v>85</v>
       </c>
@@ -12674,6 +13181,9 @@
       </c>
       <c r="AE89" s="10" t="n">
         <v>0.1981</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>0.628</v>
       </c>
     </row>
     <row r="90">
@@ -12701,6 +13211,9 @@
       <c r="K90" t="n">
         <v>0.6762</v>
       </c>
+      <c r="R90" t="n">
+        <v>0.2445</v>
+      </c>
       <c r="S90" s="1" t="n">
         <v>86</v>
       </c>
@@ -12721,6 +13234,9 @@
       </c>
       <c r="AE90" s="10" t="n">
         <v>0.19</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>0.6277</v>
       </c>
     </row>
     <row r="91">
@@ -12748,6 +13264,9 @@
       <c r="K91" t="n">
         <v>0.6767</v>
       </c>
+      <c r="R91" t="n">
+        <v>0.25</v>
+      </c>
       <c r="S91" s="1" t="n">
         <v>87</v>
       </c>
@@ -12768,6 +13287,9 @@
       </c>
       <c r="AE91" s="10" t="n">
         <v>0.2021</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>0.6293</v>
       </c>
     </row>
     <row r="92">
@@ -12795,6 +13317,9 @@
       <c r="K92" t="n">
         <v>0.674</v>
       </c>
+      <c r="R92" t="n">
+        <v>0.2406</v>
+      </c>
       <c r="S92" s="1" t="n">
         <v>88</v>
       </c>
@@ -12815,6 +13340,9 @@
       </c>
       <c r="AE92" s="10" t="n">
         <v>0.2986</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>0.6263</v>
       </c>
     </row>
     <row r="93">
@@ -12842,6 +13370,9 @@
       <c r="K93" t="n">
         <v>0.6761</v>
       </c>
+      <c r="R93" t="n">
+        <v>0.2337</v>
+      </c>
       <c r="S93" s="1" t="n">
         <v>89</v>
       </c>
@@ -12862,6 +13393,9 @@
       </c>
       <c r="AE93" s="10" t="n">
         <v>0.2919</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>0.624</v>
       </c>
     </row>
     <row r="94">
@@ -12889,6 +13423,9 @@
       <c r="K94" t="n">
         <v>0.6765</v>
       </c>
+      <c r="R94" t="n">
+        <v>0.2476</v>
+      </c>
       <c r="S94" s="1" t="n">
         <v>90</v>
       </c>
@@ -12909,6 +13446,9 @@
       </c>
       <c r="AE94" s="10" t="n">
         <v>0.206</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>0.6205000000000001</v>
       </c>
     </row>
     <row r="95">
@@ -12936,6 +13476,9 @@
       <c r="K95" t="n">
         <v>0.6778999999999999</v>
       </c>
+      <c r="R95" t="n">
+        <v>0.2476</v>
+      </c>
       <c r="S95" s="1" t="n">
         <v>91</v>
       </c>
@@ -12956,6 +13499,9 @@
       </c>
       <c r="AE95" s="10" t="n">
         <v>0.2881</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>0.6284999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -12983,6 +13529,9 @@
       <c r="K96" t="n">
         <v>0.6761</v>
       </c>
+      <c r="R96" t="n">
+        <v>0.2486</v>
+      </c>
       <c r="S96" s="1" t="n">
         <v>92</v>
       </c>
@@ -13003,6 +13552,9 @@
       </c>
       <c r="AE96" s="10" t="n">
         <v>0.21</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>0.6292</v>
       </c>
     </row>
     <row r="97">
@@ -13030,6 +13582,9 @@
       <c r="K97" t="n">
         <v>0.6765</v>
       </c>
+      <c r="R97" t="n">
+        <v>0.2454</v>
+      </c>
       <c r="S97" s="1" t="n">
         <v>93</v>
       </c>
@@ -13050,6 +13605,9 @@
       </c>
       <c r="AE97" s="10" t="n">
         <v>0.3518</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>0.6277</v>
       </c>
     </row>
     <row r="98">
@@ -13077,6 +13635,9 @@
       <c r="K98" t="n">
         <v>0.6748</v>
       </c>
+      <c r="R98" t="n">
+        <v>0.2392</v>
+      </c>
       <c r="S98" s="1" t="n">
         <v>94</v>
       </c>
@@ -13097,6 +13658,9 @@
       </c>
       <c r="AE98" s="10" t="n">
         <v>0.2094</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>0.6281</v>
       </c>
     </row>
     <row r="99">
@@ -13121,6 +13685,9 @@
       <c r="K99" t="n">
         <v>0.6791</v>
       </c>
+      <c r="R99" t="n">
+        <v>0.2409</v>
+      </c>
       <c r="S99" s="1" t="n">
         <v>95</v>
       </c>
@@ -13141,6 +13708,9 @@
       </c>
       <c r="AE99" s="10" t="n">
         <v>0.2097</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>0.6239</v>
       </c>
     </row>
     <row r="100">
@@ -13165,6 +13735,9 @@
       <c r="K100" t="n">
         <v>0.675</v>
       </c>
+      <c r="R100" t="n">
+        <v>0.2561</v>
+      </c>
       <c r="S100" s="1" t="n">
         <v>96</v>
       </c>
@@ -13185,6 +13758,9 @@
       </c>
       <c r="AE100" s="10" t="n">
         <v>0.2105</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>0.6208</v>
       </c>
     </row>
     <row r="101">
@@ -13209,6 +13785,9 @@
       <c r="K101" t="n">
         <v>0.6735</v>
       </c>
+      <c r="R101" t="n">
+        <v>0.2417</v>
+      </c>
       <c r="S101" s="1" t="n">
         <v>97</v>
       </c>
@@ -13229,6 +13808,9 @@
       </c>
       <c r="AE101" s="10" t="n">
         <v>0.3568</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>0.6208</v>
       </c>
     </row>
     <row r="102">
@@ -13253,6 +13835,9 @@
       <c r="K102" t="n">
         <v>0.6751</v>
       </c>
+      <c r="R102" t="n">
+        <v>0.2197</v>
+      </c>
       <c r="S102" s="1" t="n">
         <v>98</v>
       </c>
@@ -13273,6 +13858,9 @@
       </c>
       <c r="AE102" s="10" t="n">
         <v>0.1924</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>0.6192</v>
       </c>
     </row>
     <row r="103">
@@ -13297,6 +13885,9 @@
       <c r="K103" t="n">
         <v>0.6749000000000001</v>
       </c>
+      <c r="R103" t="n">
+        <v>0.2235</v>
+      </c>
       <c r="S103" s="1" t="n">
         <v>99</v>
       </c>
@@ -13317,6 +13908,9 @@
       </c>
       <c r="AE103" s="10" t="n">
         <v>0.1453</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>0.6284</v>
       </c>
     </row>
     <row r="104">
@@ -13341,6 +13935,9 @@
       <c r="K104" t="n">
         <v>0.6767</v>
       </c>
+      <c r="R104" t="n">
+        <v>0.2042</v>
+      </c>
       <c r="S104" s="1" t="n">
         <v>100</v>
       </c>
@@ -13361,6 +13958,9 @@
       </c>
       <c r="AE104" s="10" t="n">
         <v>0.1657</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>0.627</v>
       </c>
     </row>
     <row r="105">
@@ -13429,6 +14029,9 @@
       <c r="K108" t="n">
         <v>1</v>
       </c>
+      <c r="R108" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="S108" s="1" t="n">
         <v>1</v>
       </c>
@@ -13446,6 +14049,9 @@
       </c>
       <c r="AD108" s="10" t="n"/>
       <c r="AE108" s="10" t="n"/>
+      <c r="AF108" t="n">
+        <v>1</v>
+      </c>
       <c r="AG108" t="n">
         <v>0.8</v>
       </c>
@@ -13484,6 +14090,9 @@
       <c r="K109" t="n">
         <v>0.5833333333333334</v>
       </c>
+      <c r="R109" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="S109" s="1" t="n">
         <v>2</v>
       </c>
@@ -13501,6 +14110,9 @@
       </c>
       <c r="AD109" s="10" t="n"/>
       <c r="AE109" s="10" t="n"/>
+      <c r="AF109" t="n">
+        <v>1</v>
+      </c>
       <c r="AG109" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -13539,6 +14151,9 @@
       <c r="K110" t="n">
         <v>0.5833333333333334</v>
       </c>
+      <c r="R110" t="n">
+        <v>0.5333333333333333</v>
+      </c>
       <c r="S110" s="1" t="n">
         <v>3</v>
       </c>
@@ -13556,6 +14171,9 @@
       </c>
       <c r="AD110" s="10" t="n"/>
       <c r="AE110" s="10" t="n"/>
+      <c r="AF110" t="n">
+        <v>1</v>
+      </c>
       <c r="AG110" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -13594,6 +14212,9 @@
       <c r="K111" t="n">
         <v>0.5</v>
       </c>
+      <c r="R111" t="n">
+        <v>0.5333333333333333</v>
+      </c>
       <c r="S111" s="1" t="n">
         <v>4</v>
       </c>
@@ -13611,6 +14232,9 @@
       </c>
       <c r="AD111" s="10" t="n"/>
       <c r="AE111" s="10" t="n"/>
+      <c r="AF111" t="n">
+        <v>0.7272727272727273</v>
+      </c>
       <c r="AG111" t="n">
         <v>0.6</v>
       </c>
@@ -13649,6 +14273,9 @@
       <c r="K112" t="n">
         <v>0.9166666666666666</v>
       </c>
+      <c r="R112" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="S112" s="1" t="n">
         <v>5</v>
       </c>
@@ -13666,6 +14293,9 @@
       </c>
       <c r="AD112" s="10" t="n"/>
       <c r="AE112" s="10" t="n"/>
+      <c r="AF112" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -13698,6 +14328,9 @@
       <c r="K113" t="n">
         <v>1</v>
       </c>
+      <c r="R113" t="n">
+        <v>0.4666666666666667</v>
+      </c>
       <c r="S113" s="1" t="n">
         <v>6</v>
       </c>
@@ -13715,6 +14348,9 @@
       </c>
       <c r="AD113" s="10" t="n"/>
       <c r="AE113" s="10" t="n"/>
+      <c r="AF113" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -13747,6 +14383,9 @@
       <c r="K114" t="n">
         <v>1</v>
       </c>
+      <c r="R114" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="S114" s="1" t="n">
         <v>7</v>
       </c>
@@ -13764,6 +14403,9 @@
       </c>
       <c r="AD114" s="10" t="n"/>
       <c r="AE114" s="10" t="n"/>
+      <c r="AF114" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -13796,6 +14438,9 @@
       <c r="K115" t="n">
         <v>1</v>
       </c>
+      <c r="R115" t="n">
+        <v>0.6</v>
+      </c>
       <c r="S115" s="1" t="n">
         <v>8</v>
       </c>
@@ -13813,6 +14458,9 @@
       </c>
       <c r="AD115" s="10" t="n"/>
       <c r="AE115" s="10" t="n"/>
+      <c r="AF115" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -13845,6 +14493,9 @@
       <c r="K116" t="n">
         <v>1</v>
       </c>
+      <c r="R116" t="n">
+        <v>0.6</v>
+      </c>
       <c r="S116" s="1" t="n">
         <v>9</v>
       </c>
@@ -13862,6 +14513,9 @@
       </c>
       <c r="AD116" s="10" t="n"/>
       <c r="AE116" s="10" t="n"/>
+      <c r="AF116" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -13894,6 +14548,9 @@
       <c r="K117" t="n">
         <v>1</v>
       </c>
+      <c r="R117" t="n">
+        <v>0.5333333333333333</v>
+      </c>
       <c r="S117" s="1" t="n">
         <v>10</v>
       </c>
@@ -13911,6 +14568,9 @@
       </c>
       <c r="AD117" s="10" t="n"/>
       <c r="AE117" s="10" t="n"/>
+      <c r="AF117" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -13937,6 +14597,9 @@
       <c r="K118" t="n">
         <v>1</v>
       </c>
+      <c r="R118" t="n">
+        <v>0.6</v>
+      </c>
       <c r="S118" s="1" t="n">
         <v>11</v>
       </c>
@@ -13954,6 +14617,9 @@
       </c>
       <c r="AD118" s="10" t="n"/>
       <c r="AE118" s="10" t="n"/>
+      <c r="AF118" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -13980,6 +14646,9 @@
       <c r="K119" t="n">
         <v>1</v>
       </c>
+      <c r="R119" t="n">
+        <v>0.6</v>
+      </c>
       <c r="S119" s="1" t="n">
         <v>12</v>
       </c>
@@ -13997,6 +14666,9 @@
       </c>
       <c r="AD119" s="10" t="n"/>
       <c r="AE119" s="10" t="n"/>
+      <c r="AF119" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -14023,6 +14695,9 @@
       <c r="K120" t="n">
         <v>1</v>
       </c>
+      <c r="R120" t="n">
+        <v>0.6</v>
+      </c>
       <c r="S120" s="1" t="n">
         <v>13</v>
       </c>
@@ -14040,6 +14715,9 @@
       </c>
       <c r="AD120" s="10" t="n"/>
       <c r="AE120" s="10" t="n"/>
+      <c r="AF120" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -14066,6 +14744,9 @@
       <c r="K121" t="n">
         <v>1</v>
       </c>
+      <c r="R121" t="n">
+        <v>0.6</v>
+      </c>
       <c r="S121" s="1" t="n">
         <v>14</v>
       </c>
@@ -14083,6 +14764,9 @@
       </c>
       <c r="AD121" s="10" t="n"/>
       <c r="AE121" s="10" t="n"/>
+      <c r="AF121" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -14109,6 +14793,9 @@
       <c r="K122" t="n">
         <v>1</v>
       </c>
+      <c r="R122" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="S122" s="1" t="n">
         <v>15</v>
       </c>
@@ -14126,6 +14813,9 @@
       </c>
       <c r="AD122" s="10" t="n"/>
       <c r="AE122" s="10" t="n"/>
+      <c r="AF122" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -14152,6 +14842,9 @@
       <c r="K123" t="n">
         <v>1</v>
       </c>
+      <c r="R123" t="n">
+        <v>0.7333333333333333</v>
+      </c>
       <c r="S123" s="1" t="n">
         <v>16</v>
       </c>
@@ -14169,6 +14862,9 @@
       </c>
       <c r="AD123" s="10" t="n"/>
       <c r="AE123" s="10" t="n"/>
+      <c r="AF123" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -14195,6 +14891,9 @@
       <c r="K124" t="n">
         <v>1</v>
       </c>
+      <c r="R124" t="n">
+        <v>0.6</v>
+      </c>
       <c r="S124" s="1" t="n">
         <v>17</v>
       </c>
@@ -14212,6 +14911,9 @@
       </c>
       <c r="AD124" s="10" t="n"/>
       <c r="AE124" s="10" t="n"/>
+      <c r="AF124" t="n">
+        <v>0.1666666666666667</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -14238,6 +14940,9 @@
       <c r="K125" t="n">
         <v>1</v>
       </c>
+      <c r="R125" t="n">
+        <v>0.6</v>
+      </c>
       <c r="S125" s="1" t="n">
         <v>18</v>
       </c>
@@ -14255,6 +14960,9 @@
       </c>
       <c r="AD125" s="10" t="n"/>
       <c r="AE125" s="10" t="n"/>
+      <c r="AF125" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -14281,6 +14989,9 @@
       <c r="K126" t="n">
         <v>1</v>
       </c>
+      <c r="R126" t="n">
+        <v>0.5333333333333333</v>
+      </c>
       <c r="S126" s="1" t="n">
         <v>19</v>
       </c>
@@ -14298,6 +15009,9 @@
       </c>
       <c r="AD126" s="10" t="n"/>
       <c r="AE126" s="10" t="n"/>
+      <c r="AF126" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -14324,6 +15038,9 @@
       <c r="K127" t="n">
         <v>1</v>
       </c>
+      <c r="R127" t="n">
+        <v>0.8666666666666667</v>
+      </c>
       <c r="S127" s="1" t="n">
         <v>20</v>
       </c>
@@ -14341,6 +15058,9 @@
       </c>
       <c r="AD127" s="10" t="n"/>
       <c r="AE127" s="10" t="n"/>
+      <c r="AF127" t="n">
+        <v>0.875</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -14367,6 +15087,9 @@
       <c r="K128" t="n">
         <v>1</v>
       </c>
+      <c r="R128" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="S128" s="1" t="n">
         <v>21</v>
       </c>
@@ -14384,6 +15107,9 @@
       </c>
       <c r="AD128" s="10" t="n"/>
       <c r="AE128" s="10" t="n"/>
+      <c r="AF128" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -14410,6 +15136,9 @@
       <c r="K129" t="n">
         <v>1</v>
       </c>
+      <c r="R129" t="n">
+        <v>0.5333333333333333</v>
+      </c>
       <c r="S129" s="1" t="n">
         <v>22</v>
       </c>
@@ -14427,6 +15156,9 @@
       </c>
       <c r="AD129" s="10" t="n"/>
       <c r="AE129" s="10" t="n"/>
+      <c r="AF129" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -14453,6 +15185,9 @@
       <c r="K130" t="n">
         <v>1</v>
       </c>
+      <c r="R130" t="n">
+        <v>0.6</v>
+      </c>
       <c r="S130" s="1" t="n">
         <v>23</v>
       </c>
@@ -14470,6 +15205,9 @@
       </c>
       <c r="AD130" s="10" t="n"/>
       <c r="AE130" s="10" t="n"/>
+      <c r="AF130" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -14496,6 +15234,9 @@
       <c r="K131" t="n">
         <v>1</v>
       </c>
+      <c r="R131" t="n">
+        <v>0.6</v>
+      </c>
       <c r="S131" s="1" t="n">
         <v>24</v>
       </c>
@@ -14513,6 +15254,9 @@
       </c>
       <c r="AD131" s="10" t="n"/>
       <c r="AE131" s="10" t="n"/>
+      <c r="AF131" t="n">
+        <v>0.8888888888888888</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -14539,6 +15283,9 @@
       <c r="K132" t="n">
         <v>1</v>
       </c>
+      <c r="R132" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="S132" s="1" t="n">
         <v>25</v>
       </c>
@@ -14556,6 +15303,9 @@
       </c>
       <c r="AD132" s="10" t="n"/>
       <c r="AE132" s="10" t="n"/>
+      <c r="AF132" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -14582,6 +15332,9 @@
       <c r="K133" t="n">
         <v>1</v>
       </c>
+      <c r="R133" t="n">
+        <v>0.6</v>
+      </c>
       <c r="S133" s="1" t="n">
         <v>26</v>
       </c>
@@ -14599,6 +15352,9 @@
       </c>
       <c r="AD133" s="10" t="n"/>
       <c r="AE133" s="10" t="n"/>
+      <c r="AF133" t="n">
+        <v>0.8888888888888888</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -14625,6 +15381,9 @@
       <c r="K134" t="n">
         <v>1</v>
       </c>
+      <c r="R134" t="n">
+        <v>0.6</v>
+      </c>
       <c r="S134" s="1" t="n">
         <v>27</v>
       </c>
@@ -14642,6 +15401,9 @@
       </c>
       <c r="AD134" s="10" t="n"/>
       <c r="AE134" s="10" t="n"/>
+      <c r="AF134" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -14668,6 +15430,9 @@
       <c r="K135" t="n">
         <v>1</v>
       </c>
+      <c r="R135" t="n">
+        <v>0.6</v>
+      </c>
       <c r="S135" s="1" t="n">
         <v>28</v>
       </c>
@@ -14685,6 +15450,9 @@
       </c>
       <c r="AD135" s="10" t="n"/>
       <c r="AE135" s="10" t="n"/>
+      <c r="AF135" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -14711,6 +15479,9 @@
       <c r="K136" t="n">
         <v>1</v>
       </c>
+      <c r="R136" t="n">
+        <v>0.2666666666666667</v>
+      </c>
       <c r="S136" s="1" t="n">
         <v>29</v>
       </c>
@@ -14728,6 +15499,9 @@
       </c>
       <c r="AD136" s="10" t="n"/>
       <c r="AE136" s="10" t="n"/>
+      <c r="AF136" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -14754,6 +15528,9 @@
       <c r="K137" t="n">
         <v>1</v>
       </c>
+      <c r="R137" t="n">
+        <v>0.4615384615384616</v>
+      </c>
       <c r="S137" s="1" t="n">
         <v>30</v>
       </c>
@@ -14771,6 +15548,9 @@
       </c>
       <c r="AD137" s="10" t="n"/>
       <c r="AE137" s="10" t="n"/>
+      <c r="AF137" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -14797,6 +15577,9 @@
       <c r="K138" t="n">
         <v>1</v>
       </c>
+      <c r="R138" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S138" s="1" t="n">
         <v>31</v>
       </c>
@@ -14814,6 +15597,9 @@
       </c>
       <c r="AD138" s="10" t="n"/>
       <c r="AE138" s="10" t="n"/>
+      <c r="AF138" t="n">
+        <v>0.9090909090909091</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -14840,6 +15626,9 @@
       <c r="K139" t="n">
         <v>1</v>
       </c>
+      <c r="R139" t="n">
+        <v>0.6428571428571429</v>
+      </c>
       <c r="S139" s="1" t="n">
         <v>32</v>
       </c>
@@ -14857,6 +15646,9 @@
       </c>
       <c r="AD139" s="10" t="n"/>
       <c r="AE139" s="10" t="n"/>
+      <c r="AF139" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -14883,6 +15675,9 @@
       <c r="K140" t="n">
         <v>1</v>
       </c>
+      <c r="R140" t="n">
+        <v>0.5333333333333333</v>
+      </c>
       <c r="S140" s="1" t="n">
         <v>33</v>
       </c>
@@ -14900,6 +15695,9 @@
       </c>
       <c r="AD140" s="10" t="n"/>
       <c r="AE140" s="10" t="n"/>
+      <c r="AF140" t="n">
+        <v>0.625</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -14926,6 +15724,9 @@
       <c r="K141" t="n">
         <v>1</v>
       </c>
+      <c r="R141" t="n">
+        <v>0.6153846153846154</v>
+      </c>
       <c r="S141" s="1" t="n">
         <v>34</v>
       </c>
@@ -14943,6 +15744,9 @@
       </c>
       <c r="AD141" s="10" t="n"/>
       <c r="AE141" s="10" t="n"/>
+      <c r="AF141" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -14969,6 +15773,9 @@
       <c r="K142" t="n">
         <v>1</v>
       </c>
+      <c r="R142" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S142" s="1" t="n">
         <v>35</v>
       </c>
@@ -14986,6 +15793,9 @@
       </c>
       <c r="AD142" s="10" t="n"/>
       <c r="AE142" s="10" t="n"/>
+      <c r="AF142" t="n">
+        <v>0.1111111111111111</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -15012,6 +15822,9 @@
       <c r="K143" t="n">
         <v>1</v>
       </c>
+      <c r="R143" t="n">
+        <v>0.3076923076923077</v>
+      </c>
       <c r="S143" s="1" t="n">
         <v>36</v>
       </c>
@@ -15029,6 +15842,9 @@
       </c>
       <c r="AD143" s="10" t="n"/>
       <c r="AE143" s="10" t="n"/>
+      <c r="AF143" t="n">
+        <v>0.7777777777777778</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -15055,6 +15871,9 @@
       <c r="K144" t="n">
         <v>1</v>
       </c>
+      <c r="R144" t="n">
+        <v>0.4545454545454545</v>
+      </c>
       <c r="S144" s="1" t="n">
         <v>37</v>
       </c>
@@ -15072,6 +15891,9 @@
       </c>
       <c r="AD144" s="10" t="n"/>
       <c r="AE144" s="10" t="n"/>
+      <c r="AF144" t="n">
+        <v>0.1666666666666667</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -15098,6 +15920,9 @@
       <c r="K145" t="n">
         <v>1</v>
       </c>
+      <c r="R145" t="n">
+        <v>0.6363636363636364</v>
+      </c>
       <c r="S145" s="1" t="n">
         <v>38</v>
       </c>
@@ -15115,6 +15940,9 @@
       </c>
       <c r="AD145" s="10" t="n"/>
       <c r="AE145" s="10" t="n"/>
+      <c r="AF145" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -15141,6 +15969,9 @@
       <c r="K146" t="n">
         <v>1</v>
       </c>
+      <c r="R146" t="n">
+        <v>0.6153846153846154</v>
+      </c>
       <c r="S146" s="1" t="n">
         <v>39</v>
       </c>
@@ -15158,6 +15989,9 @@
       </c>
       <c r="AD146" s="10" t="n"/>
       <c r="AE146" s="10" t="n"/>
+      <c r="AF146" t="n">
+        <v>0.9090909090909091</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -15184,6 +16018,9 @@
       <c r="K147" t="n">
         <v>1</v>
       </c>
+      <c r="R147" t="n">
+        <v>0.5833333333333334</v>
+      </c>
       <c r="S147" s="1" t="n">
         <v>40</v>
       </c>
@@ -15201,6 +16038,9 @@
       </c>
       <c r="AD147" s="10" t="n"/>
       <c r="AE147" s="10" t="n"/>
+      <c r="AF147" t="n">
+        <v>0.4285714285714285</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -15227,6 +16067,9 @@
       <c r="K148" t="n">
         <v>1</v>
       </c>
+      <c r="R148" t="n">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="S148" s="1" t="n">
         <v>41</v>
       </c>
@@ -15244,6 +16087,9 @@
       </c>
       <c r="AD148" s="10" t="n"/>
       <c r="AE148" s="10" t="n"/>
+      <c r="AF148" t="n">
+        <v>0.6363636363636364</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -15270,6 +16116,9 @@
       <c r="K149" t="n">
         <v>0.9166666666666666</v>
       </c>
+      <c r="R149" t="n">
+        <v>0.5454545454545454</v>
+      </c>
       <c r="S149" s="1" t="n">
         <v>42</v>
       </c>
@@ -15287,6 +16136,9 @@
       </c>
       <c r="AD149" s="10" t="n"/>
       <c r="AE149" s="10" t="n"/>
+      <c r="AF149" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -15313,6 +16165,9 @@
       <c r="K150" t="n">
         <v>1</v>
       </c>
+      <c r="R150" t="n">
+        <v>0.4545454545454545</v>
+      </c>
       <c r="S150" s="1" t="n">
         <v>43</v>
       </c>
@@ -15330,6 +16185,9 @@
       </c>
       <c r="AD150" s="10" t="n"/>
       <c r="AE150" s="10" t="n"/>
+      <c r="AF150" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -15356,6 +16214,9 @@
       <c r="K151" t="n">
         <v>1</v>
       </c>
+      <c r="R151" t="n">
+        <v>0.6363636363636364</v>
+      </c>
       <c r="S151" s="1" t="n">
         <v>44</v>
       </c>
@@ -15373,6 +16234,9 @@
       </c>
       <c r="AD151" s="10" t="n"/>
       <c r="AE151" s="10" t="n"/>
+      <c r="AF151" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -15399,6 +16263,9 @@
       <c r="K152" t="n">
         <v>1</v>
       </c>
+      <c r="R152" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="S152" s="1" t="n">
         <v>45</v>
       </c>
@@ -15416,6 +16283,9 @@
       </c>
       <c r="AD152" s="10" t="n"/>
       <c r="AE152" s="10" t="n"/>
+      <c r="AF152" t="n">
+        <v>0.3333333333333333</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -15442,6 +16312,9 @@
       <c r="K153" t="n">
         <v>0.9090909090909091</v>
       </c>
+      <c r="R153" t="n">
+        <v>0.4545454545454545</v>
+      </c>
       <c r="S153" s="1" t="n">
         <v>46</v>
       </c>
@@ -15459,6 +16332,9 @@
       </c>
       <c r="AD153" s="10" t="n"/>
       <c r="AE153" s="10" t="n"/>
+      <c r="AF153" t="n">
+        <v>0.8888888888888888</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -15485,6 +16361,9 @@
       <c r="K154" t="n">
         <v>1</v>
       </c>
+      <c r="R154" t="n">
+        <v>0.7777777777777778</v>
+      </c>
       <c r="S154" s="1" t="n">
         <v>47</v>
       </c>
@@ -15502,6 +16381,9 @@
       </c>
       <c r="AD154" s="10" t="n"/>
       <c r="AE154" s="10" t="n"/>
+      <c r="AF154" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -15528,6 +16410,9 @@
       <c r="K155" t="n">
         <v>1</v>
       </c>
+      <c r="R155" t="n">
+        <v>0.375</v>
+      </c>
       <c r="S155" s="1" t="n">
         <v>48</v>
       </c>
@@ -15545,6 +16430,9 @@
       </c>
       <c r="AD155" s="10" t="n"/>
       <c r="AE155" s="10" t="n"/>
+      <c r="AF155" t="n">
+        <v>0.375</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -15571,6 +16459,9 @@
       <c r="K156" t="n">
         <v>1</v>
       </c>
+      <c r="R156" t="n">
+        <v>0.75</v>
+      </c>
       <c r="S156" s="1" t="n">
         <v>49</v>
       </c>
@@ -15588,6 +16479,9 @@
       </c>
       <c r="AD156" s="10" t="n"/>
       <c r="AE156" s="10" t="n"/>
+      <c r="AF156" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -15614,6 +16508,9 @@
       <c r="K157" t="n">
         <v>1</v>
       </c>
+      <c r="R157" t="n">
+        <v>0.4444444444444444</v>
+      </c>
       <c r="S157" s="1" t="n">
         <v>50</v>
       </c>
@@ -15631,6 +16528,9 @@
       </c>
       <c r="AD157" s="10" t="n"/>
       <c r="AE157" s="10" t="n"/>
+      <c r="AF157" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -15657,6 +16557,9 @@
       <c r="K158" t="n">
         <v>0.9</v>
       </c>
+      <c r="R158" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="S158" s="1" t="n">
         <v>51</v>
       </c>
@@ -15674,6 +16577,9 @@
       </c>
       <c r="AD158" s="10" t="n"/>
       <c r="AE158" s="10" t="n"/>
+      <c r="AF158" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -15700,6 +16606,9 @@
       <c r="K159" t="n">
         <v>1</v>
       </c>
+      <c r="R159" t="n">
+        <v>0.375</v>
+      </c>
       <c r="S159" s="1" t="n">
         <v>52</v>
       </c>
@@ -15717,6 +16626,9 @@
       </c>
       <c r="AD159" s="10" t="n"/>
       <c r="AE159" s="10" t="n"/>
+      <c r="AF159" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -15743,6 +16655,9 @@
       <c r="K160" t="n">
         <v>1</v>
       </c>
+      <c r="R160" t="n">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="S160" s="1" t="n">
         <v>53</v>
       </c>
@@ -15760,6 +16675,9 @@
       </c>
       <c r="AD160" s="10" t="n"/>
       <c r="AE160" s="10" t="n"/>
+      <c r="AF160" t="n">
+        <v>0.3333333333333333</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -15786,6 +16704,9 @@
       <c r="K161" t="n">
         <v>1</v>
       </c>
+      <c r="R161" t="n">
+        <v>0.8333333333333334</v>
+      </c>
       <c r="S161" s="1" t="n">
         <v>54</v>
       </c>
@@ -15803,6 +16724,9 @@
       </c>
       <c r="AD161" s="10" t="n"/>
       <c r="AE161" s="10" t="n"/>
+      <c r="AF161" t="n">
+        <v>0.375</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -15829,6 +16753,9 @@
       <c r="K162" t="n">
         <v>1</v>
       </c>
+      <c r="R162" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S162" s="1" t="n">
         <v>55</v>
       </c>
@@ -15846,6 +16773,9 @@
       </c>
       <c r="AD162" s="10" t="n"/>
       <c r="AE162" s="10" t="n"/>
+      <c r="AF162" t="n">
+        <v>0.4444444444444444</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -15872,6 +16802,9 @@
       <c r="K163" t="n">
         <v>1</v>
       </c>
+      <c r="R163" t="n">
+        <v>0.4545454545454545</v>
+      </c>
       <c r="S163" s="1" t="n">
         <v>56</v>
       </c>
@@ -15889,6 +16822,9 @@
       </c>
       <c r="AD163" s="10" t="n"/>
       <c r="AE163" s="10" t="n"/>
+      <c r="AF163" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -15915,6 +16851,9 @@
       <c r="K164" t="n">
         <v>0.8888888888888888</v>
       </c>
+      <c r="R164" t="n">
+        <v>0.7</v>
+      </c>
       <c r="S164" s="1" t="n">
         <v>57</v>
       </c>
@@ -15932,6 +16871,9 @@
       </c>
       <c r="AD164" s="10" t="n"/>
       <c r="AE164" s="10" t="n"/>
+      <c r="AF164" t="n">
+        <v>0.7272727272727273</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -15958,6 +16900,9 @@
       <c r="K165" t="n">
         <v>1</v>
       </c>
+      <c r="R165" t="n">
+        <v>0.7777777777777778</v>
+      </c>
       <c r="S165" s="1" t="n">
         <v>58</v>
       </c>
@@ -15975,6 +16920,9 @@
       </c>
       <c r="AD165" s="10" t="n"/>
       <c r="AE165" s="10" t="n"/>
+      <c r="AF165" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -16001,6 +16949,9 @@
       <c r="K166" t="n">
         <v>1</v>
       </c>
+      <c r="R166" t="n">
+        <v>0.7777777777777778</v>
+      </c>
       <c r="S166" s="1" t="n">
         <v>59</v>
       </c>
@@ -16018,6 +16969,9 @@
       </c>
       <c r="AD166" s="10" t="n"/>
       <c r="AE166" s="10" t="n"/>
+      <c r="AF166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -16044,6 +16998,9 @@
       <c r="K167" t="n">
         <v>1</v>
       </c>
+      <c r="R167" t="n">
+        <v>0.5555555555555556</v>
+      </c>
       <c r="S167" s="1" t="n">
         <v>60</v>
       </c>
@@ -16061,6 +17018,9 @@
       </c>
       <c r="AD167" s="10" t="n"/>
       <c r="AE167" s="10" t="n"/>
+      <c r="AF167" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -16087,6 +17047,9 @@
       <c r="K168" t="n">
         <v>1</v>
       </c>
+      <c r="R168" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S168" s="1" t="n">
         <v>61</v>
       </c>
@@ -16104,6 +17067,9 @@
       </c>
       <c r="AD168" s="10" t="n"/>
       <c r="AE168" s="10" t="n"/>
+      <c r="AF168" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -16130,6 +17096,9 @@
       <c r="K169" t="n">
         <v>1</v>
       </c>
+      <c r="R169" t="n">
+        <v>0.25</v>
+      </c>
       <c r="S169" s="1" t="n">
         <v>62</v>
       </c>
@@ -16147,6 +17116,9 @@
       </c>
       <c r="AD169" s="10" t="n"/>
       <c r="AE169" s="10" t="n"/>
+      <c r="AF169" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -16173,6 +17145,9 @@
       <c r="K170" t="n">
         <v>1</v>
       </c>
+      <c r="R170" t="n">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="S170" s="1" t="n">
         <v>63</v>
       </c>
@@ -16190,6 +17165,9 @@
       </c>
       <c r="AD170" s="10" t="n"/>
       <c r="AE170" s="10" t="n"/>
+      <c r="AF170" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -16216,6 +17194,9 @@
       <c r="K171" t="n">
         <v>1</v>
       </c>
+      <c r="R171" t="n">
+        <v>0.625</v>
+      </c>
       <c r="S171" s="1" t="n">
         <v>64</v>
       </c>
@@ -16233,6 +17214,9 @@
       </c>
       <c r="AD171" s="10" t="n"/>
       <c r="AE171" s="10" t="n"/>
+      <c r="AF171" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -16259,6 +17243,9 @@
       <c r="K172" t="n">
         <v>1</v>
       </c>
+      <c r="R172" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S172" s="1" t="n">
         <v>65</v>
       </c>
@@ -16276,6 +17263,9 @@
       </c>
       <c r="AD172" s="10" t="n"/>
       <c r="AE172" s="10" t="n"/>
+      <c r="AF172" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -16302,6 +17292,9 @@
       <c r="K173" t="n">
         <v>0.875</v>
       </c>
+      <c r="R173" t="n">
+        <v>0.8333333333333334</v>
+      </c>
       <c r="S173" s="1" t="n">
         <v>66</v>
       </c>
@@ -16319,6 +17312,9 @@
       </c>
       <c r="AD173" s="10" t="n"/>
       <c r="AE173" s="10" t="n"/>
+      <c r="AF173" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -16345,6 +17341,9 @@
       <c r="K174" t="n">
         <v>1</v>
       </c>
+      <c r="R174" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="S174" s="1" t="n">
         <v>67</v>
       </c>
@@ -16362,6 +17361,9 @@
       </c>
       <c r="AD174" s="10" t="n"/>
       <c r="AE174" s="10" t="n"/>
+      <c r="AF174" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -16388,6 +17390,9 @@
       <c r="K175" t="n">
         <v>1</v>
       </c>
+      <c r="R175" t="n">
+        <v>0.6</v>
+      </c>
       <c r="S175" s="1" t="n">
         <v>68</v>
       </c>
@@ -16405,6 +17410,9 @@
       </c>
       <c r="AD175" s="10" t="n"/>
       <c r="AE175" s="10" t="n"/>
+      <c r="AF175" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -16431,6 +17439,9 @@
       <c r="K176" t="n">
         <v>1</v>
       </c>
+      <c r="R176" t="n">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="S176" s="1" t="n">
         <v>69</v>
       </c>
@@ -16448,6 +17459,9 @@
       </c>
       <c r="AD176" s="10" t="n"/>
       <c r="AE176" s="10" t="n"/>
+      <c r="AF176" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -16474,6 +17488,9 @@
       <c r="K177" t="n">
         <v>0.8571428571428571</v>
       </c>
+      <c r="R177" t="n">
+        <v>0.375</v>
+      </c>
       <c r="S177" s="1" t="n">
         <v>70</v>
       </c>
@@ -16491,6 +17508,9 @@
       </c>
       <c r="AD177" s="10" t="n"/>
       <c r="AE177" s="10" t="n"/>
+      <c r="AF177" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -16517,6 +17537,9 @@
       <c r="K178" t="n">
         <v>1</v>
       </c>
+      <c r="R178" t="n">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="S178" s="1" t="n">
         <v>71</v>
       </c>
@@ -16534,6 +17557,9 @@
       </c>
       <c r="AD178" s="10" t="n"/>
       <c r="AE178" s="10" t="n"/>
+      <c r="AF178" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -16560,6 +17586,9 @@
       <c r="K179" t="n">
         <v>1</v>
       </c>
+      <c r="R179" t="n">
+        <v>0.625</v>
+      </c>
       <c r="S179" s="1" t="n">
         <v>72</v>
       </c>
@@ -16577,6 +17606,9 @@
       </c>
       <c r="AD179" s="10" t="n"/>
       <c r="AE179" s="10" t="n"/>
+      <c r="AF179" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -16603,6 +17635,9 @@
       <c r="K180" t="n">
         <v>0.8333333333333334</v>
       </c>
+      <c r="R180" t="n">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="S180" s="1" t="n">
         <v>73</v>
       </c>
@@ -16620,6 +17655,9 @@
       </c>
       <c r="AD180" s="10" t="n"/>
       <c r="AE180" s="10" t="n"/>
+      <c r="AF180" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -16646,6 +17684,9 @@
       <c r="K181" t="n">
         <v>1</v>
       </c>
+      <c r="R181" t="n">
+        <v>0.5555555555555556</v>
+      </c>
       <c r="S181" s="1" t="n">
         <v>74</v>
       </c>
@@ -16663,6 +17704,9 @@
       </c>
       <c r="AD181" s="10" t="n"/>
       <c r="AE181" s="10" t="n"/>
+      <c r="AF181" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -16689,6 +17733,9 @@
       <c r="K182" t="n">
         <v>0.8</v>
       </c>
+      <c r="R182" t="n">
+        <v>0.625</v>
+      </c>
       <c r="S182" s="1" t="n">
         <v>75</v>
       </c>
@@ -16706,6 +17753,9 @@
       </c>
       <c r="AD182" s="10" t="n"/>
       <c r="AE182" s="10" t="n"/>
+      <c r="AF182" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -16732,6 +17782,9 @@
       <c r="K183" t="n">
         <v>1</v>
       </c>
+      <c r="R183" t="n">
+        <v>0.4</v>
+      </c>
       <c r="S183" s="1" t="n">
         <v>76</v>
       </c>
@@ -16749,6 +17802,9 @@
       </c>
       <c r="AD183" s="10" t="n"/>
       <c r="AE183" s="10" t="n"/>
+      <c r="AF183" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -16775,6 +17831,9 @@
       <c r="K184" t="n">
         <v>0.75</v>
       </c>
+      <c r="R184" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="S184" s="1" t="n">
         <v>77</v>
       </c>
@@ -16792,6 +17851,9 @@
       </c>
       <c r="AD184" s="10" t="n"/>
       <c r="AE184" s="10" t="n"/>
+      <c r="AF184" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -16818,6 +17880,9 @@
       <c r="K185" t="n">
         <v>1</v>
       </c>
+      <c r="R185" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S185" s="1" t="n">
         <v>78</v>
       </c>
@@ -16835,6 +17900,9 @@
       </c>
       <c r="AD185" s="10" t="n"/>
       <c r="AE185" s="10" t="n"/>
+      <c r="AF185" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -16861,6 +17929,9 @@
       <c r="K186" t="n">
         <v>1</v>
       </c>
+      <c r="R186" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="S186" s="1" t="n">
         <v>79</v>
       </c>
@@ -16878,6 +17949,9 @@
       </c>
       <c r="AD186" s="10" t="n"/>
       <c r="AE186" s="10" t="n"/>
+      <c r="AF186" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -16904,6 +17978,9 @@
       <c r="K187" t="n">
         <v>1</v>
       </c>
+      <c r="R187" t="n">
+        <v>0.4</v>
+      </c>
       <c r="S187" s="1" t="n">
         <v>80</v>
       </c>
@@ -16921,6 +17998,9 @@
       </c>
       <c r="AD187" s="10" t="n"/>
       <c r="AE187" s="10" t="n"/>
+      <c r="AF187" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -16947,6 +18027,9 @@
       <c r="K188" t="n">
         <v>1</v>
       </c>
+      <c r="R188" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S188" s="1" t="n">
         <v>81</v>
       </c>
@@ -16964,6 +18047,9 @@
       </c>
       <c r="AD188" s="10" t="n"/>
       <c r="AE188" s="10" t="n"/>
+      <c r="AF188" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
@@ -16990,6 +18076,9 @@
       <c r="K189" t="n">
         <v>1</v>
       </c>
+      <c r="R189" t="n">
+        <v>0.4444444444444444</v>
+      </c>
       <c r="S189" s="1" t="n">
         <v>82</v>
       </c>
@@ -17007,6 +18096,9 @@
       </c>
       <c r="AD189" s="10" t="n"/>
       <c r="AE189" s="10" t="n"/>
+      <c r="AF189" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -17033,6 +18125,9 @@
       <c r="K190" t="n">
         <v>1</v>
       </c>
+      <c r="R190" t="n">
+        <v>0.375</v>
+      </c>
       <c r="S190" s="1" t="n">
         <v>83</v>
       </c>
@@ -17050,6 +18145,9 @@
       </c>
       <c r="AD190" s="10" t="n"/>
       <c r="AE190" s="10" t="n"/>
+      <c r="AF190" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -17076,6 +18174,9 @@
       <c r="K191" t="n">
         <v>1</v>
       </c>
+      <c r="R191" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S191" s="1" t="n">
         <v>84</v>
       </c>
@@ -17093,6 +18194,9 @@
       </c>
       <c r="AD191" s="10" t="n"/>
       <c r="AE191" s="10" t="n"/>
+      <c r="AF191" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -17119,6 +18223,9 @@
       <c r="K192" t="n">
         <v>1</v>
       </c>
+      <c r="R192" t="n">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="S192" s="1" t="n">
         <v>85</v>
       </c>
@@ -17136,6 +18243,9 @@
       </c>
       <c r="AD192" s="10" t="n"/>
       <c r="AE192" s="10" t="n"/>
+      <c r="AF192" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -17162,6 +18272,9 @@
       <c r="K193" t="n">
         <v>1</v>
       </c>
+      <c r="R193" t="n">
+        <v>0.7777777777777778</v>
+      </c>
       <c r="S193" s="1" t="n">
         <v>86</v>
       </c>
@@ -17179,6 +18292,9 @@
       </c>
       <c r="AD193" s="10" t="n"/>
       <c r="AE193" s="10" t="n"/>
+      <c r="AF193" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -17205,6 +18321,9 @@
       <c r="K194" t="n">
         <v>1</v>
       </c>
+      <c r="R194" t="n">
+        <v>0.6</v>
+      </c>
       <c r="S194" s="1" t="n">
         <v>87</v>
       </c>
@@ -17222,6 +18341,9 @@
       </c>
       <c r="AD194" s="10" t="n"/>
       <c r="AE194" s="10" t="n"/>
+      <c r="AF194" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -17248,6 +18370,9 @@
       <c r="K195" t="n">
         <v>1</v>
       </c>
+      <c r="R195" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="S195" s="1" t="n">
         <v>88</v>
       </c>
@@ -17265,6 +18390,9 @@
       </c>
       <c r="AD195" s="10" t="n"/>
       <c r="AE195" s="10" t="n"/>
+      <c r="AF195" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -17291,6 +18419,9 @@
       <c r="K196" t="n">
         <v>1</v>
       </c>
+      <c r="R196" t="n">
+        <v>0.75</v>
+      </c>
       <c r="S196" s="1" t="n">
         <v>89</v>
       </c>
@@ -17308,6 +18439,9 @@
       </c>
       <c r="AD196" s="10" t="n"/>
       <c r="AE196" s="10" t="n"/>
+      <c r="AF196" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -17334,6 +18468,9 @@
       <c r="K197" t="n">
         <v>1</v>
       </c>
+      <c r="R197" t="n">
+        <v>0.4444444444444444</v>
+      </c>
       <c r="S197" s="1" t="n">
         <v>90</v>
       </c>
@@ -17351,6 +18488,9 @@
       </c>
       <c r="AD197" s="10" t="n"/>
       <c r="AE197" s="10" t="n"/>
+      <c r="AF197" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
@@ -17377,6 +18517,9 @@
       <c r="K198" t="n">
         <v>1</v>
       </c>
+      <c r="R198" t="n">
+        <v>0.6</v>
+      </c>
       <c r="S198" s="1" t="n">
         <v>91</v>
       </c>
@@ -17394,6 +18537,9 @@
       </c>
       <c r="AD198" s="10" t="n"/>
       <c r="AE198" s="10" t="n"/>
+      <c r="AF198" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
@@ -17420,6 +18566,9 @@
       <c r="K199" t="n">
         <v>1</v>
       </c>
+      <c r="R199" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S199" s="1" t="n">
         <v>92</v>
       </c>
@@ -17437,6 +18586,9 @@
       </c>
       <c r="AD199" s="10" t="n"/>
       <c r="AE199" s="10" t="n"/>
+      <c r="AF199" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
@@ -17463,6 +18615,9 @@
       <c r="K200" t="n">
         <v>1</v>
       </c>
+      <c r="R200" t="n">
+        <v>0.625</v>
+      </c>
       <c r="S200" s="1" t="n">
         <v>93</v>
       </c>
@@ -17480,6 +18635,9 @@
       </c>
       <c r="AD200" s="10" t="n"/>
       <c r="AE200" s="10" t="n"/>
+      <c r="AF200" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -17506,6 +18664,9 @@
       <c r="K201" t="n">
         <v>1</v>
       </c>
+      <c r="R201" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="S201" s="1" t="n">
         <v>94</v>
       </c>
@@ -17523,6 +18684,9 @@
       </c>
       <c r="AD201" s="10" t="n"/>
       <c r="AE201" s="10" t="n"/>
+      <c r="AF201" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
@@ -17546,6 +18710,9 @@
       <c r="K202" t="n">
         <v>1</v>
       </c>
+      <c r="R202" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S202" s="1" t="n">
         <v>95</v>
       </c>
@@ -17563,6 +18730,9 @@
       </c>
       <c r="AD202" s="10" t="n"/>
       <c r="AE202" s="10" t="n"/>
+      <c r="AF202" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
@@ -17586,6 +18756,9 @@
       <c r="K203" t="n">
         <v>1</v>
       </c>
+      <c r="R203" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="S203" s="1" t="n">
         <v>96</v>
       </c>
@@ -17603,6 +18776,9 @@
       </c>
       <c r="AD203" s="10" t="n"/>
       <c r="AE203" s="10" t="n"/>
+      <c r="AF203" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -17626,6 +18802,9 @@
       <c r="K204" t="n">
         <v>1</v>
       </c>
+      <c r="R204" t="n">
+        <v>0.6</v>
+      </c>
       <c r="S204" s="1" t="n">
         <v>97</v>
       </c>
@@ -17643,6 +18822,9 @@
       </c>
       <c r="AD204" s="10" t="n"/>
       <c r="AE204" s="10" t="n"/>
+      <c r="AF204" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
@@ -17666,6 +18848,9 @@
       <c r="K205" t="n">
         <v>1</v>
       </c>
+      <c r="R205" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S205" s="1" t="n">
         <v>98</v>
       </c>
@@ -17683,6 +18868,9 @@
       </c>
       <c r="AD205" s="10" t="n"/>
       <c r="AE205" s="10" t="n"/>
+      <c r="AF205" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -17706,6 +18894,9 @@
       <c r="K206" t="n">
         <v>1</v>
       </c>
+      <c r="R206" t="n">
+        <v>0.625</v>
+      </c>
       <c r="S206" s="1" t="n">
         <v>99</v>
       </c>
@@ -17723,6 +18914,9 @@
       </c>
       <c r="AD206" s="10" t="n"/>
       <c r="AE206" s="10" t="n"/>
+      <c r="AF206" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
@@ -17746,6 +18940,9 @@
       <c r="K207" t="n">
         <v>1</v>
       </c>
+      <c r="R207" t="n">
+        <v>0.4</v>
+      </c>
       <c r="S207" s="1" t="n">
         <v>100</v>
       </c>
@@ -17763,6 +18960,9 @@
       </c>
       <c r="AD207" s="10" t="n"/>
       <c r="AE207" s="10" t="n"/>
+      <c r="AF207" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="208">
       <c r="AD208" s="10" t="n"/>
@@ -17834,6 +19034,9 @@
       <c r="K212" t="n">
         <v>0.9869375</v>
       </c>
+      <c r="R212" t="n">
+        <v>0.55038</v>
+      </c>
       <c r="S212" s="1" t="n">
         <v>1</v>
       </c>
@@ -17851,6 +19054,9 @@
       </c>
       <c r="AD212" s="10" t="n"/>
       <c r="AE212" s="10" t="n"/>
+      <c r="AF212" t="n">
+        <v>0.97868</v>
+      </c>
       <c r="AG212" t="n">
         <v>0.9954000000000001</v>
       </c>
@@ -17889,6 +19095,9 @@
       <c r="K213" t="n">
         <v>0.9843500000000001</v>
       </c>
+      <c r="R213" t="n">
+        <v>0.56892</v>
+      </c>
       <c r="S213" s="1" t="n">
         <v>2</v>
       </c>
@@ -17906,6 +19115,9 @@
       </c>
       <c r="AD213" s="10" t="n"/>
       <c r="AE213" s="10" t="n"/>
+      <c r="AF213" t="n">
+        <v>0.9852399999999999</v>
+      </c>
       <c r="AG213" t="n">
         <v>0.68028</v>
       </c>
@@ -17944,6 +19156,9 @@
       <c r="K214" t="n">
         <v>0.98705</v>
       </c>
+      <c r="R214" t="n">
+        <v>0.6796142857142857</v>
+      </c>
       <c r="S214" s="1" t="n">
         <v>3</v>
       </c>
@@ -17961,6 +19176,9 @@
       </c>
       <c r="AD214" s="10" t="n"/>
       <c r="AE214" s="10" t="n"/>
+      <c r="AF214" t="n">
+        <v>0.98026</v>
+      </c>
       <c r="AG214" t="n">
         <v>0.5468000000000001</v>
       </c>
@@ -17999,6 +19217,9 @@
       <c r="K215" t="n">
         <v>0.9766625</v>
       </c>
+      <c r="R215" t="n">
+        <v>0.6928428571428571</v>
+      </c>
       <c r="S215" s="1" t="n">
         <v>4</v>
       </c>
@@ -18016,6 +19237,9 @@
       </c>
       <c r="AD215" s="10" t="n"/>
       <c r="AE215" s="10" t="n"/>
+      <c r="AF215" t="n">
+        <v>0.9748250000000001</v>
+      </c>
       <c r="AG215" t="n">
         <v>0.6868833333333333</v>
       </c>
@@ -18054,6 +19278,9 @@
       <c r="K216" t="n">
         <v>0.9783624999999999</v>
       </c>
+      <c r="R216" t="n">
+        <v>0.47062</v>
+      </c>
       <c r="S216" s="1" t="n">
         <v>5</v>
       </c>
@@ -18071,6 +19298,9 @@
       </c>
       <c r="AD216" s="10" t="n"/>
       <c r="AE216" s="10" t="n"/>
+      <c r="AF216" t="n">
+        <v>0.9778000000000001</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
@@ -18103,6 +19333,9 @@
       <c r="K217" t="n">
         <v>0.976425</v>
       </c>
+      <c r="R217" t="n">
+        <v>0.6934</v>
+      </c>
       <c r="S217" s="1" t="n">
         <v>6</v>
       </c>
@@ -18120,6 +19353,9 @@
       </c>
       <c r="AD217" s="10" t="n"/>
       <c r="AE217" s="10" t="n"/>
+      <c r="AF217" t="n">
+        <v>0.9835142857142857</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
@@ -18152,6 +19388,9 @@
       <c r="K218" t="n">
         <v>0.985675</v>
       </c>
+      <c r="R218" t="n">
+        <v>0.8452</v>
+      </c>
       <c r="S218" s="1" t="n">
         <v>7</v>
       </c>
@@ -18169,6 +19408,9 @@
       </c>
       <c r="AD218" s="10" t="n"/>
       <c r="AE218" s="10" t="n"/>
+      <c r="AF218" t="n">
+        <v>0.982225</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
@@ -18203,6 +19445,9 @@
       <c r="K219" t="n">
         <v>0.9710624999999999</v>
       </c>
+      <c r="R219" t="n">
+        <v>0.8135500000000001</v>
+      </c>
       <c r="S219" s="1" t="n">
         <v>8</v>
       </c>
@@ -18220,6 +19465,9 @@
       </c>
       <c r="AD219" s="10" t="n"/>
       <c r="AE219" s="10" t="n"/>
+      <c r="AF219" t="n">
+        <v>0.9823666666666667</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
@@ -18254,6 +19502,9 @@
       <c r="K220" t="n">
         <v>0.9728249999999999</v>
       </c>
+      <c r="R220" t="n">
+        <v>0.7150666666666666</v>
+      </c>
       <c r="S220" s="1" t="n">
         <v>9</v>
       </c>
@@ -18271,6 +19522,9 @@
       </c>
       <c r="AD220" s="10" t="n"/>
       <c r="AE220" s="10" t="n"/>
+      <c r="AF220" t="n">
+        <v>0.9786</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -18303,6 +19557,9 @@
       <c r="K221" t="n">
         <v>0.9808875</v>
       </c>
+      <c r="R221" t="n">
+        <v>0.9009714285714285</v>
+      </c>
       <c r="S221" s="1" t="n">
         <v>10</v>
       </c>
@@ -18320,6 +19577,9 @@
       </c>
       <c r="AD221" s="10" t="n"/>
       <c r="AE221" s="10" t="n"/>
+      <c r="AF221" t="n">
+        <v>0.9709714285714286</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
@@ -18346,6 +19606,9 @@
       <c r="K222" t="n">
         <v>0.9815125</v>
       </c>
+      <c r="R222" t="n">
+        <v>0.8428</v>
+      </c>
       <c r="S222" s="1" t="n">
         <v>11</v>
       </c>
@@ -18363,6 +19626,9 @@
       </c>
       <c r="AD222" s="10" t="n"/>
       <c r="AE222" s="10" t="n"/>
+      <c r="AF222" t="n">
+        <v>0.9792833333333334</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
@@ -18389,6 +19655,9 @@
       <c r="K223" t="n">
         <v>0.9807125000000001</v>
       </c>
+      <c r="R223" t="n">
+        <v>0.8587833333333333</v>
+      </c>
       <c r="S223" s="1" t="n">
         <v>12</v>
       </c>
@@ -18406,6 +19675,9 @@
       </c>
       <c r="AD223" s="10" t="n"/>
       <c r="AE223" s="10" t="n"/>
+      <c r="AF223" t="n">
+        <v>0.9780624999999999</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
@@ -18432,6 +19704,9 @@
       <c r="K224" t="n">
         <v>0.9760875</v>
       </c>
+      <c r="R224" t="n">
+        <v>0.8195833333333334</v>
+      </c>
       <c r="S224" s="1" t="n">
         <v>13</v>
       </c>
@@ -18449,6 +19724,9 @@
       </c>
       <c r="AD224" s="10" t="n"/>
       <c r="AE224" s="10" t="n"/>
+      <c r="AF224" t="n">
+        <v>0.9747666666666667</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
@@ -18475,6 +19753,9 @@
       <c r="K225" t="n">
         <v>0.9808249999999999</v>
       </c>
+      <c r="R225" t="n">
+        <v>0.8251166666666666</v>
+      </c>
       <c r="S225" s="1" t="n">
         <v>14</v>
       </c>
@@ -18492,6 +19773,9 @@
       </c>
       <c r="AD225" s="10" t="n"/>
       <c r="AE225" s="10" t="n"/>
+      <c r="AF225" t="n">
+        <v>0.972942857142857</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
@@ -18518,6 +19802,9 @@
       <c r="K226" t="n">
         <v>0.9787250000000001</v>
       </c>
+      <c r="R226" t="n">
+        <v>0.7712800000000001</v>
+      </c>
       <c r="S226" s="1" t="n">
         <v>15</v>
       </c>
@@ -18535,6 +19822,9 @@
       </c>
       <c r="AD226" s="10" t="n"/>
       <c r="AE226" s="10" t="n"/>
+      <c r="AF226" t="n">
+        <v>0.9710999999999999</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
@@ -18561,6 +19851,9 @@
       <c r="K227" t="n">
         <v>0.9793625000000001</v>
       </c>
+      <c r="R227" t="n">
+        <v>0.8247749999999999</v>
+      </c>
       <c r="S227" s="1" t="n">
         <v>16</v>
       </c>
@@ -18578,6 +19871,9 @@
       </c>
       <c r="AD227" s="10" t="n"/>
       <c r="AE227" s="10" t="n"/>
+      <c r="AF227" t="n">
+        <v>0.9727125</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
@@ -18604,6 +19900,9 @@
       <c r="K228" t="n">
         <v>0.9796625</v>
       </c>
+      <c r="R228" t="n">
+        <v>0.91045</v>
+      </c>
       <c r="S228" s="1" t="n">
         <v>17</v>
       </c>
@@ -18621,6 +19920,9 @@
       </c>
       <c r="AD228" s="10" t="n"/>
       <c r="AE228" s="10" t="n"/>
+      <c r="AF228" t="n">
+        <v>0.9767666666666668</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
@@ -18647,6 +19949,9 @@
       <c r="K229" t="n">
         <v>0.978975</v>
       </c>
+      <c r="R229" t="n">
+        <v>0.8695499999999999</v>
+      </c>
       <c r="S229" s="1" t="n">
         <v>18</v>
       </c>
@@ -18664,6 +19969,9 @@
       </c>
       <c r="AD229" s="10" t="n"/>
       <c r="AE229" s="10" t="n"/>
+      <c r="AF229" t="n">
+        <v>0.9721</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
@@ -18690,6 +19998,9 @@
       <c r="K230" t="n">
         <v>0.983775</v>
       </c>
+      <c r="R230" t="n">
+        <v>0.9148285714285713</v>
+      </c>
       <c r="S230" s="1" t="n">
         <v>19</v>
       </c>
@@ -18707,6 +20018,9 @@
       </c>
       <c r="AD230" s="10" t="n"/>
       <c r="AE230" s="10" t="n"/>
+      <c r="AF230" t="n">
+        <v>0.9696750000000001</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
@@ -18733,6 +20047,9 @@
       <c r="K231" t="n">
         <v>0.9754125</v>
       </c>
+      <c r="R231" t="n">
+        <v>0.64885</v>
+      </c>
       <c r="S231" s="1" t="n">
         <v>20</v>
       </c>
@@ -18750,6 +20067,9 @@
       </c>
       <c r="AD231" s="10" t="n"/>
       <c r="AE231" s="10" t="n"/>
+      <c r="AF231" t="n">
+        <v>0.9700857142857143</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
@@ -18776,6 +20096,9 @@
       <c r="K232" t="n">
         <v>0.9789625000000001</v>
       </c>
+      <c r="R232" t="n">
+        <v>0.7614000000000001</v>
+      </c>
       <c r="S232" s="1" t="n">
         <v>21</v>
       </c>
@@ -18793,6 +20116,9 @@
       </c>
       <c r="AD232" s="10" t="n"/>
       <c r="AE232" s="10" t="n"/>
+      <c r="AF232" t="n">
+        <v>0.9662666666666667</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
@@ -18819,6 +20145,9 @@
       <c r="K233" t="n">
         <v>0.980475</v>
       </c>
+      <c r="R233" t="n">
+        <v>0.9399714285714287</v>
+      </c>
       <c r="S233" s="1" t="n">
         <v>22</v>
       </c>
@@ -18836,6 +20165,9 @@
       </c>
       <c r="AD233" s="10" t="n"/>
       <c r="AE233" s="10" t="n"/>
+      <c r="AF233" t="n">
+        <v>0.97345</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
@@ -18862,6 +20194,9 @@
       <c r="K234" t="n">
         <v>0.9764250000000001</v>
       </c>
+      <c r="R234" t="n">
+        <v>0.9480166666666666</v>
+      </c>
       <c r="S234" s="1" t="n">
         <v>23</v>
       </c>
@@ -18879,6 +20214,9 @@
       </c>
       <c r="AD234" s="10" t="n"/>
       <c r="AE234" s="10" t="n"/>
+      <c r="AF234" t="n">
+        <v>0.9702111111111112</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
@@ -18905,6 +20243,9 @@
       <c r="K235" t="n">
         <v>0.9825</v>
       </c>
+      <c r="R235" t="n">
+        <v>0.8896999999999999</v>
+      </c>
       <c r="S235" s="1" t="n">
         <v>24</v>
       </c>
@@ -18922,6 +20263,9 @@
       </c>
       <c r="AD235" s="10" t="n"/>
       <c r="AE235" s="10" t="n"/>
+      <c r="AF235" t="n">
+        <v>0.97405</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
@@ -18948,6 +20292,9 @@
       <c r="K236" t="n">
         <v>0.9820875000000001</v>
       </c>
+      <c r="R236" t="n">
+        <v>0.8600000000000001</v>
+      </c>
       <c r="S236" s="1" t="n">
         <v>25</v>
       </c>
@@ -18965,6 +20312,9 @@
       </c>
       <c r="AD236" s="10" t="n"/>
       <c r="AE236" s="10" t="n"/>
+      <c r="AF236" t="n">
+        <v>0.9692</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
@@ -18991,6 +20341,9 @@
       <c r="K237" t="n">
         <v>0.9754624999999999</v>
       </c>
+      <c r="R237" t="n">
+        <v>0.9575833333333333</v>
+      </c>
       <c r="S237" s="1" t="n">
         <v>26</v>
       </c>
@@ -19008,6 +20361,9 @@
       </c>
       <c r="AD237" s="10" t="n"/>
       <c r="AE237" s="10" t="n"/>
+      <c r="AF237" t="n">
+        <v>0.9724166666666667</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
@@ -19034,6 +20390,9 @@
       <c r="K238" t="n">
         <v>0.9835</v>
       </c>
+      <c r="R238" t="n">
+        <v>0.9113833333333333</v>
+      </c>
       <c r="S238" s="1" t="n">
         <v>27</v>
       </c>
@@ -19051,6 +20410,9 @@
       </c>
       <c r="AD238" s="10" t="n"/>
       <c r="AE238" s="10" t="n"/>
+      <c r="AF238" t="n">
+        <v>0.9685833333333335</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
@@ -19077,6 +20439,9 @@
       <c r="K239" t="n">
         <v>0.9785375000000001</v>
       </c>
+      <c r="R239" t="n">
+        <v>0.8735333333333332</v>
+      </c>
       <c r="S239" s="1" t="n">
         <v>28</v>
       </c>
@@ -19094,6 +20459,9 @@
       </c>
       <c r="AD239" s="10" t="n"/>
       <c r="AE239" s="10" t="n"/>
+      <c r="AF239" t="n">
+        <v>0.96692</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
@@ -19120,6 +20488,9 @@
       <c r="K240" t="n">
         <v>0.9798375000000001</v>
       </c>
+      <c r="R240" t="n">
+        <v>0.8441166666666665</v>
+      </c>
       <c r="S240" s="1" t="n">
         <v>29</v>
       </c>
@@ -19137,6 +20508,9 @@
       </c>
       <c r="AD240" s="10" t="n"/>
       <c r="AE240" s="10" t="n"/>
+      <c r="AF240" t="n">
+        <v>0.9688444444444444</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
@@ -19163,6 +20537,9 @@
       <c r="K241" t="n">
         <v>0.982025</v>
       </c>
+      <c r="R241" t="n">
+        <v>0.8965222222222222</v>
+      </c>
       <c r="S241" s="1" t="n">
         <v>30</v>
       </c>
@@ -19180,6 +20557,9 @@
       </c>
       <c r="AD241" s="10" t="n"/>
       <c r="AE241" s="10" t="n"/>
+      <c r="AF241" t="n">
+        <v>0.9707666666666666</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
@@ -19206,6 +20586,9 @@
       <c r="K242" t="n">
         <v>0.9791874999999999</v>
       </c>
+      <c r="R242" t="n">
+        <v>0.8689777777777778</v>
+      </c>
       <c r="S242" s="1" t="n">
         <v>31</v>
       </c>
@@ -19223,6 +20606,9 @@
       </c>
       <c r="AD242" s="10" t="n"/>
       <c r="AE242" s="10" t="n"/>
+      <c r="AF242" t="n">
+        <v>0.97265</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
@@ -19249,6 +20635,9 @@
       <c r="K243" t="n">
         <v>0.9765625</v>
       </c>
+      <c r="R243" t="n">
+        <v>0.7990333333333334</v>
+      </c>
       <c r="S243" s="1" t="n">
         <v>32</v>
       </c>
@@ -19266,6 +20655,9 @@
       </c>
       <c r="AD243" s="10" t="n"/>
       <c r="AE243" s="10" t="n"/>
+      <c r="AF243" t="n">
+        <v>0.9742166666666666</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
@@ -19292,6 +20684,9 @@
       <c r="K244" t="n">
         <v>0.981325</v>
       </c>
+      <c r="R244" t="n">
+        <v>0.9228000000000002</v>
+      </c>
       <c r="S244" s="1" t="n">
         <v>33</v>
       </c>
@@ -19309,6 +20704,9 @@
       </c>
       <c r="AD244" s="10" t="n"/>
       <c r="AE244" s="10" t="n"/>
+      <c r="AF244" t="n">
+        <v>0.9711857142857142</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
@@ -19335,6 +20733,9 @@
       <c r="K245" t="n">
         <v>0.983525</v>
       </c>
+      <c r="R245" t="n">
+        <v>0.9093285714285715</v>
+      </c>
       <c r="S245" s="1" t="n">
         <v>34</v>
       </c>
@@ -19352,6 +20753,9 @@
       </c>
       <c r="AD245" s="10" t="n"/>
       <c r="AE245" s="10" t="n"/>
+      <c r="AF245" t="n">
+        <v>0.96996</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
@@ -19378,6 +20782,9 @@
       <c r="K246" t="n">
         <v>0.976</v>
       </c>
+      <c r="R246" t="n">
+        <v>0.8874555555555557</v>
+      </c>
       <c r="S246" s="1" t="n">
         <v>35</v>
       </c>
@@ -19395,6 +20802,9 @@
       </c>
       <c r="AD246" s="10" t="n"/>
       <c r="AE246" s="10" t="n"/>
+      <c r="AF246" t="n">
+        <v>0.9704833333333335</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
@@ -19421,6 +20831,9 @@
       <c r="K247" t="n">
         <v>0.9818625</v>
       </c>
+      <c r="R247" t="n">
+        <v>0.8998363636363635</v>
+      </c>
       <c r="S247" s="1" t="n">
         <v>36</v>
       </c>
@@ -19438,6 +20851,9 @@
       </c>
       <c r="AD247" s="10" t="n"/>
       <c r="AE247" s="10" t="n"/>
+      <c r="AF247" t="n">
+        <v>0.9707833333333333</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
@@ -19464,6 +20880,9 @@
       <c r="K248" t="n">
         <v>0.9820625000000001</v>
       </c>
+      <c r="R248" t="n">
+        <v>0.9090300000000001</v>
+      </c>
       <c r="S248" s="1" t="n">
         <v>37</v>
       </c>
@@ -19481,6 +20900,9 @@
       </c>
       <c r="AD248" s="10" t="n"/>
       <c r="AE248" s="10" t="n"/>
+      <c r="AF248" t="n">
+        <v>0.9714</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
@@ -19507,6 +20929,9 @@
       <c r="K249" t="n">
         <v>0.9805625</v>
       </c>
+      <c r="R249" t="n">
+        <v>0.8992</v>
+      </c>
       <c r="S249" s="1" t="n">
         <v>38</v>
       </c>
@@ -19524,6 +20949,9 @@
       </c>
       <c r="AD249" s="10" t="n"/>
       <c r="AE249" s="10" t="n"/>
+      <c r="AF249" t="n">
+        <v>0.9726749999999998</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
@@ -19550,6 +20978,9 @@
       <c r="K250" t="n">
         <v>0.9807625</v>
       </c>
+      <c r="R250" t="n">
+        <v>0.8810428571428571</v>
+      </c>
       <c r="S250" s="1" t="n">
         <v>39</v>
       </c>
@@ -19567,6 +20998,9 @@
       </c>
       <c r="AD250" s="10" t="n"/>
       <c r="AE250" s="10" t="n"/>
+      <c r="AF250" t="n">
+        <v>0.9703249999999999</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
@@ -19593,6 +21027,9 @@
       <c r="K251" t="n">
         <v>0.9798499999999999</v>
       </c>
+      <c r="R251" t="n">
+        <v>0.9153249999999999</v>
+      </c>
       <c r="S251" s="1" t="n">
         <v>40</v>
       </c>
@@ -19610,6 +21047,9 @@
       </c>
       <c r="AD251" s="10" t="n"/>
       <c r="AE251" s="10" t="n"/>
+      <c r="AF251" t="n">
+        <v>0.9706625</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
@@ -19636,6 +21076,9 @@
       <c r="K252" t="n">
         <v>0.9819000000000001</v>
       </c>
+      <c r="R252" t="n">
+        <v>0.9631714285714285</v>
+      </c>
       <c r="S252" s="1" t="n">
         <v>41</v>
       </c>
@@ -19653,6 +21096,9 @@
       </c>
       <c r="AD252" s="10" t="n"/>
       <c r="AE252" s="10" t="n"/>
+      <c r="AF252" t="n">
+        <v>0.9692500000000001</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
@@ -19679,6 +21125,9 @@
       <c r="K253" t="n">
         <v>0.9788875</v>
       </c>
+      <c r="R253" t="n">
+        <v>0.7746142857142857</v>
+      </c>
       <c r="S253" s="1" t="n">
         <v>42</v>
       </c>
@@ -19696,6 +21145,9 @@
       </c>
       <c r="AD253" s="10" t="n"/>
       <c r="AE253" s="10" t="n"/>
+      <c r="AF253" t="n">
+        <v>0.97027</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
@@ -19722,6 +21174,9 @@
       <c r="K254" t="n">
         <v>0.8831777777777777</v>
       </c>
+      <c r="R254" t="n">
+        <v>0.85714</v>
+      </c>
       <c r="S254" s="1" t="n">
         <v>43</v>
       </c>
@@ -19739,6 +21194,9 @@
       </c>
       <c r="AD254" s="10" t="n"/>
       <c r="AE254" s="10" t="n"/>
+      <c r="AF254" t="n">
+        <v>0.9707999999999998</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
@@ -19765,6 +21223,9 @@
       <c r="K255" t="n">
         <v>0.8807222222222223</v>
       </c>
+      <c r="R255" t="n">
+        <v>0.9277124999999999</v>
+      </c>
       <c r="S255" s="1" t="n">
         <v>44</v>
       </c>
@@ -19782,6 +21243,9 @@
       </c>
       <c r="AD255" s="10" t="n"/>
       <c r="AE255" s="10" t="n"/>
+      <c r="AF255" t="n">
+        <v>0.97022</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
@@ -19808,6 +21272,9 @@
       <c r="K256" t="n">
         <v>0.8835888888888889</v>
       </c>
+      <c r="R256" t="n">
+        <v>0.8563333333333334</v>
+      </c>
       <c r="S256" s="1" t="n">
         <v>45</v>
       </c>
@@ -19825,6 +21292,9 @@
       </c>
       <c r="AD256" s="10" t="n"/>
       <c r="AE256" s="10" t="n"/>
+      <c r="AF256" t="n">
+        <v>0.9671666666666668</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
@@ -19851,6 +21321,9 @@
       <c r="K257" t="n">
         <v>0.8841333333333333</v>
       </c>
+      <c r="R257" t="n">
+        <v>0.8892428571428572</v>
+      </c>
       <c r="S257" s="1" t="n">
         <v>46</v>
       </c>
@@ -19868,6 +21341,9 @@
       </c>
       <c r="AD257" s="10" t="n"/>
       <c r="AE257" s="10" t="n"/>
+      <c r="AF257" t="n">
+        <v>0.9647333333333332</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
@@ -19894,6 +21370,9 @@
       <c r="K258" t="n">
         <v>0.8082900000000001</v>
       </c>
+      <c r="R258" t="n">
+        <v>0.8755000000000001</v>
+      </c>
       <c r="S258" s="1" t="n">
         <v>47</v>
       </c>
@@ -19911,6 +21390,9 @@
       </c>
       <c r="AD258" s="10" t="n"/>
       <c r="AE258" s="10" t="n"/>
+      <c r="AF258" t="n">
+        <v>0.9668166666666668</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
@@ -19937,6 +21419,9 @@
       <c r="K259" t="n">
         <v>0.80259</v>
       </c>
+      <c r="R259" t="n">
+        <v>0.8657916666666665</v>
+      </c>
       <c r="S259" s="1" t="n">
         <v>48</v>
       </c>
@@ -19954,6 +21439,9 @@
       </c>
       <c r="AD259" s="10" t="n"/>
       <c r="AE259" s="10" t="n"/>
+      <c r="AF259" t="n">
+        <v>0.9694571428571429</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
@@ -19980,6 +21468,9 @@
       <c r="K260" t="n">
         <v>0.8015399999999999</v>
       </c>
+      <c r="R260" t="n">
+        <v>0.920788888888889</v>
+      </c>
       <c r="S260" s="1" t="n">
         <v>49</v>
       </c>
@@ -19997,6 +21488,9 @@
       </c>
       <c r="AD260" s="10" t="n"/>
       <c r="AE260" s="10" t="n"/>
+      <c r="AF260" t="n">
+        <v>0.9680444444444445</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
@@ -20023,6 +21517,9 @@
       <c r="K261" t="n">
         <v>0.8102199999999999</v>
       </c>
+      <c r="R261" t="n">
+        <v>0.8627909090909092</v>
+      </c>
       <c r="S261" s="1" t="n">
         <v>50</v>
       </c>
@@ -20040,6 +21537,9 @@
       </c>
       <c r="AD261" s="10" t="n"/>
       <c r="AE261" s="10" t="n"/>
+      <c r="AF261" t="n">
+        <v>0.9607999999999999</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
@@ -20066,6 +21566,9 @@
       <c r="K262" t="n">
         <v>0.7989700000000001</v>
       </c>
+      <c r="R262" t="n">
+        <v>0.8626</v>
+      </c>
       <c r="S262" s="1" t="n">
         <v>51</v>
       </c>
@@ -20083,6 +21586,9 @@
       </c>
       <c r="AD262" s="10" t="n"/>
       <c r="AE262" s="10" t="n"/>
+      <c r="AF262" t="n">
+        <v>0.9705600000000001</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
@@ -20109,6 +21615,9 @@
       <c r="K263" t="n">
         <v>0.7446454545454544</v>
       </c>
+      <c r="R263" t="n">
+        <v>0.8595083333333333</v>
+      </c>
       <c r="S263" s="1" t="n">
         <v>52</v>
       </c>
@@ -20126,6 +21635,9 @@
       </c>
       <c r="AD263" s="10" t="n"/>
       <c r="AE263" s="10" t="n"/>
+      <c r="AF263" t="n">
+        <v>0.9682428571428571</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
@@ -20152,6 +21664,9 @@
       <c r="K264" t="n">
         <v>0.7403</v>
       </c>
+      <c r="R264" t="n">
+        <v>0.923346153846154</v>
+      </c>
       <c r="S264" s="1" t="n">
         <v>53</v>
       </c>
@@ -20169,6 +21684,9 @@
       </c>
       <c r="AD264" s="10" t="n"/>
       <c r="AE264" s="10" t="n"/>
+      <c r="AF264" t="n">
+        <v>0.9663</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
@@ -20195,6 +21713,9 @@
       <c r="K265" t="n">
         <v>0.743709090909091</v>
       </c>
+      <c r="R265" t="n">
+        <v>0.9103000000000001</v>
+      </c>
       <c r="S265" s="1" t="n">
         <v>54</v>
       </c>
@@ -20212,6 +21733,9 @@
       </c>
       <c r="AD265" s="10" t="n"/>
       <c r="AE265" s="10" t="n"/>
+      <c r="AF265" t="n">
+        <v>0.9757571428571429</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
@@ -20238,6 +21762,9 @@
       <c r="K266" t="n">
         <v>0.7385999999999999</v>
       </c>
+      <c r="R266" t="n">
+        <v>0.9174916666666667</v>
+      </c>
       <c r="S266" s="1" t="n">
         <v>55</v>
       </c>
@@ -20255,6 +21782,9 @@
       </c>
       <c r="AD266" s="10" t="n"/>
       <c r="AE266" s="10" t="n"/>
+      <c r="AF266" t="n">
+        <v>0.9612166666666666</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
@@ -20281,6 +21811,9 @@
       <c r="K267" t="n">
         <v>0.7437909090909091</v>
       </c>
+      <c r="R267" t="n">
+        <v>0.95428</v>
+      </c>
       <c r="S267" s="1" t="n">
         <v>56</v>
       </c>
@@ -20298,6 +21831,9 @@
       </c>
       <c r="AD267" s="10" t="n"/>
       <c r="AE267" s="10" t="n"/>
+      <c r="AF267" t="n">
+        <v>0.9699833333333333</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
@@ -20324,6 +21860,9 @@
       <c r="K268" t="n">
         <v>0.7403636363636362</v>
       </c>
+      <c r="R268" t="n">
+        <v>0.9538375</v>
+      </c>
       <c r="S268" s="1" t="n">
         <v>57</v>
       </c>
@@ -20341,6 +21880,9 @@
       </c>
       <c r="AD268" s="10" t="n"/>
       <c r="AE268" s="10" t="n"/>
+      <c r="AF268" t="n">
+        <v>0.976475</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
@@ -20367,6 +21909,9 @@
       <c r="K269" t="n">
         <v>0.6871416666666667</v>
       </c>
+      <c r="R269" t="n">
+        <v>0.9321000000000002</v>
+      </c>
       <c r="S269" s="1" t="n">
         <v>58</v>
       </c>
@@ -20384,6 +21929,9 @@
       </c>
       <c r="AD269" s="10" t="n"/>
       <c r="AE269" s="10" t="n"/>
+      <c r="AF269" t="n">
+        <v>0.96606</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
@@ -20410,6 +21958,9 @@
       <c r="K270" t="n">
         <v>0.6895666666666666</v>
       </c>
+      <c r="R270" t="n">
+        <v>0.9062874999999999</v>
+      </c>
       <c r="S270" s="1" t="n">
         <v>59</v>
       </c>
@@ -20427,6 +21978,9 @@
       </c>
       <c r="AD270" s="10" t="n"/>
       <c r="AE270" s="10" t="n"/>
+      <c r="AF270" t="n">
+        <v>0.96998</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
@@ -20453,6 +22007,9 @@
       <c r="K271" t="n">
         <v>0.684325</v>
       </c>
+      <c r="R271" t="n">
+        <v>0.8797899999999998</v>
+      </c>
       <c r="S271" s="1" t="n">
         <v>60</v>
       </c>
@@ -20470,6 +22027,9 @@
       </c>
       <c r="AD271" s="10" t="n"/>
       <c r="AE271" s="10" t="n"/>
+      <c r="AF271" t="n">
+        <v>0.97654</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
@@ -20496,6 +22056,9 @@
       <c r="K272" t="n">
         <v>0.6823916666666666</v>
       </c>
+      <c r="R272" t="n">
+        <v>0.9071499999999999</v>
+      </c>
       <c r="S272" s="1" t="n">
         <v>61</v>
       </c>
@@ -20513,6 +22076,9 @@
       </c>
       <c r="AD272" s="10" t="n"/>
       <c r="AE272" s="10" t="n"/>
+      <c r="AF272" t="n">
+        <v>0.97224</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
@@ -20539,6 +22105,9 @@
       <c r="K273" t="n">
         <v>0.6849166666666666</v>
       </c>
+      <c r="R273" t="n">
+        <v>0.8982153846153845</v>
+      </c>
       <c r="S273" s="1" t="n">
         <v>62</v>
       </c>
@@ -20556,6 +22125,9 @@
       </c>
       <c r="AD273" s="10" t="n"/>
       <c r="AE273" s="10" t="n"/>
+      <c r="AF273" t="n">
+        <v>0.9674200000000001</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
@@ -20582,6 +22154,9 @@
       <c r="K274" t="n">
         <v>0.6906</v>
       </c>
+      <c r="R274" t="n">
+        <v>0.9006636363636363</v>
+      </c>
       <c r="S274" s="1" t="n">
         <v>63</v>
       </c>
@@ -20599,6 +22174,9 @@
       </c>
       <c r="AD274" s="10" t="n"/>
       <c r="AE274" s="10" t="n"/>
+      <c r="AF274" t="n">
+        <v>0.9708571428571428</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
@@ -20625,6 +22203,9 @@
       <c r="K275" t="n">
         <v>0.6977833333333333</v>
       </c>
+      <c r="R275" t="n">
+        <v>0.8855499999999999</v>
+      </c>
       <c r="S275" s="1" t="n">
         <v>64</v>
       </c>
@@ -20642,6 +22223,9 @@
       </c>
       <c r="AD275" s="10" t="n"/>
       <c r="AE275" s="10" t="n"/>
+      <c r="AF275" t="n">
+        <v>0.9671800000000002</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
@@ -20668,6 +22252,9 @@
       <c r="K276" t="n">
         <v>0.688425</v>
       </c>
+      <c r="R276" t="n">
+        <v>0.8266</v>
+      </c>
       <c r="S276" s="1" t="n">
         <v>65</v>
       </c>
@@ -20685,6 +22272,9 @@
       </c>
       <c r="AD276" s="10" t="n"/>
       <c r="AE276" s="10" t="n"/>
+      <c r="AF276" t="n">
+        <v>0.9735999999999999</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
@@ -20711,6 +22301,9 @@
       <c r="K277" t="n">
         <v>0.6905333333333333</v>
       </c>
+      <c r="R277" t="n">
+        <v>0.88803</v>
+      </c>
       <c r="S277" s="1" t="n">
         <v>66</v>
       </c>
@@ -20728,6 +22321,9 @@
       </c>
       <c r="AD277" s="10" t="n"/>
       <c r="AE277" s="10" t="n"/>
+      <c r="AF277" t="n">
+        <v>0.9757285714285714</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
@@ -20754,6 +22350,9 @@
       <c r="K278" t="n">
         <v>0.6461076923076925</v>
       </c>
+      <c r="R278" t="n">
+        <v>0.8828</v>
+      </c>
       <c r="S278" s="1" t="n">
         <v>67</v>
       </c>
@@ -20771,6 +22370,9 @@
       </c>
       <c r="AD278" s="10" t="n"/>
       <c r="AE278" s="10" t="n"/>
+      <c r="AF278" t="n">
+        <v>0.9700857142857142</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
@@ -20797,6 +22399,9 @@
       <c r="K279" t="n">
         <v>0.6416307692307692</v>
       </c>
+      <c r="R279" t="n">
+        <v>0.9398222222222223</v>
+      </c>
       <c r="S279" s="1" t="n">
         <v>68</v>
       </c>
@@ -20814,6 +22419,9 @@
       </c>
       <c r="AD279" s="10" t="n"/>
       <c r="AE279" s="10" t="n"/>
+      <c r="AF279" t="n">
+        <v>0.9707285714285714</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
@@ -20840,6 +22448,9 @@
       <c r="K280" t="n">
         <v>0.645323076923077</v>
       </c>
+      <c r="R280" t="n">
+        <v>0.9174899999999999</v>
+      </c>
       <c r="S280" s="1" t="n">
         <v>69</v>
       </c>
@@ -20857,6 +22468,9 @@
       </c>
       <c r="AD280" s="10" t="n"/>
       <c r="AE280" s="10" t="n"/>
+      <c r="AF280" t="n">
+        <v>0.9728428571428571</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
@@ -20883,6 +22497,9 @@
       <c r="K281" t="n">
         <v>0.6458384615384615</v>
       </c>
+      <c r="R281" t="n">
+        <v>0.9313000000000001</v>
+      </c>
       <c r="S281" s="1" t="n">
         <v>70</v>
       </c>
@@ -20900,6 +22517,9 @@
       </c>
       <c r="AD281" s="10" t="n"/>
       <c r="AE281" s="10" t="n"/>
+      <c r="AF281" t="n">
+        <v>0.9738999999999999</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
@@ -20926,6 +22546,9 @@
       <c r="K282" t="n">
         <v>0.6013642857142857</v>
       </c>
+      <c r="R282" t="n">
+        <v>0.9372545454545456</v>
+      </c>
       <c r="S282" s="1" t="n">
         <v>71</v>
       </c>
@@ -20943,6 +22566,9 @@
       </c>
       <c r="AD282" s="10" t="n"/>
       <c r="AE282" s="10" t="n"/>
+      <c r="AF282" t="n">
+        <v>0.9725199999999999</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
@@ -20969,6 +22595,9 @@
       <c r="K283" t="n">
         <v>0.6023500000000002</v>
       </c>
+      <c r="R283" t="n">
+        <v>0.9462200000000001</v>
+      </c>
       <c r="S283" s="1" t="n">
         <v>72</v>
       </c>
@@ -20986,6 +22615,9 @@
       </c>
       <c r="AD283" s="10" t="n"/>
       <c r="AE283" s="10" t="n"/>
+      <c r="AF283" t="n">
+        <v>0.97072</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
@@ -21012,6 +22644,9 @@
       <c r="K284" t="n">
         <v>0.6047142857142858</v>
       </c>
+      <c r="R284" t="n">
+        <v>0.8942888888888887</v>
+      </c>
       <c r="S284" s="1" t="n">
         <v>73</v>
       </c>
@@ -21029,6 +22664,9 @@
       </c>
       <c r="AD284" s="10" t="n"/>
       <c r="AE284" s="10" t="n"/>
+      <c r="AF284" t="n">
+        <v>0.9671571428571427</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
@@ -21055,6 +22693,9 @@
       <c r="K285" t="n">
         <v>0.5702</v>
       </c>
+      <c r="R285" t="n">
+        <v>0.8787</v>
+      </c>
       <c r="S285" s="1" t="n">
         <v>74</v>
       </c>
@@ -21072,6 +22713,9 @@
       </c>
       <c r="AD285" s="10" t="n"/>
       <c r="AE285" s="10" t="n"/>
+      <c r="AF285" t="n">
+        <v>0.9697999999999999</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
@@ -21098,6 +22742,9 @@
       <c r="K286" t="n">
         <v>0.57104</v>
       </c>
+      <c r="R286" t="n">
+        <v>0.9467599999999999</v>
+      </c>
       <c r="S286" s="1" t="n">
         <v>75</v>
       </c>
@@ -21115,6 +22762,9 @@
       </c>
       <c r="AD286" s="10" t="n"/>
       <c r="AE286" s="10" t="n"/>
+      <c r="AF286" t="n">
+        <v>0.9652166666666666</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
@@ -21141,6 +22791,9 @@
       <c r="K287" t="n">
         <v>0.5406562500000001</v>
       </c>
+      <c r="R287" t="n">
+        <v>0.90693</v>
+      </c>
       <c r="S287" s="1" t="n">
         <v>76</v>
       </c>
@@ -21158,6 +22811,9 @@
       </c>
       <c r="AD287" s="10" t="n"/>
       <c r="AE287" s="10" t="n"/>
+      <c r="AF287" t="n">
+        <v>0.9759</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
@@ -21184,6 +22840,9 @@
       <c r="K288" t="n">
         <v>0.539825</v>
       </c>
+      <c r="R288" t="n">
+        <v>0.9337454545454545</v>
+      </c>
       <c r="S288" s="1" t="n">
         <v>77</v>
       </c>
@@ -21201,6 +22860,9 @@
       </c>
       <c r="AD288" s="10" t="n"/>
       <c r="AE288" s="10" t="n"/>
+      <c r="AF288" t="n">
+        <v>0.9716833333333333</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
@@ -21227,6 +22889,9 @@
       <c r="K289" t="n">
         <v>0.5139941176470588</v>
       </c>
+      <c r="R289" t="n">
+        <v>0.9486999999999999</v>
+      </c>
       <c r="S289" s="1" t="n">
         <v>78</v>
       </c>
@@ -21244,6 +22909,9 @@
       </c>
       <c r="AD289" s="10" t="n"/>
       <c r="AE289" s="10" t="n"/>
+      <c r="AF289" t="n">
+        <v>0.9722333333333334</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
@@ -21270,6 +22938,9 @@
       <c r="K290" t="n">
         <v>0.5143352941176471</v>
       </c>
+      <c r="R290" t="n">
+        <v>0.9351111111111111</v>
+      </c>
       <c r="S290" s="1" t="n">
         <v>79</v>
       </c>
@@ -21287,6 +22958,9 @@
       </c>
       <c r="AD290" s="10" t="n"/>
       <c r="AE290" s="10" t="n"/>
+      <c r="AF290" t="n">
+        <v>0.9698000000000001</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
@@ -21313,6 +22987,9 @@
       <c r="K291" t="n">
         <v>0.515435294117647</v>
       </c>
+      <c r="R291" t="n">
+        <v>0.9096692307692307</v>
+      </c>
       <c r="S291" s="1" t="n">
         <v>80</v>
       </c>
@@ -21330,6 +23007,9 @@
       </c>
       <c r="AD291" s="10" t="n"/>
       <c r="AE291" s="10" t="n"/>
+      <c r="AF291" t="n">
+        <v>0.9743625</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
@@ -21356,6 +23036,9 @@
       <c r="K292" t="n">
         <v>0.5140941176470589</v>
       </c>
+      <c r="R292" t="n">
+        <v>0.94863</v>
+      </c>
       <c r="S292" s="1" t="n">
         <v>81</v>
       </c>
@@ -21373,6 +23056,9 @@
       </c>
       <c r="AD292" s="10" t="n"/>
       <c r="AE292" s="10" t="n"/>
+      <c r="AF292" t="n">
+        <v>0.9743666666666666</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
@@ -21399,6 +23085,9 @@
       <c r="K293" t="n">
         <v>0.5135470588235294</v>
       </c>
+      <c r="R293" t="n">
+        <v>0.9114545454545454</v>
+      </c>
       <c r="S293" s="1" t="n">
         <v>82</v>
       </c>
@@ -21416,6 +23105,9 @@
       </c>
       <c r="AD293" s="10" t="n"/>
       <c r="AE293" s="10" t="n"/>
+      <c r="AF293" t="n">
+        <v>0.9705</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
@@ -21442,6 +23134,9 @@
       <c r="K294" t="n">
         <v>0.5168470588235294</v>
       </c>
+      <c r="R294" t="n">
+        <v>0.9320749999999999</v>
+      </c>
       <c r="S294" s="1" t="n">
         <v>83</v>
       </c>
@@ -21459,6 +23154,9 @@
       </c>
       <c r="AD294" s="10" t="n"/>
       <c r="AE294" s="10" t="n"/>
+      <c r="AF294" t="n">
+        <v>0.9741124999999999</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
@@ -21485,6 +23183,9 @@
       <c r="K295" t="n">
         <v>0.5150235294117647</v>
       </c>
+      <c r="R295" t="n">
+        <v>0.9523250000000001</v>
+      </c>
       <c r="S295" s="1" t="n">
         <v>84</v>
       </c>
@@ -21502,6 +23203,9 @@
       </c>
       <c r="AD295" s="10" t="n"/>
       <c r="AE295" s="10" t="n"/>
+      <c r="AF295" t="n">
+        <v>0.9752142857142857</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
@@ -21528,6 +23232,9 @@
       <c r="K296" t="n">
         <v>0.5149588235294118</v>
       </c>
+      <c r="R296" t="n">
+        <v>0.9323399999999999</v>
+      </c>
       <c r="S296" s="1" t="n">
         <v>85</v>
       </c>
@@ -21545,6 +23252,9 @@
       </c>
       <c r="AD296" s="10" t="n"/>
       <c r="AE296" s="10" t="n"/>
+      <c r="AF296" t="n">
+        <v>0.9717500000000001</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
@@ -21571,6 +23281,9 @@
       <c r="K297" t="n">
         <v>0.5075529411764707</v>
       </c>
+      <c r="R297" t="n">
+        <v>0.9244249999999999</v>
+      </c>
       <c r="S297" s="1" t="n">
         <v>86</v>
       </c>
@@ -21588,6 +23301,9 @@
       </c>
       <c r="AD297" s="10" t="n"/>
       <c r="AE297" s="10" t="n"/>
+      <c r="AF297" t="n">
+        <v>0.9662499999999999</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
@@ -21614,6 +23330,9 @@
       <c r="K298" t="n">
         <v>0.5132000000000001</v>
       </c>
+      <c r="R298" t="n">
+        <v>0.9347111111111109</v>
+      </c>
       <c r="S298" s="1" t="n">
         <v>87</v>
       </c>
@@ -21631,6 +23350,9 @@
       </c>
       <c r="AD298" s="10" t="n"/>
       <c r="AE298" s="10" t="n"/>
+      <c r="AF298" t="n">
+        <v>0.9715</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
@@ -21657,6 +23379,9 @@
       <c r="K299" t="n">
         <v>0.5103882352941176</v>
       </c>
+      <c r="R299" t="n">
+        <v>0.9296692307692308</v>
+      </c>
       <c r="S299" s="1" t="n">
         <v>88</v>
       </c>
@@ -21674,6 +23399,9 @@
       </c>
       <c r="AD299" s="10" t="n"/>
       <c r="AE299" s="10" t="n"/>
+      <c r="AF299" t="n">
+        <v>0.9764571428571429</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
@@ -21700,6 +23428,9 @@
       <c r="K300" t="n">
         <v>0.5159882352941177</v>
       </c>
+      <c r="R300" t="n">
+        <v>0.9393222222222223</v>
+      </c>
       <c r="S300" s="1" t="n">
         <v>89</v>
       </c>
@@ -21717,6 +23448,9 @@
       </c>
       <c r="AD300" s="10" t="n"/>
       <c r="AE300" s="10" t="n"/>
+      <c r="AF300" t="n">
+        <v>0.9727857142857143</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
@@ -21743,6 +23477,9 @@
       <c r="K301" t="n">
         <v>0.5152352941176471</v>
       </c>
+      <c r="R301" t="n">
+        <v>0.9253500000000001</v>
+      </c>
       <c r="S301" s="1" t="n">
         <v>90</v>
       </c>
@@ -21760,6 +23497,9 @@
       </c>
       <c r="AD301" s="10" t="n"/>
       <c r="AE301" s="10" t="n"/>
+      <c r="AF301" t="n">
+        <v>0.9731428571428572</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
@@ -21786,6 +23526,9 @@
       <c r="K302" t="n">
         <v>0.5175176470588235</v>
       </c>
+      <c r="R302" t="n">
+        <v>0.9101750000000002</v>
+      </c>
       <c r="S302" s="1" t="n">
         <v>91</v>
       </c>
@@ -21803,6 +23546,9 @@
       </c>
       <c r="AD302" s="10" t="n"/>
       <c r="AE302" s="10" t="n"/>
+      <c r="AF302" t="n">
+        <v>0.9742666666666665</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
@@ -21829,6 +23575,9 @@
       <c r="K303" t="n">
         <v>0.516435294117647</v>
       </c>
+      <c r="R303" t="n">
+        <v>0.9484153846153848</v>
+      </c>
       <c r="S303" s="1" t="n">
         <v>92</v>
       </c>
@@ -21846,6 +23595,9 @@
       </c>
       <c r="AD303" s="10" t="n"/>
       <c r="AE303" s="10" t="n"/>
+      <c r="AF303" t="n">
+        <v>0.9761999999999998</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
@@ -21872,6 +23624,9 @@
       <c r="K304" t="n">
         <v>0.5166176470588235</v>
       </c>
+      <c r="R304" t="n">
+        <v>0.93943</v>
+      </c>
       <c r="S304" s="1" t="n">
         <v>93</v>
       </c>
@@ -21889,6 +23644,9 @@
       </c>
       <c r="AD304" s="10" t="n"/>
       <c r="AE304" s="10" t="n"/>
+      <c r="AF304" t="n">
+        <v>0.9753142857142857</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
@@ -21915,6 +23673,9 @@
       <c r="K305" t="n">
         <v>0.5112294117647057</v>
       </c>
+      <c r="R305" t="n">
+        <v>0.943730769230769</v>
+      </c>
       <c r="S305" s="1" t="n">
         <v>94</v>
       </c>
@@ -21932,6 +23693,9 @@
       </c>
       <c r="AD305" s="10" t="n"/>
       <c r="AE305" s="10" t="n"/>
+      <c r="AF305" t="n">
+        <v>0.9735400000000001</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
@@ -21955,6 +23719,9 @@
       <c r="K306" t="n">
         <v>0.516264705882353</v>
       </c>
+      <c r="R306" t="n">
+        <v>0.9647818181818182</v>
+      </c>
       <c r="S306" s="1" t="n">
         <v>95</v>
       </c>
@@ -21972,6 +23739,9 @@
       </c>
       <c r="AD306" s="10" t="n"/>
       <c r="AE306" s="10" t="n"/>
+      <c r="AF306" t="n">
+        <v>0.9772</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
@@ -21995,6 +23765,9 @@
       <c r="K307" t="n">
         <v>0.5167470588235293</v>
       </c>
+      <c r="R307" t="n">
+        <v>0.9498</v>
+      </c>
       <c r="S307" s="1" t="n">
         <v>96</v>
       </c>
@@ -22012,6 +23785,9 @@
       </c>
       <c r="AD307" s="10" t="n"/>
       <c r="AE307" s="10" t="n"/>
+      <c r="AF307" t="n">
+        <v>0.9727374999999999</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
@@ -22035,6 +23811,9 @@
       <c r="K308" t="n">
         <v>0.5147176470588235</v>
       </c>
+      <c r="R308" t="n">
+        <v>0.90625</v>
+      </c>
       <c r="S308" s="1" t="n">
         <v>97</v>
       </c>
@@ -22052,6 +23831,9 @@
       </c>
       <c r="AD308" s="10" t="n"/>
       <c r="AE308" s="10" t="n"/>
+      <c r="AF308" t="n">
+        <v>0.97563</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
@@ -22075,6 +23857,9 @@
       <c r="K309" t="n">
         <v>0.5168</v>
       </c>
+      <c r="R309" t="n">
+        <v>0.9581666666666667</v>
+      </c>
       <c r="S309" s="1" t="n">
         <v>98</v>
       </c>
@@ -22092,6 +23877,9 @@
       </c>
       <c r="AD309" s="10" t="n"/>
       <c r="AE309" s="10" t="n"/>
+      <c r="AF309" t="n">
+        <v>0.9676750000000001</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
@@ -22115,6 +23903,9 @@
       <c r="K310" t="n">
         <v>0.5193941176470588</v>
       </c>
+      <c r="R310" t="n">
+        <v>0.94418</v>
+      </c>
       <c r="S310" s="1" t="n">
         <v>99</v>
       </c>
@@ -22132,6 +23923,9 @@
       </c>
       <c r="AD310" s="10" t="n"/>
       <c r="AE310" s="10" t="n"/>
+      <c r="AF310" t="n">
+        <v>0.9753999999999999</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
@@ -22155,6 +23949,9 @@
       <c r="K311" t="n">
         <v>0.5100588235294117</v>
       </c>
+      <c r="R311" t="n">
+        <v>0.9537153846153845</v>
+      </c>
       <c r="S311" s="1" t="n">
         <v>100</v>
       </c>
@@ -22174,6 +23971,9 @@
         <v>0.847</v>
       </c>
       <c r="AE311" s="10" t="n"/>
+      <c r="AF311" t="n">
+        <v>0.9733833333333332</v>
+      </c>
     </row>
     <row r="312">
       <c r="AD312" s="10" t="n"/>
@@ -22245,6 +24045,9 @@
       <c r="K316" t="n">
         <v>0</v>
       </c>
+      <c r="R316" t="n">
+        <v>0.9998</v>
+      </c>
       <c r="S316" s="1" t="n">
         <v>1</v>
       </c>
@@ -22262,6 +24065,9 @@
       </c>
       <c r="AD316" s="10" t="n"/>
       <c r="AE316" s="10" t="n"/>
+      <c r="AF316" t="n">
+        <v>0</v>
+      </c>
       <c r="AG316" t="n">
         <v>0.3727</v>
       </c>
@@ -22300,6 +24106,9 @@
       <c r="K317" t="n">
         <v>0.0025</v>
       </c>
+      <c r="R317" t="n">
+        <v>0.468</v>
+      </c>
       <c r="S317" s="1" t="n">
         <v>2</v>
       </c>
@@ -22317,6 +24126,9 @@
       </c>
       <c r="AD317" s="10" t="n"/>
       <c r="AE317" s="10" t="n"/>
+      <c r="AF317" t="n">
+        <v>0.0047</v>
+      </c>
       <c r="AG317" t="n">
         <v>0.0987</v>
       </c>
@@ -22355,6 +24167,9 @@
       <c r="K318" t="n">
         <v>0.153</v>
       </c>
+      <c r="R318" t="n">
+        <v>0.4841</v>
+      </c>
       <c r="S318" s="1" t="n">
         <v>3</v>
       </c>
@@ -22372,6 +24187,9 @@
       </c>
       <c r="AD318" s="10" t="n"/>
       <c r="AE318" s="10" t="n"/>
+      <c r="AF318" t="n">
+        <v>0.0246</v>
+      </c>
       <c r="AG318" t="n">
         <v>0.0789</v>
       </c>
@@ -22410,6 +24228,9 @@
       <c r="K319" t="n">
         <v>0.1108</v>
       </c>
+      <c r="R319" t="n">
+        <v>0.7894</v>
+      </c>
       <c r="S319" s="1" t="n">
         <v>4</v>
       </c>
@@ -22427,6 +24248,9 @@
       </c>
       <c r="AD319" s="10" t="n"/>
       <c r="AE319" s="10" t="n"/>
+      <c r="AF319" t="n">
+        <v>0.0392</v>
+      </c>
       <c r="AG319" t="n">
         <v>0.3827</v>
       </c>
@@ -22465,6 +24289,9 @@
       <c r="K320" t="n">
         <v>0.1124</v>
       </c>
+      <c r="R320" t="n">
+        <v>0.3534</v>
+      </c>
       <c r="S320" s="1" t="n">
         <v>5</v>
       </c>
@@ -22482,6 +24309,9 @@
       </c>
       <c r="AD320" s="10" t="n"/>
       <c r="AE320" s="10" t="n"/>
+      <c r="AF320" t="n">
+        <v>0.07779999999999999</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
@@ -22514,6 +24344,9 @@
       <c r="K321" t="n">
         <v>0.1032</v>
       </c>
+      <c r="R321" t="n">
+        <v>0.4287</v>
+      </c>
       <c r="S321" s="1" t="n">
         <v>6</v>
       </c>
@@ -22531,6 +24364,9 @@
       </c>
       <c r="AD321" s="10" t="n"/>
       <c r="AE321" s="10" t="n"/>
+      <c r="AF321" t="n">
+        <v>0.0926</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
@@ -22563,6 +24399,9 @@
       <c r="K322" t="n">
         <v>0.1024</v>
       </c>
+      <c r="R322" t="n">
+        <v>0.8197</v>
+      </c>
       <c r="S322" s="1" t="n">
         <v>7</v>
       </c>
@@ -22580,6 +24419,9 @@
       </c>
       <c r="AD322" s="10" t="n"/>
       <c r="AE322" s="10" t="n"/>
+      <c r="AF322" t="n">
+        <v>0.0862</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
@@ -22612,6 +24454,9 @@
       <c r="K323" t="n">
         <v>0.1155</v>
       </c>
+      <c r="R323" t="n">
+        <v>0.8357</v>
+      </c>
       <c r="S323" s="1" t="n">
         <v>8</v>
       </c>
@@ -22629,6 +24474,9 @@
       </c>
       <c r="AD323" s="10" t="n"/>
       <c r="AE323" s="10" t="n"/>
+      <c r="AF323" t="n">
+        <v>0.0994</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
@@ -22661,6 +24509,9 @@
       <c r="K324" t="n">
         <v>0.109</v>
       </c>
+      <c r="R324" t="n">
+        <v>0.8956</v>
+      </c>
       <c r="S324" s="1" t="n">
         <v>9</v>
       </c>
@@ -22678,6 +24529,9 @@
       </c>
       <c r="AD324" s="10" t="n"/>
       <c r="AE324" s="10" t="n"/>
+      <c r="AF324" t="n">
+        <v>0.1198</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
@@ -22710,6 +24564,9 @@
       <c r="K325" t="n">
         <v>0.09950000000000001</v>
       </c>
+      <c r="R325" t="n">
+        <v>0.9317</v>
+      </c>
       <c r="S325" s="1" t="n">
         <v>10</v>
       </c>
@@ -22727,6 +24584,9 @@
       </c>
       <c r="AD325" s="10" t="n"/>
       <c r="AE325" s="10" t="n"/>
+      <c r="AF325" t="n">
+        <v>0.0994</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
@@ -22753,6 +24613,9 @@
       <c r="K326" t="n">
         <v>0.1019</v>
       </c>
+      <c r="R326" t="n">
+        <v>0.8598</v>
+      </c>
       <c r="S326" s="1" t="n">
         <v>11</v>
       </c>
@@ -22770,6 +24633,9 @@
       </c>
       <c r="AD326" s="10" t="n"/>
       <c r="AE326" s="10" t="n"/>
+      <c r="AF326" t="n">
+        <v>0.0992</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
@@ -22796,6 +24662,9 @@
       <c r="K327" t="n">
         <v>0.1023</v>
       </c>
+      <c r="R327" t="n">
+        <v>0.837</v>
+      </c>
       <c r="S327" s="1" t="n">
         <v>12</v>
       </c>
@@ -22813,6 +24682,9 @@
       </c>
       <c r="AD327" s="10" t="n"/>
       <c r="AE327" s="10" t="n"/>
+      <c r="AF327" t="n">
+        <v>0.09279999999999999</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
@@ -22839,6 +24711,9 @@
       <c r="K328" t="n">
         <v>0.102</v>
       </c>
+      <c r="R328" t="n">
+        <v>0.8052</v>
+      </c>
       <c r="S328" s="1" t="n">
         <v>13</v>
       </c>
@@ -22856,6 +24731,9 @@
       </c>
       <c r="AD328" s="10" t="n"/>
       <c r="AE328" s="10" t="n"/>
+      <c r="AF328" t="n">
+        <v>0.095</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
@@ -22882,6 +24760,9 @@
       <c r="K329" t="n">
         <v>0.103</v>
       </c>
+      <c r="R329" t="n">
+        <v>0.9177</v>
+      </c>
       <c r="S329" s="1" t="n">
         <v>14</v>
       </c>
@@ -22899,6 +24780,9 @@
       </c>
       <c r="AD329" s="10" t="n"/>
       <c r="AE329" s="10" t="n"/>
+      <c r="AF329" t="n">
+        <v>0.1036</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
@@ -22925,6 +24809,9 @@
       <c r="K330" t="n">
         <v>0.09760000000000001</v>
       </c>
+      <c r="R330" t="n">
+        <v>0.845</v>
+      </c>
       <c r="S330" s="1" t="n">
         <v>15</v>
       </c>
@@ -22942,6 +24829,9 @@
       </c>
       <c r="AD330" s="10" t="n"/>
       <c r="AE330" s="10" t="n"/>
+      <c r="AF330" t="n">
+        <v>0.1041</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
@@ -22968,6 +24858,9 @@
       <c r="K331" t="n">
         <v>0.0997</v>
       </c>
+      <c r="R331" t="n">
+        <v>0.7453</v>
+      </c>
       <c r="S331" s="1" t="n">
         <v>16</v>
       </c>
@@ -22985,6 +24878,9 @@
       </c>
       <c r="AD331" s="10" t="n"/>
       <c r="AE331" s="10" t="n"/>
+      <c r="AF331" t="n">
+        <v>0.0926</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
@@ -23011,6 +24907,9 @@
       <c r="K332" t="n">
         <v>0.1007</v>
       </c>
+      <c r="R332" t="n">
+        <v>0.8873</v>
+      </c>
       <c r="S332" s="1" t="n">
         <v>17</v>
       </c>
@@ -23028,6 +24927,9 @@
       </c>
       <c r="AD332" s="10" t="n"/>
       <c r="AE332" s="10" t="n"/>
+      <c r="AF332" t="n">
+        <v>0.124</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
@@ -23054,6 +24956,9 @@
       <c r="K333" t="n">
         <v>0.0997</v>
       </c>
+      <c r="R333" t="n">
+        <v>0.8479</v>
+      </c>
       <c r="S333" s="1" t="n">
         <v>18</v>
       </c>
@@ -23071,6 +24976,9 @@
       </c>
       <c r="AD333" s="10" t="n"/>
       <c r="AE333" s="10" t="n"/>
+      <c r="AF333" t="n">
+        <v>0.1002</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
@@ -23097,6 +25005,9 @@
       <c r="K334" t="n">
         <v>0.0969</v>
       </c>
+      <c r="R334" t="n">
+        <v>0.8885</v>
+      </c>
       <c r="S334" s="1" t="n">
         <v>19</v>
       </c>
@@ -23114,6 +25025,9 @@
       </c>
       <c r="AD334" s="10" t="n"/>
       <c r="AE334" s="10" t="n"/>
+      <c r="AF334" t="n">
+        <v>0.09810000000000001</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
@@ -23140,6 +25054,9 @@
       <c r="K335" t="n">
         <v>0.0911</v>
       </c>
+      <c r="R335" t="n">
+        <v>0.8111</v>
+      </c>
       <c r="S335" s="1" t="n">
         <v>20</v>
       </c>
@@ -23157,6 +25074,9 @@
       </c>
       <c r="AD335" s="10" t="n"/>
       <c r="AE335" s="10" t="n"/>
+      <c r="AF335" t="n">
+        <v>0.1008</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
@@ -23183,6 +25103,9 @@
       <c r="K336" t="n">
         <v>0.1026</v>
       </c>
+      <c r="R336" t="n">
+        <v>0.767</v>
+      </c>
       <c r="S336" s="1" t="n">
         <v>21</v>
       </c>
@@ -23200,6 +25123,9 @@
       </c>
       <c r="AD336" s="10" t="n"/>
       <c r="AE336" s="10" t="n"/>
+      <c r="AF336" t="n">
+        <v>0.107</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
@@ -23226,6 +25152,9 @@
       <c r="K337" t="n">
         <v>0.0919</v>
       </c>
+      <c r="R337" t="n">
+        <v>0.8475</v>
+      </c>
       <c r="S337" s="1" t="n">
         <v>22</v>
       </c>
@@ -23243,6 +25172,9 @@
       </c>
       <c r="AD337" s="10" t="n"/>
       <c r="AE337" s="10" t="n"/>
+      <c r="AF337" t="n">
+        <v>0.1049</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
@@ -23269,6 +25201,9 @@
       <c r="K338" t="n">
         <v>0.0958</v>
       </c>
+      <c r="R338" t="n">
+        <v>0.9177</v>
+      </c>
       <c r="S338" s="1" t="n">
         <v>23</v>
       </c>
@@ -23286,6 +25221,9 @@
       </c>
       <c r="AD338" s="10" t="n"/>
       <c r="AE338" s="10" t="n"/>
+      <c r="AF338" t="n">
+        <v>0.1093</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
@@ -23312,6 +25250,9 @@
       <c r="K339" t="n">
         <v>0.09660000000000001</v>
       </c>
+      <c r="R339" t="n">
+        <v>0.8635</v>
+      </c>
       <c r="S339" s="1" t="n">
         <v>24</v>
       </c>
@@ -23329,6 +25270,9 @@
       </c>
       <c r="AD339" s="10" t="n"/>
       <c r="AE339" s="10" t="n"/>
+      <c r="AF339" t="n">
+        <v>0.09909999999999999</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
@@ -23355,6 +25299,9 @@
       <c r="K340" t="n">
         <v>0.0975</v>
       </c>
+      <c r="R340" t="n">
+        <v>0.8467</v>
+      </c>
       <c r="S340" s="1" t="n">
         <v>25</v>
       </c>
@@ -23372,6 +25319,9 @@
       </c>
       <c r="AD340" s="10" t="n"/>
       <c r="AE340" s="10" t="n"/>
+      <c r="AF340" t="n">
+        <v>0.1096</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
@@ -23398,6 +25348,9 @@
       <c r="K341" t="n">
         <v>0.0955</v>
       </c>
+      <c r="R341" t="n">
+        <v>0.9121</v>
+      </c>
       <c r="S341" s="1" t="n">
         <v>26</v>
       </c>
@@ -23415,6 +25368,9 @@
       </c>
       <c r="AD341" s="10" t="n"/>
       <c r="AE341" s="10" t="n"/>
+      <c r="AF341" t="n">
+        <v>0.1151</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
@@ -23441,6 +25397,9 @@
       <c r="K342" t="n">
         <v>0.0965</v>
       </c>
+      <c r="R342" t="n">
+        <v>0.9494</v>
+      </c>
       <c r="S342" s="1" t="n">
         <v>27</v>
       </c>
@@ -23458,6 +25417,9 @@
       </c>
       <c r="AD342" s="10" t="n"/>
       <c r="AE342" s="10" t="n"/>
+      <c r="AF342" t="n">
+        <v>0.1109</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
@@ -23484,6 +25446,9 @@
       <c r="K343" t="n">
         <v>0.0983</v>
       </c>
+      <c r="R343" t="n">
+        <v>0.8727</v>
+      </c>
       <c r="S343" s="1" t="n">
         <v>28</v>
       </c>
@@ -23501,6 +25466,9 @@
       </c>
       <c r="AD343" s="10" t="n"/>
       <c r="AE343" s="10" t="n"/>
+      <c r="AF343" t="n">
+        <v>0.1084</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
@@ -23527,6 +25495,9 @@
       <c r="K344" t="n">
         <v>0.09470000000000001</v>
       </c>
+      <c r="R344" t="n">
+        <v>0.9335</v>
+      </c>
       <c r="S344" s="1" t="n">
         <v>29</v>
       </c>
@@ -23544,6 +25515,9 @@
       </c>
       <c r="AD344" s="10" t="n"/>
       <c r="AE344" s="10" t="n"/>
+      <c r="AF344" t="n">
+        <v>0.1209</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
@@ -23570,6 +25544,9 @@
       <c r="K345" t="n">
         <v>0.0988</v>
       </c>
+      <c r="R345" t="n">
+        <v>0.8975</v>
+      </c>
       <c r="S345" s="1" t="n">
         <v>30</v>
       </c>
@@ -23587,6 +25564,9 @@
       </c>
       <c r="AD345" s="10" t="n"/>
       <c r="AE345" s="10" t="n"/>
+      <c r="AF345" t="n">
+        <v>0.1146</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
@@ -23613,6 +25593,9 @@
       <c r="K346" t="n">
         <v>0.09719999999999999</v>
       </c>
+      <c r="R346" t="n">
+        <v>0.8895999999999999</v>
+      </c>
       <c r="S346" s="1" t="n">
         <v>31</v>
       </c>
@@ -23630,6 +25613,9 @@
       </c>
       <c r="AD346" s="10" t="n"/>
       <c r="AE346" s="10" t="n"/>
+      <c r="AF346" t="n">
+        <v>0.1084</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
@@ -23656,6 +25642,9 @@
       <c r="K347" t="n">
         <v>0.0949</v>
       </c>
+      <c r="R347" t="n">
+        <v>0.8818</v>
+      </c>
       <c r="S347" s="1" t="n">
         <v>32</v>
       </c>
@@ -23673,6 +25662,9 @@
       </c>
       <c r="AD347" s="10" t="n"/>
       <c r="AE347" s="10" t="n"/>
+      <c r="AF347" t="n">
+        <v>0.1097</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
@@ -23699,6 +25691,9 @@
       <c r="K348" t="n">
         <v>0.0939</v>
       </c>
+      <c r="R348" t="n">
+        <v>0.9487</v>
+      </c>
       <c r="S348" s="1" t="n">
         <v>33</v>
       </c>
@@ -23716,6 +25711,9 @@
       </c>
       <c r="AD348" s="10" t="n"/>
       <c r="AE348" s="10" t="n"/>
+      <c r="AF348" t="n">
+        <v>0.1042</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
@@ -23742,6 +25740,9 @@
       <c r="K349" t="n">
         <v>0.0934</v>
       </c>
+      <c r="R349" t="n">
+        <v>0.8746</v>
+      </c>
       <c r="S349" s="1" t="n">
         <v>34</v>
       </c>
@@ -23759,6 +25760,9 @@
       </c>
       <c r="AD349" s="10" t="n"/>
       <c r="AE349" s="10" t="n"/>
+      <c r="AF349" t="n">
+        <v>0.1119</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
@@ -23785,6 +25789,9 @@
       <c r="K350" t="n">
         <v>0.0977</v>
       </c>
+      <c r="R350" t="n">
+        <v>0.9094</v>
+      </c>
       <c r="S350" s="1" t="n">
         <v>35</v>
       </c>
@@ -23802,6 +25809,9 @@
       </c>
       <c r="AD350" s="10" t="n"/>
       <c r="AE350" s="10" t="n"/>
+      <c r="AF350" t="n">
+        <v>0.1229</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
@@ -23828,6 +25838,9 @@
       <c r="K351" t="n">
         <v>0.0953</v>
       </c>
+      <c r="R351" t="n">
+        <v>0.9261</v>
+      </c>
       <c r="S351" s="1" t="n">
         <v>36</v>
       </c>
@@ -23845,6 +25858,9 @@
       </c>
       <c r="AD351" s="10" t="n"/>
       <c r="AE351" s="10" t="n"/>
+      <c r="AF351" t="n">
+        <v>0.1015</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
@@ -23871,6 +25887,9 @@
       <c r="K352" t="n">
         <v>0.0956</v>
       </c>
+      <c r="R352" t="n">
+        <v>0.9188</v>
+      </c>
       <c r="S352" s="1" t="n">
         <v>37</v>
       </c>
@@ -23888,6 +25907,9 @@
       </c>
       <c r="AD352" s="10" t="n"/>
       <c r="AE352" s="10" t="n"/>
+      <c r="AF352" t="n">
+        <v>0.09660000000000001</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
@@ -23914,6 +25936,9 @@
       <c r="K353" t="n">
         <v>0.0958</v>
       </c>
+      <c r="R353" t="n">
+        <v>0.9113</v>
+      </c>
       <c r="S353" s="1" t="n">
         <v>38</v>
       </c>
@@ -23931,6 +25956,9 @@
       </c>
       <c r="AD353" s="10" t="n"/>
       <c r="AE353" s="10" t="n"/>
+      <c r="AF353" t="n">
+        <v>0.1036</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
@@ -23957,6 +25985,9 @@
       <c r="K354" t="n">
         <v>0.09320000000000001</v>
       </c>
+      <c r="R354" t="n">
+        <v>0.9207</v>
+      </c>
       <c r="S354" s="1" t="n">
         <v>39</v>
       </c>
@@ -23974,6 +26005,9 @@
       </c>
       <c r="AD354" s="10" t="n"/>
       <c r="AE354" s="10" t="n"/>
+      <c r="AF354" t="n">
+        <v>0.104</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
@@ -24000,6 +26034,9 @@
       <c r="K355" t="n">
         <v>0.0973</v>
       </c>
+      <c r="R355" t="n">
+        <v>0.9514</v>
+      </c>
       <c r="S355" s="1" t="n">
         <v>40</v>
       </c>
@@ -24017,6 +26054,9 @@
       </c>
       <c r="AD355" s="10" t="n"/>
       <c r="AE355" s="10" t="n"/>
+      <c r="AF355" t="n">
+        <v>0.1067</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
@@ -24043,6 +26083,9 @@
       <c r="K356" t="n">
         <v>0.095</v>
       </c>
+      <c r="R356" t="n">
+        <v>0.8641</v>
+      </c>
       <c r="S356" s="1" t="n">
         <v>41</v>
       </c>
@@ -24060,6 +26103,9 @@
       </c>
       <c r="AD356" s="10" t="n"/>
       <c r="AE356" s="10" t="n"/>
+      <c r="AF356" t="n">
+        <v>0.0975</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
@@ -24086,6 +26132,9 @@
       <c r="K357" t="n">
         <v>0.09959999999999999</v>
       </c>
+      <c r="R357" t="n">
+        <v>0.8788</v>
+      </c>
       <c r="S357" s="1" t="n">
         <v>42</v>
       </c>
@@ -24103,6 +26152,9 @@
       </c>
       <c r="AD357" s="10" t="n"/>
       <c r="AE357" s="10" t="n"/>
+      <c r="AF357" t="n">
+        <v>0.1151</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
@@ -24129,6 +26181,9 @@
       <c r="K358" t="n">
         <v>0.0999</v>
       </c>
+      <c r="R358" t="n">
+        <v>0.9288999999999999</v>
+      </c>
       <c r="S358" s="1" t="n">
         <v>43</v>
       </c>
@@ -24146,6 +26201,9 @@
       </c>
       <c r="AD358" s="10" t="n"/>
       <c r="AE358" s="10" t="n"/>
+      <c r="AF358" t="n">
+        <v>0.1131</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
@@ -24172,6 +26230,9 @@
       <c r="K359" t="n">
         <v>0.1</v>
       </c>
+      <c r="R359" t="n">
+        <v>0.8987000000000001</v>
+      </c>
       <c r="S359" s="1" t="n">
         <v>44</v>
       </c>
@@ -24189,6 +26250,9 @@
       </c>
       <c r="AD359" s="10" t="n"/>
       <c r="AE359" s="10" t="n"/>
+      <c r="AF359" t="n">
+        <v>0.1038</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
@@ -24215,6 +26279,9 @@
       <c r="K360" t="n">
         <v>0.1017</v>
       </c>
+      <c r="R360" t="n">
+        <v>0.8635</v>
+      </c>
       <c r="S360" s="1" t="n">
         <v>45</v>
       </c>
@@ -24232,6 +26299,9 @@
       </c>
       <c r="AD360" s="10" t="n"/>
       <c r="AE360" s="10" t="n"/>
+      <c r="AF360" t="n">
+        <v>0.109</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
@@ -24258,6 +26328,9 @@
       <c r="K361" t="n">
         <v>0.0989</v>
       </c>
+      <c r="R361" t="n">
+        <v>0.875</v>
+      </c>
       <c r="S361" s="1" t="n">
         <v>46</v>
       </c>
@@ -24275,6 +26348,9 @@
       </c>
       <c r="AD361" s="10" t="n"/>
       <c r="AE361" s="10" t="n"/>
+      <c r="AF361" t="n">
+        <v>0.1124</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
@@ -24301,6 +26377,9 @@
       <c r="K362" t="n">
         <v>0.098</v>
       </c>
+      <c r="R362" t="n">
+        <v>0.9453</v>
+      </c>
       <c r="S362" s="1" t="n">
         <v>47</v>
       </c>
@@ -24318,6 +26397,9 @@
       </c>
       <c r="AD362" s="10" t="n"/>
       <c r="AE362" s="10" t="n"/>
+      <c r="AF362" t="n">
+        <v>0.1012</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
@@ -24344,6 +26426,9 @@
       <c r="K363" t="n">
         <v>0.099</v>
       </c>
+      <c r="R363" t="n">
+        <v>0.9683</v>
+      </c>
       <c r="S363" s="1" t="n">
         <v>48</v>
       </c>
@@ -24361,6 +26446,9 @@
       </c>
       <c r="AD363" s="10" t="n"/>
       <c r="AE363" s="10" t="n"/>
+      <c r="AF363" t="n">
+        <v>0.1186</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
@@ -24387,6 +26475,9 @@
       <c r="K364" t="n">
         <v>0.0958</v>
       </c>
+      <c r="R364" t="n">
+        <v>0.9012</v>
+      </c>
       <c r="S364" s="1" t="n">
         <v>49</v>
       </c>
@@ -24404,6 +26495,9 @@
       </c>
       <c r="AD364" s="10" t="n"/>
       <c r="AE364" s="10" t="n"/>
+      <c r="AF364" t="n">
+        <v>0.1075</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
@@ -24430,6 +26524,9 @@
       <c r="K365" t="n">
         <v>0.09810000000000001</v>
       </c>
+      <c r="R365" t="n">
+        <v>0.886</v>
+      </c>
       <c r="S365" s="1" t="n">
         <v>50</v>
       </c>
@@ -24447,6 +26544,9 @@
       </c>
       <c r="AD365" s="10" t="n"/>
       <c r="AE365" s="10" t="n"/>
+      <c r="AF365" t="n">
+        <v>0.09909999999999999</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
@@ -24473,6 +26573,9 @@
       <c r="K366" t="n">
         <v>0.0961</v>
       </c>
+      <c r="R366" t="n">
+        <v>0.8705000000000001</v>
+      </c>
       <c r="S366" s="1" t="n">
         <v>51</v>
       </c>
@@ -24490,6 +26593,9 @@
       </c>
       <c r="AD366" s="10" t="n"/>
       <c r="AE366" s="10" t="n"/>
+      <c r="AF366" t="n">
+        <v>0.0984</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
@@ -24516,6 +26622,9 @@
       <c r="K367" t="n">
         <v>0.0988</v>
       </c>
+      <c r="R367" t="n">
+        <v>0.9546</v>
+      </c>
       <c r="S367" s="1" t="n">
         <v>52</v>
       </c>
@@ -24533,6 +26642,9 @@
       </c>
       <c r="AD367" s="10" t="n"/>
       <c r="AE367" s="10" t="n"/>
+      <c r="AF367" t="n">
+        <v>0.0989</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
@@ -24559,6 +26671,9 @@
       <c r="K368" t="n">
         <v>0.1009</v>
       </c>
+      <c r="R368" t="n">
+        <v>0.9347</v>
+      </c>
       <c r="S368" s="1" t="n">
         <v>53</v>
       </c>
@@ -24576,6 +26691,9 @@
       </c>
       <c r="AD368" s="10" t="n"/>
       <c r="AE368" s="10" t="n"/>
+      <c r="AF368" t="n">
+        <v>0.1071</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
@@ -24602,6 +26720,9 @@
       <c r="K369" t="n">
         <v>0.0997</v>
       </c>
+      <c r="R369" t="n">
+        <v>0.9483</v>
+      </c>
       <c r="S369" s="1" t="n">
         <v>54</v>
       </c>
@@ -24619,6 +26740,9 @@
       </c>
       <c r="AD369" s="10" t="n"/>
       <c r="AE369" s="10" t="n"/>
+      <c r="AF369" t="n">
+        <v>0.09569999999999999</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
@@ -24645,6 +26769,9 @@
       <c r="K370" t="n">
         <v>0.1027</v>
       </c>
+      <c r="R370" t="n">
+        <v>0.9857</v>
+      </c>
       <c r="S370" s="1" t="n">
         <v>55</v>
       </c>
@@ -24662,6 +26789,9 @@
       </c>
       <c r="AD370" s="10" t="n"/>
       <c r="AE370" s="10" t="n"/>
+      <c r="AF370" t="n">
+        <v>0.1086</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
@@ -24688,6 +26818,9 @@
       <c r="K371" t="n">
         <v>0.1</v>
       </c>
+      <c r="R371" t="n">
+        <v>0.9865</v>
+      </c>
       <c r="S371" s="1" t="n">
         <v>56</v>
       </c>
@@ -24705,6 +26838,9 @@
       </c>
       <c r="AD371" s="10" t="n"/>
       <c r="AE371" s="10" t="n"/>
+      <c r="AF371" t="n">
+        <v>0.1041</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
@@ -24731,6 +26867,9 @@
       <c r="K372" t="n">
         <v>0.09950000000000001</v>
       </c>
+      <c r="R372" t="n">
+        <v>0.9675</v>
+      </c>
       <c r="S372" s="1" t="n">
         <v>57</v>
       </c>
@@ -24748,6 +26887,9 @@
       </c>
       <c r="AD372" s="10" t="n"/>
       <c r="AE372" s="10" t="n"/>
+      <c r="AF372" t="n">
+        <v>0.1086</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
@@ -24774,6 +26916,9 @@
       <c r="K373" t="n">
         <v>0.0988</v>
       </c>
+      <c r="R373" t="n">
+        <v>0.9459</v>
+      </c>
       <c r="S373" s="1" t="n">
         <v>58</v>
       </c>
@@ -24791,6 +26936,9 @@
       </c>
       <c r="AD373" s="10" t="n"/>
       <c r="AE373" s="10" t="n"/>
+      <c r="AF373" t="n">
+        <v>0.1077</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
@@ -24817,6 +26965,9 @@
       <c r="K374" t="n">
         <v>0.1024</v>
       </c>
+      <c r="R374" t="n">
+        <v>0.9024</v>
+      </c>
       <c r="S374" s="1" t="n">
         <v>59</v>
       </c>
@@ -24834,6 +26985,9 @@
       </c>
       <c r="AD374" s="10" t="n"/>
       <c r="AE374" s="10" t="n"/>
+      <c r="AF374" t="n">
+        <v>0.09660000000000001</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
@@ -24860,6 +27014,9 @@
       <c r="K375" t="n">
         <v>0.1038</v>
       </c>
+      <c r="R375" t="n">
+        <v>0.9126</v>
+      </c>
       <c r="S375" s="1" t="n">
         <v>60</v>
       </c>
@@ -24877,6 +27034,9 @@
       </c>
       <c r="AD375" s="10" t="n"/>
       <c r="AE375" s="10" t="n"/>
+      <c r="AF375" t="n">
+        <v>0.0961</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
@@ -24903,6 +27063,9 @@
       <c r="K376" t="n">
         <v>0.1005</v>
       </c>
+      <c r="R376" t="n">
+        <v>0.8904</v>
+      </c>
       <c r="S376" s="1" t="n">
         <v>61</v>
       </c>
@@ -24920,6 +27083,9 @@
       </c>
       <c r="AD376" s="10" t="n"/>
       <c r="AE376" s="10" t="n"/>
+      <c r="AF376" t="n">
+        <v>0.1027</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
@@ -24946,6 +27112,9 @@
       <c r="K377" t="n">
         <v>0.1008</v>
       </c>
+      <c r="R377" t="n">
+        <v>0.9340000000000001</v>
+      </c>
       <c r="S377" s="1" t="n">
         <v>62</v>
       </c>
@@ -24963,6 +27132,9 @@
       </c>
       <c r="AD377" s="10" t="n"/>
       <c r="AE377" s="10" t="n"/>
+      <c r="AF377" t="n">
+        <v>0.1066</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
@@ -24989,6 +27161,9 @@
       <c r="K378" t="n">
         <v>0.0999</v>
       </c>
+      <c r="R378" t="n">
+        <v>0.92</v>
+      </c>
       <c r="S378" s="1" t="n">
         <v>63</v>
       </c>
@@ -25006,6 +27181,9 @@
       </c>
       <c r="AD378" s="10" t="n"/>
       <c r="AE378" s="10" t="n"/>
+      <c r="AF378" t="n">
+        <v>0.1034</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
@@ -25032,6 +27210,9 @@
       <c r="K379" t="n">
         <v>0.09569999999999999</v>
       </c>
+      <c r="R379" t="n">
+        <v>0.9014</v>
+      </c>
       <c r="S379" s="1" t="n">
         <v>64</v>
       </c>
@@ -25049,6 +27230,9 @@
       </c>
       <c r="AD379" s="10" t="n"/>
       <c r="AE379" s="10" t="n"/>
+      <c r="AF379" t="n">
+        <v>0.0944</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
@@ -25075,6 +27259,9 @@
       <c r="K380" t="n">
         <v>0.0983</v>
       </c>
+      <c r="R380" t="n">
+        <v>0.9147</v>
+      </c>
       <c r="S380" s="1" t="n">
         <v>65</v>
       </c>
@@ -25092,6 +27279,9 @@
       </c>
       <c r="AD380" s="10" t="n"/>
       <c r="AE380" s="10" t="n"/>
+      <c r="AF380" t="n">
+        <v>0.1048</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
@@ -25118,6 +27308,9 @@
       <c r="K381" t="n">
         <v>0.09909999999999999</v>
       </c>
+      <c r="R381" t="n">
+        <v>0.8931</v>
+      </c>
       <c r="S381" s="1" t="n">
         <v>66</v>
       </c>
@@ -25135,6 +27328,9 @@
       </c>
       <c r="AD381" s="10" t="n"/>
       <c r="AE381" s="10" t="n"/>
+      <c r="AF381" t="n">
+        <v>0.1016</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
@@ -25161,6 +27357,9 @@
       <c r="K382" t="n">
         <v>0.1003</v>
       </c>
+      <c r="R382" t="n">
+        <v>0.9615</v>
+      </c>
       <c r="S382" s="1" t="n">
         <v>67</v>
       </c>
@@ -25178,6 +27377,9 @@
       </c>
       <c r="AD382" s="10" t="n"/>
       <c r="AE382" s="10" t="n"/>
+      <c r="AF382" t="n">
+        <v>0.1088</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
@@ -25204,6 +27406,9 @@
       <c r="K383" t="n">
         <v>0.0983</v>
       </c>
+      <c r="R383" t="n">
+        <v>0.974</v>
+      </c>
       <c r="S383" s="1" t="n">
         <v>68</v>
       </c>
@@ -25221,6 +27426,9 @@
       </c>
       <c r="AD383" s="10" t="n"/>
       <c r="AE383" s="10" t="n"/>
+      <c r="AF383" t="n">
+        <v>0.0989</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
@@ -25247,6 +27455,9 @@
       <c r="K384" t="n">
         <v>0.1007</v>
       </c>
+      <c r="R384" t="n">
+        <v>0.945</v>
+      </c>
       <c r="S384" s="1" t="n">
         <v>69</v>
       </c>
@@ -25264,6 +27475,9 @@
       </c>
       <c r="AD384" s="10" t="n"/>
       <c r="AE384" s="10" t="n"/>
+      <c r="AF384" t="n">
+        <v>0.1001</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
@@ -25290,6 +27504,9 @@
       <c r="K385" t="n">
         <v>0.1026</v>
       </c>
+      <c r="R385" t="n">
+        <v>0.9669</v>
+      </c>
       <c r="S385" s="1" t="n">
         <v>70</v>
       </c>
@@ -25307,6 +27524,9 @@
       </c>
       <c r="AD385" s="10" t="n"/>
       <c r="AE385" s="10" t="n"/>
+      <c r="AF385" t="n">
+        <v>0.09710000000000001</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
@@ -25333,6 +27553,9 @@
       <c r="K386" t="n">
         <v>0.1021</v>
       </c>
+      <c r="R386" t="n">
+        <v>0.9879</v>
+      </c>
       <c r="S386" s="1" t="n">
         <v>71</v>
       </c>
@@ -25350,6 +27573,9 @@
       </c>
       <c r="AD386" s="10" t="n"/>
       <c r="AE386" s="10" t="n"/>
+      <c r="AF386" t="n">
+        <v>0.1144</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
@@ -25376,6 +27602,9 @@
       <c r="K387" t="n">
         <v>0.1015</v>
       </c>
+      <c r="R387" t="n">
+        <v>0.9131</v>
+      </c>
       <c r="S387" s="1" t="n">
         <v>72</v>
       </c>
@@ -25393,6 +27622,9 @@
       </c>
       <c r="AD387" s="10" t="n"/>
       <c r="AE387" s="10" t="n"/>
+      <c r="AF387" t="n">
+        <v>0.1033</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
@@ -25419,6 +27651,9 @@
       <c r="K388" t="n">
         <v>0.1052</v>
       </c>
+      <c r="R388" t="n">
+        <v>0.883</v>
+      </c>
       <c r="S388" s="1" t="n">
         <v>73</v>
       </c>
@@ -25436,6 +27671,9 @@
       </c>
       <c r="AD388" s="10" t="n"/>
       <c r="AE388" s="10" t="n"/>
+      <c r="AF388" t="n">
+        <v>0.1058</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
@@ -25462,6 +27700,9 @@
       <c r="K389" t="n">
         <v>0.1042</v>
       </c>
+      <c r="R389" t="n">
+        <v>0.9443</v>
+      </c>
       <c r="S389" s="1" t="n">
         <v>74</v>
       </c>
@@ -25479,6 +27720,9 @@
       </c>
       <c r="AD389" s="10" t="n"/>
       <c r="AE389" s="10" t="n"/>
+      <c r="AF389" t="n">
+        <v>0.1074</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
@@ -25505,6 +27749,9 @@
       <c r="K390" t="n">
         <v>0.0993</v>
       </c>
+      <c r="R390" t="n">
+        <v>0.9343</v>
+      </c>
       <c r="S390" s="1" t="n">
         <v>75</v>
       </c>
@@ -25522,6 +27769,9 @@
       </c>
       <c r="AD390" s="10" t="n"/>
       <c r="AE390" s="10" t="n"/>
+      <c r="AF390" t="n">
+        <v>0.1012</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
@@ -25548,6 +27798,9 @@
       <c r="K391" t="n">
         <v>0.1032</v>
       </c>
+      <c r="R391" t="n">
+        <v>0.9606</v>
+      </c>
       <c r="S391" s="1" t="n">
         <v>76</v>
       </c>
@@ -25565,6 +27818,9 @@
       </c>
       <c r="AD391" s="10" t="n"/>
       <c r="AE391" s="10" t="n"/>
+      <c r="AF391" t="n">
+        <v>0.1087</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
@@ -25591,6 +27847,9 @@
       <c r="K392" t="n">
         <v>0.1014</v>
       </c>
+      <c r="R392" t="n">
+        <v>0.9734</v>
+      </c>
       <c r="S392" s="1" t="n">
         <v>77</v>
       </c>
@@ -25608,6 +27867,9 @@
       </c>
       <c r="AD392" s="10" t="n"/>
       <c r="AE392" s="10" t="n"/>
+      <c r="AF392" t="n">
+        <v>0.1065</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
@@ -25634,6 +27896,9 @@
       <c r="K393" t="n">
         <v>0.09760000000000001</v>
       </c>
+      <c r="R393" t="n">
+        <v>0.9758</v>
+      </c>
       <c r="S393" s="1" t="n">
         <v>78</v>
       </c>
@@ -25651,6 +27916,9 @@
       </c>
       <c r="AD393" s="10" t="n"/>
       <c r="AE393" s="10" t="n"/>
+      <c r="AF393" t="n">
+        <v>0.1049</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
@@ -25677,6 +27945,9 @@
       <c r="K394" t="n">
         <v>0.101</v>
       </c>
+      <c r="R394" t="n">
+        <v>0.9336</v>
+      </c>
       <c r="S394" s="1" t="n">
         <v>79</v>
       </c>
@@ -25694,6 +27965,9 @@
       </c>
       <c r="AD394" s="10" t="n"/>
       <c r="AE394" s="10" t="n"/>
+      <c r="AF394" t="n">
+        <v>0.0934</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
@@ -25720,6 +27994,9 @@
       <c r="K395" t="n">
         <v>0.1013</v>
       </c>
+      <c r="R395" t="n">
+        <v>0.9769</v>
+      </c>
       <c r="S395" s="1" t="n">
         <v>80</v>
       </c>
@@ -25737,6 +28014,9 @@
       </c>
       <c r="AD395" s="10" t="n"/>
       <c r="AE395" s="10" t="n"/>
+      <c r="AF395" t="n">
+        <v>0.1086</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
@@ -25763,6 +28043,9 @@
       <c r="K396" t="n">
         <v>0.1015</v>
       </c>
+      <c r="R396" t="n">
+        <v>0.9475</v>
+      </c>
       <c r="S396" s="1" t="n">
         <v>81</v>
       </c>
@@ -25780,6 +28063,9 @@
       </c>
       <c r="AD396" s="10" t="n"/>
       <c r="AE396" s="10" t="n"/>
+      <c r="AF396" t="n">
+        <v>0.1054</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
@@ -25806,6 +28092,9 @@
       <c r="K397" t="n">
         <v>0.09710000000000001</v>
       </c>
+      <c r="R397" t="n">
+        <v>0.9453</v>
+      </c>
       <c r="S397" s="1" t="n">
         <v>82</v>
       </c>
@@ -25823,6 +28112,9 @@
       </c>
       <c r="AD397" s="10" t="n"/>
       <c r="AE397" s="10" t="n"/>
+      <c r="AF397" t="n">
+        <v>0.1018</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
@@ -25849,6 +28141,9 @@
       <c r="K398" t="n">
         <v>0.1003</v>
       </c>
+      <c r="R398" t="n">
+        <v>0.9738</v>
+      </c>
       <c r="S398" s="1" t="n">
         <v>83</v>
       </c>
@@ -25866,6 +28161,9 @@
       </c>
       <c r="AD398" s="10" t="n"/>
       <c r="AE398" s="10" t="n"/>
+      <c r="AF398" t="n">
+        <v>0.1026</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
@@ -25892,6 +28190,9 @@
       <c r="K399" t="n">
         <v>0.09760000000000001</v>
       </c>
+      <c r="R399" t="n">
+        <v>0.9424</v>
+      </c>
       <c r="S399" s="1" t="n">
         <v>84</v>
       </c>
@@ -25909,6 +28210,9 @@
       </c>
       <c r="AD399" s="10" t="n"/>
       <c r="AE399" s="10" t="n"/>
+      <c r="AF399" t="n">
+        <v>0.1018</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
@@ -25935,6 +28239,9 @@
       <c r="K400" t="n">
         <v>0.099</v>
       </c>
+      <c r="R400" t="n">
+        <v>0.9318</v>
+      </c>
       <c r="S400" s="1" t="n">
         <v>85</v>
       </c>
@@ -25952,6 +28259,9 @@
       </c>
       <c r="AD400" s="10" t="n"/>
       <c r="AE400" s="10" t="n"/>
+      <c r="AF400" t="n">
+        <v>0.0956</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
@@ -25978,6 +28288,9 @@
       <c r="K401" t="n">
         <v>0.1026</v>
       </c>
+      <c r="R401" t="n">
+        <v>0.9518</v>
+      </c>
       <c r="S401" s="1" t="n">
         <v>86</v>
       </c>
@@ -25995,6 +28308,9 @@
       </c>
       <c r="AD401" s="10" t="n"/>
       <c r="AE401" s="10" t="n"/>
+      <c r="AF401" t="n">
+        <v>0.1031</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="n">
@@ -26021,6 +28337,9 @@
       <c r="K402" t="n">
         <v>0.1036</v>
       </c>
+      <c r="R402" t="n">
+        <v>0.95</v>
+      </c>
       <c r="S402" s="1" t="n">
         <v>87</v>
       </c>
@@ -26038,6 +28357,9 @@
       </c>
       <c r="AD402" s="10" t="n"/>
       <c r="AE402" s="10" t="n"/>
+      <c r="AF402" t="n">
+        <v>0.1059</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
@@ -26064,6 +28386,9 @@
       <c r="K403" t="n">
         <v>0.09229999999999999</v>
       </c>
+      <c r="R403" t="n">
+        <v>0.9529</v>
+      </c>
       <c r="S403" s="1" t="n">
         <v>88</v>
       </c>
@@ -26081,6 +28406,9 @@
       </c>
       <c r="AD403" s="10" t="n"/>
       <c r="AE403" s="10" t="n"/>
+      <c r="AF403" t="n">
+        <v>0.1026</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
@@ -26107,6 +28435,9 @@
       <c r="K404" t="n">
         <v>0.0931</v>
       </c>
+      <c r="R404" t="n">
+        <v>0.9696</v>
+      </c>
       <c r="S404" s="1" t="n">
         <v>89</v>
       </c>
@@ -26124,6 +28455,9 @@
       </c>
       <c r="AD404" s="10" t="n"/>
       <c r="AE404" s="10" t="n"/>
+      <c r="AF404" t="n">
+        <v>0.1088</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
@@ -26150,6 +28484,9 @@
       <c r="K405" t="n">
         <v>0.1019</v>
       </c>
+      <c r="R405" t="n">
+        <v>0.9413</v>
+      </c>
       <c r="S405" s="1" t="n">
         <v>90</v>
       </c>
@@ -26167,6 +28504,9 @@
       </c>
       <c r="AD405" s="10" t="n"/>
       <c r="AE405" s="10" t="n"/>
+      <c r="AF405" t="n">
+        <v>0.1053</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
@@ -26193,6 +28533,9 @@
       <c r="K406" t="n">
         <v>0.09719999999999999</v>
       </c>
+      <c r="R406" t="n">
+        <v>0.952</v>
+      </c>
       <c r="S406" s="1" t="n">
         <v>91</v>
       </c>
@@ -26210,6 +28553,9 @@
       </c>
       <c r="AD406" s="10" t="n"/>
       <c r="AE406" s="10" t="n"/>
+      <c r="AF406" t="n">
+        <v>0.1037</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="1" t="n">
@@ -26236,6 +28582,9 @@
       <c r="K407" t="n">
         <v>0.09760000000000001</v>
       </c>
+      <c r="R407" t="n">
+        <v>0.9508</v>
+      </c>
       <c r="S407" s="1" t="n">
         <v>92</v>
       </c>
@@ -26253,6 +28602,9 @@
       </c>
       <c r="AD407" s="10" t="n"/>
       <c r="AE407" s="10" t="n"/>
+      <c r="AF407" t="n">
+        <v>0.1005</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
@@ -26279,6 +28631,9 @@
       <c r="K408" t="n">
         <v>0.0963</v>
       </c>
+      <c r="R408" t="n">
+        <v>0.9487</v>
+      </c>
       <c r="S408" s="1" t="n">
         <v>93</v>
       </c>
@@ -26296,6 +28651,9 @@
       </c>
       <c r="AD408" s="10" t="n"/>
       <c r="AE408" s="10" t="n"/>
+      <c r="AF408" t="n">
+        <v>0.1097</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
@@ -26322,6 +28680,9 @@
       <c r="K409" t="n">
         <v>0.09520000000000001</v>
       </c>
+      <c r="R409" t="n">
+        <v>0.9686</v>
+      </c>
       <c r="S409" s="1" t="n">
         <v>94</v>
       </c>
@@ -26339,6 +28700,9 @@
       </c>
       <c r="AD409" s="10" t="n"/>
       <c r="AE409" s="10" t="n"/>
+      <c r="AF409" t="n">
+        <v>0.1061</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
@@ -26362,6 +28726,9 @@
       <c r="K410" t="n">
         <v>0.09859999999999999</v>
       </c>
+      <c r="R410" t="n">
+        <v>0.9696</v>
+      </c>
       <c r="S410" s="1" t="n">
         <v>95</v>
       </c>
@@ -26379,6 +28746,9 @@
       </c>
       <c r="AD410" s="10" t="n"/>
       <c r="AE410" s="10" t="n"/>
+      <c r="AF410" t="n">
+        <v>0.1083</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="n">
@@ -26402,6 +28772,9 @@
       <c r="K411" t="n">
         <v>0.09909999999999999</v>
       </c>
+      <c r="R411" t="n">
+        <v>0.9417</v>
+      </c>
       <c r="S411" s="1" t="n">
         <v>96</v>
       </c>
@@ -26419,6 +28792,9 @@
       </c>
       <c r="AD411" s="10" t="n"/>
       <c r="AE411" s="10" t="n"/>
+      <c r="AF411" t="n">
+        <v>0.1018</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
@@ -26442,6 +28818,9 @@
       <c r="K412" t="n">
         <v>0.1043</v>
       </c>
+      <c r="R412" t="n">
+        <v>0.9655</v>
+      </c>
       <c r="S412" s="1" t="n">
         <v>97</v>
       </c>
@@ -26459,6 +28838,9 @@
       </c>
       <c r="AD412" s="10" t="n"/>
       <c r="AE412" s="10" t="n"/>
+      <c r="AF412" t="n">
+        <v>0.1019</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
@@ -26482,6 +28864,9 @@
       <c r="K413" t="n">
         <v>0.1023</v>
       </c>
+      <c r="R413" t="n">
+        <v>0.9867</v>
+      </c>
       <c r="S413" s="1" t="n">
         <v>98</v>
       </c>
@@ -26499,6 +28884,9 @@
       </c>
       <c r="AD413" s="10" t="n"/>
       <c r="AE413" s="10" t="n"/>
+      <c r="AF413" t="n">
+        <v>0.1103</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="n">
@@ -26522,6 +28910,9 @@
       <c r="K414" t="n">
         <v>0.0956</v>
       </c>
+      <c r="R414" t="n">
+        <v>0.9837</v>
+      </c>
       <c r="S414" s="1" t="n">
         <v>99</v>
       </c>
@@ -26539,6 +28930,9 @@
       </c>
       <c r="AD414" s="10" t="n"/>
       <c r="AE414" s="10" t="n"/>
+      <c r="AF414" t="n">
+        <v>0.1009</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
@@ -26562,6 +28956,9 @@
       <c r="K415" t="n">
         <v>0.09279999999999999</v>
       </c>
+      <c r="R415" t="n">
+        <v>0.9943</v>
+      </c>
       <c r="S415" s="1" t="n">
         <v>100</v>
       </c>
@@ -26579,6 +28976,9 @@
       </c>
       <c r="AD415" s="10" t="n"/>
       <c r="AE415" s="10" t="n"/>
+      <c r="AF415" t="n">
+        <v>0.1101</v>
+      </c>
     </row>
     <row r="416">
       <c r="AD416" s="10" t="n"/>

--- a/CIFAR_Global.xlsx
+++ b/CIFAR_Global.xlsx
@@ -8383,7 +8383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG504"/>
+  <dimension ref="A1:AI504"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
   <cols>
     <col width="15.1640625" customWidth="1" style="15" min="1" max="1"/>
@@ -8658,6 +8658,9 @@
       <c r="AG5" t="n">
         <v>0.1394</v>
       </c>
+      <c r="AI5" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -8723,6 +8726,9 @@
       <c r="AG6" t="n">
         <v>0.1707</v>
       </c>
+      <c r="AI6" t="n">
+        <v>0.1174</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -8788,6 +8794,9 @@
       <c r="AG7" t="n">
         <v>0.1938</v>
       </c>
+      <c r="AI7" t="n">
+        <v>0.1047</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -8853,6 +8862,9 @@
       <c r="AG8" t="n">
         <v>0.2288</v>
       </c>
+      <c r="AI8" t="n">
+        <v>0.1551</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -8915,6 +8927,9 @@
       <c r="AF9" t="n">
         <v>0.4428</v>
       </c>
+      <c r="AI9" t="n">
+        <v>0.1579</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -8974,6 +8989,9 @@
       <c r="AF10" t="n">
         <v>0.4663</v>
       </c>
+      <c r="AI10" t="n">
+        <v>0.1858</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -9033,6 +9051,9 @@
       <c r="AF11" t="n">
         <v>0.4921</v>
       </c>
+      <c r="AI11" t="n">
+        <v>0.1743</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -9092,6 +9113,9 @@
       <c r="AF12" t="n">
         <v>0.4943</v>
       </c>
+      <c r="AI12" t="n">
+        <v>0.2206</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -9151,6 +9175,9 @@
       <c r="AF13" t="n">
         <v>0.5113</v>
       </c>
+      <c r="AI13" t="n">
+        <v>0.242</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -9210,6 +9237,9 @@
       <c r="AF14" t="n">
         <v>0.5191</v>
       </c>
+      <c r="AI14" t="n">
+        <v>0.2561</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -9263,6 +9293,9 @@
       <c r="AF15" t="n">
         <v>0.529</v>
       </c>
+      <c r="AI15" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -9316,6 +9349,9 @@
       <c r="AF16" t="n">
         <v>0.5315</v>
       </c>
+      <c r="AI16" t="n">
+        <v>0.1969</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -9369,6 +9405,9 @@
       <c r="AF17" t="n">
         <v>0.5433</v>
       </c>
+      <c r="AI17" t="n">
+        <v>0.2317</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -9422,6 +9461,9 @@
       <c r="AF18" t="n">
         <v>0.5454</v>
       </c>
+      <c r="AI18" t="n">
+        <v>0.2138</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -9475,6 +9517,9 @@
       <c r="AF19" t="n">
         <v>0.5534</v>
       </c>
+      <c r="AI19" t="n">
+        <v>0.1984</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -9528,6 +9573,9 @@
       <c r="AF20" t="n">
         <v>0.5506</v>
       </c>
+      <c r="AI20" t="n">
+        <v>0.2517</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -9581,6 +9629,9 @@
       <c r="AF21" t="n">
         <v>0.4998</v>
       </c>
+      <c r="AI21" t="n">
+        <v>0.2595</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -9634,6 +9685,9 @@
       <c r="AF22" t="n">
         <v>0.545</v>
       </c>
+      <c r="AI22" t="n">
+        <v>0.2305</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -9687,6 +9741,9 @@
       <c r="AF23" t="n">
         <v>0.5599</v>
       </c>
+      <c r="AI23" t="n">
+        <v>0.3333</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -9740,6 +9797,9 @@
       <c r="AF24" t="n">
         <v>0.5652</v>
       </c>
+      <c r="AI24" t="n">
+        <v>0.2833</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -9793,6 +9853,9 @@
       <c r="AF25" t="n">
         <v>0.5721000000000001</v>
       </c>
+      <c r="AI25" t="n">
+        <v>0.302</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -9846,6 +9909,9 @@
       <c r="AF26" t="n">
         <v>0.5728</v>
       </c>
+      <c r="AI26" t="n">
+        <v>0.3055</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -9899,6 +9965,9 @@
       <c r="AF27" t="n">
         <v>0.5707</v>
       </c>
+      <c r="AI27" t="n">
+        <v>0.3172</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -9952,6 +10021,9 @@
       <c r="AF28" t="n">
         <v>0.575</v>
       </c>
+      <c r="AI28" t="n">
+        <v>0.2667</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -10005,6 +10077,9 @@
       <c r="AF29" t="n">
         <v>0.5803</v>
       </c>
+      <c r="AI29" t="n">
+        <v>0.2967</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -10058,6 +10133,9 @@
       <c r="AF30" t="n">
         <v>0.579</v>
       </c>
+      <c r="AI30" t="n">
+        <v>0.2628</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -10111,6 +10189,9 @@
       <c r="AF31" t="n">
         <v>0.5832000000000001</v>
       </c>
+      <c r="AI31" t="n">
+        <v>0.2512</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -10164,6 +10245,9 @@
       <c r="AF32" t="n">
         <v>0.5775</v>
       </c>
+      <c r="AI32" t="n">
+        <v>0.2304</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -10217,6 +10301,9 @@
       <c r="AF33" t="n">
         <v>0.5831</v>
       </c>
+      <c r="AI33" t="n">
+        <v>0.1366</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -10270,6 +10357,9 @@
       <c r="AF34" t="n">
         <v>0.585</v>
       </c>
+      <c r="AI34" t="n">
+        <v>0.2675</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -10323,6 +10413,9 @@
       <c r="AF35" t="n">
         <v>0.594</v>
       </c>
+      <c r="AI35" t="n">
+        <v>0.2737</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -10376,6 +10469,9 @@
       <c r="AF36" t="n">
         <v>0.5963000000000001</v>
       </c>
+      <c r="AI36" t="n">
+        <v>0.1865</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -10429,6 +10525,9 @@
       <c r="AF37" t="n">
         <v>0.5869</v>
       </c>
+      <c r="AI37" t="n">
+        <v>0.265</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -10482,6 +10581,9 @@
       <c r="AF38" t="n">
         <v>0.5866</v>
       </c>
+      <c r="AI38" t="n">
+        <v>0.2295</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -10535,6 +10637,9 @@
       <c r="AF39" t="n">
         <v>0.555</v>
       </c>
+      <c r="AI39" t="n">
+        <v>0.236</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -10588,6 +10693,9 @@
       <c r="AF40" t="n">
         <v>0.5855</v>
       </c>
+      <c r="AI40" t="n">
+        <v>0.2516</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -10641,6 +10749,9 @@
       <c r="AF41" t="n">
         <v>0.5727</v>
       </c>
+      <c r="AI41" t="n">
+        <v>0.1679</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -10694,6 +10805,9 @@
       <c r="AF42" t="n">
         <v>0.5913</v>
       </c>
+      <c r="AI42" t="n">
+        <v>0.191</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -10747,6 +10861,9 @@
       <c r="AF43" t="n">
         <v>0.6002</v>
       </c>
+      <c r="AI43" t="n">
+        <v>0.2201</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -10800,6 +10917,9 @@
       <c r="AF44" t="n">
         <v>0.596</v>
       </c>
+      <c r="AI44" t="n">
+        <v>0.1767</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -10853,6 +10973,9 @@
       <c r="AF45" t="n">
         <v>0.5994</v>
       </c>
+      <c r="AI45" t="n">
+        <v>0.1789</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -10906,6 +11029,9 @@
       <c r="AF46" t="n">
         <v>0.6015</v>
       </c>
+      <c r="AI46" t="n">
+        <v>0.2614</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -10959,6 +11085,9 @@
       <c r="AF47" t="n">
         <v>0.6054</v>
       </c>
+      <c r="AI47" t="n">
+        <v>0.2344</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -11012,6 +11141,9 @@
       <c r="AF48" t="n">
         <v>0.6119</v>
       </c>
+      <c r="AI48" t="n">
+        <v>0.1859</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -11065,6 +11197,9 @@
       <c r="AF49" t="n">
         <v>0.5997</v>
       </c>
+      <c r="AI49" t="n">
+        <v>0.2143</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -11118,6 +11253,9 @@
       <c r="AF50" t="n">
         <v>0.6078</v>
       </c>
+      <c r="AI50" t="n">
+        <v>0.252</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -11171,6 +11309,9 @@
       <c r="AF51" t="n">
         <v>0.6089</v>
       </c>
+      <c r="AI51" t="n">
+        <v>0.2732</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -11224,6 +11365,9 @@
       <c r="AF52" t="n">
         <v>0.5989</v>
       </c>
+      <c r="AI52" t="n">
+        <v>0.2699</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -11277,6 +11421,9 @@
       <c r="AF53" t="n">
         <v>0.6074000000000001</v>
       </c>
+      <c r="AI53" t="n">
+        <v>0.3313</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -11330,6 +11477,9 @@
       <c r="AF54" t="n">
         <v>0.6108</v>
       </c>
+      <c r="AI54" t="n">
+        <v>0.2501</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -11383,6 +11533,9 @@
       <c r="AF55" t="n">
         <v>0.6139</v>
       </c>
+      <c r="AI55" t="n">
+        <v>0.247</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -11436,6 +11589,9 @@
       <c r="AF56" t="n">
         <v>0.6116</v>
       </c>
+      <c r="AI56" t="n">
+        <v>0.2451</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -11489,6 +11645,9 @@
       <c r="AF57" t="n">
         <v>0.6022</v>
       </c>
+      <c r="AI57" t="n">
+        <v>0.2065</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -11542,6 +11701,9 @@
       <c r="AF58" t="n">
         <v>0.6011</v>
       </c>
+      <c r="AI58" t="n">
+        <v>0.2769</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -11595,6 +11757,9 @@
       <c r="AF59" t="n">
         <v>0.6026</v>
       </c>
+      <c r="AI59" t="n">
+        <v>0.3128</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -11648,6 +11813,9 @@
       <c r="AF60" t="n">
         <v>0.6157</v>
       </c>
+      <c r="AI60" t="n">
+        <v>0.2933</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -11701,6 +11869,9 @@
       <c r="AF61" t="n">
         <v>0.6158</v>
       </c>
+      <c r="AI61" t="n">
+        <v>0.2086</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -11754,6 +11925,9 @@
       <c r="AF62" t="n">
         <v>0.6207</v>
       </c>
+      <c r="AI62" t="n">
+        <v>0.2464</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -11807,6 +11981,9 @@
       <c r="AF63" t="n">
         <v>0.6163999999999999</v>
       </c>
+      <c r="AI63" t="n">
+        <v>0.2597</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -11860,6 +12037,9 @@
       <c r="AF64" t="n">
         <v>0.6199</v>
       </c>
+      <c r="AI64" t="n">
+        <v>0.2722</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -11913,6 +12093,9 @@
       <c r="AF65" t="n">
         <v>0.617</v>
       </c>
+      <c r="AI65" t="n">
+        <v>0.204</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -11966,6 +12149,9 @@
       <c r="AF66" t="n">
         <v>0.6274</v>
       </c>
+      <c r="AI66" t="n">
+        <v>0.266</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -12019,6 +12205,9 @@
       <c r="AF67" t="n">
         <v>0.6188</v>
       </c>
+      <c r="AI67" t="n">
+        <v>0.3161</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -12072,6 +12261,9 @@
       <c r="AF68" t="n">
         <v>0.6215000000000001</v>
       </c>
+      <c r="AI68" t="n">
+        <v>0.1772</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -12125,6 +12317,9 @@
       <c r="AF69" t="n">
         <v>0.6187</v>
       </c>
+      <c r="AI69" t="n">
+        <v>0.2764</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -12178,6 +12373,9 @@
       <c r="AF70" t="n">
         <v>0.6216</v>
       </c>
+      <c r="AI70" t="n">
+        <v>0.2791</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -12231,6 +12429,9 @@
       <c r="AF71" t="n">
         <v>0.6223</v>
       </c>
+      <c r="AI71" t="n">
+        <v>0.2436</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -12284,6 +12485,9 @@
       <c r="AF72" t="n">
         <v>0.6237</v>
       </c>
+      <c r="AI72" t="n">
+        <v>0.2671</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -12337,6 +12541,9 @@
       <c r="AF73" t="n">
         <v>0.6213</v>
       </c>
+      <c r="AI73" t="n">
+        <v>0.2701</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -12390,6 +12597,9 @@
       <c r="AF74" t="n">
         <v>0.622</v>
       </c>
+      <c r="AI74" t="n">
+        <v>0.3114</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -12443,6 +12653,9 @@
       <c r="AF75" t="n">
         <v>0.621</v>
       </c>
+      <c r="AI75" t="n">
+        <v>0.2347</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -12496,6 +12709,9 @@
       <c r="AF76" t="n">
         <v>0.6233</v>
       </c>
+      <c r="AI76" t="n">
+        <v>0.2638</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -12549,6 +12765,9 @@
       <c r="AF77" t="n">
         <v>0.6254999999999999</v>
       </c>
+      <c r="AI77" t="n">
+        <v>0.2711</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -12602,6 +12821,9 @@
       <c r="AF78" t="n">
         <v>0.6232</v>
       </c>
+      <c r="AI78" t="n">
+        <v>0.3036</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -12655,6 +12877,9 @@
       <c r="AF79" t="n">
         <v>0.6225000000000001</v>
       </c>
+      <c r="AI79" t="n">
+        <v>0.279</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -12708,6 +12933,9 @@
       <c r="AF80" t="n">
         <v>0.6279</v>
       </c>
+      <c r="AI80" t="n">
+        <v>0.2574</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -12761,6 +12989,9 @@
       <c r="AF81" t="n">
         <v>0.63</v>
       </c>
+      <c r="AI81" t="n">
+        <v>0.2476</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -12814,6 +13045,9 @@
       <c r="AF82" t="n">
         <v>0.6276</v>
       </c>
+      <c r="AI82" t="n">
+        <v>0.2796</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -12867,6 +13101,9 @@
       <c r="AF83" t="n">
         <v>0.6253</v>
       </c>
+      <c r="AI83" t="n">
+        <v>0.2782</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -12920,6 +13157,9 @@
       <c r="AF84" t="n">
         <v>0.6251</v>
       </c>
+      <c r="AI84" t="n">
+        <v>0.2989</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -12973,6 +13213,9 @@
       <c r="AF85" t="n">
         <v>0.627</v>
       </c>
+      <c r="AI85" t="n">
+        <v>0.2783</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -13026,6 +13269,9 @@
       <c r="AF86" t="n">
         <v>0.6249</v>
       </c>
+      <c r="AI86" t="n">
+        <v>0.2674</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -13079,6 +13325,9 @@
       <c r="AF87" t="n">
         <v>0.6228</v>
       </c>
+      <c r="AI87" t="n">
+        <v>0.2523</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -13132,6 +13381,9 @@
       <c r="AF88" t="n">
         <v>0.6279</v>
       </c>
+      <c r="AI88" t="n">
+        <v>0.2505</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -13184,6 +13436,9 @@
       </c>
       <c r="AF89" t="n">
         <v>0.628</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>0.2463</v>
       </c>
     </row>
     <row r="90">
@@ -14055,6 +14310,9 @@
       <c r="AG108" t="n">
         <v>0.8</v>
       </c>
+      <c r="AI108" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -14116,6 +14374,9 @@
       <c r="AG109" t="n">
         <v>0.6666666666666666</v>
       </c>
+      <c r="AI109" t="n">
+        <v>0.5333333333333333</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -14176,6 +14437,9 @@
       </c>
       <c r="AG110" t="n">
         <v>0.6666666666666666</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>0.9333333333333333</v>
       </c>
     </row>
     <row r="111">
@@ -14238,6 +14502,9 @@
       <c r="AG111" t="n">
         <v>0.6</v>
       </c>
+      <c r="AI111" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -14296,6 +14563,9 @@
       <c r="AF112" t="n">
         <v>1</v>
       </c>
+      <c r="AI112" t="n">
+        <v>0.8666666666666667</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -14351,6 +14621,9 @@
       <c r="AF113" t="n">
         <v>1</v>
       </c>
+      <c r="AI113" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -14406,6 +14679,9 @@
       <c r="AF114" t="n">
         <v>1</v>
       </c>
+      <c r="AI114" t="n">
+        <v>0.8666666666666667</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -14461,6 +14737,9 @@
       <c r="AF115" t="n">
         <v>1</v>
       </c>
+      <c r="AI115" t="n">
+        <v>0.8666666666666667</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -14516,6 +14795,9 @@
       <c r="AF116" t="n">
         <v>1</v>
       </c>
+      <c r="AI116" t="n">
+        <v>0.7333333333333333</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -14571,6 +14853,9 @@
       <c r="AF117" t="n">
         <v>1</v>
       </c>
+      <c r="AI117" t="n">
+        <v>0.8666666666666667</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -14620,6 +14905,9 @@
       <c r="AF118" t="n">
         <v>1</v>
       </c>
+      <c r="AI118" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -14669,6 +14957,9 @@
       <c r="AF119" t="n">
         <v>1</v>
       </c>
+      <c r="AI119" t="n">
+        <v>0.9333333333333333</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -14718,6 +15009,9 @@
       <c r="AF120" t="n">
         <v>1</v>
       </c>
+      <c r="AI120" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -14767,6 +15061,9 @@
       <c r="AF121" t="n">
         <v>1</v>
       </c>
+      <c r="AI121" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -14816,6 +15113,9 @@
       <c r="AF122" t="n">
         <v>1</v>
       </c>
+      <c r="AI122" t="n">
+        <v>0.8461538461538461</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -14864,6 +15164,9 @@
       <c r="AE123" s="10" t="n"/>
       <c r="AF123" t="n">
         <v>1</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="124">
@@ -14914,6 +15217,9 @@
       <c r="AF124" t="n">
         <v>0.1666666666666667</v>
       </c>
+      <c r="AI124" t="n">
+        <v>0.5833333333333334</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -14963,6 +15269,9 @@
       <c r="AF125" t="n">
         <v>1</v>
       </c>
+      <c r="AI125" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -15011,6 +15320,9 @@
       <c r="AE126" s="10" t="n"/>
       <c r="AF126" t="n">
         <v>1</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.8461538461538461</v>
       </c>
     </row>
     <row r="127">
@@ -15061,6 +15373,9 @@
       <c r="AF127" t="n">
         <v>0.875</v>
       </c>
+      <c r="AI127" t="n">
+        <v>0.8181818181818182</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -15110,6 +15425,9 @@
       <c r="AF128" t="n">
         <v>1</v>
       </c>
+      <c r="AI128" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -15158,6 +15476,9 @@
       <c r="AE129" s="10" t="n"/>
       <c r="AF129" t="n">
         <v>1</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="130">
@@ -15208,6 +15529,9 @@
       <c r="AF130" t="n">
         <v>0.8333333333333334</v>
       </c>
+      <c r="AI130" t="n">
+        <v>0.9090909090909091</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -15257,6 +15581,9 @@
       <c r="AF131" t="n">
         <v>0.8888888888888888</v>
       </c>
+      <c r="AI131" t="n">
+        <v>0.375</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -15305,6 +15632,9 @@
       <c r="AE132" s="10" t="n"/>
       <c r="AF132" t="n">
         <v>1</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="133">
@@ -15355,6 +15685,9 @@
       <c r="AF133" t="n">
         <v>0.8888888888888888</v>
       </c>
+      <c r="AI133" t="n">
+        <v>0.5714285714285714</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -15403,6 +15736,9 @@
       <c r="AE134" s="10" t="n"/>
       <c r="AF134" t="n">
         <v>1</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="135">
@@ -15453,6 +15789,9 @@
       <c r="AF135" t="n">
         <v>0.3</v>
       </c>
+      <c r="AI135" t="n">
+        <v>0.7272727272727273</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -15502,6 +15841,9 @@
       <c r="AF136" t="n">
         <v>1</v>
       </c>
+      <c r="AI136" t="n">
+        <v>0.6363636363636364</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -15550,6 +15892,9 @@
       <c r="AE137" s="10" t="n"/>
       <c r="AF137" t="n">
         <v>1</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="138">
@@ -15600,6 +15945,9 @@
       <c r="AF138" t="n">
         <v>0.9090909090909091</v>
       </c>
+      <c r="AI138" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -15648,6 +15996,9 @@
       <c r="AE139" s="10" t="n"/>
       <c r="AF139" t="n">
         <v>1</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="140">
@@ -15698,6 +16049,9 @@
       <c r="AF140" t="n">
         <v>0.625</v>
       </c>
+      <c r="AI140" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -15747,6 +16101,9 @@
       <c r="AF141" t="n">
         <v>0.4</v>
       </c>
+      <c r="AI141" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -15796,6 +16153,9 @@
       <c r="AF142" t="n">
         <v>0.1111111111111111</v>
       </c>
+      <c r="AI142" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -15845,6 +16205,9 @@
       <c r="AF143" t="n">
         <v>0.7777777777777778</v>
       </c>
+      <c r="AI143" t="n">
+        <v>0.7777777777777778</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -15894,6 +16257,9 @@
       <c r="AF144" t="n">
         <v>0.1666666666666667</v>
       </c>
+      <c r="AI144" t="n">
+        <v>0.625</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -15942,6 +16308,9 @@
       <c r="AE145" s="10" t="n"/>
       <c r="AF145" t="n">
         <v>1</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="146">
@@ -15992,6 +16361,9 @@
       <c r="AF146" t="n">
         <v>0.9090909090909091</v>
       </c>
+      <c r="AI146" t="n">
+        <v>0.875</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -16041,6 +16413,9 @@
       <c r="AF147" t="n">
         <v>0.4285714285714285</v>
       </c>
+      <c r="AI147" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -16090,6 +16465,9 @@
       <c r="AF148" t="n">
         <v>0.6363636363636364</v>
       </c>
+      <c r="AI148" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -16138,6 +16516,9 @@
       <c r="AE149" s="10" t="n"/>
       <c r="AF149" t="n">
         <v>1</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="150">
@@ -16188,6 +16569,9 @@
       <c r="AF150" t="n">
         <v>0.6666666666666666</v>
       </c>
+      <c r="AI150" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -16237,6 +16621,9 @@
       <c r="AF151" t="n">
         <v>0.8</v>
       </c>
+      <c r="AI151" t="n">
+        <v>0.625</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -16286,6 +16673,9 @@
       <c r="AF152" t="n">
         <v>0.3333333333333333</v>
       </c>
+      <c r="AI152" t="n">
+        <v>0.9090909090909091</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -16335,6 +16725,9 @@
       <c r="AF153" t="n">
         <v>0.8888888888888888</v>
       </c>
+      <c r="AI153" t="n">
+        <v>0.8181818181818182</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -16383,6 +16776,9 @@
       <c r="AE154" s="10" t="n"/>
       <c r="AF154" t="n">
         <v>1</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="155">
@@ -16433,6 +16829,9 @@
       <c r="AF155" t="n">
         <v>0.375</v>
       </c>
+      <c r="AI155" t="n">
+        <v>0.8888888888888888</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -16481,6 +16880,9 @@
       <c r="AE156" s="10" t="n"/>
       <c r="AF156" t="n">
         <v>1</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="157">
@@ -16531,6 +16933,9 @@
       <c r="AF157" t="n">
         <v>0.8333333333333334</v>
       </c>
+      <c r="AI157" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -16579,6 +16984,9 @@
       <c r="AE158" s="10" t="n"/>
       <c r="AF158" t="n">
         <v>1</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>0.625</v>
       </c>
     </row>
     <row r="159">
@@ -16629,6 +17037,9 @@
       <c r="AF159" t="n">
         <v>0.75</v>
       </c>
+      <c r="AI159" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -16678,6 +17089,9 @@
       <c r="AF160" t="n">
         <v>0.3333333333333333</v>
       </c>
+      <c r="AI160" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -16727,6 +17141,9 @@
       <c r="AF161" t="n">
         <v>0.375</v>
       </c>
+      <c r="AI161" t="n">
+        <v>0.5714285714285714</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -16776,6 +17193,9 @@
       <c r="AF162" t="n">
         <v>0.4444444444444444</v>
       </c>
+      <c r="AI162" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -16824,6 +17244,9 @@
       <c r="AE163" s="10" t="n"/>
       <c r="AF163" t="n">
         <v>1</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="164">
@@ -16874,6 +17297,9 @@
       <c r="AF164" t="n">
         <v>0.7272727272727273</v>
       </c>
+      <c r="AI164" t="n">
+        <v>0.5714285714285714</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -16923,6 +17349,9 @@
       <c r="AF165" t="n">
         <v>1</v>
       </c>
+      <c r="AI165" t="n">
+        <v>0.625</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -16972,6 +17401,9 @@
       <c r="AF166" t="n">
         <v>1</v>
       </c>
+      <c r="AI166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -17021,6 +17453,9 @@
       <c r="AF167" t="n">
         <v>1</v>
       </c>
+      <c r="AI167" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -17070,6 +17505,9 @@
       <c r="AF168" t="n">
         <v>1</v>
       </c>
+      <c r="AI168" t="n">
+        <v>0.4444444444444444</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -17119,6 +17557,9 @@
       <c r="AF169" t="n">
         <v>1</v>
       </c>
+      <c r="AI169" t="n">
+        <v>0.5714285714285714</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -17168,6 +17609,9 @@
       <c r="AF170" t="n">
         <v>1</v>
       </c>
+      <c r="AI170" t="n">
+        <v>0.5555555555555556</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -17217,6 +17661,9 @@
       <c r="AF171" t="n">
         <v>1</v>
       </c>
+      <c r="AI171" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -17266,6 +17713,9 @@
       <c r="AF172" t="n">
         <v>1</v>
       </c>
+      <c r="AI172" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -17315,6 +17765,9 @@
       <c r="AF173" t="n">
         <v>1</v>
       </c>
+      <c r="AI173" t="n">
+        <v>0.8888888888888888</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -17364,6 +17817,9 @@
       <c r="AF174" t="n">
         <v>1</v>
       </c>
+      <c r="AI174" t="n">
+        <v>0.3333333333333333</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -17413,6 +17869,9 @@
       <c r="AF175" t="n">
         <v>1</v>
       </c>
+      <c r="AI175" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -17462,6 +17921,9 @@
       <c r="AF176" t="n">
         <v>1</v>
       </c>
+      <c r="AI176" t="n">
+        <v>0.625</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -17511,6 +17973,9 @@
       <c r="AF177" t="n">
         <v>1</v>
       </c>
+      <c r="AI177" t="n">
+        <v>0.8888888888888888</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -17560,6 +18025,9 @@
       <c r="AF178" t="n">
         <v>1</v>
       </c>
+      <c r="AI178" t="n">
+        <v>0.4285714285714285</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -17609,6 +18077,9 @@
       <c r="AF179" t="n">
         <v>1</v>
       </c>
+      <c r="AI179" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -17658,6 +18129,9 @@
       <c r="AF180" t="n">
         <v>1</v>
       </c>
+      <c r="AI180" t="n">
+        <v>0.4285714285714285</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -17707,6 +18181,9 @@
       <c r="AF181" t="n">
         <v>1</v>
       </c>
+      <c r="AI181" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -17756,6 +18233,9 @@
       <c r="AF182" t="n">
         <v>1</v>
       </c>
+      <c r="AI182" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -17805,6 +18285,9 @@
       <c r="AF183" t="n">
         <v>1</v>
       </c>
+      <c r="AI183" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -17854,6 +18337,9 @@
       <c r="AF184" t="n">
         <v>1</v>
       </c>
+      <c r="AI184" t="n">
+        <v>0.7777777777777778</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -17903,6 +18389,9 @@
       <c r="AF185" t="n">
         <v>1</v>
       </c>
+      <c r="AI185" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -17952,6 +18441,9 @@
       <c r="AF186" t="n">
         <v>1</v>
       </c>
+      <c r="AI186" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -18001,6 +18493,9 @@
       <c r="AF187" t="n">
         <v>1</v>
       </c>
+      <c r="AI187" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -18050,6 +18545,9 @@
       <c r="AF188" t="n">
         <v>1</v>
       </c>
+      <c r="AI188" t="n">
+        <v>0.2857142857142857</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
@@ -18099,6 +18597,9 @@
       <c r="AF189" t="n">
         <v>1</v>
       </c>
+      <c r="AI189" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -18148,6 +18649,9 @@
       <c r="AF190" t="n">
         <v>1</v>
       </c>
+      <c r="AI190" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -18197,6 +18701,9 @@
       <c r="AF191" t="n">
         <v>1</v>
       </c>
+      <c r="AI191" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -18245,6 +18752,9 @@
       <c r="AE192" s="10" t="n"/>
       <c r="AF192" t="n">
         <v>1</v>
+      </c>
+      <c r="AI192" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="193">
@@ -19060,6 +19570,9 @@
       <c r="AG212" t="n">
         <v>0.9954000000000001</v>
       </c>
+      <c r="AI212" t="n">
+        <v>0.6441333333333333</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -19121,6 +19634,9 @@
       <c r="AG213" t="n">
         <v>0.68028</v>
       </c>
+      <c r="AI213" t="n">
+        <v>0.8427142857142857</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
@@ -19182,6 +19698,9 @@
       <c r="AG214" t="n">
         <v>0.5468000000000001</v>
       </c>
+      <c r="AI214" t="n">
+        <v>0.8554875</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
@@ -19243,6 +19762,9 @@
       <c r="AG215" t="n">
         <v>0.6868833333333333</v>
       </c>
+      <c r="AI215" t="n">
+        <v>0.78698</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
@@ -19301,6 +19823,9 @@
       <c r="AF216" t="n">
         <v>0.9778000000000001</v>
       </c>
+      <c r="AI216" t="n">
+        <v>0.9508499999999999</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
@@ -19356,6 +19881,9 @@
       <c r="AF217" t="n">
         <v>0.9835142857142857</v>
       </c>
+      <c r="AI217" t="n">
+        <v>0.62295</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
@@ -19411,6 +19939,9 @@
       <c r="AF218" t="n">
         <v>0.982225</v>
       </c>
+      <c r="AI218" t="n">
+        <v>0.8391125</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
@@ -19468,6 +19999,9 @@
       <c r="AF219" t="n">
         <v>0.9823666666666667</v>
       </c>
+      <c r="AI219" t="n">
+        <v>0.6848285714285715</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
@@ -19525,6 +20059,9 @@
       <c r="AF220" t="n">
         <v>0.9786</v>
       </c>
+      <c r="AI220" t="n">
+        <v>0.8555624999999999</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -19580,6 +20117,9 @@
       <c r="AF221" t="n">
         <v>0.9709714285714286</v>
       </c>
+      <c r="AI221" t="n">
+        <v>0.6346428571428572</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
@@ -19629,6 +20169,9 @@
       <c r="AF222" t="n">
         <v>0.9792833333333334</v>
       </c>
+      <c r="AI222" t="n">
+        <v>0.9786833333333332</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
@@ -19678,6 +20221,9 @@
       <c r="AF223" t="n">
         <v>0.9780624999999999</v>
       </c>
+      <c r="AI223" t="n">
+        <v>0.9478833333333334</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
@@ -19727,6 +20273,9 @@
       <c r="AF224" t="n">
         <v>0.9747666666666667</v>
       </c>
+      <c r="AI224" t="n">
+        <v>0.79855</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
@@ -19776,6 +20325,9 @@
       <c r="AF225" t="n">
         <v>0.972942857142857</v>
       </c>
+      <c r="AI225" t="n">
+        <v>0.95045</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
@@ -19825,6 +20377,9 @@
       <c r="AF226" t="n">
         <v>0.9710999999999999</v>
       </c>
+      <c r="AI226" t="n">
+        <v>0.9483200000000001</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
@@ -19874,6 +20429,9 @@
       <c r="AF227" t="n">
         <v>0.9727125</v>
       </c>
+      <c r="AI227" t="n">
+        <v>0.6425333333333332</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
@@ -19923,6 +20481,9 @@
       <c r="AF228" t="n">
         <v>0.9767666666666668</v>
       </c>
+      <c r="AI228" t="n">
+        <v>0.6318571428571429</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
@@ -19972,6 +20533,9 @@
       <c r="AF229" t="n">
         <v>0.9721</v>
       </c>
+      <c r="AI229" t="n">
+        <v>0.8673999999999999</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
@@ -20021,6 +20585,9 @@
       <c r="AF230" t="n">
         <v>0.9696750000000001</v>
       </c>
+      <c r="AI230" t="n">
+        <v>0.7235</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
@@ -20070,6 +20637,9 @@
       <c r="AF231" t="n">
         <v>0.9700857142857143</v>
       </c>
+      <c r="AI231" t="n">
+        <v>0.8117375</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
@@ -20119,6 +20689,9 @@
       <c r="AF232" t="n">
         <v>0.9662666666666667</v>
       </c>
+      <c r="AI232" t="n">
+        <v>0.57204</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
@@ -20168,6 +20741,9 @@
       <c r="AF233" t="n">
         <v>0.97345</v>
       </c>
+      <c r="AI233" t="n">
+        <v>0.6348</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
@@ -20217,6 +20793,9 @@
       <c r="AF234" t="n">
         <v>0.9702111111111112</v>
       </c>
+      <c r="AI234" t="n">
+        <v>0.893</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
@@ -20266,6 +20845,9 @@
       <c r="AF235" t="n">
         <v>0.97405</v>
       </c>
+      <c r="AI235" t="n">
+        <v>0.8253999999999999</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
@@ -20315,6 +20897,9 @@
       <c r="AF236" t="n">
         <v>0.9692</v>
       </c>
+      <c r="AI236" t="n">
+        <v>0.7389125000000001</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
@@ -20364,6 +20949,9 @@
       <c r="AF237" t="n">
         <v>0.9724166666666667</v>
       </c>
+      <c r="AI237" t="n">
+        <v>0.8900444444444445</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
@@ -20413,6 +21001,9 @@
       <c r="AF238" t="n">
         <v>0.9685833333333335</v>
       </c>
+      <c r="AI238" t="n">
+        <v>0.8119</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
@@ -20462,6 +21053,9 @@
       <c r="AF239" t="n">
         <v>0.96692</v>
       </c>
+      <c r="AI239" t="n">
+        <v>0.8147857142857143</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
@@ -20511,6 +21105,9 @@
       <c r="AF240" t="n">
         <v>0.9688444444444444</v>
       </c>
+      <c r="AI240" t="n">
+        <v>0.741675</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
@@ -20560,6 +21157,9 @@
       <c r="AF241" t="n">
         <v>0.9707666666666666</v>
       </c>
+      <c r="AI241" t="n">
+        <v>0.9696499999999999</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
@@ -20609,6 +21209,9 @@
       <c r="AF242" t="n">
         <v>0.97265</v>
       </c>
+      <c r="AI242" t="n">
+        <v>0.7468428571428571</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
@@ -20658,6 +21261,9 @@
       <c r="AF243" t="n">
         <v>0.9742166666666666</v>
       </c>
+      <c r="AI243" t="n">
+        <v>0.7639444444444445</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
@@ -20707,6 +21313,9 @@
       <c r="AF244" t="n">
         <v>0.9711857142857142</v>
       </c>
+      <c r="AI244" t="n">
+        <v>0.6583166666666668</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
@@ -20756,6 +21365,9 @@
       <c r="AF245" t="n">
         <v>0.96996</v>
       </c>
+      <c r="AI245" t="n">
+        <v>0.9734857142857143</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
@@ -20805,6 +21417,9 @@
       <c r="AF246" t="n">
         <v>0.9704833333333335</v>
       </c>
+      <c r="AI246" t="n">
+        <v>0.8712750000000001</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
@@ -20854,6 +21469,9 @@
       <c r="AF247" t="n">
         <v>0.9707833333333333</v>
       </c>
+      <c r="AI247" t="n">
+        <v>0.619325</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
@@ -20903,6 +21521,9 @@
       <c r="AF248" t="n">
         <v>0.9714</v>
       </c>
+      <c r="AI248" t="n">
+        <v>0.8674555555555555</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
@@ -20952,6 +21573,9 @@
       <c r="AF249" t="n">
         <v>0.9726749999999998</v>
       </c>
+      <c r="AI249" t="n">
+        <v>0.9831333333333333</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
@@ -21001,6 +21625,9 @@
       <c r="AF250" t="n">
         <v>0.9703249999999999</v>
       </c>
+      <c r="AI250" t="n">
+        <v>0.72365</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
@@ -21050,6 +21677,9 @@
       <c r="AF251" t="n">
         <v>0.9706625</v>
       </c>
+      <c r="AI251" t="n">
+        <v>0.9485499999999999</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
@@ -21099,6 +21729,9 @@
       <c r="AF252" t="n">
         <v>0.9692500000000001</v>
       </c>
+      <c r="AI252" t="n">
+        <v>0.6445</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
@@ -21148,6 +21781,9 @@
       <c r="AF253" t="n">
         <v>0.97027</v>
       </c>
+      <c r="AI253" t="n">
+        <v>0.7396222222222222</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
@@ -21197,6 +21833,9 @@
       <c r="AF254" t="n">
         <v>0.9707999999999998</v>
       </c>
+      <c r="AI254" t="n">
+        <v>0.7553444444444445</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
@@ -21246,6 +21885,9 @@
       <c r="AF255" t="n">
         <v>0.97022</v>
       </c>
+      <c r="AI255" t="n">
+        <v>0.9722099999999999</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
@@ -21295,6 +21937,9 @@
       <c r="AF256" t="n">
         <v>0.9671666666666668</v>
       </c>
+      <c r="AI256" t="n">
+        <v>0.75284</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
@@ -21344,6 +21989,9 @@
       <c r="AF257" t="n">
         <v>0.9647333333333332</v>
       </c>
+      <c r="AI257" t="n">
+        <v>0.6519333333333334</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
@@ -21393,6 +22041,9 @@
       <c r="AF258" t="n">
         <v>0.9668166666666668</v>
       </c>
+      <c r="AI258" t="n">
+        <v>0.7194750000000001</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
@@ -21442,6 +22093,9 @@
       <c r="AF259" t="n">
         <v>0.9694571428571429</v>
       </c>
+      <c r="AI259" t="n">
+        <v>0.8359857142857142</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
@@ -21491,6 +22145,9 @@
       <c r="AF260" t="n">
         <v>0.9680444444444445</v>
       </c>
+      <c r="AI260" t="n">
+        <v>0.7601111111111112</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
@@ -21540,6 +22197,9 @@
       <c r="AF261" t="n">
         <v>0.9607999999999999</v>
       </c>
+      <c r="AI261" t="n">
+        <v>0.8796363636363637</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
@@ -21589,6 +22249,9 @@
       <c r="AF262" t="n">
         <v>0.9705600000000001</v>
       </c>
+      <c r="AI262" t="n">
+        <v>0.9625857142857142</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
@@ -21638,6 +22301,9 @@
       <c r="AF263" t="n">
         <v>0.9682428571428571</v>
       </c>
+      <c r="AI263" t="n">
+        <v>0.8464444444444446</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
@@ -21687,6 +22353,9 @@
       <c r="AF264" t="n">
         <v>0.9663</v>
       </c>
+      <c r="AI264" t="n">
+        <v>0.9535699999999998</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
@@ -21736,6 +22405,9 @@
       <c r="AF265" t="n">
         <v>0.9757571428571429</v>
       </c>
+      <c r="AI265" t="n">
+        <v>0.7630444444444444</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
@@ -21785,6 +22457,9 @@
       <c r="AF266" t="n">
         <v>0.9612166666666666</v>
       </c>
+      <c r="AI266" t="n">
+        <v>0.7066</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
@@ -21834,6 +22509,9 @@
       <c r="AF267" t="n">
         <v>0.9699833333333333</v>
       </c>
+      <c r="AI267" t="n">
+        <v>0.9716375</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
@@ -21883,6 +22561,9 @@
       <c r="AF268" t="n">
         <v>0.976475</v>
       </c>
+      <c r="AI268" t="n">
+        <v>0.9822375</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
@@ -21932,6 +22613,9 @@
       <c r="AF269" t="n">
         <v>0.96606</v>
       </c>
+      <c r="AI269" t="n">
+        <v>0.6172875</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
@@ -21981,6 +22665,9 @@
       <c r="AF270" t="n">
         <v>0.96998</v>
       </c>
+      <c r="AI270" t="n">
+        <v>0.9802500000000001</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
@@ -22030,6 +22717,9 @@
       <c r="AF271" t="n">
         <v>0.97654</v>
       </c>
+      <c r="AI271" t="n">
+        <v>0.5480428571428572</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
@@ -22079,6 +22769,9 @@
       <c r="AF272" t="n">
         <v>0.97224</v>
       </c>
+      <c r="AI272" t="n">
+        <v>0.5658571428571428</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
@@ -22128,6 +22821,9 @@
       <c r="AF273" t="n">
         <v>0.9674200000000001</v>
       </c>
+      <c r="AI273" t="n">
+        <v>0.727975</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
@@ -22177,6 +22873,9 @@
       <c r="AF274" t="n">
         <v>0.9708571428571428</v>
       </c>
+      <c r="AI274" t="n">
+        <v>0.6059749999999999</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
@@ -22226,6 +22925,9 @@
       <c r="AF275" t="n">
         <v>0.9671800000000002</v>
       </c>
+      <c r="AI275" t="n">
+        <v>0.8492777777777778</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
@@ -22275,6 +22977,9 @@
       <c r="AF276" t="n">
         <v>0.9735999999999999</v>
       </c>
+      <c r="AI276" t="n">
+        <v>0.4905166666666667</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
@@ -22324,6 +23029,9 @@
       <c r="AF277" t="n">
         <v>0.9757285714285714</v>
       </c>
+      <c r="AI277" t="n">
+        <v>0.7918166666666666</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
@@ -22373,6 +23081,9 @@
       <c r="AF278" t="n">
         <v>0.9700857142857142</v>
       </c>
+      <c r="AI278" t="n">
+        <v>0.7127142857142857</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
@@ -22422,6 +23133,9 @@
       <c r="AF279" t="n">
         <v>0.9707285714285714</v>
       </c>
+      <c r="AI279" t="n">
+        <v>0.5605</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
@@ -22471,6 +23185,9 @@
       <c r="AF280" t="n">
         <v>0.9728428571428571</v>
       </c>
+      <c r="AI280" t="n">
+        <v>0.871875</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
@@ -22520,6 +23237,9 @@
       <c r="AF281" t="n">
         <v>0.9738999999999999</v>
       </c>
+      <c r="AI281" t="n">
+        <v>0.7017999999999999</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
@@ -22569,6 +23289,9 @@
       <c r="AF282" t="n">
         <v>0.9725199999999999</v>
       </c>
+      <c r="AI282" t="n">
+        <v>0.875688888888889</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
@@ -22618,6 +23341,9 @@
       <c r="AF283" t="n">
         <v>0.97072</v>
       </c>
+      <c r="AI283" t="n">
+        <v>0.7208727272727273</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
@@ -22667,6 +23393,9 @@
       <c r="AF284" t="n">
         <v>0.9671571428571427</v>
       </c>
+      <c r="AI284" t="n">
+        <v>0.5140666666666668</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
@@ -22716,6 +23445,9 @@
       <c r="AF285" t="n">
         <v>0.9697999999999999</v>
       </c>
+      <c r="AI285" t="n">
+        <v>0.3332666666666667</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
@@ -22765,6 +23497,9 @@
       <c r="AF286" t="n">
         <v>0.9652166666666666</v>
       </c>
+      <c r="AI286" t="n">
+        <v>0.6473666666666666</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
@@ -22814,6 +23549,9 @@
       <c r="AF287" t="n">
         <v>0.9759</v>
       </c>
+      <c r="AI287" t="n">
+        <v>0.9545111111111111</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
@@ -22863,6 +23601,9 @@
       <c r="AF288" t="n">
         <v>0.9716833333333333</v>
       </c>
+      <c r="AI288" t="n">
+        <v>0.7038571428571428</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
@@ -22912,6 +23653,9 @@
       <c r="AF289" t="n">
         <v>0.9722333333333334</v>
       </c>
+      <c r="AI289" t="n">
+        <v>0.7050363636363636</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
@@ -22961,6 +23705,9 @@
       <c r="AF290" t="n">
         <v>0.9698000000000001</v>
       </c>
+      <c r="AI290" t="n">
+        <v>0.6691499999999999</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
@@ -23010,6 +23757,9 @@
       <c r="AF291" t="n">
         <v>0.9743625</v>
       </c>
+      <c r="AI291" t="n">
+        <v>0.4968181818181818</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
@@ -23059,6 +23809,9 @@
       <c r="AF292" t="n">
         <v>0.9743666666666666</v>
       </c>
+      <c r="AI292" t="n">
+        <v>0.7363666666666666</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
@@ -23108,6 +23861,9 @@
       <c r="AF293" t="n">
         <v>0.9705</v>
       </c>
+      <c r="AI293" t="n">
+        <v>0.7124571428571429</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
@@ -23157,6 +23913,9 @@
       <c r="AF294" t="n">
         <v>0.9741124999999999</v>
       </c>
+      <c r="AI294" t="n">
+        <v>0.7450444444444444</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
@@ -23206,6 +23965,9 @@
       <c r="AF295" t="n">
         <v>0.9752142857142857</v>
       </c>
+      <c r="AI295" t="n">
+        <v>0.6594428571428572</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
@@ -23254,6 +24016,9 @@
       <c r="AE296" s="10" t="n"/>
       <c r="AF296" t="n">
         <v>0.9717500000000001</v>
+      </c>
+      <c r="AI296" t="n">
+        <v>0.8055777777777777</v>
       </c>
     </row>
     <row r="297">
@@ -24071,6 +24836,9 @@
       <c r="AG316" t="n">
         <v>0.3727</v>
       </c>
+      <c r="AI316" t="n">
+        <v>0.3849</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
@@ -24132,6 +24900,9 @@
       <c r="AG317" t="n">
         <v>0.0987</v>
       </c>
+      <c r="AI317" t="n">
+        <v>0.3236</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
@@ -24193,6 +24964,9 @@
       <c r="AG318" t="n">
         <v>0.0789</v>
       </c>
+      <c r="AI318" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
@@ -24254,6 +25028,9 @@
       <c r="AG319" t="n">
         <v>0.3827</v>
       </c>
+      <c r="AI319" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
@@ -24312,6 +25089,9 @@
       <c r="AF320" t="n">
         <v>0.07779999999999999</v>
       </c>
+      <c r="AI320" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
@@ -24367,6 +25147,9 @@
       <c r="AF321" t="n">
         <v>0.0926</v>
       </c>
+      <c r="AI321" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
@@ -24422,6 +25205,9 @@
       <c r="AF322" t="n">
         <v>0.0862</v>
       </c>
+      <c r="AI322" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
@@ -24477,6 +25263,9 @@
       <c r="AF323" t="n">
         <v>0.0994</v>
       </c>
+      <c r="AI323" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
@@ -24532,6 +25321,9 @@
       <c r="AF324" t="n">
         <v>0.1198</v>
       </c>
+      <c r="AI324" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
@@ -24587,6 +25379,9 @@
       <c r="AF325" t="n">
         <v>0.0994</v>
       </c>
+      <c r="AI325" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
@@ -24636,6 +25431,9 @@
       <c r="AF326" t="n">
         <v>0.0992</v>
       </c>
+      <c r="AI326" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
@@ -24685,6 +25483,9 @@
       <c r="AF327" t="n">
         <v>0.09279999999999999</v>
       </c>
+      <c r="AI327" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
@@ -24734,6 +25535,9 @@
       <c r="AF328" t="n">
         <v>0.095</v>
       </c>
+      <c r="AI328" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
@@ -24783,6 +25587,9 @@
       <c r="AF329" t="n">
         <v>0.1036</v>
       </c>
+      <c r="AI329" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
@@ -24832,6 +25639,9 @@
       <c r="AF330" t="n">
         <v>0.1041</v>
       </c>
+      <c r="AI330" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
@@ -24881,6 +25691,9 @@
       <c r="AF331" t="n">
         <v>0.0926</v>
       </c>
+      <c r="AI331" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
@@ -24930,6 +25743,9 @@
       <c r="AF332" t="n">
         <v>0.124</v>
       </c>
+      <c r="AI332" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
@@ -24979,6 +25795,9 @@
       <c r="AF333" t="n">
         <v>0.1002</v>
       </c>
+      <c r="AI333" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
@@ -25028,6 +25847,9 @@
       <c r="AF334" t="n">
         <v>0.09810000000000001</v>
       </c>
+      <c r="AI334" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
@@ -25077,6 +25899,9 @@
       <c r="AF335" t="n">
         <v>0.1008</v>
       </c>
+      <c r="AI335" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
@@ -25126,6 +25951,9 @@
       <c r="AF336" t="n">
         <v>0.107</v>
       </c>
+      <c r="AI336" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
@@ -25175,6 +26003,9 @@
       <c r="AF337" t="n">
         <v>0.1049</v>
       </c>
+      <c r="AI337" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
@@ -25224,6 +26055,9 @@
       <c r="AF338" t="n">
         <v>0.1093</v>
       </c>
+      <c r="AI338" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
@@ -25273,6 +26107,9 @@
       <c r="AF339" t="n">
         <v>0.09909999999999999</v>
       </c>
+      <c r="AI339" t="n">
+        <v>0.0021</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
@@ -25322,6 +26159,9 @@
       <c r="AF340" t="n">
         <v>0.1096</v>
       </c>
+      <c r="AI340" t="n">
+        <v>0.0401</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
@@ -25371,6 +26211,9 @@
       <c r="AF341" t="n">
         <v>0.1151</v>
       </c>
+      <c r="AI341" t="n">
+        <v>0.144</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
@@ -25420,6 +26263,9 @@
       <c r="AF342" t="n">
         <v>0.1109</v>
       </c>
+      <c r="AI342" t="n">
+        <v>0.3091</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
@@ -25469,6 +26315,9 @@
       <c r="AF343" t="n">
         <v>0.1084</v>
       </c>
+      <c r="AI343" t="n">
+        <v>0.5129</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
@@ -25518,6 +26367,9 @@
       <c r="AF344" t="n">
         <v>0.1209</v>
       </c>
+      <c r="AI344" t="n">
+        <v>0.0066</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
@@ -25567,6 +26419,9 @@
       <c r="AF345" t="n">
         <v>0.1146</v>
       </c>
+      <c r="AI345" t="n">
+        <v>0.1176</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
@@ -25616,6 +26471,9 @@
       <c r="AF346" t="n">
         <v>0.1084</v>
       </c>
+      <c r="AI346" t="n">
+        <v>0.2172</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
@@ -25665,6 +26523,9 @@
       <c r="AF347" t="n">
         <v>0.1097</v>
       </c>
+      <c r="AI347" t="n">
+        <v>0.0175</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
@@ -25714,6 +26575,9 @@
       <c r="AF348" t="n">
         <v>0.1042</v>
       </c>
+      <c r="AI348" t="n">
+        <v>0.1254</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
@@ -25763,6 +26627,9 @@
       <c r="AF349" t="n">
         <v>0.1119</v>
       </c>
+      <c r="AI349" t="n">
+        <v>0.5634</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
@@ -25812,6 +26679,9 @@
       <c r="AF350" t="n">
         <v>0.1229</v>
       </c>
+      <c r="AI350" t="n">
+        <v>0.5946</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
@@ -25861,6 +26731,9 @@
       <c r="AF351" t="n">
         <v>0.1015</v>
       </c>
+      <c r="AI351" t="n">
+        <v>0.535</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
@@ -25910,6 +26783,9 @@
       <c r="AF352" t="n">
         <v>0.09660000000000001</v>
       </c>
+      <c r="AI352" t="n">
+        <v>0.011</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
@@ -25959,6 +26835,9 @@
       <c r="AF353" t="n">
         <v>0.1036</v>
       </c>
+      <c r="AI353" t="n">
+        <v>0.0022</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
@@ -26008,6 +26887,9 @@
       <c r="AF354" t="n">
         <v>0.104</v>
       </c>
+      <c r="AI354" t="n">
+        <v>0.1202</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
@@ -26057,6 +26939,9 @@
       <c r="AF355" t="n">
         <v>0.1067</v>
       </c>
+      <c r="AI355" t="n">
+        <v>0.0074</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
@@ -26106,6 +26991,9 @@
       <c r="AF356" t="n">
         <v>0.0975</v>
       </c>
+      <c r="AI356" t="n">
+        <v>0.0038</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
@@ -26155,6 +27043,9 @@
       <c r="AF357" t="n">
         <v>0.1151</v>
       </c>
+      <c r="AI357" t="n">
+        <v>0.2144</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
@@ -26204,6 +27095,9 @@
       <c r="AF358" t="n">
         <v>0.1131</v>
       </c>
+      <c r="AI358" t="n">
+        <v>0.7236</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
@@ -26253,6 +27147,9 @@
       <c r="AF359" t="n">
         <v>0.1038</v>
       </c>
+      <c r="AI359" t="n">
+        <v>0.3599</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
@@ -26302,6 +27199,9 @@
       <c r="AF360" t="n">
         <v>0.109</v>
       </c>
+      <c r="AI360" t="n">
+        <v>0.1976</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
@@ -26351,6 +27251,9 @@
       <c r="AF361" t="n">
         <v>0.1124</v>
       </c>
+      <c r="AI361" t="n">
+        <v>0.4266</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
@@ -26400,6 +27303,9 @@
       <c r="AF362" t="n">
         <v>0.1012</v>
       </c>
+      <c r="AI362" t="n">
+        <v>0.118</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
@@ -26449,6 +27355,9 @@
       <c r="AF363" t="n">
         <v>0.1186</v>
       </c>
+      <c r="AI363" t="n">
+        <v>0.0824</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
@@ -26498,6 +27407,9 @@
       <c r="AF364" t="n">
         <v>0.1075</v>
       </c>
+      <c r="AI364" t="n">
+        <v>0.0588</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
@@ -26547,6 +27459,9 @@
       <c r="AF365" t="n">
         <v>0.09909999999999999</v>
       </c>
+      <c r="AI365" t="n">
+        <v>0.0174</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
@@ -26596,6 +27511,9 @@
       <c r="AF366" t="n">
         <v>0.0984</v>
       </c>
+      <c r="AI366" t="n">
+        <v>0.0054</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
@@ -26645,6 +27563,9 @@
       <c r="AF367" t="n">
         <v>0.0989</v>
       </c>
+      <c r="AI367" t="n">
+        <v>0.0007</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
@@ -26694,6 +27615,9 @@
       <c r="AF368" t="n">
         <v>0.1071</v>
       </c>
+      <c r="AI368" t="n">
+        <v>0.0005</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
@@ -26743,6 +27667,9 @@
       <c r="AF369" t="n">
         <v>0.09569999999999999</v>
       </c>
+      <c r="AI369" t="n">
+        <v>0.0021</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
@@ -26792,6 +27719,9 @@
       <c r="AF370" t="n">
         <v>0.1086</v>
       </c>
+      <c r="AI370" t="n">
+        <v>0.0032</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
@@ -26841,6 +27771,9 @@
       <c r="AF371" t="n">
         <v>0.1041</v>
       </c>
+      <c r="AI371" t="n">
+        <v>0.0003</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
@@ -26890,6 +27823,9 @@
       <c r="AF372" t="n">
         <v>0.1086</v>
       </c>
+      <c r="AI372" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
@@ -26939,6 +27875,9 @@
       <c r="AF373" t="n">
         <v>0.1077</v>
       </c>
+      <c r="AI373" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
@@ -26988,6 +27927,9 @@
       <c r="AF374" t="n">
         <v>0.09660000000000001</v>
       </c>
+      <c r="AI374" t="n">
+        <v>0.0009</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
@@ -27037,6 +27979,9 @@
       <c r="AF375" t="n">
         <v>0.0961</v>
       </c>
+      <c r="AI375" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
@@ -27086,6 +28031,9 @@
       <c r="AF376" t="n">
         <v>0.1027</v>
       </c>
+      <c r="AI376" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
@@ -27135,6 +28083,9 @@
       <c r="AF377" t="n">
         <v>0.1066</v>
       </c>
+      <c r="AI377" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
@@ -27184,6 +28135,9 @@
       <c r="AF378" t="n">
         <v>0.1034</v>
       </c>
+      <c r="AI378" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
@@ -27233,6 +28187,9 @@
       <c r="AF379" t="n">
         <v>0.0944</v>
       </c>
+      <c r="AI379" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
@@ -27282,6 +28239,9 @@
       <c r="AF380" t="n">
         <v>0.1048</v>
       </c>
+      <c r="AI380" t="n">
+        <v>0.0001</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
@@ -27331,6 +28291,9 @@
       <c r="AF381" t="n">
         <v>0.1016</v>
       </c>
+      <c r="AI381" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
@@ -27380,6 +28343,9 @@
       <c r="AF382" t="n">
         <v>0.1088</v>
       </c>
+      <c r="AI382" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
@@ -27429,6 +28395,9 @@
       <c r="AF383" t="n">
         <v>0.0989</v>
       </c>
+      <c r="AI383" t="n">
+        <v>0.0001</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
@@ -27478,6 +28447,9 @@
       <c r="AF384" t="n">
         <v>0.1001</v>
       </c>
+      <c r="AI384" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
@@ -27527,6 +28499,9 @@
       <c r="AF385" t="n">
         <v>0.09710000000000001</v>
       </c>
+      <c r="AI385" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
@@ -27576,6 +28551,9 @@
       <c r="AF386" t="n">
         <v>0.1144</v>
       </c>
+      <c r="AI386" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
@@ -27625,6 +28603,9 @@
       <c r="AF387" t="n">
         <v>0.1033</v>
       </c>
+      <c r="AI387" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
@@ -27674,6 +28655,9 @@
       <c r="AF388" t="n">
         <v>0.1058</v>
       </c>
+      <c r="AI388" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
@@ -27723,6 +28707,9 @@
       <c r="AF389" t="n">
         <v>0.1074</v>
       </c>
+      <c r="AI389" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
@@ -27772,6 +28759,9 @@
       <c r="AF390" t="n">
         <v>0.1012</v>
       </c>
+      <c r="AI390" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
@@ -27821,6 +28811,9 @@
       <c r="AF391" t="n">
         <v>0.1087</v>
       </c>
+      <c r="AI391" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
@@ -27870,6 +28863,9 @@
       <c r="AF392" t="n">
         <v>0.1065</v>
       </c>
+      <c r="AI392" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
@@ -27919,6 +28915,9 @@
       <c r="AF393" t="n">
         <v>0.1049</v>
       </c>
+      <c r="AI393" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
@@ -27968,6 +28967,9 @@
       <c r="AF394" t="n">
         <v>0.0934</v>
       </c>
+      <c r="AI394" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
@@ -28017,6 +29019,9 @@
       <c r="AF395" t="n">
         <v>0.1086</v>
       </c>
+      <c r="AI395" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
@@ -28066,6 +29071,9 @@
       <c r="AF396" t="n">
         <v>0.1054</v>
       </c>
+      <c r="AI396" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
@@ -28115,6 +29123,9 @@
       <c r="AF397" t="n">
         <v>0.1018</v>
       </c>
+      <c r="AI397" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
@@ -28164,6 +29175,9 @@
       <c r="AF398" t="n">
         <v>0.1026</v>
       </c>
+      <c r="AI398" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
@@ -28213,6 +29227,9 @@
       <c r="AF399" t="n">
         <v>0.1018</v>
       </c>
+      <c r="AI399" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
@@ -28261,6 +29278,9 @@
       <c r="AE400" s="10" t="n"/>
       <c r="AF400" t="n">
         <v>0.0956</v>
+      </c>
+      <c r="AI400" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="401">

--- a/CIFAR_Global.xlsx
+++ b/CIFAR_Global.xlsx
@@ -8314,7 +8314,7 @@
         <v>0.0999</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.1015875007843383</v>
+        <v>0.1451</v>
       </c>
     </row>
     <row r="6">
@@ -8385,7 +8385,7 @@
         <v>0.0999</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.102340465583234</v>
+        <v>0.1776</v>
       </c>
     </row>
     <row r="7">
@@ -8456,7 +8456,7 @@
         <v>0.1529</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1670326912216854</v>
+        <v>0.2412</v>
       </c>
     </row>
     <row r="8">
@@ -8527,7 +8527,7 @@
         <v>0.1115</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.2157871619501788</v>
+        <v>0.2753</v>
       </c>
     </row>
     <row r="9">
@@ -8598,7 +8598,7 @@
         <v>0.1121</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.1</v>
+        <v>0.3397</v>
       </c>
     </row>
     <row r="10">
@@ -8666,7 +8666,7 @@
         <v>0.1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.1078</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="11">
@@ -8734,7 +8734,7 @@
         <v>0.1122</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.1078</v>
+        <v>0.371</v>
       </c>
     </row>
     <row r="12">
@@ -8802,7 +8802,7 @@
         <v>0.1314</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.1078</v>
+        <v>0.3819</v>
       </c>
     </row>
     <row r="13">
@@ -8869,6 +8869,9 @@
       <c r="AI13" t="n">
         <v>0.1433</v>
       </c>
+      <c r="AJ13" t="n">
+        <v>0.3639</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -8934,6 +8937,9 @@
       <c r="AI14" t="n">
         <v>0.1074</v>
       </c>
+      <c r="AJ14" t="n">
+        <v>0.3883</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -8993,6 +8999,9 @@
       <c r="AI15" t="n">
         <v>0.107</v>
       </c>
+      <c r="AJ15" t="n">
+        <v>0.3739</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -9052,6 +9061,9 @@
       <c r="AI16" t="n">
         <v>0.1092</v>
       </c>
+      <c r="AJ16" t="n">
+        <v>0.4131</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -9111,6 +9123,9 @@
       <c r="AI17" t="n">
         <v>0.094</v>
       </c>
+      <c r="AJ17" t="n">
+        <v>0.4237</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -9170,6 +9185,9 @@
       <c r="AI18" t="n">
         <v>0.0944</v>
       </c>
+      <c r="AJ18" t="n">
+        <v>0.4181</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -9229,6 +9247,9 @@
       <c r="AI19" t="n">
         <v>0.0955</v>
       </c>
+      <c r="AJ19" t="n">
+        <v>0.4194</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -9288,6 +9309,9 @@
       <c r="AI20" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ20" t="n">
+        <v>0.4259</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -9347,6 +9371,9 @@
       <c r="AI21" t="n">
         <v>0.1228</v>
       </c>
+      <c r="AJ21" t="n">
+        <v>0.4252</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -9406,6 +9433,9 @@
       <c r="AI22" t="n">
         <v>0.1179</v>
       </c>
+      <c r="AJ22" t="n">
+        <v>0.4283</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -9465,6 +9495,9 @@
       <c r="AI23" t="n">
         <v>0.1213</v>
       </c>
+      <c r="AJ23" t="n">
+        <v>0.4113</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -9524,6 +9557,9 @@
       <c r="AI24" t="n">
         <v>0.09760000000000001</v>
       </c>
+      <c r="AJ24" t="n">
+        <v>0.4335</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -9583,6 +9619,9 @@
       <c r="AI25" t="n">
         <v>0.1238</v>
       </c>
+      <c r="AJ25" t="n">
+        <v>0.4277</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -9642,6 +9681,9 @@
       <c r="AI26" t="n">
         <v>0.1253</v>
       </c>
+      <c r="AJ26" t="n">
+        <v>0.4239</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -9701,6 +9743,9 @@
       <c r="AI27" t="n">
         <v>0.1174</v>
       </c>
+      <c r="AJ27" t="n">
+        <v>0.4287</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -9760,6 +9805,9 @@
       <c r="AI28" t="n">
         <v>0.1014</v>
       </c>
+      <c r="AJ28" t="n">
+        <v>0.4235</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -9819,6 +9867,9 @@
       <c r="AI29" t="n">
         <v>0.103</v>
       </c>
+      <c r="AJ29" t="n">
+        <v>0.4191</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -9878,6 +9929,9 @@
       <c r="AI30" t="n">
         <v>0.1132</v>
       </c>
+      <c r="AJ30" t="n">
+        <v>0.4324</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -9937,6 +9991,9 @@
       <c r="AI31" t="n">
         <v>0.1195</v>
       </c>
+      <c r="AJ31" t="n">
+        <v>0.4328</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -9996,6 +10053,9 @@
       <c r="AI32" t="n">
         <v>0.1026</v>
       </c>
+      <c r="AJ32" t="n">
+        <v>0.4318</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -10055,6 +10115,9 @@
       <c r="AI33" t="n">
         <v>0.1197</v>
       </c>
+      <c r="AJ33" t="n">
+        <v>0.4186</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -10114,6 +10177,9 @@
       <c r="AI34" t="n">
         <v>0.097</v>
       </c>
+      <c r="AJ34" t="n">
+        <v>0.4335</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -10173,6 +10239,9 @@
       <c r="AI35" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ35" t="n">
+        <v>0.437</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -10232,6 +10301,9 @@
       <c r="AI36" t="n">
         <v>0.1132</v>
       </c>
+      <c r="AJ36" t="n">
+        <v>0.4241</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -10291,6 +10363,9 @@
       <c r="AI37" t="n">
         <v>0.1135</v>
       </c>
+      <c r="AJ37" t="n">
+        <v>0.4346</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -10350,6 +10425,9 @@
       <c r="AI38" t="n">
         <v>0.1462</v>
       </c>
+      <c r="AJ38" t="n">
+        <v>0.4284</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -10409,6 +10487,9 @@
       <c r="AI39" t="n">
         <v>0.1282</v>
       </c>
+      <c r="AJ39" t="n">
+        <v>0.4229</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -10468,6 +10549,9 @@
       <c r="AI40" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ40" t="n">
+        <v>0.4185</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -10527,6 +10611,9 @@
       <c r="AI41" t="n">
         <v>0.121</v>
       </c>
+      <c r="AJ41" t="n">
+        <v>0.4242</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -10586,6 +10673,9 @@
       <c r="AI42" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ42" t="n">
+        <v>0.4321</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -10645,6 +10735,9 @@
       <c r="AI43" t="n">
         <v>0.1129</v>
       </c>
+      <c r="AJ43" t="n">
+        <v>0.4232</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -10704,6 +10797,9 @@
       <c r="AI44" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ44" t="n">
+        <v>0.4193</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -10763,6 +10859,9 @@
       <c r="AI45" t="n">
         <v>0.1446</v>
       </c>
+      <c r="AJ45" t="n">
+        <v>0.4272</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -10822,6 +10921,9 @@
       <c r="AI46" t="n">
         <v>0.1577</v>
       </c>
+      <c r="AJ46" t="n">
+        <v>0.4304</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -10881,6 +10983,9 @@
       <c r="AI47" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ47" t="n">
+        <v>0.431</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -10940,6 +11045,9 @@
       <c r="AI48" t="n">
         <v>0.1606</v>
       </c>
+      <c r="AJ48" t="n">
+        <v>0.4311</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -10999,6 +11107,9 @@
       <c r="AI49" t="n">
         <v>0.1216</v>
       </c>
+      <c r="AJ49" t="n">
+        <v>0.4364</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -11058,6 +11169,9 @@
       <c r="AI50" t="n">
         <v>0.1731</v>
       </c>
+      <c r="AJ50" t="n">
+        <v>0.4297</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -11117,6 +11231,9 @@
       <c r="AI51" t="n">
         <v>0.1475</v>
       </c>
+      <c r="AJ51" t="n">
+        <v>0.4325</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -11176,6 +11293,9 @@
       <c r="AI52" t="n">
         <v>0.2121</v>
       </c>
+      <c r="AJ52" t="n">
+        <v>0.439</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -11235,6 +11355,9 @@
       <c r="AI53" t="n">
         <v>0.1404</v>
       </c>
+      <c r="AJ53" t="n">
+        <v>0.4266</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -11294,6 +11417,9 @@
       <c r="AI54" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ54" t="n">
+        <v>0.4419</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -11353,6 +11479,9 @@
       <c r="AI55" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ55" t="n">
+        <v>0.4387</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -11412,6 +11541,9 @@
       <c r="AI56" t="n">
         <v>0.1787</v>
       </c>
+      <c r="AJ56" t="n">
+        <v>0.4397</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -11471,6 +11603,9 @@
       <c r="AI57" t="n">
         <v>0.1458</v>
       </c>
+      <c r="AJ57" t="n">
+        <v>0.4382</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -11530,6 +11665,9 @@
       <c r="AI58" t="n">
         <v>0.1687</v>
       </c>
+      <c r="AJ58" t="n">
+        <v>0.4371</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -11589,6 +11727,9 @@
       <c r="AI59" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ59" t="n">
+        <v>0.4341</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -11648,6 +11789,9 @@
       <c r="AI60" t="n">
         <v>0.1279</v>
       </c>
+      <c r="AJ60" t="n">
+        <v>0.4353</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -11707,6 +11851,9 @@
       <c r="AI61" t="n">
         <v>0.1275</v>
       </c>
+      <c r="AJ61" t="n">
+        <v>0.4351</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -11766,6 +11913,9 @@
       <c r="AI62" t="n">
         <v>0.1001</v>
       </c>
+      <c r="AJ62" t="n">
+        <v>0.4377</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -11825,6 +11975,9 @@
       <c r="AI63" t="n">
         <v>0.1215</v>
       </c>
+      <c r="AJ63" t="n">
+        <v>0.432</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -11884,6 +12037,9 @@
       <c r="AI64" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ64" t="n">
+        <v>0.4269</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -11943,6 +12099,9 @@
       <c r="AI65" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ65" t="n">
+        <v>0.4252</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -12002,6 +12161,9 @@
       <c r="AI66" t="n">
         <v>0.1438</v>
       </c>
+      <c r="AJ66" t="n">
+        <v>0.433</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -12061,6 +12223,9 @@
       <c r="AI67" t="n">
         <v>0.1539</v>
       </c>
+      <c r="AJ67" t="n">
+        <v>0.4323</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -12120,6 +12285,9 @@
       <c r="AI68" t="n">
         <v>0.1323</v>
       </c>
+      <c r="AJ68" t="n">
+        <v>0.4351</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -12179,6 +12347,9 @@
       <c r="AI69" t="n">
         <v>0.1294</v>
       </c>
+      <c r="AJ69" t="n">
+        <v>0.4403</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -12238,6 +12409,9 @@
       <c r="AI70" t="n">
         <v>0.155</v>
       </c>
+      <c r="AJ70" t="n">
+        <v>0.4417</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -12297,6 +12471,9 @@
       <c r="AI71" t="n">
         <v>0.1347</v>
       </c>
+      <c r="AJ71" t="n">
+        <v>0.4382</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -12356,6 +12533,9 @@
       <c r="AI72" t="n">
         <v>0.1642</v>
       </c>
+      <c r="AJ72" t="n">
+        <v>0.4358</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -12415,6 +12595,9 @@
       <c r="AI73" t="n">
         <v>0.1646</v>
       </c>
+      <c r="AJ73" t="n">
+        <v>0.437</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -12474,6 +12657,9 @@
       <c r="AI74" t="n">
         <v>0.1509</v>
       </c>
+      <c r="AJ74" t="n">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -12533,6 +12719,9 @@
       <c r="AI75" t="n">
         <v>0.1643</v>
       </c>
+      <c r="AJ75" t="n">
+        <v>0.4343</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -12592,6 +12781,9 @@
       <c r="AI76" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ76" t="n">
+        <v>0.419</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -12651,6 +12843,9 @@
       <c r="AI77" t="n">
         <v>0.1346</v>
       </c>
+      <c r="AJ77" t="n">
+        <v>0.4327</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -12710,6 +12905,9 @@
       <c r="AI78" t="n">
         <v>0.1402</v>
       </c>
+      <c r="AJ78" t="n">
+        <v>0.4404</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -12769,6 +12967,9 @@
       <c r="AI79" t="n">
         <v>0.1613</v>
       </c>
+      <c r="AJ79" t="n">
+        <v>0.443</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -12828,6 +13029,9 @@
       <c r="AI80" t="n">
         <v>0.138</v>
       </c>
+      <c r="AJ80" t="n">
+        <v>0.4426</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -12887,6 +13091,9 @@
       <c r="AI81" t="n">
         <v>0.1527</v>
       </c>
+      <c r="AJ81" t="n">
+        <v>0.443</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -12946,6 +13153,9 @@
       <c r="AI82" t="n">
         <v>0.1347</v>
       </c>
+      <c r="AJ82" t="n">
+        <v>0.4362</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -13005,6 +13215,9 @@
       <c r="AI83" t="n">
         <v>0.117</v>
       </c>
+      <c r="AJ83" t="n">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -13064,6 +13277,9 @@
       <c r="AI84" t="n">
         <v>0.1112</v>
       </c>
+      <c r="AJ84" t="n">
+        <v>0.4432</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -13123,6 +13339,9 @@
       <c r="AI85" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ85" t="n">
+        <v>0.4457</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -13182,6 +13401,9 @@
       <c r="AI86" t="n">
         <v>0.1444</v>
       </c>
+      <c r="AJ86" t="n">
+        <v>0.4423</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -13241,6 +13463,9 @@
       <c r="AI87" t="n">
         <v>0.1127</v>
       </c>
+      <c r="AJ87" t="n">
+        <v>0.4405</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -13300,6 +13525,9 @@
       <c r="AI88" t="n">
         <v>0.131</v>
       </c>
+      <c r="AJ88" t="n">
+        <v>0.4459</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -13359,6 +13587,9 @@
       <c r="AI89" t="n">
         <v>0.1833</v>
       </c>
+      <c r="AJ89" t="n">
+        <v>0.4325</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -13418,6 +13649,9 @@
       <c r="AI90" t="n">
         <v>0.2327</v>
       </c>
+      <c r="AJ90" t="n">
+        <v>0.4422</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -13477,6 +13711,9 @@
       <c r="AI91" t="n">
         <v>0.2327</v>
       </c>
+      <c r="AJ91" t="n">
+        <v>0.4332</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -13536,6 +13773,9 @@
       <c r="AI92" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ92" t="n">
+        <v>0.442</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -13595,6 +13835,9 @@
       <c r="AI93" t="n">
         <v>0.1949</v>
       </c>
+      <c r="AJ93" t="n">
+        <v>0.4348</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -13654,6 +13897,9 @@
       <c r="AI94" t="n">
         <v>0.1447</v>
       </c>
+      <c r="AJ94" t="n">
+        <v>0.4344</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -13712,6 +13958,9 @@
       </c>
       <c r="AI95" t="n">
         <v>0.1</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>0.435</v>
       </c>
     </row>
     <row r="96">
@@ -14348,7 +14597,7 @@
         <v>0.9333333333333333</v>
       </c>
       <c r="AJ108" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="109">
@@ -14412,7 +14661,7 @@
         <v>1</v>
       </c>
       <c r="AJ109" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="110">
@@ -14476,7 +14725,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="AJ110" t="n">
-        <v>0.6</v>
+        <v>0.7692307692307693</v>
       </c>
     </row>
     <row r="111">
@@ -14540,7 +14789,7 @@
         <v>0.8181818181818182</v>
       </c>
       <c r="AJ111" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="112">
@@ -14604,7 +14853,7 @@
         <v>0.8181818181818182</v>
       </c>
       <c r="AJ112" t="n">
-        <v>1</v>
+        <v>0.7857142857142857</v>
       </c>
     </row>
     <row r="113">
@@ -14665,7 +14914,7 @@
         <v>0.7272727272727273</v>
       </c>
       <c r="AJ113" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="114">
@@ -14726,7 +14975,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="AJ114" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6923076923076923</v>
       </c>
     </row>
     <row r="115">
@@ -14786,6 +15035,9 @@
       <c r="AI115" t="n">
         <v>0.7</v>
       </c>
+      <c r="AJ115" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -14844,6 +15096,9 @@
       <c r="AI116" t="n">
         <v>0.7</v>
       </c>
+      <c r="AJ116" t="n">
+        <v>0.8461538461538461</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -14902,6 +15157,9 @@
       <c r="AI117" t="n">
         <v>0.7272727272727273</v>
       </c>
+      <c r="AJ117" t="n">
+        <v>0.3333333333333333</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -14954,6 +15212,9 @@
       <c r="AI118" t="n">
         <v>0.7777777777777778</v>
       </c>
+      <c r="AJ118" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -15006,6 +15267,9 @@
       <c r="AI119" t="n">
         <v>0.8333333333333334</v>
       </c>
+      <c r="AJ119" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -15058,6 +15322,9 @@
       <c r="AI120" t="n">
         <v>0.7272727272727273</v>
       </c>
+      <c r="AJ120" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -15110,6 +15377,9 @@
       <c r="AI121" t="n">
         <v>0.9</v>
       </c>
+      <c r="AJ121" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -15162,6 +15432,9 @@
       <c r="AI122" t="n">
         <v>0.9166666666666666</v>
       </c>
+      <c r="AJ122" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -15214,6 +15487,9 @@
       <c r="AI123" t="n">
         <v>0.9090909090909091</v>
       </c>
+      <c r="AJ123" t="n">
+        <v>0.7777777777777778</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -15266,6 +15542,9 @@
       <c r="AI124" t="n">
         <v>0.6666666666666666</v>
       </c>
+      <c r="AJ124" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -15318,6 +15597,9 @@
       <c r="AI125" t="n">
         <v>0.8181818181818182</v>
       </c>
+      <c r="AJ125" t="n">
+        <v>0.8181818181818182</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -15370,6 +15652,9 @@
       <c r="AI126" t="n">
         <v>1</v>
       </c>
+      <c r="AJ126" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -15422,6 +15707,9 @@
       <c r="AI127" t="n">
         <v>0.6428571428571429</v>
       </c>
+      <c r="AJ127" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -15474,6 +15762,9 @@
       <c r="AI128" t="n">
         <v>0.9</v>
       </c>
+      <c r="AJ128" t="n">
+        <v>0.7777777777777778</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -15526,6 +15817,9 @@
       <c r="AI129" t="n">
         <v>0.8</v>
       </c>
+      <c r="AJ129" t="n">
+        <v>0.7142857142857143</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -15578,6 +15872,9 @@
       <c r="AI130" t="n">
         <v>0.8</v>
       </c>
+      <c r="AJ130" t="n">
+        <v>0.5454545454545454</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -15630,6 +15927,9 @@
       <c r="AI131" t="n">
         <v>0.875</v>
       </c>
+      <c r="AJ131" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -15682,6 +15982,9 @@
       <c r="AI132" t="n">
         <v>0.9090909090909091</v>
       </c>
+      <c r="AJ132" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -15734,6 +16037,9 @@
       <c r="AI133" t="n">
         <v>0.8333333333333334</v>
       </c>
+      <c r="AJ133" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -15786,6 +16092,9 @@
       <c r="AI134" t="n">
         <v>0.8888888888888888</v>
       </c>
+      <c r="AJ134" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -15838,6 +16147,9 @@
       <c r="AI135" t="n">
         <v>0.8181818181818182</v>
       </c>
+      <c r="AJ135" t="n">
+        <v>0.7777777777777778</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -15890,6 +16202,9 @@
       <c r="AI136" t="n">
         <v>0.9</v>
       </c>
+      <c r="AJ136" t="n">
+        <v>0.4285714285714285</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -15942,6 +16257,9 @@
       <c r="AI137" t="n">
         <v>0.875</v>
       </c>
+      <c r="AJ137" t="n">
+        <v>0.8181818181818182</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -15994,6 +16312,9 @@
       <c r="AI138" t="n">
         <v>1</v>
       </c>
+      <c r="AJ138" t="n">
+        <v>0.7142857142857143</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -16046,6 +16367,9 @@
       <c r="AI139" t="n">
         <v>0.8571428571428571</v>
       </c>
+      <c r="AJ139" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -16098,6 +16422,9 @@
       <c r="AI140" t="n">
         <v>1</v>
       </c>
+      <c r="AJ140" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -16150,6 +16477,9 @@
       <c r="AI141" t="n">
         <v>1</v>
       </c>
+      <c r="AJ141" t="n">
+        <v>0.08333333333333333</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -16202,6 +16532,9 @@
       <c r="AI142" t="n">
         <v>0.8888888888888888</v>
       </c>
+      <c r="AJ142" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -16254,6 +16587,9 @@
       <c r="AI143" t="n">
         <v>1</v>
       </c>
+      <c r="AJ143" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -16306,6 +16642,9 @@
       <c r="AI144" t="n">
         <v>1</v>
       </c>
+      <c r="AJ144" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -16358,6 +16697,9 @@
       <c r="AI145" t="n">
         <v>0.5</v>
       </c>
+      <c r="AJ145" t="n">
+        <v>0.4285714285714285</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -16410,6 +16752,9 @@
       <c r="AI146" t="n">
         <v>0.5</v>
       </c>
+      <c r="AJ146" t="n">
+        <v>0.3333333333333333</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -16462,6 +16807,9 @@
       <c r="AI147" t="n">
         <v>1</v>
       </c>
+      <c r="AJ147" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -16514,6 +16862,9 @@
       <c r="AI148" t="n">
         <v>0.8</v>
       </c>
+      <c r="AJ148" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -16566,6 +16917,9 @@
       <c r="AI149" t="n">
         <v>1</v>
       </c>
+      <c r="AJ149" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -16618,6 +16972,9 @@
       <c r="AI150" t="n">
         <v>1</v>
       </c>
+      <c r="AJ150" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -16670,6 +17027,9 @@
       <c r="AI151" t="n">
         <v>0.6666666666666666</v>
       </c>
+      <c r="AJ151" t="n">
+        <v>0.3636363636363636</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -16722,6 +17082,9 @@
       <c r="AI152" t="n">
         <v>0.8333333333333334</v>
       </c>
+      <c r="AJ152" t="n">
+        <v>0.6363636363636364</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -16774,6 +17137,9 @@
       <c r="AI153" t="n">
         <v>1</v>
       </c>
+      <c r="AJ153" t="n">
+        <v>0.625</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -16826,6 +17192,9 @@
       <c r="AI154" t="n">
         <v>1</v>
       </c>
+      <c r="AJ154" t="n">
+        <v>0.7777777777777778</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -16878,6 +17247,9 @@
       <c r="AI155" t="n">
         <v>0.8571428571428571</v>
       </c>
+      <c r="AJ155" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -16930,6 +17302,9 @@
       <c r="AI156" t="n">
         <v>1</v>
       </c>
+      <c r="AJ156" t="n">
+        <v>0.5714285714285714</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -16982,6 +17357,9 @@
       <c r="AI157" t="n">
         <v>0.8571428571428571</v>
       </c>
+      <c r="AJ157" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -17034,6 +17412,9 @@
       <c r="AI158" t="n">
         <v>0.8</v>
       </c>
+      <c r="AJ158" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -17086,6 +17467,9 @@
       <c r="AI159" t="n">
         <v>1</v>
       </c>
+      <c r="AJ159" t="n">
+        <v>0.3333333333333333</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -17138,6 +17522,9 @@
       <c r="AI160" t="n">
         <v>0.625</v>
       </c>
+      <c r="AJ160" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -17190,6 +17577,9 @@
       <c r="AI161" t="n">
         <v>0.5555555555555556</v>
       </c>
+      <c r="AJ161" t="n">
+        <v>0.5555555555555556</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -17242,6 +17632,9 @@
       <c r="AI162" t="n">
         <v>0.75</v>
       </c>
+      <c r="AJ162" t="n">
+        <v>0.6363636363636364</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -17294,6 +17687,9 @@
       <c r="AI163" t="n">
         <v>0.8</v>
       </c>
+      <c r="AJ163" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -17346,6 +17742,9 @@
       <c r="AI164" t="n">
         <v>0.8571428571428571</v>
       </c>
+      <c r="AJ164" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -17398,6 +17797,9 @@
       <c r="AI165" t="n">
         <v>1</v>
       </c>
+      <c r="AJ165" t="n">
+        <v>0.3636363636363636</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -17450,6 +17852,9 @@
       <c r="AI166" t="n">
         <v>0.75</v>
       </c>
+      <c r="AJ166" t="n">
+        <v>0.625</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -17502,6 +17907,9 @@
       <c r="AI167" t="n">
         <v>1</v>
       </c>
+      <c r="AJ167" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -17554,6 +17962,9 @@
       <c r="AI168" t="n">
         <v>1</v>
       </c>
+      <c r="AJ168" t="n">
+        <v>0.5555555555555556</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -17606,6 +18017,9 @@
       <c r="AI169" t="n">
         <v>1</v>
       </c>
+      <c r="AJ169" t="n">
+        <v>0.2222222222222222</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -17658,6 +18072,9 @@
       <c r="AI170" t="n">
         <v>0.75</v>
       </c>
+      <c r="AJ170" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -17710,6 +18127,9 @@
       <c r="AI171" t="n">
         <v>1</v>
       </c>
+      <c r="AJ171" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -17762,6 +18182,9 @@
       <c r="AI172" t="n">
         <v>1</v>
       </c>
+      <c r="AJ172" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -17814,6 +18237,9 @@
       <c r="AI173" t="n">
         <v>0.8</v>
       </c>
+      <c r="AJ173" t="n">
+        <v>0.5555555555555556</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -17866,6 +18292,9 @@
       <c r="AI174" t="n">
         <v>1</v>
       </c>
+      <c r="AJ174" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -17918,6 +18347,9 @@
       <c r="AI175" t="n">
         <v>1</v>
       </c>
+      <c r="AJ175" t="n">
+        <v>0.2727272727272727</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -17970,6 +18402,9 @@
       <c r="AI176" t="n">
         <v>1</v>
       </c>
+      <c r="AJ176" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -18022,6 +18457,9 @@
       <c r="AI177" t="n">
         <v>1</v>
       </c>
+      <c r="AJ177" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -18074,6 +18512,9 @@
       <c r="AI178" t="n">
         <v>0.8</v>
       </c>
+      <c r="AJ178" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -18126,6 +18567,9 @@
       <c r="AI179" t="n">
         <v>1</v>
       </c>
+      <c r="AJ179" t="n">
+        <v>0.7142857142857143</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -18178,6 +18622,9 @@
       <c r="AI180" t="n">
         <v>0.5</v>
       </c>
+      <c r="AJ180" t="n">
+        <v>0.2857142857142857</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -18230,6 +18677,9 @@
       <c r="AI181" t="n">
         <v>1</v>
       </c>
+      <c r="AJ181" t="n">
+        <v>0.5714285714285714</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -18282,6 +18732,9 @@
       <c r="AI182" t="n">
         <v>1</v>
       </c>
+      <c r="AJ182" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -18334,6 +18787,9 @@
       <c r="AI183" t="n">
         <v>1</v>
       </c>
+      <c r="AJ183" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -18386,6 +18842,9 @@
       <c r="AI184" t="n">
         <v>1</v>
       </c>
+      <c r="AJ184" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -18438,6 +18897,9 @@
       <c r="AI185" t="n">
         <v>1</v>
       </c>
+      <c r="AJ185" t="n">
+        <v>0.5714285714285714</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -18490,6 +18952,9 @@
       <c r="AI186" t="n">
         <v>1</v>
       </c>
+      <c r="AJ186" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -18542,6 +19007,9 @@
       <c r="AI187" t="n">
         <v>1</v>
       </c>
+      <c r="AJ187" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -18594,6 +19062,9 @@
       <c r="AI188" t="n">
         <v>1</v>
       </c>
+      <c r="AJ188" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
@@ -18646,6 +19117,9 @@
       <c r="AI189" t="n">
         <v>1</v>
       </c>
+      <c r="AJ189" t="n">
+        <v>0.4285714285714285</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -18698,6 +19172,9 @@
       <c r="AI190" t="n">
         <v>1</v>
       </c>
+      <c r="AJ190" t="n">
+        <v>0.375</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -18750,6 +19227,9 @@
       <c r="AI191" t="n">
         <v>0.4</v>
       </c>
+      <c r="AJ191" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -18802,6 +19282,9 @@
       <c r="AI192" t="n">
         <v>0.75</v>
       </c>
+      <c r="AJ192" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -18854,6 +19337,9 @@
       <c r="AI193" t="n">
         <v>1</v>
       </c>
+      <c r="AJ193" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -18903,6 +19389,9 @@
       <c r="AH194" t="n">
         <v>0.6</v>
       </c>
+      <c r="AJ194" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -18955,6 +19444,9 @@
       <c r="AI195" t="n">
         <v>1</v>
       </c>
+      <c r="AJ195" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -19007,6 +19499,9 @@
       <c r="AI196" t="n">
         <v>1</v>
       </c>
+      <c r="AJ196" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -19059,6 +19554,9 @@
       <c r="AI197" t="n">
         <v>1</v>
       </c>
+      <c r="AJ197" t="n">
+        <v>0.625</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
@@ -19110,6 +19608,9 @@
       </c>
       <c r="AI198" t="n">
         <v>0.8333333333333334</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="199">
@@ -19684,7 +20185,7 @@
         <v>0.9658857142857143</v>
       </c>
       <c r="AJ212" t="n">
-        <v>0.9276857142857143</v>
+        <v>0.936111111111111</v>
       </c>
     </row>
     <row r="213">
@@ -19748,7 +20249,7 @@
         <v>0.8468571428571429</v>
       </c>
       <c r="AJ213" t="n">
-        <v>0.9668428571428571</v>
+        <v>0.9478500000000001</v>
       </c>
     </row>
     <row r="214">
@@ -19812,7 +20313,7 @@
         <v>0.8858333333333334</v>
       </c>
       <c r="AJ214" t="n">
-        <v>0.9774428571428572</v>
+        <v>0.9270400000000001</v>
       </c>
     </row>
     <row r="215">
@@ -19876,7 +20377,7 @@
         <v>0.9863166666666666</v>
       </c>
       <c r="AJ215" t="n">
-        <v>0.8854875</v>
+        <v>0.9197142857142857</v>
       </c>
     </row>
     <row r="216">
@@ -19939,10 +20440,8 @@
       <c r="AI216" t="n">
         <v>0.8197333333333333</v>
       </c>
-      <c r="AJ216" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="AJ216" t="n">
+        <v>0.9202250000000001</v>
       </c>
     </row>
     <row r="217">
@@ -20003,7 +20502,7 @@
         <v>0.9927142857142855</v>
       </c>
       <c r="AJ217" t="n">
-        <v>0.3832714285714286</v>
+        <v>0.9224333333333333</v>
       </c>
     </row>
     <row r="218">
@@ -20064,7 +20563,7 @@
         <v>0.9982200000000001</v>
       </c>
       <c r="AJ218" t="n">
-        <v>0.274</v>
+        <v>0.8960333333333333</v>
       </c>
     </row>
     <row r="219">
@@ -20126,6 +20625,9 @@
       <c r="AI219" t="n">
         <v>0.8679625</v>
       </c>
+      <c r="AJ219" t="n">
+        <v>0.9205</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
@@ -20186,6 +20688,9 @@
       <c r="AI220" t="n">
         <v>0.8760250000000001</v>
       </c>
+      <c r="AJ220" t="n">
+        <v>0.8922</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -20244,6 +20749,9 @@
       <c r="AI221" t="n">
         <v>0.9856285714285714</v>
       </c>
+      <c r="AJ221" t="n">
+        <v>0.8915166666666666</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
@@ -20296,6 +20804,9 @@
       <c r="AI222" t="n">
         <v>0.9943375</v>
       </c>
+      <c r="AJ222" t="n">
+        <v>0.9132444444444445</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
@@ -20348,6 +20859,9 @@
       <c r="AI223" t="n">
         <v>0.8468199999999999</v>
       </c>
+      <c r="AJ223" t="n">
+        <v>0.8975799999999999</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
@@ -20400,6 +20914,9 @@
       <c r="AI224" t="n">
         <v>0.9959571428571429</v>
       </c>
+      <c r="AJ224" t="n">
+        <v>0.86815</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
@@ -20452,6 +20969,9 @@
       <c r="AI225" t="n">
         <v>0.989</v>
       </c>
+      <c r="AJ225" t="n">
+        <v>0.8668142857142858</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
@@ -20504,6 +21024,9 @@
       <c r="AI226" t="n">
         <v>0.97255</v>
       </c>
+      <c r="AJ226" t="n">
+        <v>0.8794999999999999</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
@@ -20556,6 +21079,9 @@
       <c r="AI227" t="n">
         <v>0.81014</v>
       </c>
+      <c r="AJ227" t="n">
+        <v>0.8617833333333335</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
@@ -20608,6 +21134,9 @@
       <c r="AI228" t="n">
         <v>0.8912333333333334</v>
       </c>
+      <c r="AJ228" t="n">
+        <v>0.8654000000000001</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
@@ -20660,6 +21189,9 @@
       <c r="AI229" t="n">
         <v>0.9319833333333333</v>
       </c>
+      <c r="AJ229" t="n">
+        <v>0.893925</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
@@ -20712,6 +21244,9 @@
       <c r="AI230" t="n">
         <v>0.9897333333333332</v>
       </c>
+      <c r="AJ230" t="n">
+        <v>0.8520142857142857</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
@@ -20764,6 +21299,9 @@
       <c r="AI231" t="n">
         <v>0.9861333333333334</v>
       </c>
+      <c r="AJ231" t="n">
+        <v>0.8441599999999999</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
@@ -20816,6 +21354,9 @@
       <c r="AI232" t="n">
         <v>0.9921833333333333</v>
       </c>
+      <c r="AJ232" t="n">
+        <v>0.8473000000000001</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
@@ -20868,6 +21409,9 @@
       <c r="AI233" t="n">
         <v>0.9827285714285715</v>
       </c>
+      <c r="AJ233" t="n">
+        <v>0.8876000000000001</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
@@ -20920,6 +21464,9 @@
       <c r="AI234" t="n">
         <v>0.8867714285714285</v>
       </c>
+      <c r="AJ234" t="n">
+        <v>0.8675250000000001</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
@@ -20972,6 +21519,9 @@
       <c r="AI235" t="n">
         <v>0.9881375</v>
       </c>
+      <c r="AJ235" t="n">
+        <v>0.877</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
@@ -21024,6 +21574,9 @@
       <c r="AI236" t="n">
         <v>0.9941000000000001</v>
       </c>
+      <c r="AJ236" t="n">
+        <v>0.8574857142857143</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
@@ -21076,6 +21629,9 @@
       <c r="AI237" t="n">
         <v>0.9599800000000001</v>
       </c>
+      <c r="AJ237" t="n">
+        <v>0.85584</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
@@ -21128,6 +21684,9 @@
       <c r="AI238" t="n">
         <v>0.9938285714285714</v>
       </c>
+      <c r="AJ238" t="n">
+        <v>0.8513300000000001</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
@@ -21180,6 +21739,9 @@
       <c r="AI239" t="n">
         <v>0.9918833333333333</v>
       </c>
+      <c r="AJ239" t="n">
+        <v>0.8556833333333334</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
@@ -21232,6 +21794,9 @@
       <c r="AI240" t="n">
         <v>0.9929</v>
       </c>
+      <c r="AJ240" t="n">
+        <v>0.863625</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
@@ -21284,6 +21849,9 @@
       <c r="AI241" t="n">
         <v>0.9923124999999999</v>
       </c>
+      <c r="AJ241" t="n">
+        <v>0.8387500000000001</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
@@ -21336,6 +21904,9 @@
       <c r="AI242" t="n">
         <v>0.8736555555555554</v>
       </c>
+      <c r="AJ242" t="n">
+        <v>0.8280750000000001</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
@@ -21388,6 +21959,9 @@
       <c r="AI243" t="n">
         <v>0.8641999999999999</v>
       </c>
+      <c r="AJ243" t="n">
+        <v>0.87582</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
@@ -21440,6 +22014,9 @@
       <c r="AI244" t="n">
         <v>0.6879</v>
       </c>
+      <c r="AJ244" t="n">
+        <v>0.8493857142857143</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
@@ -21492,6 +22069,9 @@
       <c r="AI245" t="n">
         <v>0.99176</v>
       </c>
+      <c r="AJ245" t="n">
+        <v>0.8000666666666666</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
@@ -21544,6 +22124,9 @@
       <c r="AI246" t="n">
         <v>0.9963142857142858</v>
       </c>
+      <c r="AJ246" t="n">
+        <v>0.8438428571428572</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
@@ -21596,6 +22179,9 @@
       <c r="AI247" t="n">
         <v>0.9844714285714286</v>
       </c>
+      <c r="AJ247" t="n">
+        <v>0.8600000000000001</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
@@ -21648,6 +22234,9 @@
       <c r="AI248" t="n">
         <v>0.8516285714285715</v>
       </c>
+      <c r="AJ248" t="n">
+        <v>0.84902</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
@@ -21700,6 +22289,9 @@
       <c r="AI249" t="n">
         <v>0.9866333333333334</v>
       </c>
+      <c r="AJ249" t="n">
+        <v>0.8609499999999999</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
@@ -21752,6 +22344,9 @@
       <c r="AI250" t="n">
         <v>0.8845333333333333</v>
       </c>
+      <c r="AJ250" t="n">
+        <v>0.86485</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
@@ -21804,6 +22399,9 @@
       <c r="AI251" t="n">
         <v>0.69035</v>
       </c>
+      <c r="AJ251" t="n">
+        <v>0.85972</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
@@ -21856,6 +22454,9 @@
       <c r="AI252" t="n">
         <v>0.7249727272727272</v>
       </c>
+      <c r="AJ252" t="n">
+        <v>0.8108714285714286</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
@@ -21908,6 +22509,9 @@
       <c r="AI253" t="n">
         <v>0.8805222222222223</v>
       </c>
+      <c r="AJ253" t="n">
+        <v>0.8481099999999999</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
@@ -21960,6 +22564,9 @@
       <c r="AI254" t="n">
         <v>0.79576</v>
       </c>
+      <c r="AJ254" t="n">
+        <v>0.8564666666666666</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
@@ -22012,6 +22619,9 @@
       <c r="AI255" t="n">
         <v>0.6875538461538462</v>
       </c>
+      <c r="AJ255" t="n">
+        <v>0.8437749999999999</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
@@ -22064,6 +22674,9 @@
       <c r="AI256" t="n">
         <v>0.79863</v>
       </c>
+      <c r="AJ256" t="n">
+        <v>0.810275</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
@@ -22116,6 +22729,9 @@
       <c r="AI257" t="n">
         <v>0.6415727272727273</v>
       </c>
+      <c r="AJ257" t="n">
+        <v>0.8225857142857144</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
@@ -22168,6 +22784,9 @@
       <c r="AI258" t="n">
         <v>0.69429</v>
       </c>
+      <c r="AJ258" t="n">
+        <v>0.8418499999999999</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
@@ -22220,6 +22839,9 @@
       <c r="AI259" t="n">
         <v>0.6539555555555556</v>
       </c>
+      <c r="AJ259" t="n">
+        <v>0.8089888888888888</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
@@ -22272,6 +22894,9 @@
       <c r="AI260" t="n">
         <v>0.65415</v>
       </c>
+      <c r="AJ260" t="n">
+        <v>0.8360624999999999</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
@@ -22324,6 +22949,9 @@
       <c r="AI261" t="n">
         <v>0.8725222222222222</v>
       </c>
+      <c r="AJ261" t="n">
+        <v>0.8252166666666666</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
@@ -22376,6 +23004,9 @@
       <c r="AI262" t="n">
         <v>0.7095181818181818</v>
       </c>
+      <c r="AJ262" t="n">
+        <v>0.8382499999999999</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
@@ -22428,6 +23059,9 @@
       <c r="AI263" t="n">
         <v>0.8658857142857144</v>
       </c>
+      <c r="AJ263" t="n">
+        <v>0.8127666666666666</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
@@ -22480,6 +23114,9 @@
       <c r="AI264" t="n">
         <v>0.5676285714285714</v>
       </c>
+      <c r="AJ264" t="n">
+        <v>0.8460599999999999</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
@@ -22532,6 +23169,9 @@
       <c r="AI265" t="n">
         <v>0.4132000000000001</v>
       </c>
+      <c r="AJ265" t="n">
+        <v>0.8023166666666667</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
@@ -22584,6 +23224,9 @@
       <c r="AI266" t="n">
         <v>0.7401</v>
       </c>
+      <c r="AJ266" t="n">
+        <v>0.8532000000000001</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
@@ -22636,6 +23279,9 @@
       <c r="AI267" t="n">
         <v>0.6399181818181819</v>
       </c>
+      <c r="AJ267" t="n">
+        <v>0.86492</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
@@ -22688,6 +23334,9 @@
       <c r="AI268" t="n">
         <v>0.4583555555555556</v>
       </c>
+      <c r="AJ268" t="n">
+        <v>0.8317600000000001</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
@@ -22740,6 +23389,9 @@
       <c r="AI269" t="n">
         <v>0.9101500000000001</v>
       </c>
+      <c r="AJ269" t="n">
+        <v>0.8783500000000001</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
@@ -22792,6 +23444,9 @@
       <c r="AI270" t="n">
         <v>0.6957083333333333</v>
       </c>
+      <c r="AJ270" t="n">
+        <v>0.8458571428571429</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
@@ -22844,6 +23499,9 @@
       <c r="AI271" t="n">
         <v>0.7372083333333332</v>
       </c>
+      <c r="AJ271" t="n">
+        <v>0.8659</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
@@ -22896,6 +23554,9 @@
       <c r="AI272" t="n">
         <v>0.7539166666666667</v>
       </c>
+      <c r="AJ272" t="n">
+        <v>0.8267166666666667</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
@@ -22948,6 +23609,9 @@
       <c r="AI273" t="n">
         <v>0.4423727272727273</v>
       </c>
+      <c r="AJ273" t="n">
+        <v>0.8344499999999999</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
@@ -23000,6 +23664,9 @@
       <c r="AI274" t="n">
         <v>0.6609333333333333</v>
       </c>
+      <c r="AJ274" t="n">
+        <v>0.8324142857142857</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
@@ -23052,6 +23719,9 @@
       <c r="AI275" t="n">
         <v>0.654875</v>
       </c>
+      <c r="AJ275" t="n">
+        <v>0.8711666666666668</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
@@ -23104,6 +23774,9 @@
       <c r="AI276" t="n">
         <v>0.723509090909091</v>
       </c>
+      <c r="AJ276" t="n">
+        <v>0.8751599999999999</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
@@ -23156,6 +23829,9 @@
       <c r="AI277" t="n">
         <v>0.6337545454545453</v>
       </c>
+      <c r="AJ277" t="n">
+        <v>0.8717</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
@@ -23208,6 +23884,9 @@
       <c r="AI278" t="n">
         <v>0.6305181818181818</v>
       </c>
+      <c r="AJ278" t="n">
+        <v>0.8425428571428571</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
@@ -23260,6 +23939,9 @@
       <c r="AI279" t="n">
         <v>0.5742399999999999</v>
       </c>
+      <c r="AJ279" t="n">
+        <v>0.8514250000000001</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
@@ -23312,6 +23994,9 @@
       <c r="AI280" t="n">
         <v>0.6294818181818183</v>
       </c>
+      <c r="AJ280" t="n">
+        <v>0.8547399999999999</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
@@ -23364,6 +24049,9 @@
       <c r="AI281" t="n">
         <v>0.5350384615384616</v>
       </c>
+      <c r="AJ281" t="n">
+        <v>0.8309799999999999</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
@@ -23416,6 +24104,9 @@
       <c r="AI282" t="n">
         <v>0.5364</v>
       </c>
+      <c r="AJ282" t="n">
+        <v>0.8591499999999999</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
@@ -23468,6 +24159,9 @@
       <c r="AI283" t="n">
         <v>0.6825307692307692</v>
       </c>
+      <c r="AJ283" t="n">
+        <v>0.8156625000000001</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
@@ -23520,6 +24214,9 @@
       <c r="AI284" t="n">
         <v>0.6116714285714286</v>
       </c>
+      <c r="AJ284" t="n">
+        <v>0.815625</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
@@ -23572,6 +24269,9 @@
       <c r="AI285" t="n">
         <v>0.4963928571428571</v>
       </c>
+      <c r="AJ285" t="n">
+        <v>0.8539875</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
@@ -23624,6 +24324,9 @@
       <c r="AI286" t="n">
         <v>0.49677</v>
       </c>
+      <c r="AJ286" t="n">
+        <v>0.8410000000000001</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
@@ -23676,6 +24379,9 @@
       <c r="AI287" t="n">
         <v>0.4635083333333332</v>
       </c>
+      <c r="AJ287" t="n">
+        <v>0.83048</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
@@ -23728,6 +24434,9 @@
       <c r="AI288" t="n">
         <v>0.7629461538461538</v>
       </c>
+      <c r="AJ288" t="n">
+        <v>0.7994285714285715</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
@@ -23780,6 +24489,9 @@
       <c r="AI289" t="n">
         <v>0.5772499999999999</v>
       </c>
+      <c r="AJ289" t="n">
+        <v>0.8455625000000001</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
@@ -23832,6 +24544,9 @@
       <c r="AI290" t="n">
         <v>0.6123000000000001</v>
       </c>
+      <c r="AJ290" t="n">
+        <v>0.82806</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
@@ -23884,6 +24599,9 @@
       <c r="AI291" t="n">
         <v>0.584790909090909</v>
       </c>
+      <c r="AJ291" t="n">
+        <v>0.82032</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
@@ -23936,6 +24654,9 @@
       <c r="AI292" t="n">
         <v>0.4132416666666667</v>
       </c>
+      <c r="AJ292" t="n">
+        <v>0.8719571428571429</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
@@ -23988,6 +24709,9 @@
       <c r="AI293" t="n">
         <v>0.579175</v>
       </c>
+      <c r="AJ293" t="n">
+        <v>0.8448749999999999</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
@@ -24040,6 +24764,9 @@
       <c r="AI294" t="n">
         <v>0.6215363636363637</v>
       </c>
+      <c r="AJ294" t="n">
+        <v>0.8622</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
@@ -24092,6 +24819,9 @@
       <c r="AI295" t="n">
         <v>0.4937300000000001</v>
       </c>
+      <c r="AJ295" t="n">
+        <v>0.8437</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
@@ -24144,6 +24874,9 @@
       <c r="AI296" t="n">
         <v>0.5772666666666667</v>
       </c>
+      <c r="AJ296" t="n">
+        <v>0.8250166666666666</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
@@ -24196,6 +24929,9 @@
       <c r="AI297" t="n">
         <v>0.6120181818181818</v>
       </c>
+      <c r="AJ297" t="n">
+        <v>0.8578571428571429</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
@@ -24245,6 +24981,9 @@
       <c r="AH298" t="n">
         <v>0.9347111111111109</v>
       </c>
+      <c r="AJ298" t="n">
+        <v>0.82958</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
@@ -24297,6 +25036,9 @@
       <c r="AI299" t="n">
         <v>0.5577285714285715</v>
       </c>
+      <c r="AJ299" t="n">
+        <v>0.84924</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
@@ -24349,6 +25091,9 @@
       <c r="AI300" t="n">
         <v>0.4594153846153847</v>
       </c>
+      <c r="AJ300" t="n">
+        <v>0.8211999999999999</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
@@ -24401,6 +25146,9 @@
       <c r="AI301" t="n">
         <v>0.6131272727272727</v>
       </c>
+      <c r="AJ301" t="n">
+        <v>0.8440428571428571</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
@@ -24452,6 +25200,9 @@
       </c>
       <c r="AI302" t="n">
         <v>0.49454</v>
+      </c>
+      <c r="AJ302" t="n">
+        <v>0.8570399999999999</v>
       </c>
     </row>
     <row r="303">
@@ -25028,7 +25779,7 @@
         <v>0.9558</v>
       </c>
       <c r="AJ316" t="n">
-        <v>0</v>
+        <v>0.0035</v>
       </c>
     </row>
     <row r="317">
@@ -25092,7 +25843,7 @@
         <v>0</v>
       </c>
       <c r="AJ317" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="318">
@@ -25156,7 +25907,7 @@
         <v>0</v>
       </c>
       <c r="AJ318" t="n">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="319">
@@ -25220,7 +25971,7 @@
         <v>0.0044</v>
       </c>
       <c r="AJ319" t="n">
-        <v>0.2326</v>
+        <v>0.0188</v>
       </c>
     </row>
     <row r="320">
@@ -25284,7 +26035,7 @@
         <v>0.1013</v>
       </c>
       <c r="AJ320" t="n">
-        <v>0</v>
+        <v>0.1279</v>
       </c>
     </row>
     <row r="321">
@@ -25345,7 +26096,7 @@
         <v>1</v>
       </c>
       <c r="AJ321" t="n">
-        <v>0.743</v>
+        <v>0.1657</v>
       </c>
     </row>
     <row r="322">
@@ -25406,7 +26157,7 @@
         <v>0.9284</v>
       </c>
       <c r="AJ322" t="n">
-        <v>0.743</v>
+        <v>0.0402</v>
       </c>
     </row>
     <row r="323">
@@ -25467,7 +26218,7 @@
         <v>0.9044</v>
       </c>
       <c r="AJ323" t="n">
-        <v>0.743</v>
+        <v>0.1131</v>
       </c>
     </row>
     <row r="324">
@@ -25527,6 +26278,9 @@
       <c r="AI324" t="n">
         <v>0.7281</v>
       </c>
+      <c r="AJ324" t="n">
+        <v>0.0191</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
@@ -25585,6 +26339,9 @@
       <c r="AI325" t="n">
         <v>0.9208</v>
       </c>
+      <c r="AJ325" t="n">
+        <v>0.105</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
@@ -25637,6 +26394,9 @@
       <c r="AI326" t="n">
         <v>0.9681999999999999</v>
       </c>
+      <c r="AJ326" t="n">
+        <v>0.0219</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
@@ -25689,6 +26449,9 @@
       <c r="AI327" t="n">
         <v>0.7435</v>
       </c>
+      <c r="AJ327" t="n">
+        <v>0.1532</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
@@ -25741,6 +26504,9 @@
       <c r="AI328" t="n">
         <v>0.5639999999999999</v>
       </c>
+      <c r="AJ328" t="n">
+        <v>0.1418</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
@@ -25793,6 +26559,9 @@
       <c r="AI329" t="n">
         <v>0.2936</v>
       </c>
+      <c r="AJ329" t="n">
+        <v>0.1263</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
@@ -25845,6 +26614,9 @@
       <c r="AI330" t="n">
         <v>0.846</v>
       </c>
+      <c r="AJ330" t="n">
+        <v>0.0457</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
@@ -25897,6 +26669,9 @@
       <c r="AI331" t="n">
         <v>1</v>
       </c>
+      <c r="AJ331" t="n">
+        <v>0.0926</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
@@ -25949,6 +26724,9 @@
       <c r="AI332" t="n">
         <v>0.9996</v>
       </c>
+      <c r="AJ332" t="n">
+        <v>0.1191</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
@@ -26001,6 +26779,9 @@
       <c r="AI333" t="n">
         <v>0.9869</v>
       </c>
+      <c r="AJ333" t="n">
+        <v>0.0677</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
@@ -26053,6 +26834,9 @@
       <c r="AI334" t="n">
         <v>0.9952</v>
       </c>
+      <c r="AJ334" t="n">
+        <v>0.0469</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
@@ -26105,6 +26889,9 @@
       <c r="AI335" t="n">
         <v>0.9198</v>
       </c>
+      <c r="AJ335" t="n">
+        <v>0.1161</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
@@ -26157,6 +26944,9 @@
       <c r="AI336" t="n">
         <v>0.9959</v>
       </c>
+      <c r="AJ336" t="n">
+        <v>0.1399</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
@@ -26209,6 +26999,9 @@
       <c r="AI337" t="n">
         <v>0.8288</v>
       </c>
+      <c r="AJ337" t="n">
+        <v>0.0672</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
@@ -26261,6 +27054,9 @@
       <c r="AI338" t="n">
         <v>0.9957</v>
       </c>
+      <c r="AJ338" t="n">
+        <v>0.1072</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
@@ -26313,6 +27109,9 @@
       <c r="AI339" t="n">
         <v>1</v>
       </c>
+      <c r="AJ339" t="n">
+        <v>0.0721</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
@@ -26365,6 +27164,9 @@
       <c r="AI340" t="n">
         <v>0.9986</v>
       </c>
+      <c r="AJ340" t="n">
+        <v>0.0459</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
@@ -26417,6 +27219,9 @@
       <c r="AI341" t="n">
         <v>0.9978</v>
       </c>
+      <c r="AJ341" t="n">
+        <v>0.1061</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
@@ -26469,6 +27274,9 @@
       <c r="AI342" t="n">
         <v>0.9865</v>
       </c>
+      <c r="AJ342" t="n">
+        <v>0.1175</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
@@ -26521,6 +27329,9 @@
       <c r="AI343" t="n">
         <v>0.9486</v>
       </c>
+      <c r="AJ343" t="n">
+        <v>0.1197</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
@@ -26573,6 +27384,9 @@
       <c r="AI344" t="n">
         <v>0.9975000000000001</v>
       </c>
+      <c r="AJ344" t="n">
+        <v>0.0978</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
@@ -26625,6 +27439,9 @@
       <c r="AI345" t="n">
         <v>0.9137999999999999</v>
       </c>
+      <c r="AJ345" t="n">
+        <v>0.09470000000000001</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
@@ -26677,6 +27494,9 @@
       <c r="AI346" t="n">
         <v>0</v>
       </c>
+      <c r="AJ346" t="n">
+        <v>0.1342</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
@@ -26729,6 +27549,9 @@
       <c r="AI347" t="n">
         <v>0.9943</v>
       </c>
+      <c r="AJ347" t="n">
+        <v>0.1124</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
@@ -26781,6 +27604,9 @@
       <c r="AI348" t="n">
         <v>0</v>
       </c>
+      <c r="AJ348" t="n">
+        <v>0.1427</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
@@ -26833,6 +27659,9 @@
       <c r="AI349" t="n">
         <v>0.0578</v>
       </c>
+      <c r="AJ349" t="n">
+        <v>0.1128</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
@@ -26885,6 +27714,9 @@
       <c r="AI350" t="n">
         <v>0.9639</v>
       </c>
+      <c r="AJ350" t="n">
+        <v>0.1134</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
@@ -26937,6 +27769,9 @@
       <c r="AI351" t="n">
         <v>1</v>
       </c>
+      <c r="AJ351" t="n">
+        <v>0.1091</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
@@ -26989,6 +27824,9 @@
       <c r="AI352" t="n">
         <v>0.9802999999999999</v>
       </c>
+      <c r="AJ352" t="n">
+        <v>0.0788</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
@@ -27041,6 +27879,9 @@
       <c r="AI353" t="n">
         <v>1</v>
       </c>
+      <c r="AJ353" t="n">
+        <v>0.09859999999999999</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
@@ -27093,6 +27934,9 @@
       <c r="AI354" t="n">
         <v>0.9728</v>
       </c>
+      <c r="AJ354" t="n">
+        <v>0.1055</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
@@ -27145,6 +27989,9 @@
       <c r="AI355" t="n">
         <v>0</v>
       </c>
+      <c r="AJ355" t="n">
+        <v>0.1042</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
@@ -27197,6 +28044,9 @@
       <c r="AI356" t="n">
         <v>0.1606</v>
       </c>
+      <c r="AJ356" t="n">
+        <v>0.0961</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
@@ -27249,6 +28099,9 @@
       <c r="AI357" t="n">
         <v>0</v>
       </c>
+      <c r="AJ357" t="n">
+        <v>0.1008</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
@@ -27301,6 +28154,9 @@
       <c r="AI358" t="n">
         <v>0</v>
       </c>
+      <c r="AJ358" t="n">
+        <v>0.1019</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
@@ -27353,6 +28209,9 @@
       <c r="AI359" t="n">
         <v>0.8582</v>
       </c>
+      <c r="AJ359" t="n">
+        <v>0.1123</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
@@ -27405,6 +28264,9 @@
       <c r="AI360" t="n">
         <v>0.9298</v>
       </c>
+      <c r="AJ360" t="n">
+        <v>0.1037</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
@@ -27457,6 +28319,9 @@
       <c r="AI361" t="n">
         <v>0</v>
       </c>
+      <c r="AJ361" t="n">
+        <v>0.07779999999999999</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
@@ -27509,6 +28374,9 @@
       <c r="AI362" t="n">
         <v>0</v>
       </c>
+      <c r="AJ362" t="n">
+        <v>0.1028</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
@@ -27561,6 +28429,9 @@
       <c r="AI363" t="n">
         <v>0</v>
       </c>
+      <c r="AJ363" t="n">
+        <v>0.0945</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
@@ -27613,6 +28484,9 @@
       <c r="AI364" t="n">
         <v>0</v>
       </c>
+      <c r="AJ364" t="n">
+        <v>0.1214</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
@@ -27665,6 +28539,9 @@
       <c r="AI365" t="n">
         <v>0</v>
       </c>
+      <c r="AJ365" t="n">
+        <v>0.097</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
@@ -27717,6 +28594,9 @@
       <c r="AI366" t="n">
         <v>1</v>
       </c>
+      <c r="AJ366" t="n">
+        <v>0.0832</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
@@ -27769,6 +28649,9 @@
       <c r="AI367" t="n">
         <v>0</v>
       </c>
+      <c r="AJ367" t="n">
+        <v>0.1052</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
@@ -27821,6 +28704,9 @@
       <c r="AI368" t="n">
         <v>0</v>
       </c>
+      <c r="AJ368" t="n">
+        <v>0.1062</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
@@ -27873,6 +28759,9 @@
       <c r="AI369" t="n">
         <v>0.4487</v>
       </c>
+      <c r="AJ369" t="n">
+        <v>0.1004</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
@@ -27925,6 +28814,9 @@
       <c r="AI370" t="n">
         <v>1</v>
       </c>
+      <c r="AJ370" t="n">
+        <v>0.0853</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
@@ -27977,6 +28869,9 @@
       <c r="AI371" t="n">
         <v>0.9911</v>
       </c>
+      <c r="AJ371" t="n">
+        <v>0.09279999999999999</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
@@ -28029,6 +28924,9 @@
       <c r="AI372" t="n">
         <v>0.9928</v>
       </c>
+      <c r="AJ372" t="n">
+        <v>0.1066</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
@@ -28081,6 +28979,9 @@
       <c r="AI373" t="n">
         <v>1</v>
       </c>
+      <c r="AJ373" t="n">
+        <v>0.09959999999999999</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
@@ -28133,6 +29034,9 @@
       <c r="AI374" t="n">
         <v>0.9956</v>
       </c>
+      <c r="AJ374" t="n">
+        <v>0.0888</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
@@ -28185,6 +29089,9 @@
       <c r="AI375" t="n">
         <v>1</v>
       </c>
+      <c r="AJ375" t="n">
+        <v>0.0461</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
@@ -28237,6 +29144,9 @@
       <c r="AI376" t="n">
         <v>0</v>
       </c>
+      <c r="AJ376" t="n">
+        <v>0.0492</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
@@ -28289,6 +29199,9 @@
       <c r="AI377" t="n">
         <v>0</v>
       </c>
+      <c r="AJ377" t="n">
+        <v>0.0615</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
@@ -28341,6 +29254,9 @@
       <c r="AI378" t="n">
         <v>0</v>
       </c>
+      <c r="AJ378" t="n">
+        <v>0.1055</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
@@ -28393,6 +29309,9 @@
       <c r="AI379" t="n">
         <v>0</v>
       </c>
+      <c r="AJ379" t="n">
+        <v>0.0897</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
@@ -28445,6 +29364,9 @@
       <c r="AI380" t="n">
         <v>0.4348</v>
       </c>
+      <c r="AJ380" t="n">
+        <v>0.0881</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
@@ -28497,6 +29419,9 @@
       <c r="AI381" t="n">
         <v>0.9605</v>
       </c>
+      <c r="AJ381" t="n">
+        <v>0.1029</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
@@ -28549,6 +29474,9 @@
       <c r="AI382" t="n">
         <v>0</v>
       </c>
+      <c r="AJ382" t="n">
+        <v>0.1014</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
@@ -28601,6 +29529,9 @@
       <c r="AI383" t="n">
         <v>0</v>
       </c>
+      <c r="AJ383" t="n">
+        <v>0.1244</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
@@ -28653,6 +29584,9 @@
       <c r="AI384" t="n">
         <v>0</v>
       </c>
+      <c r="AJ384" t="n">
+        <v>0.1071</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
@@ -28705,6 +29639,9 @@
       <c r="AI385" t="n">
         <v>0</v>
       </c>
+      <c r="AJ385" t="n">
+        <v>0.1123</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
@@ -28757,6 +29694,9 @@
       <c r="AI386" t="n">
         <v>0</v>
       </c>
+      <c r="AJ386" t="n">
+        <v>0.09039999999999999</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
@@ -28809,6 +29749,9 @@
       <c r="AI387" t="n">
         <v>0</v>
       </c>
+      <c r="AJ387" t="n">
+        <v>0.07920000000000001</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
@@ -28861,6 +29804,9 @@
       <c r="AI388" t="n">
         <v>0.9457</v>
       </c>
+      <c r="AJ388" t="n">
+        <v>0.0955</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
@@ -28913,6 +29859,9 @@
       <c r="AI389" t="n">
         <v>0</v>
       </c>
+      <c r="AJ389" t="n">
+        <v>0.1156</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
@@ -28965,6 +29914,9 @@
       <c r="AI390" t="n">
         <v>0</v>
       </c>
+      <c r="AJ390" t="n">
+        <v>0.1201</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
@@ -29017,6 +29969,9 @@
       <c r="AI391" t="n">
         <v>0</v>
       </c>
+      <c r="AJ391" t="n">
+        <v>0.0934</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
@@ -29069,6 +30024,9 @@
       <c r="AI392" t="n">
         <v>0</v>
       </c>
+      <c r="AJ392" t="n">
+        <v>0.0827</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
@@ -29121,6 +30079,9 @@
       <c r="AI393" t="n">
         <v>0.8885999999999999</v>
       </c>
+      <c r="AJ393" t="n">
+        <v>0.0983</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
@@ -29173,6 +30134,9 @@
       <c r="AI394" t="n">
         <v>0</v>
       </c>
+      <c r="AJ394" t="n">
+        <v>0.0919</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
@@ -29225,6 +30189,9 @@
       <c r="AI395" t="n">
         <v>0.004</v>
       </c>
+      <c r="AJ395" t="n">
+        <v>0.1099</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
@@ -29277,6 +30244,9 @@
       <c r="AI396" t="n">
         <v>0</v>
       </c>
+      <c r="AJ396" t="n">
+        <v>0.0964</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
@@ -29329,6 +30299,9 @@
       <c r="AI397" t="n">
         <v>0</v>
       </c>
+      <c r="AJ397" t="n">
+        <v>0.0917</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
@@ -29381,6 +30354,9 @@
       <c r="AI398" t="n">
         <v>0</v>
       </c>
+      <c r="AJ398" t="n">
+        <v>0.0901</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
@@ -29433,6 +30409,9 @@
       <c r="AI399" t="n">
         <v>0</v>
       </c>
+      <c r="AJ399" t="n">
+        <v>0.0955</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
@@ -29485,6 +30464,9 @@
       <c r="AI400" t="n">
         <v>0.6539</v>
       </c>
+      <c r="AJ400" t="n">
+        <v>0.097</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
@@ -29537,6 +30519,9 @@
       <c r="AI401" t="n">
         <v>0</v>
       </c>
+      <c r="AJ401" t="n">
+        <v>0.1237</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="n">
@@ -29589,6 +30574,9 @@
       <c r="AI402" t="n">
         <v>0</v>
       </c>
+      <c r="AJ402" t="n">
+        <v>0.1138</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
@@ -29641,6 +30629,9 @@
       <c r="AI403" t="n">
         <v>0</v>
       </c>
+      <c r="AJ403" t="n">
+        <v>0.1078</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
@@ -29693,6 +30684,9 @@
       <c r="AI404" t="n">
         <v>0</v>
       </c>
+      <c r="AJ404" t="n">
+        <v>0.0984</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
@@ -29745,6 +30739,9 @@
       <c r="AI405" t="n">
         <v>0.0023</v>
       </c>
+      <c r="AJ405" t="n">
+        <v>0.1093</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
@@ -29796,6 +30793,9 @@
       </c>
       <c r="AI406" t="n">
         <v>1</v>
+      </c>
+      <c r="AJ406" t="n">
+        <v>0.1216</v>
       </c>
     </row>
     <row r="407">

--- a/CIFAR_Global.xlsx
+++ b/CIFAR_Global.xlsx
@@ -8314,7 +8314,7 @@
         <v>0.0999</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.1451</v>
+        <v>0.1178</v>
       </c>
     </row>
     <row r="6">
@@ -8385,7 +8385,7 @@
         <v>0.0999</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.1776</v>
+        <v>0.1359</v>
       </c>
     </row>
     <row r="7">
@@ -8456,7 +8456,7 @@
         <v>0.1529</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.2412</v>
+        <v>0.2568</v>
       </c>
     </row>
     <row r="8">
@@ -8527,7 +8527,7 @@
         <v>0.1115</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.2753</v>
+        <v>0.2805</v>
       </c>
     </row>
     <row r="9">
@@ -8598,7 +8598,7 @@
         <v>0.1121</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.3397</v>
+        <v>0.2879</v>
       </c>
     </row>
     <row r="10">
@@ -8666,7 +8666,7 @@
         <v>0.1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.3398</v>
+        <v>0.3319</v>
       </c>
     </row>
     <row r="11">
@@ -8734,7 +8734,7 @@
         <v>0.1122</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.371</v>
+        <v>0.3523</v>
       </c>
     </row>
     <row r="12">
@@ -8802,7 +8802,7 @@
         <v>0.1314</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.3819</v>
+        <v>0.3623</v>
       </c>
     </row>
     <row r="13">
@@ -8870,7 +8870,7 @@
         <v>0.1433</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.3639</v>
+        <v>0.3563</v>
       </c>
     </row>
     <row r="14">
@@ -8938,7 +8938,7 @@
         <v>0.1074</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.3883</v>
+        <v>0.3897</v>
       </c>
     </row>
     <row r="15">
@@ -9000,7 +9000,7 @@
         <v>0.107</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.3739</v>
+        <v>0.4156</v>
       </c>
     </row>
     <row r="16">
@@ -9062,7 +9062,7 @@
         <v>0.1092</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.4131</v>
+        <v>0.4116</v>
       </c>
     </row>
     <row r="17">
@@ -9124,7 +9124,7 @@
         <v>0.094</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.4237</v>
+        <v>0.4178</v>
       </c>
     </row>
     <row r="18">
@@ -9186,7 +9186,7 @@
         <v>0.0944</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.4181</v>
+        <v>0.3976</v>
       </c>
     </row>
     <row r="19">
@@ -9248,7 +9248,7 @@
         <v>0.0955</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.4194</v>
+        <v>0.4065</v>
       </c>
     </row>
     <row r="20">
@@ -9310,7 +9310,7 @@
         <v>0.1</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.4259</v>
+        <v>0.4254</v>
       </c>
     </row>
     <row r="21">
@@ -9372,7 +9372,7 @@
         <v>0.1228</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.4252</v>
+        <v>0.4087</v>
       </c>
     </row>
     <row r="22">
@@ -9434,7 +9434,7 @@
         <v>0.1179</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.4283</v>
+        <v>0.4222</v>
       </c>
     </row>
     <row r="23">
@@ -9496,7 +9496,7 @@
         <v>0.1213</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.4113</v>
+        <v>0.4327</v>
       </c>
     </row>
     <row r="24">
@@ -9558,7 +9558,7 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.4335</v>
+        <v>0.4324</v>
       </c>
     </row>
     <row r="25">
@@ -9620,7 +9620,7 @@
         <v>0.1238</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.4277</v>
+        <v>0.4212</v>
       </c>
     </row>
     <row r="26">
@@ -9682,7 +9682,7 @@
         <v>0.1253</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.4239</v>
+        <v>0.4345</v>
       </c>
     </row>
     <row r="27">
@@ -9744,7 +9744,7 @@
         <v>0.1174</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.4287</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="28">
@@ -9806,7 +9806,7 @@
         <v>0.1014</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.4235</v>
+        <v>0.4338</v>
       </c>
     </row>
     <row r="29">
@@ -9868,7 +9868,7 @@
         <v>0.103</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.4191</v>
+        <v>0.4344</v>
       </c>
     </row>
     <row r="30">
@@ -9930,7 +9930,7 @@
         <v>0.1132</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.4324</v>
+        <v>0.4319</v>
       </c>
     </row>
     <row r="31">
@@ -9992,7 +9992,7 @@
         <v>0.1195</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.4328</v>
+        <v>0.4309</v>
       </c>
     </row>
     <row r="32">
@@ -10054,7 +10054,7 @@
         <v>0.1026</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.4318</v>
+        <v>0.4393</v>
       </c>
     </row>
     <row r="33">
@@ -10116,7 +10116,7 @@
         <v>0.1197</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.4186</v>
+        <v>0.4252</v>
       </c>
     </row>
     <row r="34">
@@ -10178,7 +10178,7 @@
         <v>0.097</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.4335</v>
+        <v>0.4359</v>
       </c>
     </row>
     <row r="35">
@@ -10240,7 +10240,7 @@
         <v>0.1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.437</v>
+        <v>0.4432</v>
       </c>
     </row>
     <row r="36">
@@ -10302,7 +10302,7 @@
         <v>0.1132</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.4241</v>
+        <v>0.4367</v>
       </c>
     </row>
     <row r="37">
@@ -10364,7 +10364,7 @@
         <v>0.1135</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.4346</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="38">
@@ -10426,7 +10426,7 @@
         <v>0.1462</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.4284</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="39">
@@ -10488,7 +10488,7 @@
         <v>0.1282</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.4229</v>
+        <v>0.4254</v>
       </c>
     </row>
     <row r="40">
@@ -10550,7 +10550,7 @@
         <v>0.1</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.4185</v>
+        <v>0.4379</v>
       </c>
     </row>
     <row r="41">
@@ -10612,7 +10612,7 @@
         <v>0.121</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.4242</v>
+        <v>0.4403</v>
       </c>
     </row>
     <row r="42">
@@ -10674,7 +10674,7 @@
         <v>0.1</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.4321</v>
+        <v>0.4301</v>
       </c>
     </row>
     <row r="43">
@@ -10736,7 +10736,7 @@
         <v>0.1129</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.4232</v>
+        <v>0.4226</v>
       </c>
     </row>
     <row r="44">
@@ -10798,7 +10798,7 @@
         <v>0.1</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.4193</v>
+        <v>0.4324</v>
       </c>
     </row>
     <row r="45">
@@ -10860,7 +10860,7 @@
         <v>0.1446</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.4272</v>
+        <v>0.4436</v>
       </c>
     </row>
     <row r="46">
@@ -10922,7 +10922,7 @@
         <v>0.1577</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.4304</v>
+        <v>0.4406</v>
       </c>
     </row>
     <row r="47">
@@ -10984,7 +10984,7 @@
         <v>0.1</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.431</v>
+        <v>0.4378</v>
       </c>
     </row>
     <row r="48">
@@ -11046,7 +11046,7 @@
         <v>0.1606</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.4311</v>
+        <v>0.4387</v>
       </c>
     </row>
     <row r="49">
@@ -11108,7 +11108,7 @@
         <v>0.1216</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.4364</v>
+        <v>0.4355</v>
       </c>
     </row>
     <row r="50">
@@ -11170,7 +11170,7 @@
         <v>0.1731</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.4297</v>
+        <v>0.4341</v>
       </c>
     </row>
     <row r="51">
@@ -11232,7 +11232,7 @@
         <v>0.1475</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.4325</v>
+        <v>0.4388</v>
       </c>
     </row>
     <row r="52">
@@ -11294,7 +11294,7 @@
         <v>0.2121</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.439</v>
+        <v>0.4387</v>
       </c>
     </row>
     <row r="53">
@@ -11356,7 +11356,7 @@
         <v>0.1404</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.4266</v>
+        <v>0.4432</v>
       </c>
     </row>
     <row r="54">
@@ -11418,7 +11418,7 @@
         <v>0.1</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.4419</v>
+        <v>0.4442</v>
       </c>
     </row>
     <row r="55">
@@ -11480,7 +11480,7 @@
         <v>0.1</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.4387</v>
+        <v>0.4409</v>
       </c>
     </row>
     <row r="56">
@@ -11542,7 +11542,7 @@
         <v>0.1787</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.4397</v>
+        <v>0.4364</v>
       </c>
     </row>
     <row r="57">
@@ -11604,7 +11604,7 @@
         <v>0.1458</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.4382</v>
+        <v>0.4346</v>
       </c>
     </row>
     <row r="58">
@@ -11666,7 +11666,7 @@
         <v>0.1687</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.4371</v>
+        <v>0.4414</v>
       </c>
     </row>
     <row r="59">
@@ -11728,7 +11728,7 @@
         <v>0.1</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.4341</v>
+        <v>0.4398</v>
       </c>
     </row>
     <row r="60">
@@ -11790,7 +11790,7 @@
         <v>0.1279</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.4353</v>
+        <v>0.4417</v>
       </c>
     </row>
     <row r="61">
@@ -11852,7 +11852,7 @@
         <v>0.1275</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0.4351</v>
+        <v>0.4441</v>
       </c>
     </row>
     <row r="62">
@@ -11914,7 +11914,7 @@
         <v>0.1001</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.4377</v>
+        <v>0.4471</v>
       </c>
     </row>
     <row r="63">
@@ -11976,7 +11976,7 @@
         <v>0.1215</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0.432</v>
+        <v>0.4402</v>
       </c>
     </row>
     <row r="64">
@@ -12038,7 +12038,7 @@
         <v>0.1</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0.4269</v>
+        <v>0.4411</v>
       </c>
     </row>
     <row r="65">
@@ -12100,7 +12100,7 @@
         <v>0.1</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.4252</v>
+        <v>0.4438</v>
       </c>
     </row>
     <row r="66">
@@ -12162,7 +12162,7 @@
         <v>0.1438</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0.433</v>
+        <v>0.4507</v>
       </c>
     </row>
     <row r="67">
@@ -12224,7 +12224,7 @@
         <v>0.1539</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.4323</v>
+        <v>0.4478</v>
       </c>
     </row>
     <row r="68">
@@ -12286,7 +12286,7 @@
         <v>0.1323</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.4351</v>
+        <v>0.4435</v>
       </c>
     </row>
     <row r="69">
@@ -12348,7 +12348,7 @@
         <v>0.1294</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.4403</v>
+        <v>0.4447</v>
       </c>
     </row>
     <row r="70">
@@ -12410,7 +12410,7 @@
         <v>0.155</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.4417</v>
+        <v>0.4431</v>
       </c>
     </row>
     <row r="71">
@@ -12472,7 +12472,7 @@
         <v>0.1347</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.4382</v>
+        <v>0.4365</v>
       </c>
     </row>
     <row r="72">
@@ -12534,7 +12534,7 @@
         <v>0.1642</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.4358</v>
+        <v>0.4402</v>
       </c>
     </row>
     <row r="73">
@@ -12596,7 +12596,7 @@
         <v>0.1646</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.437</v>
+        <v>0.4417</v>
       </c>
     </row>
     <row r="74">
@@ -12658,7 +12658,7 @@
         <v>0.1509</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.44</v>
+        <v>0.4323</v>
       </c>
     </row>
     <row r="75">
@@ -12720,7 +12720,7 @@
         <v>0.1643</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.4343</v>
+        <v>0.4397</v>
       </c>
     </row>
     <row r="76">
@@ -12782,7 +12782,7 @@
         <v>0.1</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.419</v>
+        <v>0.4451</v>
       </c>
     </row>
     <row r="77">
@@ -12844,7 +12844,7 @@
         <v>0.1346</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.4327</v>
+        <v>0.4387</v>
       </c>
     </row>
     <row r="78">
@@ -12906,7 +12906,7 @@
         <v>0.1402</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.4404</v>
+        <v>0.4463</v>
       </c>
     </row>
     <row r="79">
@@ -12968,7 +12968,7 @@
         <v>0.1613</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
     </row>
     <row r="80">
@@ -13030,7 +13030,7 @@
         <v>0.138</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.4426</v>
+        <v>0.4459</v>
       </c>
     </row>
     <row r="81">
@@ -13092,7 +13092,7 @@
         <v>0.1527</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0.443</v>
+        <v>0.4501</v>
       </c>
     </row>
     <row r="82">
@@ -13154,7 +13154,7 @@
         <v>0.1347</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.4362</v>
+        <v>0.443</v>
       </c>
     </row>
     <row r="83">
@@ -13216,7 +13216,7 @@
         <v>0.117</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.44</v>
+        <v>0.4391</v>
       </c>
     </row>
     <row r="84">
@@ -13278,7 +13278,7 @@
         <v>0.1112</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.4432</v>
+        <v>0.4372</v>
       </c>
     </row>
     <row r="85">
@@ -13340,7 +13340,7 @@
         <v>0.1</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.4457</v>
+        <v>0.4398</v>
       </c>
     </row>
     <row r="86">
@@ -13402,7 +13402,7 @@
         <v>0.1444</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.4423</v>
+        <v>0.4451</v>
       </c>
     </row>
     <row r="87">
@@ -13464,7 +13464,7 @@
         <v>0.1127</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.4405</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="88">
@@ -13526,7 +13526,7 @@
         <v>0.131</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.4459</v>
+        <v>0.4299</v>
       </c>
     </row>
     <row r="89">
@@ -13588,7 +13588,7 @@
         <v>0.1833</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.4325</v>
+        <v>0.4279</v>
       </c>
     </row>
     <row r="90">
@@ -13650,7 +13650,7 @@
         <v>0.2327</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.4422</v>
+        <v>0.4384</v>
       </c>
     </row>
     <row r="91">
@@ -13712,7 +13712,7 @@
         <v>0.2327</v>
       </c>
       <c r="AJ91" t="n">
-        <v>0.4332</v>
+        <v>0.4458</v>
       </c>
     </row>
     <row r="92">
@@ -13774,7 +13774,7 @@
         <v>0.1</v>
       </c>
       <c r="AJ92" t="n">
-        <v>0.442</v>
+        <v>0.4474</v>
       </c>
     </row>
     <row r="93">
@@ -13836,7 +13836,7 @@
         <v>0.1949</v>
       </c>
       <c r="AJ93" t="n">
-        <v>0.4348</v>
+        <v>0.449</v>
       </c>
     </row>
     <row r="94">
@@ -13898,7 +13898,7 @@
         <v>0.1447</v>
       </c>
       <c r="AJ94" t="n">
-        <v>0.4344</v>
+        <v>0.4493</v>
       </c>
     </row>
     <row r="95">
@@ -13960,7 +13960,7 @@
         <v>0.1</v>
       </c>
       <c r="AJ95" t="n">
-        <v>0.435</v>
+        <v>0.4427</v>
       </c>
     </row>
     <row r="96">
@@ -14021,6 +14021,9 @@
       <c r="AI96" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ96" t="n">
+        <v>0.4413</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -14080,6 +14083,9 @@
       <c r="AI97" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ97" t="n">
+        <v>0.4379</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -14139,6 +14145,9 @@
       <c r="AI98" t="n">
         <v>0.2139</v>
       </c>
+      <c r="AJ98" t="n">
+        <v>0.4374</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -14198,6 +14207,9 @@
       <c r="AI99" t="n">
         <v>0.2222</v>
       </c>
+      <c r="AJ99" t="n">
+        <v>0.4365</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -14257,6 +14269,9 @@
       <c r="AI100" t="n">
         <v>0.1079</v>
       </c>
+      <c r="AJ100" t="n">
+        <v>0.4451</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -14316,6 +14331,9 @@
       <c r="AI101" t="n">
         <v>0.1193</v>
       </c>
+      <c r="AJ101" t="n">
+        <v>0.4381</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -14375,6 +14393,9 @@
       <c r="AI102" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ102" t="n">
+        <v>0.4397</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -14434,6 +14455,9 @@
       <c r="AI103" t="n">
         <v>0.1046</v>
       </c>
+      <c r="AJ103" t="n">
+        <v>0.4445</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -14492,6 +14516,9 @@
       </c>
       <c r="AI104" t="n">
         <v>0.1046</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>0.446</v>
       </c>
     </row>
     <row r="105">
@@ -14597,7 +14624,7 @@
         <v>0.9333333333333333</v>
       </c>
       <c r="AJ108" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5333333333333333</v>
       </c>
     </row>
     <row r="109">
@@ -14661,7 +14688,7 @@
         <v>1</v>
       </c>
       <c r="AJ109" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="110">
@@ -14725,7 +14752,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="AJ110" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="111">
@@ -14789,7 +14816,7 @@
         <v>0.8181818181818182</v>
       </c>
       <c r="AJ111" t="n">
-        <v>0.75</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="112">
@@ -14853,7 +14880,7 @@
         <v>0.8181818181818182</v>
       </c>
       <c r="AJ112" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.3076923076923077</v>
       </c>
     </row>
     <row r="113">
@@ -14914,7 +14941,7 @@
         <v>0.7272727272727273</v>
       </c>
       <c r="AJ113" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.6923076923076923</v>
       </c>
     </row>
     <row r="114">
@@ -14975,7 +15002,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="AJ114" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="115">
@@ -15036,7 +15063,7 @@
         <v>0.7</v>
       </c>
       <c r="AJ115" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -15097,7 +15124,7 @@
         <v>0.7</v>
       </c>
       <c r="AJ116" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="117">
@@ -15158,7 +15185,7 @@
         <v>0.7272727272727273</v>
       </c>
       <c r="AJ117" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="118">
@@ -15213,7 +15240,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="AJ118" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -15268,7 +15295,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="AJ119" t="n">
-        <v>0.8</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="120">
@@ -15378,7 +15405,7 @@
         <v>0.9</v>
       </c>
       <c r="AJ121" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -15433,7 +15460,7 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="AJ122" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="123">
@@ -15488,7 +15515,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="AJ123" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="124">
@@ -15543,7 +15570,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="AJ124" t="n">
-        <v>0.75</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="125">
@@ -15653,7 +15680,7 @@
         <v>1</v>
       </c>
       <c r="AJ126" t="n">
-        <v>0.75</v>
+        <v>0.9166666666666666</v>
       </c>
     </row>
     <row r="127">
@@ -15708,7 +15735,7 @@
         <v>0.6428571428571429</v>
       </c>
       <c r="AJ127" t="n">
-        <v>0.6</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="128">
@@ -15763,7 +15790,7 @@
         <v>0.9</v>
       </c>
       <c r="AJ128" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="129">
@@ -15818,7 +15845,7 @@
         <v>0.8</v>
       </c>
       <c r="AJ129" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="130">
@@ -15873,7 +15900,7 @@
         <v>0.8</v>
       </c>
       <c r="AJ130" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="131">
@@ -15928,7 +15955,7 @@
         <v>0.875</v>
       </c>
       <c r="AJ131" t="n">
-        <v>0.75</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="132">
@@ -15983,7 +16010,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="AJ132" t="n">
-        <v>0.75</v>
+        <v>0.3571428571428572</v>
       </c>
     </row>
     <row r="133">
@@ -16038,7 +16065,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="AJ133" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="134">
@@ -16093,7 +16120,7 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="AJ134" t="n">
-        <v>0.6</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="135">
@@ -16148,7 +16175,7 @@
         <v>0.8181818181818182</v>
       </c>
       <c r="AJ135" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="136">
@@ -16203,7 +16230,7 @@
         <v>0.9</v>
       </c>
       <c r="AJ136" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="137">
@@ -16258,7 +16285,7 @@
         <v>0.875</v>
       </c>
       <c r="AJ137" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="138">
@@ -16313,7 +16340,7 @@
         <v>1</v>
       </c>
       <c r="AJ138" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -16368,7 +16395,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="AJ139" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="140">
@@ -16423,7 +16450,7 @@
         <v>1</v>
       </c>
       <c r="AJ140" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="141">
@@ -16478,7 +16505,7 @@
         <v>1</v>
       </c>
       <c r="AJ141" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="142">
@@ -16533,7 +16560,7 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="AJ142" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -16588,7 +16615,7 @@
         <v>1</v>
       </c>
       <c r="AJ143" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="144">
@@ -16643,7 +16670,7 @@
         <v>1</v>
       </c>
       <c r="AJ144" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -16698,7 +16725,7 @@
         <v>0.5</v>
       </c>
       <c r="AJ145" t="n">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -16753,7 +16780,7 @@
         <v>0.5</v>
       </c>
       <c r="AJ146" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="147">
@@ -16808,7 +16835,7 @@
         <v>1</v>
       </c>
       <c r="AJ147" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -16863,7 +16890,7 @@
         <v>0.8</v>
       </c>
       <c r="AJ148" t="n">
-        <v>0.5</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="149">
@@ -16918,7 +16945,7 @@
         <v>1</v>
       </c>
       <c r="AJ149" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="150">
@@ -16973,7 +17000,7 @@
         <v>1</v>
       </c>
       <c r="AJ150" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3846153846153846</v>
       </c>
     </row>
     <row r="151">
@@ -17028,7 +17055,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="AJ151" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="152">
@@ -17083,7 +17110,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="AJ152" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="153">
@@ -17138,7 +17165,7 @@
         <v>1</v>
       </c>
       <c r="AJ153" t="n">
-        <v>0.625</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="154">
@@ -17193,7 +17220,7 @@
         <v>1</v>
       </c>
       <c r="AJ154" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="155">
@@ -17248,7 +17275,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="AJ155" t="n">
-        <v>1</v>
+        <v>0.2727272727272727</v>
       </c>
     </row>
     <row r="156">
@@ -17303,7 +17330,7 @@
         <v>1</v>
       </c>
       <c r="AJ156" t="n">
-        <v>0.5714285714285714</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -17358,7 +17385,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="AJ157" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="158">
@@ -17413,7 +17440,7 @@
         <v>0.8</v>
       </c>
       <c r="AJ158" t="n">
-        <v>1</v>
+        <v>0.1818181818181818</v>
       </c>
     </row>
     <row r="159">
@@ -17468,7 +17495,7 @@
         <v>1</v>
       </c>
       <c r="AJ159" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="160">
@@ -17523,7 +17550,7 @@
         <v>0.625</v>
       </c>
       <c r="AJ160" t="n">
-        <v>0.8</v>
+        <v>0.2307692307692308</v>
       </c>
     </row>
     <row r="161">
@@ -17578,7 +17605,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="AJ161" t="n">
-        <v>0.5555555555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -17633,7 +17660,7 @@
         <v>0.75</v>
       </c>
       <c r="AJ162" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="163">
@@ -17688,7 +17715,7 @@
         <v>0.8</v>
       </c>
       <c r="AJ163" t="n">
-        <v>0.7</v>
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="164">
@@ -17743,7 +17770,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="AJ164" t="n">
-        <v>0.3</v>
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="165">
@@ -17798,7 +17825,7 @@
         <v>1</v>
       </c>
       <c r="AJ165" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="166">
@@ -17853,7 +17880,7 @@
         <v>0.75</v>
       </c>
       <c r="AJ166" t="n">
-        <v>0.625</v>
+        <v>0.4285714285714285</v>
       </c>
     </row>
     <row r="167">
@@ -17908,7 +17935,7 @@
         <v>1</v>
       </c>
       <c r="AJ167" t="n">
-        <v>0.25</v>
+        <v>0.4285714285714285</v>
       </c>
     </row>
     <row r="168">
@@ -17963,7 +17990,7 @@
         <v>1</v>
       </c>
       <c r="AJ168" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="169">
@@ -18018,7 +18045,7 @@
         <v>1</v>
       </c>
       <c r="AJ169" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="170">
@@ -18073,7 +18100,7 @@
         <v>0.75</v>
       </c>
       <c r="AJ170" t="n">
-        <v>0.5</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="171">
@@ -18128,7 +18155,7 @@
         <v>1</v>
       </c>
       <c r="AJ171" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="172">
@@ -18183,7 +18210,7 @@
         <v>1</v>
       </c>
       <c r="AJ172" t="n">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="173">
@@ -18238,7 +18265,7 @@
         <v>0.8</v>
       </c>
       <c r="AJ173" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="174">
@@ -18293,7 +18320,7 @@
         <v>1</v>
       </c>
       <c r="AJ174" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="175">
@@ -18348,7 +18375,7 @@
         <v>1</v>
       </c>
       <c r="AJ175" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="176">
@@ -18403,7 +18430,7 @@
         <v>1</v>
       </c>
       <c r="AJ176" t="n">
-        <v>0.8</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="177">
@@ -18458,7 +18485,7 @@
         <v>1</v>
       </c>
       <c r="AJ177" t="n">
-        <v>0.4</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="178">
@@ -18513,7 +18540,7 @@
         <v>0.8</v>
       </c>
       <c r="AJ178" t="n">
-        <v>1</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="179">
@@ -18568,7 +18595,7 @@
         <v>1</v>
       </c>
       <c r="AJ179" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="180">
@@ -18623,7 +18650,7 @@
         <v>0.5</v>
       </c>
       <c r="AJ180" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="181">
@@ -18678,7 +18705,7 @@
         <v>1</v>
       </c>
       <c r="AJ181" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="182">
@@ -18733,7 +18760,7 @@
         <v>1</v>
       </c>
       <c r="AJ182" t="n">
-        <v>0.75</v>
+        <v>0.4166666666666667</v>
       </c>
     </row>
     <row r="183">
@@ -18843,7 +18870,7 @@
         <v>1</v>
       </c>
       <c r="AJ184" t="n">
-        <v>0.5</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="185">
@@ -18898,7 +18925,7 @@
         <v>1</v>
       </c>
       <c r="AJ185" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="186">
@@ -18953,7 +18980,7 @@
         <v>1</v>
       </c>
       <c r="AJ186" t="n">
-        <v>0.4</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="187">
@@ -19063,7 +19090,7 @@
         <v>1</v>
       </c>
       <c r="AJ188" t="n">
-        <v>0.75</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="189">
@@ -19118,7 +19145,7 @@
         <v>1</v>
       </c>
       <c r="AJ189" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="190">
@@ -19173,7 +19200,7 @@
         <v>1</v>
       </c>
       <c r="AJ190" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="191">
@@ -19228,7 +19255,7 @@
         <v>0.4</v>
       </c>
       <c r="AJ191" t="n">
-        <v>0.75</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="192">
@@ -19283,7 +19310,7 @@
         <v>0.75</v>
       </c>
       <c r="AJ192" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4545454545454545</v>
       </c>
     </row>
     <row r="193">
@@ -19338,7 +19365,7 @@
         <v>1</v>
       </c>
       <c r="AJ193" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="194">
@@ -19390,7 +19417,7 @@
         <v>0.6</v>
       </c>
       <c r="AJ194" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="195">
@@ -19445,7 +19472,7 @@
         <v>1</v>
       </c>
       <c r="AJ195" t="n">
-        <v>0.5</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="196">
@@ -19555,7 +19582,7 @@
         <v>1</v>
       </c>
       <c r="AJ197" t="n">
-        <v>0.625</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="198">
@@ -19610,7 +19637,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="AJ198" t="n">
-        <v>0.7</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="199">
@@ -19664,6 +19691,9 @@
       <c r="AI199" t="n">
         <v>1</v>
       </c>
+      <c r="AJ199" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
@@ -19716,6 +19746,9 @@
       <c r="AI200" t="n">
         <v>1</v>
       </c>
+      <c r="AJ200" t="n">
+        <v>0.4285714285714285</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -19768,6 +19801,9 @@
       <c r="AI201" t="n">
         <v>1</v>
       </c>
+      <c r="AJ201" t="n">
+        <v>0.2222222222222222</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
@@ -19820,6 +19856,9 @@
       <c r="AI202" t="n">
         <v>1</v>
       </c>
+      <c r="AJ202" t="n">
+        <v>0.1111111111111111</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
@@ -19872,6 +19911,9 @@
       <c r="AI203" t="n">
         <v>0.75</v>
       </c>
+      <c r="AJ203" t="n">
+        <v>0.2222222222222222</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -19924,6 +19966,9 @@
       <c r="AI204" t="n">
         <v>1</v>
       </c>
+      <c r="AJ204" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
@@ -19976,6 +20021,9 @@
       <c r="AI205" t="n">
         <v>0.8</v>
       </c>
+      <c r="AJ205" t="n">
+        <v>0.4444444444444444</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -20028,6 +20076,9 @@
       <c r="AI206" t="n">
         <v>1</v>
       </c>
+      <c r="AJ206" t="n">
+        <v>0.2727272727272727</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
@@ -20076,6 +20127,9 @@
       </c>
       <c r="AH207" t="n">
         <v>0.4</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="208">
@@ -20185,7 +20239,7 @@
         <v>0.9658857142857143</v>
       </c>
       <c r="AJ212" t="n">
-        <v>0.936111111111111</v>
+        <v>0.8992571428571428</v>
       </c>
     </row>
     <row r="213">
@@ -20249,7 +20303,7 @@
         <v>0.8468571428571429</v>
       </c>
       <c r="AJ213" t="n">
-        <v>0.9478500000000001</v>
+        <v>0.91915</v>
       </c>
     </row>
     <row r="214">
@@ -20313,7 +20367,7 @@
         <v>0.8858333333333334</v>
       </c>
       <c r="AJ214" t="n">
-        <v>0.9270400000000001</v>
+        <v>0.9104857142857143</v>
       </c>
     </row>
     <row r="215">
@@ -20377,7 +20431,7 @@
         <v>0.9863166666666666</v>
       </c>
       <c r="AJ215" t="n">
-        <v>0.9197142857142857</v>
+        <v>0.86638</v>
       </c>
     </row>
     <row r="216">
@@ -20441,7 +20495,7 @@
         <v>0.8197333333333333</v>
       </c>
       <c r="AJ216" t="n">
-        <v>0.9202250000000001</v>
+        <v>0.9172142857142856</v>
       </c>
     </row>
     <row r="217">
@@ -20502,7 +20556,7 @@
         <v>0.9927142857142855</v>
       </c>
       <c r="AJ217" t="n">
-        <v>0.9224333333333333</v>
+        <v>0.9212833333333333</v>
       </c>
     </row>
     <row r="218">
@@ -20563,7 +20617,7 @@
         <v>0.9982200000000001</v>
       </c>
       <c r="AJ218" t="n">
-        <v>0.8960333333333333</v>
+        <v>0.91838</v>
       </c>
     </row>
     <row r="219">
@@ -20626,7 +20680,7 @@
         <v>0.8679625</v>
       </c>
       <c r="AJ219" t="n">
-        <v>0.9205</v>
+        <v>0.8862166666666665</v>
       </c>
     </row>
     <row r="220">
@@ -20689,7 +20743,7 @@
         <v>0.8760250000000001</v>
       </c>
       <c r="AJ220" t="n">
-        <v>0.8922</v>
+        <v>0.9026000000000001</v>
       </c>
     </row>
     <row r="221">
@@ -20750,7 +20804,7 @@
         <v>0.9856285714285714</v>
       </c>
       <c r="AJ221" t="n">
-        <v>0.8915166666666666</v>
+        <v>0.9098111111111111</v>
       </c>
     </row>
     <row r="222">
@@ -20805,7 +20859,7 @@
         <v>0.9943375</v>
       </c>
       <c r="AJ222" t="n">
-        <v>0.9132444444444445</v>
+        <v>0.885825</v>
       </c>
     </row>
     <row r="223">
@@ -20860,7 +20914,7 @@
         <v>0.8468199999999999</v>
       </c>
       <c r="AJ223" t="n">
-        <v>0.8975799999999999</v>
+        <v>0.9139250000000001</v>
       </c>
     </row>
     <row r="224">
@@ -20915,7 +20969,7 @@
         <v>0.9959571428571429</v>
       </c>
       <c r="AJ224" t="n">
-        <v>0.86815</v>
+        <v>0.9009</v>
       </c>
     </row>
     <row r="225">
@@ -20970,7 +21024,7 @@
         <v>0.989</v>
       </c>
       <c r="AJ225" t="n">
-        <v>0.8668142857142858</v>
+        <v>0.8681249999999999</v>
       </c>
     </row>
     <row r="226">
@@ -21025,7 +21079,7 @@
         <v>0.97255</v>
       </c>
       <c r="AJ226" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.8482333333333333</v>
       </c>
     </row>
     <row r="227">
@@ -21080,7 +21134,7 @@
         <v>0.81014</v>
       </c>
       <c r="AJ227" t="n">
-        <v>0.8617833333333335</v>
+        <v>0.8643666666666666</v>
       </c>
     </row>
     <row r="228">
@@ -21135,7 +21189,7 @@
         <v>0.8912333333333334</v>
       </c>
       <c r="AJ228" t="n">
-        <v>0.8654000000000001</v>
+        <v>0.8840555555555555</v>
       </c>
     </row>
     <row r="229">
@@ -21190,7 +21244,7 @@
         <v>0.9319833333333333</v>
       </c>
       <c r="AJ229" t="n">
-        <v>0.893925</v>
+        <v>0.8273</v>
       </c>
     </row>
     <row r="230">
@@ -21245,7 +21299,7 @@
         <v>0.9897333333333332</v>
       </c>
       <c r="AJ230" t="n">
-        <v>0.8520142857142857</v>
+        <v>0.8815250000000001</v>
       </c>
     </row>
     <row r="231">
@@ -21300,7 +21354,7 @@
         <v>0.9861333333333334</v>
       </c>
       <c r="AJ231" t="n">
-        <v>0.8441599999999999</v>
+        <v>0.8689999999999999</v>
       </c>
     </row>
     <row r="232">
@@ -21355,7 +21409,7 @@
         <v>0.9921833333333333</v>
       </c>
       <c r="AJ232" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.8808285714285715</v>
       </c>
     </row>
     <row r="233">
@@ -21410,7 +21464,7 @@
         <v>0.9827285714285715</v>
       </c>
       <c r="AJ233" t="n">
-        <v>0.8876000000000001</v>
+        <v>0.8465625000000001</v>
       </c>
     </row>
     <row r="234">
@@ -21465,7 +21519,7 @@
         <v>0.8867714285714285</v>
       </c>
       <c r="AJ234" t="n">
-        <v>0.8675250000000001</v>
+        <v>0.8626666666666667</v>
       </c>
     </row>
     <row r="235">
@@ -21520,7 +21574,7 @@
         <v>0.9881375</v>
       </c>
       <c r="AJ235" t="n">
-        <v>0.877</v>
+        <v>0.8592571428571427</v>
       </c>
     </row>
     <row r="236">
@@ -21575,7 +21629,7 @@
         <v>0.9941000000000001</v>
       </c>
       <c r="AJ236" t="n">
-        <v>0.8574857142857143</v>
+        <v>0.8395999999999999</v>
       </c>
     </row>
     <row r="237">
@@ -21630,7 +21684,7 @@
         <v>0.9599800000000001</v>
       </c>
       <c r="AJ237" t="n">
-        <v>0.85584</v>
+        <v>0.8627799999999999</v>
       </c>
     </row>
     <row r="238">
@@ -21685,7 +21739,7 @@
         <v>0.9938285714285714</v>
       </c>
       <c r="AJ238" t="n">
-        <v>0.8513300000000001</v>
+        <v>0.8603000000000001</v>
       </c>
     </row>
     <row r="239">
@@ -21740,7 +21794,7 @@
         <v>0.9918833333333333</v>
       </c>
       <c r="AJ239" t="n">
-        <v>0.8556833333333334</v>
+        <v>0.8609399999999999</v>
       </c>
     </row>
     <row r="240">
@@ -21795,7 +21849,7 @@
         <v>0.9929</v>
       </c>
       <c r="AJ240" t="n">
-        <v>0.863625</v>
+        <v>0.8786428571428571</v>
       </c>
     </row>
     <row r="241">
@@ -21850,7 +21904,7 @@
         <v>0.9923124999999999</v>
       </c>
       <c r="AJ241" t="n">
-        <v>0.8387500000000001</v>
+        <v>0.8101799999999999</v>
       </c>
     </row>
     <row r="242">
@@ -21905,7 +21959,7 @@
         <v>0.8736555555555554</v>
       </c>
       <c r="AJ242" t="n">
-        <v>0.8280750000000001</v>
+        <v>0.8791</v>
       </c>
     </row>
     <row r="243">
@@ -21960,7 +22014,7 @@
         <v>0.8641999999999999</v>
       </c>
       <c r="AJ243" t="n">
-        <v>0.87582</v>
+        <v>0.83655</v>
       </c>
     </row>
     <row r="244">
@@ -22015,7 +22069,7 @@
         <v>0.6879</v>
       </c>
       <c r="AJ244" t="n">
-        <v>0.8493857142857143</v>
+        <v>0.8113714285714286</v>
       </c>
     </row>
     <row r="245">
@@ -22070,7 +22124,7 @@
         <v>0.99176</v>
       </c>
       <c r="AJ245" t="n">
-        <v>0.8000666666666666</v>
+        <v>0.85868</v>
       </c>
     </row>
     <row r="246">
@@ -22125,7 +22179,7 @@
         <v>0.9963142857142858</v>
       </c>
       <c r="AJ246" t="n">
-        <v>0.8438428571428572</v>
+        <v>0.8534166666666666</v>
       </c>
     </row>
     <row r="247">
@@ -22180,7 +22234,7 @@
         <v>0.9844714285714286</v>
       </c>
       <c r="AJ247" t="n">
-        <v>0.8600000000000001</v>
+        <v>0.9068666666666667</v>
       </c>
     </row>
     <row r="248">
@@ -22235,7 +22289,7 @@
         <v>0.8516285714285715</v>
       </c>
       <c r="AJ248" t="n">
-        <v>0.84902</v>
+        <v>0.8584166666666667</v>
       </c>
     </row>
     <row r="249">
@@ -22290,7 +22344,7 @@
         <v>0.9866333333333334</v>
       </c>
       <c r="AJ249" t="n">
-        <v>0.8609499999999999</v>
+        <v>0.8535875000000001</v>
       </c>
     </row>
     <row r="250">
@@ -22345,7 +22399,7 @@
         <v>0.8845333333333333</v>
       </c>
       <c r="AJ250" t="n">
-        <v>0.86485</v>
+        <v>0.8670142857142858</v>
       </c>
     </row>
     <row r="251">
@@ -22400,7 +22454,7 @@
         <v>0.69035</v>
       </c>
       <c r="AJ251" t="n">
-        <v>0.85972</v>
+        <v>0.8413777777777778</v>
       </c>
     </row>
     <row r="252">
@@ -22455,7 +22509,7 @@
         <v>0.7249727272727272</v>
       </c>
       <c r="AJ252" t="n">
-        <v>0.8108714285714286</v>
+        <v>0.8776666666666667</v>
       </c>
     </row>
     <row r="253">
@@ -22510,7 +22564,7 @@
         <v>0.8805222222222223</v>
       </c>
       <c r="AJ253" t="n">
-        <v>0.8481099999999999</v>
+        <v>0.8770399999999998</v>
       </c>
     </row>
     <row r="254">
@@ -22565,7 +22619,7 @@
         <v>0.79576</v>
       </c>
       <c r="AJ254" t="n">
-        <v>0.8564666666666666</v>
+        <v>0.84945</v>
       </c>
     </row>
     <row r="255">
@@ -22620,7 +22674,7 @@
         <v>0.6875538461538462</v>
       </c>
       <c r="AJ255" t="n">
-        <v>0.8437749999999999</v>
+        <v>0.85295</v>
       </c>
     </row>
     <row r="256">
@@ -22675,7 +22729,7 @@
         <v>0.79863</v>
       </c>
       <c r="AJ256" t="n">
-        <v>0.810275</v>
+        <v>0.8704285714285714</v>
       </c>
     </row>
     <row r="257">
@@ -22730,7 +22784,7 @@
         <v>0.6415727272727273</v>
       </c>
       <c r="AJ257" t="n">
-        <v>0.8225857142857144</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="258">
@@ -22785,7 +22839,7 @@
         <v>0.69429</v>
       </c>
       <c r="AJ258" t="n">
-        <v>0.8418499999999999</v>
+        <v>0.8561571428571428</v>
       </c>
     </row>
     <row r="259">
@@ -22840,7 +22894,7 @@
         <v>0.6539555555555556</v>
       </c>
       <c r="AJ259" t="n">
-        <v>0.8089888888888888</v>
+        <v>0.8793000000000001</v>
       </c>
     </row>
     <row r="260">
@@ -22895,7 +22949,7 @@
         <v>0.65415</v>
       </c>
       <c r="AJ260" t="n">
-        <v>0.8360624999999999</v>
+        <v>0.8612555555555557</v>
       </c>
     </row>
     <row r="261">
@@ -22950,7 +23004,7 @@
         <v>0.8725222222222222</v>
       </c>
       <c r="AJ261" t="n">
-        <v>0.8252166666666666</v>
+        <v>0.8754777777777778</v>
       </c>
     </row>
     <row r="262">
@@ -23005,7 +23059,7 @@
         <v>0.7095181818181818</v>
       </c>
       <c r="AJ262" t="n">
-        <v>0.8382499999999999</v>
+        <v>0.8676</v>
       </c>
     </row>
     <row r="263">
@@ -23060,7 +23114,7 @@
         <v>0.8658857142857144</v>
       </c>
       <c r="AJ263" t="n">
-        <v>0.8127666666666666</v>
+        <v>0.8396250000000001</v>
       </c>
     </row>
     <row r="264">
@@ -23115,7 +23169,7 @@
         <v>0.5676285714285714</v>
       </c>
       <c r="AJ264" t="n">
-        <v>0.8460599999999999</v>
+        <v>0.8308</v>
       </c>
     </row>
     <row r="265">
@@ -23170,7 +23224,7 @@
         <v>0.4132000000000001</v>
       </c>
       <c r="AJ265" t="n">
-        <v>0.8023166666666667</v>
+        <v>0.8070000000000001</v>
       </c>
     </row>
     <row r="266">
@@ -23225,7 +23279,7 @@
         <v>0.7401</v>
       </c>
       <c r="AJ266" t="n">
-        <v>0.8532000000000001</v>
+        <v>0.8821600000000001</v>
       </c>
     </row>
     <row r="267">
@@ -23280,7 +23334,7 @@
         <v>0.6399181818181819</v>
       </c>
       <c r="AJ267" t="n">
-        <v>0.86492</v>
+        <v>0.8358166666666667</v>
       </c>
     </row>
     <row r="268">
@@ -23335,7 +23389,7 @@
         <v>0.4583555555555556</v>
       </c>
       <c r="AJ268" t="n">
-        <v>0.8317600000000001</v>
+        <v>0.8592333333333332</v>
       </c>
     </row>
     <row r="269">
@@ -23390,7 +23444,7 @@
         <v>0.9101500000000001</v>
       </c>
       <c r="AJ269" t="n">
-        <v>0.8783500000000001</v>
+        <v>0.8593999999999999</v>
       </c>
     </row>
     <row r="270">
@@ -23445,7 +23499,7 @@
         <v>0.6957083333333333</v>
       </c>
       <c r="AJ270" t="n">
-        <v>0.8458571428571429</v>
+        <v>0.849225</v>
       </c>
     </row>
     <row r="271">
@@ -23500,7 +23554,7 @@
         <v>0.7372083333333332</v>
       </c>
       <c r="AJ271" t="n">
-        <v>0.8659</v>
+        <v>0.83145</v>
       </c>
     </row>
     <row r="272">
@@ -23555,7 +23609,7 @@
         <v>0.7539166666666667</v>
       </c>
       <c r="AJ272" t="n">
-        <v>0.8267166666666667</v>
+        <v>0.8759</v>
       </c>
     </row>
     <row r="273">
@@ -23610,7 +23664,7 @@
         <v>0.4423727272727273</v>
       </c>
       <c r="AJ273" t="n">
-        <v>0.8344499999999999</v>
+        <v>0.8468</v>
       </c>
     </row>
     <row r="274">
@@ -23665,7 +23719,7 @@
         <v>0.6609333333333333</v>
       </c>
       <c r="AJ274" t="n">
-        <v>0.8324142857142857</v>
+        <v>0.84355</v>
       </c>
     </row>
     <row r="275">
@@ -23720,7 +23774,7 @@
         <v>0.654875</v>
       </c>
       <c r="AJ275" t="n">
-        <v>0.8711666666666668</v>
+        <v>0.8139199999999999</v>
       </c>
     </row>
     <row r="276">
@@ -23775,7 +23829,7 @@
         <v>0.723509090909091</v>
       </c>
       <c r="AJ276" t="n">
-        <v>0.8751599999999999</v>
+        <v>0.8504571428571428</v>
       </c>
     </row>
     <row r="277">
@@ -23830,7 +23884,7 @@
         <v>0.6337545454545453</v>
       </c>
       <c r="AJ277" t="n">
-        <v>0.8717</v>
+        <v>0.83058</v>
       </c>
     </row>
     <row r="278">
@@ -23885,7 +23939,7 @@
         <v>0.6305181818181818</v>
       </c>
       <c r="AJ278" t="n">
-        <v>0.8425428571428571</v>
+        <v>0.8725428571428572</v>
       </c>
     </row>
     <row r="279">
@@ -23940,7 +23994,7 @@
         <v>0.5742399999999999</v>
       </c>
       <c r="AJ279" t="n">
-        <v>0.8514250000000001</v>
+        <v>0.8826600000000001</v>
       </c>
     </row>
     <row r="280">
@@ -23995,7 +24049,7 @@
         <v>0.6294818181818183</v>
       </c>
       <c r="AJ280" t="n">
-        <v>0.8547399999999999</v>
+        <v>0.8270166666666667</v>
       </c>
     </row>
     <row r="281">
@@ -24050,7 +24104,7 @@
         <v>0.5350384615384616</v>
       </c>
       <c r="AJ281" t="n">
-        <v>0.8309799999999999</v>
+        <v>0.8699625000000001</v>
       </c>
     </row>
     <row r="282">
@@ -24105,7 +24159,7 @@
         <v>0.5364</v>
       </c>
       <c r="AJ282" t="n">
-        <v>0.8591499999999999</v>
+        <v>0.87125</v>
       </c>
     </row>
     <row r="283">
@@ -24160,7 +24214,7 @@
         <v>0.6825307692307692</v>
       </c>
       <c r="AJ283" t="n">
-        <v>0.8156625000000001</v>
+        <v>0.8579333333333333</v>
       </c>
     </row>
     <row r="284">
@@ -24215,7 +24269,7 @@
         <v>0.6116714285714286</v>
       </c>
       <c r="AJ284" t="n">
-        <v>0.815625</v>
+        <v>0.8507166666666666</v>
       </c>
     </row>
     <row r="285">
@@ -24270,7 +24324,7 @@
         <v>0.4963928571428571</v>
       </c>
       <c r="AJ285" t="n">
-        <v>0.8539875</v>
+        <v>0.87073</v>
       </c>
     </row>
     <row r="286">
@@ -24325,7 +24379,7 @@
         <v>0.49677</v>
       </c>
       <c r="AJ286" t="n">
-        <v>0.8410000000000001</v>
+        <v>0.8167333333333334</v>
       </c>
     </row>
     <row r="287">
@@ -24380,7 +24434,7 @@
         <v>0.4635083333333332</v>
       </c>
       <c r="AJ287" t="n">
-        <v>0.83048</v>
+        <v>0.8361600000000001</v>
       </c>
     </row>
     <row r="288">
@@ -24435,7 +24489,7 @@
         <v>0.7629461538461538</v>
       </c>
       <c r="AJ288" t="n">
-        <v>0.7994285714285715</v>
+        <v>0.85105</v>
       </c>
     </row>
     <row r="289">
@@ -24490,7 +24544,7 @@
         <v>0.5772499999999999</v>
       </c>
       <c r="AJ289" t="n">
-        <v>0.8455625000000001</v>
+        <v>0.84374</v>
       </c>
     </row>
     <row r="290">
@@ -24545,7 +24599,7 @@
         <v>0.6123000000000001</v>
       </c>
       <c r="AJ290" t="n">
-        <v>0.82806</v>
+        <v>0.8558749999999999</v>
       </c>
     </row>
     <row r="291">
@@ -24600,7 +24654,7 @@
         <v>0.584790909090909</v>
       </c>
       <c r="AJ291" t="n">
-        <v>0.82032</v>
+        <v>0.8377800000000001</v>
       </c>
     </row>
     <row r="292">
@@ -24655,7 +24709,7 @@
         <v>0.4132416666666667</v>
       </c>
       <c r="AJ292" t="n">
-        <v>0.8719571428571429</v>
+        <v>0.8409142857142858</v>
       </c>
     </row>
     <row r="293">
@@ -24710,7 +24764,7 @@
         <v>0.579175</v>
       </c>
       <c r="AJ293" t="n">
-        <v>0.8448749999999999</v>
+        <v>0.8438399999999999</v>
       </c>
     </row>
     <row r="294">
@@ -24765,7 +24819,7 @@
         <v>0.6215363636363637</v>
       </c>
       <c r="AJ294" t="n">
-        <v>0.8622</v>
+        <v>0.8594571428571429</v>
       </c>
     </row>
     <row r="295">
@@ -24820,7 +24874,7 @@
         <v>0.4937300000000001</v>
       </c>
       <c r="AJ295" t="n">
-        <v>0.8437</v>
+        <v>0.8276777777777777</v>
       </c>
     </row>
     <row r="296">
@@ -24875,7 +24929,7 @@
         <v>0.5772666666666667</v>
       </c>
       <c r="AJ296" t="n">
-        <v>0.8250166666666666</v>
+        <v>0.817025</v>
       </c>
     </row>
     <row r="297">
@@ -24930,7 +24984,7 @@
         <v>0.6120181818181818</v>
       </c>
       <c r="AJ297" t="n">
-        <v>0.8578571428571429</v>
+        <v>0.8481714285714286</v>
       </c>
     </row>
     <row r="298">
@@ -24982,7 +25036,7 @@
         <v>0.9347111111111109</v>
       </c>
       <c r="AJ298" t="n">
-        <v>0.82958</v>
+        <v>0.8610833333333332</v>
       </c>
     </row>
     <row r="299">
@@ -25037,7 +25091,7 @@
         <v>0.5577285714285715</v>
       </c>
       <c r="AJ299" t="n">
-        <v>0.84924</v>
+        <v>0.8157666666666666</v>
       </c>
     </row>
     <row r="300">
@@ -25092,7 +25146,7 @@
         <v>0.4594153846153847</v>
       </c>
       <c r="AJ300" t="n">
-        <v>0.8211999999999999</v>
+        <v>0.88574</v>
       </c>
     </row>
     <row r="301">
@@ -25147,7 +25201,7 @@
         <v>0.6131272727272727</v>
       </c>
       <c r="AJ301" t="n">
-        <v>0.8440428571428571</v>
+        <v>0.8037333333333333</v>
       </c>
     </row>
     <row r="302">
@@ -25202,7 +25256,7 @@
         <v>0.49454</v>
       </c>
       <c r="AJ302" t="n">
-        <v>0.8570399999999999</v>
+        <v>0.8636500000000001</v>
       </c>
     </row>
     <row r="303">
@@ -25256,6 +25310,9 @@
       <c r="AI303" t="n">
         <v>0.39781</v>
       </c>
+      <c r="AJ303" t="n">
+        <v>0.8760200000000001</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
@@ -25308,6 +25365,9 @@
       <c r="AI304" t="n">
         <v>0.6814615384615385</v>
       </c>
+      <c r="AJ304" t="n">
+        <v>0.8511249999999999</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
@@ -25360,6 +25420,9 @@
       <c r="AI305" t="n">
         <v>0.4392727272727273</v>
       </c>
+      <c r="AJ305" t="n">
+        <v>0.8675</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
@@ -25412,6 +25475,9 @@
       <c r="AI306" t="n">
         <v>0.68553</v>
       </c>
+      <c r="AJ306" t="n">
+        <v>0.8625166666666667</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
@@ -25464,6 +25530,9 @@
       <c r="AI307" t="n">
         <v>0.3657333333333333</v>
       </c>
+      <c r="AJ307" t="n">
+        <v>0.8500833333333334</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
@@ -25516,6 +25585,9 @@
       <c r="AI308" t="n">
         <v>0.6255272727272727</v>
       </c>
+      <c r="AJ308" t="n">
+        <v>0.87418</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
@@ -25568,6 +25640,9 @@
       <c r="AI309" t="n">
         <v>0.7243545454545455</v>
       </c>
+      <c r="AJ309" t="n">
+        <v>0.8195833333333334</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
@@ -25620,6 +25695,9 @@
       <c r="AI310" t="n">
         <v>0.6400100000000001</v>
       </c>
+      <c r="AJ310" t="n">
+        <v>0.83875</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
@@ -25670,6 +25748,9 @@
       </c>
       <c r="AH311" t="n">
         <v>0.9537153846153845</v>
+      </c>
+      <c r="AJ311" t="n">
+        <v>0.8205666666666667</v>
       </c>
     </row>
     <row r="312">
@@ -25779,7 +25860,7 @@
         <v>0.9558</v>
       </c>
       <c r="AJ316" t="n">
-        <v>0.0035</v>
+        <v>0.0281</v>
       </c>
     </row>
     <row r="317">
@@ -25843,7 +25924,7 @@
         <v>0</v>
       </c>
       <c r="AJ317" t="n">
-        <v>0.0004</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="318">
@@ -25907,7 +25988,7 @@
         <v>0</v>
       </c>
       <c r="AJ318" t="n">
-        <v>0.0008</v>
+        <v>0.0607</v>
       </c>
     </row>
     <row r="319">
@@ -25971,7 +26052,7 @@
         <v>0.0044</v>
       </c>
       <c r="AJ319" t="n">
-        <v>0.0188</v>
+        <v>0.0148</v>
       </c>
     </row>
     <row r="320">
@@ -26035,7 +26116,7 @@
         <v>0.1013</v>
       </c>
       <c r="AJ320" t="n">
-        <v>0.1279</v>
+        <v>0.0166</v>
       </c>
     </row>
     <row r="321">
@@ -26096,7 +26177,7 @@
         <v>1</v>
       </c>
       <c r="AJ321" t="n">
-        <v>0.1657</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="322">
@@ -26157,7 +26238,7 @@
         <v>0.9284</v>
       </c>
       <c r="AJ322" t="n">
-        <v>0.0402</v>
+        <v>0.0448</v>
       </c>
     </row>
     <row r="323">
@@ -26218,7 +26299,7 @@
         <v>0.9044</v>
       </c>
       <c r="AJ323" t="n">
-        <v>0.1131</v>
+        <v>0.0555</v>
       </c>
     </row>
     <row r="324">
@@ -26279,7 +26360,7 @@
         <v>0.7281</v>
       </c>
       <c r="AJ324" t="n">
-        <v>0.0191</v>
+        <v>0.08119999999999999</v>
       </c>
     </row>
     <row r="325">
@@ -26340,7 +26421,7 @@
         <v>0.9208</v>
       </c>
       <c r="AJ325" t="n">
-        <v>0.105</v>
+        <v>0.1013</v>
       </c>
     </row>
     <row r="326">
@@ -26395,7 +26476,7 @@
         <v>0.9681999999999999</v>
       </c>
       <c r="AJ326" t="n">
-        <v>0.0219</v>
+        <v>0.1173</v>
       </c>
     </row>
     <row r="327">
@@ -26450,7 +26531,7 @@
         <v>0.7435</v>
       </c>
       <c r="AJ327" t="n">
-        <v>0.1532</v>
+        <v>0.0864</v>
       </c>
     </row>
     <row r="328">
@@ -26505,7 +26586,7 @@
         <v>0.5639999999999999</v>
       </c>
       <c r="AJ328" t="n">
-        <v>0.1418</v>
+        <v>0.1068</v>
       </c>
     </row>
     <row r="329">
@@ -26560,7 +26641,7 @@
         <v>0.2936</v>
       </c>
       <c r="AJ329" t="n">
-        <v>0.1263</v>
+        <v>0.0474</v>
       </c>
     </row>
     <row r="330">
@@ -26615,7 +26696,7 @@
         <v>0.846</v>
       </c>
       <c r="AJ330" t="n">
-        <v>0.0457</v>
+        <v>0.0354</v>
       </c>
     </row>
     <row r="331">
@@ -26670,7 +26751,7 @@
         <v>1</v>
       </c>
       <c r="AJ331" t="n">
-        <v>0.0926</v>
+        <v>0.1072</v>
       </c>
     </row>
     <row r="332">
@@ -26725,7 +26806,7 @@
         <v>0.9996</v>
       </c>
       <c r="AJ332" t="n">
-        <v>0.1191</v>
+        <v>0.1173</v>
       </c>
     </row>
     <row r="333">
@@ -26780,7 +26861,7 @@
         <v>0.9869</v>
       </c>
       <c r="AJ333" t="n">
-        <v>0.0677</v>
+        <v>0.0299</v>
       </c>
     </row>
     <row r="334">
@@ -26835,7 +26916,7 @@
         <v>0.9952</v>
       </c>
       <c r="AJ334" t="n">
-        <v>0.0469</v>
+        <v>0.0901</v>
       </c>
     </row>
     <row r="335">
@@ -26890,7 +26971,7 @@
         <v>0.9198</v>
       </c>
       <c r="AJ335" t="n">
-        <v>0.1161</v>
+        <v>0.07770000000000001</v>
       </c>
     </row>
     <row r="336">
@@ -26945,7 +27026,7 @@
         <v>0.9959</v>
       </c>
       <c r="AJ336" t="n">
-        <v>0.1399</v>
+        <v>0.0945</v>
       </c>
     </row>
     <row r="337">
@@ -27000,7 +27081,7 @@
         <v>0.8288</v>
       </c>
       <c r="AJ337" t="n">
-        <v>0.0672</v>
+        <v>0.0677</v>
       </c>
     </row>
     <row r="338">
@@ -27055,7 +27136,7 @@
         <v>0.9957</v>
       </c>
       <c r="AJ338" t="n">
-        <v>0.1072</v>
+        <v>0.0808</v>
       </c>
     </row>
     <row r="339">
@@ -27110,7 +27191,7 @@
         <v>1</v>
       </c>
       <c r="AJ339" t="n">
-        <v>0.0721</v>
+        <v>0.08459999999999999</v>
       </c>
     </row>
     <row r="340">
@@ -27165,7 +27246,7 @@
         <v>0.9986</v>
       </c>
       <c r="AJ340" t="n">
-        <v>0.0459</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="341">
@@ -27220,7 +27301,7 @@
         <v>0.9978</v>
       </c>
       <c r="AJ341" t="n">
-        <v>0.1061</v>
+        <v>0.1099</v>
       </c>
     </row>
     <row r="342">
@@ -27275,7 +27356,7 @@
         <v>0.9865</v>
       </c>
       <c r="AJ342" t="n">
-        <v>0.1175</v>
+        <v>0.0828</v>
       </c>
     </row>
     <row r="343">
@@ -27330,7 +27411,7 @@
         <v>0.9486</v>
       </c>
       <c r="AJ343" t="n">
-        <v>0.1197</v>
+        <v>0.1182</v>
       </c>
     </row>
     <row r="344">
@@ -27385,7 +27466,7 @@
         <v>0.9975000000000001</v>
       </c>
       <c r="AJ344" t="n">
-        <v>0.0978</v>
+        <v>0.0798</v>
       </c>
     </row>
     <row r="345">
@@ -27440,7 +27521,7 @@
         <v>0.9137999999999999</v>
       </c>
       <c r="AJ345" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="346">
@@ -27495,7 +27576,7 @@
         <v>0</v>
       </c>
       <c r="AJ346" t="n">
-        <v>0.1342</v>
+        <v>0.0898</v>
       </c>
     </row>
     <row r="347">
@@ -27550,7 +27631,7 @@
         <v>0.9943</v>
       </c>
       <c r="AJ347" t="n">
-        <v>0.1124</v>
+        <v>0.07530000000000001</v>
       </c>
     </row>
     <row r="348">
@@ -27605,7 +27686,7 @@
         <v>0</v>
       </c>
       <c r="AJ348" t="n">
-        <v>0.1427</v>
+        <v>0.09810000000000001</v>
       </c>
     </row>
     <row r="349">
@@ -27660,7 +27741,7 @@
         <v>0.0578</v>
       </c>
       <c r="AJ349" t="n">
-        <v>0.1128</v>
+        <v>0.0722</v>
       </c>
     </row>
     <row r="350">
@@ -27715,7 +27796,7 @@
         <v>0.9639</v>
       </c>
       <c r="AJ350" t="n">
-        <v>0.1134</v>
+        <v>0.0858</v>
       </c>
     </row>
     <row r="351">
@@ -27770,7 +27851,7 @@
         <v>1</v>
       </c>
       <c r="AJ351" t="n">
-        <v>0.1091</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="352">
@@ -27825,7 +27906,7 @@
         <v>0.9802999999999999</v>
       </c>
       <c r="AJ352" t="n">
-        <v>0.0788</v>
+        <v>0.07870000000000001</v>
       </c>
     </row>
     <row r="353">
@@ -27880,7 +27961,7 @@
         <v>1</v>
       </c>
       <c r="AJ353" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.06710000000000001</v>
       </c>
     </row>
     <row r="354">
@@ -27935,7 +28016,7 @@
         <v>0.9728</v>
       </c>
       <c r="AJ354" t="n">
-        <v>0.1055</v>
+        <v>0.0547</v>
       </c>
     </row>
     <row r="355">
@@ -27990,7 +28071,7 @@
         <v>0</v>
       </c>
       <c r="AJ355" t="n">
-        <v>0.1042</v>
+        <v>0.07049999999999999</v>
       </c>
     </row>
     <row r="356">
@@ -28045,7 +28126,7 @@
         <v>0.1606</v>
       </c>
       <c r="AJ356" t="n">
-        <v>0.0961</v>
+        <v>0.0529</v>
       </c>
     </row>
     <row r="357">
@@ -28100,7 +28181,7 @@
         <v>0</v>
       </c>
       <c r="AJ357" t="n">
-        <v>0.1008</v>
+        <v>0.08019999999999999</v>
       </c>
     </row>
     <row r="358">
@@ -28155,7 +28236,7 @@
         <v>0</v>
       </c>
       <c r="AJ358" t="n">
-        <v>0.1019</v>
+        <v>0.0857</v>
       </c>
     </row>
     <row r="359">
@@ -28210,7 +28291,7 @@
         <v>0.8582</v>
       </c>
       <c r="AJ359" t="n">
-        <v>0.1123</v>
+        <v>0.0673</v>
       </c>
     </row>
     <row r="360">
@@ -28265,7 +28346,7 @@
         <v>0.9298</v>
       </c>
       <c r="AJ360" t="n">
-        <v>0.1037</v>
+        <v>0.09039999999999999</v>
       </c>
     </row>
     <row r="361">
@@ -28320,7 +28401,7 @@
         <v>0</v>
       </c>
       <c r="AJ361" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0898</v>
       </c>
     </row>
     <row r="362">
@@ -28375,7 +28456,7 @@
         <v>0</v>
       </c>
       <c r="AJ362" t="n">
-        <v>0.1028</v>
+        <v>0.0911</v>
       </c>
     </row>
     <row r="363">
@@ -28430,7 +28511,7 @@
         <v>0</v>
       </c>
       <c r="AJ363" t="n">
-        <v>0.0945</v>
+        <v>0.1179</v>
       </c>
     </row>
     <row r="364">
@@ -28485,7 +28566,7 @@
         <v>0</v>
       </c>
       <c r="AJ364" t="n">
-        <v>0.1214</v>
+        <v>0.0814</v>
       </c>
     </row>
     <row r="365">
@@ -28540,7 +28621,7 @@
         <v>0</v>
       </c>
       <c r="AJ365" t="n">
-        <v>0.097</v>
+        <v>0.08749999999999999</v>
       </c>
     </row>
     <row r="366">
@@ -28595,7 +28676,7 @@
         <v>1</v>
       </c>
       <c r="AJ366" t="n">
-        <v>0.0832</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="367">
@@ -28650,7 +28731,7 @@
         <v>0</v>
       </c>
       <c r="AJ367" t="n">
-        <v>0.1052</v>
+        <v>0.0701</v>
       </c>
     </row>
     <row r="368">
@@ -28705,7 +28786,7 @@
         <v>0</v>
       </c>
       <c r="AJ368" t="n">
-        <v>0.1062</v>
+        <v>0.0939</v>
       </c>
     </row>
     <row r="369">
@@ -28760,7 +28841,7 @@
         <v>0.4487</v>
       </c>
       <c r="AJ369" t="n">
-        <v>0.1004</v>
+        <v>0.1032</v>
       </c>
     </row>
     <row r="370">
@@ -28815,7 +28896,7 @@
         <v>1</v>
       </c>
       <c r="AJ370" t="n">
-        <v>0.0853</v>
+        <v>0.0769</v>
       </c>
     </row>
     <row r="371">
@@ -28870,7 +28951,7 @@
         <v>0.9911</v>
       </c>
       <c r="AJ371" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0738</v>
       </c>
     </row>
     <row r="372">
@@ -28925,7 +29006,7 @@
         <v>0.9928</v>
       </c>
       <c r="AJ372" t="n">
-        <v>0.1066</v>
+        <v>0.0707</v>
       </c>
     </row>
     <row r="373">
@@ -28980,7 +29061,7 @@
         <v>1</v>
       </c>
       <c r="AJ373" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.08409999999999999</v>
       </c>
     </row>
     <row r="374">
@@ -29035,7 +29116,7 @@
         <v>0.9956</v>
       </c>
       <c r="AJ374" t="n">
-        <v>0.0888</v>
+        <v>0.0583</v>
       </c>
     </row>
     <row r="375">
@@ -29090,7 +29171,7 @@
         <v>1</v>
       </c>
       <c r="AJ375" t="n">
-        <v>0.0461</v>
+        <v>0.0448</v>
       </c>
     </row>
     <row r="376">
@@ -29145,7 +29226,7 @@
         <v>0</v>
       </c>
       <c r="AJ376" t="n">
-        <v>0.0492</v>
+        <v>0.0561</v>
       </c>
     </row>
     <row r="377">
@@ -29200,7 +29281,7 @@
         <v>0</v>
       </c>
       <c r="AJ377" t="n">
-        <v>0.0615</v>
+        <v>0.0481</v>
       </c>
     </row>
     <row r="378">
@@ -29255,7 +29336,7 @@
         <v>0</v>
       </c>
       <c r="AJ378" t="n">
-        <v>0.1055</v>
+        <v>0.0538</v>
       </c>
     </row>
     <row r="379">
@@ -29310,7 +29391,7 @@
         <v>0</v>
       </c>
       <c r="AJ379" t="n">
-        <v>0.0897</v>
+        <v>0.0631</v>
       </c>
     </row>
     <row r="380">
@@ -29365,7 +29446,7 @@
         <v>0.4348</v>
       </c>
       <c r="AJ380" t="n">
-        <v>0.0881</v>
+        <v>0.0728</v>
       </c>
     </row>
     <row r="381">
@@ -29420,7 +29501,7 @@
         <v>0.9605</v>
       </c>
       <c r="AJ381" t="n">
-        <v>0.1029</v>
+        <v>0.0873</v>
       </c>
     </row>
     <row r="382">
@@ -29475,7 +29556,7 @@
         <v>0</v>
       </c>
       <c r="AJ382" t="n">
-        <v>0.1014</v>
+        <v>0.07870000000000001</v>
       </c>
     </row>
     <row r="383">
@@ -29530,7 +29611,7 @@
         <v>0</v>
       </c>
       <c r="AJ383" t="n">
-        <v>0.1244</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="384">
@@ -29585,7 +29666,7 @@
         <v>0</v>
       </c>
       <c r="AJ384" t="n">
-        <v>0.1071</v>
+        <v>0.0649</v>
       </c>
     </row>
     <row r="385">
@@ -29640,7 +29721,7 @@
         <v>0</v>
       </c>
       <c r="AJ385" t="n">
-        <v>0.1123</v>
+        <v>0.06759999999999999</v>
       </c>
     </row>
     <row r="386">
@@ -29695,7 +29776,7 @@
         <v>0</v>
       </c>
       <c r="AJ386" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.0618</v>
       </c>
     </row>
     <row r="387">
@@ -29750,7 +29831,7 @@
         <v>0</v>
       </c>
       <c r="AJ387" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0556</v>
       </c>
     </row>
     <row r="388">
@@ -29805,7 +29886,7 @@
         <v>0.9457</v>
       </c>
       <c r="AJ388" t="n">
-        <v>0.0955</v>
+        <v>0.0901</v>
       </c>
     </row>
     <row r="389">
@@ -29860,7 +29941,7 @@
         <v>0</v>
       </c>
       <c r="AJ389" t="n">
-        <v>0.1156</v>
+        <v>0.0885</v>
       </c>
     </row>
     <row r="390">
@@ -29915,7 +29996,7 @@
         <v>0</v>
       </c>
       <c r="AJ390" t="n">
-        <v>0.1201</v>
+        <v>0.08110000000000001</v>
       </c>
     </row>
     <row r="391">
@@ -29970,7 +30051,7 @@
         <v>0</v>
       </c>
       <c r="AJ391" t="n">
-        <v>0.0934</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="392">
@@ -30025,7 +30106,7 @@
         <v>0</v>
       </c>
       <c r="AJ392" t="n">
-        <v>0.0827</v>
+        <v>0.1021</v>
       </c>
     </row>
     <row r="393">
@@ -30080,7 +30161,7 @@
         <v>0.8885999999999999</v>
       </c>
       <c r="AJ393" t="n">
-        <v>0.0983</v>
+        <v>0.0901</v>
       </c>
     </row>
     <row r="394">
@@ -30135,7 +30216,7 @@
         <v>0</v>
       </c>
       <c r="AJ394" t="n">
-        <v>0.0919</v>
+        <v>0.1016</v>
       </c>
     </row>
     <row r="395">
@@ -30190,7 +30271,7 @@
         <v>0.004</v>
       </c>
       <c r="AJ395" t="n">
-        <v>0.1099</v>
+        <v>0.09950000000000001</v>
       </c>
     </row>
     <row r="396">
@@ -30245,7 +30326,7 @@
         <v>0</v>
       </c>
       <c r="AJ396" t="n">
-        <v>0.0964</v>
+        <v>0.07770000000000001</v>
       </c>
     </row>
     <row r="397">
@@ -30300,7 +30381,7 @@
         <v>0</v>
       </c>
       <c r="AJ397" t="n">
-        <v>0.0917</v>
+        <v>0.0536</v>
       </c>
     </row>
     <row r="398">
@@ -30355,7 +30436,7 @@
         <v>0</v>
       </c>
       <c r="AJ398" t="n">
-        <v>0.0901</v>
+        <v>0.06759999999999999</v>
       </c>
     </row>
     <row r="399">
@@ -30410,7 +30491,7 @@
         <v>0</v>
       </c>
       <c r="AJ399" t="n">
-        <v>0.0955</v>
+        <v>0.0523</v>
       </c>
     </row>
     <row r="400">
@@ -30465,7 +30546,7 @@
         <v>0.6539</v>
       </c>
       <c r="AJ400" t="n">
-        <v>0.097</v>
+        <v>0.0427</v>
       </c>
     </row>
     <row r="401">
@@ -30520,7 +30601,7 @@
         <v>0</v>
       </c>
       <c r="AJ401" t="n">
-        <v>0.1237</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="402">
@@ -30575,7 +30656,7 @@
         <v>0</v>
       </c>
       <c r="AJ402" t="n">
-        <v>0.1138</v>
+        <v>0.0795</v>
       </c>
     </row>
     <row r="403">
@@ -30630,7 +30711,7 @@
         <v>0</v>
       </c>
       <c r="AJ403" t="n">
-        <v>0.1078</v>
+        <v>0.07770000000000001</v>
       </c>
     </row>
     <row r="404">
@@ -30685,7 +30766,7 @@
         <v>0</v>
       </c>
       <c r="AJ404" t="n">
-        <v>0.0984</v>
+        <v>0.0856</v>
       </c>
     </row>
     <row r="405">
@@ -30740,7 +30821,7 @@
         <v>0.0023</v>
       </c>
       <c r="AJ405" t="n">
-        <v>0.1093</v>
+        <v>0.0725</v>
       </c>
     </row>
     <row r="406">
@@ -30795,7 +30876,7 @@
         <v>1</v>
       </c>
       <c r="AJ406" t="n">
-        <v>0.1216</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="407">
@@ -30849,6 +30930,9 @@
       <c r="AI407" t="n">
         <v>1</v>
       </c>
+      <c r="AJ407" t="n">
+        <v>0.0885</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
@@ -30901,6 +30985,9 @@
       <c r="AI408" t="n">
         <v>0</v>
       </c>
+      <c r="AJ408" t="n">
+        <v>0.118</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
@@ -30953,6 +31040,9 @@
       <c r="AI409" t="n">
         <v>0</v>
       </c>
+      <c r="AJ409" t="n">
+        <v>0.0916</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
@@ -31005,6 +31095,9 @@
       <c r="AI410" t="n">
         <v>0.2872</v>
       </c>
+      <c r="AJ410" t="n">
+        <v>0.09619999999999999</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="n">
@@ -31057,6 +31150,9 @@
       <c r="AI411" t="n">
         <v>0</v>
       </c>
+      <c r="AJ411" t="n">
+        <v>0.08260000000000001</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
@@ -31109,6 +31205,9 @@
       <c r="AI412" t="n">
         <v>0.9851</v>
       </c>
+      <c r="AJ412" t="n">
+        <v>0.0925</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
@@ -31161,6 +31260,9 @@
       <c r="AI413" t="n">
         <v>0</v>
       </c>
+      <c r="AJ413" t="n">
+        <v>0.0693</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="n">
@@ -31213,6 +31315,9 @@
       <c r="AI414" t="n">
         <v>0</v>
       </c>
+      <c r="AJ414" t="n">
+        <v>0.0795</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
@@ -31264,6 +31369,9 @@
       </c>
       <c r="AI415" t="n">
         <v>0</v>
+      </c>
+      <c r="AJ415" t="n">
+        <v>0.079</v>
       </c>
     </row>
     <row r="416">

--- a/CIFAR_Global.xlsx
+++ b/CIFAR_Global.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashleyau/Documents/PhD/Practical_Experiment/Finalised/Finalised_Algorithm_ResNet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349419C5-9758-2545-86D8-58BD78836DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50A96C9-A087-7E40-A084-0F9245D8C0D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="28">
   <si>
     <t>100 Rounds</t>
   </si>
@@ -209,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -257,6 +257,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6517,309 +6518,309 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$V$5:$V$104</c:f>
+              <c:f>Sheet1!$AQ$5:$AQ$104</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="100"/>
                 <c:pt idx="0">
-                  <c:v>0.11269999999999999</c:v>
+                  <c:v>0.1212</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.1158</c:v>
+                  <c:v>0.12690000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.15540000000000001</c:v>
+                  <c:v>0.1222</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>0.15110000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.2127</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.9400000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.23930000000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.14019999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.14749999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.18129999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.2167</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.1636</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.1134</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.22459999999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.18859999999999999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.18240000000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.16420000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.1358</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.1356</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.2009</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.13009999999999999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.2281</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.15490000000000001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.17849999999999999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.16250000000000001</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.192</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.155</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.1197</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.1643</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.16839999999999999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>9.8900000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.10879999999999999</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.1454</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.1739</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.1193</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.1462</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.17829999999999999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.14269999999999999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.15479999999999999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.18890000000000001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.15959999999999999</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.19170000000000001</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.1003</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.1749</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.13500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.1817</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.17760000000000001</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.1749</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.15010000000000001</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.1202</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.21179999999999999</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.1187</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.1288</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.15179999999999999</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.15079999999999999</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.16619999999999999</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>0.13900000000000001</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.17660000000000001</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.20030000000000001</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.1736</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.23799999999999999</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.21310000000000001</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.20399999999999999</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.20710000000000001</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.17829999999999999</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.1951</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.18690000000000001</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.21990000000000001</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.21440000000000001</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.19589999999999999</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.18890000000000001</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.21110000000000001</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.17680000000000001</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.1905</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.2152</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.2223</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.2132</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.216</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.223</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.21</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.2072</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.221</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.2097</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.19769999999999999</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.2041</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.17069999999999999</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.21390000000000001</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.20369999999999999</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.21329999999999999</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.20169999999999999</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.20780000000000001</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.2208</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.18060000000000001</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.22500000000000001</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.2074</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.17380000000000001</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.18909999999999999</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.191</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0.2155</c:v>
-                </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="57">
+                  <c:v>0.22750000000000001</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.17860000000000001</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.22839999999999999</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.14649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.1106</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.1515</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.1004</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.15670000000000001</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>9.8599999999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.1812</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.22650000000000001</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.20799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.12939999999999999</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.1318</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.20280000000000001</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.17319999999999999</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.14910000000000001</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.2077</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.27989999999999998</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.1641</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.1207</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.22939999999999999</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.1012</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.1111</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.14269999999999999</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.13100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.14979999999999999</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.20039999999999999</c:v>
+                </c:pt>
+                <c:pt idx="85">
                   <c:v>0.1429</c:v>
                 </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.20119999999999999</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.1774</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.22120000000000001</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.2039</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.1007</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.13189999999999999</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.18770000000000001</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.1903</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.182</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.20549999999999999</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.20580000000000001</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.18540000000000001</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.20649999999999999</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.15759999999999999</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.1973</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.2046</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0.1832</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0.1414</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0.16209999999999999</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0.1618</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>0.17899999999999999</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>0.1628</c:v>
-                </c:pt>
-                <c:pt idx="69">
+                <c:pt idx="86">
                   <c:v>0.19270000000000001</c:v>
                 </c:pt>
-                <c:pt idx="70">
-                  <c:v>0.20910000000000001</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>0.18970000000000001</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>0.18640000000000001</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>0.19850000000000001</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>0.184</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>0.18959999999999999</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>0.18490000000000001</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>0.20619999999999999</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>0.2059</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>0.20100000000000001</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>0.1971</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>0.2046</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>0.21079999999999999</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>0.19339999999999999</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>0.15359999999999999</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>0.18049999999999999</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>0.16500000000000001</c:v>
-                </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.17019999999999999</c:v>
+                  <c:v>0.1096</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.20730000000000001</c:v>
+                  <c:v>0.13220000000000001</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.1895</c:v>
+                  <c:v>0.15340000000000001</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.1719</c:v>
+                  <c:v>0.1532</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.1865</c:v>
+                  <c:v>0.11609999999999999</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.14610000000000001</c:v>
+                  <c:v>0.2281</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.1462</c:v>
+                  <c:v>0.13289999999999999</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.1822</c:v>
+                  <c:v>0.13669999999999999</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.2046</c:v>
+                  <c:v>0.10100000000000001</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.15090000000000001</c:v>
+                  <c:v>0.14630000000000001</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.20810000000000001</c:v>
+                  <c:v>0.17419999999999999</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.17730000000000001</c:v>
+                  <c:v>0.1648</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.18060000000000001</c:v>
+                  <c:v>0.1593</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9673,16 +9674,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>82550</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>101504</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:rowOff>126620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>41</xdr:col>
-      <xdr:colOff>527050</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>660400</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>19713</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10027,7 +10028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ504"/>
+  <dimension ref="A1:AQ504"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -10043,9 +10044,10 @@
     <col min="32" max="32" width="12.33203125" customWidth="1"/>
     <col min="34" max="34" width="15.1640625" customWidth="1"/>
     <col min="35" max="35" width="12" customWidth="1"/>
+    <col min="42" max="43" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10055,8 +10057,11 @@
       <c r="AH1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -10102,8 +10107,12 @@
       <c r="AI2" s="13" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AQ2" s="21"/>
+    </row>
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -10171,8 +10180,12 @@
       <c r="AI3" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP3" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ3" s="18"/>
+    </row>
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
@@ -10207,8 +10220,12 @@
       <c r="AH4" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP4" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="AQ4" s="20"/>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -10272,11 +10289,14 @@
       <c r="AI5">
         <v>0.1178</v>
       </c>
-      <c r="AJ5">
+      <c r="AP5">
         <v>9.9900000000000003E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ5">
+        <v>0.1212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -10340,11 +10360,14 @@
       <c r="AI6">
         <v>0.13589999999999999</v>
       </c>
-      <c r="AJ6">
+      <c r="AP6">
         <v>9.9900000000000003E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ6">
+        <v>0.12690000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -10408,11 +10431,14 @@
       <c r="AI7">
         <v>0.25679999999999997</v>
       </c>
-      <c r="AJ7">
+      <c r="AP7">
         <v>0.15290000000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ7">
+        <v>0.1222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -10476,11 +10502,14 @@
       <c r="AI8">
         <v>0.28050000000000003</v>
       </c>
-      <c r="AJ8">
+      <c r="AP8">
         <v>0.1115</v>
       </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ8">
+        <v>0.15110000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -10544,11 +10573,14 @@
       <c r="AI9">
         <v>0.28789999999999999</v>
       </c>
-      <c r="AJ9">
+      <c r="AP9">
         <v>0.11210000000000001</v>
       </c>
-    </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ9">
+        <v>0.2127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -10609,11 +10641,14 @@
       <c r="AI10">
         <v>0.33189999999999997</v>
       </c>
-      <c r="AJ10">
+      <c r="AP10">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ10">
+        <v>9.9400000000000002E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -10674,11 +10709,14 @@
       <c r="AI11">
         <v>0.3523</v>
       </c>
-      <c r="AJ11">
+      <c r="AP11">
         <v>0.11219999999999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ11">
+        <v>0.23930000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -10739,11 +10777,14 @@
       <c r="AI12">
         <v>0.36230000000000001</v>
       </c>
-      <c r="AJ12">
+      <c r="AP12">
         <v>0.13139999999999999</v>
       </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ12">
+        <v>0.14019999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -10804,11 +10845,14 @@
       <c r="AI13">
         <v>0.35630000000000001</v>
       </c>
-      <c r="AJ13">
+      <c r="AP13">
         <v>0.14330000000000001</v>
       </c>
-    </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ13">
+        <v>0.14749999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -10869,11 +10913,14 @@
       <c r="AI14">
         <v>0.38969999999999999</v>
       </c>
-      <c r="AJ14">
+      <c r="AP14">
         <v>0.1074</v>
       </c>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ14">
+        <v>0.18129999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -10928,11 +10975,14 @@
       <c r="AI15">
         <v>0.41560000000000002</v>
       </c>
-      <c r="AJ15">
+      <c r="AP15">
         <v>0.107</v>
       </c>
-    </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ15">
+        <v>0.2167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -10987,11 +11037,14 @@
       <c r="AI16">
         <v>0.41160000000000002</v>
       </c>
-      <c r="AJ16">
+      <c r="AP16">
         <v>0.10920000000000001</v>
       </c>
-    </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ16">
+        <v>0.1636</v>
+      </c>
+    </row>
+    <row r="17" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -11046,11 +11099,14 @@
       <c r="AI17">
         <v>0.4178</v>
       </c>
-      <c r="AJ17">
+      <c r="AP17">
         <v>9.4E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ17">
+        <v>0.1134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -11105,11 +11161,14 @@
       <c r="AI18">
         <v>0.39760000000000001</v>
       </c>
-      <c r="AJ18">
+      <c r="AP18">
         <v>9.4399999999999998E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ18">
+        <v>0.22459999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -11164,11 +11223,14 @@
       <c r="AI19">
         <v>0.40649999999999997</v>
       </c>
-      <c r="AJ19">
+      <c r="AP19">
         <v>9.5500000000000002E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ19">
+        <v>0.18859999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -11223,11 +11285,14 @@
       <c r="AI20">
         <v>0.4254</v>
       </c>
-      <c r="AJ20">
+      <c r="AP20">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ20">
+        <v>0.18240000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -11282,11 +11347,14 @@
       <c r="AI21">
         <v>0.40870000000000001</v>
       </c>
-      <c r="AJ21">
+      <c r="AP21">
         <v>0.12280000000000001</v>
       </c>
-    </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ21">
+        <v>0.16420000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -11341,11 +11409,14 @@
       <c r="AI22">
         <v>0.42220000000000002</v>
       </c>
-      <c r="AJ22">
+      <c r="AP22">
         <v>0.1179</v>
       </c>
-    </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ22">
+        <v>0.1358</v>
+      </c>
+    </row>
+    <row r="23" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -11400,11 +11471,14 @@
       <c r="AI23">
         <v>0.43269999999999997</v>
       </c>
-      <c r="AJ23">
+      <c r="AP23">
         <v>0.12130000000000001</v>
       </c>
-    </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ23">
+        <v>0.1356</v>
+      </c>
+    </row>
+    <row r="24" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -11459,11 +11533,14 @@
       <c r="AI24">
         <v>0.43240000000000001</v>
       </c>
-      <c r="AJ24">
+      <c r="AP24">
         <v>9.7600000000000006E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ24">
+        <v>0.2009</v>
+      </c>
+    </row>
+    <row r="25" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -11518,11 +11595,14 @@
       <c r="AI25">
         <v>0.42120000000000002</v>
       </c>
-      <c r="AJ25">
+      <c r="AP25">
         <v>0.12379999999999999</v>
       </c>
-    </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ25">
+        <v>0.13009999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -11577,11 +11657,14 @@
       <c r="AI26">
         <v>0.4345</v>
       </c>
-      <c r="AJ26">
+      <c r="AP26">
         <v>0.12529999999999999</v>
       </c>
-    </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ26">
+        <v>0.2281</v>
+      </c>
+    </row>
+    <row r="27" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -11636,11 +11719,14 @@
       <c r="AI27">
         <v>0.43</v>
       </c>
-      <c r="AJ27">
+      <c r="AP27">
         <v>0.1174</v>
       </c>
-    </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ27">
+        <v>0.15490000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -11695,11 +11781,14 @@
       <c r="AI28">
         <v>0.43380000000000002</v>
       </c>
-      <c r="AJ28">
+      <c r="AP28">
         <v>0.1014</v>
       </c>
-    </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ28">
+        <v>0.17849999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -11754,11 +11843,14 @@
       <c r="AI29">
         <v>0.43440000000000001</v>
       </c>
-      <c r="AJ29">
+      <c r="AP29">
         <v>0.10299999999999999</v>
       </c>
-    </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ29">
+        <v>0.16250000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -11813,11 +11905,14 @@
       <c r="AI30">
         <v>0.43190000000000001</v>
       </c>
-      <c r="AJ30">
+      <c r="AP30">
         <v>0.1132</v>
       </c>
-    </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ30">
+        <v>0.192</v>
+      </c>
+    </row>
+    <row r="31" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -11872,11 +11967,14 @@
       <c r="AI31">
         <v>0.43090000000000001</v>
       </c>
-      <c r="AJ31">
+      <c r="AP31">
         <v>0.1195</v>
       </c>
-    </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ31">
+        <v>0.155</v>
+      </c>
+    </row>
+    <row r="32" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -11931,11 +12029,14 @@
       <c r="AI32">
         <v>0.43930000000000002</v>
       </c>
-      <c r="AJ32">
+      <c r="AP32">
         <v>0.1026</v>
       </c>
-    </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ32">
+        <v>0.1197</v>
+      </c>
+    </row>
+    <row r="33" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -11990,11 +12091,14 @@
       <c r="AI33">
         <v>0.42520000000000002</v>
       </c>
-      <c r="AJ33">
+      <c r="AP33">
         <v>0.1197</v>
       </c>
-    </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ33">
+        <v>0.1643</v>
+      </c>
+    </row>
+    <row r="34" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -12049,11 +12153,14 @@
       <c r="AI34">
         <v>0.43590000000000001</v>
       </c>
-      <c r="AJ34">
+      <c r="AP34">
         <v>9.7000000000000003E-2</v>
       </c>
-    </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ34">
+        <v>0.16839999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -12108,11 +12215,14 @@
       <c r="AI35">
         <v>0.44319999999999998</v>
       </c>
-      <c r="AJ35">
+      <c r="AP35">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ35">
+        <v>9.8900000000000002E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -12167,11 +12277,14 @@
       <c r="AI36">
         <v>0.43669999999999998</v>
       </c>
-      <c r="AJ36">
+      <c r="AP36">
         <v>0.1132</v>
       </c>
-    </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ36">
+        <v>0.10879999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -12226,11 +12339,14 @@
       <c r="AI37">
         <v>0.4375</v>
       </c>
-      <c r="AJ37">
+      <c r="AP37">
         <v>0.1135</v>
       </c>
-    </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ37">
+        <v>0.1454</v>
+      </c>
+    </row>
+    <row r="38" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>34</v>
       </c>
@@ -12285,11 +12401,14 @@
       <c r="AI38">
         <v>0.4375</v>
       </c>
-      <c r="AJ38">
+      <c r="AP38">
         <v>0.1462</v>
       </c>
-    </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ38">
+        <v>0.1739</v>
+      </c>
+    </row>
+    <row r="39" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>35</v>
       </c>
@@ -12344,11 +12463,14 @@
       <c r="AI39">
         <v>0.4254</v>
       </c>
-      <c r="AJ39">
+      <c r="AP39">
         <v>0.12820000000000001</v>
       </c>
-    </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ39">
+        <v>0.1193</v>
+      </c>
+    </row>
+    <row r="40" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>36</v>
       </c>
@@ -12403,11 +12525,14 @@
       <c r="AI40">
         <v>0.43790000000000001</v>
       </c>
-      <c r="AJ40">
+      <c r="AP40">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ40">
+        <v>0.1462</v>
+      </c>
+    </row>
+    <row r="41" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>37</v>
       </c>
@@ -12462,11 +12587,14 @@
       <c r="AI41">
         <v>0.44030000000000002</v>
       </c>
-      <c r="AJ41">
+      <c r="AP41">
         <v>0.121</v>
       </c>
-    </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ41">
+        <v>0.17829999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>38</v>
       </c>
@@ -12521,11 +12649,14 @@
       <c r="AI42">
         <v>0.43009999999999998</v>
       </c>
-      <c r="AJ42">
+      <c r="AP42">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ42">
+        <v>0.14269999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -12580,11 +12711,14 @@
       <c r="AI43">
         <v>0.42259999999999998</v>
       </c>
-      <c r="AJ43">
+      <c r="AP43">
         <v>0.1129</v>
       </c>
-    </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ43">
+        <v>0.15479999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>40</v>
       </c>
@@ -12639,11 +12773,14 @@
       <c r="AI44">
         <v>0.43240000000000001</v>
       </c>
-      <c r="AJ44">
+      <c r="AP44">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ44">
+        <v>0.18890000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>41</v>
       </c>
@@ -12698,11 +12835,14 @@
       <c r="AI45">
         <v>0.44359999999999999</v>
       </c>
-      <c r="AJ45">
+      <c r="AP45">
         <v>0.14460000000000001</v>
       </c>
-    </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ45">
+        <v>0.15959999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>42</v>
       </c>
@@ -12757,11 +12897,14 @@
       <c r="AI46">
         <v>0.44059999999999999</v>
       </c>
-      <c r="AJ46">
+      <c r="AP46">
         <v>0.15770000000000001</v>
       </c>
-    </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ46">
+        <v>0.19170000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>43</v>
       </c>
@@ -12816,11 +12959,14 @@
       <c r="AI47">
         <v>0.43780000000000002</v>
       </c>
-      <c r="AJ47">
+      <c r="AP47">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ47">
+        <v>0.1003</v>
+      </c>
+    </row>
+    <row r="48" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>44</v>
       </c>
@@ -12875,11 +13021,14 @@
       <c r="AI48">
         <v>0.43869999999999998</v>
       </c>
-      <c r="AJ48">
+      <c r="AP48">
         <v>0.16059999999999999</v>
       </c>
-    </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ48">
+        <v>0.1749</v>
+      </c>
+    </row>
+    <row r="49" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>45</v>
       </c>
@@ -12934,11 +13083,14 @@
       <c r="AI49">
         <v>0.4355</v>
       </c>
-      <c r="AJ49">
+      <c r="AP49">
         <v>0.1216</v>
       </c>
-    </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ49">
+        <v>0.13500000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -12993,11 +13145,14 @@
       <c r="AI50">
         <v>0.43409999999999999</v>
       </c>
-      <c r="AJ50">
+      <c r="AP50">
         <v>0.1731</v>
       </c>
-    </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ50">
+        <v>0.1817</v>
+      </c>
+    </row>
+    <row r="51" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>47</v>
       </c>
@@ -13052,11 +13207,14 @@
       <c r="AI51">
         <v>0.43880000000000002</v>
       </c>
-      <c r="AJ51">
+      <c r="AP51">
         <v>0.14749999999999999</v>
       </c>
-    </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ51">
+        <v>0.17760000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>48</v>
       </c>
@@ -13111,11 +13269,14 @@
       <c r="AI52">
         <v>0.43869999999999998</v>
       </c>
-      <c r="AJ52">
+      <c r="AP52">
         <v>0.21210000000000001</v>
       </c>
-    </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ52">
+        <v>0.1749</v>
+      </c>
+    </row>
+    <row r="53" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>49</v>
       </c>
@@ -13170,11 +13331,14 @@
       <c r="AI53">
         <v>0.44319999999999998</v>
       </c>
-      <c r="AJ53">
+      <c r="AP53">
         <v>0.1404</v>
       </c>
-    </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ53">
+        <v>0.15010000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>50</v>
       </c>
@@ -13229,11 +13393,14 @@
       <c r="AI54">
         <v>0.44419999999999998</v>
       </c>
-      <c r="AJ54">
+      <c r="AP54">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ54">
+        <v>0.1202</v>
+      </c>
+    </row>
+    <row r="55" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>51</v>
       </c>
@@ -13288,11 +13455,14 @@
       <c r="AI55">
         <v>0.44090000000000001</v>
       </c>
-      <c r="AJ55">
+      <c r="AP55">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="56" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ55">
+        <v>0.21179999999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>52</v>
       </c>
@@ -13347,11 +13517,14 @@
       <c r="AI56">
         <v>0.43640000000000001</v>
       </c>
-      <c r="AJ56">
+      <c r="AP56">
         <v>0.1787</v>
       </c>
-    </row>
-    <row r="57" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ56">
+        <v>0.1187</v>
+      </c>
+    </row>
+    <row r="57" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>53</v>
       </c>
@@ -13406,11 +13579,14 @@
       <c r="AI57">
         <v>0.43459999999999999</v>
       </c>
-      <c r="AJ57">
+      <c r="AP57">
         <v>0.14580000000000001</v>
       </c>
-    </row>
-    <row r="58" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ57">
+        <v>0.1288</v>
+      </c>
+    </row>
+    <row r="58" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>54</v>
       </c>
@@ -13465,11 +13641,14 @@
       <c r="AI58">
         <v>0.44140000000000001</v>
       </c>
-      <c r="AJ58">
+      <c r="AP58">
         <v>0.16869999999999999</v>
       </c>
-    </row>
-    <row r="59" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ58">
+        <v>0.15179999999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>55</v>
       </c>
@@ -13524,11 +13703,14 @@
       <c r="AI59">
         <v>0.43980000000000002</v>
       </c>
-      <c r="AJ59">
+      <c r="AP59">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="60" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ59">
+        <v>0.15079999999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>56</v>
       </c>
@@ -13583,11 +13765,14 @@
       <c r="AI60">
         <v>0.44169999999999998</v>
       </c>
-      <c r="AJ60">
+      <c r="AP60">
         <v>0.12790000000000001</v>
       </c>
-    </row>
-    <row r="61" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ60">
+        <v>0.16619999999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>57</v>
       </c>
@@ -13642,11 +13827,14 @@
       <c r="AI61">
         <v>0.44409999999999999</v>
       </c>
-      <c r="AJ61">
+      <c r="AP61">
         <v>0.1275</v>
       </c>
-    </row>
-    <row r="62" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ61">
+        <v>0.13900000000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>58</v>
       </c>
@@ -13701,11 +13889,14 @@
       <c r="AI62">
         <v>0.4471</v>
       </c>
-      <c r="AJ62">
+      <c r="AP62">
         <v>0.10009999999999999</v>
       </c>
-    </row>
-    <row r="63" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ62">
+        <v>0.22750000000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>59</v>
       </c>
@@ -13760,11 +13951,14 @@
       <c r="AI63">
         <v>0.44019999999999998</v>
       </c>
-      <c r="AJ63">
+      <c r="AP63">
         <v>0.1215</v>
       </c>
-    </row>
-    <row r="64" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ63">
+        <v>0.17860000000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>60</v>
       </c>
@@ -13819,11 +14013,14 @@
       <c r="AI64">
         <v>0.44109999999999999</v>
       </c>
-      <c r="AJ64">
+      <c r="AP64">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="65" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ64">
+        <v>0.22839999999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>61</v>
       </c>
@@ -13878,11 +14075,14 @@
       <c r="AI65">
         <v>0.44379999999999997</v>
       </c>
-      <c r="AJ65">
+      <c r="AP65">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="66" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ65">
+        <v>0.14649999999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>62</v>
       </c>
@@ -13937,11 +14137,14 @@
       <c r="AI66">
         <v>0.45069999999999999</v>
       </c>
-      <c r="AJ66">
+      <c r="AP66">
         <v>0.14380000000000001</v>
       </c>
-    </row>
-    <row r="67" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ66">
+        <v>0.1106</v>
+      </c>
+    </row>
+    <row r="67" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>63</v>
       </c>
@@ -13996,11 +14199,14 @@
       <c r="AI67">
         <v>0.44779999999999998</v>
       </c>
-      <c r="AJ67">
+      <c r="AP67">
         <v>0.15390000000000001</v>
       </c>
-    </row>
-    <row r="68" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ67">
+        <v>0.1515</v>
+      </c>
+    </row>
+    <row r="68" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>64</v>
       </c>
@@ -14055,11 +14261,14 @@
       <c r="AI68">
         <v>0.44350000000000001</v>
       </c>
-      <c r="AJ68">
+      <c r="AP68">
         <v>0.1323</v>
       </c>
-    </row>
-    <row r="69" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ68">
+        <v>0.1004</v>
+      </c>
+    </row>
+    <row r="69" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>65</v>
       </c>
@@ -14114,11 +14323,14 @@
       <c r="AI69">
         <v>0.44469999999999998</v>
       </c>
-      <c r="AJ69">
+      <c r="AP69">
         <v>0.12939999999999999</v>
       </c>
-    </row>
-    <row r="70" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ69">
+        <v>0.15670000000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>66</v>
       </c>
@@ -14173,11 +14385,14 @@
       <c r="AI70">
         <v>0.44309999999999999</v>
       </c>
-      <c r="AJ70">
+      <c r="AP70">
         <v>0.155</v>
       </c>
-    </row>
-    <row r="71" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ70">
+        <v>9.8599999999999993E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>67</v>
       </c>
@@ -14232,11 +14447,14 @@
       <c r="AI71">
         <v>0.4365</v>
       </c>
-      <c r="AJ71">
+      <c r="AP71">
         <v>0.13469999999999999</v>
       </c>
-    </row>
-    <row r="72" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ71">
+        <v>0.1812</v>
+      </c>
+    </row>
+    <row r="72" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>68</v>
       </c>
@@ -14291,11 +14509,14 @@
       <c r="AI72">
         <v>0.44019999999999998</v>
       </c>
-      <c r="AJ72">
+      <c r="AP72">
         <v>0.16420000000000001</v>
       </c>
-    </row>
-    <row r="73" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ72">
+        <v>0.22650000000000001</v>
+      </c>
+    </row>
+    <row r="73" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>69</v>
       </c>
@@ -14350,11 +14571,14 @@
       <c r="AI73">
         <v>0.44169999999999998</v>
       </c>
-      <c r="AJ73">
+      <c r="AP73">
         <v>0.1646</v>
       </c>
-    </row>
-    <row r="74" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ73">
+        <v>0.20799999999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>70</v>
       </c>
@@ -14409,11 +14633,14 @@
       <c r="AI74">
         <v>0.43230000000000002</v>
       </c>
-      <c r="AJ74">
+      <c r="AP74">
         <v>0.15090000000000001</v>
       </c>
-    </row>
-    <row r="75" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ74">
+        <v>0.12939999999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>71</v>
       </c>
@@ -14468,11 +14695,14 @@
       <c r="AI75">
         <v>0.43969999999999998</v>
       </c>
-      <c r="AJ75">
+      <c r="AP75">
         <v>0.1643</v>
       </c>
-    </row>
-    <row r="76" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ75">
+        <v>0.1318</v>
+      </c>
+    </row>
+    <row r="76" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>72</v>
       </c>
@@ -14527,11 +14757,14 @@
       <c r="AI76">
         <v>0.4451</v>
       </c>
-      <c r="AJ76">
+      <c r="AP76">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="77" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ76">
+        <v>0.20280000000000001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>73</v>
       </c>
@@ -14586,11 +14819,14 @@
       <c r="AI77">
         <v>0.43869999999999998</v>
       </c>
-      <c r="AJ77">
+      <c r="AP77">
         <v>0.1346</v>
       </c>
-    </row>
-    <row r="78" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ77">
+        <v>0.17319999999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>74</v>
       </c>
@@ -14645,11 +14881,14 @@
       <c r="AI78">
         <v>0.44629999999999997</v>
       </c>
-      <c r="AJ78">
+      <c r="AP78">
         <v>0.14019999999999999</v>
       </c>
-    </row>
-    <row r="79" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ78">
+        <v>0.14910000000000001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>75</v>
       </c>
@@ -14704,11 +14943,14 @@
       <c r="AI79">
         <v>0.44400000000000001</v>
       </c>
-      <c r="AJ79">
+      <c r="AP79">
         <v>0.1613</v>
       </c>
-    </row>
-    <row r="80" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ79">
+        <v>0.2077</v>
+      </c>
+    </row>
+    <row r="80" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>76</v>
       </c>
@@ -14763,11 +15005,14 @@
       <c r="AI80">
         <v>0.44590000000000002</v>
       </c>
-      <c r="AJ80">
+      <c r="AP80">
         <v>0.13800000000000001</v>
       </c>
-    </row>
-    <row r="81" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ80">
+        <v>0.27989999999999998</v>
+      </c>
+    </row>
+    <row r="81" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>77</v>
       </c>
@@ -14822,11 +15067,14 @@
       <c r="AI81">
         <v>0.4501</v>
       </c>
-      <c r="AJ81">
+      <c r="AP81">
         <v>0.1527</v>
       </c>
-    </row>
-    <row r="82" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ81">
+        <v>0.1641</v>
+      </c>
+    </row>
+    <row r="82" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>78</v>
       </c>
@@ -14881,11 +15129,14 @@
       <c r="AI82">
         <v>0.443</v>
       </c>
-      <c r="AJ82">
+      <c r="AP82">
         <v>0.13469999999999999</v>
       </c>
-    </row>
-    <row r="83" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ82">
+        <v>0.1207</v>
+      </c>
+    </row>
+    <row r="83" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>79</v>
       </c>
@@ -14940,11 +15191,14 @@
       <c r="AI83">
         <v>0.43909999999999999</v>
       </c>
-      <c r="AJ83">
+      <c r="AP83">
         <v>0.11700000000000001</v>
       </c>
-    </row>
-    <row r="84" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ83">
+        <v>0.22939999999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>80</v>
       </c>
@@ -14999,11 +15253,14 @@
       <c r="AI84">
         <v>0.43719999999999998</v>
       </c>
-      <c r="AJ84">
+      <c r="AP84">
         <v>0.11119999999999999</v>
       </c>
-    </row>
-    <row r="85" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ84">
+        <v>0.1012</v>
+      </c>
+    </row>
+    <row r="85" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>81</v>
       </c>
@@ -15058,11 +15315,14 @@
       <c r="AI85">
         <v>0.43980000000000002</v>
       </c>
-      <c r="AJ85">
+      <c r="AP85">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="86" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ85">
+        <v>0.1111</v>
+      </c>
+    </row>
+    <row r="86" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>82</v>
       </c>
@@ -15117,11 +15377,14 @@
       <c r="AI86">
         <v>0.4451</v>
       </c>
-      <c r="AJ86">
+      <c r="AP86">
         <v>0.1444</v>
       </c>
-    </row>
-    <row r="87" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ86">
+        <v>0.14269999999999999</v>
+      </c>
+    </row>
+    <row r="87" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>83</v>
       </c>
@@ -15176,11 +15439,14 @@
       <c r="AI87">
         <v>0.44800000000000001</v>
       </c>
-      <c r="AJ87">
+      <c r="AP87">
         <v>0.11269999999999999</v>
       </c>
-    </row>
-    <row r="88" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ87">
+        <v>0.13100000000000001</v>
+      </c>
+    </row>
+    <row r="88" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>84</v>
       </c>
@@ -15235,11 +15501,14 @@
       <c r="AI88">
         <v>0.4299</v>
       </c>
-      <c r="AJ88">
+      <c r="AP88">
         <v>0.13100000000000001</v>
       </c>
-    </row>
-    <row r="89" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ88">
+        <v>0.14979999999999999</v>
+      </c>
+    </row>
+    <row r="89" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>85</v>
       </c>
@@ -15294,11 +15563,14 @@
       <c r="AI89">
         <v>0.4279</v>
       </c>
-      <c r="AJ89">
+      <c r="AP89">
         <v>0.18329999999999999</v>
       </c>
-    </row>
-    <row r="90" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ89">
+        <v>0.20039999999999999</v>
+      </c>
+    </row>
+    <row r="90" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>86</v>
       </c>
@@ -15353,11 +15625,14 @@
       <c r="AI90">
         <v>0.43840000000000001</v>
       </c>
-      <c r="AJ90">
+      <c r="AP90">
         <v>0.23269999999999999</v>
       </c>
-    </row>
-    <row r="91" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ90">
+        <v>0.1429</v>
+      </c>
+    </row>
+    <row r="91" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>87</v>
       </c>
@@ -15412,11 +15687,14 @@
       <c r="AI91">
         <v>0.44579999999999997</v>
       </c>
-      <c r="AJ91">
+      <c r="AP91">
         <v>0.23269999999999999</v>
       </c>
-    </row>
-    <row r="92" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ91">
+        <v>0.19270000000000001</v>
+      </c>
+    </row>
+    <row r="92" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>88</v>
       </c>
@@ -15471,11 +15749,14 @@
       <c r="AI92">
         <v>0.44740000000000002</v>
       </c>
-      <c r="AJ92">
+      <c r="AP92">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="93" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ92">
+        <v>0.1096</v>
+      </c>
+    </row>
+    <row r="93" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>89</v>
       </c>
@@ -15530,11 +15811,14 @@
       <c r="AI93">
         <v>0.44900000000000001</v>
       </c>
-      <c r="AJ93">
+      <c r="AP93">
         <v>0.19489999999999999</v>
       </c>
-    </row>
-    <row r="94" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ93">
+        <v>0.13220000000000001</v>
+      </c>
+    </row>
+    <row r="94" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>90</v>
       </c>
@@ -15589,11 +15873,14 @@
       <c r="AI94">
         <v>0.44929999999999998</v>
       </c>
-      <c r="AJ94">
+      <c r="AP94">
         <v>0.1447</v>
       </c>
-    </row>
-    <row r="95" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ94">
+        <v>0.15340000000000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>91</v>
       </c>
@@ -15648,11 +15935,14 @@
       <c r="AI95">
         <v>0.44269999999999998</v>
       </c>
-      <c r="AJ95">
+      <c r="AP95">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="96" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ95">
+        <v>0.1532</v>
+      </c>
+    </row>
+    <row r="96" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>92</v>
       </c>
@@ -15707,11 +15997,14 @@
       <c r="AI96">
         <v>0.44130000000000003</v>
       </c>
-      <c r="AJ96">
+      <c r="AP96">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="97" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ96">
+        <v>0.11609999999999999</v>
+      </c>
+    </row>
+    <row r="97" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>93</v>
       </c>
@@ -15766,11 +16059,14 @@
       <c r="AI97">
         <v>0.43790000000000001</v>
       </c>
-      <c r="AJ97">
+      <c r="AP97">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="98" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ97">
+        <v>0.2281</v>
+      </c>
+    </row>
+    <row r="98" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>94</v>
       </c>
@@ -15825,11 +16121,14 @@
       <c r="AI98">
         <v>0.43740000000000001</v>
       </c>
-      <c r="AJ98">
+      <c r="AP98">
         <v>0.21390000000000001</v>
       </c>
-    </row>
-    <row r="99" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ98">
+        <v>0.13289999999999999</v>
+      </c>
+    </row>
+    <row r="99" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>95</v>
       </c>
@@ -15884,11 +16183,14 @@
       <c r="AI99">
         <v>0.4365</v>
       </c>
-      <c r="AJ99">
+      <c r="AP99">
         <v>0.22220000000000001</v>
       </c>
-    </row>
-    <row r="100" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ99">
+        <v>0.13669999999999999</v>
+      </c>
+    </row>
+    <row r="100" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>96</v>
       </c>
@@ -15943,11 +16245,14 @@
       <c r="AI100">
         <v>0.4451</v>
       </c>
-      <c r="AJ100">
+      <c r="AP100">
         <v>0.1079</v>
       </c>
-    </row>
-    <row r="101" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ100">
+        <v>0.10100000000000001</v>
+      </c>
+    </row>
+    <row r="101" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>97</v>
       </c>
@@ -16002,11 +16307,14 @@
       <c r="AI101">
         <v>0.43809999999999999</v>
       </c>
-      <c r="AJ101">
+      <c r="AP101">
         <v>0.1193</v>
       </c>
-    </row>
-    <row r="102" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ101">
+        <v>0.14630000000000001</v>
+      </c>
+    </row>
+    <row r="102" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>98</v>
       </c>
@@ -16061,11 +16369,14 @@
       <c r="AI102">
         <v>0.43969999999999998</v>
       </c>
-      <c r="AJ102">
+      <c r="AP102">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="103" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ102">
+        <v>0.17419999999999999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>99</v>
       </c>
@@ -16120,11 +16431,14 @@
       <c r="AI103">
         <v>0.44450000000000001</v>
       </c>
-      <c r="AJ103">
+      <c r="AP103">
         <v>0.1046</v>
       </c>
-    </row>
-    <row r="104" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ103">
+        <v>0.1648</v>
+      </c>
+    </row>
+    <row r="104" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>100</v>
       </c>
@@ -16179,15 +16493,18 @@
       <c r="AI104">
         <v>0.44600000000000001</v>
       </c>
-      <c r="AJ104">
+      <c r="AP104">
         <v>0.1046</v>
       </c>
-    </row>
-    <row r="105" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AQ104">
+        <v>0.1593</v>
+      </c>
+    </row>
+    <row r="105" spans="1:43" x14ac:dyDescent="0.2">
       <c r="AD105" s="9"/>
       <c r="AE105" s="9"/>
     </row>
-    <row r="106" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>23</v>
       </c>
@@ -16200,7 +16517,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="107" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>24</v>
       </c>
@@ -16213,7 +16530,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="108" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>1</v>
       </c>
@@ -16270,11 +16587,11 @@
       <c r="AI108">
         <v>0.53333333333333333</v>
       </c>
-      <c r="AJ108">
+      <c r="AP108">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="109" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>2</v>
       </c>
@@ -16331,11 +16648,11 @@
       <c r="AI109">
         <v>0.6</v>
       </c>
-      <c r="AJ109">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>3</v>
       </c>
@@ -16392,11 +16709,11 @@
       <c r="AI110">
         <v>0.66666666666666663</v>
       </c>
-      <c r="AJ110">
+      <c r="AP110">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="111" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>4</v>
       </c>
@@ -16453,11 +16770,11 @@
       <c r="AI111">
         <v>0.7142857142857143</v>
       </c>
-      <c r="AJ111">
+      <c r="AP111">
         <v>0.81818181818181823</v>
       </c>
     </row>
-    <row r="112" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>5</v>
       </c>
@@ -16514,11 +16831,11 @@
       <c r="AI112">
         <v>0.30769230769230771</v>
       </c>
-      <c r="AJ112">
+      <c r="AP112">
         <v>0.81818181818181823</v>
       </c>
     </row>
-    <row r="113" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>6</v>
       </c>
@@ -16572,11 +16889,11 @@
       <c r="AI113">
         <v>0.69230769230769229</v>
       </c>
-      <c r="AJ113">
+      <c r="AP113">
         <v>0.72727272727272729</v>
       </c>
     </row>
-    <row r="114" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>7</v>
       </c>
@@ -16630,11 +16947,11 @@
       <c r="AI114">
         <v>0.83333333333333337</v>
       </c>
-      <c r="AJ114">
+      <c r="AP114">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="115" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>8</v>
       </c>
@@ -16688,11 +17005,11 @@
       <c r="AI115">
         <v>1</v>
       </c>
-      <c r="AJ115">
+      <c r="AP115">
         <v>0.7</v>
       </c>
     </row>
-    <row r="116" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>9</v>
       </c>
@@ -16746,11 +17063,11 @@
       <c r="AI116">
         <v>0.9</v>
       </c>
-      <c r="AJ116">
+      <c r="AP116">
         <v>0.7</v>
       </c>
     </row>
-    <row r="117" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>10</v>
       </c>
@@ -16804,11 +17121,11 @@
       <c r="AI117">
         <v>0.8571428571428571</v>
       </c>
-      <c r="AJ117">
+      <c r="AP117">
         <v>0.72727272727272729</v>
       </c>
     </row>
-    <row r="118" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>11</v>
       </c>
@@ -16856,11 +17173,11 @@
       <c r="AI118">
         <v>1</v>
       </c>
-      <c r="AJ118">
+      <c r="AP118">
         <v>0.77777777777777779</v>
       </c>
     </row>
-    <row r="119" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>12</v>
       </c>
@@ -16908,11 +17225,11 @@
       <c r="AI119">
         <v>0.63636363636363635</v>
       </c>
-      <c r="AJ119">
+      <c r="AP119">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="120" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>13</v>
       </c>
@@ -16960,11 +17277,11 @@
       <c r="AI120">
         <v>1</v>
       </c>
-      <c r="AJ120">
+      <c r="AP120">
         <v>0.72727272727272729</v>
       </c>
     </row>
-    <row r="121" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>14</v>
       </c>
@@ -17012,11 +17329,11 @@
       <c r="AI121">
         <v>1</v>
       </c>
-      <c r="AJ121">
+      <c r="AP121">
         <v>0.9</v>
       </c>
     </row>
-    <row r="122" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>15</v>
       </c>
@@ -17064,11 +17381,11 @@
       <c r="AI122">
         <v>0.9</v>
       </c>
-      <c r="AJ122">
+      <c r="AP122">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="123" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>16</v>
       </c>
@@ -17116,11 +17433,11 @@
       <c r="AI123">
         <v>0.81818181818181823</v>
       </c>
-      <c r="AJ123">
+      <c r="AP123">
         <v>0.90909090909090906</v>
       </c>
     </row>
-    <row r="124" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>17</v>
       </c>
@@ -17168,11 +17485,11 @@
       <c r="AI124">
         <v>0.66666666666666663</v>
       </c>
-      <c r="AJ124">
+      <c r="AP124">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="125" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>18</v>
       </c>
@@ -17220,11 +17537,11 @@
       <c r="AI125">
         <v>0.81818181818181823</v>
       </c>
-      <c r="AJ125">
+      <c r="AP125">
         <v>0.81818181818181823</v>
       </c>
     </row>
-    <row r="126" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>19</v>
       </c>
@@ -17272,11 +17589,11 @@
       <c r="AI126">
         <v>0.91666666666666663</v>
       </c>
-      <c r="AJ126">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>20</v>
       </c>
@@ -17324,11 +17641,11 @@
       <c r="AI127">
         <v>0.81818181818181823</v>
       </c>
-      <c r="AJ127">
+      <c r="AP127">
         <v>0.6428571428571429</v>
       </c>
     </row>
-    <row r="128" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>21</v>
       </c>
@@ -17376,11 +17693,11 @@
       <c r="AI128">
         <v>0.88888888888888884</v>
       </c>
-      <c r="AJ128">
+      <c r="AP128">
         <v>0.9</v>
       </c>
     </row>
-    <row r="129" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>22</v>
       </c>
@@ -17428,11 +17745,11 @@
       <c r="AI129">
         <v>0.875</v>
       </c>
-      <c r="AJ129">
+      <c r="AP129">
         <v>0.8</v>
       </c>
     </row>
-    <row r="130" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>23</v>
       </c>
@@ -17480,11 +17797,11 @@
       <c r="AI130">
         <v>0.8</v>
       </c>
-      <c r="AJ130">
+      <c r="AP130">
         <v>0.8</v>
       </c>
     </row>
-    <row r="131" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>24</v>
       </c>
@@ -17532,11 +17849,11 @@
       <c r="AI131">
         <v>0.88888888888888884</v>
       </c>
-      <c r="AJ131">
+      <c r="AP131">
         <v>0.875</v>
       </c>
     </row>
-    <row r="132" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>25</v>
       </c>
@@ -17584,11 +17901,11 @@
       <c r="AI132">
         <v>0.35714285714285721</v>
       </c>
-      <c r="AJ132">
+      <c r="AP132">
         <v>0.90909090909090906</v>
       </c>
     </row>
-    <row r="133" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>26</v>
       </c>
@@ -17636,11 +17953,11 @@
       <c r="AI133">
         <v>0.7</v>
       </c>
-      <c r="AJ133">
+      <c r="AP133">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="134" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>27</v>
       </c>
@@ -17688,11 +18005,11 @@
       <c r="AI134">
         <v>0.63636363636363635</v>
       </c>
-      <c r="AJ134">
+      <c r="AP134">
         <v>0.88888888888888884</v>
       </c>
     </row>
-    <row r="135" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>28</v>
       </c>
@@ -17740,11 +18057,11 @@
       <c r="AI135">
         <v>0.54545454545454541</v>
       </c>
-      <c r="AJ135">
+      <c r="AP135">
         <v>0.81818181818181823</v>
       </c>
     </row>
-    <row r="136" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>29</v>
       </c>
@@ -17792,11 +18109,11 @@
       <c r="AI136">
         <v>0.375</v>
       </c>
-      <c r="AJ136">
+      <c r="AP136">
         <v>0.9</v>
       </c>
     </row>
-    <row r="137" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>30</v>
       </c>
@@ -17844,11 +18161,11 @@
       <c r="AI137">
         <v>0.5</v>
       </c>
-      <c r="AJ137">
+      <c r="AP137">
         <v>0.875</v>
       </c>
     </row>
-    <row r="138" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>31</v>
       </c>
@@ -17896,11 +18213,11 @@
       <c r="AI138">
         <v>1</v>
       </c>
-      <c r="AJ138">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>32</v>
       </c>
@@ -17948,11 +18265,11 @@
       <c r="AI139">
         <v>0.3</v>
       </c>
-      <c r="AJ139">
+      <c r="AP139">
         <v>0.8571428571428571</v>
       </c>
     </row>
-    <row r="140" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>33</v>
       </c>
@@ -18000,11 +18317,11 @@
       <c r="AI140">
         <v>0.375</v>
       </c>
-      <c r="AJ140">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>34</v>
       </c>
@@ -18052,11 +18369,11 @@
       <c r="AI141">
         <v>0.7</v>
       </c>
-      <c r="AJ141">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>35</v>
       </c>
@@ -18104,11 +18421,11 @@
       <c r="AI142">
         <v>1</v>
       </c>
-      <c r="AJ142">
+      <c r="AP142">
         <v>0.88888888888888884</v>
       </c>
     </row>
-    <row r="143" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>36</v>
       </c>
@@ -18156,11 +18473,11 @@
       <c r="AI143">
         <v>0.55555555555555558</v>
       </c>
-      <c r="AJ143">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>37</v>
       </c>
@@ -18208,11 +18525,11 @@
       <c r="AI144">
         <v>1</v>
       </c>
-      <c r="AJ144">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>38</v>
       </c>
@@ -18260,11 +18577,11 @@
       <c r="AI145">
         <v>1</v>
       </c>
-      <c r="AJ145">
+      <c r="AP145">
         <v>0.5</v>
       </c>
     </row>
-    <row r="146" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>39</v>
       </c>
@@ -18312,11 +18629,11 @@
       <c r="AI146">
         <v>0.5</v>
       </c>
-      <c r="AJ146">
+      <c r="AP146">
         <v>0.5</v>
       </c>
     </row>
-    <row r="147" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>40</v>
       </c>
@@ -18364,11 +18681,11 @@
       <c r="AI147">
         <v>1</v>
       </c>
-      <c r="AJ147">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>41</v>
       </c>
@@ -18416,11 +18733,11 @@
       <c r="AI148">
         <v>0.77777777777777779</v>
       </c>
-      <c r="AJ148">
+      <c r="AP148">
         <v>0.8</v>
       </c>
     </row>
-    <row r="149" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>42</v>
       </c>
@@ -18468,11 +18785,11 @@
       <c r="AI149">
         <v>0.8</v>
       </c>
-      <c r="AJ149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>43</v>
       </c>
@@ -18520,11 +18837,11 @@
       <c r="AI150">
         <v>0.38461538461538458</v>
       </c>
-      <c r="AJ150">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>44</v>
       </c>
@@ -18572,11 +18889,11 @@
       <c r="AI151">
         <v>0.54545454545454541</v>
       </c>
-      <c r="AJ151">
+      <c r="AP151">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="152" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>45</v>
       </c>
@@ -18624,11 +18941,11 @@
       <c r="AI152">
         <v>0.625</v>
       </c>
-      <c r="AJ152">
+      <c r="AP152">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="153" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>46</v>
       </c>
@@ -18676,11 +18993,11 @@
       <c r="AI153">
         <v>0.36363636363636359</v>
       </c>
-      <c r="AJ153">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>47</v>
       </c>
@@ -18728,11 +19045,11 @@
       <c r="AI154">
         <v>0.75</v>
       </c>
-      <c r="AJ154">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>48</v>
       </c>
@@ -18780,11 +19097,11 @@
       <c r="AI155">
         <v>0.27272727272727271</v>
       </c>
-      <c r="AJ155">
+      <c r="AP155">
         <v>0.8571428571428571</v>
       </c>
     </row>
-    <row r="156" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>49</v>
       </c>
@@ -18832,11 +19149,11 @@
       <c r="AI156">
         <v>1</v>
       </c>
-      <c r="AJ156">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>50</v>
       </c>
@@ -18884,11 +19201,11 @@
       <c r="AI157">
         <v>0.33333333333333331</v>
       </c>
-      <c r="AJ157">
+      <c r="AP157">
         <v>0.8571428571428571</v>
       </c>
     </row>
-    <row r="158" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>51</v>
       </c>
@@ -18936,11 +19253,11 @@
       <c r="AI158">
         <v>0.1818181818181818</v>
       </c>
-      <c r="AJ158">
+      <c r="AP158">
         <v>0.8</v>
       </c>
     </row>
-    <row r="159" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>52</v>
       </c>
@@ -18988,11 +19305,11 @@
       <c r="AI159">
         <v>0.36363636363636359</v>
       </c>
-      <c r="AJ159">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>53</v>
       </c>
@@ -19040,11 +19357,11 @@
       <c r="AI160">
         <v>0.23076923076923081</v>
       </c>
-      <c r="AJ160">
+      <c r="AP160">
         <v>0.625</v>
       </c>
     </row>
-    <row r="161" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>54</v>
       </c>
@@ -19092,11 +19409,11 @@
       <c r="AI161">
         <v>0</v>
       </c>
-      <c r="AJ161">
+      <c r="AP161">
         <v>0.55555555555555558</v>
       </c>
     </row>
-    <row r="162" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>55</v>
       </c>
@@ -19144,11 +19461,11 @@
       <c r="AI162">
         <v>0.3</v>
       </c>
-      <c r="AJ162">
+      <c r="AP162">
         <v>0.75</v>
       </c>
     </row>
-    <row r="163" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>56</v>
       </c>
@@ -19196,11 +19513,11 @@
       <c r="AI163">
         <v>0.22222222222222221</v>
       </c>
-      <c r="AJ163">
+      <c r="AP163">
         <v>0.8</v>
       </c>
     </row>
-    <row r="164" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>57</v>
       </c>
@@ -19248,11 +19565,11 @@
       <c r="AI164">
         <v>0.22222222222222221</v>
       </c>
-      <c r="AJ164">
+      <c r="AP164">
         <v>0.8571428571428571</v>
       </c>
     </row>
-    <row r="165" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>58</v>
       </c>
@@ -19300,11 +19617,11 @@
       <c r="AI165">
         <v>0.3</v>
       </c>
-      <c r="AJ165">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="166" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>59</v>
       </c>
@@ -19352,11 +19669,11 @@
       <c r="AI166">
         <v>0.42857142857142849</v>
       </c>
-      <c r="AJ166">
+      <c r="AP166">
         <v>0.75</v>
       </c>
     </row>
-    <row r="167" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>60</v>
       </c>
@@ -19404,11 +19721,11 @@
       <c r="AI167">
         <v>0.42857142857142849</v>
       </c>
-      <c r="AJ167">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="168" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>61</v>
       </c>
@@ -19456,11 +19773,11 @@
       <c r="AI168">
         <v>0.5</v>
       </c>
-      <c r="AJ168">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="169" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>62</v>
       </c>
@@ -19508,11 +19825,11 @@
       <c r="AI169">
         <v>0.8</v>
       </c>
-      <c r="AJ169">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="170" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>63</v>
       </c>
@@ -19560,11 +19877,11 @@
       <c r="AI170">
         <v>0.44444444444444442</v>
       </c>
-      <c r="AJ170">
+      <c r="AP170">
         <v>0.75</v>
       </c>
     </row>
-    <row r="171" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>64</v>
       </c>
@@ -19612,11 +19929,11 @@
       <c r="AI171">
         <v>0.3</v>
       </c>
-      <c r="AJ171">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>65</v>
       </c>
@@ -19664,11 +19981,11 @@
       <c r="AI172">
         <v>0.375</v>
       </c>
-      <c r="AJ172">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>66</v>
       </c>
@@ -19716,11 +20033,11 @@
       <c r="AI173">
         <v>0.2</v>
       </c>
-      <c r="AJ173">
+      <c r="AP173">
         <v>0.8</v>
       </c>
     </row>
-    <row r="174" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>67</v>
       </c>
@@ -19768,11 +20085,11 @@
       <c r="AI174">
         <v>0.625</v>
       </c>
-      <c r="AJ174">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="175" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>68</v>
       </c>
@@ -19820,11 +20137,11 @@
       <c r="AI175">
         <v>0.2</v>
       </c>
-      <c r="AJ175">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="176" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>69</v>
       </c>
@@ -19872,11 +20189,11 @@
       <c r="AI176">
         <v>0.44444444444444442</v>
       </c>
-      <c r="AJ176">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="177" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>70</v>
       </c>
@@ -19924,11 +20241,11 @@
       <c r="AI177">
         <v>0.2857142857142857</v>
       </c>
-      <c r="AJ177">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="178" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>71</v>
       </c>
@@ -19976,11 +20293,11 @@
       <c r="AI178">
         <v>0.44444444444444442</v>
       </c>
-      <c r="AJ178">
+      <c r="AP178">
         <v>0.8</v>
       </c>
     </row>
-    <row r="179" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>72</v>
       </c>
@@ -20028,11 +20345,11 @@
       <c r="AI179">
         <v>0.22222222222222221</v>
       </c>
-      <c r="AJ179">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="180" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>73</v>
       </c>
@@ -20080,11 +20397,11 @@
       <c r="AI180">
         <v>0.33333333333333331</v>
       </c>
-      <c r="AJ180">
+      <c r="AP180">
         <v>0.5</v>
       </c>
     </row>
-    <row r="181" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>74</v>
       </c>
@@ -20132,11 +20449,11 @@
       <c r="AI181">
         <v>0.6</v>
       </c>
-      <c r="AJ181">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>75</v>
       </c>
@@ -20184,11 +20501,11 @@
       <c r="AI182">
         <v>0.41666666666666669</v>
       </c>
-      <c r="AJ182">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>76</v>
       </c>
@@ -20236,11 +20553,11 @@
       <c r="AI183">
         <v>0.3</v>
       </c>
-      <c r="AJ183">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>77</v>
       </c>
@@ -20288,11 +20605,11 @@
       <c r="AI184">
         <v>0.1111111111111111</v>
       </c>
-      <c r="AJ184">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="185" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>78</v>
       </c>
@@ -20340,11 +20657,11 @@
       <c r="AI185">
         <v>0.1</v>
       </c>
-      <c r="AJ185">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>79</v>
       </c>
@@ -20392,11 +20709,11 @@
       <c r="AI186">
         <v>0.36363636363636359</v>
       </c>
-      <c r="AJ186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>80</v>
       </c>
@@ -20444,11 +20761,11 @@
       <c r="AI187">
         <v>0.2</v>
       </c>
-      <c r="AJ187">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="188" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>81</v>
       </c>
@@ -20496,11 +20813,11 @@
       <c r="AI188">
         <v>0.125</v>
       </c>
-      <c r="AJ188">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>82</v>
       </c>
@@ -20548,11 +20865,11 @@
       <c r="AI189">
         <v>0.4</v>
       </c>
-      <c r="AJ189">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>83</v>
       </c>
@@ -20600,11 +20917,11 @@
       <c r="AI190">
         <v>0.5</v>
       </c>
-      <c r="AJ190">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>84</v>
       </c>
@@ -20652,11 +20969,11 @@
       <c r="AI191">
         <v>0.66666666666666663</v>
       </c>
-      <c r="AJ191">
+      <c r="AP191">
         <v>0.4</v>
       </c>
     </row>
-    <row r="192" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>85</v>
       </c>
@@ -20704,11 +21021,11 @@
       <c r="AI192">
         <v>0.45454545454545447</v>
       </c>
-      <c r="AJ192">
+      <c r="AP192">
         <v>0.75</v>
       </c>
     </row>
-    <row r="193" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>86</v>
       </c>
@@ -20756,11 +21073,11 @@
       <c r="AI193">
         <v>0.375</v>
       </c>
-      <c r="AJ193">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>87</v>
       </c>
@@ -20809,7 +21126,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="195" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>88</v>
       </c>
@@ -20857,11 +21174,11 @@
       <c r="AI195">
         <v>0.16666666666666671</v>
       </c>
-      <c r="AJ195">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>89</v>
       </c>
@@ -20909,11 +21226,11 @@
       <c r="AI196">
         <v>0.2</v>
       </c>
-      <c r="AJ196">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>90</v>
       </c>
@@ -20961,11 +21278,11 @@
       <c r="AI197">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="AJ197">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>91</v>
       </c>
@@ -21013,11 +21330,11 @@
       <c r="AI198">
         <v>0.33333333333333331</v>
       </c>
-      <c r="AJ198">
+      <c r="AP198">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="199" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>92</v>
       </c>
@@ -21065,11 +21382,11 @@
       <c r="AI199">
         <v>0.2</v>
       </c>
-      <c r="AJ199">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>93</v>
       </c>
@@ -21117,11 +21434,11 @@
       <c r="AI200">
         <v>0.42857142857142849</v>
       </c>
-      <c r="AJ200">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>94</v>
       </c>
@@ -21169,11 +21486,11 @@
       <c r="AI201">
         <v>0.22222222222222221</v>
       </c>
-      <c r="AJ201">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="202" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>95</v>
       </c>
@@ -21221,11 +21538,11 @@
       <c r="AI202">
         <v>0.1111111111111111</v>
       </c>
-      <c r="AJ202">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="203" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>96</v>
       </c>
@@ -21273,11 +21590,11 @@
       <c r="AI203">
         <v>0.22222222222222221</v>
       </c>
-      <c r="AJ203">
+      <c r="AP203">
         <v>0.75</v>
       </c>
     </row>
-    <row r="204" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>97</v>
       </c>
@@ -21325,11 +21642,11 @@
       <c r="AI204">
         <v>0.2</v>
       </c>
-      <c r="AJ204">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>98</v>
       </c>
@@ -21377,11 +21694,11 @@
       <c r="AI205">
         <v>0.44444444444444442</v>
       </c>
-      <c r="AJ205">
+      <c r="AP205">
         <v>0.8</v>
       </c>
     </row>
-    <row r="206" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>99</v>
       </c>
@@ -21429,11 +21746,11 @@
       <c r="AI206">
         <v>0.27272727272727271</v>
       </c>
-      <c r="AJ206">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="207" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>100</v>
       </c>
@@ -21482,15 +21799,15 @@
         <v>0.22222222222222221</v>
       </c>
     </row>
-    <row r="208" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:42" x14ac:dyDescent="0.2">
       <c r="AD208" s="9"/>
       <c r="AE208" s="9"/>
     </row>
-    <row r="209" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:42" x14ac:dyDescent="0.2">
       <c r="AD209" s="9"/>
       <c r="AE209" s="9"/>
     </row>
-    <row r="210" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
         <v>25</v>
       </c>
@@ -21503,7 +21820,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="211" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
         <v>24</v>
       </c>
@@ -21516,7 +21833,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="212" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>1</v>
       </c>
@@ -21573,11 +21890,11 @@
       <c r="AI212">
         <v>0.89925714285714275</v>
       </c>
-      <c r="AJ212">
+      <c r="AP212">
         <v>0.96588571428571435</v>
       </c>
     </row>
-    <row r="213" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>2</v>
       </c>
@@ -21634,11 +21951,11 @@
       <c r="AI213">
         <v>0.91915000000000002</v>
       </c>
-      <c r="AJ213">
+      <c r="AP213">
         <v>0.84685714285714286</v>
       </c>
     </row>
-    <row r="214" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>3</v>
       </c>
@@ -21695,11 +22012,11 @@
       <c r="AI214">
         <v>0.91048571428571434</v>
       </c>
-      <c r="AJ214">
+      <c r="AP214">
         <v>0.88583333333333336</v>
       </c>
     </row>
-    <row r="215" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>4</v>
       </c>
@@ -21756,11 +22073,11 @@
       <c r="AI215">
         <v>0.86638000000000004</v>
       </c>
-      <c r="AJ215">
+      <c r="AP215">
         <v>0.98631666666666662</v>
       </c>
     </row>
-    <row r="216" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>5</v>
       </c>
@@ -21817,11 +22134,11 @@
       <c r="AI216">
         <v>0.91721428571428565</v>
       </c>
-      <c r="AJ216">
+      <c r="AP216">
         <v>0.81973333333333331</v>
       </c>
     </row>
-    <row r="217" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>6</v>
       </c>
@@ -21875,11 +22192,11 @@
       <c r="AI217">
         <v>0.92128333333333334</v>
       </c>
-      <c r="AJ217">
+      <c r="AP217">
         <v>0.99271428571428555</v>
       </c>
     </row>
-    <row r="218" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>7</v>
       </c>
@@ -21933,11 +22250,11 @@
       <c r="AI218">
         <v>0.91837999999999997</v>
       </c>
-      <c r="AJ218">
+      <c r="AP218">
         <v>0.99822000000000011</v>
       </c>
     </row>
-    <row r="219" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>8</v>
       </c>
@@ -21991,11 +22308,11 @@
       <c r="AI219">
         <v>0.88621666666666654</v>
       </c>
-      <c r="AJ219">
+      <c r="AP219">
         <v>0.86796249999999997</v>
       </c>
     </row>
-    <row r="220" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>9</v>
       </c>
@@ -22049,11 +22366,11 @@
       <c r="AI220">
         <v>0.90260000000000007</v>
       </c>
-      <c r="AJ220">
+      <c r="AP220">
         <v>0.87602500000000005</v>
       </c>
     </row>
-    <row r="221" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>10</v>
       </c>
@@ -22107,11 +22424,11 @@
       <c r="AI221">
         <v>0.90981111111111113</v>
       </c>
-      <c r="AJ221">
+      <c r="AP221">
         <v>0.98562857142857141</v>
       </c>
     </row>
-    <row r="222" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>11</v>
       </c>
@@ -22159,11 +22476,11 @@
       <c r="AI222">
         <v>0.88582499999999997</v>
       </c>
-      <c r="AJ222">
+      <c r="AP222">
         <v>0.99433749999999999</v>
       </c>
     </row>
-    <row r="223" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>12</v>
       </c>
@@ -22211,11 +22528,11 @@
       <c r="AI223">
         <v>0.9139250000000001</v>
       </c>
-      <c r="AJ223">
+      <c r="AP223">
         <v>0.84681999999999991</v>
       </c>
     </row>
-    <row r="224" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>13</v>
       </c>
@@ -22263,11 +22580,11 @@
       <c r="AI224">
         <v>0.90090000000000003</v>
       </c>
-      <c r="AJ224">
+      <c r="AP224">
         <v>0.99595714285714287</v>
       </c>
     </row>
-    <row r="225" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>14</v>
       </c>
@@ -22315,11 +22632,11 @@
       <c r="AI225">
         <v>0.86812499999999992</v>
       </c>
-      <c r="AJ225">
+      <c r="AP225">
         <v>0.98899999999999999</v>
       </c>
     </row>
-    <row r="226" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>15</v>
       </c>
@@ -22367,11 +22684,11 @@
       <c r="AI226">
         <v>0.84823333333333328</v>
       </c>
-      <c r="AJ226">
+      <c r="AP226">
         <v>0.97255000000000003</v>
       </c>
     </row>
-    <row r="227" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>16</v>
       </c>
@@ -22419,11 +22736,11 @@
       <c r="AI227">
         <v>0.86436666666666662</v>
       </c>
-      <c r="AJ227">
+      <c r="AP227">
         <v>0.81013999999999997</v>
       </c>
     </row>
-    <row r="228" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>17</v>
       </c>
@@ -22471,11 +22788,11 @@
       <c r="AI228">
         <v>0.88405555555555548</v>
       </c>
-      <c r="AJ228">
+      <c r="AP228">
         <v>0.89123333333333343</v>
       </c>
     </row>
-    <row r="229" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>18</v>
       </c>
@@ -22523,11 +22840,11 @@
       <c r="AI229">
         <v>0.82730000000000004</v>
       </c>
-      <c r="AJ229">
+      <c r="AP229">
         <v>0.93198333333333327</v>
       </c>
     </row>
-    <row r="230" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>19</v>
       </c>
@@ -22575,11 +22892,11 @@
       <c r="AI230">
         <v>0.88152500000000011</v>
       </c>
-      <c r="AJ230">
+      <c r="AP230">
         <v>0.98973333333333324</v>
       </c>
     </row>
-    <row r="231" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>20</v>
       </c>
@@ -22627,11 +22944,11 @@
       <c r="AI231">
         <v>0.86899999999999988</v>
       </c>
-      <c r="AJ231">
+      <c r="AP231">
         <v>0.98613333333333342</v>
       </c>
     </row>
-    <row r="232" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>21</v>
       </c>
@@ -22679,11 +22996,11 @@
       <c r="AI232">
         <v>0.88082857142857152</v>
       </c>
-      <c r="AJ232">
+      <c r="AP232">
         <v>0.99218333333333331</v>
       </c>
     </row>
-    <row r="233" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>22</v>
       </c>
@@ -22731,11 +23048,11 @@
       <c r="AI233">
         <v>0.84656250000000011</v>
       </c>
-      <c r="AJ233">
+      <c r="AP233">
         <v>0.98272857142857151</v>
       </c>
     </row>
-    <row r="234" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>23</v>
       </c>
@@ -22783,11 +23100,11 @@
       <c r="AI234">
         <v>0.86266666666666669</v>
       </c>
-      <c r="AJ234">
+      <c r="AP234">
         <v>0.88677142857142854</v>
       </c>
     </row>
-    <row r="235" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>24</v>
       </c>
@@ -22835,11 +23152,11 @@
       <c r="AI235">
         <v>0.85925714285714272</v>
       </c>
-      <c r="AJ235">
+      <c r="AP235">
         <v>0.9881375</v>
       </c>
     </row>
-    <row r="236" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>25</v>
       </c>
@@ -22887,11 +23204,11 @@
       <c r="AI236">
         <v>0.8395999999999999</v>
       </c>
-      <c r="AJ236">
+      <c r="AP236">
         <v>0.99410000000000009</v>
       </c>
     </row>
-    <row r="237" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <v>26</v>
       </c>
@@ -22939,11 +23256,11 @@
       <c r="AI237">
         <v>0.86277999999999988</v>
       </c>
-      <c r="AJ237">
+      <c r="AP237">
         <v>0.95998000000000006</v>
       </c>
     </row>
-    <row r="238" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <v>27</v>
       </c>
@@ -22991,11 +23308,11 @@
       <c r="AI238">
         <v>0.86030000000000006</v>
       </c>
-      <c r="AJ238">
+      <c r="AP238">
         <v>0.99382857142857139</v>
       </c>
     </row>
-    <row r="239" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <v>28</v>
       </c>
@@ -23043,11 +23360,11 @@
       <c r="AI239">
         <v>0.86093999999999993</v>
       </c>
-      <c r="AJ239">
+      <c r="AP239">
         <v>0.99188333333333334</v>
       </c>
     </row>
-    <row r="240" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <v>29</v>
       </c>
@@ -23095,11 +23412,11 @@
       <c r="AI240">
         <v>0.87864285714285706</v>
       </c>
-      <c r="AJ240">
+      <c r="AP240">
         <v>0.9929</v>
       </c>
     </row>
-    <row r="241" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <v>30</v>
       </c>
@@ -23147,11 +23464,11 @@
       <c r="AI241">
         <v>0.8101799999999999</v>
       </c>
-      <c r="AJ241">
+      <c r="AP241">
         <v>0.99231249999999993</v>
       </c>
     </row>
-    <row r="242" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>31</v>
       </c>
@@ -23199,11 +23516,11 @@
       <c r="AI242">
         <v>0.87909999999999999</v>
       </c>
-      <c r="AJ242">
+      <c r="AP242">
         <v>0.87365555555555541</v>
       </c>
     </row>
-    <row r="243" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <v>32</v>
       </c>
@@ -23251,11 +23568,11 @@
       <c r="AI243">
         <v>0.83655000000000002</v>
       </c>
-      <c r="AJ243">
+      <c r="AP243">
         <v>0.86419999999999986</v>
       </c>
     </row>
-    <row r="244" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>33</v>
       </c>
@@ -23303,11 +23620,11 @@
       <c r="AI244">
         <v>0.81137142857142863</v>
       </c>
-      <c r="AJ244">
+      <c r="AP244">
         <v>0.68789999999999996</v>
       </c>
     </row>
-    <row r="245" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>34</v>
       </c>
@@ -23355,11 +23672,11 @@
       <c r="AI245">
         <v>0.85868</v>
       </c>
-      <c r="AJ245">
+      <c r="AP245">
         <v>0.99175999999999997</v>
       </c>
     </row>
-    <row r="246" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>35</v>
       </c>
@@ -23407,11 +23724,11 @@
       <c r="AI246">
         <v>0.8534166666666666</v>
       </c>
-      <c r="AJ246">
+      <c r="AP246">
         <v>0.99631428571428582</v>
       </c>
     </row>
-    <row r="247" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <v>36</v>
       </c>
@@ -23459,11 +23776,11 @@
       <c r="AI247">
         <v>0.90686666666666671</v>
       </c>
-      <c r="AJ247">
+      <c r="AP247">
         <v>0.98447142857142855</v>
       </c>
     </row>
-    <row r="248" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>37</v>
       </c>
@@ -23511,11 +23828,11 @@
       <c r="AI248">
         <v>0.85841666666666672</v>
       </c>
-      <c r="AJ248">
+      <c r="AP248">
         <v>0.85162857142857151</v>
       </c>
     </row>
-    <row r="249" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>38</v>
       </c>
@@ -23563,11 +23880,11 @@
       <c r="AI249">
         <v>0.85358750000000005</v>
       </c>
-      <c r="AJ249">
+      <c r="AP249">
         <v>0.98663333333333336</v>
       </c>
     </row>
-    <row r="250" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>39</v>
       </c>
@@ -23615,11 +23932,11 @@
       <c r="AI250">
         <v>0.86701428571428585</v>
       </c>
-      <c r="AJ250">
+      <c r="AP250">
         <v>0.88453333333333328</v>
       </c>
     </row>
-    <row r="251" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>40</v>
       </c>
@@ -23667,11 +23984,11 @@
       <c r="AI251">
         <v>0.84137777777777778</v>
       </c>
-      <c r="AJ251">
+      <c r="AP251">
         <v>0.69035000000000002</v>
       </c>
     </row>
-    <row r="252" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>41</v>
       </c>
@@ -23719,11 +24036,11 @@
       <c r="AI252">
         <v>0.87766666666666671</v>
       </c>
-      <c r="AJ252">
+      <c r="AP252">
         <v>0.72497272727272721</v>
       </c>
     </row>
-    <row r="253" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>42</v>
       </c>
@@ -23771,11 +24088,11 @@
       <c r="AI253">
         <v>0.87703999999999982</v>
       </c>
-      <c r="AJ253">
+      <c r="AP253">
         <v>0.88052222222222232</v>
       </c>
     </row>
-    <row r="254" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>43</v>
       </c>
@@ -23823,11 +24140,11 @@
       <c r="AI254">
         <v>0.84945000000000004</v>
       </c>
-      <c r="AJ254">
+      <c r="AP254">
         <v>0.79576000000000002</v>
       </c>
     </row>
-    <row r="255" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>44</v>
       </c>
@@ -23875,11 +24192,11 @@
       <c r="AI255">
         <v>0.85294999999999999</v>
       </c>
-      <c r="AJ255">
+      <c r="AP255">
         <v>0.68755384615384618</v>
       </c>
     </row>
-    <row r="256" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <v>45</v>
       </c>
@@ -23927,11 +24244,11 @@
       <c r="AI256">
         <v>0.87042857142857144</v>
       </c>
-      <c r="AJ256">
+      <c r="AP256">
         <v>0.79862999999999995</v>
       </c>
     </row>
-    <row r="257" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>46</v>
       </c>
@@ -23979,11 +24296,11 @@
       <c r="AI257">
         <v>0.88300000000000001</v>
       </c>
-      <c r="AJ257">
+      <c r="AP257">
         <v>0.64157272727272729</v>
       </c>
     </row>
-    <row r="258" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <v>47</v>
       </c>
@@ -24031,11 +24348,11 @@
       <c r="AI258">
         <v>0.85615714285714284</v>
       </c>
-      <c r="AJ258">
+      <c r="AP258">
         <v>0.69428999999999996</v>
       </c>
     </row>
-    <row r="259" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>48</v>
       </c>
@@ -24083,11 +24400,11 @@
       <c r="AI259">
         <v>0.87930000000000008</v>
       </c>
-      <c r="AJ259">
+      <c r="AP259">
         <v>0.65395555555555562</v>
       </c>
     </row>
-    <row r="260" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>49</v>
       </c>
@@ -24135,11 +24452,11 @@
       <c r="AI260">
         <v>0.86125555555555566</v>
       </c>
-      <c r="AJ260">
+      <c r="AP260">
         <v>0.65415000000000001</v>
       </c>
     </row>
-    <row r="261" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>50</v>
       </c>
@@ -24187,11 +24504,11 @@
       <c r="AI261">
         <v>0.8754777777777778</v>
       </c>
-      <c r="AJ261">
+      <c r="AP261">
         <v>0.8725222222222222</v>
       </c>
     </row>
-    <row r="262" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>51</v>
       </c>
@@ -24239,11 +24556,11 @@
       <c r="AI262">
         <v>0.86760000000000004</v>
       </c>
-      <c r="AJ262">
+      <c r="AP262">
         <v>0.70951818181818183</v>
       </c>
     </row>
-    <row r="263" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>52</v>
       </c>
@@ -24291,11 +24608,11 @@
       <c r="AI263">
         <v>0.83962500000000007</v>
       </c>
-      <c r="AJ263">
+      <c r="AP263">
         <v>0.86588571428571437</v>
       </c>
     </row>
-    <row r="264" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>53</v>
       </c>
@@ -24343,11 +24660,11 @@
       <c r="AI264">
         <v>0.83079999999999998</v>
       </c>
-      <c r="AJ264">
+      <c r="AP264">
         <v>0.56762857142857137</v>
       </c>
     </row>
-    <row r="265" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>54</v>
       </c>
@@ -24395,11 +24712,11 @@
       <c r="AI265">
         <v>0.80700000000000005</v>
       </c>
-      <c r="AJ265">
+      <c r="AP265">
         <v>0.41320000000000012</v>
       </c>
     </row>
-    <row r="266" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>55</v>
       </c>
@@ -24447,11 +24764,11 @@
       <c r="AI266">
         <v>0.88216000000000006</v>
       </c>
-      <c r="AJ266">
+      <c r="AP266">
         <v>0.74009999999999998</v>
       </c>
     </row>
-    <row r="267" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>56</v>
       </c>
@@ -24499,11 +24816,11 @@
       <c r="AI267">
         <v>0.83581666666666665</v>
       </c>
-      <c r="AJ267">
+      <c r="AP267">
         <v>0.63991818181818194</v>
       </c>
     </row>
-    <row r="268" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>57</v>
       </c>
@@ -24551,11 +24868,11 @@
       <c r="AI268">
         <v>0.85923333333333318</v>
       </c>
-      <c r="AJ268">
+      <c r="AP268">
         <v>0.45835555555555563</v>
       </c>
     </row>
-    <row r="269" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>58</v>
       </c>
@@ -24603,11 +24920,11 @@
       <c r="AI269">
         <v>0.85939999999999994</v>
       </c>
-      <c r="AJ269">
+      <c r="AP269">
         <v>0.91015000000000013</v>
       </c>
     </row>
-    <row r="270" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>59</v>
       </c>
@@ -24655,11 +24972,11 @@
       <c r="AI270">
         <v>0.84922500000000001</v>
       </c>
-      <c r="AJ270">
+      <c r="AP270">
         <v>0.69570833333333326</v>
       </c>
     </row>
-    <row r="271" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>60</v>
       </c>
@@ -24707,11 +25024,11 @@
       <c r="AI271">
         <v>0.83145000000000002</v>
       </c>
-      <c r="AJ271">
+      <c r="AP271">
         <v>0.73720833333333324</v>
       </c>
     </row>
-    <row r="272" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>61</v>
       </c>
@@ -24759,11 +25076,11 @@
       <c r="AI272">
         <v>0.87590000000000001</v>
       </c>
-      <c r="AJ272">
+      <c r="AP272">
         <v>0.75391666666666668</v>
       </c>
     </row>
-    <row r="273" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>62</v>
       </c>
@@ -24811,11 +25128,11 @@
       <c r="AI273">
         <v>0.8468</v>
       </c>
-      <c r="AJ273">
+      <c r="AP273">
         <v>0.44237272727272731</v>
       </c>
     </row>
-    <row r="274" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>63</v>
       </c>
@@ -24863,11 +25180,11 @@
       <c r="AI274">
         <v>0.84355000000000002</v>
       </c>
-      <c r="AJ274">
+      <c r="AP274">
         <v>0.66093333333333326</v>
       </c>
     </row>
-    <row r="275" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>64</v>
       </c>
@@ -24915,11 +25232,11 @@
       <c r="AI275">
         <v>0.81391999999999987</v>
       </c>
-      <c r="AJ275">
+      <c r="AP275">
         <v>0.65487499999999998</v>
       </c>
     </row>
-    <row r="276" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <v>65</v>
       </c>
@@ -24967,11 +25284,11 @@
       <c r="AI276">
         <v>0.8504571428571428</v>
       </c>
-      <c r="AJ276">
+      <c r="AP276">
         <v>0.72350909090909099</v>
       </c>
     </row>
-    <row r="277" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <v>66</v>
       </c>
@@ -25019,11 +25336,11 @@
       <c r="AI277">
         <v>0.83057999999999998</v>
       </c>
-      <c r="AJ277">
+      <c r="AP277">
         <v>0.63375454545454535</v>
       </c>
     </row>
-    <row r="278" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>67</v>
       </c>
@@ -25071,11 +25388,11 @@
       <c r="AI278">
         <v>0.87254285714285718</v>
       </c>
-      <c r="AJ278">
+      <c r="AP278">
         <v>0.63051818181818176</v>
       </c>
     </row>
-    <row r="279" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>68</v>
       </c>
@@ -25123,11 +25440,11 @@
       <c r="AI279">
         <v>0.88266000000000011</v>
       </c>
-      <c r="AJ279">
+      <c r="AP279">
         <v>0.57423999999999986</v>
       </c>
     </row>
-    <row r="280" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>69</v>
       </c>
@@ -25175,11 +25492,11 @@
       <c r="AI280">
         <v>0.82701666666666673</v>
       </c>
-      <c r="AJ280">
+      <c r="AP280">
         <v>0.62948181818181825</v>
       </c>
     </row>
-    <row r="281" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>70</v>
       </c>
@@ -25227,11 +25544,11 @@
       <c r="AI281">
         <v>0.86996250000000008</v>
       </c>
-      <c r="AJ281">
+      <c r="AP281">
         <v>0.53503846153846157</v>
       </c>
     </row>
-    <row r="282" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>71</v>
       </c>
@@ -25279,11 +25596,11 @@
       <c r="AI282">
         <v>0.87124999999999997</v>
       </c>
-      <c r="AJ282">
+      <c r="AP282">
         <v>0.53639999999999999</v>
       </c>
     </row>
-    <row r="283" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>72</v>
       </c>
@@ -25331,11 +25648,11 @@
       <c r="AI283">
         <v>0.85793333333333333</v>
       </c>
-      <c r="AJ283">
+      <c r="AP283">
         <v>0.68253076923076916</v>
       </c>
     </row>
-    <row r="284" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>73</v>
       </c>
@@ -25383,11 +25700,11 @@
       <c r="AI284">
         <v>0.85071666666666657</v>
       </c>
-      <c r="AJ284">
+      <c r="AP284">
         <v>0.61167142857142864</v>
       </c>
     </row>
-    <row r="285" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>74</v>
       </c>
@@ -25435,11 +25752,11 @@
       <c r="AI285">
         <v>0.87073</v>
       </c>
-      <c r="AJ285">
+      <c r="AP285">
         <v>0.49639285714285708</v>
       </c>
     </row>
-    <row r="286" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>75</v>
       </c>
@@ -25487,11 +25804,11 @@
       <c r="AI286">
         <v>0.81673333333333342</v>
       </c>
-      <c r="AJ286">
+      <c r="AP286">
         <v>0.49676999999999999</v>
       </c>
     </row>
-    <row r="287" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>76</v>
       </c>
@@ -25539,11 +25856,11 @@
       <c r="AI287">
         <v>0.83616000000000013</v>
       </c>
-      <c r="AJ287">
+      <c r="AP287">
         <v>0.46350833333333319</v>
       </c>
     </row>
-    <row r="288" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>77</v>
       </c>
@@ -25591,11 +25908,11 @@
       <c r="AI288">
         <v>0.85104999999999997</v>
       </c>
-      <c r="AJ288">
+      <c r="AP288">
         <v>0.76294615384615383</v>
       </c>
     </row>
-    <row r="289" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>78</v>
       </c>
@@ -25643,11 +25960,11 @@
       <c r="AI289">
         <v>0.84374000000000005</v>
       </c>
-      <c r="AJ289">
+      <c r="AP289">
         <v>0.57724999999999993</v>
       </c>
     </row>
-    <row r="290" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>79</v>
       </c>
@@ -25695,11 +26012,11 @@
       <c r="AI290">
         <v>0.85587499999999994</v>
       </c>
-      <c r="AJ290">
+      <c r="AP290">
         <v>0.61230000000000007</v>
       </c>
     </row>
-    <row r="291" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>80</v>
       </c>
@@ -25747,11 +26064,11 @@
       <c r="AI291">
         <v>0.83778000000000008</v>
       </c>
-      <c r="AJ291">
+      <c r="AP291">
         <v>0.58479090909090903</v>
       </c>
     </row>
-    <row r="292" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>81</v>
       </c>
@@ -25799,11 +26116,11 @@
       <c r="AI292">
         <v>0.84091428571428584</v>
       </c>
-      <c r="AJ292">
+      <c r="AP292">
         <v>0.41324166666666667</v>
       </c>
     </row>
-    <row r="293" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>82</v>
       </c>
@@ -25851,11 +26168,11 @@
       <c r="AI293">
         <v>0.84383999999999992</v>
       </c>
-      <c r="AJ293">
+      <c r="AP293">
         <v>0.579175</v>
       </c>
     </row>
-    <row r="294" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>83</v>
       </c>
@@ -25903,11 +26220,11 @@
       <c r="AI294">
         <v>0.85945714285714292</v>
       </c>
-      <c r="AJ294">
+      <c r="AP294">
         <v>0.62153636363636366</v>
       </c>
     </row>
-    <row r="295" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>84</v>
       </c>
@@ -25955,11 +26272,11 @@
       <c r="AI295">
         <v>0.82767777777777773</v>
       </c>
-      <c r="AJ295">
+      <c r="AP295">
         <v>0.49373000000000011</v>
       </c>
     </row>
-    <row r="296" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>85</v>
       </c>
@@ -26007,11 +26324,11 @@
       <c r="AI296">
         <v>0.817025</v>
       </c>
-      <c r="AJ296">
+      <c r="AP296">
         <v>0.57726666666666671</v>
       </c>
     </row>
-    <row r="297" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>86</v>
       </c>
@@ -26059,11 +26376,11 @@
       <c r="AI297">
         <v>0.84817142857142858</v>
       </c>
-      <c r="AJ297">
+      <c r="AP297">
         <v>0.61201818181818179</v>
       </c>
     </row>
-    <row r="298" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>87</v>
       </c>
@@ -26112,7 +26429,7 @@
         <v>0.8610833333333332</v>
       </c>
     </row>
-    <row r="299" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>88</v>
       </c>
@@ -26160,11 +26477,11 @@
       <c r="AI299">
         <v>0.81576666666666664</v>
       </c>
-      <c r="AJ299">
+      <c r="AP299">
         <v>0.55772857142857146</v>
       </c>
     </row>
-    <row r="300" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>89</v>
       </c>
@@ -26212,11 +26529,11 @@
       <c r="AI300">
         <v>0.88573999999999997</v>
       </c>
-      <c r="AJ300">
+      <c r="AP300">
         <v>0.45941538461538473</v>
       </c>
     </row>
-    <row r="301" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>90</v>
       </c>
@@ -26264,11 +26581,11 @@
       <c r="AI301">
         <v>0.8037333333333333</v>
       </c>
-      <c r="AJ301">
+      <c r="AP301">
         <v>0.61312727272727274</v>
       </c>
     </row>
-    <row r="302" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>91</v>
       </c>
@@ -26316,11 +26633,11 @@
       <c r="AI302">
         <v>0.86365000000000014</v>
       </c>
-      <c r="AJ302">
+      <c r="AP302">
         <v>0.49453999999999998</v>
       </c>
     </row>
-    <row r="303" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
         <v>92</v>
       </c>
@@ -26368,11 +26685,11 @@
       <c r="AI303">
         <v>0.87602000000000013</v>
       </c>
-      <c r="AJ303">
+      <c r="AP303">
         <v>0.39781</v>
       </c>
     </row>
-    <row r="304" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
         <v>93</v>
       </c>
@@ -26420,11 +26737,11 @@
       <c r="AI304">
         <v>0.85112499999999991</v>
       </c>
-      <c r="AJ304">
+      <c r="AP304">
         <v>0.68146153846153845</v>
       </c>
     </row>
-    <row r="305" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
         <v>94</v>
       </c>
@@ -26472,11 +26789,11 @@
       <c r="AI305">
         <v>0.86750000000000005</v>
       </c>
-      <c r="AJ305">
+      <c r="AP305">
         <v>0.43927272727272731</v>
       </c>
     </row>
-    <row r="306" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
         <v>95</v>
       </c>
@@ -26524,11 +26841,11 @@
       <c r="AI306">
         <v>0.86251666666666671</v>
       </c>
-      <c r="AJ306">
+      <c r="AP306">
         <v>0.68552999999999997</v>
       </c>
     </row>
-    <row r="307" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
         <v>96</v>
       </c>
@@ -26576,11 +26893,11 @@
       <c r="AI307">
         <v>0.85008333333333341</v>
       </c>
-      <c r="AJ307">
+      <c r="AP307">
         <v>0.3657333333333333</v>
       </c>
     </row>
-    <row r="308" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A308" s="1">
         <v>97</v>
       </c>
@@ -26628,11 +26945,11 @@
       <c r="AI308">
         <v>0.87417999999999996</v>
       </c>
-      <c r="AJ308">
+      <c r="AP308">
         <v>0.62552727272727271</v>
       </c>
     </row>
-    <row r="309" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A309" s="1">
         <v>98</v>
       </c>
@@ -26680,11 +26997,11 @@
       <c r="AI309">
         <v>0.81958333333333344</v>
       </c>
-      <c r="AJ309">
+      <c r="AP309">
         <v>0.72435454545454547</v>
       </c>
     </row>
-    <row r="310" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A310" s="1">
         <v>99</v>
       </c>
@@ -26732,11 +27049,11 @@
       <c r="AI310">
         <v>0.83875</v>
       </c>
-      <c r="AJ310">
+      <c r="AP310">
         <v>0.64001000000000008</v>
       </c>
     </row>
-    <row r="311" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A311" s="1">
         <v>100</v>
       </c>
@@ -26785,15 +27102,15 @@
         <v>0.82056666666666667</v>
       </c>
     </row>
-    <row r="312" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:42" x14ac:dyDescent="0.2">
       <c r="AD312" s="9"/>
       <c r="AE312" s="9"/>
     </row>
-    <row r="313" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:42" x14ac:dyDescent="0.2">
       <c r="AD313" s="9"/>
       <c r="AE313" s="9"/>
     </row>
-    <row r="314" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
         <v>27</v>
       </c>
@@ -26806,7 +27123,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="315" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A315" s="3" t="s">
         <v>24</v>
       </c>
@@ -26819,7 +27136,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="316" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A316" s="1">
         <v>1</v>
       </c>
@@ -26876,11 +27193,11 @@
       <c r="AI316">
         <v>2.81E-2</v>
       </c>
-      <c r="AJ316">
+      <c r="AP316">
         <v>0.95579999999999998</v>
       </c>
     </row>
-    <row r="317" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A317" s="1">
         <v>2</v>
       </c>
@@ -26937,11 +27254,11 @@
       <c r="AI317">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="AJ317">
+      <c r="AP317">
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A318" s="1">
         <v>3</v>
       </c>
@@ -26998,11 +27315,11 @@
       <c r="AI318">
         <v>6.0699999999999997E-2</v>
       </c>
-      <c r="AJ318">
+      <c r="AP318">
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A319" s="1">
         <v>4</v>
       </c>
@@ -27059,11 +27376,11 @@
       <c r="AI319">
         <v>1.4800000000000001E-2</v>
       </c>
-      <c r="AJ319">
+      <c r="AP319">
         <v>4.4000000000000003E-3</v>
       </c>
     </row>
-    <row r="320" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A320" s="1">
         <v>5</v>
       </c>
@@ -27120,11 +27437,11 @@
       <c r="AI320">
         <v>1.66E-2</v>
       </c>
-      <c r="AJ320">
+      <c r="AP320">
         <v>0.1013</v>
       </c>
     </row>
-    <row r="321" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A321" s="1">
         <v>6</v>
       </c>
@@ -27178,11 +27495,11 @@
       <c r="AI321">
         <v>7.6999999999999999E-2</v>
       </c>
-      <c r="AJ321">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="322" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP321">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A322" s="1">
         <v>7</v>
       </c>
@@ -27236,11 +27553,11 @@
       <c r="AI322">
         <v>4.48E-2</v>
       </c>
-      <c r="AJ322">
+      <c r="AP322">
         <v>0.9284</v>
       </c>
     </row>
-    <row r="323" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A323" s="1">
         <v>8</v>
       </c>
@@ -27294,11 +27611,11 @@
       <c r="AI323">
         <v>5.5500000000000001E-2</v>
       </c>
-      <c r="AJ323">
+      <c r="AP323">
         <v>0.90439999999999998</v>
       </c>
     </row>
-    <row r="324" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
         <v>9</v>
       </c>
@@ -27352,11 +27669,11 @@
       <c r="AI324">
         <v>8.1199999999999994E-2</v>
       </c>
-      <c r="AJ324">
+      <c r="AP324">
         <v>0.72809999999999997</v>
       </c>
     </row>
-    <row r="325" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
         <v>10</v>
       </c>
@@ -27410,11 +27727,11 @@
       <c r="AI325">
         <v>0.1013</v>
       </c>
-      <c r="AJ325">
+      <c r="AP325">
         <v>0.92079999999999995</v>
       </c>
     </row>
-    <row r="326" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A326" s="1">
         <v>11</v>
       </c>
@@ -27462,11 +27779,11 @@
       <c r="AI326">
         <v>0.1173</v>
       </c>
-      <c r="AJ326">
+      <c r="AP326">
         <v>0.96819999999999995</v>
       </c>
     </row>
-    <row r="327" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A327" s="1">
         <v>12</v>
       </c>
@@ -27514,11 +27831,11 @@
       <c r="AI327">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AJ327">
+      <c r="AP327">
         <v>0.74350000000000005</v>
       </c>
     </row>
-    <row r="328" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
         <v>13</v>
       </c>
@@ -27566,11 +27883,11 @@
       <c r="AI328">
         <v>0.10680000000000001</v>
       </c>
-      <c r="AJ328">
+      <c r="AP328">
         <v>0.56399999999999995</v>
       </c>
     </row>
-    <row r="329" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A329" s="1">
         <v>14</v>
       </c>
@@ -27618,11 +27935,11 @@
       <c r="AI329">
         <v>4.7399999999999998E-2</v>
       </c>
-      <c r="AJ329">
+      <c r="AP329">
         <v>0.29360000000000003</v>
       </c>
     </row>
-    <row r="330" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A330" s="1">
         <v>15</v>
       </c>
@@ -27670,11 +27987,11 @@
       <c r="AI330">
         <v>3.5400000000000001E-2</v>
       </c>
-      <c r="AJ330">
+      <c r="AP330">
         <v>0.84599999999999997</v>
       </c>
     </row>
-    <row r="331" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A331" s="1">
         <v>16</v>
       </c>
@@ -27722,11 +28039,11 @@
       <c r="AI331">
         <v>0.1072</v>
       </c>
-      <c r="AJ331">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="332" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP331">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A332" s="1">
         <v>17</v>
       </c>
@@ -27774,11 +28091,11 @@
       <c r="AI332">
         <v>0.1173</v>
       </c>
-      <c r="AJ332">
+      <c r="AP332">
         <v>0.99960000000000004</v>
       </c>
     </row>
-    <row r="333" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A333" s="1">
         <v>18</v>
       </c>
@@ -27826,11 +28143,11 @@
       <c r="AI333">
         <v>2.9899999999999999E-2</v>
       </c>
-      <c r="AJ333">
+      <c r="AP333">
         <v>0.9869</v>
       </c>
     </row>
-    <row r="334" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A334" s="1">
         <v>19</v>
       </c>
@@ -27878,11 +28195,11 @@
       <c r="AI334">
         <v>9.01E-2</v>
       </c>
-      <c r="AJ334">
+      <c r="AP334">
         <v>0.99519999999999997</v>
       </c>
     </row>
-    <row r="335" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A335" s="1">
         <v>20</v>
       </c>
@@ -27930,11 +28247,11 @@
       <c r="AI335">
         <v>7.7700000000000005E-2</v>
       </c>
-      <c r="AJ335">
+      <c r="AP335">
         <v>0.91979999999999995</v>
       </c>
     </row>
-    <row r="336" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A336" s="1">
         <v>21</v>
       </c>
@@ -27982,11 +28299,11 @@
       <c r="AI336">
         <v>9.4500000000000001E-2</v>
       </c>
-      <c r="AJ336">
+      <c r="AP336">
         <v>0.99590000000000001</v>
       </c>
     </row>
-    <row r="337" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A337" s="1">
         <v>22</v>
       </c>
@@ -28034,11 +28351,11 @@
       <c r="AI337">
         <v>6.7699999999999996E-2</v>
       </c>
-      <c r="AJ337">
+      <c r="AP337">
         <v>0.82879999999999998</v>
       </c>
     </row>
-    <row r="338" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A338" s="1">
         <v>23</v>
       </c>
@@ -28086,11 +28403,11 @@
       <c r="AI338">
         <v>8.0799999999999997E-2</v>
       </c>
-      <c r="AJ338">
+      <c r="AP338">
         <v>0.99570000000000003</v>
       </c>
     </row>
-    <row r="339" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A339" s="1">
         <v>24</v>
       </c>
@@ -28138,11 +28455,11 @@
       <c r="AI339">
         <v>8.4599999999999995E-2</v>
       </c>
-      <c r="AJ339">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="340" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP339">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A340" s="1">
         <v>25</v>
       </c>
@@ -28190,11 +28507,11 @@
       <c r="AI340">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="AJ340">
+      <c r="AP340">
         <v>0.99860000000000004</v>
       </c>
     </row>
-    <row r="341" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A341" s="1">
         <v>26</v>
       </c>
@@ -28242,11 +28559,11 @@
       <c r="AI341">
         <v>0.1099</v>
       </c>
-      <c r="AJ341">
+      <c r="AP341">
         <v>0.99780000000000002</v>
       </c>
     </row>
-    <row r="342" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A342" s="1">
         <v>27</v>
       </c>
@@ -28294,11 +28611,11 @@
       <c r="AI342">
         <v>8.2799999999999999E-2</v>
       </c>
-      <c r="AJ342">
+      <c r="AP342">
         <v>0.98650000000000004</v>
       </c>
     </row>
-    <row r="343" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A343" s="1">
         <v>28</v>
       </c>
@@ -28346,11 +28663,11 @@
       <c r="AI343">
         <v>0.1182</v>
       </c>
-      <c r="AJ343">
+      <c r="AP343">
         <v>0.9486</v>
       </c>
     </row>
-    <row r="344" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A344" s="1">
         <v>29</v>
       </c>
@@ -28398,11 +28715,11 @@
       <c r="AI344">
         <v>7.9799999999999996E-2</v>
       </c>
-      <c r="AJ344">
+      <c r="AP344">
         <v>0.99750000000000005</v>
       </c>
     </row>
-    <row r="345" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A345" s="1">
         <v>30</v>
       </c>
@@ -28450,11 +28767,11 @@
       <c r="AI345">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="AJ345">
+      <c r="AP345">
         <v>0.91379999999999995</v>
       </c>
     </row>
-    <row r="346" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A346" s="1">
         <v>31</v>
       </c>
@@ -28502,11 +28819,11 @@
       <c r="AI346">
         <v>8.9800000000000005E-2</v>
       </c>
-      <c r="AJ346">
+      <c r="AP346">
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A347" s="1">
         <v>32</v>
       </c>
@@ -28554,11 +28871,11 @@
       <c r="AI347">
         <v>7.5300000000000006E-2</v>
       </c>
-      <c r="AJ347">
+      <c r="AP347">
         <v>0.99429999999999996</v>
       </c>
     </row>
-    <row r="348" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A348" s="1">
         <v>33</v>
       </c>
@@ -28606,11 +28923,11 @@
       <c r="AI348">
         <v>9.8100000000000007E-2</v>
       </c>
-      <c r="AJ348">
+      <c r="AP348">
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A349" s="1">
         <v>34</v>
       </c>
@@ -28658,11 +28975,11 @@
       <c r="AI349">
         <v>7.22E-2</v>
       </c>
-      <c r="AJ349">
+      <c r="AP349">
         <v>5.7799999999999997E-2</v>
       </c>
     </row>
-    <row r="350" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A350" s="1">
         <v>35</v>
       </c>
@@ -28710,11 +29027,11 @@
       <c r="AI350">
         <v>8.5800000000000001E-2</v>
       </c>
-      <c r="AJ350">
+      <c r="AP350">
         <v>0.96389999999999998</v>
       </c>
     </row>
-    <row r="351" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A351" s="1">
         <v>36</v>
       </c>
@@ -28762,11 +29079,11 @@
       <c r="AI351">
         <v>9.4E-2</v>
       </c>
-      <c r="AJ351">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="352" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP351">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A352" s="1">
         <v>37</v>
       </c>
@@ -28814,11 +29131,11 @@
       <c r="AI352">
         <v>7.8700000000000006E-2</v>
       </c>
-      <c r="AJ352">
+      <c r="AP352">
         <v>0.98029999999999995</v>
       </c>
     </row>
-    <row r="353" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A353" s="1">
         <v>38</v>
       </c>
@@ -28866,11 +29183,11 @@
       <c r="AI353">
         <v>6.7100000000000007E-2</v>
       </c>
-      <c r="AJ353">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="354" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP353">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A354" s="1">
         <v>39</v>
       </c>
@@ -28918,11 +29235,11 @@
       <c r="AI354">
         <v>5.4699999999999999E-2</v>
       </c>
-      <c r="AJ354">
+      <c r="AP354">
         <v>0.9728</v>
       </c>
     </row>
-    <row r="355" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A355" s="1">
         <v>40</v>
       </c>
@@ -28970,11 +29287,11 @@
       <c r="AI355">
         <v>7.0499999999999993E-2</v>
       </c>
-      <c r="AJ355">
+      <c r="AP355">
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A356" s="1">
         <v>41</v>
       </c>
@@ -29022,11 +29339,11 @@
       <c r="AI356">
         <v>5.2900000000000003E-2</v>
       </c>
-      <c r="AJ356">
+      <c r="AP356">
         <v>0.16059999999999999</v>
       </c>
     </row>
-    <row r="357" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A357" s="1">
         <v>42</v>
       </c>
@@ -29074,11 +29391,11 @@
       <c r="AI357">
         <v>8.0199999999999994E-2</v>
       </c>
-      <c r="AJ357">
+      <c r="AP357">
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A358" s="1">
         <v>43</v>
       </c>
@@ -29126,11 +29443,11 @@
       <c r="AI358">
         <v>8.5699999999999998E-2</v>
       </c>
-      <c r="AJ358">
+      <c r="AP358">
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A359" s="1">
         <v>44</v>
       </c>
@@ -29178,11 +29495,11 @@
       <c r="AI359">
         <v>6.7299999999999999E-2</v>
       </c>
-      <c r="AJ359">
+      <c r="AP359">
         <v>0.85819999999999996</v>
       </c>
     </row>
-    <row r="360" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A360" s="1">
         <v>45</v>
       </c>
@@ -29230,11 +29547,11 @@
       <c r="AI360">
         <v>9.0399999999999994E-2</v>
       </c>
-      <c r="AJ360">
+      <c r="AP360">
         <v>0.92979999999999996</v>
       </c>
     </row>
-    <row r="361" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A361" s="1">
         <v>46</v>
       </c>
@@ -29282,11 +29599,11 @@
       <c r="AI361">
         <v>8.9800000000000005E-2</v>
       </c>
-      <c r="AJ361">
+      <c r="AP361">
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A362" s="1">
         <v>47</v>
       </c>
@@ -29334,11 +29651,11 @@
       <c r="AI362">
         <v>9.11E-2</v>
       </c>
-      <c r="AJ362">
+      <c r="AP362">
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A363" s="1">
         <v>48</v>
       </c>
@@ -29386,11 +29703,11 @@
       <c r="AI363">
         <v>0.1179</v>
       </c>
-      <c r="AJ363">
+      <c r="AP363">
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A364" s="1">
         <v>49</v>
       </c>
@@ -29438,11 +29755,11 @@
       <c r="AI364">
         <v>8.14E-2</v>
       </c>
-      <c r="AJ364">
+      <c r="AP364">
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A365" s="1">
         <v>50</v>
       </c>
@@ -29490,11 +29807,11 @@
       <c r="AI365">
         <v>8.7499999999999994E-2</v>
       </c>
-      <c r="AJ365">
+      <c r="AP365">
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A366" s="1">
         <v>51</v>
       </c>
@@ -29542,11 +29859,11 @@
       <c r="AI366">
         <v>6.3E-2</v>
       </c>
-      <c r="AJ366">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="367" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP366">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A367" s="1">
         <v>52</v>
       </c>
@@ -29594,11 +29911,11 @@
       <c r="AI367">
         <v>7.0099999999999996E-2</v>
       </c>
-      <c r="AJ367">
+      <c r="AP367">
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A368" s="1">
         <v>53</v>
       </c>
@@ -29646,11 +29963,11 @@
       <c r="AI368">
         <v>9.3899999999999997E-2</v>
       </c>
-      <c r="AJ368">
+      <c r="AP368">
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A369" s="1">
         <v>54</v>
       </c>
@@ -29698,11 +30015,11 @@
       <c r="AI369">
         <v>0.1032</v>
       </c>
-      <c r="AJ369">
+      <c r="AP369">
         <v>0.44869999999999999</v>
       </c>
     </row>
-    <row r="370" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A370" s="1">
         <v>55</v>
       </c>
@@ -29750,11 +30067,11 @@
       <c r="AI370">
         <v>7.6899999999999996E-2</v>
       </c>
-      <c r="AJ370">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="371" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP370">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A371" s="1">
         <v>56</v>
       </c>
@@ -29802,11 +30119,11 @@
       <c r="AI371">
         <v>7.3800000000000004E-2</v>
       </c>
-      <c r="AJ371">
+      <c r="AP371">
         <v>0.99109999999999998</v>
       </c>
     </row>
-    <row r="372" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A372" s="1">
         <v>57</v>
       </c>
@@ -29854,11 +30171,11 @@
       <c r="AI372">
         <v>7.0699999999999999E-2</v>
       </c>
-      <c r="AJ372">
+      <c r="AP372">
         <v>0.99280000000000002</v>
       </c>
     </row>
-    <row r="373" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A373" s="1">
         <v>58</v>
       </c>
@@ -29906,11 +30223,11 @@
       <c r="AI373">
         <v>8.4099999999999994E-2</v>
       </c>
-      <c r="AJ373">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="374" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP373">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A374" s="1">
         <v>59</v>
       </c>
@@ -29958,11 +30275,11 @@
       <c r="AI374">
         <v>5.8299999999999998E-2</v>
       </c>
-      <c r="AJ374">
+      <c r="AP374">
         <v>0.99560000000000004</v>
       </c>
     </row>
-    <row r="375" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A375" s="1">
         <v>60</v>
       </c>
@@ -30010,11 +30327,11 @@
       <c r="AI375">
         <v>4.48E-2</v>
       </c>
-      <c r="AJ375">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="376" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP375">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A376" s="1">
         <v>61</v>
       </c>
@@ -30062,11 +30379,11 @@
       <c r="AI376">
         <v>5.6099999999999997E-2</v>
       </c>
-      <c r="AJ376">
+      <c r="AP376">
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A377" s="1">
         <v>62</v>
       </c>
@@ -30114,11 +30431,11 @@
       <c r="AI377">
         <v>4.8099999999999997E-2</v>
       </c>
-      <c r="AJ377">
+      <c r="AP377">
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A378" s="1">
         <v>63</v>
       </c>
@@ -30166,11 +30483,11 @@
       <c r="AI378">
         <v>5.3800000000000001E-2</v>
       </c>
-      <c r="AJ378">
+      <c r="AP378">
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A379" s="1">
         <v>64</v>
       </c>
@@ -30218,11 +30535,11 @@
       <c r="AI379">
         <v>6.3100000000000003E-2</v>
       </c>
-      <c r="AJ379">
+      <c r="AP379">
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A380" s="1">
         <v>65</v>
       </c>
@@ -30270,11 +30587,11 @@
       <c r="AI380">
         <v>7.2800000000000004E-2</v>
       </c>
-      <c r="AJ380">
+      <c r="AP380">
         <v>0.43480000000000002</v>
       </c>
     </row>
-    <row r="381" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A381" s="1">
         <v>66</v>
       </c>
@@ -30322,11 +30639,11 @@
       <c r="AI381">
         <v>8.7300000000000003E-2</v>
       </c>
-      <c r="AJ381">
+      <c r="AP381">
         <v>0.96050000000000002</v>
       </c>
     </row>
-    <row r="382" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A382" s="1">
         <v>67</v>
       </c>
@@ -30374,11 +30691,11 @@
       <c r="AI382">
         <v>7.8700000000000006E-2</v>
       </c>
-      <c r="AJ382">
+      <c r="AP382">
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A383" s="1">
         <v>68</v>
       </c>
@@ -30426,11 +30743,11 @@
       <c r="AI383">
         <v>7.0400000000000004E-2</v>
       </c>
-      <c r="AJ383">
+      <c r="AP383">
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A384" s="1">
         <v>69</v>
       </c>
@@ -30478,11 +30795,11 @@
       <c r="AI384">
         <v>6.4899999999999999E-2</v>
       </c>
-      <c r="AJ384">
+      <c r="AP384">
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A385" s="1">
         <v>70</v>
       </c>
@@ -30530,11 +30847,11 @@
       <c r="AI385">
         <v>6.7599999999999993E-2</v>
       </c>
-      <c r="AJ385">
+      <c r="AP385">
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A386" s="1">
         <v>71</v>
       </c>
@@ -30582,11 +30899,11 @@
       <c r="AI386">
         <v>6.1800000000000001E-2</v>
       </c>
-      <c r="AJ386">
+      <c r="AP386">
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A387" s="1">
         <v>72</v>
       </c>
@@ -30634,11 +30951,11 @@
       <c r="AI387">
         <v>5.5599999999999997E-2</v>
       </c>
-      <c r="AJ387">
+      <c r="AP387">
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A388" s="1">
         <v>73</v>
       </c>
@@ -30686,11 +31003,11 @@
       <c r="AI388">
         <v>9.01E-2</v>
       </c>
-      <c r="AJ388">
+      <c r="AP388">
         <v>0.94569999999999999</v>
       </c>
     </row>
-    <row r="389" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A389" s="1">
         <v>74</v>
       </c>
@@ -30738,11 +31055,11 @@
       <c r="AI389">
         <v>8.8499999999999995E-2</v>
       </c>
-      <c r="AJ389">
+      <c r="AP389">
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A390" s="1">
         <v>75</v>
       </c>
@@ -30790,11 +31107,11 @@
       <c r="AI390">
         <v>8.1100000000000005E-2</v>
       </c>
-      <c r="AJ390">
+      <c r="AP390">
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A391" s="1">
         <v>76</v>
       </c>
@@ -30842,11 +31159,11 @@
       <c r="AI391">
         <v>8.6199999999999999E-2</v>
       </c>
-      <c r="AJ391">
+      <c r="AP391">
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A392" s="1">
         <v>77</v>
       </c>
@@ -30894,11 +31211,11 @@
       <c r="AI392">
         <v>0.1021</v>
       </c>
-      <c r="AJ392">
+      <c r="AP392">
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A393" s="1">
         <v>78</v>
       </c>
@@ -30946,11 +31263,11 @@
       <c r="AI393">
         <v>9.01E-2</v>
       </c>
-      <c r="AJ393">
+      <c r="AP393">
         <v>0.88859999999999995</v>
       </c>
     </row>
-    <row r="394" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A394" s="1">
         <v>79</v>
       </c>
@@ -30998,11 +31315,11 @@
       <c r="AI394">
         <v>0.1016</v>
       </c>
-      <c r="AJ394">
+      <c r="AP394">
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A395" s="1">
         <v>80</v>
       </c>
@@ -31050,11 +31367,11 @@
       <c r="AI395">
         <v>9.9500000000000005E-2</v>
       </c>
-      <c r="AJ395">
+      <c r="AP395">
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="396" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A396" s="1">
         <v>81</v>
       </c>
@@ -31102,11 +31419,11 @@
       <c r="AI396">
         <v>7.7700000000000005E-2</v>
       </c>
-      <c r="AJ396">
+      <c r="AP396">
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A397" s="1">
         <v>82</v>
       </c>
@@ -31154,11 +31471,11 @@
       <c r="AI397">
         <v>5.3600000000000002E-2</v>
       </c>
-      <c r="AJ397">
+      <c r="AP397">
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A398" s="1">
         <v>83</v>
       </c>
@@ -31206,11 +31523,11 @@
       <c r="AI398">
         <v>6.7599999999999993E-2</v>
       </c>
-      <c r="AJ398">
+      <c r="AP398">
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A399" s="1">
         <v>84</v>
       </c>
@@ -31258,11 +31575,11 @@
       <c r="AI399">
         <v>5.2299999999999999E-2</v>
       </c>
-      <c r="AJ399">
+      <c r="AP399">
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A400" s="1">
         <v>85</v>
       </c>
@@ -31310,11 +31627,11 @@
       <c r="AI400">
         <v>4.2700000000000002E-2</v>
       </c>
-      <c r="AJ400">
+      <c r="AP400">
         <v>0.65390000000000004</v>
       </c>
     </row>
-    <row r="401" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A401" s="1">
         <v>86</v>
       </c>
@@ -31362,11 +31679,11 @@
       <c r="AI401">
         <v>5.16E-2</v>
       </c>
-      <c r="AJ401">
+      <c r="AP401">
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A402" s="1">
         <v>87</v>
       </c>
@@ -31414,11 +31731,11 @@
       <c r="AI402">
         <v>7.9500000000000001E-2</v>
       </c>
-      <c r="AJ402">
+      <c r="AP402">
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A403" s="1">
         <v>88</v>
       </c>
@@ -31466,11 +31783,11 @@
       <c r="AI403">
         <v>7.7700000000000005E-2</v>
       </c>
-      <c r="AJ403">
+      <c r="AP403">
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A404" s="1">
         <v>89</v>
       </c>
@@ -31518,11 +31835,11 @@
       <c r="AI404">
         <v>8.5599999999999996E-2</v>
       </c>
-      <c r="AJ404">
+      <c r="AP404">
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A405" s="1">
         <v>90</v>
       </c>
@@ -31570,11 +31887,11 @@
       <c r="AI405">
         <v>7.2499999999999995E-2</v>
       </c>
-      <c r="AJ405">
+      <c r="AP405">
         <v>2.3E-3</v>
       </c>
     </row>
-    <row r="406" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A406" s="1">
         <v>91</v>
       </c>
@@ -31622,11 +31939,11 @@
       <c r="AI406">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="AJ406">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="407" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP406">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A407" s="1">
         <v>92</v>
       </c>
@@ -31674,11 +31991,11 @@
       <c r="AI407">
         <v>8.8499999999999995E-2</v>
       </c>
-      <c r="AJ407">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="408" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AP407">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A408" s="1">
         <v>93</v>
       </c>
@@ -31726,11 +32043,11 @@
       <c r="AI408">
         <v>0.11799999999999999</v>
       </c>
-      <c r="AJ408">
+      <c r="AP408">
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A409" s="1">
         <v>94</v>
       </c>
@@ -31778,11 +32095,11 @@
       <c r="AI409">
         <v>9.1600000000000001E-2</v>
       </c>
-      <c r="AJ409">
+      <c r="AP409">
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A410" s="1">
         <v>95</v>
       </c>
@@ -31830,11 +32147,11 @@
       <c r="AI410">
         <v>9.6199999999999994E-2</v>
       </c>
-      <c r="AJ410">
+      <c r="AP410">
         <v>0.28720000000000001</v>
       </c>
     </row>
-    <row r="411" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A411" s="1">
         <v>96</v>
       </c>
@@ -31882,11 +32199,11 @@
       <c r="AI411">
         <v>8.2600000000000007E-2</v>
       </c>
-      <c r="AJ411">
+      <c r="AP411">
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A412" s="1">
         <v>97</v>
       </c>
@@ -31934,11 +32251,11 @@
       <c r="AI412">
         <v>9.2499999999999999E-2</v>
       </c>
-      <c r="AJ412">
+      <c r="AP412">
         <v>0.98509999999999998</v>
       </c>
     </row>
-    <row r="413" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A413" s="1">
         <v>98</v>
       </c>
@@ -31986,11 +32303,11 @@
       <c r="AI413">
         <v>6.93E-2</v>
       </c>
-      <c r="AJ413">
+      <c r="AP413">
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A414" s="1">
         <v>99</v>
       </c>
@@ -32038,11 +32355,11 @@
       <c r="AI414">
         <v>7.9500000000000001E-2</v>
       </c>
-      <c r="AJ414">
+      <c r="AP414">
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A415" s="1">
         <v>100</v>
       </c>
@@ -32090,11 +32407,11 @@
       <c r="AI415">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="AJ415">
+      <c r="AP415">
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:42" x14ac:dyDescent="0.2">
       <c r="AD416" s="9"/>
       <c r="AE416" s="9"/>
     </row>
@@ -32451,7 +32768,9 @@
       <c r="AE504" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
+    <mergeCell ref="AP3:AQ3"/>
+    <mergeCell ref="AP4:AQ4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="I4:J4"/>

--- a/CIFAR_Global.xlsx
+++ b/CIFAR_Global.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashleyau/Documents/PhD/Practical_Experiment/Finalised/Finalised_Algorithm_ResNet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DE090E-9773-E341-830A-F6CF21696C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00DA706D-56A9-A344-A1A2-3C6AF7559773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="19920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="31">
   <si>
     <t>100 Rounds</t>
   </si>
@@ -218,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -249,22 +249,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6526,309 +6528,309 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AQ$5:$AQ$104</c:f>
+              <c:f>Sheet1!$V$5:$V$104</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="100"/>
                 <c:pt idx="0">
-                  <c:v>0.1212</c:v>
+                  <c:v>0.1787</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.12690000000000001</c:v>
+                  <c:v>0.1893</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.1222</c:v>
+                  <c:v>8.2699999999999996E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.15110000000000001</c:v>
+                  <c:v>0.1087</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2127</c:v>
+                  <c:v>0.17</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.9400000000000002E-2</c:v>
+                  <c:v>0.16270000000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.23930000000000001</c:v>
+                  <c:v>0.11</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.14019999999999999</c:v>
+                  <c:v>0.28129999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.14749999999999999</c:v>
+                  <c:v>0.27929999999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.18129999999999999</c:v>
+                  <c:v>0.37730000000000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2167</c:v>
+                  <c:v>0.48070000000000002</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.1636</c:v>
+                  <c:v>0.42599999999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.1134</c:v>
+                  <c:v>0.49669999999999997</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.22459999999999999</c:v>
+                  <c:v>0.47670000000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.18859999999999999</c:v>
+                  <c:v>0.32200000000000001</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.18240000000000001</c:v>
+                  <c:v>0.50070000000000003</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.16420000000000001</c:v>
+                  <c:v>0.48670000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.1358</c:v>
+                  <c:v>0.53669999999999995</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.1356</c:v>
+                  <c:v>0.49930000000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.2009</c:v>
+                  <c:v>0.51470000000000005</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.13009999999999999</c:v>
+                  <c:v>0.55530000000000002</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.2281</c:v>
+                  <c:v>0.44529999999999997</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.15490000000000001</c:v>
+                  <c:v>0.52400000000000002</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.17849999999999999</c:v>
+                  <c:v>0.46129999999999999</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.16250000000000001</c:v>
+                  <c:v>0.47</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.192</c:v>
+                  <c:v>0.49530000000000002</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.155</c:v>
+                  <c:v>0.44</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.1197</c:v>
+                  <c:v>0.41670000000000001</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.1643</c:v>
+                  <c:v>0.54530000000000001</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.16839999999999999</c:v>
+                  <c:v>0.59599999999999997</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>9.8900000000000002E-2</c:v>
+                  <c:v>0.5393</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.10879999999999999</c:v>
+                  <c:v>0.45729999999999998</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.1454</c:v>
+                  <c:v>0.35599999999999998</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.1739</c:v>
+                  <c:v>0.40799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.1193</c:v>
+                  <c:v>0.41199999999999998</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.1462</c:v>
+                  <c:v>0.35</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.17829999999999999</c:v>
+                  <c:v>0.51129999999999998</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.14269999999999999</c:v>
+                  <c:v>0.50070000000000003</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.15479999999999999</c:v>
+                  <c:v>0.44130000000000003</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.18890000000000001</c:v>
+                  <c:v>0.52400000000000002</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.15959999999999999</c:v>
+                  <c:v>0.46600000000000003</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.19170000000000001</c:v>
+                  <c:v>0.498</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.1003</c:v>
+                  <c:v>0.42270000000000002</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.1749</c:v>
+                  <c:v>0.42930000000000001</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.13500000000000001</c:v>
+                  <c:v>0.32929999999999998</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.1817</c:v>
+                  <c:v>0.43330000000000002</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.17760000000000001</c:v>
+                  <c:v>0.38129999999999997</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.1749</c:v>
+                  <c:v>0.54400000000000004</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.15010000000000001</c:v>
+                  <c:v>0.4773</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.1202</c:v>
+                  <c:v>0.51400000000000001</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.21179999999999999</c:v>
+                  <c:v>0.54069999999999996</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.1187</c:v>
+                  <c:v>0.32</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.1288</c:v>
+                  <c:v>0.51670000000000005</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.15179999999999999</c:v>
+                  <c:v>0.44269999999999998</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.15079999999999999</c:v>
+                  <c:v>0.56730000000000003</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.16619999999999999</c:v>
+                  <c:v>0.45669999999999999</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.13900000000000001</c:v>
+                  <c:v>0.53400000000000003</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.22750000000000001</c:v>
+                  <c:v>0.47470000000000001</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.17860000000000001</c:v>
+                  <c:v>0.49869999999999998</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.22839999999999999</c:v>
+                  <c:v>0.36470000000000002</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.14649999999999999</c:v>
+                  <c:v>0.26469999999999999</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.1106</c:v>
+                  <c:v>0.47870000000000001</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.1515</c:v>
+                  <c:v>0.51470000000000005</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.1004</c:v>
+                  <c:v>0.502</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.15670000000000001</c:v>
+                  <c:v>0.29270000000000002</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>9.8599999999999993E-2</c:v>
+                  <c:v>0.44069999999999998</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.1812</c:v>
+                  <c:v>0.48470000000000002</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.22650000000000001</c:v>
+                  <c:v>0.32200000000000001</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.20799999999999999</c:v>
+                  <c:v>0.34799999999999998</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.12939999999999999</c:v>
+                  <c:v>0.47599999999999998</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.1318</c:v>
+                  <c:v>0.49070000000000003</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.20280000000000001</c:v>
+                  <c:v>0.45669999999999999</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.17319999999999999</c:v>
+                  <c:v>0.50600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.14910000000000001</c:v>
+                  <c:v>0.46329999999999999</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.2077</c:v>
+                  <c:v>0.51870000000000005</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.27989999999999998</c:v>
+                  <c:v>0.44</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.1641</c:v>
+                  <c:v>0.48799999999999999</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.1207</c:v>
+                  <c:v>0.40400000000000003</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.22939999999999999</c:v>
+                  <c:v>0.4733</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.1012</c:v>
+                  <c:v>0.47670000000000001</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.1111</c:v>
+                  <c:v>0.48</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.14269999999999999</c:v>
+                  <c:v>0.48070000000000002</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.13100000000000001</c:v>
+                  <c:v>0.52800000000000002</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.14979999999999999</c:v>
+                  <c:v>0.42070000000000002</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.20039999999999999</c:v>
+                  <c:v>0.39800000000000002</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.1429</c:v>
+                  <c:v>0.48930000000000001</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.19270000000000001</c:v>
+                  <c:v>0.40600000000000003</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.1096</c:v>
+                  <c:v>0.37469999999999998</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.13220000000000001</c:v>
+                  <c:v>0.34200000000000003</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.15340000000000001</c:v>
+                  <c:v>0.38669999999999999</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.1532</c:v>
+                  <c:v>0.34799999999999998</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.11609999999999999</c:v>
+                  <c:v>0.44929999999999998</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.2281</c:v>
+                  <c:v>0.3533</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.13289999999999999</c:v>
+                  <c:v>0.41870000000000002</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.13669999999999999</c:v>
+                  <c:v>0.26069999999999999</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.10100000000000001</c:v>
+                  <c:v>0.33400000000000002</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.14630000000000001</c:v>
+                  <c:v>0.48799999999999999</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.17419999999999999</c:v>
+                  <c:v>0.374</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.1648</c:v>
+                  <c:v>0.39800000000000002</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.1593</c:v>
+                  <c:v>0.42</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7979,345 +7981,8 @@
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:v>My Alg</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="tx2">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$AI$5:$AI$104</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="100"/>
-                <c:pt idx="0">
-                  <c:v>0.1178</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.13589999999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.25679999999999997</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.28050000000000003</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.28789999999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.33189999999999997</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.3523</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.36230000000000001</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.35630000000000001</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.38969999999999999</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.41560000000000002</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.41160000000000002</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.4178</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.39760000000000001</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.40649999999999997</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.4254</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.40870000000000001</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.42220000000000002</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.43269999999999997</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.43240000000000001</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.42120000000000002</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.4345</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.43</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.43380000000000002</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.43440000000000001</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.43190000000000001</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.43090000000000001</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.43930000000000002</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.42520000000000002</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.43590000000000001</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.44319999999999998</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.43669999999999998</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.4375</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.4375</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.4254</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.43790000000000001</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.44030000000000002</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.43009999999999998</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.42259999999999998</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.43240000000000001</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.44359999999999999</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.44059999999999999</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.43780000000000002</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.43869999999999998</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.4355</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0.43409999999999999</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.43880000000000002</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.43869999999999998</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.44319999999999998</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.44419999999999998</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.44090000000000001</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.43640000000000001</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.43459999999999999</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.44140000000000001</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.43980000000000002</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.44169999999999998</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.44409999999999999</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.4471</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.44019999999999998</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.44109999999999999</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.44379999999999997</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.45069999999999999</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.44779999999999998</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0.44350000000000001</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0.44469999999999998</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0.44309999999999999</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0.4365</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>0.44019999999999998</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>0.44169999999999998</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0.43230000000000002</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0.43969999999999998</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>0.4451</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>0.43869999999999998</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>0.44629999999999997</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>0.44400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>0.44590000000000002</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>0.4501</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>0.443</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>0.43909999999999999</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>0.43719999999999998</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>0.43980000000000002</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>0.4451</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>0.44800000000000001</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>0.4299</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>0.4279</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>0.43840000000000001</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>0.44579999999999997</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>0.44740000000000002</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>0.44900000000000001</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>0.44929999999999998</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>0.44269999999999998</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>0.44130000000000003</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>0.43790000000000001</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>0.43740000000000001</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>0.4365</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>0.4451</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>0.43809999999999999</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>0.43969999999999998</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>0.44450000000000001</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>0.44600000000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8660-5649-B405-EE2C5DE71550}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
           <c:tx>
             <c:v>FL-Defender</c:v>
           </c:tx>
@@ -8651,7 +8316,7 @@
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:order val="1"/>
           <c:tx>
             <c:v>My Alg Improved</c:v>
           </c:tx>
@@ -8665,304 +8330,304 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="100"/>
                 <c:pt idx="0">
-                  <c:v>0.1007</c:v>
+                  <c:v>0.1026</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.1724</c:v>
+                  <c:v>0.19159999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.24970000000000001</c:v>
+                  <c:v>0.23580000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.30690000000000001</c:v>
+                  <c:v>0.3251</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.35639999999999999</c:v>
+                  <c:v>0.3659</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.37419999999999998</c:v>
+                  <c:v>0.43149999999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.38919999999999999</c:v>
+                  <c:v>0.51119999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.39369999999999999</c:v>
+                  <c:v>0.52149999999999996</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.41310000000000002</c:v>
+                  <c:v>0.56189999999999996</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.4234</c:v>
+                  <c:v>0.57389999999999997</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.4088</c:v>
+                  <c:v>0.58430000000000004</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.42320000000000002</c:v>
+                  <c:v>0.63090000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.4163</c:v>
+                  <c:v>0.65859999999999996</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.41749999999999998</c:v>
+                  <c:v>0.7198</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.43090000000000001</c:v>
+                  <c:v>0.68969999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.42830000000000001</c:v>
+                  <c:v>0.66420000000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.42220000000000002</c:v>
+                  <c:v>0.59560000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.42170000000000002</c:v>
+                  <c:v>0.66359999999999997</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.4289</c:v>
+                  <c:v>0.66400000000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.43149999999999999</c:v>
+                  <c:v>0.71460000000000001</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.42859999999999998</c:v>
+                  <c:v>0.70020000000000004</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.43230000000000002</c:v>
+                  <c:v>0.67210000000000003</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.43109999999999998</c:v>
+                  <c:v>0.68079999999999996</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.42909999999999998</c:v>
+                  <c:v>0.71419999999999995</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.43380000000000002</c:v>
+                  <c:v>0.79949999999999999</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.43409999999999999</c:v>
+                  <c:v>0.64339999999999997</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.43120000000000003</c:v>
+                  <c:v>0.64349999999999996</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.4299</c:v>
+                  <c:v>0.67290000000000005</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.44009999999999999</c:v>
+                  <c:v>0.68289999999999995</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.43409999999999999</c:v>
+                  <c:v>0.71830000000000005</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.43590000000000001</c:v>
+                  <c:v>0.63109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.44040000000000001</c:v>
+                  <c:v>0.75749999999999995</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.44440000000000002</c:v>
+                  <c:v>0.71650000000000003</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.43430000000000002</c:v>
+                  <c:v>0.76029999999999998</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.43619999999999998</c:v>
+                  <c:v>0.68840000000000001</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.43669999999999998</c:v>
+                  <c:v>0.65849999999999997</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.4385</c:v>
+                  <c:v>0.65510000000000002</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.43919999999999998</c:v>
+                  <c:v>0.67449999999999999</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.43569999999999998</c:v>
+                  <c:v>0.76919999999999999</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.43619999999999998</c:v>
+                  <c:v>0.70220000000000005</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.43990000000000001</c:v>
+                  <c:v>0.71479999999999999</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.43719999999999998</c:v>
+                  <c:v>0.70299999999999996</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.43619999999999998</c:v>
+                  <c:v>0.63449999999999995</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.43419999999999997</c:v>
+                  <c:v>0.68540000000000001</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.438</c:v>
+                  <c:v>0.79759999999999998</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.43909999999999999</c:v>
+                  <c:v>0.7177</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.44219999999999998</c:v>
+                  <c:v>0.745</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.43809999999999999</c:v>
+                  <c:v>0.75460000000000005</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.43980000000000002</c:v>
+                  <c:v>0.71060000000000001</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.44019999999999998</c:v>
+                  <c:v>0.76</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.43509999999999999</c:v>
+                  <c:v>0.70389999999999997</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.4405</c:v>
+                  <c:v>0.69189999999999996</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.4405</c:v>
+                  <c:v>0.74560000000000004</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.44240000000000002</c:v>
+                  <c:v>0.71179999999999999</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.44169999999999998</c:v>
+                  <c:v>0.75760000000000005</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.44219999999999998</c:v>
+                  <c:v>0.6895</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.44240000000000002</c:v>
+                  <c:v>0.80710000000000004</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.4415</c:v>
+                  <c:v>0.68279999999999996</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.44059999999999999</c:v>
+                  <c:v>0.74950000000000006</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.44800000000000001</c:v>
+                  <c:v>0.77459999999999996</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.44419999999999998</c:v>
+                  <c:v>0.71509999999999996</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.43719999999999998</c:v>
+                  <c:v>0.81789999999999996</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.44429999999999997</c:v>
+                  <c:v>0.67359999999999998</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.44119999999999998</c:v>
+                  <c:v>0.8175</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.44319999999999998</c:v>
+                  <c:v>0.76190000000000002</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.4395</c:v>
+                  <c:v>0.66539999999999999</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.43640000000000001</c:v>
+                  <c:v>0.72970000000000002</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.44359999999999999</c:v>
+                  <c:v>0.75800000000000001</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.44040000000000001</c:v>
+                  <c:v>0.72299999999999998</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.44390000000000002</c:v>
+                  <c:v>0.70269999999999999</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.44259999999999999</c:v>
+                  <c:v>0.72330000000000005</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.44069999999999998</c:v>
+                  <c:v>0.57830000000000004</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.44190000000000002</c:v>
+                  <c:v>0.73980000000000001</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.44069999999999998</c:v>
+                  <c:v>0.71</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.4405</c:v>
+                  <c:v>0.66139999999999999</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.44290000000000002</c:v>
+                  <c:v>0.63439999999999996</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.4456</c:v>
+                  <c:v>0.73080000000000001</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.44629999999999997</c:v>
+                  <c:v>0.69210000000000005</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.44850000000000001</c:v>
+                  <c:v>0.64639999999999997</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.44440000000000002</c:v>
+                  <c:v>0.70069999999999999</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.4456</c:v>
+                  <c:v>0.68359999999999999</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.44550000000000001</c:v>
+                  <c:v>0.70899999999999996</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.44119999999999998</c:v>
+                  <c:v>0.62080000000000002</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.44040000000000001</c:v>
+                  <c:v>0.58940000000000003</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.44090000000000001</c:v>
+                  <c:v>0.69030000000000002</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.44140000000000001</c:v>
+                  <c:v>0.77159999999999995</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.4415</c:v>
+                  <c:v>0.75170000000000003</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.44109999999999999</c:v>
+                  <c:v>0.67490000000000006</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.44790000000000002</c:v>
+                  <c:v>0.67379999999999995</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.4481</c:v>
+                  <c:v>0.78300000000000003</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.44350000000000001</c:v>
+                  <c:v>0.7157</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.44219999999999998</c:v>
+                  <c:v>0.70950000000000002</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.4471</c:v>
+                  <c:v>0.66690000000000005</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.44540000000000002</c:v>
+                  <c:v>0.74470000000000003</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.44740000000000002</c:v>
+                  <c:v>0.64900000000000002</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.44369999999999998</c:v>
+                  <c:v>0.66869999999999996</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.44579999999999997</c:v>
+                  <c:v>0.7873</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.44290000000000002</c:v>
+                  <c:v>0.67920000000000003</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.44230000000000003</c:v>
+                  <c:v>0.75319999999999998</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.4446</c:v>
+                  <c:v>0.69420000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9336,15 +9001,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>55894</xdr:colOff>
+      <xdr:colOff>27030</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>111649</xdr:rowOff>
+      <xdr:rowOff>121269</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>722644</xdr:colOff>
+      <xdr:colOff>693780</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>124349</xdr:rowOff>
+      <xdr:rowOff>133969</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9407,16 +9072,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>101504</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>29540</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>126620</xdr:rowOff>
+      <xdr:rowOff>50420</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>40</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>19713</xdr:rowOff>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>575734</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9777,7 +9442,7 @@
     <col min="32" max="32" width="12.33203125" customWidth="1"/>
     <col min="34" max="34" width="15.1640625" customWidth="1"/>
     <col min="35" max="35" width="12" customWidth="1"/>
-    <col min="36" max="36" width="13" customWidth="1"/>
+    <col min="36" max="36" width="14" customWidth="1"/>
     <col min="42" max="43" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9791,9 +9456,7 @@
       <c r="AH1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AP1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="AP1" s="1"/>
     </row>
     <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -9802,14 +9465,14 @@
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="19" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="15"/>
@@ -9824,13 +9487,13 @@
       <c r="S2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="16" t="s">
+      <c r="T2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="U2" s="15"/>
       <c r="V2" s="15"/>
       <c r="W2" s="15"/>
-      <c r="AD2" s="16" t="s">
+      <c r="AD2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="AE2" s="15"/>
@@ -9838,13 +9501,12 @@
       <c r="AH2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="AI2" s="16" t="s">
+      <c r="AI2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="AJ2" s="16"/>
-      <c r="AP2" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="AJ2" s="17"/>
+      <c r="AK2" s="17"/>
+      <c r="AP2" s="2"/>
       <c r="AQ2" s="7"/>
     </row>
     <row r="3" spans="1:43" x14ac:dyDescent="0.2">
@@ -9878,7 +9540,7 @@
       <c r="J3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="19" t="s">
+      <c r="L3" s="14" t="s">
         <v>15</v>
       </c>
       <c r="M3" s="15"/>
@@ -9915,34 +9577,35 @@
       <c r="AI3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="AJ3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AP3" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AQ3" s="15"/>
+      <c r="AK3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP3" s="20"/>
+      <c r="AQ3" s="21"/>
     </row>
     <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="16" t="s">
         <v>19</v>
       </c>
       <c r="H4" s="15"/>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="16" t="s">
         <v>20</v>
       </c>
       <c r="J4" s="15"/>
       <c r="S4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T4" s="14" t="s">
+      <c r="T4" s="16" t="s">
         <v>21</v>
       </c>
       <c r="U4" s="15"/>
-      <c r="V4" s="14" t="s">
+      <c r="V4" s="16" t="s">
         <v>22</v>
       </c>
       <c r="W4" s="15"/>
@@ -9964,9 +9627,10 @@
       <c r="AJ4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AP4" s="19" t="s">
-        <v>13</v>
-      </c>
+      <c r="AK4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AP4" s="14"/>
       <c r="AQ4" s="15"/>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.2">
@@ -10013,7 +9677,7 @@
         <v>0.1134</v>
       </c>
       <c r="V5">
-        <v>0.11269999999999999</v>
+        <v>0.1787</v>
       </c>
       <c r="W5">
         <v>0.124</v>
@@ -10034,13 +9698,7 @@
         <v>0.1178</v>
       </c>
       <c r="AJ5">
-        <v>0.1007</v>
-      </c>
-      <c r="AP5">
-        <v>9.9900000000000003E-2</v>
-      </c>
-      <c r="AQ5">
-        <v>0.1212</v>
+        <v>0.1026</v>
       </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.2">
@@ -10087,7 +9745,7 @@
         <v>0.15129999999999999</v>
       </c>
       <c r="V6">
-        <v>0.1158</v>
+        <v>0.1893</v>
       </c>
       <c r="W6">
         <v>0.15890000000000001</v>
@@ -10108,13 +9766,7 @@
         <v>0.13589999999999999</v>
       </c>
       <c r="AJ6">
-        <v>0.1724</v>
-      </c>
-      <c r="AP6">
-        <v>9.9900000000000003E-2</v>
-      </c>
-      <c r="AQ6">
-        <v>0.12690000000000001</v>
+        <v>0.19159999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.2">
@@ -10161,7 +9813,7 @@
         <v>0.1401</v>
       </c>
       <c r="V7">
-        <v>0.15540000000000001</v>
+        <v>8.2699999999999996E-2</v>
       </c>
       <c r="W7">
         <v>0.15629999999999999</v>
@@ -10182,13 +9834,7 @@
         <v>0.25679999999999997</v>
       </c>
       <c r="AJ7">
-        <v>0.24970000000000001</v>
-      </c>
-      <c r="AP7">
-        <v>0.15290000000000001</v>
-      </c>
-      <c r="AQ7">
-        <v>0.1222</v>
+        <v>0.23580000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.2">
@@ -10235,7 +9881,7 @@
         <v>0.15040000000000001</v>
       </c>
       <c r="V8">
-        <v>0.13900000000000001</v>
+        <v>0.1087</v>
       </c>
       <c r="W8">
         <v>0.16350000000000001</v>
@@ -10256,13 +9902,7 @@
         <v>0.28050000000000003</v>
       </c>
       <c r="AJ8">
-        <v>0.30690000000000001</v>
-      </c>
-      <c r="AP8">
-        <v>0.1115</v>
-      </c>
-      <c r="AQ8">
-        <v>0.15110000000000001</v>
+        <v>0.3251</v>
       </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.2">
@@ -10309,7 +9949,7 @@
         <v>0.15229999999999999</v>
       </c>
       <c r="V9">
-        <v>0.17660000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="W9">
         <v>0.2044</v>
@@ -10330,13 +9970,7 @@
         <v>0.28789999999999999</v>
       </c>
       <c r="AJ9">
-        <v>0.35639999999999999</v>
-      </c>
-      <c r="AP9">
-        <v>0.11210000000000001</v>
-      </c>
-      <c r="AQ9">
-        <v>0.2127</v>
+        <v>0.3659</v>
       </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.2">
@@ -10380,7 +10014,7 @@
         <v>0.17299999999999999</v>
       </c>
       <c r="V10">
-        <v>0.20030000000000001</v>
+        <v>0.16270000000000001</v>
       </c>
       <c r="W10">
         <v>0.21340000000000001</v>
@@ -10401,13 +10035,7 @@
         <v>0.33189999999999997</v>
       </c>
       <c r="AJ10">
-        <v>0.37419999999999998</v>
-      </c>
-      <c r="AP10">
-        <v>0.1</v>
-      </c>
-      <c r="AQ10">
-        <v>9.9400000000000002E-2</v>
+        <v>0.43149999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.2">
@@ -10451,7 +10079,7 @@
         <v>0.1865</v>
       </c>
       <c r="V11">
-        <v>0.1736</v>
+        <v>0.11</v>
       </c>
       <c r="W11">
         <v>0.18579999999999999</v>
@@ -10472,13 +10100,7 @@
         <v>0.3523</v>
       </c>
       <c r="AJ11">
-        <v>0.38919999999999999</v>
-      </c>
-      <c r="AP11">
-        <v>0.11219999999999999</v>
-      </c>
-      <c r="AQ11">
-        <v>0.23930000000000001</v>
+        <v>0.51119999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.2">
@@ -10522,7 +10144,7 @@
         <v>0.1799</v>
       </c>
       <c r="V12">
-        <v>0.23799999999999999</v>
+        <v>0.28129999999999999</v>
       </c>
       <c r="W12">
         <v>0.19869999999999999</v>
@@ -10543,13 +10165,7 @@
         <v>0.36230000000000001</v>
       </c>
       <c r="AJ12">
-        <v>0.39369999999999999</v>
-      </c>
-      <c r="AP12">
-        <v>0.13139999999999999</v>
-      </c>
-      <c r="AQ12">
-        <v>0.14019999999999999</v>
+        <v>0.52149999999999996</v>
       </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.2">
@@ -10593,7 +10209,7 @@
         <v>0.1951</v>
       </c>
       <c r="V13">
-        <v>0.21310000000000001</v>
+        <v>0.27929999999999999</v>
       </c>
       <c r="W13">
         <v>0.20019999999999999</v>
@@ -10614,13 +10230,7 @@
         <v>0.35630000000000001</v>
       </c>
       <c r="AJ13">
-        <v>0.41310000000000002</v>
-      </c>
-      <c r="AP13">
-        <v>0.14330000000000001</v>
-      </c>
-      <c r="AQ13">
-        <v>0.14749999999999999</v>
+        <v>0.56189999999999996</v>
       </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.2">
@@ -10664,7 +10274,7 @@
         <v>0.189</v>
       </c>
       <c r="V14">
-        <v>0.20399999999999999</v>
+        <v>0.37730000000000002</v>
       </c>
       <c r="W14">
         <v>0.217</v>
@@ -10685,13 +10295,7 @@
         <v>0.38969999999999999</v>
       </c>
       <c r="AJ14">
-        <v>0.4234</v>
-      </c>
-      <c r="AP14">
-        <v>0.1074</v>
-      </c>
-      <c r="AQ14">
-        <v>0.18129999999999999</v>
+        <v>0.57389999999999997</v>
       </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.2">
@@ -10729,7 +10333,7 @@
         <v>0.2011</v>
       </c>
       <c r="V15">
-        <v>0.20710000000000001</v>
+        <v>0.48070000000000002</v>
       </c>
       <c r="W15">
         <v>0.2223</v>
@@ -10750,13 +10354,7 @@
         <v>0.41560000000000002</v>
       </c>
       <c r="AJ15">
-        <v>0.4088</v>
-      </c>
-      <c r="AP15">
-        <v>0.107</v>
-      </c>
-      <c r="AQ15">
-        <v>0.2167</v>
+        <v>0.58430000000000004</v>
       </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.2">
@@ -10794,7 +10392,7 @@
         <v>0.20599999999999999</v>
       </c>
       <c r="V16">
-        <v>0.17829999999999999</v>
+        <v>0.42599999999999999</v>
       </c>
       <c r="W16">
         <v>0.22850000000000001</v>
@@ -10815,16 +10413,10 @@
         <v>0.41160000000000002</v>
       </c>
       <c r="AJ16">
-        <v>0.42320000000000002</v>
-      </c>
-      <c r="AP16">
-        <v>0.10920000000000001</v>
-      </c>
-      <c r="AQ16">
-        <v>0.1636</v>
-      </c>
-    </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.63090000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -10859,7 +10451,7 @@
         <v>0.20749999999999999</v>
       </c>
       <c r="V17">
-        <v>0.1951</v>
+        <v>0.49669999999999997</v>
       </c>
       <c r="W17">
         <v>0.19500000000000001</v>
@@ -10880,16 +10472,10 @@
         <v>0.4178</v>
       </c>
       <c r="AJ17">
-        <v>0.4163</v>
-      </c>
-      <c r="AP17">
-        <v>9.4E-2</v>
-      </c>
-      <c r="AQ17">
-        <v>0.1134</v>
-      </c>
-    </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.65859999999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -10924,7 +10510,7 @@
         <v>0.1981</v>
       </c>
       <c r="V18">
-        <v>0.18690000000000001</v>
+        <v>0.47670000000000001</v>
       </c>
       <c r="W18">
         <v>0.20680000000000001</v>
@@ -10945,16 +10531,10 @@
         <v>0.39760000000000001</v>
       </c>
       <c r="AJ18">
-        <v>0.41749999999999998</v>
-      </c>
-      <c r="AP18">
-        <v>9.4399999999999998E-2</v>
-      </c>
-      <c r="AQ18">
-        <v>0.22459999999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.7198</v>
+      </c>
+    </row>
+    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -10989,7 +10569,7 @@
         <v>0.1741</v>
       </c>
       <c r="V19">
-        <v>0.21990000000000001</v>
+        <v>0.32200000000000001</v>
       </c>
       <c r="W19">
         <v>0.20910000000000001</v>
@@ -11010,16 +10590,10 @@
         <v>0.40649999999999997</v>
       </c>
       <c r="AJ19">
-        <v>0.43090000000000001</v>
-      </c>
-      <c r="AP19">
-        <v>9.5500000000000002E-2</v>
-      </c>
-      <c r="AQ19">
-        <v>0.18859999999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.68969999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -11054,7 +10628,7 @@
         <v>0.17810000000000001</v>
       </c>
       <c r="V20">
-        <v>0.21440000000000001</v>
+        <v>0.50070000000000003</v>
       </c>
       <c r="W20">
         <v>0.22459999999999999</v>
@@ -11075,16 +10649,10 @@
         <v>0.4254</v>
       </c>
       <c r="AJ20">
-        <v>0.42830000000000001</v>
-      </c>
-      <c r="AP20">
-        <v>0.1</v>
-      </c>
-      <c r="AQ20">
-        <v>0.18240000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.66420000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -11119,7 +10687,7 @@
         <v>0.2092</v>
       </c>
       <c r="V21">
-        <v>0.19589999999999999</v>
+        <v>0.48670000000000002</v>
       </c>
       <c r="W21">
         <v>0.21360000000000001</v>
@@ -11140,16 +10708,10 @@
         <v>0.40870000000000001</v>
       </c>
       <c r="AJ21">
-        <v>0.42220000000000002</v>
-      </c>
-      <c r="AP21">
-        <v>0.12280000000000001</v>
-      </c>
-      <c r="AQ21">
-        <v>0.16420000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.59560000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -11184,7 +10746,7 @@
         <v>0.21529999999999999</v>
       </c>
       <c r="V22">
-        <v>0.18890000000000001</v>
+        <v>0.53669999999999995</v>
       </c>
       <c r="W22">
         <v>0.223</v>
@@ -11205,16 +10767,10 @@
         <v>0.42220000000000002</v>
       </c>
       <c r="AJ22">
-        <v>0.42170000000000002</v>
-      </c>
-      <c r="AP22">
-        <v>0.1179</v>
-      </c>
-      <c r="AQ22">
-        <v>0.1358</v>
-      </c>
-    </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.66359999999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -11249,7 +10805,7 @@
         <v>0.19950000000000001</v>
       </c>
       <c r="V23">
-        <v>0.21110000000000001</v>
+        <v>0.49930000000000002</v>
       </c>
       <c r="W23">
         <v>0.2316</v>
@@ -11270,16 +10826,10 @@
         <v>0.43269999999999997</v>
       </c>
       <c r="AJ23">
-        <v>0.4289</v>
-      </c>
-      <c r="AP23">
-        <v>0.12130000000000001</v>
-      </c>
-      <c r="AQ23">
-        <v>0.1356</v>
-      </c>
-    </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.66400000000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -11314,7 +10864,7 @@
         <v>0.21690000000000001</v>
       </c>
       <c r="V24">
-        <v>0.17680000000000001</v>
+        <v>0.51470000000000005</v>
       </c>
       <c r="W24">
         <v>0.22670000000000001</v>
@@ -11331,20 +10881,11 @@
       <c r="AH24" s="1">
         <v>20</v>
       </c>
-      <c r="AI24">
-        <v>0.43240000000000001</v>
-      </c>
       <c r="AJ24">
-        <v>0.43149999999999999</v>
-      </c>
-      <c r="AP24">
-        <v>9.7600000000000006E-2</v>
-      </c>
-      <c r="AQ24">
-        <v>0.2009</v>
-      </c>
-    </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.71460000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -11379,7 +10920,7 @@
         <v>0.2218</v>
       </c>
       <c r="V25">
-        <v>0.1905</v>
+        <v>0.55530000000000002</v>
       </c>
       <c r="W25">
         <v>0.22020000000000001</v>
@@ -11400,16 +10941,10 @@
         <v>0.42120000000000002</v>
       </c>
       <c r="AJ25">
-        <v>0.42859999999999998</v>
-      </c>
-      <c r="AP25">
-        <v>0.12379999999999999</v>
-      </c>
-      <c r="AQ25">
-        <v>0.13009999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.70020000000000004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -11444,7 +10979,7 @@
         <v>0.20899999999999999</v>
       </c>
       <c r="V26">
-        <v>0.2152</v>
+        <v>0.44529999999999997</v>
       </c>
       <c r="W26">
         <v>0.21079999999999999</v>
@@ -11465,16 +11000,10 @@
         <v>0.4345</v>
       </c>
       <c r="AJ26">
-        <v>0.43230000000000002</v>
-      </c>
-      <c r="AP26">
-        <v>0.12529999999999999</v>
-      </c>
-      <c r="AQ26">
-        <v>0.2281</v>
-      </c>
-    </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.67210000000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -11509,7 +11038,7 @@
         <v>0.21490000000000001</v>
       </c>
       <c r="V27">
-        <v>0.2223</v>
+        <v>0.52400000000000002</v>
       </c>
       <c r="W27">
         <v>0.23400000000000001</v>
@@ -11530,16 +11059,10 @@
         <v>0.43</v>
       </c>
       <c r="AJ27">
-        <v>0.43109999999999998</v>
-      </c>
-      <c r="AP27">
-        <v>0.1174</v>
-      </c>
-      <c r="AQ27">
-        <v>0.15490000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.68079999999999996</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -11574,7 +11097,7 @@
         <v>0.21829999999999999</v>
       </c>
       <c r="V28">
-        <v>0.2132</v>
+        <v>0.46129999999999999</v>
       </c>
       <c r="W28">
         <v>0.17319999999999999</v>
@@ -11595,16 +11118,10 @@
         <v>0.43380000000000002</v>
       </c>
       <c r="AJ28">
-        <v>0.42909999999999998</v>
-      </c>
-      <c r="AP28">
-        <v>0.1014</v>
-      </c>
-      <c r="AQ28">
-        <v>0.17849999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.71419999999999995</v>
+      </c>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -11639,7 +11156,7 @@
         <v>0.22090000000000001</v>
       </c>
       <c r="V29">
-        <v>0.216</v>
+        <v>0.47</v>
       </c>
       <c r="W29">
         <v>0.20619999999999999</v>
@@ -11660,16 +11177,10 @@
         <v>0.43440000000000001</v>
       </c>
       <c r="AJ29">
-        <v>0.43380000000000002</v>
-      </c>
-      <c r="AP29">
-        <v>0.10299999999999999</v>
-      </c>
-      <c r="AQ29">
-        <v>0.16250000000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.79949999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -11704,7 +11215,7 @@
         <v>0.22670000000000001</v>
       </c>
       <c r="V30">
-        <v>0.223</v>
+        <v>0.49530000000000002</v>
       </c>
       <c r="W30">
         <v>0.18659999999999999</v>
@@ -11725,16 +11236,10 @@
         <v>0.43190000000000001</v>
       </c>
       <c r="AJ30">
-        <v>0.43409999999999999</v>
-      </c>
-      <c r="AP30">
-        <v>0.1132</v>
-      </c>
-      <c r="AQ30">
-        <v>0.192</v>
-      </c>
-    </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.64339999999999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -11769,7 +11274,7 @@
         <v>0.22589999999999999</v>
       </c>
       <c r="V31">
-        <v>0.21</v>
+        <v>0.44</v>
       </c>
       <c r="W31">
         <v>0.22459999999999999</v>
@@ -11790,16 +11295,10 @@
         <v>0.43090000000000001</v>
       </c>
       <c r="AJ31">
-        <v>0.43120000000000003</v>
-      </c>
-      <c r="AP31">
-        <v>0.1195</v>
-      </c>
-      <c r="AQ31">
-        <v>0.155</v>
-      </c>
-    </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.64349999999999996</v>
+      </c>
+    </row>
+    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -11834,7 +11333,7 @@
         <v>0.23430000000000001</v>
       </c>
       <c r="V32">
-        <v>0.2072</v>
+        <v>0.41670000000000001</v>
       </c>
       <c r="W32">
         <v>0.182</v>
@@ -11855,16 +11354,10 @@
         <v>0.43930000000000002</v>
       </c>
       <c r="AJ32">
-        <v>0.4299</v>
-      </c>
-      <c r="AP32">
-        <v>0.1026</v>
-      </c>
-      <c r="AQ32">
-        <v>0.1197</v>
-      </c>
-    </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.67290000000000005</v>
+      </c>
+    </row>
+    <row r="33" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -11899,7 +11392,7 @@
         <v>0.23219999999999999</v>
       </c>
       <c r="V33">
-        <v>0.221</v>
+        <v>0.54530000000000001</v>
       </c>
       <c r="W33">
         <v>0.17460000000000001</v>
@@ -11920,16 +11413,10 @@
         <v>0.42520000000000002</v>
       </c>
       <c r="AJ33">
-        <v>0.44009999999999999</v>
-      </c>
-      <c r="AP33">
-        <v>0.1197</v>
-      </c>
-      <c r="AQ33">
-        <v>0.1643</v>
-      </c>
-    </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.68289999999999995</v>
+      </c>
+    </row>
+    <row r="34" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -11964,7 +11451,7 @@
         <v>0.2155</v>
       </c>
       <c r="V34">
-        <v>0.2097</v>
+        <v>0.59599999999999997</v>
       </c>
       <c r="W34">
         <v>0.17510000000000001</v>
@@ -11985,16 +11472,10 @@
         <v>0.43590000000000001</v>
       </c>
       <c r="AJ34">
-        <v>0.43409999999999999</v>
-      </c>
-      <c r="AP34">
-        <v>9.7000000000000003E-2</v>
-      </c>
-      <c r="AQ34">
-        <v>0.16839999999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.71830000000000005</v>
+      </c>
+    </row>
+    <row r="35" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -12029,7 +11510,7 @@
         <v>0.2382</v>
       </c>
       <c r="V35">
-        <v>0.19769999999999999</v>
+        <v>0.5393</v>
       </c>
       <c r="W35">
         <v>0.19769999999999999</v>
@@ -12050,16 +11531,10 @@
         <v>0.44319999999999998</v>
       </c>
       <c r="AJ35">
-        <v>0.43590000000000001</v>
-      </c>
-      <c r="AP35">
-        <v>0.1</v>
-      </c>
-      <c r="AQ35">
-        <v>9.8900000000000002E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.63109999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -12094,7 +11569,7 @@
         <v>0.2266</v>
       </c>
       <c r="V36">
-        <v>0.2041</v>
+        <v>0.45729999999999998</v>
       </c>
       <c r="W36">
         <v>0.22109999999999999</v>
@@ -12115,16 +11590,10 @@
         <v>0.43669999999999998</v>
       </c>
       <c r="AJ36">
-        <v>0.44040000000000001</v>
-      </c>
-      <c r="AP36">
-        <v>0.1132</v>
-      </c>
-      <c r="AQ36">
-        <v>0.10879999999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.75749999999999995</v>
+      </c>
+    </row>
+    <row r="37" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -12159,7 +11628,7 @@
         <v>0.21940000000000001</v>
       </c>
       <c r="V37">
-        <v>0.17069999999999999</v>
+        <v>0.35599999999999998</v>
       </c>
       <c r="W37">
         <v>0.23269999999999999</v>
@@ -12180,16 +11649,10 @@
         <v>0.4375</v>
       </c>
       <c r="AJ37">
-        <v>0.44440000000000002</v>
-      </c>
-      <c r="AP37">
-        <v>0.1135</v>
-      </c>
-      <c r="AQ37">
-        <v>0.1454</v>
-      </c>
-    </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.71650000000000003</v>
+      </c>
+    </row>
+    <row r="38" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>34</v>
       </c>
@@ -12224,7 +11687,7 @@
         <v>0.22059999999999999</v>
       </c>
       <c r="V38">
-        <v>0.21390000000000001</v>
+        <v>0.40799999999999997</v>
       </c>
       <c r="W38">
         <v>0.22720000000000001</v>
@@ -12245,16 +11708,10 @@
         <v>0.4375</v>
       </c>
       <c r="AJ38">
-        <v>0.43430000000000002</v>
-      </c>
-      <c r="AP38">
-        <v>0.1462</v>
-      </c>
-      <c r="AQ38">
-        <v>0.1739</v>
-      </c>
-    </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.76029999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>35</v>
       </c>
@@ -12289,7 +11746,7 @@
         <v>0.24129999999999999</v>
       </c>
       <c r="V39">
-        <v>0.20369999999999999</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="W39">
         <v>0.22359999999999999</v>
@@ -12310,16 +11767,10 @@
         <v>0.4254</v>
       </c>
       <c r="AJ39">
-        <v>0.43619999999999998</v>
-      </c>
-      <c r="AP39">
-        <v>0.12820000000000001</v>
-      </c>
-      <c r="AQ39">
-        <v>0.1193</v>
-      </c>
-    </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.68840000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>36</v>
       </c>
@@ -12354,7 +11805,7 @@
         <v>0.2432</v>
       </c>
       <c r="V40">
-        <v>0.21329999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="W40">
         <v>0.22770000000000001</v>
@@ -12375,16 +11826,10 @@
         <v>0.43790000000000001</v>
       </c>
       <c r="AJ40">
-        <v>0.43669999999999998</v>
-      </c>
-      <c r="AP40">
-        <v>0.1</v>
-      </c>
-      <c r="AQ40">
-        <v>0.1462</v>
-      </c>
-    </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.65849999999999997</v>
+      </c>
+    </row>
+    <row r="41" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>37</v>
       </c>
@@ -12419,7 +11864,7 @@
         <v>0.2424</v>
       </c>
       <c r="V41">
-        <v>0.20169999999999999</v>
+        <v>0.51129999999999998</v>
       </c>
       <c r="W41">
         <v>0.21709999999999999</v>
@@ -12440,16 +11885,10 @@
         <v>0.44030000000000002</v>
       </c>
       <c r="AJ41">
-        <v>0.4385</v>
-      </c>
-      <c r="AP41">
-        <v>0.121</v>
-      </c>
-      <c r="AQ41">
-        <v>0.17829999999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.65510000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>38</v>
       </c>
@@ -12484,7 +11923,7 @@
         <v>0.24099999999999999</v>
       </c>
       <c r="V42">
-        <v>0.20780000000000001</v>
+        <v>0.50070000000000003</v>
       </c>
       <c r="W42">
         <v>0.21779999999999999</v>
@@ -12505,16 +11944,10 @@
         <v>0.43009999999999998</v>
       </c>
       <c r="AJ42">
-        <v>0.43919999999999998</v>
-      </c>
-      <c r="AP42">
-        <v>0.1</v>
-      </c>
-      <c r="AQ42">
-        <v>0.14269999999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.67449999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -12549,7 +11982,7 @@
         <v>0.23630000000000001</v>
       </c>
       <c r="V43">
-        <v>0.2208</v>
+        <v>0.44130000000000003</v>
       </c>
       <c r="W43">
         <v>0.20610000000000001</v>
@@ -12570,16 +12003,10 @@
         <v>0.42259999999999998</v>
       </c>
       <c r="AJ43">
-        <v>0.43569999999999998</v>
-      </c>
-      <c r="AP43">
-        <v>0.1129</v>
-      </c>
-      <c r="AQ43">
-        <v>0.15479999999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.76919999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>40</v>
       </c>
@@ -12614,7 +12041,7 @@
         <v>0.23960000000000001</v>
       </c>
       <c r="V44">
-        <v>0.18060000000000001</v>
+        <v>0.52400000000000002</v>
       </c>
       <c r="W44">
         <v>0.2064</v>
@@ -12635,16 +12062,10 @@
         <v>0.43240000000000001</v>
       </c>
       <c r="AJ44">
-        <v>0.43619999999999998</v>
-      </c>
-      <c r="AP44">
-        <v>0.1</v>
-      </c>
-      <c r="AQ44">
-        <v>0.18890000000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.70220000000000005</v>
+      </c>
+    </row>
+    <row r="45" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>41</v>
       </c>
@@ -12679,7 +12100,7 @@
         <v>0.24060000000000001</v>
       </c>
       <c r="V45">
-        <v>0.22500000000000001</v>
+        <v>0.46600000000000003</v>
       </c>
       <c r="W45">
         <v>0.19539999999999999</v>
@@ -12700,16 +12121,10 @@
         <v>0.44359999999999999</v>
       </c>
       <c r="AJ45">
-        <v>0.43990000000000001</v>
-      </c>
-      <c r="AP45">
-        <v>0.14460000000000001</v>
-      </c>
-      <c r="AQ45">
-        <v>0.15959999999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.71479999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>42</v>
       </c>
@@ -12744,7 +12159,7 @@
         <v>0.24740000000000001</v>
       </c>
       <c r="V46">
-        <v>0.2074</v>
+        <v>0.498</v>
       </c>
       <c r="W46">
         <v>0.20449999999999999</v>
@@ -12765,16 +12180,10 @@
         <v>0.44059999999999999</v>
       </c>
       <c r="AJ46">
-        <v>0.43719999999999998</v>
-      </c>
-      <c r="AP46">
-        <v>0.15770000000000001</v>
-      </c>
-      <c r="AQ46">
-        <v>0.19170000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.70299999999999996</v>
+      </c>
+    </row>
+    <row r="47" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>43</v>
       </c>
@@ -12809,7 +12218,7 @@
         <v>0.24079999999999999</v>
       </c>
       <c r="V47">
-        <v>0.17380000000000001</v>
+        <v>0.42270000000000002</v>
       </c>
       <c r="W47">
         <v>0.2165</v>
@@ -12830,16 +12239,10 @@
         <v>0.43780000000000002</v>
       </c>
       <c r="AJ47">
-        <v>0.43619999999999998</v>
-      </c>
-      <c r="AP47">
-        <v>0.1</v>
-      </c>
-      <c r="AQ47">
-        <v>0.1003</v>
-      </c>
-    </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.63449999999999995</v>
+      </c>
+    </row>
+    <row r="48" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>44</v>
       </c>
@@ -12874,7 +12277,7 @@
         <v>0.23980000000000001</v>
       </c>
       <c r="V48">
-        <v>0.18909999999999999</v>
+        <v>0.42930000000000001</v>
       </c>
       <c r="W48">
         <v>0.222</v>
@@ -12895,16 +12298,10 @@
         <v>0.43869999999999998</v>
       </c>
       <c r="AJ48">
-        <v>0.43419999999999997</v>
-      </c>
-      <c r="AP48">
-        <v>0.16059999999999999</v>
-      </c>
-      <c r="AQ48">
-        <v>0.1749</v>
-      </c>
-    </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.68540000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>45</v>
       </c>
@@ -12939,7 +12336,7 @@
         <v>0.24010000000000001</v>
       </c>
       <c r="V49">
-        <v>0.191</v>
+        <v>0.32929999999999998</v>
       </c>
       <c r="W49">
         <v>0.2276</v>
@@ -12960,16 +12357,10 @@
         <v>0.4355</v>
       </c>
       <c r="AJ49">
-        <v>0.438</v>
-      </c>
-      <c r="AP49">
-        <v>0.1216</v>
-      </c>
-      <c r="AQ49">
-        <v>0.13500000000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.79759999999999998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -13004,7 +12395,7 @@
         <v>0.24410000000000001</v>
       </c>
       <c r="V50">
-        <v>0.2155</v>
+        <v>0.43330000000000002</v>
       </c>
       <c r="W50">
         <v>0.215</v>
@@ -13025,16 +12416,10 @@
         <v>0.43409999999999999</v>
       </c>
       <c r="AJ50">
-        <v>0.43909999999999999</v>
-      </c>
-      <c r="AP50">
-        <v>0.1731</v>
-      </c>
-      <c r="AQ50">
-        <v>0.1817</v>
-      </c>
-    </row>
-    <row r="51" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.7177</v>
+      </c>
+    </row>
+    <row r="51" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>47</v>
       </c>
@@ -13069,7 +12454,7 @@
         <v>0.24149999999999999</v>
       </c>
       <c r="V51">
-        <v>0.1429</v>
+        <v>0.38129999999999997</v>
       </c>
       <c r="W51">
         <v>0.18659999999999999</v>
@@ -13090,16 +12475,10 @@
         <v>0.43880000000000002</v>
       </c>
       <c r="AJ51">
-        <v>0.44219999999999998</v>
-      </c>
-      <c r="AP51">
-        <v>0.14749999999999999</v>
-      </c>
-      <c r="AQ51">
-        <v>0.17760000000000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.745</v>
+      </c>
+    </row>
+    <row r="52" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>48</v>
       </c>
@@ -13134,7 +12513,7 @@
         <v>0.246</v>
       </c>
       <c r="V52">
-        <v>0.20119999999999999</v>
+        <v>0.54400000000000004</v>
       </c>
       <c r="W52">
         <v>0.2092</v>
@@ -13155,16 +12534,10 @@
         <v>0.43869999999999998</v>
       </c>
       <c r="AJ52">
-        <v>0.43809999999999999</v>
-      </c>
-      <c r="AP52">
-        <v>0.21210000000000001</v>
-      </c>
-      <c r="AQ52">
-        <v>0.1749</v>
-      </c>
-    </row>
-    <row r="53" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.75460000000000005</v>
+      </c>
+    </row>
+    <row r="53" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>49</v>
       </c>
@@ -13199,7 +12572,7 @@
         <v>0.24360000000000001</v>
       </c>
       <c r="V53">
-        <v>0.1774</v>
+        <v>0.4773</v>
       </c>
       <c r="W53">
         <v>0.21440000000000001</v>
@@ -13220,16 +12593,10 @@
         <v>0.44319999999999998</v>
       </c>
       <c r="AJ53">
-        <v>0.43980000000000002</v>
-      </c>
-      <c r="AP53">
-        <v>0.1404</v>
-      </c>
-      <c r="AQ53">
-        <v>0.15010000000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.71060000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>50</v>
       </c>
@@ -13264,7 +12631,7 @@
         <v>0.24579999999999999</v>
       </c>
       <c r="V54">
-        <v>0.22120000000000001</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="W54">
         <v>0.19889999999999999</v>
@@ -13285,16 +12652,10 @@
         <v>0.44419999999999998</v>
       </c>
       <c r="AJ54">
-        <v>0.44019999999999998</v>
-      </c>
-      <c r="AP54">
-        <v>0.1</v>
-      </c>
-      <c r="AQ54">
-        <v>0.1202</v>
-      </c>
-    </row>
-    <row r="55" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="55" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>51</v>
       </c>
@@ -13329,7 +12690,7 @@
         <v>0.2374</v>
       </c>
       <c r="V55">
-        <v>0.2039</v>
+        <v>0.54069999999999996</v>
       </c>
       <c r="W55">
         <v>0.1585</v>
@@ -13350,16 +12711,10 @@
         <v>0.44090000000000001</v>
       </c>
       <c r="AJ55">
-        <v>0.43509999999999999</v>
-      </c>
-      <c r="AP55">
-        <v>0.1</v>
-      </c>
-      <c r="AQ55">
-        <v>0.21179999999999999</v>
-      </c>
-    </row>
-    <row r="56" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.70389999999999997</v>
+      </c>
+    </row>
+    <row r="56" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>52</v>
       </c>
@@ -13394,7 +12749,7 @@
         <v>0.245</v>
       </c>
       <c r="V56">
-        <v>0.1007</v>
+        <v>0.32</v>
       </c>
       <c r="W56">
         <v>0.19670000000000001</v>
@@ -13415,16 +12770,10 @@
         <v>0.43640000000000001</v>
       </c>
       <c r="AJ56">
-        <v>0.4405</v>
-      </c>
-      <c r="AP56">
-        <v>0.1787</v>
-      </c>
-      <c r="AQ56">
-        <v>0.1187</v>
-      </c>
-    </row>
-    <row r="57" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.69189999999999996</v>
+      </c>
+    </row>
+    <row r="57" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>53</v>
       </c>
@@ -13459,7 +12808,7 @@
         <v>0.2477</v>
       </c>
       <c r="V57">
-        <v>0.13189999999999999</v>
+        <v>0.51670000000000005</v>
       </c>
       <c r="W57">
         <v>0.22140000000000001</v>
@@ -13480,16 +12829,10 @@
         <v>0.43459999999999999</v>
       </c>
       <c r="AJ57">
-        <v>0.4405</v>
-      </c>
-      <c r="AP57">
-        <v>0.14580000000000001</v>
-      </c>
-      <c r="AQ57">
-        <v>0.1288</v>
-      </c>
-    </row>
-    <row r="58" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.74560000000000004</v>
+      </c>
+    </row>
+    <row r="58" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>54</v>
       </c>
@@ -13524,7 +12867,7 @@
         <v>0.2477</v>
       </c>
       <c r="V58">
-        <v>0.18770000000000001</v>
+        <v>0.44269999999999998</v>
       </c>
       <c r="W58">
         <v>0.21560000000000001</v>
@@ -13545,16 +12888,10 @@
         <v>0.44140000000000001</v>
       </c>
       <c r="AJ58">
-        <v>0.44240000000000002</v>
-      </c>
-      <c r="AP58">
-        <v>0.16869999999999999</v>
-      </c>
-      <c r="AQ58">
-        <v>0.15179999999999999</v>
-      </c>
-    </row>
-    <row r="59" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.71179999999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>55</v>
       </c>
@@ -13589,7 +12926,7 @@
         <v>0.248</v>
       </c>
       <c r="V59">
-        <v>0.1903</v>
+        <v>0.56730000000000003</v>
       </c>
       <c r="W59">
         <v>0.2165</v>
@@ -13610,16 +12947,10 @@
         <v>0.43980000000000002</v>
       </c>
       <c r="AJ59">
-        <v>0.44169999999999998</v>
-      </c>
-      <c r="AP59">
-        <v>0.1</v>
-      </c>
-      <c r="AQ59">
-        <v>0.15079999999999999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.75760000000000005</v>
+      </c>
+    </row>
+    <row r="60" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>56</v>
       </c>
@@ -13654,7 +12985,7 @@
         <v>0.24379999999999999</v>
       </c>
       <c r="V60">
-        <v>0.182</v>
+        <v>0.45669999999999999</v>
       </c>
       <c r="W60">
         <v>0.20519999999999999</v>
@@ -13675,16 +13006,10 @@
         <v>0.44169999999999998</v>
       </c>
       <c r="AJ60">
-        <v>0.44219999999999998</v>
-      </c>
-      <c r="AP60">
-        <v>0.12790000000000001</v>
-      </c>
-      <c r="AQ60">
-        <v>0.16619999999999999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.6895</v>
+      </c>
+    </row>
+    <row r="61" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>57</v>
       </c>
@@ -13719,7 +13044,7 @@
         <v>0.24879999999999999</v>
       </c>
       <c r="V61">
-        <v>0.20549999999999999</v>
+        <v>0.53400000000000003</v>
       </c>
       <c r="W61">
         <v>0.21609999999999999</v>
@@ -13740,16 +13065,10 @@
         <v>0.44409999999999999</v>
       </c>
       <c r="AJ61">
-        <v>0.44240000000000002</v>
-      </c>
-      <c r="AP61">
-        <v>0.1275</v>
-      </c>
-      <c r="AQ61">
-        <v>0.13900000000000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.80710000000000004</v>
+      </c>
+    </row>
+    <row r="62" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>58</v>
       </c>
@@ -13784,7 +13103,7 @@
         <v>0.25069999999999998</v>
       </c>
       <c r="V62">
-        <v>0.20580000000000001</v>
+        <v>0.47470000000000001</v>
       </c>
       <c r="W62">
         <v>0.2049</v>
@@ -13805,16 +13124,10 @@
         <v>0.4471</v>
       </c>
       <c r="AJ62">
-        <v>0.4415</v>
-      </c>
-      <c r="AP62">
-        <v>0.10009999999999999</v>
-      </c>
-      <c r="AQ62">
-        <v>0.22750000000000001</v>
-      </c>
-    </row>
-    <row r="63" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.68279999999999996</v>
+      </c>
+    </row>
+    <row r="63" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>59</v>
       </c>
@@ -13849,7 +13162,7 @@
         <v>0.24479999999999999</v>
       </c>
       <c r="V63">
-        <v>0.18540000000000001</v>
+        <v>0.49869999999999998</v>
       </c>
       <c r="W63">
         <v>0.21390000000000001</v>
@@ -13870,16 +13183,10 @@
         <v>0.44019999999999998</v>
       </c>
       <c r="AJ63">
-        <v>0.44059999999999999</v>
-      </c>
-      <c r="AP63">
-        <v>0.1215</v>
-      </c>
-      <c r="AQ63">
-        <v>0.17860000000000001</v>
-      </c>
-    </row>
-    <row r="64" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.74950000000000006</v>
+      </c>
+    </row>
+    <row r="64" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>60</v>
       </c>
@@ -13914,7 +13221,7 @@
         <v>0.24310000000000001</v>
       </c>
       <c r="V64">
-        <v>0.20649999999999999</v>
+        <v>0.36470000000000002</v>
       </c>
       <c r="W64">
         <v>0.18729999999999999</v>
@@ -13935,16 +13242,10 @@
         <v>0.44109999999999999</v>
       </c>
       <c r="AJ64">
-        <v>0.44800000000000001</v>
-      </c>
-      <c r="AP64">
-        <v>0.1</v>
-      </c>
-      <c r="AQ64">
-        <v>0.22839999999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.77459999999999996</v>
+      </c>
+    </row>
+    <row r="65" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>61</v>
       </c>
@@ -13979,7 +13280,7 @@
         <v>0.23830000000000001</v>
       </c>
       <c r="V65">
-        <v>0.15759999999999999</v>
+        <v>0.26469999999999999</v>
       </c>
       <c r="W65">
         <v>0.21149999999999999</v>
@@ -14000,16 +13301,10 @@
         <v>0.44379999999999997</v>
       </c>
       <c r="AJ65">
-        <v>0.44419999999999998</v>
-      </c>
-      <c r="AP65">
-        <v>0.1</v>
-      </c>
-      <c r="AQ65">
-        <v>0.14649999999999999</v>
-      </c>
-    </row>
-    <row r="66" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.71509999999999996</v>
+      </c>
+    </row>
+    <row r="66" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>62</v>
       </c>
@@ -14044,7 +13339,7 @@
         <v>0.24160000000000001</v>
       </c>
       <c r="V66">
-        <v>0.1973</v>
+        <v>0.47870000000000001</v>
       </c>
       <c r="W66">
         <v>0.21460000000000001</v>
@@ -14065,16 +13360,10 @@
         <v>0.45069999999999999</v>
       </c>
       <c r="AJ66">
-        <v>0.43719999999999998</v>
-      </c>
-      <c r="AP66">
-        <v>0.14380000000000001</v>
-      </c>
-      <c r="AQ66">
-        <v>0.1106</v>
-      </c>
-    </row>
-    <row r="67" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.81789999999999996</v>
+      </c>
+    </row>
+    <row r="67" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>63</v>
       </c>
@@ -14109,7 +13398,7 @@
         <v>0.25130000000000002</v>
       </c>
       <c r="V67">
-        <v>0.2046</v>
+        <v>0.51470000000000005</v>
       </c>
       <c r="W67">
         <v>0.22620000000000001</v>
@@ -14130,16 +13419,10 @@
         <v>0.44779999999999998</v>
       </c>
       <c r="AJ67">
-        <v>0.44429999999999997</v>
-      </c>
-      <c r="AP67">
-        <v>0.15390000000000001</v>
-      </c>
-      <c r="AQ67">
-        <v>0.1515</v>
-      </c>
-    </row>
-    <row r="68" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.67359999999999998</v>
+      </c>
+    </row>
+    <row r="68" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>64</v>
       </c>
@@ -14174,7 +13457,7 @@
         <v>0.2445</v>
       </c>
       <c r="V68">
-        <v>0.1832</v>
+        <v>0.502</v>
       </c>
       <c r="W68">
         <v>0.2155</v>
@@ -14195,16 +13478,10 @@
         <v>0.44350000000000001</v>
       </c>
       <c r="AJ68">
-        <v>0.44119999999999998</v>
-      </c>
-      <c r="AP68">
-        <v>0.1323</v>
-      </c>
-      <c r="AQ68">
-        <v>0.1004</v>
-      </c>
-    </row>
-    <row r="69" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.8175</v>
+      </c>
+    </row>
+    <row r="69" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>65</v>
       </c>
@@ -14239,7 +13516,7 @@
         <v>0.24429999999999999</v>
       </c>
       <c r="V69">
-        <v>0.1414</v>
+        <v>0.29270000000000002</v>
       </c>
       <c r="W69">
         <v>0.2268</v>
@@ -14260,16 +13537,10 @@
         <v>0.44469999999999998</v>
       </c>
       <c r="AJ69">
-        <v>0.44319999999999998</v>
-      </c>
-      <c r="AP69">
-        <v>0.12939999999999999</v>
-      </c>
-      <c r="AQ69">
-        <v>0.15670000000000001</v>
-      </c>
-    </row>
-    <row r="70" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.76190000000000002</v>
+      </c>
+    </row>
+    <row r="70" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>66</v>
       </c>
@@ -14304,7 +13575,7 @@
         <v>0.2467</v>
       </c>
       <c r="V70">
-        <v>0.16209999999999999</v>
+        <v>0.44069999999999998</v>
       </c>
       <c r="W70">
         <v>0.224</v>
@@ -14325,16 +13596,10 @@
         <v>0.44309999999999999</v>
       </c>
       <c r="AJ70">
-        <v>0.4395</v>
-      </c>
-      <c r="AP70">
-        <v>0.155</v>
-      </c>
-      <c r="AQ70">
-        <v>9.8599999999999993E-2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.66539999999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>67</v>
       </c>
@@ -14369,7 +13634,7 @@
         <v>0.2389</v>
       </c>
       <c r="V71">
-        <v>0.1618</v>
+        <v>0.48470000000000002</v>
       </c>
       <c r="W71">
         <v>0.22670000000000001</v>
@@ -14390,16 +13655,10 @@
         <v>0.4365</v>
       </c>
       <c r="AJ71">
-        <v>0.43640000000000001</v>
-      </c>
-      <c r="AP71">
-        <v>0.13469999999999999</v>
-      </c>
-      <c r="AQ71">
-        <v>0.1812</v>
-      </c>
-    </row>
-    <row r="72" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.72970000000000002</v>
+      </c>
+    </row>
+    <row r="72" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>68</v>
       </c>
@@ -14434,7 +13693,7 @@
         <v>0.2482</v>
       </c>
       <c r="V72">
-        <v>0.17899999999999999</v>
+        <v>0.32200000000000001</v>
       </c>
       <c r="W72">
         <v>0.2172</v>
@@ -14455,16 +13714,10 @@
         <v>0.44019999999999998</v>
       </c>
       <c r="AJ72">
-        <v>0.44359999999999999</v>
-      </c>
-      <c r="AP72">
-        <v>0.16420000000000001</v>
-      </c>
-      <c r="AQ72">
-        <v>0.22650000000000001</v>
-      </c>
-    </row>
-    <row r="73" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.75800000000000001</v>
+      </c>
+    </row>
+    <row r="73" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>69</v>
       </c>
@@ -14499,7 +13752,7 @@
         <v>0.25190000000000001</v>
       </c>
       <c r="V73">
-        <v>0.1628</v>
+        <v>0.34799999999999998</v>
       </c>
       <c r="W73">
         <v>0.19470000000000001</v>
@@ -14520,16 +13773,10 @@
         <v>0.44169999999999998</v>
       </c>
       <c r="AJ73">
-        <v>0.44040000000000001</v>
-      </c>
-      <c r="AP73">
-        <v>0.1646</v>
-      </c>
-      <c r="AQ73">
-        <v>0.20799999999999999</v>
-      </c>
-    </row>
-    <row r="74" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.72299999999999998</v>
+      </c>
+    </row>
+    <row r="74" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>70</v>
       </c>
@@ -14564,7 +13811,7 @@
         <v>0.24970000000000001</v>
       </c>
       <c r="V74">
-        <v>0.19270000000000001</v>
+        <v>0.47599999999999998</v>
       </c>
       <c r="W74">
         <v>0.19769999999999999</v>
@@ -14585,16 +13832,10 @@
         <v>0.43230000000000002</v>
       </c>
       <c r="AJ74">
-        <v>0.44390000000000002</v>
-      </c>
-      <c r="AP74">
-        <v>0.15090000000000001</v>
-      </c>
-      <c r="AQ74">
-        <v>0.12939999999999999</v>
-      </c>
-    </row>
-    <row r="75" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.70269999999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>71</v>
       </c>
@@ -14629,7 +13870,7 @@
         <v>0.25059999999999999</v>
       </c>
       <c r="V75">
-        <v>0.20910000000000001</v>
+        <v>0.49070000000000003</v>
       </c>
       <c r="W75">
         <v>0.2036</v>
@@ -14650,16 +13891,10 @@
         <v>0.43969999999999998</v>
       </c>
       <c r="AJ75">
-        <v>0.44259999999999999</v>
-      </c>
-      <c r="AP75">
-        <v>0.1643</v>
-      </c>
-      <c r="AQ75">
-        <v>0.1318</v>
-      </c>
-    </row>
-    <row r="76" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.72330000000000005</v>
+      </c>
+    </row>
+    <row r="76" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>72</v>
       </c>
@@ -14694,7 +13929,7 @@
         <v>0.24840000000000001</v>
       </c>
       <c r="V76">
-        <v>0.18970000000000001</v>
+        <v>0.45669999999999999</v>
       </c>
       <c r="W76">
         <v>0.2122</v>
@@ -14715,16 +13950,10 @@
         <v>0.4451</v>
       </c>
       <c r="AJ76">
-        <v>0.44069999999999998</v>
-      </c>
-      <c r="AP76">
-        <v>0.1</v>
-      </c>
-      <c r="AQ76">
-        <v>0.20280000000000001</v>
-      </c>
-    </row>
-    <row r="77" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.57830000000000004</v>
+      </c>
+    </row>
+    <row r="77" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>73</v>
       </c>
@@ -14759,7 +13988,7 @@
         <v>0.2442</v>
       </c>
       <c r="V77">
-        <v>0.18640000000000001</v>
+        <v>0.50600000000000001</v>
       </c>
       <c r="W77">
         <v>0.2276</v>
@@ -14780,16 +14009,10 @@
         <v>0.43869999999999998</v>
       </c>
       <c r="AJ77">
-        <v>0.44190000000000002</v>
-      </c>
-      <c r="AP77">
-        <v>0.1346</v>
-      </c>
-      <c r="AQ77">
-        <v>0.17319999999999999</v>
-      </c>
-    </row>
-    <row r="78" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.73980000000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>74</v>
       </c>
@@ -14824,7 +14047,7 @@
         <v>0.2457</v>
       </c>
       <c r="V78">
-        <v>0.19850000000000001</v>
+        <v>0.46329999999999999</v>
       </c>
       <c r="W78">
         <v>0.2059</v>
@@ -14845,16 +14068,10 @@
         <v>0.44629999999999997</v>
       </c>
       <c r="AJ78">
-        <v>0.44069999999999998</v>
-      </c>
-      <c r="AP78">
-        <v>0.14019999999999999</v>
-      </c>
-      <c r="AQ78">
-        <v>0.14910000000000001</v>
-      </c>
-    </row>
-    <row r="79" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="79" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>75</v>
       </c>
@@ -14889,7 +14106,7 @@
         <v>0.25019999999999998</v>
       </c>
       <c r="V79">
-        <v>0.184</v>
+        <v>0.51870000000000005</v>
       </c>
       <c r="W79">
         <v>0.20810000000000001</v>
@@ -14910,16 +14127,10 @@
         <v>0.44400000000000001</v>
       </c>
       <c r="AJ79">
-        <v>0.4405</v>
-      </c>
-      <c r="AP79">
-        <v>0.1613</v>
-      </c>
-      <c r="AQ79">
-        <v>0.2077</v>
-      </c>
-    </row>
-    <row r="80" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.66139999999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>76</v>
       </c>
@@ -14954,7 +14165,7 @@
         <v>0.25019999999999998</v>
       </c>
       <c r="V80">
-        <v>0.18959999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="W80">
         <v>0.2102</v>
@@ -14975,16 +14186,10 @@
         <v>0.44590000000000002</v>
       </c>
       <c r="AJ80">
-        <v>0.44290000000000002</v>
-      </c>
-      <c r="AP80">
-        <v>0.13800000000000001</v>
-      </c>
-      <c r="AQ80">
-        <v>0.27989999999999998</v>
-      </c>
-    </row>
-    <row r="81" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.63439999999999996</v>
+      </c>
+    </row>
+    <row r="81" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>77</v>
       </c>
@@ -15019,7 +14224,7 @@
         <v>0.25019999999999998</v>
       </c>
       <c r="V81">
-        <v>0.18490000000000001</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="W81">
         <v>0.2147</v>
@@ -15040,16 +14245,10 @@
         <v>0.4501</v>
       </c>
       <c r="AJ81">
-        <v>0.4456</v>
-      </c>
-      <c r="AP81">
-        <v>0.1527</v>
-      </c>
-      <c r="AQ81">
-        <v>0.1641</v>
-      </c>
-    </row>
-    <row r="82" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.73080000000000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>78</v>
       </c>
@@ -15084,7 +14283,7 @@
         <v>0.25159999999999999</v>
       </c>
       <c r="V82">
-        <v>0.20619999999999999</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="W82">
         <v>0.1915</v>
@@ -15105,16 +14304,10 @@
         <v>0.443</v>
       </c>
       <c r="AJ82">
-        <v>0.44629999999999997</v>
-      </c>
-      <c r="AP82">
-        <v>0.13469999999999999</v>
-      </c>
-      <c r="AQ82">
-        <v>0.1207</v>
-      </c>
-    </row>
-    <row r="83" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.69210000000000005</v>
+      </c>
+    </row>
+    <row r="83" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>79</v>
       </c>
@@ -15149,7 +14342,7 @@
         <v>0.24410000000000001</v>
       </c>
       <c r="V83">
-        <v>0.2059</v>
+        <v>0.4733</v>
       </c>
       <c r="W83">
         <v>0.14699999999999999</v>
@@ -15170,16 +14363,10 @@
         <v>0.43909999999999999</v>
       </c>
       <c r="AJ83">
-        <v>0.44850000000000001</v>
-      </c>
-      <c r="AP83">
-        <v>0.11700000000000001</v>
-      </c>
-      <c r="AQ83">
-        <v>0.22939999999999999</v>
-      </c>
-    </row>
-    <row r="84" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.64639999999999997</v>
+      </c>
+    </row>
+    <row r="84" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>80</v>
       </c>
@@ -15214,7 +14401,7 @@
         <v>0.2399</v>
       </c>
       <c r="V84">
-        <v>0.20100000000000001</v>
+        <v>0.47670000000000001</v>
       </c>
       <c r="W84">
         <v>0.1002</v>
@@ -15235,16 +14422,10 @@
         <v>0.43719999999999998</v>
       </c>
       <c r="AJ84">
-        <v>0.44440000000000002</v>
-      </c>
-      <c r="AP84">
-        <v>0.11119999999999999</v>
-      </c>
-      <c r="AQ84">
-        <v>0.1012</v>
-      </c>
-    </row>
-    <row r="85" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.70069999999999999</v>
+      </c>
+    </row>
+    <row r="85" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>81</v>
       </c>
@@ -15279,7 +14460,7 @@
         <v>0.25</v>
       </c>
       <c r="V85">
-        <v>0.1971</v>
+        <v>0.48</v>
       </c>
       <c r="W85">
         <v>0.123</v>
@@ -15300,16 +14481,10 @@
         <v>0.43980000000000002</v>
       </c>
       <c r="AJ85">
-        <v>0.4456</v>
-      </c>
-      <c r="AP85">
-        <v>0.1</v>
-      </c>
-      <c r="AQ85">
-        <v>0.1111</v>
-      </c>
-    </row>
-    <row r="86" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.68359999999999999</v>
+      </c>
+    </row>
+    <row r="86" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>82</v>
       </c>
@@ -15344,7 +14519,7 @@
         <v>0.25269999999999998</v>
       </c>
       <c r="V86">
-        <v>0.2046</v>
+        <v>0.48070000000000002</v>
       </c>
       <c r="W86">
         <v>0.1628</v>
@@ -15365,16 +14540,10 @@
         <v>0.4451</v>
       </c>
       <c r="AJ86">
-        <v>0.44550000000000001</v>
-      </c>
-      <c r="AP86">
-        <v>0.1444</v>
-      </c>
-      <c r="AQ86">
-        <v>0.14269999999999999</v>
-      </c>
-    </row>
-    <row r="87" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.70899999999999996</v>
+      </c>
+    </row>
+    <row r="87" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>83</v>
       </c>
@@ -15409,7 +14578,7 @@
         <v>0.25569999999999998</v>
       </c>
       <c r="V87">
-        <v>0.21079999999999999</v>
+        <v>0.52800000000000002</v>
       </c>
       <c r="W87">
         <v>0.15890000000000001</v>
@@ -15430,16 +14599,10 @@
         <v>0.44800000000000001</v>
       </c>
       <c r="AJ87">
-        <v>0.44119999999999998</v>
-      </c>
-      <c r="AP87">
-        <v>0.11269999999999999</v>
-      </c>
-      <c r="AQ87">
-        <v>0.13100000000000001</v>
-      </c>
-    </row>
-    <row r="88" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.62080000000000002</v>
+      </c>
+    </row>
+    <row r="88" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>84</v>
       </c>
@@ -15474,7 +14637,7 @@
         <v>0.25340000000000001</v>
       </c>
       <c r="V88">
-        <v>0.19339999999999999</v>
+        <v>0.42070000000000002</v>
       </c>
       <c r="W88">
         <v>0.1055</v>
@@ -15495,16 +14658,10 @@
         <v>0.4299</v>
       </c>
       <c r="AJ88">
-        <v>0.44040000000000001</v>
-      </c>
-      <c r="AP88">
-        <v>0.13100000000000001</v>
-      </c>
-      <c r="AQ88">
-        <v>0.14979999999999999</v>
-      </c>
-    </row>
-    <row r="89" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.58940000000000003</v>
+      </c>
+    </row>
+    <row r="89" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>85</v>
       </c>
@@ -15539,7 +14696,7 @@
         <v>0.24540000000000001</v>
       </c>
       <c r="V89">
-        <v>0.15359999999999999</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="W89">
         <v>0.1656</v>
@@ -15560,16 +14717,10 @@
         <v>0.4279</v>
       </c>
       <c r="AJ89">
-        <v>0.44090000000000001</v>
-      </c>
-      <c r="AP89">
-        <v>0.18329999999999999</v>
-      </c>
-      <c r="AQ89">
-        <v>0.20039999999999999</v>
-      </c>
-    </row>
-    <row r="90" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.69030000000000002</v>
+      </c>
+    </row>
+    <row r="90" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>86</v>
       </c>
@@ -15604,7 +14755,7 @@
         <v>0.25269999999999998</v>
       </c>
       <c r="V90">
-        <v>0.18049999999999999</v>
+        <v>0.48930000000000001</v>
       </c>
       <c r="W90">
         <v>0.1789</v>
@@ -15625,16 +14776,10 @@
         <v>0.43840000000000001</v>
       </c>
       <c r="AJ90">
-        <v>0.44140000000000001</v>
-      </c>
-      <c r="AP90">
-        <v>0.23269999999999999</v>
-      </c>
-      <c r="AQ90">
-        <v>0.1429</v>
-      </c>
-    </row>
-    <row r="91" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.77159999999999995</v>
+      </c>
+    </row>
+    <row r="91" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>87</v>
       </c>
@@ -15669,7 +14814,7 @@
         <v>0.2477</v>
       </c>
       <c r="V91">
-        <v>0.16500000000000001</v>
+        <v>0.40600000000000003</v>
       </c>
       <c r="W91">
         <v>0.18140000000000001</v>
@@ -15690,16 +14835,10 @@
         <v>0.44579999999999997</v>
       </c>
       <c r="AJ91">
-        <v>0.4415</v>
-      </c>
-      <c r="AP91">
-        <v>0.23269999999999999</v>
-      </c>
-      <c r="AQ91">
-        <v>0.19270000000000001</v>
-      </c>
-    </row>
-    <row r="92" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.75170000000000003</v>
+      </c>
+    </row>
+    <row r="92" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>88</v>
       </c>
@@ -15734,7 +14873,7 @@
         <v>0.24970000000000001</v>
       </c>
       <c r="V92">
-        <v>0.17019999999999999</v>
+        <v>0.37469999999999998</v>
       </c>
       <c r="W92">
         <v>0.14680000000000001</v>
@@ -15755,16 +14894,10 @@
         <v>0.44740000000000002</v>
       </c>
       <c r="AJ92">
-        <v>0.44109999999999999</v>
-      </c>
-      <c r="AP92">
-        <v>0.1</v>
-      </c>
-      <c r="AQ92">
-        <v>0.1096</v>
-      </c>
-    </row>
-    <row r="93" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.67490000000000006</v>
+      </c>
+    </row>
+    <row r="93" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>89</v>
       </c>
@@ -15799,7 +14932,7 @@
         <v>0.25119999999999998</v>
       </c>
       <c r="V93">
-        <v>0.20730000000000001</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="W93">
         <v>0.18640000000000001</v>
@@ -15820,16 +14953,10 @@
         <v>0.44900000000000001</v>
       </c>
       <c r="AJ93">
-        <v>0.44790000000000002</v>
-      </c>
-      <c r="AP93">
-        <v>0.19489999999999999</v>
-      </c>
-      <c r="AQ93">
-        <v>0.13220000000000001</v>
-      </c>
-    </row>
-    <row r="94" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.67379999999999995</v>
+      </c>
+    </row>
+    <row r="94" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>90</v>
       </c>
@@ -15864,7 +14991,7 @@
         <v>0.2404</v>
       </c>
       <c r="V94">
-        <v>0.1895</v>
+        <v>0.38669999999999999</v>
       </c>
       <c r="W94">
         <v>0.20610000000000001</v>
@@ -15885,16 +15012,10 @@
         <v>0.44929999999999998</v>
       </c>
       <c r="AJ94">
-        <v>0.4481</v>
-      </c>
-      <c r="AP94">
-        <v>0.1447</v>
-      </c>
-      <c r="AQ94">
-        <v>0.15340000000000001</v>
-      </c>
-    </row>
-    <row r="95" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.78300000000000003</v>
+      </c>
+    </row>
+    <row r="95" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>91</v>
       </c>
@@ -15929,7 +15050,7 @@
         <v>0.24840000000000001</v>
       </c>
       <c r="V95">
-        <v>0.1719</v>
+        <v>0.34799999999999998</v>
       </c>
       <c r="W95">
         <v>0.1961</v>
@@ -15950,16 +15071,10 @@
         <v>0.44269999999999998</v>
       </c>
       <c r="AJ95">
-        <v>0.44350000000000001</v>
-      </c>
-      <c r="AP95">
-        <v>0.1</v>
-      </c>
-      <c r="AQ95">
-        <v>0.1532</v>
-      </c>
-    </row>
-    <row r="96" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.7157</v>
+      </c>
+    </row>
+    <row r="96" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>92</v>
       </c>
@@ -15994,7 +15109,7 @@
         <v>0.25069999999999998</v>
       </c>
       <c r="V96">
-        <v>0.1865</v>
+        <v>0.44929999999999998</v>
       </c>
       <c r="W96">
         <v>0.18690000000000001</v>
@@ -16015,16 +15130,10 @@
         <v>0.44130000000000003</v>
       </c>
       <c r="AJ96">
-        <v>0.44219999999999998</v>
-      </c>
-      <c r="AP96">
-        <v>0.1</v>
-      </c>
-      <c r="AQ96">
-        <v>0.11609999999999999</v>
-      </c>
-    </row>
-    <row r="97" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.70950000000000002</v>
+      </c>
+    </row>
+    <row r="97" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>93</v>
       </c>
@@ -16059,7 +15168,7 @@
         <v>0.2515</v>
       </c>
       <c r="V97">
-        <v>0.14610000000000001</v>
+        <v>0.3533</v>
       </c>
       <c r="W97">
         <v>0.14130000000000001</v>
@@ -16080,16 +15189,10 @@
         <v>0.43790000000000001</v>
       </c>
       <c r="AJ97">
-        <v>0.4471</v>
-      </c>
-      <c r="AP97">
-        <v>0.1</v>
-      </c>
-      <c r="AQ97">
-        <v>0.2281</v>
-      </c>
-    </row>
-    <row r="98" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.66690000000000005</v>
+      </c>
+    </row>
+    <row r="98" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>94</v>
       </c>
@@ -16124,7 +15227,7 @@
         <v>0.24199999999999999</v>
       </c>
       <c r="V98">
-        <v>0.1462</v>
+        <v>0.41870000000000002</v>
       </c>
       <c r="W98">
         <v>0.16600000000000001</v>
@@ -16145,16 +15248,10 @@
         <v>0.43740000000000001</v>
       </c>
       <c r="AJ98">
-        <v>0.44540000000000002</v>
-      </c>
-      <c r="AP98">
-        <v>0.21390000000000001</v>
-      </c>
-      <c r="AQ98">
-        <v>0.13289999999999999</v>
-      </c>
-    </row>
-    <row r="99" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.74470000000000003</v>
+      </c>
+    </row>
+    <row r="99" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>95</v>
       </c>
@@ -16189,7 +15286,7 @@
         <v>0.25309999999999999</v>
       </c>
       <c r="V99">
-        <v>0.1822</v>
+        <v>0.26069999999999999</v>
       </c>
       <c r="W99">
         <v>0.1646</v>
@@ -16210,16 +15307,10 @@
         <v>0.4365</v>
       </c>
       <c r="AJ99">
-        <v>0.44740000000000002</v>
-      </c>
-      <c r="AP99">
-        <v>0.22220000000000001</v>
-      </c>
-      <c r="AQ99">
-        <v>0.13669999999999999</v>
-      </c>
-    </row>
-    <row r="100" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.64900000000000002</v>
+      </c>
+    </row>
+    <row r="100" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>96</v>
       </c>
@@ -16254,7 +15345,7 @@
         <v>0.246</v>
       </c>
       <c r="V100">
-        <v>0.2046</v>
+        <v>0.33400000000000002</v>
       </c>
       <c r="W100">
         <v>0.1951</v>
@@ -16275,16 +15366,10 @@
         <v>0.4451</v>
       </c>
       <c r="AJ100">
-        <v>0.44369999999999998</v>
-      </c>
-      <c r="AP100">
-        <v>0.1079</v>
-      </c>
-      <c r="AQ100">
-        <v>0.10100000000000001</v>
-      </c>
-    </row>
-    <row r="101" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.66869999999999996</v>
+      </c>
+    </row>
+    <row r="101" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>97</v>
       </c>
@@ -16319,7 +15404,7 @@
         <v>0.24410000000000001</v>
       </c>
       <c r="V101">
-        <v>0.15090000000000001</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="W101">
         <v>0.18859999999999999</v>
@@ -16340,16 +15425,10 @@
         <v>0.43809999999999999</v>
       </c>
       <c r="AJ101">
-        <v>0.44579999999999997</v>
-      </c>
-      <c r="AP101">
-        <v>0.1193</v>
-      </c>
-      <c r="AQ101">
-        <v>0.14630000000000001</v>
-      </c>
-    </row>
-    <row r="102" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.7873</v>
+      </c>
+    </row>
+    <row r="102" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>98</v>
       </c>
@@ -16384,7 +15463,7 @@
         <v>0.24410000000000001</v>
       </c>
       <c r="V102">
-        <v>0.20810000000000001</v>
+        <v>0.374</v>
       </c>
       <c r="W102">
         <v>0.186</v>
@@ -16405,16 +15484,10 @@
         <v>0.43969999999999998</v>
       </c>
       <c r="AJ102">
-        <v>0.44290000000000002</v>
-      </c>
-      <c r="AP102">
-        <v>0.1</v>
-      </c>
-      <c r="AQ102">
-        <v>0.17419999999999999</v>
-      </c>
-    </row>
-    <row r="103" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.67920000000000003</v>
+      </c>
+    </row>
+    <row r="103" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>99</v>
       </c>
@@ -16449,7 +15522,7 @@
         <v>0.24629999999999999</v>
       </c>
       <c r="V103">
-        <v>0.17730000000000001</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="W103">
         <v>0.15590000000000001</v>
@@ -16470,16 +15543,10 @@
         <v>0.44450000000000001</v>
       </c>
       <c r="AJ103">
-        <v>0.44230000000000003</v>
-      </c>
-      <c r="AP103">
-        <v>0.1046</v>
-      </c>
-      <c r="AQ103">
-        <v>0.1648</v>
-      </c>
-    </row>
-    <row r="104" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.75319999999999998</v>
+      </c>
+    </row>
+    <row r="104" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>100</v>
       </c>
@@ -16514,7 +15581,7 @@
         <v>0.248</v>
       </c>
       <c r="V104">
-        <v>0.18060000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="W104">
         <v>0.17030000000000001</v>
@@ -16535,20 +15602,14 @@
         <v>0.44600000000000001</v>
       </c>
       <c r="AJ104">
-        <v>0.4446</v>
-      </c>
-      <c r="AP104">
-        <v>0.1046</v>
-      </c>
-      <c r="AQ104">
-        <v>0.1593</v>
-      </c>
-    </row>
-    <row r="105" spans="1:43" x14ac:dyDescent="0.2">
+        <v>0.69420000000000004</v>
+      </c>
+    </row>
+    <row r="105" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AD105" s="9"/>
       <c r="AE105" s="9"/>
     </row>
-    <row r="106" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>23</v>
       </c>
@@ -16561,7 +15622,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="107" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>24</v>
       </c>
@@ -16574,7 +15635,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="108" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>1</v>
       </c>
@@ -16634,11 +15695,8 @@
       <c r="AJ108">
         <v>0.8666666666666667</v>
       </c>
-      <c r="AP108">
-        <v>0.93333333333333335</v>
-      </c>
-    </row>
-    <row r="109" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="109" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>2</v>
       </c>
@@ -16698,11 +15756,8 @@
       <c r="AJ109">
         <v>0.6</v>
       </c>
-      <c r="AP109">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="110" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>3</v>
       </c>
@@ -16762,11 +15817,8 @@
       <c r="AJ110">
         <v>0.8</v>
       </c>
-      <c r="AP110">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="111" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="111" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>4</v>
       </c>
@@ -16826,11 +15878,8 @@
       <c r="AJ111">
         <v>0.6</v>
       </c>
-      <c r="AP111">
-        <v>0.81818181818181823</v>
-      </c>
-    </row>
-    <row r="112" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="112" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>5</v>
       </c>
@@ -16890,11 +15939,8 @@
       <c r="AJ112">
         <v>0.6</v>
       </c>
-      <c r="AP112">
-        <v>0.81818181818181823</v>
-      </c>
-    </row>
-    <row r="113" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="113" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>6</v>
       </c>
@@ -16951,11 +15997,8 @@
       <c r="AJ113">
         <v>0.53333333333333333</v>
       </c>
-      <c r="AP113">
-        <v>0.72727272727272729</v>
-      </c>
-    </row>
-    <row r="114" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="114" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>7</v>
       </c>
@@ -17012,11 +16055,8 @@
       <c r="AJ114">
         <v>0.4</v>
       </c>
-      <c r="AP114">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="115" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="115" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>8</v>
       </c>
@@ -17073,11 +16113,8 @@
       <c r="AJ115">
         <v>0.53333333333333333</v>
       </c>
-      <c r="AP115">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="116" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="116" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>9</v>
       </c>
@@ -17134,11 +16171,8 @@
       <c r="AJ116">
         <v>0.53333333333333333</v>
       </c>
-      <c r="AP116">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="117" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="117" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>10</v>
       </c>
@@ -17195,11 +16229,8 @@
       <c r="AJ117">
         <v>0.6</v>
       </c>
-      <c r="AP117">
-        <v>0.72727272727272729</v>
-      </c>
-    </row>
-    <row r="118" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="118" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>11</v>
       </c>
@@ -17250,11 +16281,8 @@
       <c r="AJ118">
         <v>0.66666666666666663</v>
       </c>
-      <c r="AP118">
-        <v>0.77777777777777779</v>
-      </c>
-    </row>
-    <row r="119" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="119" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>12</v>
       </c>
@@ -17305,11 +16333,8 @@
       <c r="AJ119">
         <v>0.66666666666666663</v>
       </c>
-      <c r="AP119">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="120" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="120" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>13</v>
       </c>
@@ -17360,11 +16385,8 @@
       <c r="AJ120">
         <v>0.53333333333333333</v>
       </c>
-      <c r="AP120">
-        <v>0.72727272727272729</v>
-      </c>
-    </row>
-    <row r="121" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="121" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>14</v>
       </c>
@@ -17415,11 +16437,8 @@
       <c r="AJ121">
         <v>0.53333333333333333</v>
       </c>
-      <c r="AP121">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="122" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="122" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>15</v>
       </c>
@@ -17470,11 +16489,8 @@
       <c r="AJ122">
         <v>0.66666666666666663</v>
       </c>
-      <c r="AP122">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="123" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="123" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>16</v>
       </c>
@@ -17525,11 +16541,8 @@
       <c r="AJ123">
         <v>0.53333333333333333</v>
       </c>
-      <c r="AP123">
-        <v>0.90909090909090906</v>
-      </c>
-    </row>
-    <row r="124" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="124" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>17</v>
       </c>
@@ -17580,11 +16593,8 @@
       <c r="AJ124">
         <v>0.93333333333333335</v>
       </c>
-      <c r="AP124">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="125" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="125" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>18</v>
       </c>
@@ -17635,11 +16645,8 @@
       <c r="AJ125">
         <v>0.5714285714285714</v>
       </c>
-      <c r="AP125">
-        <v>0.81818181818181823</v>
-      </c>
-    </row>
-    <row r="126" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="126" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>19</v>
       </c>
@@ -17690,11 +16697,8 @@
       <c r="AJ126">
         <v>0.6</v>
       </c>
-      <c r="AP126">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="127" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>20</v>
       </c>
@@ -17745,11 +16749,8 @@
       <c r="AJ127">
         <v>0.8666666666666667</v>
       </c>
-      <c r="AP127">
-        <v>0.6428571428571429</v>
-      </c>
-    </row>
-    <row r="128" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="128" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>21</v>
       </c>
@@ -17800,11 +16801,8 @@
       <c r="AJ128">
         <v>0.6</v>
       </c>
-      <c r="AP128">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="129" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="129" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>22</v>
       </c>
@@ -17855,11 +16853,8 @@
       <c r="AJ129">
         <v>0.5714285714285714</v>
       </c>
-      <c r="AP129">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="130" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="130" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>23</v>
       </c>
@@ -17910,11 +16905,8 @@
       <c r="AJ130">
         <v>0.7857142857142857</v>
       </c>
-      <c r="AP130">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="131" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="131" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>24</v>
       </c>
@@ -17965,11 +16957,8 @@
       <c r="AJ131">
         <v>1</v>
       </c>
-      <c r="AP131">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="132" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="132" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>25</v>
       </c>
@@ -18020,11 +17009,8 @@
       <c r="AJ132">
         <v>1</v>
       </c>
-      <c r="AP132">
-        <v>0.90909090909090906</v>
-      </c>
-    </row>
-    <row r="133" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="133" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>26</v>
       </c>
@@ -18075,11 +17061,8 @@
       <c r="AJ133">
         <v>0.63636363636363635</v>
       </c>
-      <c r="AP133">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="134" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="134" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>27</v>
       </c>
@@ -18130,11 +17113,8 @@
       <c r="AJ134">
         <v>1</v>
       </c>
-      <c r="AP134">
-        <v>0.88888888888888884</v>
-      </c>
-    </row>
-    <row r="135" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="135" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>28</v>
       </c>
@@ -18185,11 +17165,8 @@
       <c r="AJ135">
         <v>1</v>
       </c>
-      <c r="AP135">
-        <v>0.81818181818181823</v>
-      </c>
-    </row>
-    <row r="136" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="136" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>29</v>
       </c>
@@ -18240,11 +17217,8 @@
       <c r="AJ136">
         <v>0.84615384615384615</v>
       </c>
-      <c r="AP136">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="137" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="137" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>30</v>
       </c>
@@ -18295,11 +17269,8 @@
       <c r="AJ137">
         <v>0.8571428571428571</v>
       </c>
-      <c r="AP137">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="138" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="138" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>31</v>
       </c>
@@ -18350,11 +17321,8 @@
       <c r="AJ138">
         <v>1</v>
       </c>
-      <c r="AP138">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="139" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>32</v>
       </c>
@@ -18405,11 +17373,8 @@
       <c r="AJ139">
         <v>1</v>
       </c>
-      <c r="AP139">
-        <v>0.8571428571428571</v>
-      </c>
-    </row>
-    <row r="140" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="140" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>33</v>
       </c>
@@ -18460,11 +17425,8 @@
       <c r="AJ140">
         <v>1</v>
       </c>
-      <c r="AP140">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="141" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>34</v>
       </c>
@@ -18515,11 +17477,8 @@
       <c r="AJ141">
         <v>1</v>
       </c>
-      <c r="AP141">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="142" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>35</v>
       </c>
@@ -18570,11 +17529,8 @@
       <c r="AJ142">
         <v>1</v>
       </c>
-      <c r="AP142">
-        <v>0.88888888888888884</v>
-      </c>
-    </row>
-    <row r="143" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="143" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>36</v>
       </c>
@@ -18625,11 +17581,8 @@
       <c r="AJ143">
         <v>0.9</v>
       </c>
-      <c r="AP143">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="144" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>37</v>
       </c>
@@ -18680,11 +17633,8 @@
       <c r="AJ144">
         <v>0.83333333333333337</v>
       </c>
-      <c r="AP144">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="145" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>38</v>
       </c>
@@ -18735,11 +17685,8 @@
       <c r="AJ145">
         <v>1</v>
       </c>
-      <c r="AP145">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="146" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="146" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>39</v>
       </c>
@@ -18790,11 +17737,8 @@
       <c r="AJ146">
         <v>0.8</v>
       </c>
-      <c r="AP146">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="147" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="147" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>40</v>
       </c>
@@ -18845,11 +17789,8 @@
       <c r="AJ147">
         <v>1</v>
       </c>
-      <c r="AP147">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="148" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>41</v>
       </c>
@@ -18900,11 +17841,8 @@
       <c r="AJ148">
         <v>0.5714285714285714</v>
       </c>
-      <c r="AP148">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="149" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="149" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>42</v>
       </c>
@@ -18955,11 +17893,8 @@
       <c r="AJ149">
         <v>1</v>
       </c>
-      <c r="AP149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="150" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>43</v>
       </c>
@@ -19010,11 +17945,8 @@
       <c r="AJ150">
         <v>1</v>
       </c>
-      <c r="AP150">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="151" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>44</v>
       </c>
@@ -19065,11 +17997,8 @@
       <c r="AJ151">
         <v>1</v>
       </c>
-      <c r="AP151">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="152" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="152" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>45</v>
       </c>
@@ -19120,11 +18049,8 @@
       <c r="AJ152">
         <v>1</v>
       </c>
-      <c r="AP152">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="153" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="153" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>46</v>
       </c>
@@ -19175,11 +18101,8 @@
       <c r="AJ153">
         <v>0.66666666666666663</v>
       </c>
-      <c r="AP153">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="154" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>47</v>
       </c>
@@ -19230,11 +18153,8 @@
       <c r="AJ154">
         <v>1</v>
       </c>
-      <c r="AP154">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="155" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>48</v>
       </c>
@@ -19285,11 +18205,8 @@
       <c r="AJ155">
         <v>1</v>
       </c>
-      <c r="AP155">
-        <v>0.8571428571428571</v>
-      </c>
-    </row>
-    <row r="156" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="156" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>49</v>
       </c>
@@ -19340,11 +18257,8 @@
       <c r="AJ156">
         <v>0.75</v>
       </c>
-      <c r="AP156">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="157" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>50</v>
       </c>
@@ -19395,11 +18309,8 @@
       <c r="AJ157">
         <v>1</v>
       </c>
-      <c r="AP157">
-        <v>0.8571428571428571</v>
-      </c>
-    </row>
-    <row r="158" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="158" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>51</v>
       </c>
@@ -19450,11 +18361,8 @@
       <c r="AJ158">
         <v>1</v>
       </c>
-      <c r="AP158">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="159" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="159" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>52</v>
       </c>
@@ -19505,11 +18413,8 @@
       <c r="AJ159">
         <v>1</v>
       </c>
-      <c r="AP159">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="160" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>53</v>
       </c>
@@ -19560,11 +18465,8 @@
       <c r="AJ160">
         <v>0.8</v>
       </c>
-      <c r="AP160">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="161" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="161" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>54</v>
       </c>
@@ -19615,11 +18517,8 @@
       <c r="AJ161">
         <v>1</v>
       </c>
-      <c r="AP161">
-        <v>0.55555555555555558</v>
-      </c>
-    </row>
-    <row r="162" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="162" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>55</v>
       </c>
@@ -19670,11 +18569,8 @@
       <c r="AJ162">
         <v>1</v>
       </c>
-      <c r="AP162">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="163" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="163" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>56</v>
       </c>
@@ -19725,11 +18621,8 @@
       <c r="AJ163">
         <v>1</v>
       </c>
-      <c r="AP163">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="164" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="164" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>57</v>
       </c>
@@ -19780,11 +18673,8 @@
       <c r="AJ164">
         <v>1</v>
       </c>
-      <c r="AP164">
-        <v>0.8571428571428571</v>
-      </c>
-    </row>
-    <row r="165" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="165" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>58</v>
       </c>
@@ -19835,11 +18725,8 @@
       <c r="AJ165">
         <v>1</v>
       </c>
-      <c r="AP165">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="166" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="166" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>59</v>
       </c>
@@ -19890,11 +18777,8 @@
       <c r="AJ166">
         <v>1</v>
       </c>
-      <c r="AP166">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="167" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="167" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>60</v>
       </c>
@@ -19945,11 +18829,8 @@
       <c r="AJ167">
         <v>1</v>
       </c>
-      <c r="AP167">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="168" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="168" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>61</v>
       </c>
@@ -20000,11 +18881,8 @@
       <c r="AJ168">
         <v>0.8571428571428571</v>
       </c>
-      <c r="AP168">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="169" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="169" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>62</v>
       </c>
@@ -20055,11 +18933,8 @@
       <c r="AJ169">
         <v>0.8571428571428571</v>
       </c>
-      <c r="AP169">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="170" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="170" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>63</v>
       </c>
@@ -20110,11 +18985,8 @@
       <c r="AJ170">
         <v>1</v>
       </c>
-      <c r="AP170">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="171" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="171" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>64</v>
       </c>
@@ -20165,11 +19037,8 @@
       <c r="AJ171">
         <v>1</v>
       </c>
-      <c r="AP171">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="172" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>65</v>
       </c>
@@ -20220,11 +19089,8 @@
       <c r="AJ172">
         <v>0.75</v>
       </c>
-      <c r="AP172">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="173" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>66</v>
       </c>
@@ -20275,11 +19141,8 @@
       <c r="AJ173">
         <v>0.75</v>
       </c>
-      <c r="AP173">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="174" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="174" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>67</v>
       </c>
@@ -20330,11 +19193,8 @@
       <c r="AJ174">
         <v>1</v>
       </c>
-      <c r="AP174">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="175" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="175" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>68</v>
       </c>
@@ -20385,11 +19245,8 @@
       <c r="AJ175">
         <v>0.6</v>
       </c>
-      <c r="AP175">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="176" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="176" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>69</v>
       </c>
@@ -20440,11 +19297,8 @@
       <c r="AJ176">
         <v>0.66666666666666663</v>
       </c>
-      <c r="AP176">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="177" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="177" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>70</v>
       </c>
@@ -20495,11 +19349,8 @@
       <c r="AJ177">
         <v>1</v>
       </c>
-      <c r="AP177">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="178" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="178" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>71</v>
       </c>
@@ -20550,11 +19401,8 @@
       <c r="AJ178">
         <v>0.4</v>
       </c>
-      <c r="AP178">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="179" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="179" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>72</v>
       </c>
@@ -20605,11 +19453,8 @@
       <c r="AJ179">
         <v>0.83333333333333337</v>
       </c>
-      <c r="AP179">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="180" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="180" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>73</v>
       </c>
@@ -20660,11 +19505,8 @@
       <c r="AJ180">
         <v>0.8571428571428571</v>
       </c>
-      <c r="AP180">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="181" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="181" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>74</v>
       </c>
@@ -20715,11 +19557,8 @@
       <c r="AJ181">
         <v>0.88888888888888884</v>
       </c>
-      <c r="AP181">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="182" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>75</v>
       </c>
@@ -20770,11 +19609,8 @@
       <c r="AJ182">
         <v>1</v>
       </c>
-      <c r="AP182">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="183" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>76</v>
       </c>
@@ -20825,11 +19661,8 @@
       <c r="AJ183">
         <v>1</v>
       </c>
-      <c r="AP183">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="184" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>77</v>
       </c>
@@ -20880,11 +19713,8 @@
       <c r="AJ184">
         <v>0.8</v>
       </c>
-      <c r="AP184">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="185" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="185" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>78</v>
       </c>
@@ -20935,11 +19765,8 @@
       <c r="AJ185">
         <v>1</v>
       </c>
-      <c r="AP185">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="186" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>79</v>
       </c>
@@ -20990,11 +19817,8 @@
       <c r="AJ186">
         <v>0.8571428571428571</v>
       </c>
-      <c r="AP186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="187" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>80</v>
       </c>
@@ -21045,11 +19869,8 @@
       <c r="AJ187">
         <v>0.875</v>
       </c>
-      <c r="AP187">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="188" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="188" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>81</v>
       </c>
@@ -21100,11 +19921,8 @@
       <c r="AJ188">
         <v>1</v>
       </c>
-      <c r="AP188">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="189" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>82</v>
       </c>
@@ -21155,11 +19973,8 @@
       <c r="AJ189">
         <v>0.66666666666666663</v>
       </c>
-      <c r="AP189">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="190" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>83</v>
       </c>
@@ -21210,11 +20025,8 @@
       <c r="AJ190">
         <v>1</v>
       </c>
-      <c r="AP190">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="191" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>84</v>
       </c>
@@ -21265,11 +20077,8 @@
       <c r="AJ191">
         <v>0.6</v>
       </c>
-      <c r="AP191">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="192" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="192" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>85</v>
       </c>
@@ -21320,11 +20129,8 @@
       <c r="AJ192">
         <v>1</v>
       </c>
-      <c r="AP192">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="193" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="193" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>86</v>
       </c>
@@ -21375,11 +20181,8 @@
       <c r="AJ193">
         <v>1</v>
       </c>
-      <c r="AP193">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="194" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>87</v>
       </c>
@@ -21431,7 +20234,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="195" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>88</v>
       </c>
@@ -21482,11 +20285,8 @@
       <c r="AJ195">
         <v>0.6</v>
       </c>
-      <c r="AP195">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="196" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>89</v>
       </c>
@@ -21537,11 +20337,8 @@
       <c r="AJ196">
         <v>0.9</v>
       </c>
-      <c r="AP196">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="197" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>90</v>
       </c>
@@ -21592,11 +20389,8 @@
       <c r="AJ197">
         <v>0.6</v>
       </c>
-      <c r="AP197">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="198" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>91</v>
       </c>
@@ -21647,11 +20441,8 @@
       <c r="AJ198">
         <v>0.83333333333333337</v>
       </c>
-      <c r="AP198">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="199" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="199" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>92</v>
       </c>
@@ -21702,11 +20493,8 @@
       <c r="AJ199">
         <v>0.5</v>
       </c>
-      <c r="AP199">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="200" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>93</v>
       </c>
@@ -21757,11 +20545,8 @@
       <c r="AJ200">
         <v>1</v>
       </c>
-      <c r="AP200">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="201" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>94</v>
       </c>
@@ -21812,11 +20597,8 @@
       <c r="AJ201">
         <v>1</v>
       </c>
-      <c r="AP201">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="202" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="202" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>95</v>
       </c>
@@ -21867,11 +20649,8 @@
       <c r="AJ202">
         <v>0.3</v>
       </c>
-      <c r="AP202">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="203" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="203" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>96</v>
       </c>
@@ -21922,11 +20701,8 @@
       <c r="AJ203">
         <v>0.9</v>
       </c>
-      <c r="AP203">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="204" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="204" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>97</v>
       </c>
@@ -21977,11 +20753,8 @@
       <c r="AJ204">
         <v>0.7142857142857143</v>
       </c>
-      <c r="AP204">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="205" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>98</v>
       </c>
@@ -22032,11 +20805,8 @@
       <c r="AJ205">
         <v>1</v>
       </c>
-      <c r="AP205">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="206" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="206" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>99</v>
       </c>
@@ -22087,11 +20857,8 @@
       <c r="AJ206">
         <v>1</v>
       </c>
-      <c r="AP206">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="207" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="207" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>100</v>
       </c>
@@ -22143,15 +20910,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AD208" s="9"/>
       <c r="AE208" s="9"/>
     </row>
-    <row r="209" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AD209" s="9"/>
       <c r="AE209" s="9"/>
     </row>
-    <row r="210" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
         <v>25</v>
       </c>
@@ -22164,7 +20931,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="211" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
         <v>24</v>
       </c>
@@ -22177,7 +20944,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="212" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>1</v>
       </c>
@@ -22237,11 +21004,8 @@
       <c r="AJ212">
         <v>0.94840000000000002</v>
       </c>
-      <c r="AP212">
-        <v>0.96588571428571435</v>
-      </c>
-    </row>
-    <row r="213" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="213" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>2</v>
       </c>
@@ -22301,11 +21065,8 @@
       <c r="AJ213">
         <v>0.95518571428571419</v>
       </c>
-      <c r="AP213">
-        <v>0.84685714285714286</v>
-      </c>
-    </row>
-    <row r="214" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="214" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>3</v>
       </c>
@@ -22365,11 +21126,8 @@
       <c r="AJ214">
         <v>0.91201428571428578</v>
       </c>
-      <c r="AP214">
-        <v>0.88583333333333336</v>
-      </c>
-    </row>
-    <row r="215" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="215" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>4</v>
       </c>
@@ -22429,11 +21187,8 @@
       <c r="AJ215">
         <v>0.9232499999999999</v>
       </c>
-      <c r="AP215">
-        <v>0.98631666666666662</v>
-      </c>
-    </row>
-    <row r="216" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="216" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>5</v>
       </c>
@@ -22493,11 +21248,8 @@
       <c r="AJ216">
         <v>0.87988333333333335</v>
       </c>
-      <c r="AP216">
-        <v>0.81973333333333331</v>
-      </c>
-    </row>
-    <row r="217" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="217" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>6</v>
       </c>
@@ -22554,11 +21306,8 @@
       <c r="AJ217">
         <v>0.91148571428571423</v>
       </c>
-      <c r="AP217">
-        <v>0.99271428571428555</v>
-      </c>
-    </row>
-    <row r="218" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="218" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>7</v>
       </c>
@@ -22615,11 +21364,8 @@
       <c r="AJ218">
         <v>0.88939999999999997</v>
       </c>
-      <c r="AP218">
-        <v>0.99822000000000011</v>
-      </c>
-    </row>
-    <row r="219" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="219" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>8</v>
       </c>
@@ -22676,11 +21422,8 @@
       <c r="AJ219">
         <v>0.93872857142857147</v>
       </c>
-      <c r="AP219">
-        <v>0.86796249999999997</v>
-      </c>
-    </row>
-    <row r="220" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="220" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>9</v>
       </c>
@@ -22737,11 +21480,8 @@
       <c r="AJ220">
         <v>0.90980000000000005</v>
       </c>
-      <c r="AP220">
-        <v>0.87602500000000005</v>
-      </c>
-    </row>
-    <row r="221" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="221" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>10</v>
       </c>
@@ -22798,11 +21538,8 @@
       <c r="AJ221">
         <v>0.87303333333333333</v>
       </c>
-      <c r="AP221">
-        <v>0.98562857142857141</v>
-      </c>
-    </row>
-    <row r="222" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="222" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>11</v>
       </c>
@@ -22853,11 +21590,8 @@
       <c r="AJ222">
         <v>0.90468888888888876</v>
       </c>
-      <c r="AP222">
-        <v>0.99433749999999999</v>
-      </c>
-    </row>
-    <row r="223" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="223" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>12</v>
       </c>
@@ -22908,11 +21642,8 @@
       <c r="AJ223">
         <v>0.83130000000000004</v>
       </c>
-      <c r="AP223">
-        <v>0.84681999999999991</v>
-      </c>
-    </row>
-    <row r="224" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="224" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>13</v>
       </c>
@@ -22963,11 +21694,8 @@
       <c r="AJ224">
         <v>0.87777142857142854</v>
       </c>
-      <c r="AP224">
-        <v>0.99595714285714287</v>
-      </c>
-    </row>
-    <row r="225" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="225" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>14</v>
       </c>
@@ -23018,11 +21746,8 @@
       <c r="AJ225">
         <v>0.86574285714285715</v>
       </c>
-      <c r="AP225">
-        <v>0.98899999999999999</v>
-      </c>
-    </row>
-    <row r="226" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="226" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>15</v>
       </c>
@@ -23073,11 +21798,8 @@
       <c r="AJ226">
         <v>0.86186000000000007</v>
       </c>
-      <c r="AP226">
-        <v>0.97255000000000003</v>
-      </c>
-    </row>
-    <row r="227" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="227" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>16</v>
       </c>
@@ -23128,11 +21850,8 @@
       <c r="AJ227">
         <v>0.80818000000000012</v>
       </c>
-      <c r="AP227">
-        <v>0.81013999999999997</v>
-      </c>
-    </row>
-    <row r="228" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="228" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>17</v>
       </c>
@@ -23183,11 +21902,8 @@
       <c r="AJ228">
         <v>0.82950000000000002</v>
       </c>
-      <c r="AP228">
-        <v>0.89123333333333343</v>
-      </c>
-    </row>
-    <row r="229" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="229" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>18</v>
       </c>
@@ -23238,11 +21954,8 @@
       <c r="AJ229">
         <v>0.83834285714285717</v>
       </c>
-      <c r="AP229">
-        <v>0.93198333333333327</v>
-      </c>
-    </row>
-    <row r="230" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="230" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>19</v>
       </c>
@@ -23293,11 +22006,8 @@
       <c r="AJ230">
         <v>0.86308333333333331</v>
       </c>
-      <c r="AP230">
-        <v>0.98973333333333324</v>
-      </c>
-    </row>
-    <row r="231" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="231" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>20</v>
       </c>
@@ -23348,11 +22058,8 @@
       <c r="AJ231">
         <v>0.83986666666666665</v>
       </c>
-      <c r="AP231">
-        <v>0.98613333333333342</v>
-      </c>
-    </row>
-    <row r="232" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="232" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>21</v>
       </c>
@@ -23403,11 +22110,8 @@
       <c r="AJ232">
         <v>0.89100000000000001</v>
       </c>
-      <c r="AP232">
-        <v>0.99218333333333331</v>
-      </c>
-    </row>
-    <row r="233" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="233" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>22</v>
       </c>
@@ -23458,11 +22162,8 @@
       <c r="AJ233">
         <v>0.89295000000000002</v>
       </c>
-      <c r="AP233">
-        <v>0.98272857142857151</v>
-      </c>
-    </row>
-    <row r="234" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="234" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>23</v>
       </c>
@@ -23513,11 +22214,8 @@
       <c r="AJ234">
         <v>0.84792857142857136</v>
       </c>
-      <c r="AP234">
-        <v>0.88677142857142854</v>
-      </c>
-    </row>
-    <row r="235" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="235" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>24</v>
       </c>
@@ -23568,11 +22266,8 @@
       <c r="AJ235">
         <v>0.78702857142857141</v>
       </c>
-      <c r="AP235">
-        <v>0.9881375</v>
-      </c>
-    </row>
-    <row r="236" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="236" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>25</v>
       </c>
@@ -23623,11 +22318,8 @@
       <c r="AJ236">
         <v>0.62981428571428566</v>
       </c>
-      <c r="AP236">
-        <v>0.99410000000000009</v>
-      </c>
-    </row>
-    <row r="237" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="237" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <v>26</v>
       </c>
@@ -23678,11 +22370,8 @@
       <c r="AJ237">
         <v>0.89146250000000005</v>
       </c>
-      <c r="AP237">
-        <v>0.95998000000000006</v>
-      </c>
-    </row>
-    <row r="238" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="238" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <v>27</v>
       </c>
@@ -23733,11 +22422,8 @@
       <c r="AJ238">
         <v>0.6767777777777777</v>
       </c>
-      <c r="AP238">
-        <v>0.99382857142857139</v>
-      </c>
-    </row>
-    <row r="239" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="239" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <v>28</v>
       </c>
@@ -23788,11 +22474,8 @@
       <c r="AJ239">
         <v>0.74308750000000001</v>
       </c>
-      <c r="AP239">
-        <v>0.99188333333333334</v>
-      </c>
-    </row>
-    <row r="240" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="240" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <v>29</v>
       </c>
@@ -23843,11 +22526,8 @@
       <c r="AJ240">
         <v>0.87226000000000004</v>
       </c>
-      <c r="AP240">
-        <v>0.9929</v>
-      </c>
-    </row>
-    <row r="241" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="241" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <v>30</v>
       </c>
@@ -23898,11 +22578,8 @@
       <c r="AJ241">
         <v>0.65734444444444451</v>
       </c>
-      <c r="AP241">
-        <v>0.99231249999999993</v>
-      </c>
-    </row>
-    <row r="242" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="242" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>31</v>
       </c>
@@ -23953,11 +22630,8 @@
       <c r="AJ242">
         <v>0.71184999999999998</v>
       </c>
-      <c r="AP242">
-        <v>0.87365555555555541</v>
-      </c>
-    </row>
-    <row r="243" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="243" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <v>32</v>
       </c>
@@ -24008,11 +22682,8 @@
       <c r="AJ243">
         <v>0.75962857142857143</v>
       </c>
-      <c r="AP243">
-        <v>0.86419999999999986</v>
-      </c>
-    </row>
-    <row r="244" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="244" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>33</v>
       </c>
@@ -24063,11 +22734,8 @@
       <c r="AJ244">
         <v>0.70450999999999997</v>
       </c>
-      <c r="AP244">
-        <v>0.68789999999999996</v>
-      </c>
-    </row>
-    <row r="245" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="245" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>34</v>
       </c>
@@ -24118,11 +22786,8 @@
       <c r="AJ245">
         <v>0.84362499999999985</v>
       </c>
-      <c r="AP245">
-        <v>0.99175999999999997</v>
-      </c>
-    </row>
-    <row r="246" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="246" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>35</v>
       </c>
@@ -24173,11 +22838,8 @@
       <c r="AJ246">
         <v>0.68784999999999996</v>
       </c>
-      <c r="AP246">
-        <v>0.99631428571428582</v>
-      </c>
-    </row>
-    <row r="247" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="247" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <v>36</v>
       </c>
@@ -24228,11 +22890,8 @@
       <c r="AJ247">
         <v>0.86825999999999992</v>
       </c>
-      <c r="AP247">
-        <v>0.98447142857142855</v>
-      </c>
-    </row>
-    <row r="248" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="248" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>37</v>
       </c>
@@ -24283,11 +22942,8 @@
       <c r="AJ248">
         <v>0.61045555555555553</v>
       </c>
-      <c r="AP248">
-        <v>0.85162857142857151</v>
-      </c>
-    </row>
-    <row r="249" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="249" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>38</v>
       </c>
@@ -24338,11 +22994,8 @@
       <c r="AJ249">
         <v>0.64860000000000007</v>
       </c>
-      <c r="AP249">
-        <v>0.98663333333333336</v>
-      </c>
-    </row>
-    <row r="250" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="250" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>39</v>
       </c>
@@ -24393,11 +23046,8 @@
       <c r="AJ250">
         <v>0.77678000000000014</v>
       </c>
-      <c r="AP250">
-        <v>0.88453333333333328</v>
-      </c>
-    </row>
-    <row r="251" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="251" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>40</v>
       </c>
@@ -24448,11 +23098,8 @@
       <c r="AJ251">
         <v>0.67050999999999994</v>
       </c>
-      <c r="AP251">
-        <v>0.69035000000000002</v>
-      </c>
-    </row>
-    <row r="252" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="252" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>41</v>
       </c>
@@ -24503,11 +23150,8 @@
       <c r="AJ252">
         <v>0.65640000000000009</v>
       </c>
-      <c r="AP252">
-        <v>0.72497272727272721</v>
-      </c>
-    </row>
-    <row r="253" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="253" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>42</v>
       </c>
@@ -24558,11 +23202,8 @@
       <c r="AJ253">
         <v>0.70287777777777771</v>
       </c>
-      <c r="AP253">
-        <v>0.88052222222222232</v>
-      </c>
-    </row>
-    <row r="254" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="254" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>43</v>
       </c>
@@ -24613,11 +23254,8 @@
       <c r="AJ254">
         <v>0.69740000000000002</v>
       </c>
-      <c r="AP254">
-        <v>0.79576000000000002</v>
-      </c>
-    </row>
-    <row r="255" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="255" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>44</v>
       </c>
@@ -24668,11 +23306,8 @@
       <c r="AJ255">
         <v>0.76264285714285707</v>
       </c>
-      <c r="AP255">
-        <v>0.68755384615384618</v>
-      </c>
-    </row>
-    <row r="256" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="256" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <v>45</v>
       </c>
@@ -24723,11 +23358,8 @@
       <c r="AJ256">
         <v>0.65340000000000009</v>
       </c>
-      <c r="AP256">
-        <v>0.79862999999999995</v>
-      </c>
-    </row>
-    <row r="257" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="257" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>46</v>
       </c>
@@ -24778,11 +23410,8 @@
       <c r="AJ257">
         <v>0.67939999999999989</v>
       </c>
-      <c r="AP257">
-        <v>0.64157272727272729</v>
-      </c>
-    </row>
-    <row r="258" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="258" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <v>47</v>
       </c>
@@ -24833,11 +23462,8 @@
       <c r="AJ258">
         <v>0.63927</v>
       </c>
-      <c r="AP258">
-        <v>0.69428999999999996</v>
-      </c>
-    </row>
-    <row r="259" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="259" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>48</v>
       </c>
@@ -24888,11 +23514,8 @@
       <c r="AJ259">
         <v>0.53298571428571428</v>
       </c>
-      <c r="AP259">
-        <v>0.65395555555555562</v>
-      </c>
-    </row>
-    <row r="260" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="260" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>49</v>
       </c>
@@ -24943,11 +23566,8 @@
       <c r="AJ260">
         <v>0.66066363636363645</v>
       </c>
-      <c r="AP260">
-        <v>0.65415000000000001</v>
-      </c>
-    </row>
-    <row r="261" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="261" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>50</v>
       </c>
@@ -24998,11 +23618,8 @@
       <c r="AJ261">
         <v>0.56563333333333332</v>
       </c>
-      <c r="AP261">
-        <v>0.8725222222222222</v>
-      </c>
-    </row>
-    <row r="262" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="262" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>51</v>
       </c>
@@ -25053,11 +23670,8 @@
       <c r="AJ262">
         <v>0.70489999999999997</v>
       </c>
-      <c r="AP262">
-        <v>0.70951818181818183</v>
-      </c>
-    </row>
-    <row r="263" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="263" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>52</v>
       </c>
@@ -25108,11 +23722,8 @@
       <c r="AJ263">
         <v>0.6487857142857143</v>
       </c>
-      <c r="AP263">
-        <v>0.86588571428571437</v>
-      </c>
-    </row>
-    <row r="264" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="264" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>53</v>
       </c>
@@ -25163,11 +23774,8 @@
       <c r="AJ264">
         <v>0.72321999999999997</v>
       </c>
-      <c r="AP264">
-        <v>0.56762857142857137</v>
-      </c>
-    </row>
-    <row r="265" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="265" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>54</v>
       </c>
@@ -25218,11 +23826,8 @@
       <c r="AJ265">
         <v>0.78342857142857147</v>
       </c>
-      <c r="AP265">
-        <v>0.41320000000000012</v>
-      </c>
-    </row>
-    <row r="266" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="266" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>55</v>
       </c>
@@ -25273,11 +23878,8 @@
       <c r="AJ266">
         <v>0.75134999999999996</v>
       </c>
-      <c r="AP266">
-        <v>0.74009999999999998</v>
-      </c>
-    </row>
-    <row r="267" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="267" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>56</v>
       </c>
@@ -25328,11 +23930,8 @@
       <c r="AJ267">
         <v>0.77541249999999995</v>
       </c>
-      <c r="AP267">
-        <v>0.63991818181818194</v>
-      </c>
-    </row>
-    <row r="268" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="268" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>57</v>
       </c>
@@ -25383,11 +23982,8 @@
       <c r="AJ268">
         <v>0.47424285714285708</v>
       </c>
-      <c r="AP268">
-        <v>0.45835555555555563</v>
-      </c>
-    </row>
-    <row r="269" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="269" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>58</v>
       </c>
@@ -25438,11 +24034,8 @@
       <c r="AJ269">
         <v>0.62215555555555546</v>
       </c>
-      <c r="AP269">
-        <v>0.91015000000000013</v>
-      </c>
-    </row>
-    <row r="270" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="270" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>59</v>
       </c>
@@ -25493,11 +24086,8 @@
       <c r="AJ270">
         <v>0.64953333333333341</v>
       </c>
-      <c r="AP270">
-        <v>0.69570833333333326</v>
-      </c>
-    </row>
-    <row r="271" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="271" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>60</v>
       </c>
@@ -25548,11 +24138,8 @@
       <c r="AJ271">
         <v>0.78591250000000001</v>
       </c>
-      <c r="AP271">
-        <v>0.73720833333333324</v>
-      </c>
-    </row>
-    <row r="272" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="272" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>61</v>
       </c>
@@ -25603,11 +24190,8 @@
       <c r="AJ272">
         <v>0.64844999999999997</v>
       </c>
-      <c r="AP272">
-        <v>0.75391666666666668</v>
-      </c>
-    </row>
-    <row r="273" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="273" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>62</v>
       </c>
@@ -25658,11 +24242,8 @@
       <c r="AJ273">
         <v>0.71858750000000005</v>
       </c>
-      <c r="AP273">
-        <v>0.44237272727272731</v>
-      </c>
-    </row>
-    <row r="274" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="274" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>63</v>
       </c>
@@ -25713,11 +24294,8 @@
       <c r="AJ274">
         <v>0.54236249999999997</v>
       </c>
-      <c r="AP274">
-        <v>0.66093333333333326</v>
-      </c>
-    </row>
-    <row r="275" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="275" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>64</v>
       </c>
@@ -25768,11 +24346,8 @@
       <c r="AJ275">
         <v>0.76857142857142857</v>
       </c>
-      <c r="AP275">
-        <v>0.65487499999999998</v>
-      </c>
-    </row>
-    <row r="276" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="276" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <v>65</v>
       </c>
@@ -25823,11 +24398,8 @@
       <c r="AJ276">
         <v>0.66451818181818179</v>
       </c>
-      <c r="AP276">
-        <v>0.72350909090909099</v>
-      </c>
-    </row>
-    <row r="277" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="277" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <v>66</v>
       </c>
@@ -25878,11 +24450,8 @@
       <c r="AJ277">
         <v>0.59106363636363635</v>
       </c>
-      <c r="AP277">
-        <v>0.63375454545454535</v>
-      </c>
-    </row>
-    <row r="278" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="278" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>67</v>
       </c>
@@ -25933,11 +24502,8 @@
       <c r="AJ278">
         <v>0.60653333333333326</v>
       </c>
-      <c r="AP278">
-        <v>0.63051818181818176</v>
-      </c>
-    </row>
-    <row r="279" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="279" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>68</v>
       </c>
@@ -25988,11 +24554,8 @@
       <c r="AJ279">
         <v>0.62543000000000004</v>
       </c>
-      <c r="AP279">
-        <v>0.57423999999999986</v>
-      </c>
-    </row>
-    <row r="280" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="280" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>69</v>
       </c>
@@ -26043,11 +24606,8 @@
       <c r="AJ280">
         <v>0.60089999999999999</v>
       </c>
-      <c r="AP280">
-        <v>0.62948181818181825</v>
-      </c>
-    </row>
-    <row r="281" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="281" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>70</v>
       </c>
@@ -26098,11 +24658,8 @@
       <c r="AJ281">
         <v>0.65381428571428568</v>
       </c>
-      <c r="AP281">
-        <v>0.53503846153846157</v>
-      </c>
-    </row>
-    <row r="282" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="282" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>71</v>
       </c>
@@ -26153,11 +24710,8 @@
       <c r="AJ282">
         <v>0.66636999999999991</v>
       </c>
-      <c r="AP282">
-        <v>0.53639999999999999</v>
-      </c>
-    </row>
-    <row r="283" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="283" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>72</v>
       </c>
@@ -26208,11 +24762,8 @@
       <c r="AJ283">
         <v>0.59946666666666681</v>
       </c>
-      <c r="AP283">
-        <v>0.68253076923076916</v>
-      </c>
-    </row>
-    <row r="284" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="284" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>73</v>
       </c>
@@ -26263,11 +24814,8 @@
       <c r="AJ284">
         <v>0.77036249999999995</v>
       </c>
-      <c r="AP284">
-        <v>0.61167142857142864</v>
-      </c>
-    </row>
-    <row r="285" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="285" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>74</v>
       </c>
@@ -26318,11 +24866,8 @@
       <c r="AJ285">
         <v>0.70809999999999995</v>
       </c>
-      <c r="AP285">
-        <v>0.49639285714285708</v>
-      </c>
-    </row>
-    <row r="286" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="286" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>75</v>
       </c>
@@ -26373,11 +24918,8 @@
       <c r="AJ286">
         <v>0.5573499999999999</v>
       </c>
-      <c r="AP286">
-        <v>0.49676999999999999</v>
-      </c>
-    </row>
-    <row r="287" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="287" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>76</v>
       </c>
@@ -26428,11 +24970,8 @@
       <c r="AJ287">
         <v>0.66404000000000007</v>
       </c>
-      <c r="AP287">
-        <v>0.46350833333333319</v>
-      </c>
-    </row>
-    <row r="288" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="288" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>77</v>
       </c>
@@ -26483,11 +25022,8 @@
       <c r="AJ288">
         <v>0.70097000000000009</v>
       </c>
-      <c r="AP288">
-        <v>0.76294615384615383</v>
-      </c>
-    </row>
-    <row r="289" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="289" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>78</v>
       </c>
@@ -26538,11 +25074,8 @@
       <c r="AJ289">
         <v>0.62295</v>
       </c>
-      <c r="AP289">
-        <v>0.57724999999999993</v>
-      </c>
-    </row>
-    <row r="290" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="290" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>79</v>
       </c>
@@ -26593,11 +25126,8 @@
       <c r="AJ290">
         <v>0.85675000000000001</v>
       </c>
-      <c r="AP290">
-        <v>0.61230000000000007</v>
-      </c>
-    </row>
-    <row r="291" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="291" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>80</v>
       </c>
@@ -26648,11 +25178,8 @@
       <c r="AJ291">
         <v>0.47498571428571429</v>
       </c>
-      <c r="AP291">
-        <v>0.58479090909090903</v>
-      </c>
-    </row>
-    <row r="292" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="292" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>81</v>
       </c>
@@ -26703,11 +25230,8 @@
       <c r="AJ292">
         <v>0.65175454545454548</v>
       </c>
-      <c r="AP292">
-        <v>0.41324166666666667</v>
-      </c>
-    </row>
-    <row r="293" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="293" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>82</v>
       </c>
@@ -26758,11 +25282,8 @@
       <c r="AJ293">
         <v>0.68932222222222217</v>
       </c>
-      <c r="AP293">
-        <v>0.579175</v>
-      </c>
-    </row>
-    <row r="294" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="294" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>83</v>
       </c>
@@ -26813,11 +25334,8 @@
       <c r="AJ294">
         <v>0.51730999999999994</v>
       </c>
-      <c r="AP294">
-        <v>0.62153636363636366</v>
-      </c>
-    </row>
-    <row r="295" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="295" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>84</v>
       </c>
@@ -26868,11 +25386,8 @@
       <c r="AJ295">
         <v>0.64646000000000003</v>
       </c>
-      <c r="AP295">
-        <v>0.49373000000000011</v>
-      </c>
-    </row>
-    <row r="296" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="296" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>85</v>
       </c>
@@ -26923,11 +25438,8 @@
       <c r="AJ296">
         <v>0.70033000000000012</v>
       </c>
-      <c r="AP296">
-        <v>0.57726666666666671</v>
-      </c>
-    </row>
-    <row r="297" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="297" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>86</v>
       </c>
@@ -26978,11 +25490,8 @@
       <c r="AJ297">
         <v>0.67696363636363632</v>
       </c>
-      <c r="AP297">
-        <v>0.61201818181818179</v>
-      </c>
-    </row>
-    <row r="298" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="298" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>87</v>
       </c>
@@ -27034,7 +25543,7 @@
         <v>0.87895999999999996</v>
       </c>
     </row>
-    <row r="299" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>88</v>
       </c>
@@ -27085,11 +25594,8 @@
       <c r="AJ299">
         <v>0.62807999999999997</v>
       </c>
-      <c r="AP299">
-        <v>0.55772857142857146</v>
-      </c>
-    </row>
-    <row r="300" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="300" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>89</v>
       </c>
@@ -27140,11 +25646,8 @@
       <c r="AJ300">
         <v>0.88214000000000004</v>
       </c>
-      <c r="AP300">
-        <v>0.45941538461538473</v>
-      </c>
-    </row>
-    <row r="301" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="301" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>90</v>
       </c>
@@ -27195,11 +25698,8 @@
       <c r="AJ301">
         <v>0.66266000000000003</v>
       </c>
-      <c r="AP301">
-        <v>0.61312727272727274</v>
-      </c>
-    </row>
-    <row r="302" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="302" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>91</v>
       </c>
@@ -27250,11 +25750,8 @@
       <c r="AJ302">
         <v>0.62342222222222221</v>
       </c>
-      <c r="AP302">
-        <v>0.49453999999999998</v>
-      </c>
-    </row>
-    <row r="303" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="303" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
         <v>92</v>
       </c>
@@ -27305,11 +25802,8 @@
       <c r="AJ303">
         <v>0.60370000000000001</v>
       </c>
-      <c r="AP303">
-        <v>0.39781</v>
-      </c>
-    </row>
-    <row r="304" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="304" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
         <v>93</v>
       </c>
@@ -27360,11 +25854,8 @@
       <c r="AJ304">
         <v>0.68594444444444447</v>
       </c>
-      <c r="AP304">
-        <v>0.68146153846153845</v>
-      </c>
-    </row>
-    <row r="305" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="305" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
         <v>94</v>
       </c>
@@ -27415,11 +25906,8 @@
       <c r="AJ305">
         <v>0.63656000000000001</v>
       </c>
-      <c r="AP305">
-        <v>0.43927272727272731</v>
-      </c>
-    </row>
-    <row r="306" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="306" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
         <v>95</v>
       </c>
@@ -27470,11 +25958,8 @@
       <c r="AJ306">
         <v>0.70723999999999998</v>
       </c>
-      <c r="AP306">
-        <v>0.68552999999999997</v>
-      </c>
-    </row>
-    <row r="307" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="307" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
         <v>96</v>
       </c>
@@ -27525,11 +26010,8 @@
       <c r="AJ307">
         <v>0.82989999999999997</v>
       </c>
-      <c r="AP307">
-        <v>0.3657333333333333</v>
-      </c>
-    </row>
-    <row r="308" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="308" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A308" s="1">
         <v>97</v>
       </c>
@@ -27580,11 +26062,8 @@
       <c r="AJ308">
         <v>0.85723749999999999</v>
       </c>
-      <c r="AP308">
-        <v>0.62552727272727271</v>
-      </c>
-    </row>
-    <row r="309" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="309" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A309" s="1">
         <v>98</v>
       </c>
@@ -27635,11 +26114,8 @@
       <c r="AJ309">
         <v>0.50706666666666667</v>
       </c>
-      <c r="AP309">
-        <v>0.72435454545454547</v>
-      </c>
-    </row>
-    <row r="310" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="310" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A310" s="1">
         <v>99</v>
       </c>
@@ -27690,11 +26166,8 @@
       <c r="AJ310">
         <v>0.62878000000000001</v>
       </c>
-      <c r="AP310">
-        <v>0.64001000000000008</v>
-      </c>
-    </row>
-    <row r="311" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="311" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A311" s="1">
         <v>100</v>
       </c>
@@ -27746,15 +26219,15 @@
         <v>0.51706000000000008</v>
       </c>
     </row>
-    <row r="312" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AD312" s="9"/>
       <c r="AE312" s="9"/>
     </row>
-    <row r="313" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AD313" s="9"/>
       <c r="AE313" s="9"/>
     </row>
-    <row r="314" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
         <v>27</v>
       </c>
@@ -27767,7 +26240,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="315" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A315" s="3" t="s">
         <v>24</v>
       </c>
@@ -27780,7 +26253,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="316" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A316" s="1">
         <v>1</v>
       </c>
@@ -27840,11 +26313,8 @@
       <c r="AJ316">
         <v>0</v>
       </c>
-      <c r="AP316">
-        <v>0.95579999999999998</v>
-      </c>
-    </row>
-    <row r="317" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="317" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A317" s="1">
         <v>2</v>
       </c>
@@ -27904,11 +26374,8 @@
       <c r="AJ317">
         <v>1.54E-2</v>
       </c>
-      <c r="AP317">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="318" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A318" s="1">
         <v>3</v>
       </c>
@@ -27968,11 +26435,8 @@
       <c r="AJ318">
         <v>4.5600000000000002E-2</v>
       </c>
-      <c r="AP318">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="319" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="319" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A319" s="1">
         <v>4</v>
       </c>
@@ -28032,11 +26496,8 @@
       <c r="AJ319">
         <v>6.0199999999999997E-2</v>
       </c>
-      <c r="AP319">
-        <v>4.4000000000000003E-3</v>
-      </c>
-    </row>
-    <row r="320" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="320" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A320" s="1">
         <v>5</v>
       </c>
@@ -28096,11 +26557,8 @@
       <c r="AJ320">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="AP320">
-        <v>0.1013</v>
-      </c>
-    </row>
-    <row r="321" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="321" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A321" s="1">
         <v>6</v>
       </c>
@@ -28157,11 +26615,8 @@
       <c r="AJ321">
         <v>9.3399999999999997E-2</v>
       </c>
-      <c r="AP321">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="322" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="322" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A322" s="1">
         <v>7</v>
       </c>
@@ -28218,11 +26673,8 @@
       <c r="AJ322">
         <v>0.15870000000000001</v>
       </c>
-      <c r="AP322">
-        <v>0.9284</v>
-      </c>
-    </row>
-    <row r="323" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="323" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A323" s="1">
         <v>8</v>
       </c>
@@ -28279,11 +26731,8 @@
       <c r="AJ323">
         <v>0.14449999999999999</v>
       </c>
-      <c r="AP323">
-        <v>0.90439999999999998</v>
-      </c>
-    </row>
-    <row r="324" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="324" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
         <v>9</v>
       </c>
@@ -28340,11 +26789,8 @@
       <c r="AJ324">
         <v>0.13719999999999999</v>
       </c>
-      <c r="AP324">
-        <v>0.72809999999999997</v>
-      </c>
-    </row>
-    <row r="325" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="325" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
         <v>10</v>
       </c>
@@ -28401,11 +26847,8 @@
       <c r="AJ325">
         <v>8.2600000000000007E-2</v>
       </c>
-      <c r="AP325">
-        <v>0.92079999999999995</v>
-      </c>
-    </row>
-    <row r="326" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="326" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A326" s="1">
         <v>11</v>
       </c>
@@ -28456,11 +26899,8 @@
       <c r="AJ326">
         <v>0.15970000000000001</v>
       </c>
-      <c r="AP326">
-        <v>0.96819999999999995</v>
-      </c>
-    </row>
-    <row r="327" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="327" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A327" s="1">
         <v>12</v>
       </c>
@@ -28511,11 +26951,8 @@
       <c r="AJ327">
         <v>0.1368</v>
       </c>
-      <c r="AP327">
-        <v>0.74350000000000005</v>
-      </c>
-    </row>
-    <row r="328" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="328" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
         <v>13</v>
       </c>
@@ -28566,11 +27003,8 @@
       <c r="AJ328">
         <v>0.18579999999999999</v>
       </c>
-      <c r="AP328">
-        <v>0.56399999999999995</v>
-      </c>
-    </row>
-    <row r="329" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="329" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A329" s="1">
         <v>14</v>
       </c>
@@ -28621,11 +27055,8 @@
       <c r="AJ329">
         <v>0.12709999999999999</v>
       </c>
-      <c r="AP329">
-        <v>0.29360000000000003</v>
-      </c>
-    </row>
-    <row r="330" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="330" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A330" s="1">
         <v>15</v>
       </c>
@@ -28676,11 +27107,8 @@
       <c r="AJ330">
         <v>0.1187</v>
       </c>
-      <c r="AP330">
-        <v>0.84599999999999997</v>
-      </c>
-    </row>
-    <row r="331" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="331" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A331" s="1">
         <v>16</v>
       </c>
@@ -28731,11 +27159,8 @@
       <c r="AJ331">
         <v>0.13170000000000001</v>
       </c>
-      <c r="AP331">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="332" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="332" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A332" s="1">
         <v>17</v>
       </c>
@@ -28786,11 +27211,8 @@
       <c r="AJ332">
         <v>0.1295</v>
       </c>
-      <c r="AP332">
-        <v>0.99960000000000004</v>
-      </c>
-    </row>
-    <row r="333" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="333" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A333" s="1">
         <v>18</v>
       </c>
@@ -28841,11 +27263,8 @@
       <c r="AJ333">
         <v>0.1454</v>
       </c>
-      <c r="AP333">
-        <v>0.9869</v>
-      </c>
-    </row>
-    <row r="334" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="334" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A334" s="1">
         <v>19</v>
       </c>
@@ -28896,11 +27315,8 @@
       <c r="AJ334">
         <v>9.4100000000000003E-2</v>
       </c>
-      <c r="AP334">
-        <v>0.99519999999999997</v>
-      </c>
-    </row>
-    <row r="335" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="335" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A335" s="1">
         <v>20</v>
       </c>
@@ -28951,11 +27367,8 @@
       <c r="AJ335">
         <v>0.1145</v>
       </c>
-      <c r="AP335">
-        <v>0.91979999999999995</v>
-      </c>
-    </row>
-    <row r="336" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="336" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A336" s="1">
         <v>21</v>
       </c>
@@ -29006,11 +27419,8 @@
       <c r="AJ336">
         <v>0.115</v>
       </c>
-      <c r="AP336">
-        <v>0.99590000000000001</v>
-      </c>
-    </row>
-    <row r="337" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="337" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A337" s="1">
         <v>22</v>
       </c>
@@ -29061,11 +27471,8 @@
       <c r="AJ337">
         <v>0.1366</v>
       </c>
-      <c r="AP337">
-        <v>0.82879999999999998</v>
-      </c>
-    </row>
-    <row r="338" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="338" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A338" s="1">
         <v>23</v>
       </c>
@@ -29116,11 +27523,8 @@
       <c r="AJ338">
         <v>0.1172</v>
       </c>
-      <c r="AP338">
-        <v>0.99570000000000003</v>
-      </c>
-    </row>
-    <row r="339" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="339" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A339" s="1">
         <v>24</v>
       </c>
@@ -29171,11 +27575,8 @@
       <c r="AJ339">
         <v>0.11409999999999999</v>
       </c>
-      <c r="AP339">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="340" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="340" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A340" s="1">
         <v>25</v>
       </c>
@@ -29226,11 +27627,8 @@
       <c r="AJ340">
         <v>0.1133</v>
       </c>
-      <c r="AP340">
-        <v>0.99860000000000004</v>
-      </c>
-    </row>
-    <row r="341" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="341" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A341" s="1">
         <v>26</v>
       </c>
@@ -29281,11 +27679,8 @@
       <c r="AJ341">
         <v>0.1265</v>
       </c>
-      <c r="AP341">
-        <v>0.99780000000000002</v>
-      </c>
-    </row>
-    <row r="342" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="342" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A342" s="1">
         <v>27</v>
       </c>
@@ -29336,11 +27731,8 @@
       <c r="AJ342">
         <v>0.1072</v>
       </c>
-      <c r="AP342">
-        <v>0.98650000000000004</v>
-      </c>
-    </row>
-    <row r="343" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="343" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A343" s="1">
         <v>28</v>
       </c>
@@ -29391,11 +27783,8 @@
       <c r="AJ343">
         <v>0.11</v>
       </c>
-      <c r="AP343">
-        <v>0.9486</v>
-      </c>
-    </row>
-    <row r="344" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="344" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A344" s="1">
         <v>29</v>
       </c>
@@ -29446,11 +27835,8 @@
       <c r="AJ344">
         <v>0.1009</v>
       </c>
-      <c r="AP344">
-        <v>0.99750000000000005</v>
-      </c>
-    </row>
-    <row r="345" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="345" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A345" s="1">
         <v>30</v>
       </c>
@@ -29501,11 +27887,8 @@
       <c r="AJ345">
         <v>0.11119999999999999</v>
       </c>
-      <c r="AP345">
-        <v>0.91379999999999995</v>
-      </c>
-    </row>
-    <row r="346" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="346" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A346" s="1">
         <v>31</v>
       </c>
@@ -29556,11 +27939,8 @@
       <c r="AJ346">
         <v>8.6599999999999996E-2</v>
       </c>
-      <c r="AP346">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="347" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A347" s="1">
         <v>32</v>
       </c>
@@ -29611,11 +27991,8 @@
       <c r="AJ347">
         <v>0.1046</v>
       </c>
-      <c r="AP347">
-        <v>0.99429999999999996</v>
-      </c>
-    </row>
-    <row r="348" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="348" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A348" s="1">
         <v>33</v>
       </c>
@@ -29666,11 +28043,8 @@
       <c r="AJ348">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="AP348">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="349" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="349" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A349" s="1">
         <v>34</v>
       </c>
@@ -29721,11 +28095,8 @@
       <c r="AJ349">
         <v>8.6099999999999996E-2</v>
       </c>
-      <c r="AP349">
-        <v>5.7799999999999997E-2</v>
-      </c>
-    </row>
-    <row r="350" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="350" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A350" s="1">
         <v>35</v>
       </c>
@@ -29776,11 +28147,8 @@
       <c r="AJ350">
         <v>0.13389999999999999</v>
       </c>
-      <c r="AP350">
-        <v>0.96389999999999998</v>
-      </c>
-    </row>
-    <row r="351" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="351" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A351" s="1">
         <v>36</v>
       </c>
@@ -29831,11 +28199,8 @@
       <c r="AJ351">
         <v>0.14510000000000001</v>
       </c>
-      <c r="AP351">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="352" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="352" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A352" s="1">
         <v>37</v>
       </c>
@@ -29886,11 +28251,8 @@
       <c r="AJ352">
         <v>0.12859999999999999</v>
       </c>
-      <c r="AP352">
-        <v>0.98029999999999995</v>
-      </c>
-    </row>
-    <row r="353" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="353" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A353" s="1">
         <v>38</v>
       </c>
@@ -29941,11 +28303,8 @@
       <c r="AJ353">
         <v>0.1171</v>
       </c>
-      <c r="AP353">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="354" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="354" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A354" s="1">
         <v>39</v>
       </c>
@@ -29996,11 +28355,8 @@
       <c r="AJ354">
         <v>0.13020000000000001</v>
       </c>
-      <c r="AP354">
-        <v>0.9728</v>
-      </c>
-    </row>
-    <row r="355" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="355" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A355" s="1">
         <v>40</v>
       </c>
@@ -30051,11 +28407,8 @@
       <c r="AJ355">
         <v>0.13739999999999999</v>
       </c>
-      <c r="AP355">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="356" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A356" s="1">
         <v>41</v>
       </c>
@@ -30106,11 +28459,8 @@
       <c r="AJ356">
         <v>0.1671</v>
       </c>
-      <c r="AP356">
-        <v>0.16059999999999999</v>
-      </c>
-    </row>
-    <row r="357" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="357" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A357" s="1">
         <v>42</v>
       </c>
@@ -30161,11 +28511,8 @@
       <c r="AJ357">
         <v>0.15140000000000001</v>
       </c>
-      <c r="AP357">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="358" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="358" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A358" s="1">
         <v>43</v>
       </c>
@@ -30216,11 +28563,8 @@
       <c r="AJ358">
         <v>0.1288</v>
       </c>
-      <c r="AP358">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="359" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="359" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A359" s="1">
         <v>44</v>
       </c>
@@ -30271,11 +28615,8 @@
       <c r="AJ359">
         <v>0.1283</v>
       </c>
-      <c r="AP359">
-        <v>0.85819999999999996</v>
-      </c>
-    </row>
-    <row r="360" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="360" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A360" s="1">
         <v>45</v>
       </c>
@@ -30326,11 +28667,8 @@
       <c r="AJ360">
         <v>0.1303</v>
       </c>
-      <c r="AP360">
-        <v>0.92979999999999996</v>
-      </c>
-    </row>
-    <row r="361" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="361" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A361" s="1">
         <v>46</v>
       </c>
@@ -30381,11 +28719,8 @@
       <c r="AJ361">
         <v>0.13400000000000001</v>
       </c>
-      <c r="AP361">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="362" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A362" s="1">
         <v>47</v>
       </c>
@@ -30436,11 +28771,8 @@
       <c r="AJ362">
         <v>0.121</v>
       </c>
-      <c r="AP362">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="363" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A363" s="1">
         <v>48</v>
       </c>
@@ -30491,11 +28823,8 @@
       <c r="AJ363">
         <v>0.1263</v>
       </c>
-      <c r="AP363">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="364" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="364" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A364" s="1">
         <v>49</v>
       </c>
@@ -30546,11 +28875,8 @@
       <c r="AJ364">
         <v>0.15870000000000001</v>
       </c>
-      <c r="AP364">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="365" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="365" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A365" s="1">
         <v>50</v>
       </c>
@@ -30601,11 +28927,8 @@
       <c r="AJ365">
         <v>0.11840000000000001</v>
       </c>
-      <c r="AP365">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="366" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="366" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A366" s="1">
         <v>51</v>
       </c>
@@ -30656,11 +28979,8 @@
       <c r="AJ366">
         <v>0.1172</v>
       </c>
-      <c r="AP366">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="367" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="367" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A367" s="1">
         <v>52</v>
       </c>
@@ -30711,11 +29031,8 @@
       <c r="AJ367">
         <v>0.12740000000000001</v>
       </c>
-      <c r="AP367">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="368" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="368" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A368" s="1">
         <v>53</v>
       </c>
@@ -30766,11 +29083,8 @@
       <c r="AJ368">
         <v>0.14549999999999999</v>
       </c>
-      <c r="AP368">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="369" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="369" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A369" s="1">
         <v>54</v>
       </c>
@@ -30821,11 +29135,8 @@
       <c r="AJ369">
         <v>0.15670000000000001</v>
       </c>
-      <c r="AP369">
-        <v>0.44869999999999999</v>
-      </c>
-    </row>
-    <row r="370" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="370" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A370" s="1">
         <v>55</v>
       </c>
@@ -30876,11 +29187,8 @@
       <c r="AJ370">
         <v>0.14949999999999999</v>
       </c>
-      <c r="AP370">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="371" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="371" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A371" s="1">
         <v>56</v>
       </c>
@@ -30931,11 +29239,8 @@
       <c r="AJ371">
         <v>0.13950000000000001</v>
       </c>
-      <c r="AP371">
-        <v>0.99109999999999998</v>
-      </c>
-    </row>
-    <row r="372" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="372" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A372" s="1">
         <v>57</v>
       </c>
@@ -30986,11 +29291,8 @@
       <c r="AJ372">
         <v>0.14030000000000001</v>
       </c>
-      <c r="AP372">
-        <v>0.99280000000000002</v>
-      </c>
-    </row>
-    <row r="373" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="373" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A373" s="1">
         <v>58</v>
       </c>
@@ -31041,11 +29343,8 @@
       <c r="AJ373">
         <v>0.14460000000000001</v>
       </c>
-      <c r="AP373">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="374" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="374" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A374" s="1">
         <v>59</v>
       </c>
@@ -31096,11 +29395,8 @@
       <c r="AJ374">
         <v>0.13350000000000001</v>
       </c>
-      <c r="AP374">
-        <v>0.99560000000000004</v>
-      </c>
-    </row>
-    <row r="375" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="375" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A375" s="1">
         <v>60</v>
       </c>
@@ -31151,11 +29447,8 @@
       <c r="AJ375">
         <v>0.14680000000000001</v>
       </c>
-      <c r="AP375">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="376" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="376" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A376" s="1">
         <v>61</v>
       </c>
@@ -31206,11 +29499,8 @@
       <c r="AJ376">
         <v>0.1588</v>
       </c>
-      <c r="AP376">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="377" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="377" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A377" s="1">
         <v>62</v>
       </c>
@@ -31261,11 +29551,8 @@
       <c r="AJ377">
         <v>0.1366</v>
       </c>
-      <c r="AP377">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="378" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="378" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A378" s="1">
         <v>63</v>
       </c>
@@ -31316,11 +29603,8 @@
       <c r="AJ378">
         <v>0.1356</v>
       </c>
-      <c r="AP378">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="379" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="379" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A379" s="1">
         <v>64</v>
       </c>
@@ -31371,11 +29655,8 @@
       <c r="AJ379">
         <v>0.13420000000000001</v>
       </c>
-      <c r="AP379">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="380" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A380" s="1">
         <v>65</v>
       </c>
@@ -31426,11 +29707,8 @@
       <c r="AJ380">
         <v>0.1333</v>
       </c>
-      <c r="AP380">
-        <v>0.43480000000000002</v>
-      </c>
-    </row>
-    <row r="381" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="381" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A381" s="1">
         <v>66</v>
       </c>
@@ -31481,11 +29759,8 @@
       <c r="AJ381">
         <v>0.13489999999999999</v>
       </c>
-      <c r="AP381">
-        <v>0.96050000000000002</v>
-      </c>
-    </row>
-    <row r="382" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="382" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A382" s="1">
         <v>67</v>
       </c>
@@ -31536,11 +29811,8 @@
       <c r="AJ382">
         <v>0.1318</v>
       </c>
-      <c r="AP382">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="383" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="383" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A383" s="1">
         <v>68</v>
       </c>
@@ -31591,11 +29863,8 @@
       <c r="AJ383">
         <v>0.13800000000000001</v>
       </c>
-      <c r="AP383">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="384" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="384" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A384" s="1">
         <v>69</v>
       </c>
@@ -31646,11 +29915,8 @@
       <c r="AJ384">
         <v>0.1492</v>
       </c>
-      <c r="AP384">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="385" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="385" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A385" s="1">
         <v>70</v>
       </c>
@@ -31701,11 +29967,8 @@
       <c r="AJ385">
         <v>0.1207</v>
       </c>
-      <c r="AP385">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="386" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="386" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A386" s="1">
         <v>71</v>
       </c>
@@ -31756,11 +30019,8 @@
       <c r="AJ386">
         <v>0.1186</v>
       </c>
-      <c r="AP386">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="387" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="387" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A387" s="1">
         <v>72</v>
       </c>
@@ -31811,11 +30071,8 @@
       <c r="AJ387">
         <v>0.13439999999999999</v>
       </c>
-      <c r="AP387">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="388" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="388" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A388" s="1">
         <v>73</v>
       </c>
@@ -31866,11 +30123,8 @@
       <c r="AJ388">
         <v>0.13120000000000001</v>
       </c>
-      <c r="AP388">
-        <v>0.94569999999999999</v>
-      </c>
-    </row>
-    <row r="389" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="389" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A389" s="1">
         <v>74</v>
       </c>
@@ -31921,11 +30175,8 @@
       <c r="AJ389">
         <v>0.1285</v>
       </c>
-      <c r="AP389">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="390" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="390" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A390" s="1">
         <v>75</v>
       </c>
@@ -31976,11 +30227,8 @@
       <c r="AJ390">
         <v>0.13850000000000001</v>
       </c>
-      <c r="AP390">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="391" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="391" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A391" s="1">
         <v>76</v>
       </c>
@@ -32031,11 +30279,8 @@
       <c r="AJ391">
         <v>0.13400000000000001</v>
       </c>
-      <c r="AP391">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="392" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="392" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A392" s="1">
         <v>77</v>
       </c>
@@ -32086,11 +30331,8 @@
       <c r="AJ392">
         <v>0.125</v>
       </c>
-      <c r="AP392">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="393" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="393" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A393" s="1">
         <v>78</v>
       </c>
@@ -32141,11 +30383,8 @@
       <c r="AJ393">
         <v>0.12</v>
       </c>
-      <c r="AP393">
-        <v>0.88859999999999995</v>
-      </c>
-    </row>
-    <row r="394" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="394" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A394" s="1">
         <v>79</v>
       </c>
@@ -32196,11 +30435,8 @@
       <c r="AJ394">
         <v>0.1268</v>
       </c>
-      <c r="AP394">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="395" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="395" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A395" s="1">
         <v>80</v>
       </c>
@@ -32251,11 +30487,8 @@
       <c r="AJ395">
         <v>0.13109999999999999</v>
       </c>
-      <c r="AP395">
-        <v>4.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="396" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="396" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A396" s="1">
         <v>81</v>
       </c>
@@ -32306,11 +30539,8 @@
       <c r="AJ396">
         <v>0.127</v>
       </c>
-      <c r="AP396">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="397" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="397" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A397" s="1">
         <v>82</v>
       </c>
@@ -32361,11 +30591,8 @@
       <c r="AJ397">
         <v>0.12709999999999999</v>
       </c>
-      <c r="AP397">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="398" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="398" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A398" s="1">
         <v>83</v>
       </c>
@@ -32416,11 +30643,8 @@
       <c r="AJ398">
         <v>0.13469999999999999</v>
       </c>
-      <c r="AP398">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="399" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="399" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A399" s="1">
         <v>84</v>
       </c>
@@ -32471,11 +30695,8 @@
       <c r="AJ399">
         <v>0.1192</v>
       </c>
-      <c r="AP399">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="400" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="400" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A400" s="1">
         <v>85</v>
       </c>
@@ -32526,11 +30747,8 @@
       <c r="AJ400">
         <v>0.12959999999999999</v>
       </c>
-      <c r="AP400">
-        <v>0.65390000000000004</v>
-      </c>
-    </row>
-    <row r="401" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="401" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A401" s="1">
         <v>86</v>
       </c>
@@ -32581,11 +30799,8 @@
       <c r="AJ401">
         <v>0.15870000000000001</v>
       </c>
-      <c r="AP401">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="402" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="402" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A402" s="1">
         <v>87</v>
       </c>
@@ -32636,11 +30851,8 @@
       <c r="AJ402">
         <v>0.12189999999999999</v>
       </c>
-      <c r="AP402">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="403" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="403" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A403" s="1">
         <v>88</v>
       </c>
@@ -32691,11 +30903,8 @@
       <c r="AJ403">
         <v>0.12429999999999999</v>
       </c>
-      <c r="AP403">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="404" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="404" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A404" s="1">
         <v>89</v>
       </c>
@@ -32746,11 +30955,8 @@
       <c r="AJ404">
         <v>0.1298</v>
       </c>
-      <c r="AP404">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="405" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="405" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A405" s="1">
         <v>90</v>
       </c>
@@ -32801,11 +31007,8 @@
       <c r="AJ405">
         <v>0.1452</v>
       </c>
-      <c r="AP405">
-        <v>2.3E-3</v>
-      </c>
-    </row>
-    <row r="406" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="406" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A406" s="1">
         <v>91</v>
       </c>
@@ -32856,11 +31059,8 @@
       <c r="AJ406">
         <v>0.1321</v>
       </c>
-      <c r="AP406">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="407" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="407" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A407" s="1">
         <v>92</v>
       </c>
@@ -32911,11 +31111,8 @@
       <c r="AJ407">
         <v>0.13</v>
       </c>
-      <c r="AP407">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="408" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="408" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A408" s="1">
         <v>93</v>
       </c>
@@ -32966,11 +31163,8 @@
       <c r="AJ408">
         <v>0.1172</v>
       </c>
-      <c r="AP408">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="409" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="409" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A409" s="1">
         <v>94</v>
       </c>
@@ -33021,11 +31215,8 @@
       <c r="AJ409">
         <v>0.1208</v>
       </c>
-      <c r="AP409">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="410" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="410" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A410" s="1">
         <v>95</v>
       </c>
@@ -33076,11 +31267,8 @@
       <c r="AJ410">
         <v>0.1293</v>
       </c>
-      <c r="AP410">
-        <v>0.28720000000000001</v>
-      </c>
-    </row>
-    <row r="411" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="411" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A411" s="1">
         <v>96</v>
       </c>
@@ -33131,11 +31319,8 @@
       <c r="AJ411">
         <v>0.12939999999999999</v>
       </c>
-      <c r="AP411">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="412" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="412" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A412" s="1">
         <v>97</v>
       </c>
@@ -33186,11 +31371,8 @@
       <c r="AJ412">
         <v>0.13930000000000001</v>
       </c>
-      <c r="AP412">
-        <v>0.98509999999999998</v>
-      </c>
-    </row>
-    <row r="413" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="413" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A413" s="1">
         <v>98</v>
       </c>
@@ -33241,11 +31423,8 @@
       <c r="AJ413">
         <v>0.12590000000000001</v>
       </c>
-      <c r="AP413">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="414" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="414" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A414" s="1">
         <v>99</v>
       </c>
@@ -33296,11 +31475,8 @@
       <c r="AJ414">
         <v>0.12479999999999999</v>
       </c>
-      <c r="AP414">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="415" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="415" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A415" s="1">
         <v>100</v>
       </c>
@@ -33351,11 +31527,8 @@
       <c r="AJ415">
         <v>0.104</v>
       </c>
-      <c r="AP415">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="416" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="416" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AD416" s="9"/>
       <c r="AE416" s="9"/>
     </row>
@@ -33712,11 +31885,11 @@
       <c r="AE504" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="AI2:AK2"/>
     <mergeCell ref="AP4:AQ4"/>
     <mergeCell ref="T4:U4"/>
-    <mergeCell ref="AI2:AJ2"/>
-    <mergeCell ref="AP3:AQ3"/>
     <mergeCell ref="F2:J2"/>
     <mergeCell ref="T2:W2"/>
     <mergeCell ref="AD3:AF3"/>
@@ -33725,7 +31898,6 @@
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="C2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/CIFAR_Global.xlsx
+++ b/CIFAR_Global.xlsx
@@ -1345,7 +1345,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -1407,7 +1407,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2205,7 +2205,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2267,7 +2267,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2305,7 +2305,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -3431,7 +3431,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -3493,7 +3493,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -3531,7 +3531,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -4658,7 +4658,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -4720,7 +4720,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -4758,7 +4758,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -5560,7 +5560,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -5622,7 +5622,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -5660,7 +5660,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -6791,7 +6791,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -6853,7 +6853,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -6891,7 +6891,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -7688,7 +7688,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -7750,7 +7750,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -7788,7 +7788,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -8575,7 +8575,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -8637,7 +8637,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -8675,7 +8675,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -9594,6 +9594,9 @@
       <c r="AK5" t="n">
         <v>0.1386380281690141</v>
       </c>
+      <c r="AL5" t="n">
+        <v>0.1257924444444445</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -9665,6 +9668,9 @@
       <c r="AK6" t="n">
         <v>0.1263564516129032</v>
       </c>
+      <c r="AL6" t="n">
+        <v>0.2064377777777778</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -9736,6 +9742,9 @@
       <c r="AK7" t="n">
         <v>0.2278352112676056</v>
       </c>
+      <c r="AL7" t="n">
+        <v>0.2912142222222222</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -9807,6 +9816,9 @@
       <c r="AK8" t="n">
         <v>0.3192188405797101</v>
       </c>
+      <c r="AL8" t="n">
+        <v>0.2724973333333334</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -9878,6 +9890,9 @@
       <c r="AK9" t="n">
         <v>0.3822619718309859</v>
       </c>
+      <c r="AL9" t="n">
+        <v>0.4219419354838709</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -9946,6 +9961,9 @@
       <c r="AK10" t="n">
         <v>0.2692161290322581</v>
       </c>
+      <c r="AL10" t="n">
+        <v>0.4521516129032258</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -10014,6 +10032,9 @@
       <c r="AK11" t="n">
         <v>0.4131238095238096</v>
       </c>
+      <c r="AL11" t="n">
+        <v>0.613716129032258</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -10082,6 +10103,9 @@
       <c r="AK12" t="n">
         <v>0.5052111111111111</v>
       </c>
+      <c r="AL12" t="n">
+        <v>0.6452322580645162</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -10150,6 +10174,9 @@
       <c r="AK13" t="n">
         <v>0.5099348484848485</v>
       </c>
+      <c r="AL13" t="n">
+        <v>0.7020000000000001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -10218,6 +10245,9 @@
       <c r="AK14" t="n">
         <v>0.3749688524590164</v>
       </c>
+      <c r="AL14" t="n">
+        <v>0.7480032258064517</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -10280,6 +10310,9 @@
       <c r="AK15" t="n">
         <v>0.4214145161290322</v>
       </c>
+      <c r="AL15" t="n">
+        <v>0.7608903225806452</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -10342,6 +10375,9 @@
       <c r="AK16" t="n">
         <v>0.5007138888888888</v>
       </c>
+      <c r="AL16" t="n">
+        <v>0.7893354838709676</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -10404,6 +10440,9 @@
       <c r="AK17" t="n">
         <v>0.5127846153846154</v>
       </c>
+      <c r="AL17" t="n">
+        <v>0.678616129032258</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -10466,6 +10505,9 @@
       <c r="AK18" t="n">
         <v>0.5511027397260275</v>
       </c>
+      <c r="AL18" t="n">
+        <v>0.799683870967742</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -10528,6 +10570,9 @@
       <c r="AK19" t="n">
         <v>0.5746581081081081</v>
       </c>
+      <c r="AL19" t="n">
+        <v>0.806683870967742</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -10590,6 +10635,9 @@
       <c r="AK20" t="n">
         <v>0.6574028985507248</v>
       </c>
+      <c r="AL20" t="n">
+        <v>0.7787569444444444</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -10652,6 +10700,9 @@
       <c r="AK21" t="n">
         <v>0.6831257575757576</v>
       </c>
+      <c r="AL21" t="n">
+        <v>0.7809166666666667</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -10714,6 +10765,9 @@
       <c r="AK22" t="n">
         <v>0.6550805555555556</v>
       </c>
+      <c r="AL22" t="n">
+        <v>0.7907125000000002</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -10776,6 +10830,9 @@
       <c r="AK23" t="n">
         <v>0.613557627118644</v>
       </c>
+      <c r="AL23" t="n">
+        <v>0.7956861111111111</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -10835,6 +10892,9 @@
       <c r="AK24" t="n">
         <v>0.6791958333333333</v>
       </c>
+      <c r="AL24" t="n">
+        <v>0.70665</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -10897,6 +10957,9 @@
       <c r="AK25" t="n">
         <v>0.7276928571428571</v>
       </c>
+      <c r="AL25" t="n">
+        <v>0.6999527777777778</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -10959,6 +11022,9 @@
       <c r="AK26" t="n">
         <v>0.7134131147540983</v>
       </c>
+      <c r="AL26" t="n">
+        <v>0.7919349397590361</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -11021,6 +11087,9 @@
       <c r="AK27" t="n">
         <v>0.6768915492957748</v>
       </c>
+      <c r="AL27" t="n">
+        <v>0.7334602409638553</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -11083,6 +11152,9 @@
       <c r="AK28" t="n">
         <v>0.7085553571428571</v>
       </c>
+      <c r="AL28" t="n">
+        <v>0.8108012048192771</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -11145,6 +11217,9 @@
       <c r="AK29" t="n">
         <v>0.6852384615384616</v>
       </c>
+      <c r="AL29" t="n">
+        <v>0.8244975903614457</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -11207,6 +11282,9 @@
       <c r="AK30" t="n">
         <v>0.7506045454545455</v>
       </c>
+      <c r="AL30" t="n">
+        <v>0.820410891089109</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -11269,6 +11347,9 @@
       <c r="AK31" t="n">
         <v>0.6440066666666666</v>
       </c>
+      <c r="AL31" t="n">
+        <v>0.8277792079207921</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -11331,6 +11412,9 @@
       <c r="AK32" t="n">
         <v>0.7112148648648648</v>
       </c>
+      <c r="AL32" t="n">
+        <v>0.8313495049504952</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -11393,6 +11477,9 @@
       <c r="AK33" t="n">
         <v>0.6834353846153844</v>
       </c>
+      <c r="AL33" t="n">
+        <v>0.8318485148514851</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -11455,6 +11542,9 @@
       <c r="AK34" t="n">
         <v>0.733590277777778</v>
       </c>
+      <c r="AL34" t="n">
+        <v>0.8316237623762376</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -11517,6 +11607,9 @@
       <c r="AK35" t="n">
         <v>0.7530107692307693</v>
       </c>
+      <c r="AL35" t="n">
+        <v>0.8332514851485149</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -11579,6 +11672,9 @@
       <c r="AK36" t="n">
         <v>0.7217968253968254</v>
       </c>
+      <c r="AL36" t="n">
+        <v>0.8387316831683169</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -11641,6 +11737,9 @@
       <c r="AK37" t="n">
         <v>0.6556320512820513</v>
       </c>
+      <c r="AL37" t="n">
+        <v>0.8406821782178218</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -11703,6 +11802,9 @@
       <c r="AK38" t="n">
         <v>0.7118328358208956</v>
       </c>
+      <c r="AL38" t="n">
+        <v>0.8404247524752473</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -11765,6 +11867,9 @@
       <c r="AK39" t="n">
         <v>0.727708064516129</v>
       </c>
+      <c r="AL39" t="n">
+        <v>0.815509900990099</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -11827,6 +11932,9 @@
       <c r="AK40" t="n">
         <v>0.7886147058823529</v>
       </c>
+      <c r="AL40" t="n">
+        <v>0.759640594059406</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -11889,6 +11997,9 @@
       <c r="AK41" t="n">
         <v>0.730413924050633</v>
       </c>
+      <c r="AL41" t="n">
+        <v>0.8379663366336634</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -11951,6 +12062,9 @@
       <c r="AK42" t="n">
         <v>0.7489522388059702</v>
       </c>
+      <c r="AL42" t="n">
+        <v>0.8441514851485149</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -12013,6 +12127,9 @@
       <c r="AK43" t="n">
         <v>0.8208923076923078</v>
       </c>
+      <c r="AL43" t="n">
+        <v>0.8480742574257425</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -12075,6 +12192,9 @@
       <c r="AK44" t="n">
         <v>0.7826338983050848</v>
       </c>
+      <c r="AL44" t="n">
+        <v>0.8473623762376237</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -12137,6 +12257,9 @@
       <c r="AK45" t="n">
         <v>0.7787951612903227</v>
       </c>
+      <c r="AL45" t="n">
+        <v>0.8486405940594061</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -12199,6 +12322,9 @@
       <c r="AK46" t="n">
         <v>0.7767076923076923</v>
       </c>
+      <c r="AL46" t="n">
+        <v>0.8488920792079209</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -12261,6 +12387,9 @@
       <c r="AK47" t="n">
         <v>0.7021123287671233</v>
       </c>
+      <c r="AL47" t="n">
+        <v>0.8508752475247526</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -12323,6 +12452,9 @@
       <c r="AK48" t="n">
         <v>0.7712261538461539</v>
       </c>
+      <c r="AL48" t="n">
+        <v>0.8473059405940595</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -12385,6 +12517,9 @@
       <c r="AK49" t="n">
         <v>0.7681384615384615</v>
       </c>
+      <c r="AL49" t="n">
+        <v>0.8531970297029702</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -12447,6 +12582,9 @@
       <c r="AK50" t="n">
         <v>0.7171411764705882</v>
       </c>
+      <c r="AL50" t="n">
+        <v>0.8547524752475247</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -12509,6 +12647,9 @@
       <c r="AK51" t="n">
         <v>0.8009735294117647</v>
       </c>
+      <c r="AL51" t="n">
+        <v>0.8533653465346536</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -12571,6 +12712,9 @@
       <c r="AK52" t="n">
         <v>0.7202890410958904</v>
       </c>
+      <c r="AL52" t="n">
+        <v>0.852157425742574</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -12633,6 +12777,9 @@
       <c r="AK53" t="n">
         <v>0.8416580645161291</v>
       </c>
+      <c r="AL53" t="n">
+        <v>0.8567633663366339</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -12695,6 +12842,9 @@
       <c r="AK54" t="n">
         <v>0.7825277777777777</v>
       </c>
+      <c r="AL54" t="n">
+        <v>0.8566742574257424</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -12757,6 +12907,9 @@
       <c r="AK55" t="n">
         <v>0.7369144927536232</v>
       </c>
+      <c r="AL55" t="n">
+        <v>0.857609900990099</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -12819,6 +12972,9 @@
       <c r="AK56" t="n">
         <v>0.7390823529411765</v>
       </c>
+      <c r="AL56" t="n">
+        <v>0.8575356435643562</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -12881,6 +13037,9 @@
       <c r="AK57" t="n">
         <v>0.7775129870129872</v>
       </c>
+      <c r="AL57" t="n">
+        <v>0.8549257425742576</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -12943,6 +13102,9 @@
       <c r="AK58" t="n">
         <v>0.7486031746031747</v>
       </c>
+      <c r="AL58" t="n">
+        <v>0.8533702970297031</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -13005,6 +13167,9 @@
       <c r="AK59" t="n">
         <v>0.7671826086956521</v>
       </c>
+      <c r="AL59" t="n">
+        <v>0.8534118811881187</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -13067,6 +13232,9 @@
       <c r="AK60" t="n">
         <v>0.7363104477611941</v>
       </c>
+      <c r="AL60" t="n">
+        <v>0.8553277227722773</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -13129,6 +13297,9 @@
       <c r="AK61" t="n">
         <v>0.7403500000000001</v>
       </c>
+      <c r="AL61" t="n">
+        <v>0.8560514851485148</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -13191,6 +13362,9 @@
       <c r="AK62" t="n">
         <v>0.7158892307692311</v>
       </c>
+      <c r="AL62" t="n">
+        <v>0.8540465346534654</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -13253,6 +13427,9 @@
       <c r="AK63" t="n">
         <v>0.7896105263157897</v>
       </c>
+      <c r="AL63" t="n">
+        <v>0.8577435643564357</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -13315,6 +13492,9 @@
       <c r="AK64" t="n">
         <v>0.814346875</v>
       </c>
+      <c r="AL64" t="n">
+        <v>0.8582801980198017</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -13377,6 +13557,9 @@
       <c r="AK65" t="n">
         <v>0.8171692307692306</v>
       </c>
+      <c r="AL65" t="n">
+        <v>0.8607544554455445</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -13439,6 +13622,9 @@
       <c r="AK66" t="n">
         <v>0.8209578125</v>
       </c>
+      <c r="AL66" t="n">
+        <v>0.8574138613861384</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -13501,6 +13687,9 @@
       <c r="AK67" t="n">
         <v>0.761528813559322</v>
       </c>
+      <c r="AL67" t="n">
+        <v>0.8573910891089108</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -13563,6 +13752,9 @@
       <c r="AK68" t="n">
         <v>0.7867015625000001</v>
       </c>
+      <c r="AL68" t="n">
+        <v>0.8564237623762374</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -13625,6 +13817,9 @@
       <c r="AK69" t="n">
         <v>0.7044828124999999</v>
       </c>
+      <c r="AL69" t="n">
+        <v>0.8576514851485149</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -13687,6 +13882,9 @@
       <c r="AK70" t="n">
         <v>0.7776037974683545</v>
       </c>
+      <c r="AL70" t="n">
+        <v>0.8563851485148515</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -13749,6 +13947,9 @@
       <c r="AK71" t="n">
         <v>0.7818285714285714</v>
       </c>
+      <c r="AL71" t="n">
+        <v>0.8533762376237624</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -13811,6 +14012,9 @@
       <c r="AK72" t="n">
         <v>0.8061909090909091</v>
       </c>
+      <c r="AL72" t="n">
+        <v>0.8248316831683168</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -13873,6 +14077,9 @@
       <c r="AK73" t="n">
         <v>0.7662701492537314</v>
       </c>
+      <c r="AL73" t="n">
+        <v>0.8533960396039604</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -13935,6 +14142,9 @@
       <c r="AK74" t="n">
         <v>0.7658607594936709</v>
       </c>
+      <c r="AL74" t="n">
+        <v>0.8568435643564355</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -13997,6 +14207,9 @@
       <c r="AK75" t="n">
         <v>0.7839774647887323</v>
       </c>
+      <c r="AL75" t="n">
+        <v>0.8583366336633663</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -14059,6 +14272,9 @@
       <c r="AK76" t="n">
         <v>0.8069718309859155</v>
       </c>
+      <c r="AL76" t="n">
+        <v>0.8568079207920793</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -14121,6 +14337,9 @@
       <c r="AK77" t="n">
         <v>0.7310378787878788</v>
       </c>
+      <c r="AL77" t="n">
+        <v>0.8567465346534653</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -14183,6 +14402,9 @@
       <c r="AK78" t="n">
         <v>0.8205750000000001</v>
       </c>
+      <c r="AL78" t="n">
+        <v>0.8502207920792079</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -14245,6 +14467,9 @@
       <c r="AK79" t="n">
         <v>0.7998083333333335</v>
       </c>
+      <c r="AL79" t="n">
+        <v>0.8551613861386139</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -14307,6 +14532,9 @@
       <c r="AK80" t="n">
         <v>0.7687053333333332</v>
       </c>
+      <c r="AL80" t="n">
+        <v>0.8564306930693069</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -14369,6 +14597,9 @@
       <c r="AK81" t="n">
         <v>0.7361242424242423</v>
       </c>
+      <c r="AL81" t="n">
+        <v>0.8601782178217823</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -14431,6 +14662,9 @@
       <c r="AK82" t="n">
         <v>0.7815644736842104</v>
       </c>
+      <c r="AL82" t="n">
+        <v>0.8631752475247524</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -14493,6 +14727,9 @@
       <c r="AK83" t="n">
         <v>0.7586675675675676</v>
       </c>
+      <c r="AL83" t="n">
+        <v>0.860357425742574</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -14555,6 +14792,9 @@
       <c r="AK84" t="n">
         <v>0.7499753424657535</v>
       </c>
+      <c r="AL84" t="n">
+        <v>0.8586079207920793</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -14617,6 +14857,9 @@
       <c r="AK85" t="n">
         <v>0.7529120481927711</v>
       </c>
+      <c r="AL85" t="n">
+        <v>0.860190099009901</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -14679,6 +14922,9 @@
       <c r="AK86" t="n">
         <v>0.822119696969697</v>
       </c>
+      <c r="AL86" t="n">
+        <v>0.8616356435643563</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -14741,6 +14987,9 @@
       <c r="AK87" t="n">
         <v>0.7708620253164559</v>
       </c>
+      <c r="AL87" t="n">
+        <v>0.8628950495049506</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -14803,6 +15052,9 @@
       <c r="AK88" t="n">
         <v>0.7890983333333333</v>
       </c>
+      <c r="AL88" t="n">
+        <v>0.8622138613861385</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -14865,6 +15117,9 @@
       <c r="AK89" t="n">
         <v>0.7864472222222223</v>
       </c>
+      <c r="AL89" t="n">
+        <v>0.8618584158415841</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -14927,6 +15182,9 @@
       <c r="AK90" t="n">
         <v>0.8617999999999999</v>
       </c>
+      <c r="AL90" t="n">
+        <v>0.8626693069306932</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -14989,6 +15247,9 @@
       <c r="AK91" t="n">
         <v>0.7949593749999999</v>
       </c>
+      <c r="AL91" t="n">
+        <v>0.863278217821782</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -15051,6 +15312,9 @@
       <c r="AK92" t="n">
         <v>0.7444309859154931</v>
       </c>
+      <c r="AL92" t="n">
+        <v>0.8649485148514851</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -15113,6 +15377,9 @@
       <c r="AK93" t="n">
         <v>0.7964983606557376</v>
       </c>
+      <c r="AL93" t="n">
+        <v>0.8657425742574256</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -15175,6 +15442,9 @@
       <c r="AK94" t="n">
         <v>0.7408680555555555</v>
       </c>
+      <c r="AL94" t="n">
+        <v>0.8632188118811879</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -15237,6 +15507,9 @@
       <c r="AK95" t="n">
         <v>0.7842112676056338</v>
       </c>
+      <c r="AL95" t="n">
+        <v>0.8626455445544554</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -15299,6 +15572,9 @@
       <c r="AK96" t="n">
         <v>0.7533506849315068</v>
       </c>
+      <c r="AL96" t="n">
+        <v>0.8630930693069305</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -15361,6 +15637,9 @@
       <c r="AK97" t="n">
         <v>0.7617279411764707</v>
       </c>
+      <c r="AL97" t="n">
+        <v>0.8640217821782178</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -15423,6 +15702,9 @@
       <c r="AK98" t="n">
         <v>0.8191549295774647</v>
       </c>
+      <c r="AL98" t="n">
+        <v>0.8638712871287128</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -15485,6 +15767,9 @@
       <c r="AK99" t="n">
         <v>0.7839013888888888</v>
       </c>
+      <c r="AL99" t="n">
+        <v>0.8640188118811879</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -15547,6 +15832,9 @@
       <c r="AK100" t="n">
         <v>0.7579888888888889</v>
       </c>
+      <c r="AL100" t="n">
+        <v>0.8624108910891091</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -15609,6 +15897,9 @@
       <c r="AK101" t="n">
         <v>0.7934216216216218</v>
       </c>
+      <c r="AL101" t="n">
+        <v>0.8657178217821783</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -15671,6 +15962,9 @@
       <c r="AK102" t="n">
         <v>0.8001478873239436</v>
       </c>
+      <c r="AL102" t="n">
+        <v>0.8638841584158417</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -15733,6 +16027,9 @@
       <c r="AK103" t="n">
         <v>0.7302142857142857</v>
       </c>
+      <c r="AL103" t="n">
+        <v>0.8634346534653465</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -15794,6 +16091,9 @@
       </c>
       <c r="AK104" t="n">
         <v>0.7005187500000001</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>0.8626009900990097</v>
       </c>
     </row>
     <row r="105">
@@ -15901,6 +16201,9 @@
       <c r="AK108" t="n">
         <v>0.8666666666666667</v>
       </c>
+      <c r="AL108" t="n">
+        <v>0.9333333333333333</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -15965,6 +16268,9 @@
       <c r="AK109" t="n">
         <v>0.6666666666666666</v>
       </c>
+      <c r="AL109" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -16029,6 +16335,9 @@
       <c r="AK110" t="n">
         <v>0.1333333333333333</v>
       </c>
+      <c r="AL110" t="n">
+        <v>0.7333333333333333</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -16093,6 +16402,9 @@
       <c r="AK111" t="n">
         <v>0.6666666666666666</v>
       </c>
+      <c r="AL111" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -16157,6 +16469,9 @@
       <c r="AK112" t="n">
         <v>0.8</v>
       </c>
+      <c r="AL112" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -16218,6 +16533,9 @@
       <c r="AK113" t="n">
         <v>0.5333333333333333</v>
       </c>
+      <c r="AL113" t="n">
+        <v>0.3846153846153846</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -16279,6 +16597,9 @@
       <c r="AK114" t="n">
         <v>0.6</v>
       </c>
+      <c r="AL114" t="n">
+        <v>0.5833333333333334</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -16340,6 +16661,9 @@
       <c r="AK115" t="n">
         <v>0.5</v>
       </c>
+      <c r="AL115" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -16401,6 +16725,9 @@
       <c r="AK116" t="n">
         <v>0.6</v>
       </c>
+      <c r="AL116" t="n">
+        <v>0.8181818181818182</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -16462,6 +16789,9 @@
       <c r="AK117" t="n">
         <v>0.5333333333333333</v>
       </c>
+      <c r="AL117" t="n">
+        <v>0.7692307692307693</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -16517,6 +16847,9 @@
       <c r="AK118" t="n">
         <v>0.5714285714285714</v>
       </c>
+      <c r="AL118" t="n">
+        <v>0.9166666666666666</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -16572,6 +16905,9 @@
       <c r="AK119" t="n">
         <v>0.5333333333333333</v>
       </c>
+      <c r="AL119" t="n">
+        <v>0.7692307692307693</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -16627,6 +16963,9 @@
       <c r="AK120" t="n">
         <v>0.5333333333333333</v>
       </c>
+      <c r="AL120" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -16682,6 +17021,9 @@
       <c r="AK121" t="n">
         <v>0.6666666666666666</v>
       </c>
+      <c r="AL121" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -16737,6 +17079,9 @@
       <c r="AK122" t="n">
         <v>0.5333333333333333</v>
       </c>
+      <c r="AL122" t="n">
+        <v>0.6428571428571429</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -16792,6 +17137,9 @@
       <c r="AK123" t="n">
         <v>0.5333333333333333</v>
       </c>
+      <c r="AL123" t="n">
+        <v>0.9166666666666666</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -16847,6 +17195,9 @@
       <c r="AK124" t="n">
         <v>0.6</v>
       </c>
+      <c r="AL124" t="n">
+        <v>0.6428571428571429</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -16902,6 +17253,9 @@
       <c r="AK125" t="n">
         <v>0.5333333333333333</v>
       </c>
+      <c r="AL125" t="n">
+        <v>0.5714285714285714</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -16957,6 +17311,9 @@
       <c r="AK126" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="AL126" t="n">
+        <v>0.7272727272727273</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -17012,6 +17369,9 @@
       <c r="AK127" t="n">
         <v>0.8571428571428571</v>
       </c>
+      <c r="AL127" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -17067,6 +17427,9 @@
       <c r="AK128" t="n">
         <v>0.5714285714285714</v>
       </c>
+      <c r="AL128" t="n">
+        <v>0.4545454545454545</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -17122,6 +17485,9 @@
       <c r="AK129" t="n">
         <v>0.5714285714285714</v>
       </c>
+      <c r="AL129" t="n">
+        <v>0.9230769230769231</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -17177,6 +17543,9 @@
       <c r="AK130" t="n">
         <v>0.5333333333333333</v>
       </c>
+      <c r="AL130" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -17232,6 +17601,9 @@
       <c r="AK131" t="n">
         <v>0.6153846153846154</v>
       </c>
+      <c r="AL131" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -17287,6 +17659,9 @@
       <c r="AK132" t="n">
         <v>0.4615384615384616</v>
       </c>
+      <c r="AL132" t="n">
+        <v>0.8181818181818182</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -17342,6 +17717,9 @@
       <c r="AK133" t="n">
         <v>0.6</v>
       </c>
+      <c r="AL133" t="n">
+        <v>0.875</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -17397,6 +17775,9 @@
       <c r="AK134" t="n">
         <v>0.5</v>
       </c>
+      <c r="AL134" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -17452,6 +17833,9 @@
       <c r="AK135" t="n">
         <v>0.5714285714285714</v>
       </c>
+      <c r="AL135" t="n">
+        <v>0.8181818181818182</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -17507,6 +17891,9 @@
       <c r="AK136" t="n">
         <v>0.4615384615384616</v>
       </c>
+      <c r="AL136" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -17562,6 +17949,9 @@
       <c r="AK137" t="n">
         <v>0.5</v>
       </c>
+      <c r="AL137" t="n">
+        <v>0.9090909090909091</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -17617,6 +18007,9 @@
       <c r="AK138" t="n">
         <v>0.5384615384615384</v>
       </c>
+      <c r="AL138" t="n">
+        <v>0.9166666666666666</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -17672,6 +18065,9 @@
       <c r="AK139" t="n">
         <v>0.7142857142857143</v>
       </c>
+      <c r="AL139" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -17727,6 +18123,9 @@
       <c r="AK140" t="n">
         <v>0.7333333333333333</v>
       </c>
+      <c r="AL140" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -17782,6 +18181,9 @@
       <c r="AK141" t="n">
         <v>0.6</v>
       </c>
+      <c r="AL141" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -17837,6 +18239,9 @@
       <c r="AK142" t="n">
         <v>0.6</v>
       </c>
+      <c r="AL142" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -17892,6 +18297,9 @@
       <c r="AK143" t="n">
         <v>0.4615384615384616</v>
       </c>
+      <c r="AL143" t="n">
+        <v>0.1666666666666667</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -17947,6 +18355,9 @@
       <c r="AK144" t="n">
         <v>0.4285714285714285</v>
       </c>
+      <c r="AL144" t="n">
+        <v>0.875</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -18002,6 +18413,9 @@
       <c r="AK145" t="n">
         <v>0.5714285714285714</v>
       </c>
+      <c r="AL145" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -18057,6 +18471,9 @@
       <c r="AK146" t="n">
         <v>0.6153846153846154</v>
       </c>
+      <c r="AL146" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -18112,6 +18529,9 @@
       <c r="AK147" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="AL147" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -18167,6 +18587,9 @@
       <c r="AK148" t="n">
         <v>0.6666666666666666</v>
       </c>
+      <c r="AL148" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -18222,6 +18645,9 @@
       <c r="AK149" t="n">
         <v>0.6666666666666666</v>
       </c>
+      <c r="AL149" t="n">
+        <v>0.875</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -18277,6 +18703,9 @@
       <c r="AK150" t="n">
         <v>0.8666666666666667</v>
       </c>
+      <c r="AL150" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -18332,6 +18761,9 @@
       <c r="AK151" t="n">
         <v>0.6</v>
       </c>
+      <c r="AL151" t="n">
+        <v>0.7777777777777778</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -18387,6 +18819,9 @@
       <c r="AK152" t="n">
         <v>0.6428571428571429</v>
       </c>
+      <c r="AL152" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -18442,6 +18877,9 @@
       <c r="AK153" t="n">
         <v>0.6923076923076923</v>
       </c>
+      <c r="AL153" t="n">
+        <v>0.8181818181818182</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -18497,6 +18935,9 @@
       <c r="AK154" t="n">
         <v>0.8571428571428571</v>
       </c>
+      <c r="AL154" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -18552,6 +18993,9 @@
       <c r="AK155" t="n">
         <v>0.6428571428571429</v>
       </c>
+      <c r="AL155" t="n">
+        <v>0.7777777777777778</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -18607,6 +19051,9 @@
       <c r="AK156" t="n">
         <v>0.5833333333333334</v>
       </c>
+      <c r="AL156" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -18662,6 +19109,9 @@
       <c r="AK157" t="n">
         <v>0.6923076923076923</v>
       </c>
+      <c r="AL157" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -18717,6 +19167,9 @@
       <c r="AK158" t="n">
         <v>0.5714285714285714</v>
       </c>
+      <c r="AL158" t="n">
+        <v>0.9090909090909091</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -18772,6 +19225,9 @@
       <c r="AK159" t="n">
         <v>0.4285714285714285</v>
       </c>
+      <c r="AL159" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -18827,6 +19283,9 @@
       <c r="AK160" t="n">
         <v>0.6</v>
       </c>
+      <c r="AL160" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -18882,6 +19341,9 @@
       <c r="AK161" t="n">
         <v>0.5714285714285714</v>
       </c>
+      <c r="AL161" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -18937,6 +19399,9 @@
       <c r="AK162" t="n">
         <v>0.5714285714285714</v>
       </c>
+      <c r="AL162" t="n">
+        <v>0.8181818181818182</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -18992,6 +19457,9 @@
       <c r="AK163" t="n">
         <v>0.2857142857142857</v>
       </c>
+      <c r="AL163" t="n">
+        <v>0.7142857142857143</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -19047,6 +19515,9 @@
       <c r="AK164" t="n">
         <v>0.3846153846153846</v>
       </c>
+      <c r="AL164" t="n">
+        <v>0.9166666666666666</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -19102,6 +19573,9 @@
       <c r="AK165" t="n">
         <v>0.6</v>
       </c>
+      <c r="AL165" t="n">
+        <v>0.7777777777777778</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -19157,6 +19631,9 @@
       <c r="AK166" t="n">
         <v>0.6153846153846154</v>
       </c>
+      <c r="AL166" t="n">
+        <v>0.7777777777777778</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -19212,6 +19689,9 @@
       <c r="AK167" t="n">
         <v>0.5714285714285714</v>
       </c>
+      <c r="AL167" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -19267,6 +19747,9 @@
       <c r="AK168" t="n">
         <v>0.6923076923076923</v>
       </c>
+      <c r="AL168" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -19322,6 +19805,9 @@
       <c r="AK169" t="n">
         <v>0.5833333333333334</v>
       </c>
+      <c r="AL169" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -19377,6 +19863,9 @@
       <c r="AK170" t="n">
         <v>0.5384615384615384</v>
       </c>
+      <c r="AL170" t="n">
+        <v>0.7777777777777778</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -19432,6 +19921,9 @@
       <c r="AK171" t="n">
         <v>0.5</v>
       </c>
+      <c r="AL171" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -19487,6 +19979,9 @@
       <c r="AK172" t="n">
         <v>0.5714285714285714</v>
       </c>
+      <c r="AL172" t="n">
+        <v>0.8181818181818182</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -19542,6 +20037,9 @@
       <c r="AK173" t="n">
         <v>0.5384615384615384</v>
       </c>
+      <c r="AL173" t="n">
+        <v>0.2727272727272727</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -19597,6 +20095,9 @@
       <c r="AK174" t="n">
         <v>0.7142857142857143</v>
       </c>
+      <c r="AL174" t="n">
+        <v>0.2727272727272727</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -19652,6 +20153,9 @@
       <c r="AK175" t="n">
         <v>0.6153846153846154</v>
       </c>
+      <c r="AL175" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -19707,6 +20211,9 @@
       <c r="AK176" t="n">
         <v>0.3333333333333333</v>
       </c>
+      <c r="AL176" t="n">
+        <v>0.7777777777777778</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -19762,6 +20269,9 @@
       <c r="AK177" t="n">
         <v>0.5384615384615384</v>
       </c>
+      <c r="AL177" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -19817,6 +20327,9 @@
       <c r="AK178" t="n">
         <v>0.5833333333333334</v>
       </c>
+      <c r="AL178" t="n">
+        <v>0.8571428571428571</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -19872,6 +20385,9 @@
       <c r="AK179" t="n">
         <v>1</v>
       </c>
+      <c r="AL179" t="n">
+        <v>0.1818181818181818</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -19927,6 +20443,9 @@
       <c r="AK180" t="n">
         <v>0.6428571428571429</v>
       </c>
+      <c r="AL180" t="n">
+        <v>0.8181818181818182</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -19982,6 +20501,9 @@
       <c r="AK181" t="n">
         <v>0.4615384615384616</v>
       </c>
+      <c r="AL181" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -20037,6 +20559,9 @@
       <c r="AK182" t="n">
         <v>0.6153846153846154</v>
       </c>
+      <c r="AL182" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -20092,6 +20617,9 @@
       <c r="AK183" t="n">
         <v>0.4</v>
       </c>
+      <c r="AL183" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -20147,6 +20675,9 @@
       <c r="AK184" t="n">
         <v>0.3846153846153846</v>
       </c>
+      <c r="AL184" t="n">
+        <v>0.8181818181818182</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -20202,6 +20733,9 @@
       <c r="AK185" t="n">
         <v>0.5384615384615384</v>
       </c>
+      <c r="AL185" t="n">
+        <v>0.8571428571428571</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -20257,6 +20791,9 @@
       <c r="AK186" t="n">
         <v>0.3076923076923077</v>
       </c>
+      <c r="AL186" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -20312,6 +20849,9 @@
       <c r="AK187" t="n">
         <v>0.6428571428571429</v>
       </c>
+      <c r="AL187" t="n">
+        <v>0.7777777777777778</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -20367,6 +20907,9 @@
       <c r="AK188" t="n">
         <v>0.5384615384615384</v>
       </c>
+      <c r="AL188" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
@@ -20422,6 +20965,9 @@
       <c r="AK189" t="n">
         <v>0.7142857142857143</v>
       </c>
+      <c r="AL189" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -20477,6 +21023,9 @@
       <c r="AK190" t="n">
         <v>1</v>
       </c>
+      <c r="AL190" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -20532,6 +21081,9 @@
       <c r="AK191" t="n">
         <v>0.5714285714285714</v>
       </c>
+      <c r="AL191" t="n">
+        <v>0.9090909090909091</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -20587,6 +21139,9 @@
       <c r="AK192" t="n">
         <v>0.6153846153846154</v>
       </c>
+      <c r="AL192" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -20642,6 +21197,9 @@
       <c r="AK193" t="n">
         <v>0.5333333333333333</v>
       </c>
+      <c r="AL193" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -20697,6 +21255,9 @@
       <c r="AK194" t="n">
         <v>0.5384615384615384</v>
       </c>
+      <c r="AL194" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -20752,6 +21313,9 @@
       <c r="AK195" t="n">
         <v>0.7142857142857143</v>
       </c>
+      <c r="AL195" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -20807,6 +21371,9 @@
       <c r="AK196" t="n">
         <v>0.4285714285714285</v>
       </c>
+      <c r="AL196" t="n">
+        <v>0.9166666666666666</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -20862,6 +21429,9 @@
       <c r="AK197" t="n">
         <v>0.6153846153846154</v>
       </c>
+      <c r="AL197" t="n">
+        <v>0.8181818181818182</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
@@ -20917,6 +21487,9 @@
       <c r="AK198" t="n">
         <v>0.5833333333333334</v>
       </c>
+      <c r="AL198" t="n">
+        <v>0.8571428571428571</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
@@ -20972,6 +21545,9 @@
       <c r="AK199" t="n">
         <v>0.3571428571428572</v>
       </c>
+      <c r="AL199" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
@@ -21027,6 +21603,9 @@
       <c r="AK200" t="n">
         <v>0.2857142857142857</v>
       </c>
+      <c r="AL200" t="n">
+        <v>0.8888888888888888</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -21082,6 +21661,9 @@
       <c r="AK201" t="n">
         <v>0.4545454545454545</v>
       </c>
+      <c r="AL201" t="n">
+        <v>0.7272727272727273</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
@@ -21137,6 +21719,9 @@
       <c r="AK202" t="n">
         <v>0.5</v>
       </c>
+      <c r="AL202" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
@@ -21192,6 +21777,9 @@
       <c r="AK203" t="n">
         <v>0.5333333333333333</v>
       </c>
+      <c r="AL203" t="n">
+        <v>0.9090909090909091</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -21247,6 +21835,9 @@
       <c r="AK204" t="n">
         <v>0.4</v>
       </c>
+      <c r="AL204" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
@@ -21302,6 +21893,9 @@
       <c r="AK205" t="n">
         <v>0.6</v>
       </c>
+      <c r="AL205" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -21357,6 +21951,9 @@
       <c r="AK206" t="n">
         <v>0.6153846153846154</v>
       </c>
+      <c r="AL206" t="n">
+        <v>0.8181818181818182</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
@@ -21411,6 +22008,9 @@
       </c>
       <c r="AK207" t="n">
         <v>0.5714285714285714</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="208">
@@ -21522,6 +22122,9 @@
       <c r="AK212" t="n">
         <v>0.9234142857142859</v>
       </c>
+      <c r="AL212" t="n">
+        <v>0.931325</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -21586,6 +22189,9 @@
       <c r="AK213" t="n">
         <v>0.928675</v>
       </c>
+      <c r="AL213" t="n">
+        <v>0.93224</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
@@ -21650,6 +22256,9 @@
       <c r="AK214" t="n">
         <v>0.9277166666666665</v>
       </c>
+      <c r="AL214" t="n">
+        <v>0.9252600000000001</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
@@ -21714,6 +22323,9 @@
       <c r="AK215" t="n">
         <v>0.9521500000000001</v>
       </c>
+      <c r="AL215" t="n">
+        <v>0.8901000000000001</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
@@ -21778,6 +22390,9 @@
       <c r="AK216" t="n">
         <v>0.96014</v>
       </c>
+      <c r="AL216" t="n">
+        <v>0.9435428571428572</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
@@ -21839,6 +22454,9 @@
       <c r="AK217" t="n">
         <v>0.9616999999999999</v>
       </c>
+      <c r="AL217" t="n">
+        <v>0.9278666666666666</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
@@ -21900,6 +22518,9 @@
       <c r="AK218" t="n">
         <v>0.9511142857142857</v>
       </c>
+      <c r="AL218" t="n">
+        <v>0.9022999999999999</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
@@ -21963,6 +22584,9 @@
       <c r="AK219" t="n">
         <v>0.9538142857142857</v>
       </c>
+      <c r="AL219" t="n">
+        <v>0.8905999999999999</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
@@ -22026,6 +22650,9 @@
       <c r="AK220" t="n">
         <v>0.9679399999999999</v>
       </c>
+      <c r="AL220" t="n">
+        <v>0.9401833333333333</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -22087,6 +22714,9 @@
       <c r="AK221" t="n">
         <v>0.9442142857142857</v>
       </c>
+      <c r="AL221" t="n">
+        <v>0.91234</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
@@ -22142,6 +22772,9 @@
       <c r="AK222" t="n">
         <v>0.8791375</v>
       </c>
+      <c r="AL222" t="n">
+        <v>0.9351</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
@@ -22197,6 +22830,9 @@
       <c r="AK223" t="n">
         <v>0.941342857142857</v>
       </c>
+      <c r="AL223" t="n">
+        <v>0.9156599999999999</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
@@ -22252,6 +22888,9 @@
       <c r="AK224" t="n">
         <v>0.9188166666666667</v>
       </c>
+      <c r="AL224" t="n">
+        <v>0.8979857142857143</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
@@ -22307,6 +22946,9 @@
       <c r="AK225" t="n">
         <v>0.944742857142857</v>
       </c>
+      <c r="AL225" t="n">
+        <v>0.8933444444444445</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
@@ -22362,6 +23004,9 @@
       <c r="AK226" t="n">
         <v>0.9272666666666666</v>
       </c>
+      <c r="AL226" t="n">
+        <v>0.9359000000000001</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
@@ -22417,6 +23062,9 @@
       <c r="AK227" t="n">
         <v>0.9517166666666667</v>
       </c>
+      <c r="AL227" t="n">
+        <v>0.9597000000000001</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
@@ -22472,6 +23120,9 @@
       <c r="AK228" t="n">
         <v>0.9434666666666667</v>
       </c>
+      <c r="AL228" t="n">
+        <v>0.9311000000000001</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
@@ -22527,6 +23178,9 @@
       <c r="AK229" t="n">
         <v>0.9695999999999999</v>
       </c>
+      <c r="AL229" t="n">
+        <v>0.9164571428571427</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
@@ -22582,6 +23236,9 @@
       <c r="AK230" t="n">
         <v>0.9595166666666667</v>
       </c>
+      <c r="AL230" t="n">
+        <v>0.9412714285714285</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
@@ -22637,6 +23294,9 @@
       <c r="AK231" t="n">
         <v>0.9349333333333334</v>
       </c>
+      <c r="AL231" t="n">
+        <v>0.9440875</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
@@ -22692,6 +23352,9 @@
       <c r="AK232" t="n">
         <v>0.9292285714285714</v>
       </c>
+      <c r="AL232" t="n">
+        <v>0.9350625000000001</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
@@ -22747,6 +23410,9 @@
       <c r="AK233" t="n">
         <v>0.9402666666666666</v>
       </c>
+      <c r="AL233" t="n">
+        <v>0.9423499999999999</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
@@ -22802,6 +23468,9 @@
       <c r="AK234" t="n">
         <v>0.9615499999999999</v>
       </c>
+      <c r="AL234" t="n">
+        <v>0.9471857142857143</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
@@ -22857,6 +23526,9 @@
       <c r="AK235" t="n">
         <v>0.9381857142857143</v>
       </c>
+      <c r="AL235" t="n">
+        <v>0.93145</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
@@ -22912,6 +23584,9 @@
       <c r="AK236" t="n">
         <v>0.9203714285714286</v>
       </c>
+      <c r="AL236" t="n">
+        <v>0.8386166666666667</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
@@ -22967,6 +23642,9 @@
       <c r="AK237" t="n">
         <v>0.9512999999999999</v>
       </c>
+      <c r="AL237" t="n">
+        <v>0.8813111111111112</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
@@ -23022,6 +23700,9 @@
       <c r="AK238" t="n">
         <v>0.955557142857143</v>
       </c>
+      <c r="AL238" t="n">
+        <v>0.9318166666666667</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
@@ -23077,6 +23758,9 @@
       <c r="AK239" t="n">
         <v>0.90438</v>
       </c>
+      <c r="AL239" t="n">
+        <v>0.9227000000000001</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
@@ -23132,6 +23816,9 @@
       <c r="AK240" t="n">
         <v>0.9602749999999999</v>
       </c>
+      <c r="AL240" t="n">
+        <v>0.9375</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
@@ -23187,6 +23874,9 @@
       <c r="AK241" t="n">
         <v>0.9457</v>
       </c>
+      <c r="AL241" t="n">
+        <v>0.92286</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
@@ -23242,6 +23932,9 @@
       <c r="AK242" t="n">
         <v>0.956225</v>
       </c>
+      <c r="AL242" t="n">
+        <v>0.916075</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
@@ -23297,6 +23990,9 @@
       <c r="AK243" t="n">
         <v>0.9604199999999998</v>
       </c>
+      <c r="AL243" t="n">
+        <v>0.85334</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
@@ -23352,6 +24048,9 @@
       <c r="AK244" t="n">
         <v>0.9639999999999999</v>
       </c>
+      <c r="AL244" t="n">
+        <v>0.9238499999999999</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
@@ -23407,6 +24106,9 @@
       <c r="AK245" t="n">
         <v>0.9513750000000001</v>
       </c>
+      <c r="AL245" t="n">
+        <v>0.9060400000000002</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
@@ -23462,6 +24164,9 @@
       <c r="AK246" t="n">
         <v>0.9569333333333333</v>
       </c>
+      <c r="AL246" t="n">
+        <v>0.9267</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
@@ -23517,6 +24222,9 @@
       <c r="AK247" t="n">
         <v>0.9393888888888888</v>
       </c>
+      <c r="AL247" t="n">
+        <v>0.922175</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
@@ -23572,6 +24280,9 @@
       <c r="AK248" t="n">
         <v>0.9691</v>
       </c>
+      <c r="AL248" t="n">
+        <v>0.8397857142857142</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
@@ -23627,6 +24338,9 @@
       <c r="AK249" t="n">
         <v>0.9608166666666667</v>
       </c>
+      <c r="AL249" t="n">
+        <v>0.9059333333333334</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
@@ -23682,6 +24396,9 @@
       <c r="AK250" t="n">
         <v>0.9698285714285715</v>
       </c>
+      <c r="AL250" t="n">
+        <v>0.908</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
@@ -23737,6 +24454,9 @@
       <c r="AK251" t="n">
         <v>0.9695714285714285</v>
       </c>
+      <c r="AL251" t="n">
+        <v>0.9016999999999999</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
@@ -23792,6 +24512,9 @@
       <c r="AK252" t="n">
         <v>0.9761666666666667</v>
       </c>
+      <c r="AL252" t="n">
+        <v>0.90358</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
@@ -23847,6 +24570,9 @@
       <c r="AK253" t="n">
         <v>0.9565857142857144</v>
       </c>
+      <c r="AL253" t="n">
+        <v>0.9084142857142857</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
@@ -23902,6 +24628,9 @@
       <c r="AK254" t="n">
         <v>0.96565</v>
       </c>
+      <c r="AL254" t="n">
+        <v>0.9245000000000001</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
@@ -23957,6 +24686,9 @@
       <c r="AK255" t="n">
         <v>0.9622000000000001</v>
       </c>
+      <c r="AL255" t="n">
+        <v>0.9242</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
@@ -24012,6 +24744,9 @@
       <c r="AK256" t="n">
         <v>0.971525</v>
       </c>
+      <c r="AL256" t="n">
+        <v>0.9340000000000001</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
@@ -24067,6 +24802,9 @@
       <c r="AK257" t="n">
         <v>0.8904000000000001</v>
       </c>
+      <c r="AL257" t="n">
+        <v>0.93344</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
@@ -24122,6 +24860,9 @@
       <c r="AK258" t="n">
         <v>0.9167500000000001</v>
       </c>
+      <c r="AL258" t="n">
+        <v>0.9218374999999999</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
@@ -24177,6 +24918,9 @@
       <c r="AK259" t="n">
         <v>0.9031666666666668</v>
       </c>
+      <c r="AL259" t="n">
+        <v>0.9323714285714286</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
@@ -24232,6 +24976,9 @@
       <c r="AK260" t="n">
         <v>0.9232624999999999</v>
       </c>
+      <c r="AL260" t="n">
+        <v>0.9307</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
@@ -24287,6 +25034,9 @@
       <c r="AK261" t="n">
         <v>0.9395625000000001</v>
       </c>
+      <c r="AL261" t="n">
+        <v>0.9276857142857142</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
@@ -24342,6 +25092,9 @@
       <c r="AK262" t="n">
         <v>0.9276333333333332</v>
       </c>
+      <c r="AL262" t="n">
+        <v>0.8508</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
@@ -24397,6 +25150,9 @@
       <c r="AK263" t="n">
         <v>0.96855</v>
       </c>
+      <c r="AL263" t="n">
+        <v>0.9155750000000001</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
@@ -24452,6 +25208,9 @@
       <c r="AK264" t="n">
         <v>0.9761000000000001</v>
       </c>
+      <c r="AL264" t="n">
+        <v>0.9184833333333332</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
@@ -24507,6 +25266,9 @@
       <c r="AK265" t="n">
         <v>0.9752624999999999</v>
       </c>
+      <c r="AL265" t="n">
+        <v>0.9153625</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
@@ -24562,6 +25324,9 @@
       <c r="AK266" t="n">
         <v>0.8939199999999999</v>
       </c>
+      <c r="AL266" t="n">
+        <v>0.89458</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
@@ -24617,6 +25382,9 @@
       <c r="AK267" t="n">
         <v>0.9657</v>
       </c>
+      <c r="AL267" t="n">
+        <v>0.9073500000000001</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
@@ -24672,6 +25440,9 @@
       <c r="AK268" t="n">
         <v>0.9323375</v>
       </c>
+      <c r="AL268" t="n">
+        <v>0.89745</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
@@ -24727,6 +25498,9 @@
       <c r="AK269" t="n">
         <v>0.9784</v>
       </c>
+      <c r="AL269" t="n">
+        <v>0.9156857142857142</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
@@ -24782,6 +25556,9 @@
       <c r="AK270" t="n">
         <v>0.9554999999999999</v>
       </c>
+      <c r="AL270" t="n">
+        <v>0.9327142857142857</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
@@ -24837,6 +25614,9 @@
       <c r="AK271" t="n">
         <v>0.9751500000000002</v>
       </c>
+      <c r="AL271" t="n">
+        <v>0.8998333333333334</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
@@ -24892,6 +25672,9 @@
       <c r="AK272" t="n">
         <v>0.76898</v>
       </c>
+      <c r="AL272" t="n">
+        <v>0.9416166666666669</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
@@ -24947,6 +25730,9 @@
       <c r="AK273" t="n">
         <v>0.9248749999999999</v>
       </c>
+      <c r="AL273" t="n">
+        <v>0.95128</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
@@ -25002,6 +25788,9 @@
       <c r="AK274" t="n">
         <v>0.9533111111111112</v>
       </c>
+      <c r="AL274" t="n">
+        <v>0.9404</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
@@ -25057,6 +25846,9 @@
       <c r="AK275" t="n">
         <v>0.9154874999999999</v>
       </c>
+      <c r="AL275" t="n">
+        <v>0.9392857142857143</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
@@ -25112,6 +25904,9 @@
       <c r="AK276" t="n">
         <v>0.9205000000000001</v>
       </c>
+      <c r="AL276" t="n">
+        <v>0.9520500000000001</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
@@ -25167,6 +25962,9 @@
       <c r="AK277" t="n">
         <v>0.9105125000000001</v>
       </c>
+      <c r="AL277" t="n">
+        <v>0.9341199999999998</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
@@ -25222,6 +26020,9 @@
       <c r="AK278" t="n">
         <v>0.9320333333333334</v>
       </c>
+      <c r="AL278" t="n">
+        <v>0.94374</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
@@ -25277,6 +26078,9 @@
       <c r="AK279" t="n">
         <v>0.9031833333333333</v>
       </c>
+      <c r="AL279" t="n">
+        <v>0.94098</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
@@ -25332,6 +26136,9 @@
       <c r="AK280" t="n">
         <v>0.9307800000000001</v>
       </c>
+      <c r="AL280" t="n">
+        <v>0.9321</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
@@ -25387,6 +26194,9 @@
       <c r="AK281" t="n">
         <v>0.887625</v>
       </c>
+      <c r="AL281" t="n">
+        <v>0.927675</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
@@ -25442,6 +26252,9 @@
       <c r="AK282" t="n">
         <v>0.9702875000000001</v>
       </c>
+      <c r="AL282" t="n">
+        <v>0.95495</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
@@ -25497,6 +26310,9 @@
       <c r="AK283" t="n">
         <v>0.8214600000000001</v>
       </c>
+      <c r="AL283" t="n">
+        <v>0.94316</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
@@ -25552,6 +26368,9 @@
       <c r="AK284" t="n">
         <v>0.9089571428571429</v>
       </c>
+      <c r="AL284" t="n">
+        <v>0.9449799999999999</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
@@ -25607,6 +26426,9 @@
       <c r="AK285" t="n">
         <v>0.9274777777777778</v>
       </c>
+      <c r="AL285" t="n">
+        <v>0.934642857142857</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
@@ -25662,6 +26484,9 @@
       <c r="AK286" t="n">
         <v>0.9525333333333332</v>
       </c>
+      <c r="AL286" t="n">
+        <v>0.91616</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
@@ -25717,6 +26542,9 @@
       <c r="AK287" t="n">
         <v>0.9794428571428572</v>
       </c>
+      <c r="AL287" t="n">
+        <v>0.94125</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
@@ -25772,6 +26600,9 @@
       <c r="AK288" t="n">
         <v>0.9242125</v>
       </c>
+      <c r="AL288" t="n">
+        <v>0.90412</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
@@ -25827,6 +26658,9 @@
       <c r="AK289" t="n">
         <v>0.9079444444444444</v>
       </c>
+      <c r="AL289" t="n">
+        <v>0.9233625</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
@@ -25882,6 +26716,9 @@
       <c r="AK290" t="n">
         <v>0.9758500000000001</v>
       </c>
+      <c r="AL290" t="n">
+        <v>0.9205444444444445</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
@@ -25937,6 +26774,9 @@
       <c r="AK291" t="n">
         <v>0.9763125</v>
       </c>
+      <c r="AL291" t="n">
+        <v>0.9487499999999999</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
@@ -25992,6 +26832,9 @@
       <c r="AK292" t="n">
         <v>0.96155</v>
       </c>
+      <c r="AL292" t="n">
+        <v>0.9234</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
@@ -26047,6 +26890,9 @@
       <c r="AK293" t="n">
         <v>0.970675</v>
       </c>
+      <c r="AL293" t="n">
+        <v>0.94446</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
@@ -26102,6 +26948,9 @@
       <c r="AK294" t="n">
         <v>0.95748</v>
       </c>
+      <c r="AL294" t="n">
+        <v>0.9338500000000001</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
@@ -26157,6 +27006,9 @@
       <c r="AK295" t="n">
         <v>0.9533444444444444</v>
       </c>
+      <c r="AL295" t="n">
+        <v>0.9437166666666666</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
@@ -26212,6 +27064,9 @@
       <c r="AK296" t="n">
         <v>0.8929400000000001</v>
       </c>
+      <c r="AL296" t="n">
+        <v>0.9023</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
@@ -26267,6 +27122,9 @@
       <c r="AK297" t="n">
         <v>0.9756166666666667</v>
       </c>
+      <c r="AL297" t="n">
+        <v>0.9024428571428571</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
@@ -26322,6 +27180,9 @@
       <c r="AK298" t="n">
         <v>0.9476222222222224</v>
       </c>
+      <c r="AL298" t="n">
+        <v>0.9085</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
@@ -26377,6 +27238,9 @@
       <c r="AK299" t="n">
         <v>0.84368</v>
       </c>
+      <c r="AL299" t="n">
+        <v>0.9461666666666666</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
@@ -26432,6 +27296,9 @@
       <c r="AK300" t="n">
         <v>0.9693750000000001</v>
       </c>
+      <c r="AL300" t="n">
+        <v>0.9084</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
@@ -26487,6 +27354,9 @@
       <c r="AK301" t="n">
         <v>0.8427666666666668</v>
       </c>
+      <c r="AL301" t="n">
+        <v>0.9345800000000001</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
@@ -26542,6 +27412,9 @@
       <c r="AK302" t="n">
         <v>0.8727545454545456</v>
       </c>
+      <c r="AL302" t="n">
+        <v>0.9203375</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
@@ -26597,6 +27470,9 @@
       <c r="AK303" t="n">
         <v>0.9712000000000002</v>
       </c>
+      <c r="AL303" t="n">
+        <v>0.8888285714285713</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
@@ -26652,6 +27528,9 @@
       <c r="AK304" t="n">
         <v>0.9714375</v>
       </c>
+      <c r="AL304" t="n">
+        <v>0.9393166666666667</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
@@ -26707,6 +27586,9 @@
       <c r="AK305" t="n">
         <v>0.8745111111111111</v>
       </c>
+      <c r="AL305" t="n">
+        <v>0.9506333333333332</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
@@ -26762,6 +27644,9 @@
       <c r="AK306" t="n">
         <v>0.900475</v>
       </c>
+      <c r="AL306" t="n">
+        <v>0.9536166666666667</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
@@ -26817,6 +27702,9 @@
       <c r="AK307" t="n">
         <v>0.9775333333333331</v>
       </c>
+      <c r="AL307" t="n">
+        <v>0.915875</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
@@ -26872,6 +27760,9 @@
       <c r="AK308" t="n">
         <v>0.9787333333333331</v>
       </c>
+      <c r="AL308" t="n">
+        <v>0.9108333333333333</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
@@ -26927,6 +27818,9 @@
       <c r="AK309" t="n">
         <v>0.9787142857142858</v>
       </c>
+      <c r="AL309" t="n">
+        <v>0.9468333333333333</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
@@ -26982,6 +27876,9 @@
       <c r="AK310" t="n">
         <v>0.9100000000000001</v>
       </c>
+      <c r="AL310" t="n">
+        <v>0.94325</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
@@ -27036,6 +27933,9 @@
       </c>
       <c r="AK311" t="n">
         <v>0.976757142857143</v>
+      </c>
+      <c r="AL311" t="n">
+        <v>0.900825</v>
       </c>
     </row>
     <row r="312">
@@ -27147,6 +28047,9 @@
       <c r="AK316" t="n">
         <v>0.0107</v>
       </c>
+      <c r="AL316" t="n">
+        <v>0.0089</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
@@ -27211,6 +28114,9 @@
       <c r="AK317" t="n">
         <v>0.0177</v>
       </c>
+      <c r="AL317" t="n">
+        <v>0.0126</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
@@ -27275,6 +28181,9 @@
       <c r="AK318" t="n">
         <v>0.7292</v>
       </c>
+      <c r="AL318" t="n">
+        <v>0.0241</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
@@ -27339,6 +28248,9 @@
       <c r="AK319" t="n">
         <v>0.1263</v>
       </c>
+      <c r="AL319" t="n">
+        <v>0.0594</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
@@ -27403,6 +28315,9 @@
       <c r="AK320" t="n">
         <v>0.5432</v>
       </c>
+      <c r="AL320" t="n">
+        <v>0.0508</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
@@ -27464,6 +28379,9 @@
       <c r="AK321" t="n">
         <v>0.0214</v>
       </c>
+      <c r="AL321" t="n">
+        <v>0.0115</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
@@ -27525,6 +28443,9 @@
       <c r="AK322" t="n">
         <v>0.5604</v>
       </c>
+      <c r="AL322" t="n">
+        <v>0.1132</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
@@ -27586,6 +28507,9 @@
       <c r="AK323" t="n">
         <v>0.738</v>
       </c>
+      <c r="AL323" t="n">
+        <v>0.2205</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
@@ -27647,6 +28571,9 @@
       <c r="AK324" t="n">
         <v>0.8437</v>
       </c>
+      <c r="AL324" t="n">
+        <v>0.2434</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
@@ -27708,6 +28635,9 @@
       <c r="AK325" t="n">
         <v>0.623</v>
       </c>
+      <c r="AL325" t="n">
+        <v>0.2845</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
@@ -27763,6 +28693,9 @@
       <c r="AK326" t="n">
         <v>0.6113</v>
       </c>
+      <c r="AL326" t="n">
+        <v>0.313</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
@@ -27818,6 +28751,9 @@
       <c r="AK327" t="n">
         <v>0.2872</v>
       </c>
+      <c r="AL327" t="n">
+        <v>0.3369</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
@@ -27873,6 +28809,9 @@
       <c r="AK328" t="n">
         <v>0.761</v>
       </c>
+      <c r="AL328" t="n">
+        <v>0.2533</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
@@ -27928,6 +28867,9 @@
       <c r="AK329" t="n">
         <v>0.6369</v>
       </c>
+      <c r="AL329" t="n">
+        <v>0.5447</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
@@ -27983,6 +28925,9 @@
       <c r="AK330" t="n">
         <v>0.7791</v>
       </c>
+      <c r="AL330" t="n">
+        <v>0.7426</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
@@ -28038,6 +28983,9 @@
       <c r="AK331" t="n">
         <v>0.9051</v>
       </c>
+      <c r="AL331" t="n">
+        <v>0.7345</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
@@ -28093,6 +29041,9 @@
       <c r="AK332" t="n">
         <v>0.8895</v>
       </c>
+      <c r="AL332" t="n">
+        <v>0.6671</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
@@ -28148,6 +29099,9 @@
       <c r="AK333" t="n">
         <v>0.9349</v>
       </c>
+      <c r="AL333" t="n">
+        <v>0.7753</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
@@ -28203,6 +29157,9 @@
       <c r="AK334" t="n">
         <v>0.7105</v>
       </c>
+      <c r="AL334" t="n">
+        <v>0.7947</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
@@ -28258,6 +29215,9 @@
       <c r="AK335" t="n">
         <v>0.7983</v>
       </c>
+      <c r="AL335" t="n">
+        <v>0.7077</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
@@ -28313,6 +29273,9 @@
       <c r="AK336" t="n">
         <v>0.8174</v>
       </c>
+      <c r="AL336" t="n">
+        <v>0.4733</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
@@ -28368,6 +29331,9 @@
       <c r="AK337" t="n">
         <v>0.883</v>
       </c>
+      <c r="AL337" t="n">
+        <v>0.5746</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
@@ -28423,6 +29389,9 @@
       <c r="AK338" t="n">
         <v>0.9278999999999999</v>
       </c>
+      <c r="AL338" t="n">
+        <v>0.2351</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
@@ -28478,6 +29447,9 @@
       <c r="AK339" t="n">
         <v>0.9481000000000001</v>
       </c>
+      <c r="AL339" t="n">
+        <v>0.4727</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
@@ -28533,6 +29505,9 @@
       <c r="AK340" t="n">
         <v>0.8835</v>
       </c>
+      <c r="AL340" t="n">
+        <v>0.5871</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
@@ -28588,6 +29563,9 @@
       <c r="AK341" t="n">
         <v>0.9258999999999999</v>
       </c>
+      <c r="AL341" t="n">
+        <v>0.6556999999999999</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
@@ -28643,6 +29621,9 @@
       <c r="AK342" t="n">
         <v>0.8378</v>
       </c>
+      <c r="AL342" t="n">
+        <v>0.6911</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
@@ -28698,6 +29679,9 @@
       <c r="AK343" t="n">
         <v>0.9206</v>
       </c>
+      <c r="AL343" t="n">
+        <v>0.7198</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
@@ -28753,6 +29737,9 @@
       <c r="AK344" t="n">
         <v>0.9482</v>
       </c>
+      <c r="AL344" t="n">
+        <v>0.7431</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
@@ -28808,6 +29795,9 @@
       <c r="AK345" t="n">
         <v>0.946</v>
       </c>
+      <c r="AL345" t="n">
+        <v>0.7573</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
@@ -28863,6 +29853,9 @@
       <c r="AK346" t="n">
         <v>0.9533</v>
       </c>
+      <c r="AL346" t="n">
+        <v>0.7464</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
@@ -28918,6 +29911,9 @@
       <c r="AK347" t="n">
         <v>0.9453</v>
       </c>
+      <c r="AL347" t="n">
+        <v>0.7292999999999999</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
@@ -28973,6 +29969,9 @@
       <c r="AK348" t="n">
         <v>0.9406</v>
       </c>
+      <c r="AL348" t="n">
+        <v>0.7313</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
@@ -29028,6 +30027,9 @@
       <c r="AK349" t="n">
         <v>0.8991</v>
       </c>
+      <c r="AL349" t="n">
+        <v>0.7282999999999999</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
@@ -29083,6 +30085,9 @@
       <c r="AK350" t="n">
         <v>0.9386</v>
       </c>
+      <c r="AL350" t="n">
+        <v>0.472</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
@@ -29138,6 +30143,9 @@
       <c r="AK351" t="n">
         <v>0.9575</v>
       </c>
+      <c r="AL351" t="n">
+        <v>0.5149</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
@@ -29193,6 +30201,9 @@
       <c r="AK352" t="n">
         <v>0.9748</v>
       </c>
+      <c r="AL352" t="n">
+        <v>0.5433</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
@@ -29248,6 +30259,9 @@
       <c r="AK353" t="n">
         <v>0.9671</v>
       </c>
+      <c r="AL353" t="n">
+        <v>0.5747</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
@@ -29303,6 +30317,9 @@
       <c r="AK354" t="n">
         <v>0.9665</v>
       </c>
+      <c r="AL354" t="n">
+        <v>0.6355</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
@@ -29358,6 +30375,9 @@
       <c r="AK355" t="n">
         <v>0.961</v>
       </c>
+      <c r="AL355" t="n">
+        <v>0.6669</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
@@ -29413,6 +30433,9 @@
       <c r="AK356" t="n">
         <v>0.9676</v>
       </c>
+      <c r="AL356" t="n">
+        <v>0.5778</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
@@ -29468,6 +30491,9 @@
       <c r="AK357" t="n">
         <v>0.9621</v>
       </c>
+      <c r="AL357" t="n">
+        <v>0.624</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
@@ -29523,6 +30549,9 @@
       <c r="AK358" t="n">
         <v>0.9564</v>
       </c>
+      <c r="AL358" t="n">
+        <v>0.599</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
@@ -29578,6 +30607,9 @@
       <c r="AK359" t="n">
         <v>0.9504</v>
       </c>
+      <c r="AL359" t="n">
+        <v>0.6332</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
@@ -29633,6 +30665,9 @@
       <c r="AK360" t="n">
         <v>0.9086</v>
       </c>
+      <c r="AL360" t="n">
+        <v>0.7316</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
@@ -29688,6 +30723,9 @@
       <c r="AK361" t="n">
         <v>0.9409999999999999</v>
       </c>
+      <c r="AL361" t="n">
+        <v>0.7899</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
@@ -29743,6 +30781,9 @@
       <c r="AK362" t="n">
         <v>0.9598</v>
       </c>
+      <c r="AL362" t="n">
+        <v>0.7783</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
@@ -29798,6 +30839,9 @@
       <c r="AK363" t="n">
         <v>0.9587</v>
       </c>
+      <c r="AL363" t="n">
+        <v>0.7603</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
@@ -29853,6 +30897,9 @@
       <c r="AK364" t="n">
         <v>0.9675</v>
       </c>
+      <c r="AL364" t="n">
+        <v>0.765</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
@@ -29908,6 +30955,9 @@
       <c r="AK365" t="n">
         <v>0.9722</v>
       </c>
+      <c r="AL365" t="n">
+        <v>0.7526</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
@@ -29963,6 +31013,9 @@
       <c r="AK366" t="n">
         <v>0.9719</v>
       </c>
+      <c r="AL366" t="n">
+        <v>0.7314000000000001</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
@@ -30018,6 +31071,9 @@
       <c r="AK367" t="n">
         <v>0.9677</v>
       </c>
+      <c r="AL367" t="n">
+        <v>0.7802</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
@@ -30073,6 +31129,9 @@
       <c r="AK368" t="n">
         <v>0.9679</v>
       </c>
+      <c r="AL368" t="n">
+        <v>0.8155</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
@@ -30128,6 +31187,9 @@
       <c r="AK369" t="n">
         <v>0.9742</v>
       </c>
+      <c r="AL369" t="n">
+        <v>0.8442</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
@@ -30183,6 +31245,9 @@
       <c r="AK370" t="n">
         <v>0.9703000000000001</v>
       </c>
+      <c r="AL370" t="n">
+        <v>0.8464</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
@@ -30238,6 +31303,9 @@
       <c r="AK371" t="n">
         <v>0.9567</v>
       </c>
+      <c r="AL371" t="n">
+        <v>0.8151</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
@@ -30293,6 +31361,9 @@
       <c r="AK372" t="n">
         <v>0.9675</v>
       </c>
+      <c r="AL372" t="n">
+        <v>0.7921</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
@@ -30348,6 +31419,9 @@
       <c r="AK373" t="n">
         <v>0.9771</v>
       </c>
+      <c r="AL373" t="n">
+        <v>0.8169999999999999</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
@@ -30403,6 +31477,9 @@
       <c r="AK374" t="n">
         <v>0.9751</v>
       </c>
+      <c r="AL374" t="n">
+        <v>0.7999000000000001</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
@@ -30458,6 +31535,9 @@
       <c r="AK375" t="n">
         <v>0.9715</v>
       </c>
+      <c r="AL375" t="n">
+        <v>0.8289</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
@@ -30513,6 +31593,9 @@
       <c r="AK376" t="n">
         <v>0.9712</v>
       </c>
+      <c r="AL376" t="n">
+        <v>0.8406</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
@@ -30568,6 +31651,9 @@
       <c r="AK377" t="n">
         <v>0.9788</v>
       </c>
+      <c r="AL377" t="n">
+        <v>0.8452</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
@@ -30623,6 +31709,9 @@
       <c r="AK378" t="n">
         <v>0.9814000000000001</v>
       </c>
+      <c r="AL378" t="n">
+        <v>0.8502</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
@@ -30678,6 +31767,9 @@
       <c r="AK379" t="n">
         <v>0.9818</v>
       </c>
+      <c r="AL379" t="n">
+        <v>0.8938</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
@@ -30733,6 +31825,9 @@
       <c r="AK380" t="n">
         <v>0.9796</v>
       </c>
+      <c r="AL380" t="n">
+        <v>0.8748</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
@@ -30788,6 +31883,9 @@
       <c r="AK381" t="n">
         <v>0.9796</v>
       </c>
+      <c r="AL381" t="n">
+        <v>0.7267</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
@@ -30843,6 +31941,9 @@
       <c r="AK382" t="n">
         <v>0.9796</v>
       </c>
+      <c r="AL382" t="n">
+        <v>0.6847</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
@@ -30898,6 +31999,9 @@
       <c r="AK383" t="n">
         <v>0.9752</v>
       </c>
+      <c r="AL383" t="n">
+        <v>0.6011</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
@@ -30953,6 +32057,9 @@
       <c r="AK384" t="n">
         <v>0.9767</v>
       </c>
+      <c r="AL384" t="n">
+        <v>0.7789</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
@@ -31008,6 +32115,9 @@
       <c r="AK385" t="n">
         <v>0.9789</v>
       </c>
+      <c r="AL385" t="n">
+        <v>0.8401</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
@@ -31063,6 +32173,9 @@
       <c r="AK386" t="n">
         <v>0.9751</v>
       </c>
+      <c r="AL386" t="n">
+        <v>0.8865</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
@@ -31118,6 +32231,9 @@
       <c r="AK387" t="n">
         <v>0.9679</v>
       </c>
+      <c r="AL387" t="n">
+        <v>0.7979000000000001</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
@@ -31173,6 +32289,9 @@
       <c r="AK388" t="n">
         <v>0.9698</v>
       </c>
+      <c r="AL388" t="n">
+        <v>0.8171</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
@@ -31228,6 +32347,9 @@
       <c r="AK389" t="n">
         <v>0.9776</v>
       </c>
+      <c r="AL389" t="n">
+        <v>0.7969000000000001</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
@@ -31283,6 +32405,9 @@
       <c r="AK390" t="n">
         <v>0.9784</v>
       </c>
+      <c r="AL390" t="n">
+        <v>0.7825</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
@@ -31338,6 +32463,9 @@
       <c r="AK391" t="n">
         <v>0.9777</v>
       </c>
+      <c r="AL391" t="n">
+        <v>0.7829</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
@@ -31393,6 +32521,9 @@
       <c r="AK392" t="n">
         <v>0.9799</v>
       </c>
+      <c r="AL392" t="n">
+        <v>0.7756999999999999</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
@@ -31448,6 +32579,9 @@
       <c r="AK393" t="n">
         <v>0.985</v>
       </c>
+      <c r="AL393" t="n">
+        <v>0.7816</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
@@ -31503,6 +32637,9 @@
       <c r="AK394" t="n">
         <v>0.9774</v>
       </c>
+      <c r="AL394" t="n">
+        <v>0.8124</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
@@ -31558,6 +32695,9 @@
       <c r="AK395" t="n">
         <v>0.9665</v>
       </c>
+      <c r="AL395" t="n">
+        <v>0.8264</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
@@ -31613,6 +32753,9 @@
       <c r="AK396" t="n">
         <v>0.9686</v>
       </c>
+      <c r="AL396" t="n">
+        <v>0.8048</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
@@ -31668,6 +32811,9 @@
       <c r="AK397" t="n">
         <v>0.9414</v>
       </c>
+      <c r="AL397" t="n">
+        <v>0.7065</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
@@ -31723,6 +32869,9 @@
       <c r="AK398" t="n">
         <v>0.9338</v>
       </c>
+      <c r="AL398" t="n">
+        <v>0.7691</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
@@ -31778,6 +32927,9 @@
       <c r="AK399" t="n">
         <v>0.9701</v>
       </c>
+      <c r="AL399" t="n">
+        <v>0.8087</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
@@ -31833,6 +32985,9 @@
       <c r="AK400" t="n">
         <v>0.9801</v>
       </c>
+      <c r="AL400" t="n">
+        <v>0.7674</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
@@ -31888,6 +33043,9 @@
       <c r="AK401" t="n">
         <v>0.9802</v>
       </c>
+      <c r="AL401" t="n">
+        <v>0.8303</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="n">
@@ -31943,6 +33101,9 @@
       <c r="AK402" t="n">
         <v>0.9775</v>
       </c>
+      <c r="AL402" t="n">
+        <v>0.8729</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
@@ -31998,6 +33159,9 @@
       <c r="AK403" t="n">
         <v>0.9806</v>
       </c>
+      <c r="AL403" t="n">
+        <v>0.8695000000000001</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
@@ -32053,6 +33217,9 @@
       <c r="AK404" t="n">
         <v>0.9795</v>
       </c>
+      <c r="AL404" t="n">
+        <v>0.87</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
@@ -32108,6 +33275,9 @@
       <c r="AK405" t="n">
         <v>0.9821</v>
       </c>
+      <c r="AL405" t="n">
+        <v>0.8831</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
@@ -32163,6 +33333,9 @@
       <c r="AK406" t="n">
         <v>0.9827</v>
       </c>
+      <c r="AL406" t="n">
+        <v>0.8893</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="1" t="n">
@@ -32218,6 +33391,9 @@
       <c r="AK407" t="n">
         <v>0.9823</v>
       </c>
+      <c r="AL407" t="n">
+        <v>0.8922</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
@@ -32273,6 +33449,9 @@
       <c r="AK408" t="n">
         <v>0.9786</v>
       </c>
+      <c r="AL408" t="n">
+        <v>0.9031</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
@@ -32328,6 +33507,9 @@
       <c r="AK409" t="n">
         <v>0.9791</v>
       </c>
+      <c r="AL409" t="n">
+        <v>0.9071</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
@@ -32383,6 +33565,9 @@
       <c r="AK410" t="n">
         <v>0.9799</v>
       </c>
+      <c r="AL410" t="n">
+        <v>0.9253</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="n">
@@ -32438,6 +33623,9 @@
       <c r="AK411" t="n">
         <v>0.9814000000000001</v>
       </c>
+      <c r="AL411" t="n">
+        <v>0.9103</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
@@ -32493,6 +33681,9 @@
       <c r="AK412" t="n">
         <v>0.9848</v>
       </c>
+      <c r="AL412" t="n">
+        <v>0.9077</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
@@ -32548,6 +33739,9 @@
       <c r="AK413" t="n">
         <v>0.9819</v>
       </c>
+      <c r="AL413" t="n">
+        <v>0.9049</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="n">
@@ -32603,6 +33797,9 @@
       <c r="AK414" t="n">
         <v>0.9782999999999999</v>
       </c>
+      <c r="AL414" t="n">
+        <v>0.8942</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
@@ -32657,6 +33854,9 @@
       </c>
       <c r="AK415" t="n">
         <v>0.9786</v>
+      </c>
+      <c r="AL415" t="n">
+        <v>0.903</v>
       </c>
     </row>
     <row r="416">

--- a/CIFAR_Global.xlsx
+++ b/CIFAR_Global.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashleyau/Documents/PhD/Practical_Experiment/Finalised/Finalised_Algorithm_ResNet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC010050-BA28-5F44-8337-AE8C27FDF108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE680B22-A17D-1449-AE2A-D077C033D699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="36">
   <si>
     <t>100 Rounds</t>
   </si>
@@ -119,6 +119,15 @@
   </si>
   <si>
     <t>Equally Aggregate</t>
+  </si>
+  <si>
+    <t>PR = 0.6</t>
+  </si>
+  <si>
+    <t>BR = 0.6</t>
+  </si>
+  <si>
+    <t>BR = 0.4</t>
   </si>
 </sst>
 </file>
@@ -267,26 +276,26 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -13412,7 +13421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AS504"/>
+  <dimension ref="A1:BG504"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -13433,9 +13442,10 @@
     <col min="39" max="39" width="15.1640625" customWidth="1"/>
     <col min="41" max="41" width="11.5" customWidth="1"/>
     <col min="42" max="43" width="12.33203125" customWidth="1"/>
+    <col min="53" max="53" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13445,35 +13455,54 @@
       <c r="AH1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AM1" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN1" s="15"/>
-      <c r="AO1" s="15"/>
-      <c r="AP1" s="15"/>
-      <c r="AQ1" s="15"/>
-    </row>
-    <row r="2" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AM1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN1" s="17"/>
+      <c r="AO1" s="17"/>
+      <c r="AP1" s="17"/>
+      <c r="AQ1" s="17"/>
+      <c r="AR1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BA1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB1" s="17"/>
+      <c r="BC1" s="17"/>
+      <c r="BD1" s="17"/>
+      <c r="BE1" s="17"/>
+      <c r="BF1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="15"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
       <c r="K2" s="12" t="s">
         <v>7</v>
       </c>
@@ -13482,39 +13511,50 @@
       <c r="S2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="T2" s="14" t="s">
+      <c r="T2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="AD2" s="14" t="s">
+      <c r="U2" s="17"/>
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
+      <c r="AD2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
+      <c r="AE2" s="17"/>
+      <c r="AF2" s="17"/>
       <c r="AH2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AI2" s="14" t="s">
+      <c r="AI2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AJ2" s="15"/>
-      <c r="AK2" s="15"/>
+      <c r="AJ2" s="17"/>
+      <c r="AK2" s="17"/>
       <c r="AL2" s="7"/>
       <c r="AM2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AN2" s="14" t="s">
+      <c r="AN2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AO2" s="14"/>
-      <c r="AP2" s="14"/>
-      <c r="AQ2" s="14"/>
-      <c r="AR2" s="14"/>
-      <c r="AS2" s="14"/>
-    </row>
-    <row r="3" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AO2" s="15"/>
+      <c r="AP2" s="15"/>
+      <c r="AQ2" s="15"/>
+      <c r="AR2" s="15"/>
+      <c r="AS2" s="15"/>
+      <c r="BA2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BB2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="BC2" s="15"/>
+      <c r="BD2" s="15"/>
+      <c r="BE2" s="15"/>
+      <c r="BF2" s="15"/>
+      <c r="BG2" s="15"/>
+    </row>
+    <row r="3" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -13545,14 +13585,14 @@
       <c r="J3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="19" t="s">
+      <c r="L3" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
       <c r="S3" s="1" t="s">
         <v>10</v>
       </c>
@@ -13571,11 +13611,11 @@
       <c r="Z3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="AD3" s="21" t="s">
+      <c r="AD3" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="AE3" s="15"/>
-      <c r="AF3" s="15"/>
+      <c r="AE3" s="17"/>
+      <c r="AF3" s="17"/>
       <c r="AH3" s="1" t="s">
         <v>10</v>
       </c>
@@ -13592,42 +13632,57 @@
       <c r="AM3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="AN3" s="19" t="s">
+      <c r="AN3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="AO3" s="15"/>
-      <c r="AP3" s="20" t="s">
+      <c r="AO3" s="17"/>
+      <c r="AP3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="AQ3" s="15"/>
-      <c r="AR3" s="19" t="s">
+      <c r="AQ3" s="17"/>
+      <c r="AR3" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="AS3" s="19"/>
-    </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AS3" s="14"/>
+      <c r="BA3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="BB3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="BC3" s="17"/>
+      <c r="BD3" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="BE3" s="17"/>
+      <c r="BF3" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="BG3" s="14"/>
+    </row>
+    <row r="4" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="15"/>
-      <c r="I4" s="16" t="s">
+      <c r="H4" s="17"/>
+      <c r="I4" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="15"/>
+      <c r="J4" s="17"/>
       <c r="S4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="T4" s="16" t="s">
+      <c r="T4" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="U4" s="15"/>
-      <c r="V4" s="16" t="s">
+      <c r="U4" s="17"/>
+      <c r="V4" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="W4" s="15"/>
+      <c r="W4" s="17"/>
       <c r="AD4" s="10" t="s">
         <v>2</v>
       </c>
@@ -13671,8 +13726,29 @@
       <c r="AS4" s="11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BB4" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="BC4" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="BD4" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE4" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF4" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG4" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -13763,8 +13839,11 @@
       <c r="AS5">
         <v>0.15193200000000001</v>
       </c>
-    </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -13855,8 +13934,11 @@
       <c r="AS6">
         <v>0.19969733333333339</v>
       </c>
-    </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -13947,8 +14029,11 @@
       <c r="AS7">
         <v>0.30287599999999992</v>
       </c>
-    </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA7" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -14039,8 +14124,11 @@
       <c r="AS8">
         <v>0.36052577777777778</v>
       </c>
-    </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA8" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -14131,8 +14219,11 @@
       <c r="AS9">
         <v>0.42925600000000003</v>
       </c>
-    </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA9" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -14220,8 +14311,11 @@
       <c r="AS10">
         <v>0.43320792079207932</v>
       </c>
-    </row>
-    <row r="11" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA10" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -14309,8 +14403,11 @@
       <c r="AS11">
         <v>0.53846336633663361</v>
       </c>
-    </row>
-    <row r="12" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA11" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -14398,8 +14495,11 @@
       <c r="AS12">
         <v>0.54693168316831697</v>
       </c>
-    </row>
-    <row r="13" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA12" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -14487,8 +14587,11 @@
       <c r="AS13">
         <v>0.47148316831683168</v>
       </c>
-    </row>
-    <row r="14" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA13" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -14576,8 +14679,11 @@
       <c r="AS14">
         <v>0.59837416666666665</v>
       </c>
-    </row>
-    <row r="15" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA14" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -14659,8 +14765,11 @@
       <c r="AS15">
         <v>0.59457749999999998</v>
       </c>
-    </row>
-    <row r="16" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA15" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -14742,8 +14851,11 @@
       <c r="AS16">
         <v>0.63541583333333329</v>
       </c>
-    </row>
-    <row r="17" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA16" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -14825,8 +14937,11 @@
       <c r="AS17">
         <v>0.68208239999999987</v>
       </c>
-    </row>
-    <row r="18" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA17" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -14908,8 +15023,11 @@
       <c r="AS18">
         <v>0.71206960000000008</v>
       </c>
-    </row>
-    <row r="19" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA18" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -14991,8 +15109,11 @@
       <c r="AS19">
         <v>0.73942959999999991</v>
       </c>
-    </row>
-    <row r="20" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA19" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -15074,8 +15195,11 @@
       <c r="AS20">
         <v>0.74612719999999999</v>
       </c>
-    </row>
-    <row r="21" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA20" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -15157,8 +15281,11 @@
       <c r="AS21">
         <v>0.7612855999999999</v>
       </c>
-    </row>
-    <row r="22" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA21" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -15240,8 +15367,11 @@
       <c r="AS22">
         <v>0.76184960000000013</v>
       </c>
-    </row>
-    <row r="23" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA22" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -15323,8 +15453,11 @@
       <c r="AS23">
         <v>0.76934959999999997</v>
       </c>
-    </row>
-    <row r="24" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA23" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -15403,8 +15536,11 @@
       <c r="AS24">
         <v>0.77543440000000008</v>
       </c>
-    </row>
-    <row r="25" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA24" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -15486,8 +15622,11 @@
       <c r="AS25">
         <v>0.77086080000000012</v>
       </c>
-    </row>
-    <row r="26" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA25" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -15569,8 +15708,11 @@
       <c r="AS26">
         <v>0.79095040000000005</v>
       </c>
-    </row>
-    <row r="27" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA26" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -15652,8 +15794,11 @@
       <c r="AS27">
         <v>0.78997040000000018</v>
       </c>
-    </row>
-    <row r="28" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA27" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -15735,8 +15880,11 @@
       <c r="AS28">
         <v>0.80537520000000007</v>
       </c>
-    </row>
-    <row r="29" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA28" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -15818,8 +15966,11 @@
       <c r="AS29">
         <v>0.79584079999999979</v>
       </c>
-    </row>
-    <row r="30" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA29" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -15901,8 +16052,11 @@
       <c r="AS30">
         <v>0.80313120000000005</v>
       </c>
-    </row>
-    <row r="31" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA30" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -15984,8 +16138,11 @@
       <c r="AS31">
         <v>0.8021296</v>
       </c>
-    </row>
-    <row r="32" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA31" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -16067,8 +16224,11 @@
       <c r="AS32">
         <v>0.8142408000000001</v>
       </c>
-    </row>
-    <row r="33" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA32" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -16150,8 +16310,11 @@
       <c r="AS33">
         <v>0.80844319999999981</v>
       </c>
-    </row>
-    <row r="34" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA33" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -16233,8 +16396,11 @@
       <c r="AS34">
         <v>0.81313040000000003</v>
       </c>
-    </row>
-    <row r="35" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA34" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -16316,8 +16482,11 @@
       <c r="AS35">
         <v>0.81595280000000003</v>
       </c>
-    </row>
-    <row r="36" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA35" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -16399,8 +16568,11 @@
       <c r="AS36">
         <v>0.79812183098591538</v>
       </c>
-    </row>
-    <row r="37" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA36" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -16482,8 +16654,11 @@
       <c r="AS37">
         <v>0.79277183098591564</v>
       </c>
-    </row>
-    <row r="38" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA37" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>34</v>
       </c>
@@ -16565,8 +16740,11 @@
       <c r="AS38">
         <v>0.79626619718309855</v>
       </c>
-    </row>
-    <row r="39" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA38" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>35</v>
       </c>
@@ -16648,8 +16826,11 @@
       <c r="AS39">
         <v>0.80234507042253511</v>
       </c>
-    </row>
-    <row r="40" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA39" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>36</v>
       </c>
@@ -16731,8 +16912,11 @@
       <c r="AS40">
         <v>0.80220211267605634</v>
       </c>
-    </row>
-    <row r="41" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA40" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>37</v>
       </c>
@@ -16814,8 +16998,11 @@
       <c r="AS41">
         <v>0.80015845070422531</v>
       </c>
-    </row>
-    <row r="42" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA41" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>38</v>
       </c>
@@ -16897,8 +17084,11 @@
       <c r="AS42">
         <v>0.80405563380281697</v>
       </c>
-    </row>
-    <row r="43" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA42" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -16980,8 +17170,11 @@
       <c r="AS43">
         <v>0.80141056338028205</v>
       </c>
-    </row>
-    <row r="44" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA43" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>40</v>
       </c>
@@ -17063,8 +17256,11 @@
       <c r="AS44">
         <v>0.80365985915492955</v>
       </c>
-    </row>
-    <row r="45" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA44" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>41</v>
       </c>
@@ -17146,8 +17342,11 @@
       <c r="AS45">
         <v>0.80587323943661993</v>
       </c>
-    </row>
-    <row r="46" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA45" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>42</v>
       </c>
@@ -17229,8 +17428,11 @@
       <c r="AS46">
         <v>0.80613450704225342</v>
       </c>
-    </row>
-    <row r="47" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA46" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>43</v>
       </c>
@@ -17312,8 +17514,11 @@
       <c r="AS47">
         <v>0.80423521126760567</v>
       </c>
-    </row>
-    <row r="48" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA47" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>44</v>
       </c>
@@ -17395,8 +17600,11 @@
       <c r="AS48">
         <v>0.81017535211267599</v>
       </c>
-    </row>
-    <row r="49" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA48" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>45</v>
       </c>
@@ -17478,8 +17686,11 @@
       <c r="AS49">
         <v>0.81007535211267612</v>
       </c>
-    </row>
-    <row r="50" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA49" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -17561,8 +17772,11 @@
       <c r="AS50">
         <v>0.81107887323943662</v>
       </c>
-    </row>
-    <row r="51" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA50" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>47</v>
       </c>
@@ -17644,8 +17858,11 @@
       <c r="AS51">
         <v>0.81032253521126762</v>
       </c>
-    </row>
-    <row r="52" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA51" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>48</v>
       </c>
@@ -17727,8 +17944,11 @@
       <c r="AS52">
         <v>0.81442394366197191</v>
       </c>
-    </row>
-    <row r="53" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA52" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>49</v>
       </c>
@@ -17810,8 +18030,11 @@
       <c r="AS53">
         <v>0.81248169014084504</v>
       </c>
-    </row>
-    <row r="54" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA53" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>50</v>
       </c>
@@ -17893,8 +18116,11 @@
       <c r="AS54">
         <v>0.81412042253521122</v>
       </c>
-    </row>
-    <row r="55" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA54" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>51</v>
       </c>
@@ -17976,8 +18202,11 @@
       <c r="AS55">
         <v>0.81110704225352104</v>
       </c>
-    </row>
-    <row r="56" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA55" s="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>52</v>
       </c>
@@ -18059,8 +18288,11 @@
       <c r="AS56">
         <v>0.81221619718309845</v>
       </c>
-    </row>
-    <row r="57" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA56" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>53</v>
       </c>
@@ -18142,8 +18374,11 @@
       <c r="AS57">
         <v>0.81178450704225358</v>
       </c>
-    </row>
-    <row r="58" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA57" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>54</v>
       </c>
@@ -18225,8 +18460,11 @@
       <c r="AS58">
         <v>0.81004366197183097</v>
       </c>
-    </row>
-    <row r="59" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA58" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="59" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>55</v>
       </c>
@@ -18308,8 +18546,11 @@
       <c r="AS59">
         <v>0.81071971830985923</v>
       </c>
-    </row>
-    <row r="60" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA59" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>56</v>
       </c>
@@ -18391,8 +18632,11 @@
       <c r="AS60">
         <v>0.81124507042253513</v>
       </c>
-    </row>
-    <row r="61" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA60" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="61" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>57</v>
       </c>
@@ -18474,8 +18718,11 @@
       <c r="AS61">
         <v>0.81254577464788735</v>
       </c>
-    </row>
-    <row r="62" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA61" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="62" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>58</v>
       </c>
@@ -18557,8 +18804,11 @@
       <c r="AS62">
         <v>0.81472746478873237</v>
       </c>
-    </row>
-    <row r="63" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA62" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>59</v>
       </c>
@@ -18640,8 +18890,11 @@
       <c r="AS63">
         <v>0.80495442176870768</v>
       </c>
-    </row>
-    <row r="64" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA63" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="64" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>60</v>
       </c>
@@ -18723,8 +18976,11 @@
       <c r="AS64">
         <v>0.81103401360544247</v>
       </c>
-    </row>
-    <row r="65" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA64" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>61</v>
       </c>
@@ -18806,8 +19062,11 @@
       <c r="AS65">
         <v>0.80847074829931953</v>
       </c>
-    </row>
-    <row r="66" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA65" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>62</v>
       </c>
@@ -18889,8 +19148,11 @@
       <c r="AS66">
         <v>0.81066258503401356</v>
       </c>
-    </row>
-    <row r="67" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA66" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>63</v>
       </c>
@@ -18972,8 +19234,11 @@
       <c r="AS67">
         <v>0.80869455782312938</v>
       </c>
-    </row>
-    <row r="68" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA67" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>64</v>
       </c>
@@ -19055,8 +19320,11 @@
       <c r="AS68">
         <v>0.80790680272108839</v>
       </c>
-    </row>
-    <row r="69" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA68" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="69" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>65</v>
       </c>
@@ -19138,8 +19406,11 @@
       <c r="AS69">
         <v>0.81028231292517006</v>
       </c>
-    </row>
-    <row r="70" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA69" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>66</v>
       </c>
@@ -19221,8 +19492,11 @@
       <c r="AS70">
         <v>0.80654761904761896</v>
       </c>
-    </row>
-    <row r="71" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA70" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="71" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>67</v>
       </c>
@@ -19304,8 +19578,11 @@
       <c r="AS71">
         <v>0.80808707482993203</v>
       </c>
-    </row>
-    <row r="72" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA71" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="72" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>68</v>
       </c>
@@ -19387,8 +19664,11 @@
       <c r="AS72">
         <v>0.81250068027210887</v>
       </c>
-    </row>
-    <row r="73" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA72" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="73" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>69</v>
       </c>
@@ -19470,8 +19750,11 @@
       <c r="AS73">
         <v>0.81179115646258515</v>
       </c>
-    </row>
-    <row r="74" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA73" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="74" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>70</v>
       </c>
@@ -19553,8 +19836,11 @@
       <c r="AS74">
         <v>0.80799931972789119</v>
       </c>
-    </row>
-    <row r="75" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA74" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>71</v>
       </c>
@@ -19636,8 +19922,11 @@
       <c r="AS75">
         <v>0.81016598639455772</v>
       </c>
-    </row>
-    <row r="76" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA75" s="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="76" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>72</v>
       </c>
@@ -19719,8 +20008,11 @@
       <c r="AS76">
         <v>0.81091292517006808</v>
       </c>
-    </row>
-    <row r="77" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA76" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="77" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>73</v>
       </c>
@@ -19802,8 +20094,11 @@
       <c r="AS77">
         <v>0.81166666666666687</v>
       </c>
-    </row>
-    <row r="78" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA77" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="78" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>74</v>
       </c>
@@ -19885,8 +20180,11 @@
       <c r="AS78">
         <v>0.81071768707483016</v>
       </c>
-    </row>
-    <row r="79" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA78" s="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="79" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>75</v>
       </c>
@@ -19968,8 +20266,11 @@
       <c r="AS79">
         <v>0.81036666666666668</v>
       </c>
-    </row>
-    <row r="80" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA79" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>76</v>
       </c>
@@ -20051,8 +20352,11 @@
       <c r="AS80">
         <v>0.80965102040816328</v>
       </c>
-    </row>
-    <row r="81" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA80" s="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="81" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>77</v>
       </c>
@@ -20134,8 +20438,11 @@
       <c r="AS81">
         <v>0.81004829931972799</v>
       </c>
-    </row>
-    <row r="82" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA81" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>78</v>
       </c>
@@ -20217,8 +20524,11 @@
       <c r="AS82">
         <v>0.81050068027210886</v>
       </c>
-    </row>
-    <row r="83" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA82" s="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="83" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>79</v>
       </c>
@@ -20300,8 +20610,11 @@
       <c r="AS83">
         <v>0.81060748299319729</v>
       </c>
-    </row>
-    <row r="84" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA83" s="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="84" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>80</v>
       </c>
@@ -20383,8 +20696,11 @@
       <c r="AS84">
         <v>0.80938843537414951</v>
       </c>
-    </row>
-    <row r="85" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA84" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="85" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>81</v>
       </c>
@@ -20466,8 +20782,11 @@
       <c r="AS85">
         <v>0.81358095238095229</v>
       </c>
-    </row>
-    <row r="86" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA85" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="86" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>82</v>
       </c>
@@ -20549,8 +20868,11 @@
       <c r="AS86">
         <v>0.80860272108843534</v>
       </c>
-    </row>
-    <row r="87" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA86" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>83</v>
       </c>
@@ -20632,8 +20954,11 @@
       <c r="AS87">
         <v>0.81354285714285712</v>
       </c>
-    </row>
-    <row r="88" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA87" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="88" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>84</v>
       </c>
@@ -20715,8 +21040,11 @@
       <c r="AS88">
         <v>0.81114421768707468</v>
       </c>
-    </row>
-    <row r="89" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA88" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="89" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>85</v>
       </c>
@@ -20798,8 +21126,11 @@
       <c r="AS89">
         <v>0.81210816326530622</v>
       </c>
-    </row>
-    <row r="90" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA89" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="90" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>86</v>
       </c>
@@ -20881,8 +21212,11 @@
       <c r="AS90">
         <v>0.81085442176870759</v>
       </c>
-    </row>
-    <row r="91" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA90" s="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="91" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>87</v>
       </c>
@@ -20964,8 +21298,11 @@
       <c r="AS91">
         <v>0.80994421768707492</v>
       </c>
-    </row>
-    <row r="92" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA91" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="92" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>88</v>
       </c>
@@ -21047,8 +21384,11 @@
       <c r="AS92">
         <v>0.80906870748299309</v>
       </c>
-    </row>
-    <row r="93" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA92" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="93" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>89</v>
       </c>
@@ -21130,8 +21470,11 @@
       <c r="AS93">
         <v>0.81204217687074831</v>
       </c>
-    </row>
-    <row r="94" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA93" s="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="94" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>90</v>
       </c>
@@ -21213,8 +21556,11 @@
       <c r="AS94">
         <v>0.8134925170068027</v>
       </c>
-    </row>
-    <row r="95" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA94" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="95" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>91</v>
       </c>
@@ -21296,8 +21642,11 @@
       <c r="AS95">
         <v>0.80902517006802732</v>
       </c>
-    </row>
-    <row r="96" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA95" s="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="96" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>92</v>
       </c>
@@ -21379,8 +21728,11 @@
       <c r="AS96">
         <v>0.81401972789115651</v>
       </c>
-    </row>
-    <row r="97" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA96" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="97" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>93</v>
       </c>
@@ -21462,8 +21814,11 @@
       <c r="AS97">
         <v>0.8160911564625849</v>
       </c>
-    </row>
-    <row r="98" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA97" s="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="98" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>94</v>
       </c>
@@ -21545,8 +21900,11 @@
       <c r="AS98">
         <v>0.81066666666666665</v>
       </c>
-    </row>
-    <row r="99" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA98" s="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="99" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>95</v>
       </c>
@@ -21628,8 +21986,11 @@
       <c r="AS99">
         <v>0.81570068027210874</v>
       </c>
-    </row>
-    <row r="100" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA99" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="100" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>96</v>
       </c>
@@ -21711,8 +22072,11 @@
       <c r="AS100">
         <v>0.81308367346938792</v>
       </c>
-    </row>
-    <row r="101" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA100" s="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="101" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>97</v>
       </c>
@@ -21794,8 +22158,11 @@
       <c r="AS101">
         <v>0.81644829931972784</v>
       </c>
-    </row>
-    <row r="102" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA101" s="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="102" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>98</v>
       </c>
@@ -21877,8 +22244,11 @@
       <c r="AS102">
         <v>0.81563333333333343</v>
       </c>
-    </row>
-    <row r="103" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA102" s="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="103" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>99</v>
       </c>
@@ -21960,8 +22330,11 @@
       <c r="AS103">
         <v>0.81184489795918369</v>
       </c>
-    </row>
-    <row r="104" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA103" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="104" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>100</v>
       </c>
@@ -22043,12 +22416,15 @@
       <c r="AS104">
         <v>0.81176054421768706</v>
       </c>
-    </row>
-    <row r="105" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA104" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="105" spans="1:53" x14ac:dyDescent="0.2">
       <c r="AD105" s="9"/>
       <c r="AE105" s="9"/>
     </row>
-    <row r="106" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>27</v>
       </c>
@@ -22063,8 +22439,11 @@
       <c r="AM106" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="107" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA106" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="107" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>28</v>
       </c>
@@ -22079,8 +22458,11 @@
       <c r="AM107" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="108" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA107" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="108" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>1</v>
       </c>
@@ -22164,8 +22546,11 @@
       <c r="AS108">
         <v>0.8666666666666667</v>
       </c>
-    </row>
-    <row r="109" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA108" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>2</v>
       </c>
@@ -22249,8 +22634,11 @@
       <c r="AS109">
         <v>0.8666666666666667</v>
       </c>
-    </row>
-    <row r="110" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA109" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>3</v>
       </c>
@@ -22334,8 +22722,11 @@
       <c r="AS110">
         <v>0.8666666666666667</v>
       </c>
-    </row>
-    <row r="111" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA110" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>4</v>
       </c>
@@ -22419,8 +22810,11 @@
       <c r="AS111">
         <v>0.93333333333333335</v>
       </c>
-    </row>
-    <row r="112" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA111" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>5</v>
       </c>
@@ -22504,8 +22898,11 @@
       <c r="AS112">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA112" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>6</v>
       </c>
@@ -22586,8 +22983,11 @@
       <c r="AS113">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="114" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA113" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>7</v>
       </c>
@@ -22668,8 +23068,11 @@
       <c r="AS114">
         <v>0.38461538461538458</v>
       </c>
-    </row>
-    <row r="115" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA114" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>8</v>
       </c>
@@ -22750,8 +23153,11 @@
       <c r="AS115">
         <v>0.53846153846153844</v>
       </c>
-    </row>
-    <row r="116" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA115" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>9</v>
       </c>
@@ -22832,8 +23238,11 @@
       <c r="AS116">
         <v>0.42857142857142849</v>
       </c>
-    </row>
-    <row r="117" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA116" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>10</v>
       </c>
@@ -22914,8 +23323,11 @@
       <c r="AS117">
         <v>0.66666666666666663</v>
       </c>
-    </row>
-    <row r="118" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA117" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>11</v>
       </c>
@@ -22990,8 +23402,11 @@
       <c r="AS118">
         <v>0.42857142857142849</v>
       </c>
-    </row>
-    <row r="119" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA118" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>12</v>
       </c>
@@ -23066,8 +23481,11 @@
       <c r="AS119">
         <v>0.58333333333333337</v>
       </c>
-    </row>
-    <row r="120" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA119" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>13</v>
       </c>
@@ -23142,8 +23560,11 @@
       <c r="AS120">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA120" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="121" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>14</v>
       </c>
@@ -23218,8 +23639,11 @@
       <c r="AS121">
         <v>0.45454545454545447</v>
       </c>
-    </row>
-    <row r="122" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA121" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>15</v>
       </c>
@@ -23294,8 +23718,11 @@
       <c r="AS122">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="123" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA122" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>16</v>
       </c>
@@ -23370,8 +23797,11 @@
       <c r="AS123">
         <v>0.63636363636363635</v>
       </c>
-    </row>
-    <row r="124" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA123" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="124" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>17</v>
       </c>
@@ -23446,8 +23876,11 @@
       <c r="AS124">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="125" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA124" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="125" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>18</v>
       </c>
@@ -23522,8 +23955,11 @@
       <c r="AS125">
         <v>0.8571428571428571</v>
       </c>
-    </row>
-    <row r="126" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA125" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>19</v>
       </c>
@@ -23598,8 +24034,11 @@
       <c r="AS126">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="127" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA126" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>20</v>
       </c>
@@ -23674,8 +24113,11 @@
       <c r="AS127">
         <v>0.66666666666666663</v>
       </c>
-    </row>
-    <row r="128" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA127" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="128" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>21</v>
       </c>
@@ -23750,8 +24192,11 @@
       <c r="AS128">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="129" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA128" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="129" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>22</v>
       </c>
@@ -23826,8 +24271,11 @@
       <c r="AS129">
         <v>0.41666666666666669</v>
       </c>
-    </row>
-    <row r="130" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA129" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="130" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>23</v>
       </c>
@@ -23902,8 +24350,11 @@
       <c r="AS130">
         <v>0.55555555555555558</v>
       </c>
-    </row>
-    <row r="131" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA130" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="131" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>24</v>
       </c>
@@ -23978,8 +24429,11 @@
       <c r="AS131">
         <v>0.54545454545454541</v>
       </c>
-    </row>
-    <row r="132" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA131" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>25</v>
       </c>
@@ -24054,8 +24508,11 @@
       <c r="AS132">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="133" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA132" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="133" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>26</v>
       </c>
@@ -24130,8 +24587,11 @@
       <c r="AS133">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="134" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA133" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="134" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>27</v>
       </c>
@@ -24206,8 +24666,11 @@
       <c r="AS134">
         <v>0.625</v>
       </c>
-    </row>
-    <row r="135" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA134" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="135" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>28</v>
       </c>
@@ -24282,8 +24745,11 @@
       <c r="AS135">
         <v>0.58333333333333337</v>
       </c>
-    </row>
-    <row r="136" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA135" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="136" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>29</v>
       </c>
@@ -24358,8 +24824,11 @@
       <c r="AS136">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="137" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA136" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="137" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>30</v>
       </c>
@@ -24434,8 +24903,11 @@
       <c r="AS137">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="138" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA137" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="138" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>31</v>
       </c>
@@ -24510,8 +24982,11 @@
       <c r="AS138">
         <v>0.54545454545454541</v>
       </c>
-    </row>
-    <row r="139" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA138" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="139" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>32</v>
       </c>
@@ -24586,8 +25061,11 @@
       <c r="AS139">
         <v>0.55555555555555558</v>
       </c>
-    </row>
-    <row r="140" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA139" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="140" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>33</v>
       </c>
@@ -24662,8 +25140,11 @@
       <c r="AS140">
         <v>0.81818181818181823</v>
       </c>
-    </row>
-    <row r="141" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA140" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="141" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>34</v>
       </c>
@@ -24738,8 +25219,11 @@
       <c r="AS141">
         <v>0.44444444444444442</v>
       </c>
-    </row>
-    <row r="142" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA141" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="142" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>35</v>
       </c>
@@ -24814,8 +25298,11 @@
       <c r="AS142">
         <v>0.54545454545454541</v>
       </c>
-    </row>
-    <row r="143" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA142" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="143" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>36</v>
       </c>
@@ -24890,8 +25377,11 @@
       <c r="AS143">
         <v>0.54545454545454541</v>
       </c>
-    </row>
-    <row r="144" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA143" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="144" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>37</v>
       </c>
@@ -24966,8 +25456,11 @@
       <c r="AS144">
         <v>0.45454545454545447</v>
       </c>
-    </row>
-    <row r="145" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA144" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="145" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>38</v>
       </c>
@@ -25042,8 +25535,11 @@
       <c r="AS145">
         <v>0.54545454545454541</v>
       </c>
-    </row>
-    <row r="146" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA145" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="146" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>39</v>
       </c>
@@ -25118,8 +25614,11 @@
       <c r="AS146">
         <v>0.55555555555555558</v>
       </c>
-    </row>
-    <row r="147" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA146" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="147" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>40</v>
       </c>
@@ -25194,8 +25693,11 @@
       <c r="AS147">
         <v>0.66666666666666663</v>
       </c>
-    </row>
-    <row r="148" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA147" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="148" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>41</v>
       </c>
@@ -25270,8 +25772,11 @@
       <c r="AS148">
         <v>0.63636363636363635</v>
       </c>
-    </row>
-    <row r="149" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA148" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="149" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>42</v>
       </c>
@@ -25346,8 +25851,11 @@
       <c r="AS149">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="150" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA149" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="150" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>43</v>
       </c>
@@ -25422,8 +25930,11 @@
       <c r="AS150">
         <v>0.66666666666666663</v>
       </c>
-    </row>
-    <row r="151" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA150" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="151" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>44</v>
       </c>
@@ -25498,8 +26009,11 @@
       <c r="AS151">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="152" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA151" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="152" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>45</v>
       </c>
@@ -25574,8 +26088,11 @@
       <c r="AS152">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="153" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA152" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="153" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>46</v>
       </c>
@@ -25650,8 +26167,11 @@
       <c r="AS153">
         <v>0.88888888888888884</v>
       </c>
-    </row>
-    <row r="154" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA153" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="154" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>47</v>
       </c>
@@ -25726,8 +26246,11 @@
       <c r="AS154">
         <v>0.54545454545454541</v>
       </c>
-    </row>
-    <row r="155" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA154" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="155" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>48</v>
       </c>
@@ -25802,8 +26325,11 @@
       <c r="AS155">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="156" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA155" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="156" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>49</v>
       </c>
@@ -25878,8 +26404,11 @@
       <c r="AS156">
         <v>0.81818181818181823</v>
       </c>
-    </row>
-    <row r="157" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA156" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="157" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>50</v>
       </c>
@@ -25954,8 +26483,11 @@
       <c r="AS157">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="158" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA157" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="158" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>51</v>
       </c>
@@ -26030,8 +26562,11 @@
       <c r="AS158">
         <v>0.36363636363636359</v>
       </c>
-    </row>
-    <row r="159" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA158" s="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="159" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>52</v>
       </c>
@@ -26106,8 +26641,11 @@
       <c r="AS159">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="160" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA159" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="160" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>53</v>
       </c>
@@ -26182,8 +26720,11 @@
       <c r="AS160">
         <v>0.58333333333333337</v>
       </c>
-    </row>
-    <row r="161" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA160" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="161" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>54</v>
       </c>
@@ -26258,8 +26799,11 @@
       <c r="AS161">
         <v>0.81818181818181823</v>
       </c>
-    </row>
-    <row r="162" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA161" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="162" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>55</v>
       </c>
@@ -26334,8 +26878,11 @@
       <c r="AS162">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="163" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA162" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="163" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>56</v>
       </c>
@@ -26410,8 +26957,11 @@
       <c r="AS163">
         <v>0.45454545454545447</v>
       </c>
-    </row>
-    <row r="164" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA163" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="164" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>57</v>
       </c>
@@ -26486,8 +27036,11 @@
       <c r="AS164">
         <v>0.38461538461538458</v>
       </c>
-    </row>
-    <row r="165" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA164" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="165" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>58</v>
       </c>
@@ -26562,8 +27115,11 @@
       <c r="AS165">
         <v>0.63636363636363635</v>
       </c>
-    </row>
-    <row r="166" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA165" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="166" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>59</v>
       </c>
@@ -26638,8 +27194,11 @@
       <c r="AS166">
         <v>0.54545454545454541</v>
       </c>
-    </row>
-    <row r="167" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA166" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="167" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>60</v>
       </c>
@@ -26714,8 +27273,11 @@
       <c r="AS167">
         <v>0.33333333333333331</v>
       </c>
-    </row>
-    <row r="168" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA167" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="168" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>61</v>
       </c>
@@ -26790,8 +27352,11 @@
       <c r="AS168">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="169" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA168" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="169" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>62</v>
       </c>
@@ -26866,8 +27431,11 @@
       <c r="AS169">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="170" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA169" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="170" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>63</v>
       </c>
@@ -26942,8 +27510,11 @@
       <c r="AS170">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="171" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA170" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="171" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>64</v>
       </c>
@@ -27018,8 +27589,11 @@
       <c r="AS171">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="172" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA171" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="172" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>65</v>
       </c>
@@ -27094,8 +27668,11 @@
       <c r="AS172">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="173" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA172" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="173" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>66</v>
       </c>
@@ -27170,8 +27747,11 @@
       <c r="AS173">
         <v>0.58333333333333337</v>
       </c>
-    </row>
-    <row r="174" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA173" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="174" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>67</v>
       </c>
@@ -27246,8 +27826,11 @@
       <c r="AS174">
         <v>0.44444444444444442</v>
       </c>
-    </row>
-    <row r="175" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA174" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="175" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>68</v>
       </c>
@@ -27322,8 +27905,11 @@
       <c r="AS175">
         <v>0.46153846153846162</v>
       </c>
-    </row>
-    <row r="176" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA175" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="176" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>69</v>
       </c>
@@ -27398,8 +27984,11 @@
       <c r="AS176">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="177" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA176" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="177" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>70</v>
       </c>
@@ -27474,8 +28063,11 @@
       <c r="AS177">
         <v>0.5714285714285714</v>
       </c>
-    </row>
-    <row r="178" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA177" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="178" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>71</v>
       </c>
@@ -27550,8 +28142,11 @@
       <c r="AS178">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="179" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA178" s="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="179" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>72</v>
       </c>
@@ -27626,8 +28221,11 @@
       <c r="AS179">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="180" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA179" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="180" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>73</v>
       </c>
@@ -27702,8 +28300,11 @@
       <c r="AS180">
         <v>0.33333333333333331</v>
       </c>
-    </row>
-    <row r="181" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA180" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="181" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>74</v>
       </c>
@@ -27778,8 +28379,11 @@
       <c r="AS181">
         <v>0.625</v>
       </c>
-    </row>
-    <row r="182" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA181" s="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="182" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>75</v>
       </c>
@@ -27854,8 +28458,11 @@
       <c r="AS182">
         <v>0.45454545454545447</v>
       </c>
-    </row>
-    <row r="183" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA182" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="183" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>76</v>
       </c>
@@ -27930,8 +28537,11 @@
       <c r="AS183">
         <v>0.45454545454545447</v>
       </c>
-    </row>
-    <row r="184" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA183" s="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="184" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>77</v>
       </c>
@@ -28006,8 +28616,11 @@
       <c r="AS184">
         <v>0.33333333333333331</v>
       </c>
-    </row>
-    <row r="185" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA184" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="185" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>78</v>
       </c>
@@ -28082,8 +28695,11 @@
       <c r="AS185">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="186" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA185" s="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="186" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>79</v>
       </c>
@@ -28158,8 +28774,11 @@
       <c r="AS186">
         <v>0.54545454545454541</v>
       </c>
-    </row>
-    <row r="187" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA186" s="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="187" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>80</v>
       </c>
@@ -28234,8 +28853,11 @@
       <c r="AS187">
         <v>0.66666666666666663</v>
       </c>
-    </row>
-    <row r="188" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA187" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="188" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>81</v>
       </c>
@@ -28310,8 +28932,11 @@
       <c r="AS188">
         <v>0.44444444444444442</v>
       </c>
-    </row>
-    <row r="189" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA188" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="189" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>82</v>
       </c>
@@ -28386,8 +29011,11 @@
       <c r="AS189">
         <v>0.44444444444444442</v>
       </c>
-    </row>
-    <row r="190" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA189" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="190" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>83</v>
       </c>
@@ -28462,8 +29090,11 @@
       <c r="AS190">
         <v>0.38461538461538458</v>
       </c>
-    </row>
-    <row r="191" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA190" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="191" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>84</v>
       </c>
@@ -28538,8 +29169,11 @@
       <c r="AS191">
         <v>0.22222222222222221</v>
       </c>
-    </row>
-    <row r="192" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA191" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="192" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>85</v>
       </c>
@@ -28614,8 +29248,11 @@
       <c r="AS192">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="193" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA192" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="193" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>86</v>
       </c>
@@ -28690,8 +29327,11 @@
       <c r="AS193">
         <v>0.46153846153846162</v>
       </c>
-    </row>
-    <row r="194" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA193" s="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="194" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>87</v>
       </c>
@@ -28766,8 +29406,11 @@
       <c r="AS194">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="195" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA194" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="195" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>88</v>
       </c>
@@ -28842,8 +29485,11 @@
       <c r="AS195">
         <v>0.33333333333333331</v>
       </c>
-    </row>
-    <row r="196" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA195" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="196" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>89</v>
       </c>
@@ -28918,8 +29564,11 @@
       <c r="AS196">
         <v>0.36363636363636359</v>
       </c>
-    </row>
-    <row r="197" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA196" s="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="197" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>90</v>
       </c>
@@ -28994,8 +29643,11 @@
       <c r="AS197">
         <v>0.53846153846153844</v>
       </c>
-    </row>
-    <row r="198" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA197" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="198" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>91</v>
       </c>
@@ -29070,8 +29722,11 @@
       <c r="AS198">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="199" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA198" s="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="199" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>92</v>
       </c>
@@ -29146,8 +29801,11 @@
       <c r="AS199">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="200" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA199" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="200" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>93</v>
       </c>
@@ -29222,8 +29880,11 @@
       <c r="AS200">
         <v>0.33333333333333331</v>
       </c>
-    </row>
-    <row r="201" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA200" s="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="201" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>94</v>
       </c>
@@ -29298,8 +29959,11 @@
       <c r="AS201">
         <v>0.58333333333333337</v>
       </c>
-    </row>
-    <row r="202" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA201" s="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="202" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>95</v>
       </c>
@@ -29374,8 +30038,11 @@
       <c r="AS202">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="203" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA202" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="203" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>96</v>
       </c>
@@ -29450,8 +30117,11 @@
       <c r="AS203">
         <v>0.27272727272727271</v>
       </c>
-    </row>
-    <row r="204" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA203" s="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="204" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>97</v>
       </c>
@@ -29526,8 +30196,11 @@
       <c r="AS204">
         <v>0.63636363636363635</v>
       </c>
-    </row>
-    <row r="205" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA204" s="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="205" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>98</v>
       </c>
@@ -29602,8 +30275,11 @@
       <c r="AS205">
         <v>0.81818181818181823</v>
       </c>
-    </row>
-    <row r="206" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA205" s="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="206" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>99</v>
       </c>
@@ -29678,8 +30354,11 @@
       <c r="AS206">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="207" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA206" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="207" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>100</v>
       </c>
@@ -29754,16 +30433,19 @@
       <c r="AS207">
         <v>0.38461538461538458</v>
       </c>
-    </row>
-    <row r="208" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA207" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="208" spans="1:53" x14ac:dyDescent="0.2">
       <c r="AD208" s="9"/>
       <c r="AE208" s="9"/>
     </row>
-    <row r="209" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:53" x14ac:dyDescent="0.2">
       <c r="AD209" s="9"/>
       <c r="AE209" s="9"/>
     </row>
-    <row r="210" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
         <v>29</v>
       </c>
@@ -29778,8 +30460,11 @@
       <c r="AM210" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="211" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA210" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="211" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
         <v>28</v>
       </c>
@@ -29794,8 +30479,11 @@
       <c r="AM211" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="212" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA211" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="212" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>1</v>
       </c>
@@ -29879,8 +30567,11 @@
       <c r="AS212">
         <v>0.94198333333333328</v>
       </c>
-    </row>
-    <row r="213" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA212" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>2</v>
       </c>
@@ -29964,8 +30655,11 @@
       <c r="AS213">
         <v>0.95471666666666666</v>
       </c>
-    </row>
-    <row r="214" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA213" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>3</v>
       </c>
@@ -30049,8 +30743,11 @@
       <c r="AS214">
         <v>0.91738571428571436</v>
       </c>
-    </row>
-    <row r="215" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA214" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="215" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>4</v>
       </c>
@@ -30134,8 +30831,11 @@
       <c r="AS215">
         <v>0.91511428571428577</v>
       </c>
-    </row>
-    <row r="216" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA215" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>5</v>
       </c>
@@ -30219,8 +30919,11 @@
       <c r="AS216">
         <v>0.89755000000000007</v>
       </c>
-    </row>
-    <row r="217" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA216" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>6</v>
       </c>
@@ -30301,8 +31004,11 @@
       <c r="AS217">
         <v>0.92395000000000005</v>
       </c>
-    </row>
-    <row r="218" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA217" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="218" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>7</v>
       </c>
@@ -30383,8 +31089,11 @@
       <c r="AS218">
         <v>0.77978571428571442</v>
       </c>
-    </row>
-    <row r="219" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA218" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="219" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>8</v>
       </c>
@@ -30465,8 +31174,11 @@
       <c r="AS219">
         <v>0.91272857142857144</v>
       </c>
-    </row>
-    <row r="220" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA219" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="220" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>9</v>
       </c>
@@ -30547,8 +31259,11 @@
       <c r="AS220">
         <v>0.91278333333333339</v>
       </c>
-    </row>
-    <row r="221" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA220" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="221" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>10</v>
       </c>
@@ -30629,8 +31344,11 @@
       <c r="AS221">
         <v>0.75797999999999988</v>
       </c>
-    </row>
-    <row r="222" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA221" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="222" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>11</v>
       </c>
@@ -30705,8 +31423,11 @@
       <c r="AS222">
         <v>0.90810000000000002</v>
       </c>
-    </row>
-    <row r="223" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA222" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="223" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>12</v>
       </c>
@@ -30781,8 +31502,11 @@
       <c r="AS223">
         <v>0.80993749999999998</v>
       </c>
-    </row>
-    <row r="224" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA223" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="224" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>13</v>
       </c>
@@ -30857,8 +31581,11 @@
       <c r="AS224">
         <v>0.90215714285714277</v>
       </c>
-    </row>
-    <row r="225" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA224" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="225" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>14</v>
       </c>
@@ -30933,8 +31660,11 @@
       <c r="AS225">
         <v>0.7567600000000001</v>
       </c>
-    </row>
-    <row r="226" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA225" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="226" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>15</v>
       </c>
@@ -31009,8 +31739,11 @@
       <c r="AS226">
         <v>0.86181666666666679</v>
       </c>
-    </row>
-    <row r="227" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA226" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="227" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>16</v>
       </c>
@@ -31085,8 +31818,11 @@
       <c r="AS227">
         <v>0.90218571428571426</v>
       </c>
-    </row>
-    <row r="228" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA227" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="228" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>17</v>
       </c>
@@ -31161,8 +31897,11 @@
       <c r="AS228">
         <v>0.89542499999999992</v>
       </c>
-    </row>
-    <row r="229" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA228" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="229" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>18</v>
       </c>
@@ -31237,8 +31976,11 @@
       <c r="AS229">
         <v>0.91136666666666655</v>
       </c>
-    </row>
-    <row r="230" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA229" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="230" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>19</v>
       </c>
@@ -31313,8 +32055,11 @@
       <c r="AS230">
         <v>0.89470000000000016</v>
       </c>
-    </row>
-    <row r="231" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA230" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="231" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>20</v>
       </c>
@@ -31389,8 +32134,11 @@
       <c r="AS231">
         <v>0.96038333333333326</v>
       </c>
-    </row>
-    <row r="232" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA231" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="232" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>21</v>
       </c>
@@ -31465,8 +32213,11 @@
       <c r="AS232">
         <v>0.92231666666666667</v>
       </c>
-    </row>
-    <row r="233" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA232" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="233" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>22</v>
       </c>
@@ -31541,8 +32292,11 @@
       <c r="AS233">
         <v>0.91542499999999982</v>
       </c>
-    </row>
-    <row r="234" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA233" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="234" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>23</v>
       </c>
@@ -31617,8 +32371,11 @@
       <c r="AS234">
         <v>0.90136666666666676</v>
       </c>
-    </row>
-    <row r="235" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA234" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="235" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>24</v>
       </c>
@@ -31693,8 +32450,11 @@
       <c r="AS235">
         <v>0.94268333333333321</v>
       </c>
-    </row>
-    <row r="236" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA235" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="236" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>25</v>
       </c>
@@ -31769,8 +32529,11 @@
       <c r="AS236">
         <v>0.95360909090909085</v>
       </c>
-    </row>
-    <row r="237" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA236" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="237" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <v>26</v>
       </c>
@@ -31845,8 +32608,11 @@
       <c r="AS237">
         <v>0.95623999999999987</v>
       </c>
-    </row>
-    <row r="238" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA237" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="238" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <v>27</v>
       </c>
@@ -31921,8 +32687,11 @@
       <c r="AS238">
         <v>0.96153</v>
       </c>
-    </row>
-    <row r="239" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA238" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="239" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <v>28</v>
       </c>
@@ -31997,8 +32766,11 @@
       <c r="AS239">
         <v>0.96458333333333324</v>
       </c>
-    </row>
-    <row r="240" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA239" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="240" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <v>29</v>
       </c>
@@ -32073,8 +32845,11 @@
       <c r="AS240">
         <v>0.96186249999999995</v>
       </c>
-    </row>
-    <row r="241" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA240" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="241" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <v>30</v>
       </c>
@@ -32149,8 +32924,11 @@
       <c r="AS241">
         <v>0.9386444444444445</v>
       </c>
-    </row>
-    <row r="242" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA241" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="242" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>31</v>
       </c>
@@ -32225,8 +33003,11 @@
       <c r="AS242">
         <v>0.91652857142857158</v>
       </c>
-    </row>
-    <row r="243" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA242" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="243" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <v>32</v>
       </c>
@@ -32301,8 +33082,11 @@
       <c r="AS243">
         <v>0.96307777777777781</v>
       </c>
-    </row>
-    <row r="244" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA243" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="244" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>33</v>
       </c>
@@ -32377,8 +33161,11 @@
       <c r="AS244">
         <v>0.95486666666666675</v>
       </c>
-    </row>
-    <row r="245" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA244" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="245" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>34</v>
       </c>
@@ -32453,8 +33240,11 @@
       <c r="AS245">
         <v>0.94298888888888888</v>
       </c>
-    </row>
-    <row r="246" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA245" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="246" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>35</v>
       </c>
@@ -32529,8 +33319,11 @@
       <c r="AS246">
         <v>0.97228571428571431</v>
       </c>
-    </row>
-    <row r="247" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA246" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="247" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <v>36</v>
       </c>
@@ -32605,8 +33398,11 @@
       <c r="AS247">
         <v>0.93649999999999989</v>
       </c>
-    </row>
-    <row r="248" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA247" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="248" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>37</v>
       </c>
@@ -32681,8 +33477,11 @@
       <c r="AS248">
         <v>0.9419142857142857</v>
       </c>
-    </row>
-    <row r="249" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA248" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="249" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>38</v>
       </c>
@@ -32757,8 +33556,11 @@
       <c r="AS249">
         <v>0.95831428571428567</v>
       </c>
-    </row>
-    <row r="250" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA249" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="250" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>39</v>
       </c>
@@ -32833,8 +33635,11 @@
       <c r="AS250">
         <v>0.94653749999999992</v>
       </c>
-    </row>
-    <row r="251" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA250" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="251" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>40</v>
       </c>
@@ -32909,8 +33714,11 @@
       <c r="AS251">
         <v>0.96586666666666654</v>
       </c>
-    </row>
-    <row r="252" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA251" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="252" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>41</v>
       </c>
@@ -32985,8 +33793,11 @@
       <c r="AS252">
         <v>0.92795000000000005</v>
       </c>
-    </row>
-    <row r="253" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA252" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="253" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>42</v>
       </c>
@@ -33061,8 +33872,11 @@
       <c r="AS253">
         <v>0.96031111111111123</v>
       </c>
-    </row>
-    <row r="254" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA253" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="254" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>43</v>
       </c>
@@ -33137,8 +33951,11 @@
       <c r="AS254">
         <v>0.96823333333333339</v>
       </c>
-    </row>
-    <row r="255" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA254" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="255" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>44</v>
       </c>
@@ -33213,8 +34030,11 @@
       <c r="AS255">
         <v>0.96959999999999991</v>
       </c>
-    </row>
-    <row r="256" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA255" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="256" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <v>45</v>
       </c>
@@ -33289,8 +34109,11 @@
       <c r="AS256">
         <v>0.96101250000000005</v>
       </c>
-    </row>
-    <row r="257" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA256" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="257" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>46</v>
       </c>
@@ -33365,8 +34188,11 @@
       <c r="AS257">
         <v>0.92866666666666686</v>
       </c>
-    </row>
-    <row r="258" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA257" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="258" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <v>47</v>
       </c>
@@ -33441,8 +34267,11 @@
       <c r="AS258">
         <v>0.96888571428571435</v>
       </c>
-    </row>
-    <row r="259" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA258" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="259" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>48</v>
       </c>
@@ -33517,8 +34346,11 @@
       <c r="AS259">
         <v>0.95882000000000001</v>
       </c>
-    </row>
-    <row r="260" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA259" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="260" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>49</v>
       </c>
@@ -33593,8 +34425,11 @@
       <c r="AS260">
         <v>0.96733333333333338</v>
       </c>
-    </row>
-    <row r="261" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA260" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="261" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>50</v>
       </c>
@@ -33669,8 +34504,11 @@
       <c r="AS261">
         <v>0.97041428571428578</v>
       </c>
-    </row>
-    <row r="262" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA261" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="262" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>51</v>
       </c>
@@ -33745,8 +34583,11 @@
       <c r="AS262">
         <v>0.95366249999999997</v>
       </c>
-    </row>
-    <row r="263" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA262" s="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="263" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>52</v>
       </c>
@@ -33821,8 +34662,11 @@
       <c r="AS263">
         <v>0.93544285714285713</v>
       </c>
-    </row>
-    <row r="264" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA263" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="264" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>53</v>
       </c>
@@ -33897,8 +34741,11 @@
       <c r="AS264">
         <v>0.95155000000000001</v>
       </c>
-    </row>
-    <row r="265" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA264" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="265" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>54</v>
       </c>
@@ -33973,8 +34820,11 @@
       <c r="AS265">
         <v>0.95768000000000009</v>
       </c>
-    </row>
-    <row r="266" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA265" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="266" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>55</v>
       </c>
@@ -34049,8 +34899,11 @@
       <c r="AS266">
         <v>0.90600000000000003</v>
       </c>
-    </row>
-    <row r="267" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA266" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="267" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>56</v>
       </c>
@@ -34125,8 +34978,11 @@
       <c r="AS267">
         <v>0.96723333333333328</v>
       </c>
-    </row>
-    <row r="268" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA267" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="268" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>57</v>
       </c>
@@ -34201,8 +35057,11 @@
       <c r="AS268">
         <v>0.96689999999999998</v>
       </c>
-    </row>
-    <row r="269" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA268" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="269" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>58</v>
       </c>
@@ -34277,8 +35136,11 @@
       <c r="AS269">
         <v>0.97011666666666663</v>
       </c>
-    </row>
-    <row r="270" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA269" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="270" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>59</v>
       </c>
@@ -34353,8 +35215,11 @@
       <c r="AS270">
         <v>0.96818750000000009</v>
       </c>
-    </row>
-    <row r="271" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA270" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="271" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>60</v>
       </c>
@@ -34429,8 +35294,11 @@
       <c r="AS271">
         <v>0.97386249999999996</v>
       </c>
-    </row>
-    <row r="272" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA271" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="272" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>61</v>
       </c>
@@ -34505,8 +35373,11 @@
       <c r="AS272">
         <v>0.9821833333333333</v>
       </c>
-    </row>
-    <row r="273" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA272" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="273" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>62</v>
       </c>
@@ -34581,8 +35452,11 @@
       <c r="AS273">
         <v>0.97032000000000007</v>
       </c>
-    </row>
-    <row r="274" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA273" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="274" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>63</v>
       </c>
@@ -34657,8 +35531,11 @@
       <c r="AS274">
         <v>0.96582500000000004</v>
       </c>
-    </row>
-    <row r="275" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA274" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="275" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>64</v>
       </c>
@@ -34733,8 +35610,11 @@
       <c r="AS275">
         <v>0.96600000000000008</v>
       </c>
-    </row>
-    <row r="276" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA275" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="276" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <v>65</v>
       </c>
@@ -34809,8 +35689,11 @@
       <c r="AS276">
         <v>0.96755000000000002</v>
       </c>
-    </row>
-    <row r="277" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA276" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="277" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <v>66</v>
       </c>
@@ -34885,8 +35768,11 @@
       <c r="AS277">
         <v>0.96891666666666676</v>
       </c>
-    </row>
-    <row r="278" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA277" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="278" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>67</v>
       </c>
@@ -34961,8 +35847,11 @@
       <c r="AS278">
         <v>0.94248750000000003</v>
       </c>
-    </row>
-    <row r="279" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA278" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="279" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>68</v>
       </c>
@@ -35037,8 +35926,11 @@
       <c r="AS279">
         <v>0.95763999999999994</v>
       </c>
-    </row>
-    <row r="280" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA279" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="280" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>69</v>
       </c>
@@ -35113,8 +36005,11 @@
       <c r="AS280">
         <v>0.975275</v>
       </c>
-    </row>
-    <row r="281" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA280" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="281" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>70</v>
       </c>
@@ -35189,8 +36084,11 @@
       <c r="AS281">
         <v>0.9575499999999999</v>
       </c>
-    </row>
-    <row r="282" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA281" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="282" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>71</v>
       </c>
@@ -35265,8 +36163,11 @@
       <c r="AS282">
         <v>0.90613333333333335</v>
       </c>
-    </row>
-    <row r="283" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA282" s="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="283" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>72</v>
       </c>
@@ -35341,8 +36242,11 @@
       <c r="AS283">
         <v>0.96537142857142855</v>
       </c>
-    </row>
-    <row r="284" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA283" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="284" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>73</v>
       </c>
@@ -35417,8 +36321,11 @@
       <c r="AS284">
         <v>0.95901111111111115</v>
       </c>
-    </row>
-    <row r="285" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA284" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="285" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>74</v>
       </c>
@@ -35493,8 +36400,11 @@
       <c r="AS285">
         <v>0.96733749999999996</v>
       </c>
-    </row>
-    <row r="286" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA285" s="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="286" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>75</v>
       </c>
@@ -35569,8 +36479,11 @@
       <c r="AS286">
         <v>0.91441249999999996</v>
       </c>
-    </row>
-    <row r="287" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA286" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="287" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>76</v>
       </c>
@@ -35645,8 +36558,11 @@
       <c r="AS287">
         <v>0.9417428571428571</v>
       </c>
-    </row>
-    <row r="288" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA287" s="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="288" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>77</v>
       </c>
@@ -35721,8 +36637,11 @@
       <c r="AS288">
         <v>0.91981111111111113</v>
       </c>
-    </row>
-    <row r="289" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA288" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="289" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>78</v>
       </c>
@@ -35797,8 +36716,11 @@
       <c r="AS289">
         <v>0.95840000000000014</v>
       </c>
-    </row>
-    <row r="290" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA289" s="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="290" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>79</v>
       </c>
@@ -35873,8 +36795,11 @@
       <c r="AS290">
         <v>0.96347142857142865</v>
       </c>
-    </row>
-    <row r="291" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA290" s="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="291" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>80</v>
       </c>
@@ -35949,8 +36874,11 @@
       <c r="AS291">
         <v>0.95381249999999995</v>
       </c>
-    </row>
-    <row r="292" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA291" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="292" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>81</v>
       </c>
@@ -36025,8 +36953,11 @@
       <c r="AS292">
         <v>0.95383333333333331</v>
       </c>
-    </row>
-    <row r="293" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA292" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="293" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>82</v>
       </c>
@@ -36101,8 +37032,11 @@
       <c r="AS293">
         <v>0.97686666666666666</v>
       </c>
-    </row>
-    <row r="294" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA293" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="294" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>83</v>
       </c>
@@ -36177,8 +37111,11 @@
       <c r="AS294">
         <v>0.95933333333333337</v>
       </c>
-    </row>
-    <row r="295" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA294" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="295" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>84</v>
       </c>
@@ -36253,8 +37190,11 @@
       <c r="AS295">
         <v>0.96682999999999986</v>
       </c>
-    </row>
-    <row r="296" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA295" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="296" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>85</v>
       </c>
@@ -36329,8 +37269,11 @@
       <c r="AS296">
         <v>0.97610000000000008</v>
       </c>
-    </row>
-    <row r="297" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA296" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="297" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>86</v>
       </c>
@@ -36405,8 +37348,11 @@
       <c r="AS297">
         <v>0.97502500000000003</v>
       </c>
-    </row>
-    <row r="298" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA297" s="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="298" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>87</v>
       </c>
@@ -36481,8 +37427,11 @@
       <c r="AS298">
         <v>0.92469000000000001</v>
       </c>
-    </row>
-    <row r="299" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA298" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="299" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>88</v>
       </c>
@@ -36557,8 +37506,11 @@
       <c r="AS299">
         <v>0.97700999999999993</v>
       </c>
-    </row>
-    <row r="300" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA299" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="300" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>89</v>
       </c>
@@ -36633,8 +37585,11 @@
       <c r="AS300">
         <v>0.96512857142857145</v>
       </c>
-    </row>
-    <row r="301" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA300" s="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="301" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>90</v>
       </c>
@@ -36709,8 +37664,11 @@
       <c r="AS301">
         <v>0.97598000000000007</v>
       </c>
-    </row>
-    <row r="302" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA301" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="302" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>91</v>
       </c>
@@ -36785,8 +37743,11 @@
       <c r="AS302">
         <v>0.97645000000000004</v>
       </c>
-    </row>
-    <row r="303" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA302" s="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="303" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
         <v>92</v>
       </c>
@@ -36861,8 +37822,11 @@
       <c r="AS303">
         <v>0.97387777777777784</v>
       </c>
-    </row>
-    <row r="304" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA303" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="304" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
         <v>93</v>
       </c>
@@ -36937,8 +37901,11 @@
       <c r="AS304">
         <v>0.95833333333333337</v>
       </c>
-    </row>
-    <row r="305" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA304" s="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="305" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
         <v>94</v>
       </c>
@@ -37013,8 +37980,11 @@
       <c r="AS305">
         <v>0.91301428571428578</v>
       </c>
-    </row>
-    <row r="306" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA305" s="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="306" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
         <v>95</v>
       </c>
@@ -37089,8 +38059,11 @@
       <c r="AS306">
         <v>0.90313749999999993</v>
       </c>
-    </row>
-    <row r="307" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA306" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="307" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
         <v>96</v>
       </c>
@@ -37165,8 +38138,11 @@
       <c r="AS307">
         <v>0.88618333333333332</v>
       </c>
-    </row>
-    <row r="308" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA307" s="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="308" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A308" s="1">
         <v>97</v>
       </c>
@@ -37241,8 +38217,11 @@
       <c r="AS308">
         <v>0.97451249999999989</v>
       </c>
-    </row>
-    <row r="309" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA308" s="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="309" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A309" s="1">
         <v>98</v>
       </c>
@@ -37317,8 +38296,11 @@
       <c r="AS309">
         <v>0.9770833333333333</v>
       </c>
-    </row>
-    <row r="310" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA309" s="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="310" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A310" s="1">
         <v>99</v>
       </c>
@@ -37393,8 +38375,11 @@
       <c r="AS310">
         <v>0.96742499999999998</v>
       </c>
-    </row>
-    <row r="311" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA310" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="311" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A311" s="1">
         <v>100</v>
       </c>
@@ -37469,16 +38454,19 @@
       <c r="AS311">
         <v>0.97483750000000002</v>
       </c>
-    </row>
-    <row r="312" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA311" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="312" spans="1:53" x14ac:dyDescent="0.2">
       <c r="AD312" s="9"/>
       <c r="AE312" s="9"/>
     </row>
-    <row r="313" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:53" x14ac:dyDescent="0.2">
       <c r="AD313" s="9"/>
       <c r="AE313" s="9"/>
     </row>
-    <row r="314" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
         <v>31</v>
       </c>
@@ -37493,8 +38481,11 @@
       <c r="AM314" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="315" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA314" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="315" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A315" s="3" t="s">
         <v>28</v>
       </c>
@@ -37509,8 +38500,11 @@
       <c r="AM315" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="316" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA315" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="316" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A316" s="1">
         <v>1</v>
       </c>
@@ -37594,8 +38588,11 @@
       <c r="AS316">
         <v>4.48E-2</v>
       </c>
-    </row>
-    <row r="317" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA316" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A317" s="1">
         <v>2</v>
       </c>
@@ -37679,8 +38676,11 @@
       <c r="AS317">
         <v>3.32E-2</v>
       </c>
-    </row>
-    <row r="318" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA317" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="318" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A318" s="1">
         <v>3</v>
       </c>
@@ -37764,8 +38764,11 @@
       <c r="AS318">
         <v>0.16289999999999999</v>
       </c>
-    </row>
-    <row r="319" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA318" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="319" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A319" s="1">
         <v>4</v>
       </c>
@@ -37849,8 +38852,11 @@
       <c r="AS319">
         <v>0.2114</v>
       </c>
-    </row>
-    <row r="320" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA319" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="320" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A320" s="1">
         <v>5</v>
       </c>
@@ -37934,8 +38940,11 @@
       <c r="AS320">
         <v>0.22700000000000001</v>
       </c>
-    </row>
-    <row r="321" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA320" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="321" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A321" s="1">
         <v>6</v>
       </c>
@@ -38016,8 +39025,11 @@
       <c r="AS321">
         <v>8.1299999999999997E-2</v>
       </c>
-    </row>
-    <row r="322" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA321" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="322" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A322" s="1">
         <v>7</v>
       </c>
@@ -38098,8 +39110,11 @@
       <c r="AS322">
         <v>0.1993</v>
       </c>
-    </row>
-    <row r="323" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA322" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="323" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A323" s="1">
         <v>8</v>
       </c>
@@ -38180,8 +39195,11 @@
       <c r="AS323">
         <v>0.36909999999999998</v>
       </c>
-    </row>
-    <row r="324" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA323" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="324" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
         <v>9</v>
       </c>
@@ -38262,8 +39280,11 @@
       <c r="AS324">
         <v>0.42449999999999999</v>
       </c>
-    </row>
-    <row r="325" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA324" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="325" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
         <v>10</v>
       </c>
@@ -38344,8 +39365,11 @@
       <c r="AS325">
         <v>0.37519999999999998</v>
       </c>
-    </row>
-    <row r="326" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA325" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="326" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A326" s="1">
         <v>11</v>
       </c>
@@ -38420,8 +39444,11 @@
       <c r="AS326">
         <v>0.44729999999999998</v>
       </c>
-    </row>
-    <row r="327" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA326" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="327" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A327" s="1">
         <v>12</v>
       </c>
@@ -38496,8 +39523,11 @@
       <c r="AS327">
         <v>0.55310000000000004</v>
       </c>
-    </row>
-    <row r="328" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA327" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="328" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
         <v>13</v>
       </c>
@@ -38572,8 +39602,11 @@
       <c r="AS328">
         <v>0.5373</v>
       </c>
-    </row>
-    <row r="329" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA328" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="329" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A329" s="1">
         <v>14</v>
       </c>
@@ -38648,8 +39681,11 @@
       <c r="AS329">
         <v>0.65339999999999998</v>
       </c>
-    </row>
-    <row r="330" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA329" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="330" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A330" s="1">
         <v>15</v>
       </c>
@@ -38724,8 +39760,11 @@
       <c r="AS330">
         <v>0.7944</v>
       </c>
-    </row>
-    <row r="331" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA330" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="331" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A331" s="1">
         <v>16</v>
       </c>
@@ -38800,8 +39839,11 @@
       <c r="AS331">
         <v>0.80310000000000004</v>
       </c>
-    </row>
-    <row r="332" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA331" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="332" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A332" s="1">
         <v>17</v>
       </c>
@@ -38876,8 +39918,11 @@
       <c r="AS332">
         <v>0.86119999999999997</v>
       </c>
-    </row>
-    <row r="333" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA332" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="333" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A333" s="1">
         <v>18</v>
       </c>
@@ -38952,8 +39997,11 @@
       <c r="AS333">
         <v>0.89319999999999999</v>
       </c>
-    </row>
-    <row r="334" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA333" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="334" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A334" s="1">
         <v>19</v>
       </c>
@@ -39028,8 +40076,11 @@
       <c r="AS334">
         <v>0.89270000000000005</v>
       </c>
-    </row>
-    <row r="335" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA334" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="335" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A335" s="1">
         <v>20</v>
       </c>
@@ -39104,8 +40155,11 @@
       <c r="AS335">
         <v>0.87260000000000004</v>
       </c>
-    </row>
-    <row r="336" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA335" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="336" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A336" s="1">
         <v>21</v>
       </c>
@@ -39180,8 +40234,11 @@
       <c r="AS336">
         <v>0.86250000000000004</v>
       </c>
-    </row>
-    <row r="337" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA336" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="337" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A337" s="1">
         <v>22</v>
       </c>
@@ -39256,8 +40313,11 @@
       <c r="AS337">
         <v>0.83189999999999997</v>
       </c>
-    </row>
-    <row r="338" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA337" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="338" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A338" s="1">
         <v>23</v>
       </c>
@@ -39332,8 +40392,11 @@
       <c r="AS338">
         <v>0.87290000000000001</v>
       </c>
-    </row>
-    <row r="339" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA338" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="339" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A339" s="1">
         <v>24</v>
       </c>
@@ -39408,8 +40471,11 @@
       <c r="AS339">
         <v>0.93689999999999996</v>
       </c>
-    </row>
-    <row r="340" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA339" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="340" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A340" s="1">
         <v>25</v>
       </c>
@@ -39484,8 +40550,11 @@
       <c r="AS340">
         <v>0.93459999999999999</v>
       </c>
-    </row>
-    <row r="341" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA340" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="341" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A341" s="1">
         <v>26</v>
       </c>
@@ -39560,8 +40629,11 @@
       <c r="AS341">
         <v>0.92900000000000005</v>
       </c>
-    </row>
-    <row r="342" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA341" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="342" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A342" s="1">
         <v>27</v>
       </c>
@@ -39636,8 +40708,11 @@
       <c r="AS342">
         <v>0.96940000000000004</v>
       </c>
-    </row>
-    <row r="343" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA342" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="343" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A343" s="1">
         <v>28</v>
       </c>
@@ -39712,8 +40787,11 @@
       <c r="AS343">
         <v>0.95079999999999998</v>
       </c>
-    </row>
-    <row r="344" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA343" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="344" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A344" s="1">
         <v>29</v>
       </c>
@@ -39788,8 +40866,11 @@
       <c r="AS344">
         <v>0.94779999999999998</v>
       </c>
-    </row>
-    <row r="345" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA344" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="345" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A345" s="1">
         <v>30</v>
       </c>
@@ -39864,8 +40945,11 @@
       <c r="AS345">
         <v>0.94289999999999996</v>
       </c>
-    </row>
-    <row r="346" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA345" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="346" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A346" s="1">
         <v>31</v>
       </c>
@@ -39940,8 +41024,11 @@
       <c r="AS346">
         <v>0.9385</v>
       </c>
-    </row>
-    <row r="347" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA346" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="347" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A347" s="1">
         <v>32</v>
       </c>
@@ -40016,8 +41103,11 @@
       <c r="AS347">
         <v>0.95279999999999998</v>
       </c>
-    </row>
-    <row r="348" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA347" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="348" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A348" s="1">
         <v>33</v>
       </c>
@@ -40092,8 +41182,11 @@
       <c r="AS348">
         <v>0.96430000000000005</v>
       </c>
-    </row>
-    <row r="349" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA348" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="349" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A349" s="1">
         <v>34</v>
       </c>
@@ -40168,8 +41261,11 @@
       <c r="AS349">
         <v>0.94230000000000003</v>
       </c>
-    </row>
-    <row r="350" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA349" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="350" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A350" s="1">
         <v>35</v>
       </c>
@@ -40244,8 +41340,11 @@
       <c r="AS350">
         <v>0.96440000000000003</v>
       </c>
-    </row>
-    <row r="351" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA350" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="351" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A351" s="1">
         <v>36</v>
       </c>
@@ -40320,8 +41419,11 @@
       <c r="AS351">
         <v>0.96189999999999998</v>
       </c>
-    </row>
-    <row r="352" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA351" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="352" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A352" s="1">
         <v>37</v>
       </c>
@@ -40396,8 +41498,11 @@
       <c r="AS352">
         <v>0.95809999999999995</v>
       </c>
-    </row>
-    <row r="353" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA352" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="353" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A353" s="1">
         <v>38</v>
       </c>
@@ -40472,8 +41577,11 @@
       <c r="AS353">
         <v>0.96230000000000004</v>
       </c>
-    </row>
-    <row r="354" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA353" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="354" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A354" s="1">
         <v>39</v>
       </c>
@@ -40548,8 +41656,11 @@
       <c r="AS354">
         <v>0.96430000000000005</v>
       </c>
-    </row>
-    <row r="355" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA354" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="355" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A355" s="1">
         <v>40</v>
       </c>
@@ -40624,8 +41735,11 @@
       <c r="AS355">
         <v>0.95709999999999995</v>
       </c>
-    </row>
-    <row r="356" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA355" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="356" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A356" s="1">
         <v>41</v>
       </c>
@@ -40700,8 +41814,11 @@
       <c r="AS356">
         <v>0.9607</v>
       </c>
-    </row>
-    <row r="357" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA356" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="357" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A357" s="1">
         <v>42</v>
       </c>
@@ -40776,8 +41893,11 @@
       <c r="AS357">
         <v>0.95430000000000004</v>
       </c>
-    </row>
-    <row r="358" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA357" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="358" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A358" s="1">
         <v>43</v>
       </c>
@@ -40852,8 +41972,11 @@
       <c r="AS358">
         <v>0.96299999999999997</v>
       </c>
-    </row>
-    <row r="359" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA358" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="359" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A359" s="1">
         <v>44</v>
       </c>
@@ -40928,8 +42051,11 @@
       <c r="AS359">
         <v>0.96099999999999997</v>
       </c>
-    </row>
-    <row r="360" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA359" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="360" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A360" s="1">
         <v>45</v>
       </c>
@@ -41004,8 +42130,11 @@
       <c r="AS360">
         <v>0.96560000000000001</v>
       </c>
-    </row>
-    <row r="361" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA360" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="361" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A361" s="1">
         <v>46</v>
       </c>
@@ -41080,8 +42209,11 @@
       <c r="AS361">
         <v>0.96020000000000005</v>
       </c>
-    </row>
-    <row r="362" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA361" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="362" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A362" s="1">
         <v>47</v>
       </c>
@@ -41156,8 +42288,11 @@
       <c r="AS362">
         <v>0.96430000000000005</v>
       </c>
-    </row>
-    <row r="363" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA362" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="363" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A363" s="1">
         <v>48</v>
       </c>
@@ -41232,8 +42367,11 @@
       <c r="AS363">
         <v>0.95950000000000002</v>
       </c>
-    </row>
-    <row r="364" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA363" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="364" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A364" s="1">
         <v>49</v>
       </c>
@@ -41308,8 +42446,11 @@
       <c r="AS364">
         <v>0.97550000000000003</v>
       </c>
-    </row>
-    <row r="365" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA364" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="365" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A365" s="1">
         <v>50</v>
       </c>
@@ -41384,8 +42525,11 @@
       <c r="AS365">
         <v>0.9718</v>
       </c>
-    </row>
-    <row r="366" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA365" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="366" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A366" s="1">
         <v>51</v>
       </c>
@@ -41460,8 +42604,11 @@
       <c r="AS366">
         <v>0.96040000000000003</v>
       </c>
-    </row>
-    <row r="367" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA366" s="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="367" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A367" s="1">
         <v>52</v>
       </c>
@@ -41536,8 +42683,11 @@
       <c r="AS367">
         <v>0.96809999999999996</v>
       </c>
-    </row>
-    <row r="368" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA367" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="368" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A368" s="1">
         <v>53</v>
       </c>
@@ -41612,8 +42762,11 @@
       <c r="AS368">
         <v>0.96419999999999995</v>
       </c>
-    </row>
-    <row r="369" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA368" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="369" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A369" s="1">
         <v>54</v>
       </c>
@@ -41688,8 +42841,11 @@
       <c r="AS369">
         <v>0.96430000000000005</v>
       </c>
-    </row>
-    <row r="370" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA369" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="370" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A370" s="1">
         <v>55</v>
       </c>
@@ -41764,8 +42920,11 @@
       <c r="AS370">
         <v>0.96809999999999996</v>
       </c>
-    </row>
-    <row r="371" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA370" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="371" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A371" s="1">
         <v>56</v>
       </c>
@@ -41840,8 +42999,11 @@
       <c r="AS371">
         <v>0.96799999999999997</v>
       </c>
-    </row>
-    <row r="372" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA371" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="372" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A372" s="1">
         <v>57</v>
       </c>
@@ -41916,8 +43078,11 @@
       <c r="AS372">
         <v>0.97560000000000002</v>
       </c>
-    </row>
-    <row r="373" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA372" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="373" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A373" s="1">
         <v>58</v>
       </c>
@@ -41992,8 +43157,11 @@
       <c r="AS373">
         <v>0.98329999999999995</v>
       </c>
-    </row>
-    <row r="374" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA373" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="374" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A374" s="1">
         <v>59</v>
       </c>
@@ -42068,8 +43236,11 @@
       <c r="AS374">
         <v>0.98399999999999999</v>
       </c>
-    </row>
-    <row r="375" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA374" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="375" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A375" s="1">
         <v>60</v>
       </c>
@@ -42144,8 +43315,11 @@
       <c r="AS375">
         <v>0.97489999999999999</v>
       </c>
-    </row>
-    <row r="376" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA375" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="376" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A376" s="1">
         <v>61</v>
       </c>
@@ -42220,8 +43394,11 @@
       <c r="AS376">
         <v>0.97709999999999997</v>
       </c>
-    </row>
-    <row r="377" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA376" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="377" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A377" s="1">
         <v>62</v>
       </c>
@@ -42296,8 +43473,11 @@
       <c r="AS377">
         <v>0.97419999999999995</v>
       </c>
-    </row>
-    <row r="378" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA377" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="378" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A378" s="1">
         <v>63</v>
       </c>
@@ -42372,8 +43552,11 @@
       <c r="AS378">
         <v>0.97340000000000004</v>
       </c>
-    </row>
-    <row r="379" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA378" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="379" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A379" s="1">
         <v>64</v>
       </c>
@@ -42448,8 +43631,11 @@
       <c r="AS379">
         <v>0.97599999999999998</v>
       </c>
-    </row>
-    <row r="380" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA379" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="380" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A380" s="1">
         <v>65</v>
       </c>
@@ -42524,8 +43710,11 @@
       <c r="AS380">
         <v>0.9788</v>
       </c>
-    </row>
-    <row r="381" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA380" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="381" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A381" s="1">
         <v>66</v>
       </c>
@@ -42600,8 +43789,11 @@
       <c r="AS381">
         <v>0.97340000000000004</v>
       </c>
-    </row>
-    <row r="382" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA381" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="382" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A382" s="1">
         <v>67</v>
       </c>
@@ -42676,8 +43868,11 @@
       <c r="AS382">
         <v>0.97629999999999995</v>
       </c>
-    </row>
-    <row r="383" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA382" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="383" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A383" s="1">
         <v>68</v>
       </c>
@@ -42752,8 +43947,11 @@
       <c r="AS383">
         <v>0.97330000000000005</v>
       </c>
-    </row>
-    <row r="384" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA383" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="384" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A384" s="1">
         <v>69</v>
       </c>
@@ -42828,8 +44026,11 @@
       <c r="AS384">
         <v>0.97740000000000005</v>
       </c>
-    </row>
-    <row r="385" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA384" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="385" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A385" s="1">
         <v>70</v>
       </c>
@@ -42904,8 +44105,11 @@
       <c r="AS385">
         <v>0.96909999999999996</v>
       </c>
-    </row>
-    <row r="386" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA385" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="386" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A386" s="1">
         <v>71</v>
       </c>
@@ -42980,8 +44184,11 @@
       <c r="AS386">
         <v>0.97729999999999995</v>
       </c>
-    </row>
-    <row r="387" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA386" s="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="387" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A387" s="1">
         <v>72</v>
       </c>
@@ -43056,8 +44263,11 @@
       <c r="AS387">
         <v>0.96970000000000001</v>
       </c>
-    </row>
-    <row r="388" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA387" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="388" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A388" s="1">
         <v>73</v>
       </c>
@@ -43132,8 +44342,11 @@
       <c r="AS388">
         <v>0.96640000000000004</v>
       </c>
-    </row>
-    <row r="389" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA388" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="389" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A389" s="1">
         <v>74</v>
       </c>
@@ -43208,8 +44421,11 @@
       <c r="AS389">
         <v>0.97819999999999996</v>
       </c>
-    </row>
-    <row r="390" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA389" s="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="390" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A390" s="1">
         <v>75</v>
       </c>
@@ -43284,8 +44500,11 @@
       <c r="AS390">
         <v>0.97419999999999995</v>
       </c>
-    </row>
-    <row r="391" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA390" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="391" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A391" s="1">
         <v>76</v>
       </c>
@@ -43360,8 +44579,11 @@
       <c r="AS391">
         <v>0.98009999999999997</v>
       </c>
-    </row>
-    <row r="392" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA391" s="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="392" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A392" s="1">
         <v>77</v>
       </c>
@@ -43436,8 +44658,11 @@
       <c r="AS392">
         <v>0.97670000000000001</v>
       </c>
-    </row>
-    <row r="393" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA392" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="393" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A393" s="1">
         <v>78</v>
       </c>
@@ -43512,8 +44737,11 @@
       <c r="AS393">
         <v>0.97909999999999997</v>
       </c>
-    </row>
-    <row r="394" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA393" s="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="394" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A394" s="1">
         <v>79</v>
       </c>
@@ -43588,8 +44816,11 @@
       <c r="AS394">
         <v>0.97609999999999997</v>
       </c>
-    </row>
-    <row r="395" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA394" s="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="395" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A395" s="1">
         <v>80</v>
       </c>
@@ -43664,8 +44895,11 @@
       <c r="AS395">
         <v>0.97919999999999996</v>
       </c>
-    </row>
-    <row r="396" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA395" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="396" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A396" s="1">
         <v>81</v>
       </c>
@@ -43740,8 +44974,11 @@
       <c r="AS396">
         <v>0.97709999999999997</v>
       </c>
-    </row>
-    <row r="397" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA396" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="397" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A397" s="1">
         <v>82</v>
       </c>
@@ -43816,8 +45053,11 @@
       <c r="AS397">
         <v>0.98029999999999995</v>
       </c>
-    </row>
-    <row r="398" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA397" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="398" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A398" s="1">
         <v>83</v>
       </c>
@@ -43892,8 +45132,11 @@
       <c r="AS398">
         <v>0.97770000000000001</v>
       </c>
-    </row>
-    <row r="399" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA398" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="399" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A399" s="1">
         <v>84</v>
       </c>
@@ -43968,8 +45211,11 @@
       <c r="AS399">
         <v>0.97760000000000002</v>
       </c>
-    </row>
-    <row r="400" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA399" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="400" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A400" s="1">
         <v>85</v>
       </c>
@@ -44044,8 +45290,11 @@
       <c r="AS400">
         <v>0.97809999999999997</v>
       </c>
-    </row>
-    <row r="401" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA400" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="401" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A401" s="1">
         <v>86</v>
       </c>
@@ -44120,8 +45369,11 @@
       <c r="AS401">
         <v>0.98050000000000004</v>
       </c>
-    </row>
-    <row r="402" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA401" s="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="402" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A402" s="1">
         <v>87</v>
       </c>
@@ -44196,8 +45448,11 @@
       <c r="AS402">
         <v>0.97829999999999995</v>
       </c>
-    </row>
-    <row r="403" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA402" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="403" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A403" s="1">
         <v>88</v>
       </c>
@@ -44272,8 +45527,11 @@
       <c r="AS403">
         <v>0.98440000000000005</v>
       </c>
-    </row>
-    <row r="404" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA403" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="404" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A404" s="1">
         <v>89</v>
       </c>
@@ -44348,8 +45606,11 @@
       <c r="AS404">
         <v>0.97850000000000004</v>
       </c>
-    </row>
-    <row r="405" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA404" s="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="405" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A405" s="1">
         <v>90</v>
       </c>
@@ -44424,8 +45685,11 @@
       <c r="AS405">
         <v>0.98140000000000005</v>
       </c>
-    </row>
-    <row r="406" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA405" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="406" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A406" s="1">
         <v>91</v>
       </c>
@@ -44500,8 +45764,11 @@
       <c r="AS406">
         <v>0.98129999999999995</v>
       </c>
-    </row>
-    <row r="407" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA406" s="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="407" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A407" s="1">
         <v>92</v>
       </c>
@@ -44576,8 +45843,11 @@
       <c r="AS407">
         <v>0.98729999999999996</v>
       </c>
-    </row>
-    <row r="408" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA407" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="408" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A408" s="1">
         <v>93</v>
       </c>
@@ -44652,8 +45922,11 @@
       <c r="AS408">
         <v>0.97670000000000001</v>
       </c>
-    </row>
-    <row r="409" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA408" s="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="409" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A409" s="1">
         <v>94</v>
       </c>
@@ -44728,8 +46001,11 @@
       <c r="AS409">
         <v>0.97760000000000002</v>
       </c>
-    </row>
-    <row r="410" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA409" s="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="410" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A410" s="1">
         <v>95</v>
       </c>
@@ -44804,8 +46080,11 @@
       <c r="AS410">
         <v>0.97340000000000004</v>
       </c>
-    </row>
-    <row r="411" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA410" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="411" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A411" s="1">
         <v>96</v>
       </c>
@@ -44880,8 +46159,11 @@
       <c r="AS411">
         <v>0.9778</v>
       </c>
-    </row>
-    <row r="412" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA411" s="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="412" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A412" s="1">
         <v>97</v>
       </c>
@@ -44956,8 +46238,11 @@
       <c r="AS412">
         <v>0.98540000000000005</v>
       </c>
-    </row>
-    <row r="413" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA412" s="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="413" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A413" s="1">
         <v>98</v>
       </c>
@@ -45032,8 +46317,11 @@
       <c r="AS413">
         <v>0.98370000000000002</v>
       </c>
-    </row>
-    <row r="414" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA413" s="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="414" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A414" s="1">
         <v>99</v>
       </c>
@@ -45108,8 +46396,11 @@
       <c r="AS414">
         <v>0.97599999999999998</v>
       </c>
-    </row>
-    <row r="415" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA414" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="415" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A415" s="1">
         <v>100</v>
       </c>
@@ -45184,8 +46475,11 @@
       <c r="AS415">
         <v>0.98070000000000002</v>
       </c>
-    </row>
-    <row r="416" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="BA415" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="416" spans="1:53" x14ac:dyDescent="0.2">
       <c r="AD416" s="9"/>
       <c r="AE416" s="9"/>
     </row>
@@ -45542,7 +46836,17 @@
       <c r="AE504" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="21">
+    <mergeCell ref="BB2:BG2"/>
+    <mergeCell ref="BB3:BC3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BA1:BE1"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="AM1:AQ1"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="T4:U4"/>
     <mergeCell ref="AR3:AS3"/>
     <mergeCell ref="AN2:AS2"/>
     <mergeCell ref="C2:D2"/>
@@ -45554,11 +46858,6 @@
     <mergeCell ref="L3:Q3"/>
     <mergeCell ref="F2:J2"/>
     <mergeCell ref="AI2:AK2"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="AM1:AQ1"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="T4:U4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/CIFAR_Global.xlsx
+++ b/CIFAR_Global.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashleyau/Documents/PhD/Practical_Experiment/Finalised/Finalised_Algorithm_ResNet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9911E2-28E4-E245-84ED-F52106B1A04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20AE327E-4359-BF43-8216-36BD49D60ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -276,23 +276,23 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -13409,7 +13409,7 @@
       <c r="AH1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AM1" s="19" t="s">
+      <c r="AM1" s="18" t="s">
         <v>1</v>
       </c>
       <c r="AN1" s="15"/>
@@ -13422,7 +13422,7 @@
       <c r="AS1" t="s">
         <v>3</v>
       </c>
-      <c r="BA1" s="19" t="s">
+      <c r="BA1" s="18" t="s">
         <v>1</v>
       </c>
       <c r="BB1" s="15"/>
@@ -13443,14 +13443,14 @@
       <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="19" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="20" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="15"/>
@@ -13465,13 +13465,13 @@
       <c r="S2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="T2" s="18" t="s">
+      <c r="T2" s="20" t="s">
         <v>9</v>
       </c>
       <c r="U2" s="15"/>
       <c r="V2" s="15"/>
       <c r="W2" s="15"/>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="20" t="s">
         <v>9</v>
       </c>
       <c r="AE2" s="15"/>
@@ -13479,7 +13479,7 @@
       <c r="AH2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AI2" s="18" t="s">
+      <c r="AI2" s="20" t="s">
         <v>9</v>
       </c>
       <c r="AJ2" s="15"/>
@@ -13488,7 +13488,7 @@
       <c r="AM2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AN2" s="18" t="s">
+      <c r="AN2" s="20" t="s">
         <v>9</v>
       </c>
       <c r="AO2" s="15"/>
@@ -13499,7 +13499,7 @@
       <c r="BA2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="BB2" s="18" t="s">
+      <c r="BB2" s="20" t="s">
         <v>9</v>
       </c>
       <c r="BC2" s="15"/>
@@ -13539,7 +13539,7 @@
       <c r="J3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="14" t="s">
+      <c r="L3" s="16" t="s">
         <v>19</v>
       </c>
       <c r="M3" s="15"/>
@@ -13586,30 +13586,30 @@
       <c r="AM3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AN3" s="14" t="s">
+      <c r="AN3" s="16" t="s">
         <v>17</v>
       </c>
       <c r="AO3" s="15"/>
-      <c r="AP3" s="16" t="s">
+      <c r="AP3" s="14" t="s">
         <v>16</v>
       </c>
       <c r="AQ3" s="15"/>
-      <c r="AR3" s="14" t="s">
+      <c r="AR3" s="16" t="s">
         <v>23</v>
       </c>
       <c r="AS3" s="15"/>
       <c r="BA3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="BB3" s="14" t="s">
+      <c r="BB3" s="16" t="s">
         <v>17</v>
       </c>
       <c r="BC3" s="15"/>
-      <c r="BD3" s="16" t="s">
+      <c r="BD3" s="14" t="s">
         <v>16</v>
       </c>
       <c r="BE3" s="15"/>
-      <c r="BF3" s="14" t="s">
+      <c r="BF3" s="16" t="s">
         <v>23</v>
       </c>
       <c r="BG3" s="15"/>
@@ -14103,7 +14103,7 @@
         <v>0.41214285714285709</v>
       </c>
       <c r="BC8">
-        <v>0.35339999999999999</v>
+        <v>0.35349999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:59" x14ac:dyDescent="0.2">
@@ -14400,7 +14400,7 @@
         <v>0.49111111111111122</v>
       </c>
       <c r="BC11">
-        <v>0.55169999999999997</v>
+        <v>0.55179999999999996</v>
       </c>
     </row>
     <row r="12" spans="1:59" x14ac:dyDescent="0.2">
@@ -14497,6 +14497,9 @@
       <c r="BB12">
         <v>0.51</v>
       </c>
+      <c r="BC12">
+        <v>0.5968</v>
+      </c>
     </row>
     <row r="13" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
@@ -14592,6 +14595,9 @@
       <c r="BB13">
         <v>0.51555555555555554</v>
       </c>
+      <c r="BC13">
+        <v>0.66159999999999997</v>
+      </c>
     </row>
     <row r="14" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
@@ -14687,6 +14693,9 @@
       <c r="BB14">
         <v>0.51833333333333331</v>
       </c>
+      <c r="BC14">
+        <v>0.52400000000000002</v>
+      </c>
     </row>
     <row r="15" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
@@ -14776,6 +14785,9 @@
       <c r="BB15">
         <v>0.53277777777777779</v>
       </c>
+      <c r="BC15">
+        <v>0.66769999999999996</v>
+      </c>
     </row>
     <row r="16" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
@@ -14865,8 +14877,11 @@
       <c r="BB16">
         <v>0.5411111111111111</v>
       </c>
-    </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC16">
+        <v>0.54849999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -14954,8 +14969,11 @@
       <c r="BB17">
         <v>0.55166666666666675</v>
       </c>
-    </row>
-    <row r="18" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC17">
+        <v>0.62280000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -15043,8 +15061,11 @@
       <c r="BB18">
         <v>0.56333333333333324</v>
       </c>
-    </row>
-    <row r="19" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC18">
+        <v>0.6653</v>
+      </c>
+    </row>
+    <row r="19" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -15132,8 +15153,11 @@
       <c r="BB19">
         <v>0.56333333333333324</v>
       </c>
-    </row>
-    <row r="20" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC19">
+        <v>0.76100000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -15221,8 +15245,11 @@
       <c r="BB20">
         <v>0.56611111111111101</v>
       </c>
-    </row>
-    <row r="21" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC20">
+        <v>0.79449999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -15310,8 +15337,11 @@
       <c r="BB21">
         <v>0.56444444444444453</v>
       </c>
-    </row>
-    <row r="22" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC21">
+        <v>0.79790000000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -15399,8 +15429,11 @@
       <c r="BB22">
         <v>0.56500000000000006</v>
       </c>
-    </row>
-    <row r="23" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC22">
+        <v>0.75790000000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -15488,8 +15521,11 @@
       <c r="BB23">
         <v>0.56666666666666654</v>
       </c>
-    </row>
-    <row r="24" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC23">
+        <v>0.81200000000000006</v>
+      </c>
+    </row>
+    <row r="24" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -15574,8 +15610,11 @@
       <c r="BB24">
         <v>0.51222222222222225</v>
       </c>
-    </row>
-    <row r="25" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC24">
+        <v>0.7409</v>
+      </c>
+    </row>
+    <row r="25" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -15663,8 +15702,11 @@
       <c r="BB25">
         <v>0.51222222222222213</v>
       </c>
-    </row>
-    <row r="26" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC25">
+        <v>0.79059999999999997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -15752,8 +15794,11 @@
       <c r="BB26">
         <v>0.51833333333333331</v>
       </c>
-    </row>
-    <row r="27" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC26">
+        <v>0.7399</v>
+      </c>
+    </row>
+    <row r="27" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -15841,8 +15886,11 @@
       <c r="BB27">
         <v>0.54888888888888898</v>
       </c>
-    </row>
-    <row r="28" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC27">
+        <v>0.82089999999999996</v>
+      </c>
+    </row>
+    <row r="28" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -15930,8 +15978,11 @@
       <c r="BB28">
         <v>0.52944444444444427</v>
       </c>
-    </row>
-    <row r="29" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC28">
+        <v>0.8266</v>
+      </c>
+    </row>
+    <row r="29" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -16019,8 +16070,11 @@
       <c r="BB29">
         <v>0.57444444444444442</v>
       </c>
-    </row>
-    <row r="30" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC29">
+        <v>0.83389999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -16108,8 +16162,11 @@
       <c r="BB30">
         <v>0.55166666666666664</v>
       </c>
-    </row>
-    <row r="31" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC30">
+        <v>0.73450000000000004</v>
+      </c>
+    </row>
+    <row r="31" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -16197,8 +16254,11 @@
       <c r="BB31">
         <v>0.56722222222222229</v>
       </c>
-    </row>
-    <row r="32" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC31">
+        <v>0.67920000000000003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -16286,8 +16346,11 @@
       <c r="BB32">
         <v>0.57777777777777783</v>
       </c>
-    </row>
-    <row r="33" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC32">
+        <v>0.73180000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -16375,8 +16438,11 @@
       <c r="BB33">
         <v>0.58111111111111113</v>
       </c>
-    </row>
-    <row r="34" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC33">
+        <v>0.71160000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -16464,8 +16530,11 @@
       <c r="BB34">
         <v>0.58555555555555538</v>
       </c>
-    </row>
-    <row r="35" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC34">
+        <v>0.73160000000000003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -16553,8 +16622,11 @@
       <c r="BB35">
         <v>0.58000000000000007</v>
       </c>
-    </row>
-    <row r="36" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC35">
+        <v>0.749</v>
+      </c>
+    </row>
+    <row r="36" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -16642,8 +16714,11 @@
       <c r="BB36">
         <v>0.55388888888888888</v>
       </c>
-    </row>
-    <row r="37" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC36">
+        <v>0.75090000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -16731,8 +16806,11 @@
       <c r="BB37">
         <v>0.57166666666666677</v>
       </c>
-    </row>
-    <row r="38" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC37">
+        <v>0.75980000000000003</v>
+      </c>
+    </row>
+    <row r="38" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>34</v>
       </c>
@@ -16820,8 +16898,11 @@
       <c r="BB38">
         <v>0.57055555555555559</v>
       </c>
-    </row>
-    <row r="39" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC38">
+        <v>0.75780000000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>35</v>
       </c>
@@ -16909,8 +16990,11 @@
       <c r="BB39">
         <v>0.58277777777777784</v>
       </c>
-    </row>
-    <row r="40" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC39">
+        <v>0.72170000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>36</v>
       </c>
@@ -16998,8 +17082,11 @@
       <c r="BB40">
         <v>0.59166666666666679</v>
       </c>
-    </row>
-    <row r="41" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC40">
+        <v>0.75560000000000005</v>
+      </c>
+    </row>
+    <row r="41" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>37</v>
       </c>
@@ -17087,8 +17174,11 @@
       <c r="BB41">
         <v>0.58333333333333337</v>
       </c>
-    </row>
-    <row r="42" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC41">
+        <v>0.72230000000000005</v>
+      </c>
+    </row>
+    <row r="42" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>38</v>
       </c>
@@ -17176,8 +17266,11 @@
       <c r="BB42">
         <v>0.58222222222222209</v>
       </c>
-    </row>
-    <row r="43" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC42">
+        <v>0.754</v>
+      </c>
+    </row>
+    <row r="43" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -17265,8 +17358,11 @@
       <c r="BB43">
         <v>0.58777777777777773</v>
       </c>
-    </row>
-    <row r="44" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC43">
+        <v>0.75570000000000004</v>
+      </c>
+    </row>
+    <row r="44" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>40</v>
       </c>
@@ -17354,8 +17450,11 @@
       <c r="BB44">
         <v>0.59555555555555562</v>
       </c>
-    </row>
-    <row r="45" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC44">
+        <v>0.73719999999999997</v>
+      </c>
+    </row>
+    <row r="45" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>41</v>
       </c>
@@ -17443,8 +17542,11 @@
       <c r="BB45">
         <v>0.59666666666666657</v>
       </c>
-    </row>
-    <row r="46" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC45">
+        <v>0.76770000000000005</v>
+      </c>
+    </row>
+    <row r="46" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>42</v>
       </c>
@@ -17532,8 +17634,11 @@
       <c r="BB46">
         <v>0.57444444444444442</v>
       </c>
-    </row>
-    <row r="47" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC46">
+        <v>0.7702</v>
+      </c>
+    </row>
+    <row r="47" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>43</v>
       </c>
@@ -17621,8 +17726,11 @@
       <c r="BB47">
         <v>0.58444444444444443</v>
       </c>
-    </row>
-    <row r="48" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC47">
+        <v>0.76170000000000004</v>
+      </c>
+    </row>
+    <row r="48" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>44</v>
       </c>
@@ -17710,8 +17818,11 @@
       <c r="BB48">
         <v>0.58444444444444443</v>
       </c>
-    </row>
-    <row r="49" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC48">
+        <v>0.76949999999999996</v>
+      </c>
+    </row>
+    <row r="49" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>45</v>
       </c>
@@ -17799,8 +17910,11 @@
       <c r="BB49">
         <v>0.58111111111111102</v>
       </c>
-    </row>
-    <row r="50" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC49">
+        <v>0.77290000000000003</v>
+      </c>
+    </row>
+    <row r="50" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -17888,8 +18002,11 @@
       <c r="BB50">
         <v>0.58611111111111103</v>
       </c>
-    </row>
-    <row r="51" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC50">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="51" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>47</v>
       </c>
@@ -17977,8 +18094,11 @@
       <c r="BB51">
         <v>0.5872222222222222</v>
       </c>
-    </row>
-    <row r="52" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC51">
+        <v>0.77580000000000005</v>
+      </c>
+    </row>
+    <row r="52" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>48</v>
       </c>
@@ -18066,8 +18186,11 @@
       <c r="BB52">
         <v>0.58666666666666667</v>
       </c>
-    </row>
-    <row r="53" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC52">
+        <v>0.77470000000000006</v>
+      </c>
+    </row>
+    <row r="53" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>49</v>
       </c>
@@ -18155,8 +18278,11 @@
       <c r="BB53">
         <v>0.5872222222222222</v>
       </c>
-    </row>
-    <row r="54" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC53">
+        <v>0.74709999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>50</v>
       </c>
@@ -18244,8 +18370,11 @@
       <c r="BB54">
         <v>0.59888888888888892</v>
       </c>
-    </row>
-    <row r="55" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC54">
+        <v>0.76880000000000004</v>
+      </c>
+    </row>
+    <row r="55" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>51</v>
       </c>
@@ -18333,8 +18462,11 @@
       <c r="BB55">
         <v>0.6000000000000002</v>
       </c>
-    </row>
-    <row r="56" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC55">
+        <v>0.76970000000000005</v>
+      </c>
+    </row>
+    <row r="56" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>52</v>
       </c>
@@ -18422,8 +18554,11 @@
       <c r="BB56">
         <v>0.5872222222222222</v>
       </c>
-    </row>
-    <row r="57" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC56">
+        <v>0.77339999999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>53</v>
       </c>
@@ -18511,8 +18646,11 @@
       <c r="BB57">
         <v>0.59222222222222221</v>
       </c>
-    </row>
-    <row r="58" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC57">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="58" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>54</v>
       </c>
@@ -18600,8 +18738,11 @@
       <c r="BB58">
         <v>0.58166666666666678</v>
       </c>
-    </row>
-    <row r="59" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC58">
+        <v>0.77829999999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>55</v>
       </c>
@@ -18689,8 +18830,11 @@
       <c r="BB59">
         <v>0.58333333333333315</v>
       </c>
-    </row>
-    <row r="60" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC59">
+        <v>0.7833</v>
+      </c>
+    </row>
+    <row r="60" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>56</v>
       </c>
@@ -18778,8 +18922,11 @@
       <c r="BB60">
         <v>0.59111111111111103</v>
       </c>
-    </row>
-    <row r="61" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC60">
+        <v>0.77490000000000003</v>
+      </c>
+    </row>
+    <row r="61" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>57</v>
       </c>
@@ -18867,8 +19014,11 @@
       <c r="BB61">
         <v>0.60111111111111115</v>
       </c>
-    </row>
-    <row r="62" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC61">
+        <v>0.77539999999999998</v>
+      </c>
+    </row>
+    <row r="62" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>58</v>
       </c>
@@ -18956,8 +19106,11 @@
       <c r="BB62">
         <v>0.58222222222222209</v>
       </c>
-    </row>
-    <row r="63" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC62">
+        <v>0.7752</v>
+      </c>
+    </row>
+    <row r="63" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>59</v>
       </c>
@@ -19045,8 +19198,11 @@
       <c r="BB63">
         <v>0.59722222222222221</v>
       </c>
-    </row>
-    <row r="64" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC63">
+        <v>0.77739999999999998</v>
+      </c>
+    </row>
+    <row r="64" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>60</v>
       </c>
@@ -19134,8 +19290,11 @@
       <c r="BB64">
         <v>0.58666666666666667</v>
       </c>
-    </row>
-    <row r="65" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC64">
+        <v>0.77810000000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>61</v>
       </c>
@@ -19223,8 +19382,11 @@
       <c r="BB65">
         <v>0.5905555555555555</v>
       </c>
-    </row>
-    <row r="66" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC65">
+        <v>0.77349999999999997</v>
+      </c>
+    </row>
+    <row r="66" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>62</v>
       </c>
@@ -19312,8 +19474,11 @@
       <c r="BB66">
         <v>0.60444444444444445</v>
       </c>
-    </row>
-    <row r="67" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC66">
+        <v>0.76359999999999995</v>
+      </c>
+    </row>
+    <row r="67" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>63</v>
       </c>
@@ -19401,8 +19566,11 @@
       <c r="BB67">
         <v>0.59166666666666667</v>
       </c>
-    </row>
-    <row r="68" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC67">
+        <v>0.78180000000000005</v>
+      </c>
+    </row>
+    <row r="68" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>64</v>
       </c>
@@ -19490,8 +19658,11 @@
       <c r="BB68">
         <v>0.59555555555555562</v>
       </c>
-    </row>
-    <row r="69" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC68">
+        <v>0.77569999999999995</v>
+      </c>
+    </row>
+    <row r="69" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>65</v>
       </c>
@@ -19579,8 +19750,11 @@
       <c r="BB69">
         <v>0.60499999999999998</v>
       </c>
-    </row>
-    <row r="70" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC69">
+        <v>0.78210000000000002</v>
+      </c>
+    </row>
+    <row r="70" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>66</v>
       </c>
@@ -19668,8 +19842,11 @@
       <c r="BB70">
         <v>0.59777777777777774</v>
       </c>
-    </row>
-    <row r="71" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC70">
+        <v>0.78420000000000001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>67</v>
       </c>
@@ -19757,8 +19934,11 @@
       <c r="BB71">
         <v>0.59388888888888902</v>
       </c>
-    </row>
-    <row r="72" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC71">
+        <v>0.78280000000000005</v>
+      </c>
+    </row>
+    <row r="72" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>68</v>
       </c>
@@ -19846,8 +20026,11 @@
       <c r="BB72">
         <v>0.6038888888888887</v>
       </c>
-    </row>
-    <row r="73" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC72">
+        <v>0.78739999999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>69</v>
       </c>
@@ -19935,8 +20118,11 @@
       <c r="BB73">
         <v>0.60555555555555551</v>
       </c>
-    </row>
-    <row r="74" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC73">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="74" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>70</v>
       </c>
@@ -20024,8 +20210,11 @@
       <c r="BB74">
         <v>0.60833333333333328</v>
       </c>
-    </row>
-    <row r="75" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC74">
+        <v>0.78979999999999995</v>
+      </c>
+    </row>
+    <row r="75" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>71</v>
       </c>
@@ -20113,8 +20302,11 @@
       <c r="BB75">
         <v>0.61222222222222233</v>
       </c>
-    </row>
-    <row r="76" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC75">
+        <v>0.78039999999999998</v>
+      </c>
+    </row>
+    <row r="76" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>72</v>
       </c>
@@ -20202,8 +20394,11 @@
       <c r="BB76">
         <v>0.60777777777777775</v>
       </c>
-    </row>
-    <row r="77" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC76">
+        <v>0.78910000000000002</v>
+      </c>
+    </row>
+    <row r="77" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>73</v>
       </c>
@@ -20291,8 +20486,11 @@
       <c r="BB77">
         <v>0.60222222222222221</v>
       </c>
-    </row>
-    <row r="78" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC77">
+        <v>0.78520000000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>74</v>
       </c>
@@ -20380,8 +20578,11 @@
       <c r="BB78">
         <v>0.60277777777777775</v>
       </c>
-    </row>
-    <row r="79" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC78">
+        <v>0.7762</v>
+      </c>
+    </row>
+    <row r="79" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>75</v>
       </c>
@@ -20469,8 +20670,11 @@
       <c r="BB79">
         <v>0.59555555555555539</v>
       </c>
-    </row>
-    <row r="80" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC79">
+        <v>0.78469999999999995</v>
+      </c>
+    </row>
+    <row r="80" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>76</v>
       </c>
@@ -20558,8 +20762,11 @@
       <c r="BB80">
         <v>0.60499999999999998</v>
       </c>
-    </row>
-    <row r="81" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC80">
+        <v>0.78090000000000004</v>
+      </c>
+    </row>
+    <row r="81" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>77</v>
       </c>
@@ -20647,8 +20854,11 @@
       <c r="BB81">
         <v>0.60111111111111104</v>
       </c>
-    </row>
-    <row r="82" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC81">
+        <v>0.78269999999999995</v>
+      </c>
+    </row>
+    <row r="82" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>78</v>
       </c>
@@ -20736,8 +20946,11 @@
       <c r="BB82">
         <v>0.60333333333333328</v>
       </c>
-    </row>
-    <row r="83" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC82">
+        <v>0.79210000000000003</v>
+      </c>
+    </row>
+    <row r="83" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>79</v>
       </c>
@@ -20825,8 +21038,11 @@
       <c r="BB83">
         <v>0.60499999999999998</v>
       </c>
-    </row>
-    <row r="84" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC83">
+        <v>0.78879999999999995</v>
+      </c>
+    </row>
+    <row r="84" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>80</v>
       </c>
@@ -20914,8 +21130,11 @@
       <c r="BB84">
         <v>0.60444444444444456</v>
       </c>
-    </row>
-    <row r="85" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC84">
+        <v>0.7903</v>
+      </c>
+    </row>
+    <row r="85" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>81</v>
       </c>
@@ -21003,8 +21222,11 @@
       <c r="BB85">
         <v>0.59833333333333338</v>
       </c>
-    </row>
-    <row r="86" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC85">
+        <v>0.79039999999999999</v>
+      </c>
+    </row>
+    <row r="86" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>82</v>
       </c>
@@ -21092,8 +21314,11 @@
       <c r="BB86">
         <v>0.60333333333333339</v>
       </c>
-    </row>
-    <row r="87" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC86">
+        <v>0.78769999999999996</v>
+      </c>
+    </row>
+    <row r="87" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>83</v>
       </c>
@@ -21181,8 +21406,11 @@
       <c r="BB87">
         <v>0.60222222222222233</v>
       </c>
-    </row>
-    <row r="88" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC87">
+        <v>0.79190000000000005</v>
+      </c>
+    </row>
+    <row r="88" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>84</v>
       </c>
@@ -21270,8 +21498,11 @@
       <c r="BB88">
         <v>0.60277777777777786</v>
       </c>
-    </row>
-    <row r="89" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC88">
+        <v>0.78200000000000003</v>
+      </c>
+    </row>
+    <row r="89" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>85</v>
       </c>
@@ -21359,8 +21590,11 @@
       <c r="BB89">
         <v>0.60333333333333339</v>
       </c>
-    </row>
-    <row r="90" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC89">
+        <v>0.79049999999999998</v>
+      </c>
+    </row>
+    <row r="90" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>86</v>
       </c>
@@ -21448,8 +21682,11 @@
       <c r="BB90">
         <v>0.60222222222222221</v>
       </c>
-    </row>
-    <row r="91" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC90">
+        <v>0.78969999999999996</v>
+      </c>
+    </row>
+    <row r="91" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>87</v>
       </c>
@@ -21537,8 +21774,11 @@
       <c r="BB91">
         <v>0.59777777777777763</v>
       </c>
-    </row>
-    <row r="92" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC91">
+        <v>0.78959999999999997</v>
+      </c>
+    </row>
+    <row r="92" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>88</v>
       </c>
@@ -21626,8 +21866,11 @@
       <c r="BB92">
         <v>0.60722222222222233</v>
       </c>
-    </row>
-    <row r="93" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC92">
+        <v>0.79090000000000005</v>
+      </c>
+    </row>
+    <row r="93" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>89</v>
       </c>
@@ -21715,8 +21958,11 @@
       <c r="BB93">
         <v>0.60111111111111115</v>
       </c>
-    </row>
-    <row r="94" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC93">
+        <v>0.79269999999999996</v>
+      </c>
+    </row>
+    <row r="94" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>90</v>
       </c>
@@ -21804,8 +22050,11 @@
       <c r="BB94">
         <v>0.59722222222222232</v>
       </c>
-    </row>
-    <row r="95" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC94">
+        <v>0.79379999999999995</v>
+      </c>
+    </row>
+    <row r="95" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>91</v>
       </c>
@@ -21893,8 +22142,11 @@
       <c r="BB95">
         <v>0.59333333333333338</v>
       </c>
-    </row>
-    <row r="96" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC95">
+        <v>0.78939999999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>92</v>
       </c>
@@ -21982,8 +22234,11 @@
       <c r="BB96">
         <v>0.60666666666666669</v>
       </c>
-    </row>
-    <row r="97" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC96">
+        <v>0.79020000000000001</v>
+      </c>
+    </row>
+    <row r="97" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>93</v>
       </c>
@@ -22071,8 +22326,11 @@
       <c r="BB97">
         <v>0.61055555555555541</v>
       </c>
-    </row>
-    <row r="98" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC97">
+        <v>0.78869999999999996</v>
+      </c>
+    </row>
+    <row r="98" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>94</v>
       </c>
@@ -22160,8 +22418,11 @@
       <c r="BB98">
         <v>0.60833333333333328</v>
       </c>
-    </row>
-    <row r="99" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC98">
+        <v>0.79500000000000004</v>
+      </c>
+    </row>
+    <row r="99" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>95</v>
       </c>
@@ -22249,8 +22510,11 @@
       <c r="BB99">
         <v>0.60888888888888881</v>
       </c>
-    </row>
-    <row r="100" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC99">
+        <v>0.79449999999999998</v>
+      </c>
+    </row>
+    <row r="100" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>96</v>
       </c>
@@ -22338,8 +22602,11 @@
       <c r="BB100">
         <v>0.60277777777777775</v>
       </c>
-    </row>
-    <row r="101" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC100">
+        <v>0.79239999999999999</v>
+      </c>
+    </row>
+    <row r="101" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>97</v>
       </c>
@@ -22427,8 +22694,11 @@
       <c r="BB101">
         <v>0.59666666666666657</v>
       </c>
-    </row>
-    <row r="102" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC101">
+        <v>0.7944</v>
+      </c>
+    </row>
+    <row r="102" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>98</v>
       </c>
@@ -22516,8 +22786,11 @@
       <c r="BB102">
         <v>0.60111111111111104</v>
       </c>
-    </row>
-    <row r="103" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC102">
+        <v>0.79530000000000001</v>
+      </c>
+    </row>
+    <row r="103" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>99</v>
       </c>
@@ -22605,8 +22878,11 @@
       <c r="BB103">
         <v>0.60111111111111104</v>
       </c>
-    </row>
-    <row r="104" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC103">
+        <v>0.79679999999999995</v>
+      </c>
+    </row>
+    <row r="104" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>100</v>
       </c>
@@ -22694,12 +22970,15 @@
       <c r="BB104">
         <v>0.60222222222222233</v>
       </c>
-    </row>
-    <row r="105" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BC104">
+        <v>0.79369999999999996</v>
+      </c>
+    </row>
+    <row r="105" spans="1:55" x14ac:dyDescent="0.2">
       <c r="AD105" s="9"/>
       <c r="AE105" s="9"/>
     </row>
-    <row r="106" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>31</v>
       </c>
@@ -22718,7 +22997,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>32</v>
       </c>
@@ -22737,7 +23016,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="108" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>1</v>
       </c>
@@ -22828,7 +23107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>2</v>
       </c>
@@ -22919,7 +23198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>3</v>
       </c>
@@ -23010,7 +23289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>4</v>
       </c>
@@ -23101,7 +23380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>5</v>
       </c>

--- a/CIFAR_Global.xlsx
+++ b/CIFAR_Global.xlsx
@@ -13697,6 +13697,12 @@
       <c r="BE5" t="n">
         <v>0.1575354260089686</v>
       </c>
+      <c r="BF5" t="n">
+        <v>0.1257142857142857</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0.09867073684210527</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -13804,6 +13810,12 @@
       <c r="BE6" t="n">
         <v>0.198314798206278</v>
       </c>
+      <c r="BF6" t="n">
+        <v>0.2133333333333333</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.1407564210526315</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -13911,6 +13923,12 @@
       <c r="BE7" t="n">
         <v>0.2447394618834081</v>
       </c>
+      <c r="BF7" t="n">
+        <v>0.2763636363636364</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.1838216842105263</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -14018,6 +14036,12 @@
       <c r="BE8" t="n">
         <v>0.2754251121076233</v>
       </c>
+      <c r="BF8" t="n">
+        <v>0.4086666666666667</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0.2289385263157895</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -14125,6 +14149,12 @@
       <c r="BE9" t="n">
         <v>0.2932739910313902</v>
       </c>
+      <c r="BF9" t="n">
+        <v>0.443125</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.247993052631579</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -14229,6 +14259,12 @@
       <c r="BE10" t="n">
         <v>0.3676686098654709</v>
       </c>
+      <c r="BF10" t="n">
+        <v>0.4906250000000001</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0.2540195789473684</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -14333,6 +14369,12 @@
       <c r="BE11" t="n">
         <v>0.3515089686098656</v>
       </c>
+      <c r="BF11" t="n">
+        <v>0.4893750000000001</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.288542947368421</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -14437,6 +14479,12 @@
       <c r="BE12" t="n">
         <v>0.4605448430493272</v>
       </c>
+      <c r="BF12" t="n">
+        <v>0.5024999999999999</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.2971932631578947</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -14541,6 +14589,12 @@
       <c r="BE13" t="n">
         <v>0.4833358744394617</v>
       </c>
+      <c r="BF13" t="n">
+        <v>0.52125</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.3155610526315789</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -14645,6 +14699,12 @@
       <c r="BE14" t="n">
         <v>0.5108044843049326</v>
       </c>
+      <c r="BF14" t="n">
+        <v>0.536875</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.2700669473684211</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -14743,6 +14803,12 @@
       <c r="BE15" t="n">
         <v>0.5405596412556054</v>
       </c>
+      <c r="BF15" t="n">
+        <v>0.5443749999999998</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0.2999741052631579</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -14841,6 +14907,12 @@
       <c r="BE16" t="n">
         <v>0.4975035874439462</v>
       </c>
+      <c r="BF16" t="n">
+        <v>0.5373684210526315</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0.363306105263158</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -14939,6 +15011,12 @@
       <c r="BE17" t="n">
         <v>0.5269439461883407</v>
       </c>
+      <c r="BF17" t="n">
+        <v>0.5563157894736842</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0.3157046315789473</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -15037,6 +15115,12 @@
       <c r="BE18" t="n">
         <v>0.5471677130044843</v>
       </c>
+      <c r="BF18" t="n">
+        <v>0.5421052631578948</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0.4038296842105263</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -15135,6 +15219,12 @@
       <c r="BE19" t="n">
         <v>0.5044331838565022</v>
       </c>
+      <c r="BF19" t="n">
+        <v>0.5615789473684211</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0.375962947368421</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -15233,6 +15323,12 @@
       <c r="BE20" t="n">
         <v>0.5587484304932736</v>
       </c>
+      <c r="BF20" t="n">
+        <v>0.5742105263157894</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0.3333903157894738</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -15331,6 +15427,12 @@
       <c r="BE21" t="n">
         <v>0.5531744394618835</v>
       </c>
+      <c r="BF21" t="n">
+        <v>0.5794736842105265</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0.3619646315789474</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -15429,6 +15531,12 @@
       <c r="BE22" t="n">
         <v>0.5909139013452914</v>
       </c>
+      <c r="BF22" t="n">
+        <v>0.5763157894736843</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0.4509541052631579</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -15527,6 +15635,12 @@
       <c r="BE23" t="n">
         <v>0.621508520179372</v>
       </c>
+      <c r="BF23" t="n">
+        <v>0.5721052631578948</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0.4656357894736841</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -15622,6 +15736,12 @@
       <c r="BE24" t="n">
         <v>0.6434152466367712</v>
       </c>
+      <c r="BF24" t="n">
+        <v>0.5878947368421051</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0.3967764210526316</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -15720,6 +15840,12 @@
       <c r="BE25" t="n">
         <v>0.6534569506726456</v>
       </c>
+      <c r="BF25" t="n">
+        <v>0.5894736842105264</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0.4950850526315789</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -15818,6 +15944,12 @@
       <c r="BE26" t="n">
         <v>0.6730134529147983</v>
       </c>
+      <c r="BF26" t="n">
+        <v>0.5978947368421053</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0.5054147368421052</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -15916,6 +16048,12 @@
       <c r="BE27" t="n">
         <v>0.5627811659192825</v>
       </c>
+      <c r="BF27" t="n">
+        <v>0.5868421052631579</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0.5369458947368421</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -16014,6 +16152,12 @@
       <c r="BE28" t="n">
         <v>0.5759152466367713</v>
       </c>
+      <c r="BF28" t="n">
+        <v>0.5421052631578948</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0.441674947368421</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -16112,6 +16256,12 @@
       <c r="BE29" t="n">
         <v>0.6585569506726457</v>
       </c>
+      <c r="BF29" t="n">
+        <v>0.5910526315789474</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0.4810970526315789</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -16210,6 +16360,12 @@
       <c r="BE30" t="n">
         <v>0.6118730941704035</v>
       </c>
+      <c r="BF30" t="n">
+        <v>0.5989473684210527</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0.5535056842105264</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -16308,6 +16464,12 @@
       <c r="BE31" t="n">
         <v>0.6772179372197309</v>
       </c>
+      <c r="BF31" t="n">
+        <v>0.6121052631578947</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0.5085135593220339</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -16406,6 +16568,12 @@
       <c r="BE32" t="n">
         <v>0.6837726457399105</v>
       </c>
+      <c r="BF32" t="n">
+        <v>0.6110526315789473</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0.5563770212765957</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -16504,6 +16672,12 @@
       <c r="BE33" t="n">
         <v>0.6940121076233183</v>
       </c>
+      <c r="BF33" t="n">
+        <v>0.6105263157894736</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0.5090693617021276</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -16602,6 +16776,12 @@
       <c r="BE34" t="n">
         <v>0.6937807174887893</v>
       </c>
+      <c r="BF34" t="n">
+        <v>0.6105263157894736</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0.5907612765957446</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -16700,6 +16880,12 @@
       <c r="BE35" t="n">
         <v>0.7034327354260089</v>
       </c>
+      <c r="BF35" t="n">
+        <v>0.6268421052631579</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0.4545306382978723</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -16798,6 +16984,12 @@
       <c r="BE36" t="n">
         <v>0.7048874439461883</v>
       </c>
+      <c r="BF36" t="n">
+        <v>0.6131578947368421</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0.546320754716981</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -16896,6 +17088,12 @@
       <c r="BE37" t="n">
         <v>0.7060977578475339</v>
       </c>
+      <c r="BF37" t="n">
+        <v>0.6215789473684211</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0.5582569811320757</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -16994,6 +17192,12 @@
       <c r="BE38" t="n">
         <v>0.7067484304932734</v>
       </c>
+      <c r="BF38" t="n">
+        <v>0.6178947368421052</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0.5558573584905661</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -17092,6 +17296,12 @@
       <c r="BE39" t="n">
         <v>0.7058587443946189</v>
       </c>
+      <c r="BF39" t="n">
+        <v>0.6115789473684211</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0.5608003773584905</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -17190,6 +17400,12 @@
       <c r="BE40" t="n">
         <v>0.7118959641255606</v>
       </c>
+      <c r="BF40" t="n">
+        <v>0.6173684210526316</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0.6071049056603773</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -17288,6 +17504,12 @@
       <c r="BE41" t="n">
         <v>0.7156264573991031</v>
       </c>
+      <c r="BF41" t="n">
+        <v>0.6042105263157895</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0.6207049056603774</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -17386,6 +17608,12 @@
       <c r="BE42" t="n">
         <v>0.7158843049327354</v>
       </c>
+      <c r="BF42" t="n">
+        <v>0.6010526315789473</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0.5654098113207549</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -17484,6 +17712,12 @@
       <c r="BE43" t="n">
         <v>0.7148690582959643</v>
       </c>
+      <c r="BF43" t="n">
+        <v>0.6168421052631579</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0.5758237735849056</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -17582,6 +17816,12 @@
       <c r="BE44" t="n">
         <v>0.7180865470852015</v>
       </c>
+      <c r="BF44" t="n">
+        <v>0.591578947368421</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>0.6283984905660377</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -17680,6 +17920,12 @@
       <c r="BE45" t="n">
         <v>0.7200627802690582</v>
       </c>
+      <c r="BF45" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>0.5212694339622642</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -17778,6 +18024,12 @@
       <c r="BE46" t="n">
         <v>0.7222174887892375</v>
       </c>
+      <c r="BF46" t="n">
+        <v>0.6073684210526314</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>0.5646245283018867</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -17876,6 +18128,12 @@
       <c r="BE47" t="n">
         <v>0.7229112107623318</v>
       </c>
+      <c r="BF47" t="n">
+        <v>0.6305263157894736</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>0.6290992452830189</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -17974,6 +18232,12 @@
       <c r="BE48" t="n">
         <v>0.7236596412556053</v>
       </c>
+      <c r="BF48" t="n">
+        <v>0.6252631578947369</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>0.6496249056603772</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -18072,6 +18336,12 @@
       <c r="BE49" t="n">
         <v>0.7230699551569506</v>
       </c>
+      <c r="BF49" t="n">
+        <v>0.6168421052631579</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>0.5695184905660375</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -18170,6 +18440,12 @@
       <c r="BE50" t="n">
         <v>0.7232434977578476</v>
       </c>
+      <c r="BF50" t="n">
+        <v>0.6278947368421053</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>0.6110290566037735</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -18268,6 +18544,12 @@
       <c r="BE51" t="n">
         <v>0.7958000000000001</v>
       </c>
+      <c r="BF51" t="n">
+        <v>0.6394736842105263</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>0.5971803773584904</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -18366,6 +18648,9 @@
       <c r="BE52" t="n">
         <v>0.7986233333333332</v>
       </c>
+      <c r="BF52" t="n">
+        <v>0.6289473684210526</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -18464,6 +18749,9 @@
       <c r="BE53" t="n">
         <v>0.7997633333333332</v>
       </c>
+      <c r="BF53" t="n">
+        <v>0.5878947368421052</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -18562,6 +18850,9 @@
       <c r="BE54" t="n">
         <v>0.7898916666666669</v>
       </c>
+      <c r="BF54" t="n">
+        <v>0.6052631578947368</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -18660,6 +18951,9 @@
       <c r="BE55" t="n">
         <v>0.7931683333333335</v>
       </c>
+      <c r="BF55" t="n">
+        <v>0.6263157894736842</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -18758,6 +19052,9 @@
       <c r="BE56" t="n">
         <v>0.7926483333333331</v>
       </c>
+      <c r="BF56" t="n">
+        <v>0.6247368421052631</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -18856,6 +19153,9 @@
       <c r="BE57" t="n">
         <v>0.7969450000000001</v>
       </c>
+      <c r="BF57" t="n">
+        <v>0.628421052631579</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -18954,6 +19254,9 @@
       <c r="BE58" t="n">
         <v>0.7999600000000001</v>
       </c>
+      <c r="BF58" t="n">
+        <v>0.6521052631578947</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -19052,6 +19355,9 @@
       <c r="BE59" t="n">
         <v>0.8054766666666667</v>
       </c>
+      <c r="BF59" t="n">
+        <v>0.6363157894736841</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -19150,6 +19456,9 @@
       <c r="BE60" t="n">
         <v>0.8047033333333331</v>
       </c>
+      <c r="BF60" t="n">
+        <v>0.6389473684210527</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -19248,6 +19557,9 @@
       <c r="BE61" t="n">
         <v>0.7992283333333333</v>
       </c>
+      <c r="BF61" t="n">
+        <v>0.6284210526315789</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -19346,6 +19658,9 @@
       <c r="BE62" t="n">
         <v>0.8005450000000001</v>
       </c>
+      <c r="BF62" t="n">
+        <v>0.6289473684210526</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -19444,6 +19759,9 @@
       <c r="BE63" t="n">
         <v>0.7999483333333333</v>
       </c>
+      <c r="BF63" t="n">
+        <v>0.6326315789473684</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -19542,6 +19860,9 @@
       <c r="BE64" t="n">
         <v>0.8025483333333334</v>
       </c>
+      <c r="BF64" t="n">
+        <v>0.6484210526315788</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -19640,6 +19961,9 @@
       <c r="BE65" t="n">
         <v>0.8056966666666667</v>
       </c>
+      <c r="BF65" t="n">
+        <v>0.6405263157894736</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -19738,6 +20062,9 @@
       <c r="BE66" t="n">
         <v>0.798335</v>
       </c>
+      <c r="BF66" t="n">
+        <v>0.6421052631578946</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -19836,6 +20163,9 @@
       <c r="BE67" t="n">
         <v>0.8056316666666667</v>
       </c>
+      <c r="BF67" t="n">
+        <v>0.638421052631579</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -19934,6 +20264,9 @@
       <c r="BE68" t="n">
         <v>0.8057449999999999</v>
       </c>
+      <c r="BF68" t="n">
+        <v>0.6236842105263158</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -20032,6 +20365,9 @@
       <c r="BE69" t="n">
         <v>0.8054450000000001</v>
       </c>
+      <c r="BF69" t="n">
+        <v>0.6310526315789474</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -20130,6 +20466,9 @@
       <c r="BE70" t="n">
         <v>0.8058200000000001</v>
       </c>
+      <c r="BF70" t="n">
+        <v>0.6278947368421054</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -20228,6 +20567,9 @@
       <c r="BE71" t="n">
         <v>0.80486</v>
       </c>
+      <c r="BF71" t="n">
+        <v>0.6357894736842105</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -20326,6 +20668,9 @@
       <c r="BE72" t="n">
         <v>0.8099900000000001</v>
       </c>
+      <c r="BF72" t="n">
+        <v>0.6347368421052632</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -20424,6 +20769,9 @@
       <c r="BE73" t="n">
         <v>0.80768</v>
       </c>
+      <c r="BF73" t="n">
+        <v>0.6378947368421052</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -20522,6 +20870,9 @@
       <c r="BE74" t="n">
         <v>0.8045200000000001</v>
       </c>
+      <c r="BF74" t="n">
+        <v>0.6468421052631577</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -20620,6 +20971,9 @@
       <c r="BE75" t="n">
         <v>0.8053583333333333</v>
       </c>
+      <c r="BF75" t="n">
+        <v>0.6426315789473683</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -20718,6 +21072,9 @@
       <c r="BE76" t="n">
         <v>0.8056283333333333</v>
       </c>
+      <c r="BF76" t="n">
+        <v>0.628421052631579</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -20816,6 +21173,9 @@
       <c r="BE77" t="n">
         <v>0.80439</v>
       </c>
+      <c r="BF77" t="n">
+        <v>0.6426315789473684</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -20914,6 +21274,9 @@
       <c r="BE78" t="n">
         <v>0.8109966666666667</v>
       </c>
+      <c r="BF78" t="n">
+        <v>0.6394736842105263</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -21012,6 +21375,9 @@
       <c r="BE79" t="n">
         <v>0.8035266666666666</v>
       </c>
+      <c r="BF79" t="n">
+        <v>0.6526315789473685</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -21110,6 +21476,9 @@
       <c r="BE80" t="n">
         <v>0.8037133333333333</v>
       </c>
+      <c r="BF80" t="n">
+        <v>0.6405263157894737</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -21208,6 +21577,9 @@
       <c r="BE81" t="n">
         <v>0.8086749999999998</v>
       </c>
+      <c r="BF81" t="n">
+        <v>0.6389473684210527</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -21306,6 +21678,9 @@
       <c r="BE82" t="n">
         <v>0.8089516666666666</v>
       </c>
+      <c r="BF82" t="n">
+        <v>0.6310526315789473</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -21404,6 +21779,9 @@
       <c r="BE83" t="n">
         <v>0.8082316666666667</v>
       </c>
+      <c r="BF83" t="n">
+        <v>0.6378947368421054</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -21502,6 +21880,9 @@
       <c r="BE84" t="n">
         <v>0.8115816666666666</v>
       </c>
+      <c r="BF84" t="n">
+        <v>0.6442105263157895</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -21600,6 +21981,9 @@
       <c r="BE85" t="n">
         <v>0.8070400000000001</v>
       </c>
+      <c r="BF85" t="n">
+        <v>0.636842105263158</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -21698,6 +22082,9 @@
       <c r="BE86" t="n">
         <v>0.804825</v>
       </c>
+      <c r="BF86" t="n">
+        <v>0.6452631578947368</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -21796,6 +22183,9 @@
       <c r="BE87" t="n">
         <v>0.8019266666666667</v>
       </c>
+      <c r="BF87" t="n">
+        <v>0.6473684210526315</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -21894,6 +22284,9 @@
       <c r="BE88" t="n">
         <v>0.803175</v>
       </c>
+      <c r="BF88" t="n">
+        <v>0.6442105263157895</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -21992,6 +22385,9 @@
       <c r="BE89" t="n">
         <v>0.8018166666666667</v>
       </c>
+      <c r="BF89" t="n">
+        <v>0.6431578947368422</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -22090,6 +22486,9 @@
       <c r="BE90" t="n">
         <v>0.8102550000000001</v>
       </c>
+      <c r="BF90" t="n">
+        <v>0.6384210526315791</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -22188,6 +22587,9 @@
       <c r="BE91" t="n">
         <v>0.8078649999999998</v>
       </c>
+      <c r="BF91" t="n">
+        <v>0.6368421052631578</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -22286,6 +22688,9 @@
       <c r="BE92" t="n">
         <v>0.805285</v>
       </c>
+      <c r="BF92" t="n">
+        <v>0.6394736842105264</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -22384,6 +22789,9 @@
       <c r="BE93" t="n">
         <v>0.8061533333333332</v>
       </c>
+      <c r="BF93" t="n">
+        <v>0.6442105263157895</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -22482,6 +22890,9 @@
       <c r="BE94" t="n">
         <v>0.8087716666666666</v>
       </c>
+      <c r="BF94" t="n">
+        <v>0.6373684210526316</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -22580,6 +22991,9 @@
       <c r="BE95" t="n">
         <v>0.8024350000000001</v>
       </c>
+      <c r="BF95" t="n">
+        <v>0.6557894736842106</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -22678,6 +23092,9 @@
       <c r="BE96" t="n">
         <v>0.8032716666666666</v>
       </c>
+      <c r="BF96" t="n">
+        <v>0.6336842105263158</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -22776,6 +23193,9 @@
       <c r="BE97" t="n">
         <v>0.8049083333333333</v>
       </c>
+      <c r="BF97" t="n">
+        <v>0.6426315789473683</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -22874,6 +23294,9 @@
       <c r="BE98" t="n">
         <v>0.8056266666666666</v>
       </c>
+      <c r="BF98" t="n">
+        <v>0.6436842105263159</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -22972,6 +23395,9 @@
       <c r="BE99" t="n">
         <v>0.8004183333333332</v>
       </c>
+      <c r="BF99" t="n">
+        <v>0.6494736842105263</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -23070,6 +23496,9 @@
       <c r="BE100" t="n">
         <v>0.8043533333333334</v>
       </c>
+      <c r="BF100" t="n">
+        <v>0.6526315789473685</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -23168,6 +23597,9 @@
       <c r="BE101" t="n">
         <v>0.8029616666666667</v>
       </c>
+      <c r="BF101" t="n">
+        <v>0.6610526315789473</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -23266,6 +23698,9 @@
       <c r="BE102" t="n">
         <v>0.8059516666666667</v>
       </c>
+      <c r="BF102" t="n">
+        <v>0.646842105263158</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -23364,6 +23799,9 @@
       <c r="BE103" t="n">
         <v>0.8051583333333333</v>
       </c>
+      <c r="BF103" t="n">
+        <v>0.6478947368421052</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -23461,6 +23899,9 @@
       </c>
       <c r="BE104" t="n">
         <v>0.8053816666666669</v>
+      </c>
+      <c r="BF104" t="n">
+        <v>0.6410526315789474</v>
       </c>
     </row>
     <row r="105">
@@ -23621,6 +24062,12 @@
       <c r="BE108" t="n">
         <v>0.6</v>
       </c>
+      <c r="BF108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG108" t="n">
+        <v>0.1333333333333333</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -23718,6 +24165,12 @@
       <c r="BE109" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="BF109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG109" t="n">
+        <v>0.9333333333333333</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -23815,6 +24268,12 @@
       <c r="BE110" t="n">
         <v>0.9333333333333333</v>
       </c>
+      <c r="BF110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG110" t="n">
+        <v>0.8666666666666667</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -23912,6 +24371,12 @@
       <c r="BE111" t="n">
         <v>0.8666666666666667</v>
       </c>
+      <c r="BF111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG111" t="n">
+        <v>0.5333333333333333</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -24009,6 +24474,12 @@
       <c r="BE112" t="n">
         <v>0.9333333333333333</v>
       </c>
+      <c r="BF112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG112" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -24103,6 +24574,12 @@
       <c r="BE113" t="n">
         <v>0.6666666666666666</v>
       </c>
+      <c r="BF113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG113" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -24197,6 +24674,12 @@
       <c r="BE114" t="n">
         <v>0.8666666666666667</v>
       </c>
+      <c r="BF114" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="BG114" t="n">
+        <v>0.2666666666666667</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -24291,6 +24774,12 @@
       <c r="BE115" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="BF115" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>0.4666666666666667</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -24385,6 +24874,12 @@
       <c r="BE116" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="BF116" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -24479,6 +24974,12 @@
       <c r="BE117" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="BF117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -24567,6 +25068,12 @@
       <c r="BE118" t="n">
         <v>0.3333333333333333</v>
       </c>
+      <c r="BF118" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.8666666666666667</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -24655,6 +25162,12 @@
       <c r="BE119" t="n">
         <v>0.8</v>
       </c>
+      <c r="BF119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.4666666666666667</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -24743,6 +25256,12 @@
       <c r="BE120" t="n">
         <v>0.8</v>
       </c>
+      <c r="BF120" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -24831,6 +25350,12 @@
       <c r="BE121" t="n">
         <v>0.8666666666666667</v>
       </c>
+      <c r="BF121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.4666666666666667</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -24919,6 +25444,12 @@
       <c r="BE122" t="n">
         <v>0.6666666666666666</v>
       </c>
+      <c r="BF122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>0.2666666666666667</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -25007,6 +25538,12 @@
       <c r="BE123" t="n">
         <v>1</v>
       </c>
+      <c r="BF123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -25095,6 +25632,12 @@
       <c r="BE124" t="n">
         <v>0.9333333333333333</v>
       </c>
+      <c r="BF124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3333333333333333</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -25183,6 +25726,12 @@
       <c r="BE125" t="n">
         <v>0.6</v>
       </c>
+      <c r="BF125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.4666666666666667</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -25271,6 +25820,12 @@
       <c r="BE126" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="BF126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.4666666666666667</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -25359,6 +25914,12 @@
       <c r="BE127" t="n">
         <v>0.2</v>
       </c>
+      <c r="BF127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.8666666666666667</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -25447,6 +26008,12 @@
       <c r="BE128" t="n">
         <v>0.5333333333333333</v>
       </c>
+      <c r="BF128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.4666666666666667</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -25535,6 +26102,12 @@
       <c r="BE129" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="BF129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.5333333333333333</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -25623,6 +26196,12 @@
       <c r="BE130" t="n">
         <v>0.6</v>
       </c>
+      <c r="BF130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.5333333333333333</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -25711,6 +26290,12 @@
       <c r="BE131" t="n">
         <v>0.9333333333333333</v>
       </c>
+      <c r="BF131" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.7333333333333333</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -25799,6 +26384,12 @@
       <c r="BE132" t="n">
         <v>0.6</v>
       </c>
+      <c r="BF132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.2666666666666667</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -25887,6 +26478,12 @@
       <c r="BE133" t="n">
         <v>0.7333333333333333</v>
       </c>
+      <c r="BF133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.4666666666666667</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -25975,6 +26572,12 @@
       <c r="BE134" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="BF134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.2666666666666667</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -26063,6 +26666,12 @@
       <c r="BE135" t="n">
         <v>0.5333333333333333</v>
       </c>
+      <c r="BF135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -26151,6 +26760,12 @@
       <c r="BE136" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="BF136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.8571428571428571</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -26239,6 +26854,12 @@
       <c r="BE137" t="n">
         <v>0.5333333333333333</v>
       </c>
+      <c r="BF137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.2857142857142857</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -26327,6 +26948,12 @@
       <c r="BE138" t="n">
         <v>0.3333333333333333</v>
       </c>
+      <c r="BF138" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.7857142857142857</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -26415,6 +27042,12 @@
       <c r="BE139" t="n">
         <v>0.2666666666666667</v>
       </c>
+      <c r="BF139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.8666666666666667</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -26503,6 +27136,12 @@
       <c r="BE140" t="n">
         <v>0.2666666666666667</v>
       </c>
+      <c r="BF140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -26591,6 +27230,12 @@
       <c r="BE141" t="n">
         <v>0.4</v>
       </c>
+      <c r="BF141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -26679,6 +27324,12 @@
       <c r="BE142" t="n">
         <v>0.4</v>
       </c>
+      <c r="BF142" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -26767,6 +27418,12 @@
       <c r="BE143" t="n">
         <v>0.3333333333333333</v>
       </c>
+      <c r="BF143" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.4166666666666667</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -26855,6 +27512,12 @@
       <c r="BE144" t="n">
         <v>0.4</v>
       </c>
+      <c r="BF144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG144" t="n">
+        <v>0.1111111111111111</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -26943,6 +27606,12 @@
       <c r="BE145" t="n">
         <v>0.5333333333333333</v>
       </c>
+      <c r="BF145" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BG145" t="n">
+        <v>0.6363636363636364</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -27031,6 +27700,12 @@
       <c r="BE146" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="BF146" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="BG146" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -27119,6 +27794,12 @@
       <c r="BE147" t="n">
         <v>0.2</v>
       </c>
+      <c r="BF147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG147" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -27207,6 +27888,12 @@
       <c r="BE148" t="n">
         <v>0.4</v>
       </c>
+      <c r="BF148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG148" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -27295,6 +27982,12 @@
       <c r="BE149" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="BF149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG149" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -27383,6 +28076,12 @@
       <c r="BE150" t="n">
         <v>0.4</v>
       </c>
+      <c r="BF150" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BG150" t="n">
+        <v>0.2727272727272727</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -27471,6 +28170,12 @@
       <c r="BE151" t="n">
         <v>0.2</v>
       </c>
+      <c r="BF151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG151" t="n">
+        <v>0.3333333333333333</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -27559,6 +28264,12 @@
       <c r="BE152" t="n">
         <v>0.3333333333333333</v>
       </c>
+      <c r="BF152" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="BG152" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -27647,6 +28358,12 @@
       <c r="BE153" t="n">
         <v>0.2666666666666667</v>
       </c>
+      <c r="BF153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG153" t="n">
+        <v>0.7272727272727273</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -27735,6 +28452,12 @@
       <c r="BE154" t="n">
         <v>0.5333333333333333</v>
       </c>
+      <c r="BF154" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BG154" t="n">
+        <v>0.9090909090909091</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -27823,6 +28546,9 @@
       <c r="BE155" t="n">
         <v>0.2</v>
       </c>
+      <c r="BF155" t="n">
+        <v>0.7142857142857143</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -27911,6 +28637,9 @@
       <c r="BE156" t="n">
         <v>0.3333333333333333</v>
       </c>
+      <c r="BF156" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -27999,6 +28728,9 @@
       <c r="BE157" t="n">
         <v>0.5333333333333333</v>
       </c>
+      <c r="BF157" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -28087,6 +28819,9 @@
       <c r="BE158" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="BF158" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -28175,6 +28910,9 @@
       <c r="BE159" t="n">
         <v>0.3333333333333333</v>
       </c>
+      <c r="BF159" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -28263,6 +29001,9 @@
       <c r="BE160" t="n">
         <v>0.3333333333333333</v>
       </c>
+      <c r="BF160" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -28351,6 +29092,9 @@
       <c r="BE161" t="n">
         <v>0.4285714285714285</v>
       </c>
+      <c r="BF161" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -28439,6 +29183,9 @@
       <c r="BE162" t="n">
         <v>0.3333333333333333</v>
       </c>
+      <c r="BF162" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -28527,6 +29274,9 @@
       <c r="BE163" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="BF163" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -28615,6 +29365,9 @@
       <c r="BE164" t="n">
         <v>0.5</v>
       </c>
+      <c r="BF164" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -28703,6 +29456,9 @@
       <c r="BE165" t="n">
         <v>0.5333333333333333</v>
       </c>
+      <c r="BF165" t="n">
+        <v>0.375</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -28791,6 +29547,9 @@
       <c r="BE166" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="BF166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -28879,6 +29638,9 @@
       <c r="BE167" t="n">
         <v>0.2142857142857143</v>
       </c>
+      <c r="BF167" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -28967,6 +29729,9 @@
       <c r="BE168" t="n">
         <v>0.2666666666666667</v>
       </c>
+      <c r="BF168" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -29055,6 +29820,9 @@
       <c r="BE169" t="n">
         <v>0.2666666666666667</v>
       </c>
+      <c r="BF169" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -29143,6 +29911,9 @@
       <c r="BE170" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="BF170" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -29231,6 +30002,9 @@
       <c r="BE171" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="BF171" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -29319,6 +30093,9 @@
       <c r="BE172" t="n">
         <v>0.4285714285714285</v>
       </c>
+      <c r="BF172" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -29407,6 +30184,9 @@
       <c r="BE173" t="n">
         <v>0.2</v>
       </c>
+      <c r="BF173" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -29495,6 +30275,9 @@
       <c r="BE174" t="n">
         <v>0.5333333333333333</v>
       </c>
+      <c r="BF174" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -29583,6 +30366,9 @@
       <c r="BE175" t="n">
         <v>0.4</v>
       </c>
+      <c r="BF175" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -29671,6 +30457,9 @@
       <c r="BE176" t="n">
         <v>0.2666666666666667</v>
       </c>
+      <c r="BF176" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -29759,6 +30548,9 @@
       <c r="BE177" t="n">
         <v>0.2142857142857143</v>
       </c>
+      <c r="BF177" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -29847,6 +30639,9 @@
       <c r="BE178" t="n">
         <v>0.5</v>
       </c>
+      <c r="BF178" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -29935,6 +30730,9 @@
       <c r="BE179" t="n">
         <v>0.5</v>
       </c>
+      <c r="BF179" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -30023,6 +30821,9 @@
       <c r="BE180" t="n">
         <v>0.2666666666666667</v>
       </c>
+      <c r="BF180" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -30111,6 +30912,9 @@
       <c r="BE181" t="n">
         <v>0.2666666666666667</v>
       </c>
+      <c r="BF181" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -30199,6 +31003,9 @@
       <c r="BE182" t="n">
         <v>0.2</v>
       </c>
+      <c r="BF182" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -30287,6 +31094,9 @@
       <c r="BE183" t="n">
         <v>0.2</v>
       </c>
+      <c r="BF183" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -30375,6 +31185,9 @@
       <c r="BE184" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="BF184" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -30463,6 +31276,9 @@
       <c r="BE185" t="n">
         <v>0.3571428571428572</v>
       </c>
+      <c r="BF185" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -30551,6 +31367,9 @@
       <c r="BE186" t="n">
         <v>0.2666666666666667</v>
       </c>
+      <c r="BF186" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -30639,6 +31458,9 @@
       <c r="BE187" t="n">
         <v>0.3571428571428572</v>
       </c>
+      <c r="BF187" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -30727,6 +31549,9 @@
       <c r="BE188" t="n">
         <v>0.4285714285714285</v>
       </c>
+      <c r="BF188" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
@@ -30815,6 +31640,9 @@
       <c r="BE189" t="n">
         <v>0.4</v>
       </c>
+      <c r="BF189" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -30903,6 +31731,9 @@
       <c r="BE190" t="n">
         <v>0.4285714285714285</v>
       </c>
+      <c r="BF190" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -30991,6 +31822,9 @@
       <c r="BE191" t="n">
         <v>0.2666666666666667</v>
       </c>
+      <c r="BF191" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -31079,6 +31913,9 @@
       <c r="BE192" t="n">
         <v>0.3571428571428572</v>
       </c>
+      <c r="BF192" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -31167,6 +32004,9 @@
       <c r="BE193" t="n">
         <v>0.2666666666666667</v>
       </c>
+      <c r="BF193" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -31255,6 +32095,9 @@
       <c r="BE194" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="BF194" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -31343,6 +32186,9 @@
       <c r="BE195" t="n">
         <v>0.4666666666666667</v>
       </c>
+      <c r="BF195" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -31431,6 +32277,9 @@
       <c r="BE196" t="n">
         <v>0.2</v>
       </c>
+      <c r="BF196" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -31519,6 +32368,9 @@
       <c r="BE197" t="n">
         <v>0.5</v>
       </c>
+      <c r="BF197" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
@@ -31607,6 +32459,9 @@
       <c r="BE198" t="n">
         <v>0.2666666666666667</v>
       </c>
+      <c r="BF198" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
@@ -31695,6 +32550,9 @@
       <c r="BE199" t="n">
         <v>0.1333333333333333</v>
       </c>
+      <c r="BF199" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
@@ -31783,6 +32641,9 @@
       <c r="BE200" t="n">
         <v>0.1333333333333333</v>
       </c>
+      <c r="BF200" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -31871,6 +32732,9 @@
       <c r="BE201" t="n">
         <v>0.1333333333333333</v>
       </c>
+      <c r="BF201" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
@@ -31959,6 +32823,9 @@
       <c r="BE202" t="n">
         <v>0.2142857142857143</v>
       </c>
+      <c r="BF202" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
@@ -32047,6 +32914,9 @@
       <c r="BE203" t="n">
         <v>0.1333333333333333</v>
       </c>
+      <c r="BF203" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -32135,6 +33005,9 @@
       <c r="BE204" t="n">
         <v>0.2</v>
       </c>
+      <c r="BF204" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
@@ -32223,6 +33096,9 @@
       <c r="BE205" t="n">
         <v>0.2</v>
       </c>
+      <c r="BF205" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -32311,6 +33187,9 @@
       <c r="BE206" t="n">
         <v>0.2666666666666667</v>
       </c>
+      <c r="BF206" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
@@ -32398,6 +33277,9 @@
       </c>
       <c r="BE207" t="n">
         <v>0.4666666666666667</v>
+      </c>
+      <c r="BF207" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="208">
@@ -32562,6 +33444,12 @@
       <c r="BE212" t="n">
         <v>0.89244</v>
       </c>
+      <c r="BF212" t="n">
+        <v>0.952475</v>
+      </c>
+      <c r="BG212" t="n">
+        <v>0.8830749999999999</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -32659,6 +33547,12 @@
       <c r="BE213" t="n">
         <v>0.9293400000000001</v>
       </c>
+      <c r="BF213" t="n">
+        <v>0.955590909090909</v>
+      </c>
+      <c r="BG213" t="n">
+        <v>0.88665</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
@@ -32756,6 +33650,12 @@
       <c r="BE214" t="n">
         <v>0.9603249999999999</v>
       </c>
+      <c r="BF214" t="n">
+        <v>0.9666300000000001</v>
+      </c>
+      <c r="BG214" t="n">
+        <v>0.92681</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
@@ -32853,6 +33753,12 @@
       <c r="BE215" t="n">
         <v>0.9615166666666668</v>
       </c>
+      <c r="BF215" t="n">
+        <v>0.9554333333333334</v>
+      </c>
+      <c r="BG215" t="n">
+        <v>0.89337</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
@@ -32950,6 +33856,12 @@
       <c r="BE216" t="n">
         <v>0.9339333333333331</v>
       </c>
+      <c r="BF216" t="n">
+        <v>0.9477100000000001</v>
+      </c>
+      <c r="BG216" t="n">
+        <v>0.9323166666666668</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
@@ -33044,6 +33956,12 @@
       <c r="BE217" t="n">
         <v>0.9397375000000001</v>
       </c>
+      <c r="BF217" t="n">
+        <v>0.9568111111111111</v>
+      </c>
+      <c r="BG217" t="n">
+        <v>0.8899222222222222</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
@@ -33138,6 +34056,12 @@
       <c r="BE218" t="n">
         <v>0.9449700000000002</v>
       </c>
+      <c r="BF218" t="n">
+        <v>0.962011111111111</v>
+      </c>
+      <c r="BG218" t="n">
+        <v>0.9138454545454544</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
@@ -33234,6 +34158,12 @@
       <c r="BE219" t="n">
         <v>0.946542857142857</v>
       </c>
+      <c r="BF219" t="n">
+        <v>0.8356857142857143</v>
+      </c>
+      <c r="BG219" t="n">
+        <v>0.9451625</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
@@ -33330,6 +34260,12 @@
       <c r="BE220" t="n">
         <v>0.9375749999999999</v>
       </c>
+      <c r="BF220" t="n">
+        <v>0.9596111111111113</v>
+      </c>
+      <c r="BG220" t="n">
+        <v>0.9459583333333333</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -33424,6 +34360,12 @@
       <c r="BE221" t="n">
         <v>0.9474</v>
       </c>
+      <c r="BF221" t="n">
+        <v>0.8743299999999999</v>
+      </c>
+      <c r="BG221" t="n">
+        <v>0.9537799999999999</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
@@ -33512,6 +34454,12 @@
       <c r="BE222" t="n">
         <v>0.9600899999999999</v>
       </c>
+      <c r="BF222" t="n">
+        <v>0.860425</v>
+      </c>
+      <c r="BG222" t="n">
+        <v>0.9525363636363636</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
@@ -33600,6 +34548,12 @@
       <c r="BE223" t="n">
         <v>0.9658100000000001</v>
       </c>
+      <c r="BF223" t="n">
+        <v>0.9625166666666667</v>
+      </c>
+      <c r="BG223" t="n">
+        <v>0.9395874999999999</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
@@ -33688,6 +34642,12 @@
       <c r="BE224" t="n">
         <v>0.9409875</v>
       </c>
+      <c r="BF224" t="n">
+        <v>0.8754799999999999</v>
+      </c>
+      <c r="BG224" t="n">
+        <v>0.9442999999999999</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
@@ -33776,6 +34736,12 @@
       <c r="BE225" t="n">
         <v>0.9482250000000002</v>
       </c>
+      <c r="BF225" t="n">
+        <v>0.88605</v>
+      </c>
+      <c r="BG225" t="n">
+        <v>0.9608375</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
@@ -33864,6 +34830,12 @@
       <c r="BE226" t="n">
         <v>0.9568625000000001</v>
       </c>
+      <c r="BF226" t="n">
+        <v>0.9682000000000001</v>
+      </c>
+      <c r="BG226" t="n">
+        <v>0.9460199999999999</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
@@ -33952,6 +34924,12 @@
       <c r="BE227" t="n">
         <v>0.9567</v>
       </c>
+      <c r="BF227" t="n">
+        <v>0.8959</v>
+      </c>
+      <c r="BG227" t="n">
+        <v>0.9682333333333334</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
@@ -34040,6 +35018,12 @@
       <c r="BE228" t="n">
         <v>0.9221545454545456</v>
       </c>
+      <c r="BF228" t="n">
+        <v>0.9548375000000001</v>
+      </c>
+      <c r="BG228" t="n">
+        <v>0.9419888888888889</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
@@ -34128,6 +35112,12 @@
       <c r="BE229" t="n">
         <v>0.9052666666666666</v>
       </c>
+      <c r="BF229" t="n">
+        <v>0.9539333333333334</v>
+      </c>
+      <c r="BG229" t="n">
+        <v>0.9613125</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
@@ -34216,6 +35206,12 @@
       <c r="BE230" t="n">
         <v>0.9493571428571429</v>
       </c>
+      <c r="BF230" t="n">
+        <v>0.9618333333333334</v>
+      </c>
+      <c r="BG230" t="n">
+        <v>0.9615250000000001</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
@@ -34304,6 +35300,12 @@
       <c r="BE231" t="n">
         <v>0.95522</v>
       </c>
+      <c r="BF231" t="n">
+        <v>0.9561400000000001</v>
+      </c>
+      <c r="BG231" t="n">
+        <v>0.9636454545454547</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
@@ -34392,6 +35394,12 @@
       <c r="BE232" t="n">
         <v>0.9768285714285714</v>
       </c>
+      <c r="BF232" t="n">
+        <v>0.9550999999999999</v>
+      </c>
+      <c r="BG232" t="n">
+        <v>0.9611875</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
@@ -34480,6 +35488,12 @@
       <c r="BE233" t="n">
         <v>0.9506</v>
       </c>
+      <c r="BF233" t="n">
+        <v>0.8328857142857143</v>
+      </c>
+      <c r="BG233" t="n">
+        <v>0.9725142857142858</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
@@ -34568,6 +35582,12 @@
       <c r="BE234" t="n">
         <v>0.96745</v>
       </c>
+      <c r="BF234" t="n">
+        <v>0.8848454545454545</v>
+      </c>
+      <c r="BG234" t="n">
+        <v>0.9622571428571428</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
@@ -34656,6 +35676,12 @@
       <c r="BE235" t="n">
         <v>0.9390833333333334</v>
       </c>
+      <c r="BF235" t="n">
+        <v>0.9568714285714286</v>
+      </c>
+      <c r="BG235" t="n">
+        <v>0.95403</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
@@ -34744,6 +35770,12 @@
       <c r="BE236" t="n">
         <v>0.9601000000000001</v>
       </c>
+      <c r="BF236" t="n">
+        <v>0.9571222222222221</v>
+      </c>
+      <c r="BG236" t="n">
+        <v>0.9451699999999998</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
@@ -34832,6 +35864,12 @@
       <c r="BE237" t="n">
         <v>0.9623799999999999</v>
       </c>
+      <c r="BF237" t="n">
+        <v>0.8895272727272726</v>
+      </c>
+      <c r="BG237" t="n">
+        <v>0.95625</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
@@ -34920,6 +35958,12 @@
       <c r="BE238" t="n">
         <v>0.9418124999999999</v>
       </c>
+      <c r="BF238" t="n">
+        <v>0.9581900000000001</v>
+      </c>
+      <c r="BG238" t="n">
+        <v>0.9655199999999997</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
@@ -35008,6 +36052,12 @@
       <c r="BE239" t="n">
         <v>0.9592142857142859</v>
       </c>
+      <c r="BF239" t="n">
+        <v>0.8529625000000001</v>
+      </c>
+      <c r="BG239" t="n">
+        <v>0.966990909090909</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
@@ -35096,6 +36146,12 @@
       <c r="BE240" t="n">
         <v>0.9667375</v>
       </c>
+      <c r="BF240" t="n">
+        <v>0.9582555555555557</v>
+      </c>
+      <c r="BG240" t="n">
+        <v>0.9268399999999998</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
@@ -35184,6 +36240,12 @@
       <c r="BE241" t="n">
         <v>0.9664285714285714</v>
       </c>
+      <c r="BF241" t="n">
+        <v>0.952288888888889</v>
+      </c>
+      <c r="BG241" t="n">
+        <v>0.9166000000000001</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
@@ -35272,6 +36334,12 @@
       <c r="BE242" t="n">
         <v>0.96296</v>
       </c>
+      <c r="BF242" t="n">
+        <v>0.848325</v>
+      </c>
+      <c r="BG242" t="n">
+        <v>0.9422818181818182</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
@@ -35360,6 +36428,12 @@
       <c r="BE243" t="n">
         <v>0.9732800000000001</v>
       </c>
+      <c r="BF243" t="n">
+        <v>0.8861636363636364</v>
+      </c>
+      <c r="BG243" t="n">
+        <v>0.9687666666666667</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
@@ -35448,6 +36522,12 @@
       <c r="BE244" t="n">
         <v>0.9769555555555554</v>
       </c>
+      <c r="BF244" t="n">
+        <v>0.9588428571428571</v>
+      </c>
+      <c r="BG244" t="n">
+        <v>0.73382</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
@@ -35536,6 +36616,12 @@
       <c r="BE245" t="n">
         <v>0.9739375</v>
       </c>
+      <c r="BF245" t="n">
+        <v>0.962188888888889</v>
+      </c>
+      <c r="BG245" t="n">
+        <v>0.7406900000000001</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
@@ -35624,6 +36710,12 @@
       <c r="BE246" t="n">
         <v>0.9766571428571428</v>
       </c>
+      <c r="BF246" t="n">
+        <v>0.8626555555555556</v>
+      </c>
+      <c r="BG246" t="n">
+        <v>0.7878909090909091</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
@@ -35712,6 +36804,12 @@
       <c r="BE247" t="n">
         <v>0.9820555555555556</v>
       </c>
+      <c r="BF247" t="n">
+        <v>0.9586222222222222</v>
+      </c>
+      <c r="BG247" t="n">
+        <v>0.8926333333333333</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
@@ -35800,6 +36898,12 @@
       <c r="BE248" t="n">
         <v>0.975175</v>
       </c>
+      <c r="BF248" t="n">
+        <v>0.9596499999999999</v>
+      </c>
+      <c r="BG248" t="n">
+        <v>0.8787857142857142</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
@@ -35888,6 +36992,12 @@
       <c r="BE249" t="n">
         <v>0.9775499999999999</v>
       </c>
+      <c r="BF249" t="n">
+        <v>0.8409428571428571</v>
+      </c>
+      <c r="BG249" t="n">
+        <v>0.95533</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
@@ -35976,6 +37086,12 @@
       <c r="BE250" t="n">
         <v>0.9759999999999999</v>
       </c>
+      <c r="BF250" t="n">
+        <v>0.8519249999999999</v>
+      </c>
+      <c r="BG250" t="n">
+        <v>0.8770900000000001</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
@@ -36064,6 +37180,12 @@
       <c r="BE251" t="n">
         <v>0.9773200000000001</v>
       </c>
+      <c r="BF251" t="n">
+        <v>0.895753846153846</v>
+      </c>
+      <c r="BG251" t="n">
+        <v>0.8311333333333333</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
@@ -36152,6 +37274,12 @@
       <c r="BE252" t="n">
         <v>0.9817454545454546</v>
       </c>
+      <c r="BF252" t="n">
+        <v>0.9607</v>
+      </c>
+      <c r="BG252" t="n">
+        <v>0.8708083333333335</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
@@ -36240,6 +37368,12 @@
       <c r="BE253" t="n">
         <v>0.9760500000000001</v>
       </c>
+      <c r="BF253" t="n">
+        <v>0.8966615384615384</v>
+      </c>
+      <c r="BG253" t="n">
+        <v>0.9071692307692308</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
@@ -36328,6 +37462,12 @@
       <c r="BE254" t="n">
         <v>0.980025</v>
       </c>
+      <c r="BF254" t="n">
+        <v>0.8609111111111111</v>
+      </c>
+      <c r="BG254" t="n">
+        <v>0.9167099999999999</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
@@ -36416,6 +37556,12 @@
       <c r="BE255" t="n">
         <v>0.9775545454545455</v>
       </c>
+      <c r="BF255" t="n">
+        <v>0.9605181818181818</v>
+      </c>
+      <c r="BG255" t="n">
+        <v>0.9184636363636364</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
@@ -36504,6 +37650,12 @@
       <c r="BE256" t="n">
         <v>0.9766875</v>
       </c>
+      <c r="BF256" t="n">
+        <v>0.96385</v>
+      </c>
+      <c r="BG256" t="n">
+        <v>0.8949416666666666</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
@@ -36592,6 +37744,12 @@
       <c r="BE257" t="n">
         <v>0.9798818181818182</v>
       </c>
+      <c r="BF257" t="n">
+        <v>0.8855545454545454</v>
+      </c>
+      <c r="BG257" t="n">
+        <v>0.9074900000000001</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
@@ -36680,6 +37838,12 @@
       <c r="BE258" t="n">
         <v>0.9808499999999999</v>
       </c>
+      <c r="BF258" t="n">
+        <v>0.8382857142857143</v>
+      </c>
+      <c r="BG258" t="n">
+        <v>0.8935916666666667</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
@@ -36768,6 +37932,9 @@
       <c r="BE259" t="n">
         <v>0.976375</v>
       </c>
+      <c r="BF259" t="n">
+        <v>0.9629874999999999</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
@@ -36856,6 +38023,9 @@
       <c r="BE260" t="n">
         <v>0.9795</v>
       </c>
+      <c r="BF260" t="n">
+        <v>0.9613727272727272</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
@@ -36944,6 +38114,9 @@
       <c r="BE261" t="n">
         <v>0.9849375</v>
       </c>
+      <c r="BF261" t="n">
+        <v>0.9602222222222222</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
@@ -37032,6 +38205,9 @@
       <c r="BE262" t="n">
         <v>0.9760099999999999</v>
       </c>
+      <c r="BF262" t="n">
+        <v>0.961957142857143</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
@@ -37120,6 +38296,9 @@
       <c r="BE263" t="n">
         <v>0.9736799999999999</v>
       </c>
+      <c r="BF263" t="n">
+        <v>0.9589833333333334</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
@@ -37208,6 +38387,9 @@
       <c r="BE264" t="n">
         <v>0.9801125000000001</v>
       </c>
+      <c r="BF264" t="n">
+        <v>0.9596363636363637</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
@@ -37296,6 +38478,9 @@
       <c r="BE265" t="n">
         <v>0.9664285714285715</v>
       </c>
+      <c r="BF265" t="n">
+        <v>0.9623</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
@@ -37384,6 +38569,9 @@
       <c r="BE266" t="n">
         <v>0.9752555555555555</v>
       </c>
+      <c r="BF266" t="n">
+        <v>0.862822222222222</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
@@ -37472,6 +38660,9 @@
       <c r="BE267" t="n">
         <v>0.9769999999999999</v>
       </c>
+      <c r="BF267" t="n">
+        <v>0.9571666666666666</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
@@ -37560,6 +38751,9 @@
       <c r="BE268" t="n">
         <v>0.9697125</v>
       </c>
+      <c r="BF268" t="n">
+        <v>0.9622888888888887</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
@@ -37648,6 +38842,9 @@
       <c r="BE269" t="n">
         <v>0.9846499999999999</v>
       </c>
+      <c r="BF269" t="n">
+        <v>0.9581285714285716</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
@@ -37736,6 +38933,9 @@
       <c r="BE270" t="n">
         <v>0.9801857142857144</v>
       </c>
+      <c r="BF270" t="n">
+        <v>0.8865636363636362</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
@@ -37824,6 +39024,9 @@
       <c r="BE271" t="n">
         <v>0.9551181818181818</v>
       </c>
+      <c r="BF271" t="n">
+        <v>0.9654777777777777</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
@@ -37912,6 +39115,9 @@
       <c r="BE272" t="n">
         <v>0.98016</v>
       </c>
+      <c r="BF272" t="n">
+        <v>0.96285</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
@@ -38000,6 +39206,9 @@
       <c r="BE273" t="n">
         <v>0.9834375</v>
       </c>
+      <c r="BF273" t="n">
+        <v>0.959</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
@@ -38088,6 +39297,9 @@
       <c r="BE274" t="n">
         <v>0.9758999999999999</v>
       </c>
+      <c r="BF274" t="n">
+        <v>0.8634444444444445</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
@@ -38176,6 +39388,9 @@
       <c r="BE275" t="n">
         <v>0.9790142857142857</v>
       </c>
+      <c r="BF275" t="n">
+        <v>0.882618181818182</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
@@ -38264,6 +39479,9 @@
       <c r="BE276" t="n">
         <v>0.9585444444444445</v>
       </c>
+      <c r="BF276" t="n">
+        <v>0.9684272727272727</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
@@ -38352,6 +39570,9 @@
       <c r="BE277" t="n">
         <v>0.9768272727272728</v>
       </c>
+      <c r="BF277" t="n">
+        <v>0.9672272727272727</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
@@ -38440,6 +39661,9 @@
       <c r="BE278" t="n">
         <v>0.9836571428571429</v>
       </c>
+      <c r="BF278" t="n">
+        <v>0.8606888888888888</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
@@ -38528,6 +39752,9 @@
       <c r="BE279" t="n">
         <v>0.98106</v>
       </c>
+      <c r="BF279" t="n">
+        <v>0.96653</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
@@ -38616,6 +39843,9 @@
       <c r="BE280" t="n">
         <v>0.9815777777777777</v>
       </c>
+      <c r="BF280" t="n">
+        <v>0.960325</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
@@ -38704,6 +39934,9 @@
       <c r="BE281" t="n">
         <v>0.9546800000000001</v>
       </c>
+      <c r="BF281" t="n">
+        <v>0.9625499999999999</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
@@ -38792,6 +40025,9 @@
       <c r="BE282" t="n">
         <v>0.9562999999999999</v>
       </c>
+      <c r="BF282" t="n">
+        <v>0.8701111111111112</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
@@ -38880,6 +40116,9 @@
       <c r="BE283" t="n">
         <v>0.9720222222222223</v>
       </c>
+      <c r="BF283" t="n">
+        <v>0.963976923076923</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
@@ -38968,6 +40207,9 @@
       <c r="BE284" t="n">
         <v>0.9773333333333333</v>
       </c>
+      <c r="BF284" t="n">
+        <v>0.9670200000000001</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
@@ -39056,6 +40298,9 @@
       <c r="BE285" t="n">
         <v>0.9808222222222223</v>
       </c>
+      <c r="BF285" t="n">
+        <v>0.9606909090909092</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
@@ -39144,6 +40389,9 @@
       <c r="BE286" t="n">
         <v>0.9789727272727273</v>
       </c>
+      <c r="BF286" t="n">
+        <v>0.9681166666666666</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
@@ -39232,6 +40480,9 @@
       <c r="BE287" t="n">
         <v>0.9826999999999998</v>
       </c>
+      <c r="BF287" t="n">
+        <v>0.9677636363636363</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
@@ -39320,6 +40571,9 @@
       <c r="BE288" t="n">
         <v>0.9788428571428571</v>
       </c>
+      <c r="BF288" t="n">
+        <v>0.96423</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
@@ -39408,6 +40662,9 @@
       <c r="BE289" t="n">
         <v>0.9475111111111111</v>
       </c>
+      <c r="BF289" t="n">
+        <v>0.9663888888888889</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
@@ -39496,6 +40753,9 @@
       <c r="BE290" t="n">
         <v>0.9807083333333334</v>
       </c>
+      <c r="BF290" t="n">
+        <v>0.96839</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
@@ -39584,6 +40844,9 @@
       <c r="BE291" t="n">
         <v>0.9050899999999998</v>
       </c>
+      <c r="BF291" t="n">
+        <v>0.9610857142857142</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
@@ -39672,6 +40935,9 @@
       <c r="BE292" t="n">
         <v>0.9422999999999999</v>
       </c>
+      <c r="BF292" t="n">
+        <v>0.8707333333333334</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
@@ -39760,6 +41026,9 @@
       <c r="BE293" t="n">
         <v>0.9802444444444445</v>
       </c>
+      <c r="BF293" t="n">
+        <v>0.9634200000000002</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
@@ -39848,6 +41117,9 @@
       <c r="BE294" t="n">
         <v>0.8999249999999999</v>
       </c>
+      <c r="BF294" t="n">
+        <v>0.8696111111111111</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
@@ -39936,6 +41208,9 @@
       <c r="BE295" t="n">
         <v>0.9832333333333333</v>
       </c>
+      <c r="BF295" t="n">
+        <v>0.96451</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
@@ -40024,6 +41299,9 @@
       <c r="BE296" t="n">
         <v>0.9396875</v>
       </c>
+      <c r="BF296" t="n">
+        <v>0.9722777777777778</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
@@ -40112,6 +41390,9 @@
       <c r="BE297" t="n">
         <v>0.9800111111111112</v>
       </c>
+      <c r="BF297" t="n">
+        <v>0.9664363636363635</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
@@ -40200,6 +41481,9 @@
       <c r="BE298" t="n">
         <v>0.9829</v>
       </c>
+      <c r="BF298" t="n">
+        <v>0.8846636363636364</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
@@ -40288,6 +41572,9 @@
       <c r="BE299" t="n">
         <v>0.9824499999999999</v>
       </c>
+      <c r="BF299" t="n">
+        <v>0.8937333333333332</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
@@ -40376,6 +41663,9 @@
       <c r="BE300" t="n">
         <v>0.98261</v>
       </c>
+      <c r="BF300" t="n">
+        <v>0.8772200000000001</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
@@ -40464,6 +41754,9 @@
       <c r="BE301" t="n">
         <v>0.93211</v>
       </c>
+      <c r="BF301" t="n">
+        <v>0.9120428571428573</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
@@ -40552,6 +41845,9 @@
       <c r="BE302" t="n">
         <v>0.9803333333333334</v>
       </c>
+      <c r="BF302" t="n">
+        <v>0.8565375000000001</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
@@ -40640,6 +41936,9 @@
       <c r="BE303" t="n">
         <v>0.9811666666666667</v>
       </c>
+      <c r="BF303" t="n">
+        <v>0.9022461538461537</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
@@ -40728,6 +42027,9 @@
       <c r="BE304" t="n">
         <v>0.98559</v>
       </c>
+      <c r="BF304" t="n">
+        <v>0.9714500000000001</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
@@ -40816,6 +42118,9 @@
       <c r="BE305" t="n">
         <v>0.98393</v>
       </c>
+      <c r="BF305" t="n">
+        <v>0.96532</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
@@ -40904,6 +42209,9 @@
       <c r="BE306" t="n">
         <v>0.9450500000000002</v>
       </c>
+      <c r="BF306" t="n">
+        <v>0.8569</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
@@ -40992,6 +42300,9 @@
       <c r="BE307" t="n">
         <v>0.9837749999999998</v>
       </c>
+      <c r="BF307" t="n">
+        <v>0.9703999999999999</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
@@ -41080,6 +42391,9 @@
       <c r="BE308" t="n">
         <v>0.9829636363636365</v>
       </c>
+      <c r="BF308" t="n">
+        <v>0.9734714285714287</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
@@ -41168,6 +42482,9 @@
       <c r="BE309" t="n">
         <v>0.9838666666666666</v>
       </c>
+      <c r="BF309" t="n">
+        <v>0.9657285714285714</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
@@ -41256,6 +42573,9 @@
       <c r="BE310" t="n">
         <v>0.9817181818181819</v>
       </c>
+      <c r="BF310" t="n">
+        <v>0.9751124999999999</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
@@ -41343,6 +42663,9 @@
       </c>
       <c r="BE311" t="n">
         <v>0.9866083333333332</v>
+      </c>
+      <c r="BF311" t="n">
+        <v>0.8713888888888888</v>
       </c>
     </row>
     <row r="312">
@@ -41507,6 +42830,12 @@
       <c r="BE316" t="n">
         <v>0.3257</v>
       </c>
+      <c r="BF316" t="n">
+        <v>0.2789</v>
+      </c>
+      <c r="BG316" t="n">
+        <v>0.0365</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
@@ -41604,6 +42933,12 @@
       <c r="BE317" t="n">
         <v>0.7362</v>
       </c>
+      <c r="BF317" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="BG317" t="n">
+        <v>0.2218</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
@@ -41701,6 +43036,12 @@
       <c r="BE318" t="n">
         <v>0.3744</v>
       </c>
+      <c r="BF318" t="n">
+        <v>0.5828</v>
+      </c>
+      <c r="BG318" t="n">
+        <v>0.5504</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
@@ -41798,6 +43139,12 @@
       <c r="BE319" t="n">
         <v>0.3098</v>
       </c>
+      <c r="BF319" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="BG319" t="n">
+        <v>0.7239</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
@@ -41895,6 +43242,12 @@
       <c r="BE320" t="n">
         <v>0.1654</v>
       </c>
+      <c r="BF320" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="BG320" t="n">
+        <v>0.5588</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
@@ -41989,6 +43342,12 @@
       <c r="BE321" t="n">
         <v>0.3476</v>
       </c>
+      <c r="BF321" t="n">
+        <v>0.2304</v>
+      </c>
+      <c r="BG321" t="n">
+        <v>0.7191</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
@@ -42083,6 +43442,12 @@
       <c r="BE322" t="n">
         <v>0.3166</v>
       </c>
+      <c r="BF322" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="BG322" t="n">
+        <v>0.8658</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
@@ -42177,6 +43542,12 @@
       <c r="BE323" t="n">
         <v>0.7334000000000001</v>
       </c>
+      <c r="BF323" t="n">
+        <v>0.1656</v>
+      </c>
+      <c r="BG323" t="n">
+        <v>0.9086</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
@@ -42271,6 +43642,12 @@
       <c r="BE324" t="n">
         <v>0.8638</v>
       </c>
+      <c r="BF324" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="BG324" t="n">
+        <v>0.9530999999999999</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
@@ -42365,6 +43742,12 @@
       <c r="BE325" t="n">
         <v>0.9081</v>
       </c>
+      <c r="BF325" t="n">
+        <v>0.2432</v>
+      </c>
+      <c r="BG325" t="n">
+        <v>0.8599</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
@@ -42453,6 +43836,12 @@
       <c r="BE326" t="n">
         <v>0.9543</v>
       </c>
+      <c r="BF326" t="n">
+        <v>0.1868</v>
+      </c>
+      <c r="BG326" t="n">
+        <v>0.8884</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
@@ -42541,6 +43930,12 @@
       <c r="BE327" t="n">
         <v>0.8605</v>
       </c>
+      <c r="BF327" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BG327" t="n">
+        <v>0.9055</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
@@ -42629,6 +44024,12 @@
       <c r="BE328" t="n">
         <v>0.764</v>
       </c>
+      <c r="BF328" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="BG328" t="n">
+        <v>0.7675999999999999</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
@@ -42717,6 +44118,12 @@
       <c r="BE329" t="n">
         <v>0.8537</v>
       </c>
+      <c r="BF329" t="n">
+        <v>0.4008</v>
+      </c>
+      <c r="BG329" t="n">
+        <v>0.9478</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
@@ -42805,6 +44212,12 @@
       <c r="BE330" t="n">
         <v>0.8612</v>
       </c>
+      <c r="BF330" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="BG330" t="n">
+        <v>0.8951</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
@@ -42893,6 +44306,12 @@
       <c r="BE331" t="n">
         <v>0.7425</v>
       </c>
+      <c r="BF331" t="n">
+        <v>0.2773</v>
+      </c>
+      <c r="BG331" t="n">
+        <v>0.8316</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
@@ -42981,6 +44400,12 @@
       <c r="BE332" t="n">
         <v>0.6448</v>
       </c>
+      <c r="BF332" t="n">
+        <v>0.2637</v>
+      </c>
+      <c r="BG332" t="n">
+        <v>0.8259</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
@@ -43069,6 +44494,12 @@
       <c r="BE333" t="n">
         <v>0.8525</v>
       </c>
+      <c r="BF333" t="n">
+        <v>0.2553</v>
+      </c>
+      <c r="BG333" t="n">
+        <v>0.9608</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
@@ -43157,6 +44588,12 @@
       <c r="BE334" t="n">
         <v>0.911</v>
       </c>
+      <c r="BF334" t="n">
+        <v>0.2416</v>
+      </c>
+      <c r="BG334" t="n">
+        <v>0.9537</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
@@ -43245,6 +44682,12 @@
       <c r="BE335" t="n">
         <v>0.9564</v>
       </c>
+      <c r="BF335" t="n">
+        <v>0.2326</v>
+      </c>
+      <c r="BG335" t="n">
+        <v>0.9349</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
@@ -43333,6 +44776,12 @@
       <c r="BE336" t="n">
         <v>0.9645</v>
       </c>
+      <c r="BF336" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="BG336" t="n">
+        <v>0.9389999999999999</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
@@ -43421,6 +44870,12 @@
       <c r="BE337" t="n">
         <v>0.9464</v>
       </c>
+      <c r="BF337" t="n">
+        <v>0.2037</v>
+      </c>
+      <c r="BG337" t="n">
+        <v>0.9508</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
@@ -43509,6 +44964,12 @@
       <c r="BE338" t="n">
         <v>0.8401999999999999</v>
       </c>
+      <c r="BF338" t="n">
+        <v>0.2388</v>
+      </c>
+      <c r="BG338" t="n">
+        <v>0.9352</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
@@ -43597,6 +45058,12 @@
       <c r="BE339" t="n">
         <v>0.8076</v>
       </c>
+      <c r="BF339" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="BG339" t="n">
+        <v>0.8747</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
@@ -43685,6 +45152,12 @@
       <c r="BE340" t="n">
         <v>0.8968</v>
       </c>
+      <c r="BF340" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="BG340" t="n">
+        <v>0.8488</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
@@ -43773,6 +45246,12 @@
       <c r="BE341" t="n">
         <v>0.8572</v>
       </c>
+      <c r="BF341" t="n">
+        <v>0.2147</v>
+      </c>
+      <c r="BG341" t="n">
+        <v>0.9520999999999999</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
@@ -43861,6 +45340,12 @@
       <c r="BE342" t="n">
         <v>0.9332</v>
       </c>
+      <c r="BF342" t="n">
+        <v>0.2068</v>
+      </c>
+      <c r="BG342" t="n">
+        <v>0.8691</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
@@ -43949,6 +45434,12 @@
       <c r="BE343" t="n">
         <v>0.9633</v>
       </c>
+      <c r="BF343" t="n">
+        <v>0.2116</v>
+      </c>
+      <c r="BG343" t="n">
+        <v>0.9172</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
@@ -44037,6 +45528,12 @@
       <c r="BE344" t="n">
         <v>0.9689</v>
       </c>
+      <c r="BF344" t="n">
+        <v>0.1843</v>
+      </c>
+      <c r="BG344" t="n">
+        <v>0.9038</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
@@ -44125,6 +45622,12 @@
       <c r="BE345" t="n">
         <v>0.9664</v>
       </c>
+      <c r="BF345" t="n">
+        <v>0.2251</v>
+      </c>
+      <c r="BG345" t="n">
+        <v>0.8544</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
@@ -44213,6 +45716,12 @@
       <c r="BE346" t="n">
         <v>0.9654</v>
       </c>
+      <c r="BF346" t="n">
+        <v>0.1677</v>
+      </c>
+      <c r="BG346" t="n">
+        <v>0.9261</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
@@ -44301,6 +45810,12 @@
       <c r="BE347" t="n">
         <v>0.9762</v>
       </c>
+      <c r="BF347" t="n">
+        <v>0.2032</v>
+      </c>
+      <c r="BG347" t="n">
+        <v>0.9384</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
@@ -44389,6 +45904,12 @@
       <c r="BE348" t="n">
         <v>0.9786</v>
       </c>
+      <c r="BF348" t="n">
+        <v>0.2093</v>
+      </c>
+      <c r="BG348" t="n">
+        <v>0.9023</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
@@ -44477,6 +45998,12 @@
       <c r="BE349" t="n">
         <v>0.9768</v>
       </c>
+      <c r="BF349" t="n">
+        <v>0.2025</v>
+      </c>
+      <c r="BG349" t="n">
+        <v>0.9091</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
@@ -44565,6 +46092,12 @@
       <c r="BE350" t="n">
         <v>0.9782999999999999</v>
       </c>
+      <c r="BF350" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="BG350" t="n">
+        <v>0.9194</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
@@ -44653,6 +46186,12 @@
       <c r="BE351" t="n">
         <v>0.9788</v>
       </c>
+      <c r="BF351" t="n">
+        <v>0.1665</v>
+      </c>
+      <c r="BG351" t="n">
+        <v>0.9278</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
@@ -44741,6 +46280,12 @@
       <c r="BE352" t="n">
         <v>0.9787</v>
       </c>
+      <c r="BF352" t="n">
+        <v>0.2416</v>
+      </c>
+      <c r="BG352" t="n">
+        <v>0.9671999999999999</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
@@ -44829,6 +46374,12 @@
       <c r="BE353" t="n">
         <v>0.9703000000000001</v>
       </c>
+      <c r="BF353" t="n">
+        <v>0.1473</v>
+      </c>
+      <c r="BG353" t="n">
+        <v>0.966</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
@@ -44917,6 +46468,12 @@
       <c r="BE354" t="n">
         <v>0.9747</v>
       </c>
+      <c r="BF354" t="n">
+        <v>0.1658</v>
+      </c>
+      <c r="BG354" t="n">
+        <v>0.9383</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
@@ -45005,6 +46562,12 @@
       <c r="BE355" t="n">
         <v>0.9821</v>
       </c>
+      <c r="BF355" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="BG355" t="n">
+        <v>0.946</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
@@ -45093,6 +46656,12 @@
       <c r="BE356" t="n">
         <v>0.985</v>
       </c>
+      <c r="BF356" t="n">
+        <v>0.2153</v>
+      </c>
+      <c r="BG356" t="n">
+        <v>0.9701</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
@@ -45181,6 +46750,12 @@
       <c r="BE357" t="n">
         <v>0.9771</v>
       </c>
+      <c r="BF357" t="n">
+        <v>0.1784</v>
+      </c>
+      <c r="BG357" t="n">
+        <v>0.9428</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
@@ -45269,6 +46844,12 @@
       <c r="BE358" t="n">
         <v>0.9791</v>
       </c>
+      <c r="BF358" t="n">
+        <v>0.1398</v>
+      </c>
+      <c r="BG358" t="n">
+        <v>0.905</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
@@ -45357,6 +46938,12 @@
       <c r="BE359" t="n">
         <v>0.9797</v>
       </c>
+      <c r="BF359" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="BG359" t="n">
+        <v>0.9689</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
@@ -45445,6 +47032,12 @@
       <c r="BE360" t="n">
         <v>0.9828</v>
       </c>
+      <c r="BF360" t="n">
+        <v>0.1635</v>
+      </c>
+      <c r="BG360" t="n">
+        <v>0.9789</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
@@ -45533,6 +47126,12 @@
       <c r="BE361" t="n">
         <v>0.9827</v>
       </c>
+      <c r="BF361" t="n">
+        <v>0.2021</v>
+      </c>
+      <c r="BG361" t="n">
+        <v>0.9095</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
@@ -45621,6 +47220,12 @@
       <c r="BE362" t="n">
         <v>0.9802</v>
       </c>
+      <c r="BF362" t="n">
+        <v>0.1584</v>
+      </c>
+      <c r="BG362" t="n">
+        <v>0.9401</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
@@ -45709,6 +47314,9 @@
       <c r="BE363" t="n">
         <v>0.9791</v>
       </c>
+      <c r="BF363" t="n">
+        <v>0.1647</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
@@ -45797,6 +47405,9 @@
       <c r="BE364" t="n">
         <v>0.9824000000000001</v>
       </c>
+      <c r="BF364" t="n">
+        <v>0.1839</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
@@ -45885,6 +47496,9 @@
       <c r="BE365" t="n">
         <v>0.9837</v>
       </c>
+      <c r="BF365" t="n">
+        <v>0.1642</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
@@ -45973,6 +47587,9 @@
       <c r="BE366" t="n">
         <v>0.9799</v>
       </c>
+      <c r="BF366" t="n">
+        <v>0.2275</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
@@ -46061,6 +47678,9 @@
       <c r="BE367" t="n">
         <v>0.9804</v>
       </c>
+      <c r="BF367" t="n">
+        <v>0.197</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
@@ -46149,6 +47769,9 @@
       <c r="BE368" t="n">
         <v>0.9809</v>
       </c>
+      <c r="BF368" t="n">
+        <v>0.1667</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
@@ -46237,6 +47860,9 @@
       <c r="BE369" t="n">
         <v>0.9812</v>
       </c>
+      <c r="BF369" t="n">
+        <v>0.147</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
@@ -46325,6 +47951,9 @@
       <c r="BE370" t="n">
         <v>0.9811</v>
       </c>
+      <c r="BF370" t="n">
+        <v>0.1556</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
@@ -46413,6 +48042,9 @@
       <c r="BE371" t="n">
         <v>0.9782999999999999</v>
       </c>
+      <c r="BF371" t="n">
+        <v>0.1512</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
@@ -46501,6 +48133,9 @@
       <c r="BE372" t="n">
         <v>0.9792</v>
       </c>
+      <c r="BF372" t="n">
+        <v>0.1573</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
@@ -46589,6 +48224,9 @@
       <c r="BE373" t="n">
         <v>0.9832</v>
       </c>
+      <c r="BF373" t="n">
+        <v>0.1569</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
@@ -46677,6 +48315,9 @@
       <c r="BE374" t="n">
         <v>0.9832</v>
       </c>
+      <c r="BF374" t="n">
+        <v>0.2007</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
@@ -46765,6 +48406,9 @@
       <c r="BE375" t="n">
         <v>0.9825</v>
       </c>
+      <c r="BF375" t="n">
+        <v>0.2004</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
@@ -46853,6 +48497,9 @@
       <c r="BE376" t="n">
         <v>0.9827</v>
       </c>
+      <c r="BF376" t="n">
+        <v>0.1801</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
@@ -46941,6 +48588,9 @@
       <c r="BE377" t="n">
         <v>0.9843</v>
       </c>
+      <c r="BF377" t="n">
+        <v>0.1693</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
@@ -47029,6 +48679,9 @@
       <c r="BE378" t="n">
         <v>0.9823</v>
       </c>
+      <c r="BF378" t="n">
+        <v>0.136</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
@@ -47117,6 +48770,9 @@
       <c r="BE379" t="n">
         <v>0.9845</v>
       </c>
+      <c r="BF379" t="n">
+        <v>0.1731</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
@@ -47205,6 +48861,9 @@
       <c r="BE380" t="n">
         <v>0.9839</v>
       </c>
+      <c r="BF380" t="n">
+        <v>0.1872</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
@@ -47293,6 +48952,9 @@
       <c r="BE381" t="n">
         <v>0.9805</v>
       </c>
+      <c r="BF381" t="n">
+        <v>0.1701</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
@@ -47381,6 +49043,9 @@
       <c r="BE382" t="n">
         <v>0.9849</v>
       </c>
+      <c r="BF382" t="n">
+        <v>0.1648</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
@@ -47469,6 +49134,9 @@
       <c r="BE383" t="n">
         <v>0.9854000000000001</v>
       </c>
+      <c r="BF383" t="n">
+        <v>0.1707</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
@@ -47557,6 +49225,9 @@
       <c r="BE384" t="n">
         <v>0.9836</v>
       </c>
+      <c r="BF384" t="n">
+        <v>0.1767</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
@@ -47645,6 +49316,9 @@
       <c r="BE385" t="n">
         <v>0.9799</v>
       </c>
+      <c r="BF385" t="n">
+        <v>0.1658</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
@@ -47733,6 +49407,9 @@
       <c r="BE386" t="n">
         <v>0.9844000000000001</v>
       </c>
+      <c r="BF386" t="n">
+        <v>0.1493</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
@@ -47821,6 +49498,9 @@
       <c r="BE387" t="n">
         <v>0.9837</v>
       </c>
+      <c r="BF387" t="n">
+        <v>0.1699</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
@@ -47909,6 +49589,9 @@
       <c r="BE388" t="n">
         <v>0.9821</v>
       </c>
+      <c r="BF388" t="n">
+        <v>0.1922</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
@@ -47997,6 +49680,9 @@
       <c r="BE389" t="n">
         <v>0.9832</v>
       </c>
+      <c r="BF389" t="n">
+        <v>0.1832</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
@@ -48085,6 +49771,9 @@
       <c r="BE390" t="n">
         <v>0.9802</v>
       </c>
+      <c r="BF390" t="n">
+        <v>0.167</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
@@ -48173,6 +49862,9 @@
       <c r="BE391" t="n">
         <v>0.9853</v>
       </c>
+      <c r="BF391" t="n">
+        <v>0.1965</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
@@ -48261,6 +49953,9 @@
       <c r="BE392" t="n">
         <v>0.9817</v>
       </c>
+      <c r="BF392" t="n">
+        <v>0.1735</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
@@ -48349,6 +50044,9 @@
       <c r="BE393" t="n">
         <v>0.9788</v>
       </c>
+      <c r="BF393" t="n">
+        <v>0.1743</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
@@ -48437,6 +50135,9 @@
       <c r="BE394" t="n">
         <v>0.9836</v>
       </c>
+      <c r="BF394" t="n">
+        <v>0.1663</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
@@ -48525,6 +50226,9 @@
       <c r="BE395" t="n">
         <v>0.9858</v>
       </c>
+      <c r="BF395" t="n">
+        <v>0.1612</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
@@ -48613,6 +50317,9 @@
       <c r="BE396" t="n">
         <v>0.9842</v>
       </c>
+      <c r="BF396" t="n">
+        <v>0.157</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
@@ -48701,6 +50408,9 @@
       <c r="BE397" t="n">
         <v>0.9834000000000001</v>
       </c>
+      <c r="BF397" t="n">
+        <v>0.1481</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
@@ -48789,6 +50499,9 @@
       <c r="BE398" t="n">
         <v>0.9881</v>
       </c>
+      <c r="BF398" t="n">
+        <v>0.1461</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
@@ -48877,6 +50590,9 @@
       <c r="BE399" t="n">
         <v>0.9869</v>
       </c>
+      <c r="BF399" t="n">
+        <v>0.1603</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
@@ -48965,6 +50681,9 @@
       <c r="BE400" t="n">
         <v>0.9875</v>
       </c>
+      <c r="BF400" t="n">
+        <v>0.1567</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
@@ -49053,6 +50772,9 @@
       <c r="BE401" t="n">
         <v>0.9828</v>
       </c>
+      <c r="BF401" t="n">
+        <v>0.1861</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="n">
@@ -49141,6 +50863,9 @@
       <c r="BE402" t="n">
         <v>0.9859</v>
       </c>
+      <c r="BF402" t="n">
+        <v>0.1553</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
@@ -49229,6 +50954,9 @@
       <c r="BE403" t="n">
         <v>0.9867</v>
       </c>
+      <c r="BF403" t="n">
+        <v>0.1409</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
@@ -49317,6 +51045,9 @@
       <c r="BE404" t="n">
         <v>0.9831</v>
       </c>
+      <c r="BF404" t="n">
+        <v>0.1491</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
@@ -49405,6 +51136,9 @@
       <c r="BE405" t="n">
         <v>0.9839</v>
       </c>
+      <c r="BF405" t="n">
+        <v>0.1745</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
@@ -49493,6 +51227,9 @@
       <c r="BE406" t="n">
         <v>0.9833</v>
       </c>
+      <c r="BF406" t="n">
+        <v>0.1384</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="1" t="n">
@@ -49581,6 +51318,9 @@
       <c r="BE407" t="n">
         <v>0.9854000000000001</v>
       </c>
+      <c r="BF407" t="n">
+        <v>0.1253</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
@@ -49669,6 +51409,9 @@
       <c r="BE408" t="n">
         <v>0.9867</v>
       </c>
+      <c r="BF408" t="n">
+        <v>0.1356</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
@@ -49757,6 +51500,9 @@
       <c r="BE409" t="n">
         <v>0.9854000000000001</v>
       </c>
+      <c r="BF409" t="n">
+        <v>0.1401</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
@@ -49845,6 +51591,9 @@
       <c r="BE410" t="n">
         <v>0.9845</v>
       </c>
+      <c r="BF410" t="n">
+        <v>0.1441</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="n">
@@ -49933,6 +51682,9 @@
       <c r="BE411" t="n">
         <v>0.9852</v>
       </c>
+      <c r="BF411" t="n">
+        <v>0.1448</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
@@ -50021,6 +51773,9 @@
       <c r="BE412" t="n">
         <v>0.9867</v>
       </c>
+      <c r="BF412" t="n">
+        <v>0.1469</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
@@ -50109,6 +51864,9 @@
       <c r="BE413" t="n">
         <v>0.9846</v>
       </c>
+      <c r="BF413" t="n">
+        <v>0.1648</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="n">
@@ -50197,6 +51955,9 @@
       <c r="BE414" t="n">
         <v>0.9842</v>
       </c>
+      <c r="BF414" t="n">
+        <v>0.1534</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
@@ -50284,6 +52045,9 @@
       </c>
       <c r="BE415" t="n">
         <v>0.99</v>
+      </c>
+      <c r="BF415" t="n">
+        <v>0.1304</v>
       </c>
     </row>
     <row r="416">

--- a/CIFAR_Global.xlsx
+++ b/CIFAR_Global.xlsx
@@ -18651,6 +18651,9 @@
       <c r="BF52" t="n">
         <v>0.6289473684210526</v>
       </c>
+      <c r="BG52" t="n">
+        <v>0.6050992452830188</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -18752,6 +18755,9 @@
       <c r="BF53" t="n">
         <v>0.5878947368421052</v>
       </c>
+      <c r="BG53" t="n">
+        <v>0.6230675471698113</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -18853,6 +18859,9 @@
       <c r="BF54" t="n">
         <v>0.6052631578947368</v>
       </c>
+      <c r="BG54" t="n">
+        <v>0.6566667924528302</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -18954,6 +18963,9 @@
       <c r="BF55" t="n">
         <v>0.6263157894736842</v>
       </c>
+      <c r="BG55" t="n">
+        <v>0.6638977358490565</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -19055,6 +19067,9 @@
       <c r="BF56" t="n">
         <v>0.6247368421052631</v>
       </c>
+      <c r="BG56" t="n">
+        <v>0.6090445283018868</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -19156,6 +19171,9 @@
       <c r="BF57" t="n">
         <v>0.628421052631579</v>
       </c>
+      <c r="BG57" t="n">
+        <v>0.5946067924528301</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -19257,6 +19275,9 @@
       <c r="BF58" t="n">
         <v>0.6521052631578947</v>
       </c>
+      <c r="BG58" t="n">
+        <v>0.6574324528301888</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -19358,6 +19379,9 @@
       <c r="BF59" t="n">
         <v>0.6363157894736841</v>
       </c>
+      <c r="BG59" t="n">
+        <v>0.6187441509433962</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -19459,6 +19483,9 @@
       <c r="BF60" t="n">
         <v>0.6389473684210527</v>
       </c>
+      <c r="BG60" t="n">
+        <v>0.617183396226415</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -19560,6 +19587,9 @@
       <c r="BF61" t="n">
         <v>0.6284210526315789</v>
       </c>
+      <c r="BG61" t="n">
+        <v>0.6451803773584905</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -19661,6 +19691,9 @@
       <c r="BF62" t="n">
         <v>0.6289473684210526</v>
       </c>
+      <c r="BG62" t="n">
+        <v>0.6761698113207546</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -19762,6 +19795,9 @@
       <c r="BF63" t="n">
         <v>0.6326315789473684</v>
       </c>
+      <c r="BG63" t="n">
+        <v>0.6531656603773585</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -19863,6 +19899,9 @@
       <c r="BF64" t="n">
         <v>0.6484210526315788</v>
       </c>
+      <c r="BG64" t="n">
+        <v>0.660345283018868</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -19964,6 +20003,9 @@
       <c r="BF65" t="n">
         <v>0.6405263157894736</v>
       </c>
+      <c r="BG65" t="n">
+        <v>0.693247547169811</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -20065,6 +20107,9 @@
       <c r="BF66" t="n">
         <v>0.6421052631578946</v>
       </c>
+      <c r="BG66" t="n">
+        <v>0.6822196226415093</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -20166,6 +20211,9 @@
       <c r="BF67" t="n">
         <v>0.638421052631579</v>
       </c>
+      <c r="BG67" t="n">
+        <v>0.6818377358490565</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -20267,6 +20315,9 @@
       <c r="BF68" t="n">
         <v>0.6236842105263158</v>
       </c>
+      <c r="BG68" t="n">
+        <v>0.6476943396226416</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -20368,6 +20419,9 @@
       <c r="BF69" t="n">
         <v>0.6310526315789474</v>
       </c>
+      <c r="BG69" t="n">
+        <v>0.6710226415094337</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -20469,6 +20523,9 @@
       <c r="BF70" t="n">
         <v>0.6278947368421054</v>
       </c>
+      <c r="BG70" t="n">
+        <v>0.669270188679245</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -20570,6 +20627,9 @@
       <c r="BF71" t="n">
         <v>0.6357894736842105</v>
       </c>
+      <c r="BG71" t="n">
+        <v>0.5993241509433963</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -20671,6 +20731,9 @@
       <c r="BF72" t="n">
         <v>0.6347368421052632</v>
       </c>
+      <c r="BG72" t="n">
+        <v>0.6305166037735849</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -20772,6 +20835,9 @@
       <c r="BF73" t="n">
         <v>0.6378947368421052</v>
       </c>
+      <c r="BG73" t="n">
+        <v>0.6133811320754716</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -20873,6 +20939,9 @@
       <c r="BF74" t="n">
         <v>0.6468421052631577</v>
       </c>
+      <c r="BG74" t="n">
+        <v>0.6816116981132075</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -20974,6 +21043,9 @@
       <c r="BF75" t="n">
         <v>0.6426315789473683</v>
       </c>
+      <c r="BG75" t="n">
+        <v>0.6809418867924529</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -21075,6 +21147,9 @@
       <c r="BF76" t="n">
         <v>0.628421052631579</v>
       </c>
+      <c r="BG76" t="n">
+        <v>0.653607924528302</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -21176,6 +21251,9 @@
       <c r="BF77" t="n">
         <v>0.6426315789473684</v>
       </c>
+      <c r="BG77" t="n">
+        <v>0.6614271698113209</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -21277,6 +21355,9 @@
       <c r="BF78" t="n">
         <v>0.6394736842105263</v>
       </c>
+      <c r="BG78" t="n">
+        <v>0.6530407547169812</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -21378,6 +21459,9 @@
       <c r="BF79" t="n">
         <v>0.6526315789473685</v>
       </c>
+      <c r="BG79" t="n">
+        <v>0.6707618867924529</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -21479,6 +21563,9 @@
       <c r="BF80" t="n">
         <v>0.6405263157894737</v>
       </c>
+      <c r="BG80" t="n">
+        <v>0.686423396226415</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -21580,6 +21667,9 @@
       <c r="BF81" t="n">
         <v>0.6389473684210527</v>
       </c>
+      <c r="BG81" t="n">
+        <v>0.6873184501845019</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -21681,6 +21771,9 @@
       <c r="BF82" t="n">
         <v>0.6310526315789473</v>
       </c>
+      <c r="BG82" t="n">
+        <v>0.6646970479704796</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -21782,6 +21875,9 @@
       <c r="BF83" t="n">
         <v>0.6378947368421054</v>
       </c>
+      <c r="BG83" t="n">
+        <v>0.6589003690036901</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -21883,6 +21979,9 @@
       <c r="BF84" t="n">
         <v>0.6442105263157895</v>
       </c>
+      <c r="BG84" t="n">
+        <v>0.6461885608856089</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -21984,6 +22083,9 @@
       <c r="BF85" t="n">
         <v>0.636842105263158</v>
       </c>
+      <c r="BG85" t="n">
+        <v>0.6637239852398523</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -22085,6 +22187,9 @@
       <c r="BF86" t="n">
         <v>0.6452631578947368</v>
       </c>
+      <c r="BG86" t="n">
+        <v>0.6798527675276752</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -22186,6 +22291,9 @@
       <c r="BF87" t="n">
         <v>0.6473684210526315</v>
       </c>
+      <c r="BG87" t="n">
+        <v>0.6784003690036902</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -22287,6 +22395,9 @@
       <c r="BF88" t="n">
         <v>0.6442105263157895</v>
       </c>
+      <c r="BG88" t="n">
+        <v>0.6797616236162364</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -22388,6 +22499,9 @@
       <c r="BF89" t="n">
         <v>0.6431578947368422</v>
       </c>
+      <c r="BG89" t="n">
+        <v>0.6648022140221402</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -22489,6 +22603,9 @@
       <c r="BF90" t="n">
         <v>0.6384210526315791</v>
       </c>
+      <c r="BG90" t="n">
+        <v>0.6738372693726936</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -22590,6 +22707,9 @@
       <c r="BF91" t="n">
         <v>0.6368421052631578</v>
       </c>
+      <c r="BG91" t="n">
+        <v>0.6865826568265684</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -22691,6 +22811,9 @@
       <c r="BF92" t="n">
         <v>0.6394736842105264</v>
       </c>
+      <c r="BG92" t="n">
+        <v>0.6861523985239852</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -22792,6 +22915,9 @@
       <c r="BF93" t="n">
         <v>0.6442105263157895</v>
       </c>
+      <c r="BG93" t="n">
+        <v>0.6773756457564577</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -22893,6 +23019,9 @@
       <c r="BF94" t="n">
         <v>0.6373684210526316</v>
       </c>
+      <c r="BG94" t="n">
+        <v>0.661150553505535</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -22994,6 +23123,9 @@
       <c r="BF95" t="n">
         <v>0.6557894736842106</v>
       </c>
+      <c r="BG95" t="n">
+        <v>0.672740959409594</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -23095,6 +23227,9 @@
       <c r="BF96" t="n">
         <v>0.6336842105263158</v>
       </c>
+      <c r="BG96" t="n">
+        <v>0.6811103321033211</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -23196,6 +23331,9 @@
       <c r="BF97" t="n">
         <v>0.6426315789473683</v>
       </c>
+      <c r="BG97" t="n">
+        <v>0.7077682656826567</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -23297,6 +23435,9 @@
       <c r="BF98" t="n">
         <v>0.6436842105263159</v>
       </c>
+      <c r="BG98" t="n">
+        <v>0.6791287822878228</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -23398,6 +23539,9 @@
       <c r="BF99" t="n">
         <v>0.6494736842105263</v>
       </c>
+      <c r="BG99" t="n">
+        <v>0.6885416974169742</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -23499,6 +23643,9 @@
       <c r="BF100" t="n">
         <v>0.6526315789473685</v>
       </c>
+      <c r="BG100" t="n">
+        <v>0.6987885608856089</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -23600,6 +23747,9 @@
       <c r="BF101" t="n">
         <v>0.6610526315789473</v>
       </c>
+      <c r="BG101" t="n">
+        <v>0.7072981549815499</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -23701,6 +23851,9 @@
       <c r="BF102" t="n">
         <v>0.646842105263158</v>
       </c>
+      <c r="BG102" t="n">
+        <v>0.677380442804428</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -23802,6 +23955,9 @@
       <c r="BF103" t="n">
         <v>0.6478947368421052</v>
       </c>
+      <c r="BG103" t="n">
+        <v>0.6866948339483396</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -23902,6 +24058,9 @@
       </c>
       <c r="BF104" t="n">
         <v>0.6410526315789474</v>
+      </c>
+      <c r="BG104" t="n">
+        <v>0.7072520295202951</v>
       </c>
     </row>
     <row r="105">
@@ -28549,6 +28708,9 @@
       <c r="BF155" t="n">
         <v>0.7142857142857143</v>
       </c>
+      <c r="BG155" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -28640,6 +28802,9 @@
       <c r="BF156" t="n">
         <v>0.25</v>
       </c>
+      <c r="BG156" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -28731,6 +28896,9 @@
       <c r="BF157" t="n">
         <v>0.5</v>
       </c>
+      <c r="BG157" t="n">
+        <v>0.1428571428571428</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -28822,6 +28990,9 @@
       <c r="BF158" t="n">
         <v>1</v>
       </c>
+      <c r="BG158" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -28913,6 +29084,9 @@
       <c r="BF159" t="n">
         <v>1</v>
       </c>
+      <c r="BG159" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -29004,6 +29178,9 @@
       <c r="BF160" t="n">
         <v>1</v>
       </c>
+      <c r="BG160" t="n">
+        <v>0.5833333333333334</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -29095,6 +29272,9 @@
       <c r="BF161" t="n">
         <v>0.5</v>
       </c>
+      <c r="BG161" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -29186,6 +29366,9 @@
       <c r="BF162" t="n">
         <v>0.5</v>
       </c>
+      <c r="BG162" t="n">
+        <v>0.8181818181818182</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -29277,6 +29460,9 @@
       <c r="BF163" t="n">
         <v>0.5</v>
       </c>
+      <c r="BG163" t="n">
+        <v>0.5384615384615384</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -29368,6 +29554,9 @@
       <c r="BF164" t="n">
         <v>0.5</v>
       </c>
+      <c r="BG164" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -29459,6 +29648,9 @@
       <c r="BF165" t="n">
         <v>0.375</v>
       </c>
+      <c r="BG165" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -29550,6 +29742,9 @@
       <c r="BF166" t="n">
         <v>1</v>
       </c>
+      <c r="BG166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -29641,6 +29836,9 @@
       <c r="BF167" t="n">
         <v>1</v>
       </c>
+      <c r="BG167" t="n">
+        <v>0.9166666666666666</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -29732,6 +29930,9 @@
       <c r="BF168" t="n">
         <v>1</v>
       </c>
+      <c r="BG168" t="n">
+        <v>0.3636363636363636</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -29823,6 +30024,9 @@
       <c r="BF169" t="n">
         <v>1</v>
       </c>
+      <c r="BG169" t="n">
+        <v>0.3846153846153846</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -29914,6 +30118,9 @@
       <c r="BF170" t="n">
         <v>0.5</v>
       </c>
+      <c r="BG170" t="n">
+        <v>0.4615384615384616</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -30005,6 +30212,9 @@
       <c r="BF171" t="n">
         <v>1</v>
       </c>
+      <c r="BG171" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -30096,6 +30306,9 @@
       <c r="BF172" t="n">
         <v>1</v>
       </c>
+      <c r="BG172" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -30187,6 +30400,9 @@
       <c r="BF173" t="n">
         <v>1</v>
       </c>
+      <c r="BG173" t="n">
+        <v>0.7272727272727273</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -30278,6 +30494,9 @@
       <c r="BF174" t="n">
         <v>1</v>
       </c>
+      <c r="BG174" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -30369,6 +30588,9 @@
       <c r="BF175" t="n">
         <v>1</v>
       </c>
+      <c r="BG175" t="n">
+        <v>0.8181818181818182</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -30460,6 +30682,9 @@
       <c r="BF176" t="n">
         <v>1</v>
       </c>
+      <c r="BG176" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -30551,6 +30776,9 @@
       <c r="BF177" t="n">
         <v>1</v>
       </c>
+      <c r="BG177" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -30642,6 +30870,9 @@
       <c r="BF178" t="n">
         <v>1</v>
       </c>
+      <c r="BG178" t="n">
+        <v>0.4615384615384616</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -30733,6 +30964,9 @@
       <c r="BF179" t="n">
         <v>1</v>
       </c>
+      <c r="BG179" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -30824,6 +31058,9 @@
       <c r="BF180" t="n">
         <v>1</v>
       </c>
+      <c r="BG180" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -30915,6 +31152,9 @@
       <c r="BF181" t="n">
         <v>1</v>
       </c>
+      <c r="BG181" t="n">
+        <v>0.8181818181818182</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -31006,6 +31246,9 @@
       <c r="BF182" t="n">
         <v>1</v>
       </c>
+      <c r="BG182" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -31097,6 +31340,9 @@
       <c r="BF183" t="n">
         <v>1</v>
       </c>
+      <c r="BG183" t="n">
+        <v>0.7777777777777778</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -31188,6 +31434,9 @@
       <c r="BF184" t="n">
         <v>1</v>
       </c>
+      <c r="BG184" t="n">
+        <v>0.7777777777777778</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -31279,6 +31528,9 @@
       <c r="BF185" t="n">
         <v>1</v>
       </c>
+      <c r="BG185" t="n">
+        <v>0.8181818181818182</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -31370,6 +31622,9 @@
       <c r="BF186" t="n">
         <v>1</v>
       </c>
+      <c r="BG186" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -31461,6 +31716,9 @@
       <c r="BF187" t="n">
         <v>1</v>
       </c>
+      <c r="BG187" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -31552,6 +31810,9 @@
       <c r="BF188" t="n">
         <v>1</v>
       </c>
+      <c r="BG188" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
@@ -31643,6 +31904,9 @@
       <c r="BF189" t="n">
         <v>1</v>
       </c>
+      <c r="BG189" t="n">
+        <v>0.6363636363636364</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -31734,6 +31998,9 @@
       <c r="BF190" t="n">
         <v>1</v>
       </c>
+      <c r="BG190" t="n">
+        <v>0.7777777777777778</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -31825,6 +32092,9 @@
       <c r="BF191" t="n">
         <v>1</v>
       </c>
+      <c r="BG191" t="n">
+        <v>0.875</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -31916,6 +32186,9 @@
       <c r="BF192" t="n">
         <v>1</v>
       </c>
+      <c r="BG192" t="n">
+        <v>0.875</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -32007,6 +32280,9 @@
       <c r="BF193" t="n">
         <v>1</v>
       </c>
+      <c r="BG193" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -32098,6 +32374,9 @@
       <c r="BF194" t="n">
         <v>1</v>
       </c>
+      <c r="BG194" t="n">
+        <v>0.9090909090909091</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -32189,6 +32468,9 @@
       <c r="BF195" t="n">
         <v>1</v>
       </c>
+      <c r="BG195" t="n">
+        <v>0.9166666666666666</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -32280,6 +32562,9 @@
       <c r="BF196" t="n">
         <v>1</v>
       </c>
+      <c r="BG196" t="n">
+        <v>0.9090909090909091</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -32371,6 +32656,9 @@
       <c r="BF197" t="n">
         <v>1</v>
       </c>
+      <c r="BG197" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
@@ -32462,6 +32750,9 @@
       <c r="BF198" t="n">
         <v>1</v>
       </c>
+      <c r="BG198" t="n">
+        <v>0.8888888888888888</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
@@ -32553,6 +32844,9 @@
       <c r="BF199" t="n">
         <v>1</v>
       </c>
+      <c r="BG199" t="n">
+        <v>0.8888888888888888</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
@@ -32644,6 +32938,9 @@
       <c r="BF200" t="n">
         <v>1</v>
       </c>
+      <c r="BG200" t="n">
+        <v>0.3333333333333333</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -32735,6 +33032,9 @@
       <c r="BF201" t="n">
         <v>1</v>
       </c>
+      <c r="BG201" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
@@ -32826,6 +33126,9 @@
       <c r="BF202" t="n">
         <v>1</v>
       </c>
+      <c r="BG202" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
@@ -32917,6 +33220,9 @@
       <c r="BF203" t="n">
         <v>1</v>
       </c>
+      <c r="BG203" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -33008,6 +33314,9 @@
       <c r="BF204" t="n">
         <v>1</v>
       </c>
+      <c r="BG204" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
@@ -33099,6 +33408,9 @@
       <c r="BF205" t="n">
         <v>1</v>
       </c>
+      <c r="BG205" t="n">
+        <v>0.8888888888888888</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -33190,6 +33502,9 @@
       <c r="BF206" t="n">
         <v>1</v>
       </c>
+      <c r="BG206" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
@@ -33280,6 +33595,9 @@
       </c>
       <c r="BF207" t="n">
         <v>1</v>
+      </c>
+      <c r="BG207" t="n">
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="208">
@@ -37935,6 +38253,9 @@
       <c r="BF259" t="n">
         <v>0.9629874999999999</v>
       </c>
+      <c r="BG259" t="n">
+        <v>0.8597636363636364</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
@@ -38026,6 +38347,9 @@
       <c r="BF260" t="n">
         <v>0.9613727272727272</v>
       </c>
+      <c r="BG260" t="n">
+        <v>0.9469181818181819</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
@@ -38117,6 +38441,9 @@
       <c r="BF261" t="n">
         <v>0.9602222222222222</v>
       </c>
+      <c r="BG261" t="n">
+        <v>0.8108083333333332</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
@@ -38208,6 +38535,9 @@
       <c r="BF262" t="n">
         <v>0.961957142857143</v>
       </c>
+      <c r="BG262" t="n">
+        <v>0.8957222222222223</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
@@ -38299,6 +38629,9 @@
       <c r="BF263" t="n">
         <v>0.9589833333333334</v>
       </c>
+      <c r="BG263" t="n">
+        <v>0.9577583333333335</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
@@ -38390,6 +38723,9 @@
       <c r="BF264" t="n">
         <v>0.9596363636363637</v>
       </c>
+      <c r="BG264" t="n">
+        <v>0.9477666666666666</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
@@ -38481,6 +38817,9 @@
       <c r="BF265" t="n">
         <v>0.9623</v>
       </c>
+      <c r="BG265" t="n">
+        <v>0.8106</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
@@ -38572,6 +38911,9 @@
       <c r="BF266" t="n">
         <v>0.862822222222222</v>
       </c>
+      <c r="BG266" t="n">
+        <v>0.9420399999999999</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
@@ -38663,6 +39005,9 @@
       <c r="BF267" t="n">
         <v>0.9571666666666666</v>
       </c>
+      <c r="BG267" t="n">
+        <v>0.9681875</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
@@ -38754,6 +39099,9 @@
       <c r="BF268" t="n">
         <v>0.9622888888888887</v>
       </c>
+      <c r="BG268" t="n">
+        <v>0.847288888888889</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
@@ -38845,6 +39193,9 @@
       <c r="BF269" t="n">
         <v>0.9581285714285716</v>
       </c>
+      <c r="BG269" t="n">
+        <v>0.9301333333333334</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
@@ -38936,6 +39287,9 @@
       <c r="BF270" t="n">
         <v>0.8865636363636362</v>
       </c>
+      <c r="BG270" t="n">
+        <v>0.8725083333333333</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
@@ -39027,6 +39381,9 @@
       <c r="BF271" t="n">
         <v>0.9654777777777777</v>
       </c>
+      <c r="BG271" t="n">
+        <v>0.8951400000000002</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
@@ -39118,6 +39475,9 @@
       <c r="BF272" t="n">
         <v>0.96285</v>
       </c>
+      <c r="BG272" t="n">
+        <v>0.8238909090909092</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
@@ -39209,6 +39569,9 @@
       <c r="BF273" t="n">
         <v>0.959</v>
       </c>
+      <c r="BG273" t="n">
+        <v>0.9604222222222223</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
@@ -39300,6 +39663,9 @@
       <c r="BF274" t="n">
         <v>0.8634444444444445</v>
       </c>
+      <c r="BG274" t="n">
+        <v>0.9573666666666666</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
@@ -39391,6 +39757,9 @@
       <c r="BF275" t="n">
         <v>0.882618181818182</v>
       </c>
+      <c r="BG275" t="n">
+        <v>0.96996</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
@@ -39482,6 +39851,9 @@
       <c r="BF276" t="n">
         <v>0.9684272727272727</v>
       </c>
+      <c r="BG276" t="n">
+        <v>0.95899</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
@@ -39573,6 +39945,9 @@
       <c r="BF277" t="n">
         <v>0.9672272727272727</v>
       </c>
+      <c r="BG277" t="n">
+        <v>0.8626111111111111</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
@@ -39664,6 +40039,9 @@
       <c r="BF278" t="n">
         <v>0.8606888888888888</v>
       </c>
+      <c r="BG278" t="n">
+        <v>0.9550181818181817</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
@@ -39755,6 +40133,9 @@
       <c r="BF279" t="n">
         <v>0.96653</v>
       </c>
+      <c r="BG279" t="n">
+        <v>0.9537999999999999</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
@@ -39846,6 +40227,9 @@
       <c r="BF280" t="n">
         <v>0.960325</v>
       </c>
+      <c r="BG280" t="n">
+        <v>0.8121599999999999</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
@@ -39937,6 +40321,9 @@
       <c r="BF281" t="n">
         <v>0.9625499999999999</v>
       </c>
+      <c r="BG281" t="n">
+        <v>0.9116923076923076</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
@@ -40028,6 +40415,9 @@
       <c r="BF282" t="n">
         <v>0.8701111111111112</v>
       </c>
+      <c r="BG282" t="n">
+        <v>0.9644888888888887</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
@@ -40119,6 +40509,9 @@
       <c r="BF283" t="n">
         <v>0.963976923076923</v>
       </c>
+      <c r="BG283" t="n">
+        <v>0.9640818181818183</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
@@ -40210,6 +40603,9 @@
       <c r="BF284" t="n">
         <v>0.9670200000000001</v>
       </c>
+      <c r="BG284" t="n">
+        <v>0.8893818181818181</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
@@ -40301,6 +40697,9 @@
       <c r="BF285" t="n">
         <v>0.9606909090909092</v>
       </c>
+      <c r="BG285" t="n">
+        <v>0.8815166666666667</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
@@ -40392,6 +40791,9 @@
       <c r="BF286" t="n">
         <v>0.9681166666666666</v>
       </c>
+      <c r="BG286" t="n">
+        <v>0.8752599999999999</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
@@ -40483,6 +40885,9 @@
       <c r="BF287" t="n">
         <v>0.9677636363636363</v>
       </c>
+      <c r="BG287" t="n">
+        <v>0.72095</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
@@ -40574,6 +40979,9 @@
       <c r="BF288" t="n">
         <v>0.96423</v>
       </c>
+      <c r="BG288" t="n">
+        <v>0.86972</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
@@ -40665,6 +41073,9 @@
       <c r="BF289" t="n">
         <v>0.9663888888888889</v>
       </c>
+      <c r="BG289" t="n">
+        <v>0.9247545454545455</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
@@ -40756,6 +41167,9 @@
       <c r="BF290" t="n">
         <v>0.96839</v>
       </c>
+      <c r="BG290" t="n">
+        <v>0.9640222222222222</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
@@ -40847,6 +41261,9 @@
       <c r="BF291" t="n">
         <v>0.9610857142857142</v>
       </c>
+      <c r="BG291" t="n">
+        <v>0.8970181818181818</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
@@ -40938,6 +41355,9 @@
       <c r="BF292" t="n">
         <v>0.8707333333333334</v>
       </c>
+      <c r="BG292" t="n">
+        <v>0.9469666666666665</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
@@ -41029,6 +41449,9 @@
       <c r="BF293" t="n">
         <v>0.9634200000000002</v>
       </c>
+      <c r="BG293" t="n">
+        <v>0.8725666666666666</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
@@ -41120,6 +41543,9 @@
       <c r="BF294" t="n">
         <v>0.8696111111111111</v>
       </c>
+      <c r="BG294" t="n">
+        <v>0.9071000000000001</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
@@ -41211,6 +41637,9 @@
       <c r="BF295" t="n">
         <v>0.96451</v>
       </c>
+      <c r="BG295" t="n">
+        <v>0.9326</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
@@ -41302,6 +41731,9 @@
       <c r="BF296" t="n">
         <v>0.9722777777777778</v>
       </c>
+      <c r="BG296" t="n">
+        <v>0.9411333333333335</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
@@ -41393,6 +41825,9 @@
       <c r="BF297" t="n">
         <v>0.9664363636363635</v>
       </c>
+      <c r="BG297" t="n">
+        <v>0.8701181818181817</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
@@ -41484,6 +41919,9 @@
       <c r="BF298" t="n">
         <v>0.8846636363636364</v>
       </c>
+      <c r="BG298" t="n">
+        <v>0.8770222222222223</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
@@ -41575,6 +42013,9 @@
       <c r="BF299" t="n">
         <v>0.8937333333333332</v>
       </c>
+      <c r="BG299" t="n">
+        <v>0.8660099999999999</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
@@ -41666,6 +42107,9 @@
       <c r="BF300" t="n">
         <v>0.8772200000000001</v>
       </c>
+      <c r="BG300" t="n">
+        <v>0.9540636363636363</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
@@ -41757,6 +42201,9 @@
       <c r="BF301" t="n">
         <v>0.9120428571428573</v>
       </c>
+      <c r="BG301" t="n">
+        <v>0.9176090909090909</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
@@ -41848,6 +42295,9 @@
       <c r="BF302" t="n">
         <v>0.8565375000000001</v>
       </c>
+      <c r="BG302" t="n">
+        <v>0.8618499999999999</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
@@ -41939,6 +42389,9 @@
       <c r="BF303" t="n">
         <v>0.9022461538461537</v>
       </c>
+      <c r="BG303" t="n">
+        <v>0.8685499999999999</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
@@ -42030,6 +42483,9 @@
       <c r="BF304" t="n">
         <v>0.9714500000000001</v>
       </c>
+      <c r="BG304" t="n">
+        <v>0.9268454545454545</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
@@ -42121,6 +42577,9 @@
       <c r="BF305" t="n">
         <v>0.96532</v>
       </c>
+      <c r="BG305" t="n">
+        <v>0.9679181818181818</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
@@ -42212,6 +42671,9 @@
       <c r="BF306" t="n">
         <v>0.8569</v>
       </c>
+      <c r="BG306" t="n">
+        <v>0.9537222222222221</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
@@ -42303,6 +42765,9 @@
       <c r="BF307" t="n">
         <v>0.9703999999999999</v>
       </c>
+      <c r="BG307" t="n">
+        <v>0.9499299999999999</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
@@ -42394,6 +42859,9 @@
       <c r="BF308" t="n">
         <v>0.9734714285714287</v>
       </c>
+      <c r="BG308" t="n">
+        <v>0.8201363636363636</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
@@ -42485,6 +42953,9 @@
       <c r="BF309" t="n">
         <v>0.9657285714285714</v>
       </c>
+      <c r="BG309" t="n">
+        <v>0.9557909090909091</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
@@ -42576,6 +43047,9 @@
       <c r="BF310" t="n">
         <v>0.9751124999999999</v>
       </c>
+      <c r="BG310" t="n">
+        <v>0.9102428571428572</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
@@ -42666,6 +43140,9 @@
       </c>
       <c r="BF311" t="n">
         <v>0.8713888888888888</v>
+      </c>
+      <c r="BG311" t="n">
+        <v>0.8132076923076922</v>
       </c>
     </row>
     <row r="312">
@@ -47317,6 +47794,9 @@
       <c r="BF363" t="n">
         <v>0.1647</v>
       </c>
+      <c r="BG363" t="n">
+        <v>0.9342</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
@@ -47408,6 +47888,9 @@
       <c r="BF364" t="n">
         <v>0.1839</v>
       </c>
+      <c r="BG364" t="n">
+        <v>0.9377</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
@@ -47499,6 +47982,9 @@
       <c r="BF365" t="n">
         <v>0.1642</v>
       </c>
+      <c r="BG365" t="n">
+        <v>0.9243</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
@@ -47590,6 +48076,9 @@
       <c r="BF366" t="n">
         <v>0.2275</v>
       </c>
+      <c r="BG366" t="n">
+        <v>0.9657</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
@@ -47681,6 +48170,9 @@
       <c r="BF367" t="n">
         <v>0.197</v>
       </c>
+      <c r="BG367" t="n">
+        <v>0.967</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
@@ -47772,6 +48264,9 @@
       <c r="BF368" t="n">
         <v>0.1667</v>
       </c>
+      <c r="BG368" t="n">
+        <v>0.9526</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
@@ -47863,6 +48358,9 @@
       <c r="BF369" t="n">
         <v>0.147</v>
       </c>
+      <c r="BG369" t="n">
+        <v>0.9386</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
@@ -47954,6 +48452,9 @@
       <c r="BF370" t="n">
         <v>0.1556</v>
       </c>
+      <c r="BG370" t="n">
+        <v>0.9619</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
@@ -48045,6 +48546,9 @@
       <c r="BF371" t="n">
         <v>0.1512</v>
       </c>
+      <c r="BG371" t="n">
+        <v>0.8193</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
@@ -48136,6 +48640,9 @@
       <c r="BF372" t="n">
         <v>0.1573</v>
       </c>
+      <c r="BG372" t="n">
+        <v>0.9499</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
@@ -48227,6 +48734,9 @@
       <c r="BF373" t="n">
         <v>0.1569</v>
       </c>
+      <c r="BG373" t="n">
+        <v>0.9664</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
@@ -48318,6 +48828,9 @@
       <c r="BF374" t="n">
         <v>0.2007</v>
       </c>
+      <c r="BG374" t="n">
+        <v>0.9432</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
@@ -48409,6 +48922,9 @@
       <c r="BF375" t="n">
         <v>0.2004</v>
       </c>
+      <c r="BG375" t="n">
+        <v>0.9361</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
@@ -48500,6 +49016,9 @@
       <c r="BF376" t="n">
         <v>0.1801</v>
       </c>
+      <c r="BG376" t="n">
+        <v>0.9438</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
@@ -48591,6 +49110,9 @@
       <c r="BF377" t="n">
         <v>0.1693</v>
       </c>
+      <c r="BG377" t="n">
+        <v>0.9698</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
@@ -48682,6 +49204,9 @@
       <c r="BF378" t="n">
         <v>0.136</v>
       </c>
+      <c r="BG378" t="n">
+        <v>0.9835</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
@@ -48773,6 +49298,9 @@
       <c r="BF379" t="n">
         <v>0.1731</v>
       </c>
+      <c r="BG379" t="n">
+        <v>0.9843</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
@@ -48864,6 +49392,9 @@
       <c r="BF380" t="n">
         <v>0.1872</v>
       </c>
+      <c r="BG380" t="n">
+        <v>0.9635</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
@@ -48955,6 +49486,9 @@
       <c r="BF381" t="n">
         <v>0.1701</v>
       </c>
+      <c r="BG381" t="n">
+        <v>0.921</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
@@ -49046,6 +49580,9 @@
       <c r="BF382" t="n">
         <v>0.1648</v>
       </c>
+      <c r="BG382" t="n">
+        <v>0.9358</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
@@ -49137,6 +49674,9 @@
       <c r="BF383" t="n">
         <v>0.1707</v>
       </c>
+      <c r="BG383" t="n">
+        <v>0.9507</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
@@ -49228,6 +49768,9 @@
       <c r="BF384" t="n">
         <v>0.1767</v>
       </c>
+      <c r="BG384" t="n">
+        <v>0.8853</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
@@ -49319,6 +49862,9 @@
       <c r="BF385" t="n">
         <v>0.1658</v>
       </c>
+      <c r="BG385" t="n">
+        <v>0.9539</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
@@ -49410,6 +49956,9 @@
       <c r="BF386" t="n">
         <v>0.1493</v>
       </c>
+      <c r="BG386" t="n">
+        <v>0.9796</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
@@ -49501,6 +50050,9 @@
       <c r="BF387" t="n">
         <v>0.1699</v>
       </c>
+      <c r="BG387" t="n">
+        <v>0.9534</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
@@ -49592,6 +50144,9 @@
       <c r="BF388" t="n">
         <v>0.1922</v>
       </c>
+      <c r="BG388" t="n">
+        <v>0.955</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
@@ -49683,6 +50238,9 @@
       <c r="BF389" t="n">
         <v>0.1832</v>
       </c>
+      <c r="BG389" t="n">
+        <v>0.909</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
@@ -49774,6 +50332,9 @@
       <c r="BF390" t="n">
         <v>0.167</v>
       </c>
+      <c r="BG390" t="n">
+        <v>0.9595</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
@@ -49865,6 +50426,9 @@
       <c r="BF391" t="n">
         <v>0.1965</v>
       </c>
+      <c r="BG391" t="n">
+        <v>0.8857</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
@@ -49956,6 +50520,9 @@
       <c r="BF392" t="n">
         <v>0.1735</v>
       </c>
+      <c r="BG392" t="n">
+        <v>0.9575</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
@@ -50047,6 +50614,9 @@
       <c r="BF393" t="n">
         <v>0.1743</v>
       </c>
+      <c r="BG393" t="n">
+        <v>0.9376</v>
+      </c>
 